--- a/src/xlsx/enriched_data.xlsx
+++ b/src/xlsx/enriched_data.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,137 +421,137 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>run_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>current_price</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>market_cap_rank</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>total_volume</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>high_24h</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>low_24h</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price_change_24h</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>price_change_percentage_24h</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>circulating_supply</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>total_supply</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>ath</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>ath_date</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>last_updated</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>is_price_change_outlier</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>market_cap_normalized</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>subcategoria</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>mecanismo_consenso</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>anio_lanzamiento</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>sitio_web</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>caso_de_uso</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>tipo_red</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>nota</t>
         </is>
@@ -572,7 +560,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -591,46 +579,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>86124</v>
+        <v>86238</v>
       </c>
       <c r="F2" t="n">
-        <v>1728665546532</v>
+        <v>1732793991467</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>53399664432</v>
+        <v>43485131868</v>
       </c>
       <c r="I2" t="n">
-        <v>86048</v>
+        <v>86722</v>
       </c>
       <c r="J2" t="n">
-        <v>80631</v>
+        <v>85107</v>
       </c>
       <c r="K2" t="n">
-        <v>5263.94</v>
+        <v>-377.4880582667683</v>
       </c>
       <c r="L2" t="n">
-        <v>6.50996</v>
+        <v>-0.42991</v>
       </c>
       <c r="M2" t="n">
-        <v>20087478</v>
+        <v>20088034</v>
       </c>
       <c r="N2" t="n">
-        <v>20087478</v>
+        <v>20088056</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="P2" s="1" t="n">
         <v>45936.45673611111</v>
       </c>
-      <c r="Q2" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q2" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -677,7 +665,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -696,49 +684,49 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2750.02</v>
+        <v>2748.95</v>
       </c>
       <c r="F3" t="n">
-        <v>335133212622</v>
+        <v>335700394407</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>24352107151</v>
+        <v>16208315503</v>
       </c>
       <c r="I3" t="n">
-        <v>2751.07</v>
+        <v>2786.01</v>
       </c>
       <c r="J3" t="n">
-        <v>2607</v>
+        <v>2716.11</v>
       </c>
       <c r="K3" t="n">
-        <v>144.87</v>
+        <v>-21.36690103358978</v>
       </c>
       <c r="L3" t="n">
-        <v>5.56097</v>
+        <v>-0.75097</v>
       </c>
       <c r="M3" t="n">
-        <v>122067645.9189046</v>
+        <v>122070499.1930826</v>
       </c>
       <c r="N3" t="n">
-        <v>122067645.9189046</v>
+        <v>122070499.1930825</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
       </c>
-      <c r="P3" s="2" t="n">
+      <c r="P3" s="1" t="n">
         <v>45893.47295138889</v>
       </c>
-      <c r="Q3" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q3" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1935827213788247</v>
+        <v>0.1934418838473869</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -782,7 +770,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -801,28 +789,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999874</v>
+        <v>0.999898</v>
       </c>
       <c r="F4" t="n">
-        <v>183365978384</v>
+        <v>183363689877</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>93897835021</v>
+        <v>78958984976</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999816</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999577</v>
+        <v>0.999627</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00023771</v>
+        <v>6.751e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02378</v>
+        <v>0.00721</v>
       </c>
       <c r="M4" t="n">
         <v>183384649781.6938</v>
@@ -833,17 +821,17 @@
       <c r="O4" t="n">
         <v>1.32</v>
       </c>
-      <c r="P4" s="2" t="n">
+      <c r="P4" s="1" t="n">
         <v>43304.66666666666</v>
       </c>
-      <c r="Q4" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q4" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1057571883503426</v>
+        <v>0.1054961616100404</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -887,7 +875,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -906,49 +894,49 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>805.13</v>
+        <v>784.49</v>
       </c>
       <c r="F5" t="n">
-        <v>107128051029</v>
+        <v>104509508003</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1861840599</v>
+        <v>1338733134</v>
       </c>
       <c r="I5" t="n">
-        <v>798.53</v>
+        <v>806.75</v>
       </c>
       <c r="J5" t="n">
-        <v>756.27</v>
+        <v>781.83</v>
       </c>
       <c r="K5" t="n">
-        <v>48.91</v>
+        <v>-20.06454466473849</v>
       </c>
       <c r="L5" t="n">
-        <v>6.46797</v>
+        <v>-2.48689</v>
       </c>
       <c r="M5" t="n">
-        <v>133160157.48</v>
+        <v>133160045.24</v>
       </c>
       <c r="N5" t="n">
-        <v>133160152.56</v>
+        <v>133160043.94</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
       </c>
-      <c r="P5" s="2" t="n">
+      <c r="P5" s="1" t="n">
         <v>45943.02875</v>
       </c>
-      <c r="Q5" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q5" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06163938755785053</v>
+        <v>0.05997274033254849</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -992,7 +980,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1011,28 +999,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="F6" t="n">
-        <v>94051358788</v>
+        <v>98935861541</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>4723578943</v>
+        <v>6013941970</v>
       </c>
       <c r="I6" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="J6" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="K6" t="n">
-        <v>0.112485</v>
+        <v>0.02050936</v>
       </c>
       <c r="L6" t="n">
-        <v>8.11206</v>
+        <v>1.26594</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -1043,17 +1031,17 @@
       <c r="O6" t="n">
         <v>3.65</v>
       </c>
-      <c r="P6" s="2" t="n">
+      <c r="P6" s="1" t="n">
         <v>45855.82005787037</v>
       </c>
-      <c r="Q6" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q6" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05407209233710331</v>
+        <v>0.05675501046824196</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1097,7 +1085,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1116,49 +1104,49 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9999169999999999</v>
+        <v>0.999892</v>
       </c>
       <c r="F7" t="n">
-        <v>74231800122</v>
+        <v>75082614224</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>24254647063</v>
+        <v>20211770616</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9998629999999999</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999598</v>
+        <v>0.999695</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00021933</v>
+        <v>8.51e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02194</v>
+        <v>0.00201</v>
       </c>
       <c r="M7" t="n">
-        <v>74237004006.76027</v>
+        <v>75091582641.99438</v>
       </c>
       <c r="N7" t="n">
-        <v>74254811731.89992</v>
+        <v>75091431783.64163</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
       </c>
-      <c r="P7" s="2" t="n">
+      <c r="P7" s="1" t="n">
         <v>43418.66666666666</v>
       </c>
-      <c r="Q7" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q7" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04260279652387772</v>
+        <v>0.04298425791407672</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1202,7 +1190,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1221,49 +1209,49 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>118.05</v>
+        <v>118.13</v>
       </c>
       <c r="F8" t="n">
-        <v>69255259901</v>
+        <v>69442081520</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>6440764344</v>
+        <v>4713073391</v>
       </c>
       <c r="I8" t="n">
-        <v>118.69</v>
+        <v>119.82</v>
       </c>
       <c r="J8" t="n">
-        <v>108.51</v>
+        <v>115.58</v>
       </c>
       <c r="K8" t="n">
-        <v>9.619999999999999</v>
+        <v>-1.022544647266727</v>
       </c>
       <c r="L8" t="n">
-        <v>8.87163</v>
+        <v>-0.84705</v>
       </c>
       <c r="M8" t="n">
-        <v>587437261.0683235</v>
+        <v>587507395.8954812</v>
       </c>
       <c r="N8" t="n">
-        <v>634453375.546979</v>
+        <v>634531021.326126</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="P8" s="1" t="n">
         <v>45676.13572916666</v>
       </c>
-      <c r="Q8" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q8" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03972294370359374</v>
+        <v>0.03972791385709364</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1307,7 +1295,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1326,49 +1314,49 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.345544</v>
+        <v>0.34165</v>
       </c>
       <c r="F9" t="n">
-        <v>32816706862</v>
+        <v>32442198365</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>440937993</v>
+        <v>605341752</v>
       </c>
       <c r="I9" t="n">
-        <v>0.345088</v>
+        <v>0.349178</v>
       </c>
       <c r="J9" t="n">
-        <v>0.342488</v>
+        <v>0.34041</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00109724</v>
+        <v>-0.002637683000221824</v>
       </c>
       <c r="L9" t="n">
-        <v>0.31855</v>
+        <v>-0.75484</v>
       </c>
       <c r="M9" t="n">
-        <v>94960364758.90469</v>
+        <v>94961729708.24278</v>
       </c>
       <c r="N9" t="n">
-        <v>94960365761.90469</v>
+        <v>94962102587.18929</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
       </c>
-      <c r="P9" s="2" t="n">
+      <c r="P9" s="1" t="n">
         <v>45629.67407407407</v>
       </c>
-      <c r="Q9" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q9" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01863647296763626</v>
+        <v>0.01836745803783905</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1412,7 +1400,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1431,49 +1419,49 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1495.75</v>
+        <v>1518.81</v>
       </c>
       <c r="F10" t="n">
-        <v>25309984948</v>
+        <v>25756147448</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>1431547468</v>
+        <v>1389815932</v>
       </c>
       <c r="I10" t="n">
-        <v>1568.53</v>
+        <v>1562.57</v>
       </c>
       <c r="J10" t="n">
-        <v>1439.75</v>
+        <v>1445.89</v>
       </c>
       <c r="K10" t="n">
-        <v>53.35</v>
+        <v>56.04</v>
       </c>
       <c r="L10" t="n">
-        <v>3.69892</v>
+        <v>3.7356</v>
       </c>
       <c r="M10" t="n">
-        <v>16942351.7280448</v>
+        <v>16945106.4155448</v>
       </c>
       <c r="N10" t="n">
-        <v>16944709.5405448</v>
+        <v>16946950.1655448</v>
       </c>
       <c r="O10" t="n">
         <v>3191.93</v>
       </c>
-      <c r="P10" s="2" t="n">
+      <c r="P10" s="1" t="n">
         <v>42671.66666666666</v>
       </c>
-      <c r="Q10" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q10" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R10" t="b">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01429244010241479</v>
+        <v>0.01450752435589808</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1517,7 +1505,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1536,49 +1524,49 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.04</v>
+        <v>1.039</v>
       </c>
       <c r="F11" t="n">
-        <v>23664863580</v>
+        <v>23858934286</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>16837398</v>
+        <v>83847558</v>
       </c>
       <c r="I11" t="n">
-        <v>1.021</v>
+        <v>1.043</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>1.006</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.0261228</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.57897</v>
       </c>
       <c r="M11" t="n">
-        <v>22764228455.528</v>
+        <v>22966221270.418</v>
       </c>
       <c r="N11" t="n">
-        <v>22764228455.528</v>
+        <v>22966221270.418</v>
       </c>
       <c r="O11" t="n">
         <v>1.061</v>
       </c>
-      <c r="P11" s="2" t="n">
+      <c r="P11" s="1" t="n">
         <v>46237.59675925926</v>
       </c>
-      <c r="Q11" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q11" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R11" t="b">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01334043183945489</v>
+        <v>0.01341224149360253</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
@@ -1592,7 +1580,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1611,28 +1599,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>93.40000000000001</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>20757345051</v>
+        <v>21655414643</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1256686450</v>
+        <v>1249913907</v>
       </c>
       <c r="I12" t="n">
-        <v>95.98999999999999</v>
+        <v>96.87</v>
       </c>
       <c r="J12" t="n">
-        <v>91.90000000000001</v>
+        <v>92.19</v>
       </c>
       <c r="K12" t="n">
-        <v>1.53</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.66271</v>
+        <v>4.26103</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1641,19 +1629,19 @@
         <v>955307079.4341414</v>
       </c>
       <c r="O12" t="n">
-        <v>95.98999999999999</v>
-      </c>
-      <c r="P12" s="2" t="n">
-        <v>46286.47291666667</v>
-      </c>
-      <c r="Q12" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>97.72</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>46287.91296296296</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R12" t="b">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01165789235139143</v>
+        <v>0.01214012439571919</v>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
@@ -1667,7 +1655,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1686,49 +1674,49 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.097469</v>
+        <v>0.100125</v>
       </c>
       <c r="F13" t="n">
-        <v>15181065525</v>
+        <v>15635492125</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>1882978328</v>
+        <v>2382661626</v>
       </c>
       <c r="I13" t="n">
-        <v>0.095163</v>
+        <v>0.105575</v>
       </c>
       <c r="J13" t="n">
-        <v>0.085616</v>
+        <v>0.097356</v>
       </c>
       <c r="K13" t="n">
-        <v>0.01187787</v>
+        <v>0.00082386</v>
       </c>
       <c r="L13" t="n">
-        <v>13.87742</v>
+        <v>0.82324</v>
       </c>
       <c r="M13" t="n">
-        <v>156008016383.7053</v>
+        <v>156025536383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>156008916383.7052</v>
+        <v>171737883126.579</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
       </c>
-      <c r="P13" s="2" t="n">
+      <c r="P13" s="1" t="n">
         <v>44323.88082175926</v>
       </c>
-      <c r="Q13" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q13" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.008430978952424452</v>
+        <v>0.008664754258943556</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1772,7 +1760,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1791,49 +1779,49 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>572.01</v>
+        <v>567.3</v>
       </c>
       <c r="F14" t="n">
-        <v>10738217262</v>
+        <v>10671971138</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>235272967</v>
+        <v>163415960</v>
       </c>
       <c r="I14" t="n">
-        <v>630.51</v>
+        <v>601.01</v>
       </c>
       <c r="J14" t="n">
-        <v>540.97</v>
+        <v>561.65</v>
       </c>
       <c r="K14" t="n">
-        <v>29.3</v>
+        <v>-29.0335298218157</v>
       </c>
       <c r="L14" t="n">
-        <v>5.39931</v>
+        <v>-4.86632</v>
       </c>
       <c r="M14" t="n">
-        <v>18807603.12217533</v>
+        <v>18808120.908502</v>
       </c>
       <c r="N14" t="n">
-        <v>18807625.32201612</v>
+        <v>18808149.70786505</v>
       </c>
       <c r="O14" t="n">
         <v>797.73</v>
       </c>
-      <c r="P14" s="2" t="n">
+      <c r="P14" s="1" t="n">
         <v>46036.48202546296</v>
       </c>
-      <c r="Q14" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q14" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.005859966053482513</v>
+        <v>0.005799256811110969</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1877,7 +1865,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1896,49 +1884,49 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>86.64</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>10291846518</v>
+        <v>10304856260</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>215315698</v>
+        <v>148065627</v>
       </c>
       <c r="I15" t="n">
-        <v>86.64</v>
+        <v>87.28</v>
       </c>
       <c r="J15" t="n">
-        <v>82.23999999999999</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>4.33</v>
+        <v>-0.4387106662780695</v>
       </c>
       <c r="L15" t="n">
-        <v>5.26004</v>
+        <v>-0.49605</v>
       </c>
       <c r="M15" t="n">
-        <v>118887984</v>
+        <v>118852171</v>
       </c>
       <c r="N15" t="n">
-        <v>293457483</v>
+        <v>293421670</v>
       </c>
       <c r="O15" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="P15" s="2" t="n">
-        <v>46286.63425925926</v>
-      </c>
-      <c r="Q15" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>87.91</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>46286.85358796296</v>
+      </c>
+      <c r="Q15" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.005601657672777343</v>
+        <v>0.005587317192294894</v>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
@@ -1952,367 +1940,367 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>chainlink</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.01414863</v>
+        <v>12.91</v>
       </c>
       <c r="F16" t="n">
-        <v>10032920141</v>
+        <v>9671530693</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>29041461</v>
+        <v>581165005</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01427443</v>
+        <v>13.26</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01325824</v>
+        <v>12.78</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00097359</v>
+        <v>-0.2186754109027937</v>
       </c>
       <c r="L16" t="n">
-        <v>7.38968</v>
+        <v>-1.64853</v>
       </c>
       <c r="M16" t="n">
-        <v>709239296767.5244</v>
+        <v>748099970.424884</v>
       </c>
       <c r="N16" t="n">
-        <v>1142408526965.963</v>
+        <v>1000000000</v>
       </c>
       <c r="O16" t="n">
-        <v>0.01946402</v>
-      </c>
-      <c r="P16" s="2" t="n">
-        <v>46259.82847222222</v>
-      </c>
-      <c r="Q16" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>52.7</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>44325.67635416667</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.005451820672786307</v>
-      </c>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
+        <v>0.005221691097303301</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Oráculo</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Infraestructura Web3</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>N/A (token ERC-20, red de oráculos)</t>
+        </is>
+      </c>
+      <c r="W16" t="n">
+        <v>2017</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>chain.link</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Conexión de datos externos a contratos inteligentes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Token ERC-20 sobre Ethereum</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Provee datos del mundo real (oráculos) a contratos inteligentes.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>USDS</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>13.03</v>
+        <v>0.999922</v>
       </c>
       <c r="F17" t="n">
-        <v>9741654136</v>
+        <v>9592786193</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>695570017</v>
+        <v>247011578</v>
       </c>
       <c r="I17" t="n">
-        <v>13.16</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>12.32</v>
+        <v>0.999729</v>
       </c>
       <c r="K17" t="n">
-        <v>0.717199</v>
+        <v>-5.5729221229095e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>5.82362</v>
+        <v>-0.00507</v>
       </c>
       <c r="M17" t="n">
-        <v>748099970.424884</v>
+        <v>9593648553.437454</v>
       </c>
       <c r="N17" t="n">
-        <v>1000000000</v>
+        <v>9593648553.437454</v>
       </c>
       <c r="O17" t="n">
-        <v>52.7</v>
-      </c>
-      <c r="P17" s="2" t="n">
-        <v>44325.67635416667</v>
-      </c>
-      <c r="Q17" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>1.057</v>
+      </c>
+      <c r="P17" s="1" t="n">
+        <v>45593.90336805556</v>
+      </c>
+      <c r="Q17" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.005283269191495647</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Oráculo</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Infraestructura Web3</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>N/A (token ERC-20, red de oráculos)</t>
-        </is>
-      </c>
-      <c r="W17" t="n">
-        <v>2017</v>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>chain.link</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Conexión de datos externos a contratos inteligentes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Token ERC-20 sobre Ethereum</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Provee datos del mundo real (oráculos) a contratos inteligentes.</t>
-        </is>
-      </c>
+        <v>0.005176230996626415</v>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>cardano</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>ada</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>USDS</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0.251416</v>
       </c>
       <c r="F18" t="n">
-        <v>9595586523</v>
+        <v>9443905073</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>196078899</v>
+        <v>878661987</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0.253817</v>
       </c>
       <c r="J18" t="n">
-        <v>0.999754</v>
+        <v>0.240769</v>
       </c>
       <c r="K18" t="n">
-        <v>0.00015973</v>
+        <v>0.00659619</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01598</v>
+        <v>2.72814</v>
       </c>
       <c r="M18" t="n">
-        <v>9594149705.433596</v>
+        <v>37529061988.53558</v>
       </c>
       <c r="N18" t="n">
-        <v>9594892921.253408</v>
+        <v>45000000000</v>
       </c>
       <c r="O18" t="n">
-        <v>1.057</v>
-      </c>
-      <c r="P18" s="2" t="n">
-        <v>45593.90336805556</v>
-      </c>
-      <c r="Q18" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>3.09</v>
+      </c>
+      <c r="P18" s="1" t="n">
+        <v>44440.91678240741</v>
+      </c>
+      <c r="Q18" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R18" t="b">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.005198741947955018</v>
-      </c>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
+        <v>0.005090280222869678</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Plataforma de contratos inteligentes</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Layer 1</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Proof of Stake (Ouroboros)</t>
+        </is>
+      </c>
+      <c r="W18" t="n">
+        <v>2017</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>cardano.org</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Contratos inteligentes con enfoque académico</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Layer 1)</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Desarrollada con un enfoque académico y revisión por pares en su investigación.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>cardano</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ada</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.245391</v>
+        <v>0.01309167</v>
       </c>
       <c r="F19" t="n">
-        <v>9197046672</v>
+        <v>9284605249</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>826630614</v>
+        <v>24775479</v>
       </c>
       <c r="I19" t="n">
-        <v>0.248479</v>
+        <v>0.01400767</v>
       </c>
       <c r="J19" t="n">
-        <v>0.22404</v>
+        <v>0.0130726</v>
       </c>
       <c r="K19" t="n">
-        <v>0.02123083</v>
+        <v>-0.000864517740068033</v>
       </c>
       <c r="L19" t="n">
-        <v>9.471270000000001</v>
+        <v>-6.27118</v>
       </c>
       <c r="M19" t="n">
-        <v>37522923322.16203</v>
+        <v>709239749032.6418</v>
       </c>
       <c r="N19" t="n">
-        <v>45000000000</v>
+        <v>1142408526965.963</v>
       </c>
       <c r="O19" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="P19" s="2" t="n">
-        <v>44440.91678240741</v>
-      </c>
-      <c r="Q19" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>0.01946402</v>
+      </c>
+      <c r="P19" s="1" t="n">
+        <v>46259.82847222222</v>
+      </c>
+      <c r="Q19" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R19" t="b">
         <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>0.004968112622574567</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Plataforma de contratos inteligentes</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Layer 1</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Proof of Stake (Ouroboros)</t>
-        </is>
-      </c>
-      <c r="W19" t="n">
-        <v>2017</v>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>cardano.org</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Contratos inteligentes con enfoque académico</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Layer 1)</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Desarrollada con un enfoque académico y revisión por pares en su investigación.</t>
-        </is>
-      </c>
+        <v>0.004998314612105115</v>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2331,28 +2319,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8.92</v>
+        <v>8.98</v>
       </c>
       <c r="F20" t="n">
-        <v>8205789399</v>
+        <v>8260445947</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>45234</v>
+        <v>127098</v>
       </c>
       <c r="I20" t="n">
-        <v>8.99</v>
+        <v>9</v>
       </c>
       <c r="J20" t="n">
         <v>8.880000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.01354870721141488</v>
+        <v>0.02568804</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.15166</v>
+        <v>0.28873</v>
       </c>
       <c r="M20" t="n">
         <v>919857851.9</v>
@@ -2363,17 +2351,17 @@
       <c r="O20" t="n">
         <v>10.61</v>
       </c>
-      <c r="P20" s="2" t="n">
+      <c r="P20" s="1" t="n">
         <v>46146.39930555555</v>
       </c>
-      <c r="Q20" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q20" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.004394486182014535</v>
+        <v>0.004407055730810693</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2417,7 +2405,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2436,31 +2424,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.210781</v>
+        <v>0.215138</v>
       </c>
       <c r="F21" t="n">
-        <v>7340660289</v>
+        <v>7524022577</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>385358090</v>
+        <v>382146995</v>
       </c>
       <c r="I21" t="n">
-        <v>0.212907</v>
+        <v>0.219762</v>
       </c>
       <c r="J21" t="n">
-        <v>0.193655</v>
+        <v>0.209091</v>
       </c>
       <c r="K21" t="n">
-        <v>0.01715873</v>
+        <v>-0.001449679238016699</v>
       </c>
       <c r="L21" t="n">
-        <v>8.861940000000001</v>
+        <v>-0.76252</v>
       </c>
       <c r="M21" t="n">
-        <v>34882253227.52757</v>
+        <v>34931895481.5965</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70148</v>
@@ -2468,17 +2456,17 @@
       <c r="O21" t="n">
         <v>0.875563</v>
       </c>
-      <c r="P21" s="2" t="n">
+      <c r="P21" s="1" t="n">
         <v>43102.66666666666</v>
       </c>
-      <c r="Q21" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q21" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.003893848309777537</v>
+        <v>0.003981910094721682</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2522,217 +2510,217 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>uniswap</t>
+          <t>bitcoin-cash</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>uni</t>
+          <t>bch</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Uniswap</t>
+          <t>Bitcoin Cash</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>8.890000000000001</v>
+        <v>340.47</v>
       </c>
       <c r="F22" t="n">
-        <v>5515671145</v>
+        <v>6849206386</v>
       </c>
       <c r="G22" t="n">
         <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>1170568252</v>
+        <v>1186844804</v>
       </c>
       <c r="I22" t="n">
-        <v>9.25</v>
+        <v>346.9</v>
       </c>
       <c r="J22" t="n">
-        <v>8.529999999999999</v>
+        <v>261.8</v>
       </c>
       <c r="K22" t="n">
-        <v>0.21966</v>
+        <v>72.33</v>
       </c>
       <c r="L22" t="n">
-        <v>2.53223</v>
+        <v>26.79209</v>
       </c>
       <c r="M22" t="n">
-        <v>620798422.6104751</v>
+        <v>20092971.77165077</v>
       </c>
       <c r="N22" t="n">
-        <v>888046418.9163101</v>
+        <v>20092968.64665077</v>
       </c>
       <c r="O22" t="n">
-        <v>44.92</v>
-      </c>
-      <c r="P22" s="2" t="n">
-        <v>44318.89240740741</v>
-      </c>
-      <c r="Q22" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>3785.82</v>
+      </c>
+      <c r="P22" s="1" t="n">
+        <v>43088.66666666666</v>
+      </c>
+      <c r="Q22" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0.002837753131211902</v>
+        <v>0.003592330987847522</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>DeFi</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Exchange descentralizado</t>
+          <t>Fork de Bitcoin</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>N/A (token ERC-20)</t>
+          <t>Proof of Work</t>
         </is>
       </c>
       <c r="W22" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>uniswap.org</t>
+          <t>bitcoincash.org</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>Intercambio descentralizado de tokens</t>
+          <t>Pagos cotidianos de bajo costo</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>Token ERC-20 sobre Ethereum</t>
+          <t>Blockchain propia (fork de Bitcoin)</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Uno de los mayores exchanges descentralizados (DEX) del ecosistema Ethereum.</t>
+          <t>Surgió de una bifurcación de Bitcoin en 2017 para aumentar el tamaño de bloque.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>bitcoin-cash</t>
+          <t>uniswap</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>bch</t>
+          <t>uni</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Bitcoin Cash</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>264.35</v>
+        <v>9.44</v>
       </c>
       <c r="F23" t="n">
-        <v>5307183344</v>
+        <v>5869006543</v>
       </c>
       <c r="G23" t="n">
         <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>296383774</v>
+        <v>1593380024</v>
       </c>
       <c r="I23" t="n">
-        <v>271.86</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>247.88</v>
+        <v>8.68</v>
       </c>
       <c r="K23" t="n">
-        <v>16.82</v>
+        <v>0.672496</v>
       </c>
       <c r="L23" t="n">
-        <v>6.79536</v>
+        <v>7.57425</v>
       </c>
       <c r="M23" t="n">
-        <v>20092153.02165077</v>
+        <v>620708422.6104751</v>
       </c>
       <c r="N23" t="n">
-        <v>20092453.02165077</v>
+        <v>887956418.9163101</v>
       </c>
       <c r="O23" t="n">
-        <v>3785.82</v>
-      </c>
-      <c r="P23" s="2" t="n">
-        <v>43088.66666666666</v>
-      </c>
-      <c r="Q23" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>44.92</v>
+      </c>
+      <c r="P23" s="1" t="n">
+        <v>44318.89240740741</v>
+      </c>
+      <c r="Q23" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R23" t="b">
         <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>0.002717104215491091</v>
+        <v>0.00302645040512432</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>DeFi</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>Fork de Bitcoin</t>
+          <t>Exchange descentralizado</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Proof of Work</t>
+          <t>N/A (token ERC-20)</t>
         </is>
       </c>
       <c r="W23" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>bitcoincash.org</t>
+          <t>uniswap.org</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>Pagos cotidianos de bajo costo</t>
+          <t>Intercambio descentralizado de tokens</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>Blockchain propia (fork de Bitcoin)</t>
+          <t>Token ERC-20 sobre Ethereum</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Surgió de una bifurcación de Bitcoin en 2017 para aumentar el tamaño de bloque.</t>
+          <t>Uno de los mayores exchanges descentralizados (DEX) del ecosistema Ethereum.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2751,49 +2739,49 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4.04</v>
+        <v>4.33</v>
       </c>
       <c r="F24" t="n">
-        <v>5280599037</v>
+        <v>5662458523</v>
       </c>
       <c r="G24" t="n">
         <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>1859521787</v>
+        <v>1682767802</v>
       </c>
       <c r="I24" t="n">
-        <v>4.44</v>
+        <v>4.65</v>
       </c>
       <c r="J24" t="n">
-        <v>3.87</v>
+        <v>4.12</v>
       </c>
       <c r="K24" t="n">
-        <v>0.255399</v>
+        <v>0.193685</v>
       </c>
       <c r="L24" t="n">
-        <v>6.74642</v>
+        <v>4.56812</v>
       </c>
       <c r="M24" t="n">
-        <v>1306919679</v>
+        <v>1307027733</v>
       </c>
       <c r="N24" t="n">
-        <v>1306919694</v>
+        <v>1307027728</v>
       </c>
       <c r="O24" t="n">
         <v>20.44</v>
       </c>
-      <c r="P24" s="2" t="n">
+      <c r="P24" s="1" t="n">
         <v>44577.59010416667</v>
       </c>
-      <c r="Q24" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q24" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.002701720256336861</v>
+        <v>0.002907207870295712</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2837,7 +2825,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2856,49 +2844,49 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>11.2</v>
+        <v>11.08</v>
       </c>
       <c r="F25" t="n">
-        <v>4956319449</v>
+        <v>4909205600</v>
       </c>
       <c r="G25" t="n">
         <v>24</v>
       </c>
       <c r="H25" t="n">
-        <v>1232465817</v>
+        <v>633782095</v>
       </c>
       <c r="I25" t="n">
-        <v>11.78</v>
+        <v>11.35</v>
       </c>
       <c r="J25" t="n">
-        <v>10.92</v>
+        <v>10.53</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.05499586640539</v>
+        <v>-0.2567119165716321</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.4887</v>
+        <v>-2.2405</v>
       </c>
       <c r="M25" t="n">
-        <v>442892841.602698</v>
+        <v>442927404.050358</v>
       </c>
       <c r="N25" t="n">
-        <v>469561413.4440742</v>
+        <v>469596104.050358</v>
       </c>
       <c r="O25" t="n">
         <v>144.96</v>
       </c>
-      <c r="P25" s="2" t="n">
+      <c r="P25" s="1" t="n">
         <v>44521.26314814815</v>
       </c>
-      <c r="Q25" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q25" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.002514064285604111</v>
+        <v>0.002472346340731893</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2942,7 +2930,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2961,49 +2949,49 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0.999824</v>
       </c>
       <c r="F26" t="n">
-        <v>4883273448</v>
+        <v>4898876763</v>
       </c>
       <c r="G26" t="n">
         <v>25</v>
       </c>
       <c r="H26" t="n">
-        <v>43152985</v>
+        <v>175765816</v>
       </c>
       <c r="I26" t="n">
-        <v>0.999964</v>
+        <v>0.999931</v>
       </c>
       <c r="J26" t="n">
-        <v>0.999695</v>
+        <v>0.998631</v>
       </c>
       <c r="K26" t="n">
-        <v>0.00034911</v>
+        <v>2.905e-05</v>
       </c>
       <c r="L26" t="n">
-        <v>0.03492</v>
+        <v>0.00317</v>
       </c>
       <c r="M26" t="n">
-        <v>4882671688.190312</v>
+        <v>4899806603.894896</v>
       </c>
       <c r="N26" t="n">
-        <v>4883552134.801312</v>
+        <v>4897763014.332197</v>
       </c>
       <c r="O26" t="n">
         <v>1.034</v>
       </c>
-      <c r="P26" s="2" t="n">
+      <c r="P26" s="1" t="n">
         <v>46000.38208333333</v>
       </c>
-      <c r="Q26" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q26" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R26" t="b">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.002471793607050638</v>
+        <v>0.002466383384971235</v>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
@@ -3017,7 +3005,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3036,49 +3024,49 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>62.5</v>
+        <v>62.62</v>
       </c>
       <c r="F27" t="n">
-        <v>4854766688</v>
+        <v>4864663052</v>
       </c>
       <c r="G27" t="n">
         <v>26</v>
       </c>
       <c r="H27" t="n">
-        <v>555253226</v>
+        <v>500958406</v>
       </c>
       <c r="I27" t="n">
-        <v>63.74</v>
+        <v>63.44</v>
       </c>
       <c r="J27" t="n">
-        <v>57.44</v>
+        <v>59.82</v>
       </c>
       <c r="K27" t="n">
-        <v>5.09</v>
+        <v>0.593382</v>
       </c>
       <c r="L27" t="n">
-        <v>8.866899999999999</v>
+        <v>0.98769</v>
       </c>
       <c r="M27" t="n">
-        <v>77632004.46059512</v>
+        <v>77636779.47670597</v>
       </c>
       <c r="N27" t="n">
-        <v>77635191.97028677</v>
+        <v>77639516.98369066</v>
       </c>
       <c r="O27" t="n">
         <v>410.26</v>
       </c>
-      <c r="P27" s="2" t="n">
+      <c r="P27" s="1" t="n">
         <v>44325.80077546297</v>
       </c>
-      <c r="Q27" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q27" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.002455297151774997</v>
+        <v>0.002446631418210511</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3122,187 +3110,187 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>canton-network</t>
+          <t>dai</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>dai</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Canton</t>
+          <t>Dai</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.116617</v>
+        <v>0.999915</v>
       </c>
       <c r="F28" t="n">
-        <v>4621327246</v>
+        <v>4575720883</v>
       </c>
       <c r="G28" t="n">
         <v>27</v>
       </c>
       <c r="H28" t="n">
-        <v>17034306</v>
+        <v>235945685</v>
       </c>
       <c r="I28" t="n">
-        <v>0.118847</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>0.106795</v>
+        <v>0.998871</v>
       </c>
       <c r="K28" t="n">
-        <v>0.009704809999999999</v>
+        <v>3.684e-05</v>
       </c>
       <c r="L28" t="n">
-        <v>9.077400000000001</v>
+        <v>0.00452</v>
       </c>
       <c r="M28" t="n">
-        <v>39650914855.51295</v>
+        <v>4575753580.16673</v>
       </c>
       <c r="N28" t="n">
-        <v>39650914855.51295</v>
+        <v>4592088883.495623</v>
       </c>
       <c r="O28" t="n">
-        <v>0.194152</v>
-      </c>
-      <c r="P28" s="2" t="n">
-        <v>46056.00148148148</v>
-      </c>
-      <c r="Q28" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>1.22</v>
+      </c>
+      <c r="P28" s="1" t="n">
+        <v>43902.79363425926</v>
+      </c>
+      <c r="Q28" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.002320209077419168</v>
-      </c>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
+        <v>0.002279821798585806</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stablecoin</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Colateralizada por cripto</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>N/A (token, colateral cripto)</t>
+        </is>
+      </c>
+      <c r="W28" t="n">
+        <v>2017</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>makerdao.com</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Estabilidad de valor descentralizada</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>Token ERC-20 sobre Ethereum</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>Stablecoin descentralizada, generada mediante colateral cripto sobrecolateralizado.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>dai</t>
+          <t>canton-network</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>dai</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Dai</t>
+          <t>Canton</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>0.114167</v>
       </c>
       <c r="F29" t="n">
-        <v>4587287767</v>
+        <v>4528241072</v>
       </c>
       <c r="G29" t="n">
         <v>28</v>
       </c>
       <c r="H29" t="n">
-        <v>332234991</v>
+        <v>17809362</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0.119967</v>
       </c>
       <c r="J29" t="n">
-        <v>0.999663</v>
+        <v>0.111864</v>
       </c>
       <c r="K29" t="n">
-        <v>4.657e-05</v>
+        <v>-0.001610986985493751</v>
       </c>
       <c r="L29" t="n">
-        <v>0.00466</v>
+        <v>-1.38068</v>
       </c>
       <c r="M29" t="n">
-        <v>4587555760.165159</v>
+        <v>39662232770.86527</v>
       </c>
       <c r="N29" t="n">
-        <v>4589397370.72186</v>
+        <v>39662232770.86527</v>
       </c>
       <c r="O29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P29" s="2" t="n">
-        <v>43902.79363425926</v>
-      </c>
-      <c r="Q29" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>0.194152</v>
+      </c>
+      <c r="P29" s="1" t="n">
+        <v>46056.00148148148</v>
+      </c>
+      <c r="Q29" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R29" t="b">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.002300510916599431</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Stablecoin</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Colateralizada por cripto</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>N/A (token, colateral cripto)</t>
-        </is>
-      </c>
-      <c r="W29" t="n">
-        <v>2017</v>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>makerdao.com</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>Estabilidad de valor descentralizada</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>Token ERC-20 sobre Ethereum</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>Stablecoin descentralizada, generada mediante colateral cripto sobrecolateralizado.</t>
-        </is>
-      </c>
+        <v>0.002252411160532615</v>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3321,49 +3309,49 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.999808</v>
+        <v>0.999344</v>
       </c>
       <c r="F30" t="n">
-        <v>4356161972</v>
+        <v>4392803585</v>
       </c>
       <c r="G30" t="n">
         <v>29</v>
       </c>
       <c r="H30" t="n">
-        <v>1388534334</v>
+        <v>1317635380</v>
       </c>
       <c r="I30" t="n">
-        <v>0.999771</v>
+        <v>0.999651</v>
       </c>
       <c r="J30" t="n">
-        <v>0.99937</v>
+        <v>0.999131</v>
       </c>
       <c r="K30" t="n">
-        <v>0.00033205</v>
+        <v>-0.000230891299258684</v>
       </c>
       <c r="L30" t="n">
-        <v>0.03322</v>
+        <v>-0.0249</v>
       </c>
       <c r="M30" t="n">
-        <v>4356796476.280436</v>
+        <v>4395796475.062263</v>
       </c>
       <c r="N30" t="n">
-        <v>4356796476.280436</v>
+        <v>4395796475.062263</v>
       </c>
       <c r="O30" t="n">
         <v>1.048</v>
       </c>
-      <c r="P30" s="2" t="n">
+      <c r="P30" s="1" t="n">
         <v>46212.42696759259</v>
       </c>
-      <c r="Q30" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q30" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R30" t="b">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.002166761716751232</v>
+        <v>0.002174221549900198</v>
       </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
@@ -3377,143 +3365,173 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>sui</t>
+          <t>hedera-hashgraph</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>sui</t>
+          <t>hbar</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sui</t>
+          <t>Hedera</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.022</v>
+        <v>0.099762</v>
       </c>
       <c r="F31" t="n">
-        <v>4178422617</v>
+        <v>4381497354</v>
       </c>
       <c r="G31" t="n">
         <v>30</v>
       </c>
       <c r="H31" t="n">
-        <v>2166507655</v>
+        <v>253199661</v>
       </c>
       <c r="I31" t="n">
-        <v>1.054</v>
+        <v>0.100667</v>
       </c>
       <c r="J31" t="n">
-        <v>0.843444</v>
+        <v>0.091183</v>
       </c>
       <c r="K31" t="n">
-        <v>0.181534</v>
+        <v>0.007907839999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>21.60945</v>
+        <v>8.63801</v>
       </c>
       <c r="M31" t="n">
-        <v>4096537146.540959</v>
+        <v>43831706400.35046</v>
       </c>
       <c r="N31" t="n">
-        <v>10000000000</v>
+        <v>50000000000</v>
       </c>
       <c r="O31" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="P31" s="2" t="n">
-        <v>45661.62243055556</v>
-      </c>
-      <c r="Q31" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>0.569229</v>
+      </c>
+      <c r="P31" s="1" t="n">
+        <v>44454.11143518519</v>
+      </c>
+      <c r="Q31" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R31" t="b">
         <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>0.002063906488009737</v>
-      </c>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
+        <v>0.002167694333402079</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Infraestructura empresarial</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>DLT</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Hashgraph (aBFT)</t>
+        </is>
+      </c>
+      <c r="W31" t="n">
+        <v>2019</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>hedera.com</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Aplicaciones empresariales y tokenización</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>Red propia (hashgraph, no blockchain tradicional)</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Gobernada por un consejo de grandes empresas globales.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>the-open-network</t>
+          <t>sui</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>gram</t>
+          <t>sui</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Gram (prev. Toncoin)</t>
+          <t>Sui</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1.43</v>
+        <v>1.011</v>
       </c>
       <c r="F32" t="n">
-        <v>4028994265</v>
+        <v>4147213010</v>
       </c>
       <c r="G32" t="n">
         <v>31</v>
       </c>
       <c r="H32" t="n">
-        <v>60620535</v>
+        <v>1118620738</v>
       </c>
       <c r="I32" t="n">
-        <v>1.44</v>
+        <v>1.079</v>
       </c>
       <c r="J32" t="n">
-        <v>1.37</v>
+        <v>0.988259</v>
       </c>
       <c r="K32" t="n">
-        <v>0.061308</v>
+        <v>-0.008432258001915161</v>
       </c>
       <c r="L32" t="n">
-        <v>4.46488</v>
+        <v>-0.78915</v>
       </c>
       <c r="M32" t="n">
-        <v>2810474514.130084</v>
+        <v>4096537146.540959</v>
       </c>
       <c r="N32" t="n">
-        <v>5253006691.507872</v>
+        <v>10000000000</v>
       </c>
       <c r="O32" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="P32" s="2" t="n">
-        <v>45457.69225694444</v>
-      </c>
-      <c r="Q32" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>5.35</v>
+      </c>
+      <c r="P32" s="1" t="n">
+        <v>45661.62243055556</v>
+      </c>
+      <c r="Q32" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R32" t="b">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.001977434432761057</v>
+        <v>0.002032439301428316</v>
       </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
@@ -3527,112 +3545,82 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>hedera-hashgraph</t>
+          <t>the-open-network</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>hbar</t>
+          <t>gram</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Hedera</t>
+          <t>Gram (prev. Toncoin)</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.091629</v>
+        <v>1.45</v>
       </c>
       <c r="F33" t="n">
-        <v>4010077306</v>
+        <v>4086969910</v>
       </c>
       <c r="G33" t="n">
         <v>32</v>
       </c>
       <c r="H33" t="n">
-        <v>222101860</v>
+        <v>52837490</v>
       </c>
       <c r="I33" t="n">
-        <v>0.092859</v>
+        <v>1.47</v>
       </c>
       <c r="J33" t="n">
-        <v>0.084797</v>
+        <v>1.41</v>
       </c>
       <c r="K33" t="n">
-        <v>0.00531559</v>
+        <v>0.00408983</v>
       </c>
       <c r="L33" t="n">
-        <v>6.15846</v>
+        <v>0.24221</v>
       </c>
       <c r="M33" t="n">
-        <v>43831706400.74403</v>
+        <v>2810942525.236758</v>
       </c>
       <c r="N33" t="n">
-        <v>50000000000</v>
+        <v>5253728562.764504</v>
       </c>
       <c r="O33" t="n">
-        <v>0.569229</v>
-      </c>
-      <c r="P33" s="2" t="n">
-        <v>44454.11143518519</v>
-      </c>
-      <c r="Q33" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>8.25</v>
+      </c>
+      <c r="P33" s="1" t="n">
+        <v>45457.69225694444</v>
+      </c>
+      <c r="Q33" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.001966487458496193</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Infraestructura empresarial</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>DLT</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Hashgraph (aBFT)</t>
-        </is>
-      </c>
-      <c r="W33" t="n">
-        <v>2019</v>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>hedera.com</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>Aplicaciones empresariales y tokenización</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>Red propia (hashgraph, no blockchain tradicional)</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>Gobernada por un consejo de grandes empresas globales.</t>
-        </is>
-      </c>
+        <v>0.001997660270625051</v>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3651,49 +3639,49 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5.97e-06</v>
+        <v>6.05e-06</v>
       </c>
       <c r="F34" t="n">
-        <v>3499895427</v>
+        <v>3567256021</v>
       </c>
       <c r="G34" t="n">
         <v>33</v>
       </c>
       <c r="H34" t="n">
-        <v>133814849</v>
+        <v>213804939</v>
       </c>
       <c r="I34" t="n">
-        <v>5.87e-06</v>
+        <v>6.25e-06</v>
       </c>
       <c r="J34" t="n">
-        <v>5.4e-06</v>
+        <v>5.9e-06</v>
       </c>
       <c r="K34" t="n">
-        <v>5.74284e-07</v>
+        <v>8.1711e-08</v>
       </c>
       <c r="L34" t="n">
-        <v>10.6398</v>
+        <v>1.4441</v>
       </c>
       <c r="M34" t="n">
-        <v>589238972680230.1</v>
+        <v>589238968628246.4</v>
       </c>
       <c r="N34" t="n">
-        <v>589496072572615.9</v>
+        <v>589496070402766.1</v>
       </c>
       <c r="O34" t="n">
         <v>8.616e-05</v>
       </c>
-      <c r="P34" s="2" t="n">
+      <c r="P34" s="1" t="n">
         <v>44496.82980324074</v>
       </c>
-      <c r="Q34" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q34" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0.001671252484428065</v>
+        <v>0.001697623497045746</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3737,68 +3725,68 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>memecore</t>
+          <t>bittensor</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>tao</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MemeCore</t>
+          <t>Bittensor</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1.49</v>
+        <v>309.22</v>
       </c>
       <c r="F35" t="n">
-        <v>3393781990</v>
+        <v>3508186486</v>
       </c>
       <c r="G35" t="n">
         <v>34</v>
       </c>
       <c r="H35" t="n">
-        <v>2344197</v>
+        <v>545675077</v>
       </c>
       <c r="I35" t="n">
-        <v>1.61</v>
+        <v>325.76</v>
       </c>
       <c r="J35" t="n">
-        <v>1.45</v>
+        <v>302.22</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.04122143441758852</v>
+        <v>1.068</v>
       </c>
       <c r="L35" t="n">
-        <v>-2.69026</v>
+        <v>0.49825</v>
       </c>
       <c r="M35" t="n">
-        <v>2276129700.761904</v>
+        <v>11339645.9251</v>
       </c>
       <c r="N35" t="n">
-        <v>5416704127.604535</v>
+        <v>21000000</v>
       </c>
       <c r="O35" t="n">
-        <v>5.64</v>
-      </c>
-      <c r="P35" s="2" t="n">
-        <v>46205.17638888889</v>
-      </c>
-      <c r="Q35" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>757.6</v>
+      </c>
+      <c r="P35" s="1" t="n">
+        <v>45358.44833333333</v>
+      </c>
+      <c r="Q35" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R35" t="b">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.001609846152469781</v>
+        <v>0.001663521978742413</v>
       </c>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
@@ -3812,82 +3800,112 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>bittensor</t>
+          <t>crypto-com-chain</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>tao</t>
+          <t>cro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Bittensor</t>
+          <t>Cronos</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>289.07</v>
+        <v>0.06623999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>3267924960</v>
+        <v>3294501272</v>
       </c>
       <c r="G36" t="n">
         <v>35</v>
       </c>
       <c r="H36" t="n">
-        <v>470609612</v>
+        <v>16354864</v>
       </c>
       <c r="I36" t="n">
-        <v>288.6</v>
+        <v>0.068842</v>
       </c>
       <c r="J36" t="n">
-        <v>254.14</v>
+        <v>0.06461500000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>35.18</v>
+        <v>0.0008701</v>
       </c>
       <c r="L36" t="n">
-        <v>13.85522</v>
+        <v>1.33228</v>
       </c>
       <c r="M36" t="n">
-        <v>11339645.9251</v>
+        <v>49737707457.07803</v>
       </c>
       <c r="N36" t="n">
-        <v>21000000</v>
+        <v>98937691623.08702</v>
       </c>
       <c r="O36" t="n">
-        <v>757.6</v>
-      </c>
-      <c r="P36" s="2" t="n">
-        <v>45358.44833333333</v>
-      </c>
-      <c r="Q36" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>0.891544</v>
+      </c>
+      <c r="P36" s="1" t="n">
+        <v>44523.66666666666</v>
+      </c>
+      <c r="Q36" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.001537014484945302</v>
-      </c>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
+        <v>0.001540159060169029</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Token de exchange</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Layer 1 (Cronos)</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Proof of Stake</t>
+        </is>
+      </c>
+      <c r="W36" t="n">
+        <v>2018</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>cronos.org</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Pagos y DeFi en el ecosistema Crypto.com</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Cronos, EVM-compatible)</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>Token nativo del ecosistema Crypto.com y su red Cronos.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3906,49 +3924,49 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.9999479999999999</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>3244051484</v>
+        <v>3258615171</v>
       </c>
       <c r="G37" t="n">
         <v>36</v>
       </c>
       <c r="H37" t="n">
-        <v>1028610394</v>
+        <v>916316571</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>0.99979</v>
+        <v>0.999787</v>
       </c>
       <c r="K37" t="n">
-        <v>-7.465353777646999e-05</v>
+        <v>-1.5706744024069e-05</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.00747</v>
+        <v>-0.00083</v>
       </c>
       <c r="M37" t="n">
-        <v>3244126367.123568</v>
+        <v>3258647890.048256</v>
       </c>
       <c r="N37" t="n">
-        <v>3247147890.103568</v>
+        <v>3258647890.048256</v>
       </c>
       <c r="O37" t="n">
         <v>1.65</v>
       </c>
-      <c r="P37" s="2" t="n">
+      <c r="P37" s="1" t="n">
         <v>45686.67436342593</v>
       </c>
-      <c r="Q37" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q37" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R37" t="b">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.001523199245012454</v>
+        <v>0.00151944160352938</v>
       </c>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
@@ -3962,112 +3980,82 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>crypto-com-chain</t>
+          <t>memecore</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>cro</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cronos</t>
+          <t>MemeCore</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.0636</v>
+        <v>1.31</v>
       </c>
       <c r="F38" t="n">
-        <v>3161313953</v>
+        <v>2977606566</v>
       </c>
       <c r="G38" t="n">
         <v>37</v>
       </c>
       <c r="H38" t="n">
-        <v>13759695</v>
+        <v>1787037</v>
       </c>
       <c r="I38" t="n">
-        <v>0.06450500000000001</v>
+        <v>1.48</v>
       </c>
       <c r="J38" t="n">
-        <v>0.058538</v>
+        <v>1.29</v>
       </c>
       <c r="K38" t="n">
-        <v>0.00494188</v>
+        <v>-0.1573793546544873</v>
       </c>
       <c r="L38" t="n">
-        <v>8.42489</v>
+        <v>-10.74441</v>
       </c>
       <c r="M38" t="n">
-        <v>49735222151.92632</v>
+        <v>2277592661.72997</v>
       </c>
       <c r="N38" t="n">
-        <v>98935195279.49802</v>
+        <v>5417166988.519834</v>
       </c>
       <c r="O38" t="n">
-        <v>0.891544</v>
-      </c>
-      <c r="P38" s="2" t="n">
-        <v>44523.66666666666</v>
-      </c>
-      <c r="Q38" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>5.64</v>
+      </c>
+      <c r="P38" s="1" t="n">
+        <v>46205.17638888889</v>
+      </c>
+      <c r="Q38" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R38" t="b">
         <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>0.00147532021632738</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Token de exchange</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Layer 1 (Cronos)</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Proof of Stake</t>
-        </is>
-      </c>
-      <c r="W38" t="n">
-        <v>2018</v>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>cronos.org</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>Pagos y DeFi en el ecosistema Crypto.com</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Cronos, EVM-compatible)</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>Token nativo del ecosistema Crypto.com y su red Cronos.</t>
-        </is>
-      </c>
+        <v>0.00135721212116082</v>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4089,46 +4077,46 @@
         <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>2780507392</v>
+        <v>2823592224</v>
       </c>
       <c r="G39" t="n">
         <v>38</v>
       </c>
       <c r="H39" t="n">
-        <v>80675032</v>
+        <v>157981743</v>
       </c>
       <c r="I39" t="n">
         <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>0.99975</v>
+        <v>0.99978</v>
       </c>
       <c r="K39" t="n">
-        <v>0.00024728</v>
+        <v>6.4e-06</v>
       </c>
       <c r="L39" t="n">
-        <v>0.02473</v>
+        <v>0.00118</v>
       </c>
       <c r="M39" t="n">
-        <v>2780174063.099801</v>
+        <v>2823558770.164367</v>
       </c>
       <c r="N39" t="n">
-        <v>2780171733.0998</v>
+        <v>2823558770.164366</v>
       </c>
       <c r="O39" t="n">
         <v>1.021</v>
       </c>
-      <c r="P39" s="2" t="n">
+      <c r="P39" s="1" t="n">
         <v>45222.61454861111</v>
       </c>
-      <c r="Q39" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q39" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001254952892850162</v>
+        <v>0.001268297879620087</v>
       </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
@@ -4142,7 +4130,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4161,28 +4149,28 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4351.16</v>
+        <v>4355.93</v>
       </c>
       <c r="F40" t="n">
-        <v>2709821109</v>
+        <v>2712967630</v>
       </c>
       <c r="G40" t="n">
         <v>39</v>
       </c>
       <c r="H40" t="n">
-        <v>178966320</v>
+        <v>209976775</v>
       </c>
       <c r="I40" t="n">
-        <v>4381.92</v>
+        <v>4372.67</v>
       </c>
       <c r="J40" t="n">
-        <v>4328.37</v>
+        <v>4295.64</v>
       </c>
       <c r="K40" t="n">
-        <v>-17.7913020598844</v>
+        <v>15.59</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.40722</v>
+        <v>0.34468</v>
       </c>
       <c r="M40" t="n">
         <v>622823.6595320001</v>
@@ -4193,17 +4181,17 @@
       <c r="O40" t="n">
         <v>5504.62</v>
       </c>
-      <c r="P40" s="2" t="n">
+      <c r="P40" s="1" t="n">
         <v>46050.66666666666</v>
       </c>
-      <c r="Q40" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q40" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R40" t="b">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.001214047749434675</v>
+        <v>0.001204433035972854</v>
       </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
@@ -4217,7 +4205,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4236,28 +4224,28 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>123.32</v>
+        <v>123.13</v>
       </c>
       <c r="F41" t="n">
-        <v>2591259374</v>
+        <v>2587013448</v>
       </c>
       <c r="G41" t="n">
         <v>40</v>
       </c>
       <c r="H41" t="n">
-        <v>48633818</v>
+        <v>40188551</v>
       </c>
       <c r="I41" t="n">
-        <v>124.08</v>
+        <v>126.4</v>
       </c>
       <c r="J41" t="n">
-        <v>116.9</v>
+        <v>120.48</v>
       </c>
       <c r="K41" t="n">
-        <v>6.83</v>
+        <v>-0.1176173684437742</v>
       </c>
       <c r="L41" t="n">
-        <v>5.86617</v>
+        <v>-0.16008</v>
       </c>
       <c r="M41" t="n">
         <v>21000000</v>
@@ -4268,17 +4256,17 @@
       <c r="O41" t="n">
         <v>228.74</v>
       </c>
-      <c r="P41" s="2" t="n">
+      <c r="P41" s="1" t="n">
         <v>45934.66666666666</v>
       </c>
-      <c r="Q41" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q41" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R41" t="b">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.00114543776503694</v>
+        <v>0.001131718245804718</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4322,7 +4310,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4344,7 +4332,7 @@
         <v>1.14</v>
       </c>
       <c r="F42" t="n">
-        <v>2508517113</v>
+        <v>2508825557</v>
       </c>
       <c r="G42" t="n">
         <v>41</v>
@@ -4359,31 +4347,31 @@
         <v>1.14</v>
       </c>
       <c r="K42" t="n">
-        <v>8.125e-05</v>
+        <v>0.00010508</v>
       </c>
       <c r="L42" t="n">
-        <v>0.00714</v>
+        <v>0.00923</v>
       </c>
       <c r="M42" t="n">
-        <v>2204409826.472634</v>
+        <v>2204477317.470919</v>
       </c>
       <c r="N42" t="n">
-        <v>2204409826.472634</v>
+        <v>2204477317.470919</v>
       </c>
       <c r="O42" t="n">
         <v>1.14</v>
       </c>
-      <c r="P42" s="2" t="n">
-        <v>46286.54189814815</v>
-      </c>
-      <c r="Q42" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="P42" s="1" t="n">
+        <v>46287.53819444445</v>
+      </c>
+      <c r="Q42" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R42" t="b">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.001097555999168354</v>
+        <v>0.001086579481871068</v>
       </c>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
@@ -4397,68 +4385,68 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>bitway</t>
+          <t>ripple-usd</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>btw</t>
+          <t>rlusd</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Bitway</t>
+          <t>Ripple USD</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.908653</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>2455127227</v>
+        <v>2414668604</v>
       </c>
       <c r="G43" t="n">
         <v>42</v>
       </c>
       <c r="H43" t="n">
-        <v>29155304</v>
+        <v>423709547</v>
       </c>
       <c r="I43" t="n">
-        <v>0.922215</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
-        <v>0.692906</v>
+        <v>0.9997740000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>0.198456</v>
+        <v>9.699e-05</v>
       </c>
       <c r="L43" t="n">
-        <v>27.94389</v>
+        <v>0.00021</v>
       </c>
       <c r="M43" t="n">
-        <v>2708142280.000001</v>
+        <v>2414682344.087236</v>
       </c>
       <c r="N43" t="n">
-        <v>10000000000</v>
+        <v>2417586212.607235</v>
       </c>
       <c r="O43" t="n">
-        <v>0.922215</v>
-      </c>
-      <c r="P43" s="2" t="n">
-        <v>46286.57083333333</v>
-      </c>
-      <c r="Q43" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>1.073</v>
+      </c>
+      <c r="P43" s="1" t="n">
+        <v>45652.11518518518</v>
+      </c>
+      <c r="Q43" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.001066660033910618</v>
+        <v>0.001032221595760816</v>
       </c>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
@@ -4472,68 +4460,68 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ripple-usd</t>
+          <t>bitway</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>rlusd</t>
+          <t>btw</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ripple USD</t>
+          <t>Bitway</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>0.882043</v>
       </c>
       <c r="F44" t="n">
-        <v>2368658098</v>
+        <v>2386426149</v>
       </c>
       <c r="G44" t="n">
         <v>43</v>
       </c>
       <c r="H44" t="n">
-        <v>386949611</v>
+        <v>13777728</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0.885736</v>
       </c>
       <c r="J44" t="n">
-        <v>0.999826</v>
+        <v>0.717963</v>
       </c>
       <c r="K44" t="n">
-        <v>0.00019016</v>
+        <v>0.01416612</v>
       </c>
       <c r="L44" t="n">
-        <v>0.01902</v>
+        <v>1.3311</v>
       </c>
       <c r="M44" t="n">
-        <v>2368466183.08722</v>
+        <v>2708142280.000001</v>
       </c>
       <c r="N44" t="n">
-        <v>2373816183.087221</v>
+        <v>10000000000</v>
       </c>
       <c r="O44" t="n">
-        <v>1.073</v>
-      </c>
-      <c r="P44" s="2" t="n">
-        <v>45652.11518518518</v>
-      </c>
-      <c r="Q44" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>0.972034</v>
+      </c>
+      <c r="P44" s="1" t="n">
+        <v>46286.79398148148</v>
+      </c>
+      <c r="Q44" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R44" t="b">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.001016621582705633</v>
+        <v>0.001015916903399287</v>
       </c>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
@@ -4547,7 +4535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4569,7 +4557,7 @@
         <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>2329036631</v>
+        <v>2280893730</v>
       </c>
       <c r="G45" t="n">
         <v>44</v>
@@ -4590,25 +4578,25 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>2329036630.620449</v>
+        <v>2280893730.007649</v>
       </c>
       <c r="N45" t="n">
-        <v>2329735522.270449</v>
+        <v>2280893730.007649</v>
       </c>
       <c r="O45" t="n">
         <v>1</v>
       </c>
-      <c r="P45" s="2" t="n">
+      <c r="P45" s="1" t="n">
         <v>45699.87511574074</v>
       </c>
-      <c r="Q45" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q45" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R45" t="b">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.0009936932050744745</v>
+        <v>0.0009549918306333762</v>
       </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
@@ -4622,7 +4610,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4644,13 +4632,13 @@
         <v>1.15</v>
       </c>
       <c r="F46" t="n">
-        <v>2246038869</v>
+        <v>2246400476</v>
       </c>
       <c r="G46" t="n">
         <v>45</v>
       </c>
       <c r="H46" t="n">
-        <v>1173758</v>
+        <v>2779332</v>
       </c>
       <c r="I46" t="n">
         <v>1.15</v>
@@ -4659,31 +4647,31 @@
         <v>1.13</v>
       </c>
       <c r="K46" t="n">
-        <v>0.0005346800000000001</v>
+        <v>0.0046907</v>
       </c>
       <c r="L46" t="n">
-        <v>0.04665</v>
+        <v>0.42566</v>
       </c>
       <c r="M46" t="n">
-        <v>1969763856.975529</v>
+        <v>1963554625.495198</v>
       </c>
       <c r="N46" t="n">
-        <v>1969996524.04932</v>
+        <v>1963554625.495198</v>
       </c>
       <c r="O46" t="n">
         <v>1.26</v>
       </c>
-      <c r="P46" s="2" t="n">
+      <c r="P46" s="1" t="n">
         <v>45377.89175925926</v>
       </c>
-      <c r="Q46" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q46" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R46" t="b">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.0009456635844226938</v>
+        <v>0.0009350784805008161</v>
       </c>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
@@ -4697,7 +4685,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4716,31 +4704,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>143.63</v>
+        <v>144.82</v>
       </c>
       <c r="F47" t="n">
-        <v>2214275421</v>
+        <v>2236997529</v>
       </c>
       <c r="G47" t="n">
         <v>46</v>
       </c>
       <c r="H47" t="n">
-        <v>363017691</v>
+        <v>267338061</v>
       </c>
       <c r="I47" t="n">
-        <v>148.98</v>
+        <v>146.7</v>
       </c>
       <c r="J47" t="n">
-        <v>135.04</v>
+        <v>140.18</v>
       </c>
       <c r="K47" t="n">
-        <v>8.01</v>
+        <v>1.28</v>
       </c>
       <c r="L47" t="n">
-        <v>5.90774</v>
+        <v>0.85148</v>
       </c>
       <c r="M47" t="n">
-        <v>15428777.33265995</v>
+        <v>15428919.91855954</v>
       </c>
       <c r="N47" t="n">
         <v>16000000</v>
@@ -4748,17 +4736,17 @@
       <c r="O47" t="n">
         <v>661.6900000000001</v>
       </c>
-      <c r="P47" s="2" t="n">
+      <c r="P47" s="1" t="n">
         <v>44334.55554398148</v>
       </c>
-      <c r="Q47" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q47" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R47" t="b">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0.0009272825302680943</v>
+        <v>0.0009296500516292197</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -4802,68 +4790,68 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ethena</t>
+          <t>mantle</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ena</t>
+          <t>mnt</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Ethena</t>
+          <t>Mantle</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.216225</v>
+        <v>0.668858</v>
       </c>
       <c r="F48" t="n">
-        <v>2181612757</v>
+        <v>2210124703</v>
       </c>
       <c r="G48" t="n">
         <v>47</v>
       </c>
       <c r="H48" t="n">
-        <v>720364026</v>
+        <v>56060834</v>
       </c>
       <c r="I48" t="n">
-        <v>0.230131</v>
+        <v>0.671764</v>
       </c>
       <c r="J48" t="n">
-        <v>0.203336</v>
+        <v>0.636514</v>
       </c>
       <c r="K48" t="n">
-        <v>0.01567105</v>
+        <v>0.02171301</v>
       </c>
       <c r="L48" t="n">
-        <v>7.81387</v>
+        <v>3.34798</v>
       </c>
       <c r="M48" t="n">
-        <v>10095312500</v>
+        <v>3302294382.53684</v>
       </c>
       <c r="N48" t="n">
-        <v>15000000000</v>
+        <v>6219316794.889999</v>
       </c>
       <c r="O48" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P48" s="2" t="n">
-        <v>45393.21892361111</v>
-      </c>
-      <c r="Q48" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>2.86</v>
+      </c>
+      <c r="P48" s="1" t="n">
+        <v>45938.71164351852</v>
+      </c>
+      <c r="Q48" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0.0009083811126443688</v>
+        <v>0.0009141360617577694</v>
       </c>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
@@ -4877,7 +4865,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4896,28 +4884,28 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.444165</v>
+        <v>0.435294</v>
       </c>
       <c r="F49" t="n">
-        <v>2161052269</v>
+        <v>2121311587</v>
       </c>
       <c r="G49" t="n">
         <v>48</v>
       </c>
       <c r="H49" t="n">
-        <v>291126477</v>
+        <v>252008569</v>
       </c>
       <c r="I49" t="n">
-        <v>0.458235</v>
+        <v>0.463533</v>
       </c>
       <c r="J49" t="n">
-        <v>0.415353</v>
+        <v>0.422514</v>
       </c>
       <c r="K49" t="n">
-        <v>0.03020456</v>
+        <v>-0.01531617904591515</v>
       </c>
       <c r="L49" t="n">
-        <v>7.29649</v>
+        <v>-3.43312</v>
       </c>
       <c r="M49" t="n">
         <v>4869330647</v>
@@ -4928,17 +4916,17 @@
       <c r="O49" t="n">
         <v>2.14</v>
       </c>
-      <c r="P49" s="2" t="n">
+      <c r="P49" s="1" t="n">
         <v>45641.69166666667</v>
       </c>
-      <c r="Q49" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q49" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>0.0008964830515971866</v>
+        <v>0.0008628632338804206</v>
       </c>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
@@ -4952,68 +4940,68 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>mantle</t>
+          <t>ethena</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>mnt</t>
+          <t>ena</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Mantle</t>
+          <t>Ethena</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.642248</v>
+        <v>0.208918</v>
       </c>
       <c r="F50" t="n">
-        <v>2119720789</v>
+        <v>2112989817</v>
       </c>
       <c r="G50" t="n">
         <v>49</v>
       </c>
       <c r="H50" t="n">
-        <v>46036318</v>
+        <v>443685103</v>
       </c>
       <c r="I50" t="n">
-        <v>0.638996</v>
+        <v>0.218605</v>
       </c>
       <c r="J50" t="n">
-        <v>0.600169</v>
+        <v>0.203656</v>
       </c>
       <c r="K50" t="n">
-        <v>0.04491815</v>
+        <v>0.00058719</v>
       </c>
       <c r="L50" t="n">
-        <v>7.51982</v>
+        <v>0.33878</v>
       </c>
       <c r="M50" t="n">
-        <v>3302294382.53684</v>
+        <v>10095312500</v>
       </c>
       <c r="N50" t="n">
-        <v>6219316794.889999</v>
+        <v>15000000000</v>
       </c>
       <c r="O50" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="P50" s="2" t="n">
-        <v>45938.71164351852</v>
-      </c>
-      <c r="Q50" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>1.52</v>
+      </c>
+      <c r="P50" s="1" t="n">
+        <v>45393.21892361111</v>
+      </c>
+      <c r="Q50" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0.0008725651138415076</v>
+        <v>0.0008580589808594492</v>
       </c>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
@@ -5027,68 +5015,68 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>pump-fun</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Pepe</t>
+          <t>Pump.fun</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5.03e-06</v>
+        <v>0.00445687</v>
       </c>
       <c r="F51" t="n">
-        <v>2102717236</v>
+        <v>2083585191</v>
       </c>
       <c r="G51" t="n">
         <v>50</v>
       </c>
       <c r="H51" t="n">
-        <v>813645807</v>
+        <v>226448298</v>
       </c>
       <c r="I51" t="n">
-        <v>4.87e-06</v>
+        <v>0.00469623</v>
       </c>
       <c r="J51" t="n">
-        <v>3.92e-06</v>
+        <v>0.00431196</v>
       </c>
       <c r="K51" t="n">
-        <v>1.07e-06</v>
+        <v>0.00013924</v>
       </c>
       <c r="L51" t="n">
-        <v>27.03744</v>
+        <v>3.18771</v>
       </c>
       <c r="M51" t="n">
-        <v>420690000000000</v>
+        <v>467008882120.3215</v>
       </c>
       <c r="N51" t="n">
-        <v>420690000000000</v>
+        <v>832520702375.5927</v>
       </c>
       <c r="O51" t="n">
-        <v>2.803e-05</v>
-      </c>
-      <c r="P51" s="2" t="n">
-        <v>45635.35457175926</v>
-      </c>
-      <c r="Q51" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>0.00881908</v>
+      </c>
+      <c r="P51" s="1" t="n">
+        <v>45914.36296296296</v>
+      </c>
+      <c r="Q51" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0.000862725400328239</v>
+        <v>0.0008410833538845346</v>
       </c>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
@@ -5102,68 +5090,68 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>aster-2</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>aster</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Pepe</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.7507239999999999</v>
+        <v>4.91e-06</v>
       </c>
       <c r="F52" t="n">
-        <v>2035419904</v>
+        <v>2067006553</v>
       </c>
       <c r="G52" t="n">
         <v>51</v>
       </c>
       <c r="H52" t="n">
-        <v>176946024</v>
+        <v>961220641</v>
       </c>
       <c r="I52" t="n">
-        <v>0.766236</v>
+        <v>5.34e-06</v>
       </c>
       <c r="J52" t="n">
-        <v>0.732133</v>
+        <v>4.71e-06</v>
       </c>
       <c r="K52" t="n">
-        <v>0.02004207</v>
+        <v>9.7696e-08</v>
       </c>
       <c r="L52" t="n">
-        <v>2.74293</v>
+        <v>1.97647</v>
       </c>
       <c r="M52" t="n">
-        <v>2710487455.649731</v>
+        <v>420690000000000</v>
       </c>
       <c r="N52" t="n">
-        <v>7795741639.279952</v>
+        <v>420690000000000</v>
       </c>
       <c r="O52" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="P52" s="2" t="n">
-        <v>45924.13766203704</v>
-      </c>
-      <c r="Q52" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>2.803e-05</v>
+      </c>
+      <c r="P52" s="1" t="n">
+        <v>45635.35457175926</v>
+      </c>
+      <c r="Q52" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R52" t="b">
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0.0008237813945026729</v>
+        <v>0.0008315123165096623</v>
       </c>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
@@ -5177,248 +5165,248 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>pump-fun</t>
+          <t>polkadot</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>dot</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Pump.fun</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.00435338</v>
+        <v>1.2</v>
       </c>
       <c r="F53" t="n">
-        <v>2030520104</v>
+        <v>2039692689</v>
       </c>
       <c r="G53" t="n">
         <v>52</v>
       </c>
       <c r="H53" t="n">
-        <v>184922999</v>
+        <v>176420599</v>
       </c>
       <c r="I53" t="n">
-        <v>0.00451054</v>
+        <v>1.22</v>
       </c>
       <c r="J53" t="n">
-        <v>0.00407465</v>
+        <v>1.15</v>
       </c>
       <c r="K53" t="n">
-        <v>0.00027591</v>
+        <v>0.00602479</v>
       </c>
       <c r="L53" t="n">
-        <v>6.7666</v>
+        <v>0.45589</v>
       </c>
       <c r="M53" t="n">
-        <v>467279734243.4806</v>
+        <v>1704000796.081443</v>
       </c>
       <c r="N53" t="n">
-        <v>832769967768.4836</v>
+        <v>1704007261.631945</v>
       </c>
       <c r="O53" t="n">
-        <v>0.00881908</v>
-      </c>
-      <c r="P53" s="2" t="n">
-        <v>45914.36296296296</v>
-      </c>
-      <c r="Q53" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>54.98</v>
+      </c>
+      <c r="P53" s="1" t="n">
+        <v>44504.25704861111</v>
+      </c>
+      <c r="Q53" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0.0008209459501533471</v>
-      </c>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
-      <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr"/>
-      <c r="AA53" t="inlineStr"/>
+        <v>0.0008157437103553943</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Layer 0</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Proof of Stake (NPoS)</t>
+        </is>
+      </c>
+      <c r="W53" t="n">
+        <v>2020</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>polkadot.network</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>Interoperabilidad entre blockchains</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Layer 0, relay chain)</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>Permite que blockchains distintas (parachains) se comuniquen entre sí.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>polkadot</t>
+          <t>aster-2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>dot</t>
+          <t>aster</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1.18</v>
+        <v>0.727623</v>
       </c>
       <c r="F54" t="n">
-        <v>2017115893</v>
+        <v>1974213251</v>
       </c>
       <c r="G54" t="n">
         <v>53</v>
       </c>
       <c r="H54" t="n">
-        <v>266894098</v>
+        <v>165809899</v>
       </c>
       <c r="I54" t="n">
-        <v>1.2</v>
+        <v>0.748964</v>
       </c>
       <c r="J54" t="n">
-        <v>1.11</v>
+        <v>0.7117059999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>0.076651</v>
+        <v>-0.01163590523736624</v>
       </c>
       <c r="L54" t="n">
-        <v>6.92083</v>
+        <v>-1.59472</v>
       </c>
       <c r="M54" t="n">
-        <v>1703808907.243623</v>
+        <v>2710487455.649731</v>
       </c>
       <c r="N54" t="n">
-        <v>1703819243.637835</v>
+        <v>7795741639.279952</v>
       </c>
       <c r="O54" t="n">
-        <v>54.98</v>
-      </c>
-      <c r="P54" s="2" t="n">
-        <v>44504.25704861111</v>
-      </c>
-      <c r="Q54" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>2.41</v>
+      </c>
+      <c r="P54" s="1" t="n">
+        <v>45924.13766203704</v>
+      </c>
+      <c r="Q54" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>0.0008131891244998261</v>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Interoperabilidad</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Layer 0</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Proof of Stake (NPoS)</t>
-        </is>
-      </c>
-      <c r="W54" t="n">
-        <v>2020</v>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>polkadot.network</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>Interoperabilidad entre blockchains</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Layer 0, relay chain)</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>Permite que blockchains distintas (parachains) se comuniquen entre sí.</t>
-        </is>
-      </c>
+        <v>0.0007779416817217009</v>
+      </c>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>pax-gold</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>paxg</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Morpho</t>
+          <t>PAX Gold</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2.75</v>
+        <v>4355.91</v>
       </c>
       <c r="F55" t="n">
-        <v>1919720910</v>
+        <v>1894407221</v>
       </c>
       <c r="G55" t="n">
         <v>54</v>
       </c>
       <c r="H55" t="n">
-        <v>52265765</v>
+        <v>199072964</v>
       </c>
       <c r="I55" t="n">
-        <v>2.84</v>
+        <v>4369.08</v>
       </c>
       <c r="J55" t="n">
-        <v>2.52</v>
+        <v>4295.5</v>
       </c>
       <c r="K55" t="n">
-        <v>0.227306</v>
+        <v>18.53</v>
       </c>
       <c r="L55" t="n">
-        <v>9.02125</v>
+        <v>0.41116</v>
       </c>
       <c r="M55" t="n">
-        <v>699207451.3256872</v>
+        <v>434903.623539</v>
       </c>
       <c r="N55" t="n">
-        <v>1000000000</v>
+        <v>434903.623539</v>
       </c>
       <c r="O55" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="P55" s="2" t="n">
-        <v>45674.19883101852</v>
-      </c>
-      <c r="Q55" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>5619.09</v>
+      </c>
+      <c r="P55" s="1" t="n">
+        <v>46050.93814814815</v>
+      </c>
+      <c r="Q55" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0007568280374758575</v>
+        <v>0.0007318687476320498</v>
       </c>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
@@ -5432,68 +5420,68 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>pax-gold</t>
+          <t>world-liberty-financial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>paxg</t>
+          <t>wlfi</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>PAX Gold</t>
+          <t>World Liberty Financial</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4347.76</v>
+        <v>0.058378</v>
       </c>
       <c r="F56" t="n">
-        <v>1889049810</v>
+        <v>1855309470</v>
       </c>
       <c r="G56" t="n">
         <v>55</v>
       </c>
       <c r="H56" t="n">
-        <v>160372105</v>
+        <v>57287055</v>
       </c>
       <c r="I56" t="n">
-        <v>4372.34</v>
+        <v>0.058528</v>
       </c>
       <c r="J56" t="n">
-        <v>4326.12</v>
+        <v>0.056703</v>
       </c>
       <c r="K56" t="n">
-        <v>-11.95432789098686</v>
+        <v>0.00125043</v>
       </c>
       <c r="L56" t="n">
-        <v>-0.2742</v>
+        <v>2.19569</v>
       </c>
       <c r="M56" t="n">
-        <v>434499.367539</v>
+        <v>31777768006</v>
       </c>
       <c r="N56" t="n">
-        <v>434499.367539</v>
+        <v>100000000000</v>
       </c>
       <c r="O56" t="n">
-        <v>5619.09</v>
-      </c>
-      <c r="P56" s="2" t="n">
-        <v>46050.93814814815</v>
-      </c>
-      <c r="Q56" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>0.331336</v>
+      </c>
+      <c r="P56" s="1" t="n">
+        <v>45901.18065972222</v>
+      </c>
+      <c r="Q56" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R56" t="b">
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0.0007390791095231636</v>
+        <v>0.0007092971687065402</v>
       </c>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
@@ -5507,68 +5495,68 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>world-liberty-financial</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>wlfi</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>World Liberty Financial</t>
+          <t>Morpho</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.05751</v>
+        <v>2.59</v>
       </c>
       <c r="F57" t="n">
-        <v>1827430362</v>
+        <v>1807976374</v>
       </c>
       <c r="G57" t="n">
         <v>56</v>
       </c>
       <c r="H57" t="n">
-        <v>50977157</v>
+        <v>33520122</v>
       </c>
       <c r="I57" t="n">
-        <v>0.05868</v>
+        <v>2.67</v>
       </c>
       <c r="J57" t="n">
-        <v>0.057433</v>
+        <v>2.56</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.000690303918718715</v>
+        <v>-0.0698690106453359</v>
       </c>
       <c r="L57" t="n">
-        <v>-1.18608</v>
+        <v>-2.64098</v>
       </c>
       <c r="M57" t="n">
-        <v>31777471043</v>
+        <v>699288962.8606994</v>
       </c>
       <c r="N57" t="n">
-        <v>100000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="O57" t="n">
-        <v>0.331336</v>
-      </c>
-      <c r="P57" s="2" t="n">
-        <v>45901.18065972222</v>
-      </c>
-      <c r="Q57" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>4.17</v>
+      </c>
+      <c r="P57" s="1" t="n">
+        <v>45674.19883101852</v>
+      </c>
+      <c r="Q57" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R57" t="b">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0.0007034208141559688</v>
+        <v>0.0006819712309012499</v>
       </c>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
@@ -5582,68 +5570,68 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>worldcoin-wld</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>wld</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Sky</t>
+          <t>Worldcoin</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.072577</v>
+        <v>0.460206</v>
       </c>
       <c r="F58" t="n">
-        <v>1699069436</v>
+        <v>1680569073</v>
       </c>
       <c r="G58" t="n">
         <v>57</v>
       </c>
       <c r="H58" t="n">
-        <v>17930234</v>
+        <v>249743884</v>
       </c>
       <c r="I58" t="n">
-        <v>0.07318</v>
+        <v>0.476706</v>
       </c>
       <c r="J58" t="n">
-        <v>0.068775</v>
+        <v>0.441742</v>
       </c>
       <c r="K58" t="n">
-        <v>0.00370732</v>
+        <v>0.00849258</v>
       </c>
       <c r="L58" t="n">
-        <v>5.38306</v>
+        <v>1.89246</v>
       </c>
       <c r="M58" t="n">
-        <v>23426953149.00353</v>
+        <v>3646959224.069938</v>
       </c>
       <c r="N58" t="n">
-        <v>23459804203.60596</v>
+        <v>10000000000</v>
       </c>
       <c r="O58" t="n">
-        <v>0.100535</v>
-      </c>
-      <c r="P58" s="2" t="n">
-        <v>45630.09302083333</v>
-      </c>
-      <c r="Q58" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>11.74</v>
+      </c>
+      <c r="P58" s="1" t="n">
+        <v>45360.67409722223</v>
+      </c>
+      <c r="Q58" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R58" t="b">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0006291401777420459</v>
+        <v>0.0006084175385109214</v>
       </c>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
@@ -5657,7 +5645,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5676,49 +5664,49 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="F59" t="n">
-        <v>1643500300</v>
+        <v>1662258969</v>
       </c>
       <c r="G59" t="n">
         <v>58</v>
       </c>
       <c r="H59" t="n">
-        <v>89056182</v>
+        <v>71912870</v>
       </c>
       <c r="I59" t="n">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="J59" t="n">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="K59" t="n">
-        <v>0.15801</v>
+        <v>0.01167413</v>
       </c>
       <c r="L59" t="n">
-        <v>5.65301</v>
+        <v>0.40321</v>
       </c>
       <c r="M59" t="n">
-        <v>556899589.1864374</v>
+        <v>556905624.1128303</v>
       </c>
       <c r="N59" t="n">
-        <v>556899589.1864374</v>
+        <v>556905641.1775453</v>
       </c>
       <c r="O59" t="n">
         <v>700.65</v>
       </c>
-      <c r="P59" s="2" t="n">
+      <c r="P59" s="1" t="n">
         <v>44326.33741898148</v>
       </c>
-      <c r="Q59" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q59" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R59" t="b">
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>0.0005969831116029949</v>
+        <v>0.0005978469060065021</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -5762,68 +5750,68 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>worldcoin-wld</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>wld</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Worldcoin</t>
+          <t>Sky</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.440412</v>
+        <v>0.069689</v>
       </c>
       <c r="F60" t="n">
-        <v>1602016980</v>
+        <v>1632669937</v>
       </c>
       <c r="G60" t="n">
         <v>59</v>
       </c>
       <c r="H60" t="n">
-        <v>267402589</v>
+        <v>18938739</v>
       </c>
       <c r="I60" t="n">
-        <v>0.457331</v>
+        <v>0.072129</v>
       </c>
       <c r="J60" t="n">
-        <v>0.429347</v>
+        <v>0.066889</v>
       </c>
       <c r="K60" t="n">
-        <v>0.01056067</v>
+        <v>-0.002276997225677535</v>
       </c>
       <c r="L60" t="n">
-        <v>2.45682</v>
+        <v>-3.19928</v>
       </c>
       <c r="M60" t="n">
-        <v>3645494676.034653</v>
+        <v>23425011020.63758</v>
       </c>
       <c r="N60" t="n">
-        <v>10000000000</v>
+        <v>23459804203.60596</v>
       </c>
       <c r="O60" t="n">
-        <v>11.74</v>
-      </c>
-      <c r="P60" s="2" t="n">
-        <v>45360.67409722223</v>
-      </c>
-      <c r="Q60" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>0.100535</v>
+      </c>
+      <c r="P60" s="1" t="n">
+        <v>45630.09302083333</v>
+      </c>
+      <c r="Q60" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R60" t="b">
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0.0005729773062057792</v>
+        <v>0.0005807648193382068</v>
       </c>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
@@ -5837,68 +5825,68 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>htx-dao</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>arb</t>
+          <t>htx</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Arbitrum</t>
+          <t>HTX DAO</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.230271</v>
+        <v>1.73e-06</v>
       </c>
       <c r="F61" t="n">
-        <v>1559573761</v>
+        <v>1554986701</v>
       </c>
       <c r="G61" t="n">
         <v>60</v>
       </c>
       <c r="H61" t="n">
-        <v>553235680</v>
+        <v>6629811</v>
       </c>
       <c r="I61" t="n">
-        <v>0.247068</v>
+        <v>1.75e-06</v>
       </c>
       <c r="J61" t="n">
-        <v>0.203259</v>
+        <v>1.71e-06</v>
       </c>
       <c r="K61" t="n">
-        <v>0.02840191</v>
+        <v>4.177e-09</v>
       </c>
       <c r="L61" t="n">
-        <v>14.0695</v>
+        <v>0.28796</v>
       </c>
       <c r="M61" t="n">
-        <v>6785574605</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="N61" t="n">
-        <v>10000000000</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="O61" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="P61" s="2" t="n">
-        <v>45303.18748842592</v>
-      </c>
-      <c r="Q61" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>3.75e-06</v>
+      </c>
+      <c r="P61" s="1" t="n">
+        <v>45629.67800925926</v>
+      </c>
+      <c r="Q61" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>0.0005484160209531665</v>
+        <v>0.0005359173985092443</v>
       </c>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
@@ -5912,68 +5900,68 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>htx-dao</t>
+          <t>venice-token</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>htx</t>
+          <t>vvv</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>HTX DAO</t>
+          <t>Venice Token</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1.72e-06</v>
+        <v>31.94</v>
       </c>
       <c r="F62" t="n">
-        <v>1546353942</v>
+        <v>1538893470</v>
       </c>
       <c r="G62" t="n">
         <v>61</v>
       </c>
       <c r="H62" t="n">
-        <v>9478676</v>
+        <v>78339005</v>
       </c>
       <c r="I62" t="n">
-        <v>1.72e-06</v>
+        <v>32.8</v>
       </c>
       <c r="J62" t="n">
-        <v>1.7e-06</v>
+        <v>30.32</v>
       </c>
       <c r="K62" t="n">
-        <v>2.336e-09</v>
+        <v>-0.5217021934352672</v>
       </c>
       <c r="L62" t="n">
-        <v>0.13596</v>
+        <v>-1.64228</v>
       </c>
       <c r="M62" t="n">
-        <v>898232728634017.2</v>
+        <v>48110483.86115634</v>
       </c>
       <c r="N62" t="n">
-        <v>898232728634017.2</v>
+        <v>81028467.06059173</v>
       </c>
       <c r="O62" t="n">
-        <v>3.75e-06</v>
-      </c>
-      <c r="P62" s="2" t="n">
-        <v>45629.67800925926</v>
-      </c>
-      <c r="Q62" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>34.53</v>
+      </c>
+      <c r="P62" s="1" t="n">
+        <v>46286.34548611111</v>
+      </c>
+      <c r="Q62" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R62" t="b">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0.0005407659003191282</v>
+        <v>0.0005266265921484651</v>
       </c>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
@@ -5987,7 +5975,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6006,49 +5994,49 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.998678</v>
+        <v>0.998385</v>
       </c>
       <c r="F63" t="n">
-        <v>1509307672</v>
+        <v>1514650093</v>
       </c>
       <c r="G63" t="n">
         <v>62</v>
       </c>
       <c r="H63" t="n">
-        <v>13809872</v>
+        <v>2022187</v>
       </c>
       <c r="I63" t="n">
-        <v>0.999596</v>
+        <v>0.999239</v>
       </c>
       <c r="J63" t="n">
-        <v>0.99781</v>
+        <v>0.998009</v>
       </c>
       <c r="K63" t="n">
-        <v>0.00053826</v>
+        <v>-0.000319527799870545</v>
       </c>
       <c r="L63" t="n">
-        <v>0.05393</v>
+        <v>-0.03532</v>
       </c>
       <c r="M63" t="n">
-        <v>1511273305</v>
+        <v>1517125649</v>
       </c>
       <c r="N63" t="n">
-        <v>1511042343</v>
+        <v>1527073089</v>
       </c>
       <c r="O63" t="n">
         <v>1.24</v>
       </c>
-      <c r="P63" s="2" t="n">
+      <c r="P63" s="1" t="n">
         <v>46212.39942129629</v>
       </c>
-      <c r="Q63" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q63" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R63" t="b">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0.0005193277524487862</v>
+        <v>0.000512630613265271</v>
       </c>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
@@ -6062,68 +6050,68 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>venice-token</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>vvv</t>
+          <t>arb</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Venice Token</t>
+          <t>Arbitrum</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>31.31</v>
+        <v>0.217939</v>
       </c>
       <c r="F64" t="n">
-        <v>1505283839</v>
+        <v>1479790029</v>
       </c>
       <c r="G64" t="n">
         <v>63</v>
       </c>
       <c r="H64" t="n">
-        <v>137801425</v>
+        <v>312111878</v>
       </c>
       <c r="I64" t="n">
-        <v>34.53</v>
+        <v>0.230082</v>
       </c>
       <c r="J64" t="n">
-        <v>27.73</v>
+        <v>0.211434</v>
       </c>
       <c r="K64" t="n">
-        <v>2.32</v>
+        <v>-0.003795146315592746</v>
       </c>
       <c r="L64" t="n">
-        <v>8.005699999999999</v>
+        <v>-1.6999</v>
       </c>
       <c r="M64" t="n">
-        <v>48098269.92982138</v>
+        <v>6785574605</v>
       </c>
       <c r="N64" t="n">
-        <v>81020526.78963831</v>
+        <v>10000000000</v>
       </c>
       <c r="O64" t="n">
-        <v>34.53</v>
-      </c>
-      <c r="P64" s="2" t="n">
-        <v>46286.34548611111</v>
-      </c>
-      <c r="Q64" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>2.39</v>
+      </c>
+      <c r="P64" s="1" t="n">
+        <v>45303.18748842592</v>
+      </c>
+      <c r="Q64" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0005169992177040046</v>
+        <v>0.000492505499523452</v>
       </c>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
@@ -6137,143 +6125,173 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>bitget-token</t>
+          <t>ethereum-classic</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>bgb</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Bitget Token</t>
+          <t>Ethereum Classic</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2.12</v>
+        <v>9.34</v>
       </c>
       <c r="F65" t="n">
-        <v>1484368859</v>
+        <v>1478692181</v>
       </c>
       <c r="G65" t="n">
         <v>64</v>
       </c>
       <c r="H65" t="n">
-        <v>21371401</v>
+        <v>105301995</v>
       </c>
       <c r="I65" t="n">
-        <v>2.15</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="J65" t="n">
-        <v>2</v>
+        <v>8.56</v>
       </c>
       <c r="K65" t="n">
-        <v>0.105322</v>
+        <v>0.556522</v>
       </c>
       <c r="L65" t="n">
-        <v>5.22639</v>
+        <v>6.33342</v>
       </c>
       <c r="M65" t="n">
-        <v>699992029.6481038</v>
+        <v>158251635.651071</v>
       </c>
       <c r="N65" t="n">
-        <v>910920874.6481038</v>
+        <v>158251635.651071</v>
       </c>
       <c r="O65" t="n">
-        <v>8.449999999999999</v>
-      </c>
-      <c r="P65" s="2" t="n">
-        <v>45653.15375</v>
-      </c>
-      <c r="Q65" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>167.09</v>
+      </c>
+      <c r="P65" s="1" t="n">
+        <v>44322.44053240741</v>
+      </c>
+      <c r="Q65" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S65" t="n">
-        <v>0.0005048960171943381</v>
-      </c>
-      <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr"/>
-      <c r="X65" t="inlineStr"/>
-      <c r="Y65" t="inlineStr"/>
-      <c r="Z65" t="inlineStr"/>
-      <c r="AA65" t="inlineStr"/>
+        <v>0.000491871699313813</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Plataforma de contratos inteligentes</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Layer 1</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Proof of Work</t>
+        </is>
+      </c>
+      <c r="W65" t="n">
+        <v>2016</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>ethereumclassic.org</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>Contratos inteligentes (cadena original)</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>Blockchain propia (fork de Ethereum)</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>Mantiene la cadena original de Ethereum tras la bifurcación de 2016.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>united-stables</t>
+          <t>bitget-token</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>bgb</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>United Stables</t>
+          <t>Bitget Token</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.999817</v>
+        <v>2.11</v>
       </c>
       <c r="F66" t="n">
-        <v>1412321040</v>
+        <v>1475117403</v>
       </c>
       <c r="G66" t="n">
         <v>65</v>
       </c>
       <c r="H66" t="n">
-        <v>232093814</v>
+        <v>16504894</v>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>2.18</v>
       </c>
       <c r="J66" t="n">
-        <v>0.999466</v>
+        <v>2.08</v>
       </c>
       <c r="K66" t="n">
-        <v>6.242e-05</v>
+        <v>-0.04551146207062784</v>
       </c>
       <c r="L66" t="n">
-        <v>0.00624</v>
+        <v>-2.09981</v>
       </c>
       <c r="M66" t="n">
-        <v>1412429007.8</v>
+        <v>699992029.6481038</v>
       </c>
       <c r="N66" t="n">
-        <v>1412429007.8</v>
+        <v>910920874.6481038</v>
       </c>
       <c r="O66" t="n">
-        <v>1.008</v>
-      </c>
-      <c r="P66" s="2" t="n">
-        <v>46058.54591435185</v>
-      </c>
-      <c r="Q66" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>8.449999999999999</v>
+      </c>
+      <c r="P66" s="1" t="n">
+        <v>45653.15375</v>
+      </c>
+      <c r="Q66" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R66" t="b">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0.0004632029723221382</v>
+        <v>0.0004898079390794154</v>
       </c>
       <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr"/>
@@ -6287,7 +6305,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6309,7 +6327,7 @@
         <v>1.16</v>
       </c>
       <c r="F67" t="n">
-        <v>1406563294</v>
+        <v>1449857663</v>
       </c>
       <c r="G67" t="n">
         <v>66</v>
@@ -6324,31 +6342,31 @@
         <v>1.16</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.000997568167990126</v>
+        <v>-0.001720484800925348</v>
       </c>
       <c r="L67" t="n">
-        <v>-0.08579000000000001</v>
+        <v>-0.14811</v>
       </c>
       <c r="M67" t="n">
-        <v>1210660472.36437</v>
+        <v>1249985019.14243</v>
       </c>
       <c r="N67" t="n">
-        <v>1210660472.36437</v>
+        <v>1249985019.14243</v>
       </c>
       <c r="O67" t="n">
         <v>1.18</v>
       </c>
-      <c r="P67" s="2" t="n">
+      <c r="P67" s="1" t="n">
         <v>46255.48263888889</v>
       </c>
-      <c r="Q67" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q67" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R67" t="b">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.0004598710468638433</v>
+        <v>0.0004752252022092601</v>
       </c>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
@@ -6362,68 +6380,68 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>usdgo</t>
+          <t>united-stables</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>usdgo</t>
+          <t>u</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>USDGO</t>
+          <t>United Stables</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.9997509999999999</v>
+        <v>0.999519</v>
       </c>
       <c r="F68" t="n">
-        <v>1404123443</v>
+        <v>1418612169</v>
       </c>
       <c r="G68" t="n">
         <v>67</v>
       </c>
       <c r="H68" t="n">
-        <v>42030632</v>
+        <v>160832716</v>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>0.999923</v>
       </c>
       <c r="J68" t="n">
-        <v>0.999719</v>
+        <v>0.999328</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.000266318963444978</v>
+        <v>-0.000312985174393487</v>
       </c>
       <c r="L68" t="n">
-        <v>-0.02663</v>
+        <v>-0.03296</v>
       </c>
       <c r="M68" t="n">
-        <v>1403784804.97</v>
+        <v>1419429007.8</v>
       </c>
       <c r="N68" t="n">
-        <v>1403784804.97</v>
+        <v>1419429007.8</v>
       </c>
       <c r="O68" t="n">
-        <v>1.002</v>
-      </c>
-      <c r="P68" s="2" t="n">
-        <v>46092.00303240741</v>
-      </c>
-      <c r="Q68" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>1.008</v>
+      </c>
+      <c r="P68" s="1" t="n">
+        <v>46058.54591435185</v>
+      </c>
+      <c r="Q68" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R68" t="b">
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0.0004584591399021005</v>
+        <v>0.000457186821078654</v>
       </c>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
@@ -6437,112 +6455,82 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ethereum-classic</t>
+          <t>usdgo</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>usdgo</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Ethereum Classic</t>
+          <t>USDGO</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>8.779999999999999</v>
+        <v>0.9997819999999999</v>
       </c>
       <c r="F69" t="n">
-        <v>1387516750</v>
+        <v>1403486151</v>
       </c>
       <c r="G69" t="n">
         <v>68</v>
       </c>
       <c r="H69" t="n">
-        <v>73190996</v>
+        <v>81824505</v>
       </c>
       <c r="I69" t="n">
-        <v>8.85</v>
+        <v>1.001</v>
       </c>
       <c r="J69" t="n">
-        <v>8.369999999999999</v>
+        <v>0.999711</v>
       </c>
       <c r="K69" t="n">
-        <v>0.351076</v>
+        <v>6.707000000000001e-05</v>
       </c>
       <c r="L69" t="n">
-        <v>4.16573</v>
+        <v>-0.05448</v>
       </c>
       <c r="M69" t="n">
-        <v>158238312.7479364</v>
+        <v>1403784805.97</v>
       </c>
       <c r="N69" t="n">
-        <v>158238719.9927364</v>
+        <v>1403784805.97</v>
       </c>
       <c r="O69" t="n">
-        <v>167.09</v>
-      </c>
-      <c r="P69" s="2" t="n">
-        <v>44322.44053240741</v>
-      </c>
-      <c r="Q69" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>1.002</v>
+      </c>
+      <c r="P69" s="1" t="n">
+        <v>46092.00303240741</v>
+      </c>
+      <c r="Q69" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R69" t="b">
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>0.0004488490836084069</v>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Plataforma de contratos inteligentes</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Layer 1</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Proof of Work</t>
-        </is>
-      </c>
-      <c r="W69" t="n">
-        <v>2016</v>
-      </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>ethereumclassic.org</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>Contratos inteligentes (cadena original)</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>Blockchain propia (fork de Ethereum)</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>Mantiene la cadena original de Ethereum tras la bifurcación de 2016.</t>
-        </is>
-      </c>
+        <v>0.0004484543978475663</v>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr"/>
+      <c r="X69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6561,28 +6549,28 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.996047</v>
+        <v>0.995766</v>
       </c>
       <c r="F70" t="n">
-        <v>1371628457</v>
+        <v>1371171784</v>
       </c>
       <c r="G70" t="n">
         <v>69</v>
       </c>
       <c r="H70" t="n">
-        <v>899679</v>
+        <v>346364</v>
       </c>
       <c r="I70" t="n">
-        <v>0.996566</v>
+        <v>0.996614</v>
       </c>
       <c r="J70" t="n">
-        <v>0.995507</v>
+        <v>0.995093</v>
       </c>
       <c r="K70" t="n">
-        <v>0.00023299</v>
+        <v>-0.000223555758983696</v>
       </c>
       <c r="L70" t="n">
-        <v>0.0234</v>
+        <v>-0.02179</v>
       </c>
       <c r="M70" t="n">
         <v>1377035569.737884</v>
@@ -6593,17 +6581,17 @@
       <c r="O70" t="n">
         <v>1.075</v>
       </c>
-      <c r="P70" s="2" t="n">
+      <c r="P70" s="1" t="n">
         <v>45785.55951388889</v>
       </c>
-      <c r="Q70" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q70" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R70" t="b">
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>0.0004396547551445341</v>
+        <v>0.0004297989441062914</v>
       </c>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
@@ -6617,7 +6605,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6636,28 +6624,28 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.999924</v>
+        <v>0.999819</v>
       </c>
       <c r="F71" t="n">
-        <v>1319931512</v>
+        <v>1319746233</v>
       </c>
       <c r="G71" t="n">
         <v>70</v>
       </c>
       <c r="H71" t="n">
-        <v>4921075</v>
+        <v>9371061</v>
       </c>
       <c r="I71" t="n">
-        <v>0.999837</v>
+        <v>0.999993</v>
       </c>
       <c r="J71" t="n">
-        <v>0.99952</v>
+        <v>0.999553</v>
       </c>
       <c r="K71" t="n">
-        <v>0.00035509</v>
+        <v>4.122e-05</v>
       </c>
       <c r="L71" t="n">
-        <v>0.03552</v>
+        <v>0.00457</v>
       </c>
       <c r="M71" t="n">
         <v>1320000000</v>
@@ -6668,17 +6656,17 @@
       <c r="O71" t="n">
         <v>1.007</v>
       </c>
-      <c r="P71" s="2" t="n">
+      <c r="P71" s="1" t="n">
         <v>45940.56990740741</v>
       </c>
-      <c r="Q71" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q71" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R71" t="b">
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>0.0004097384706885029</v>
+        <v>0.0004001103852123458</v>
       </c>
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
@@ -6692,7 +6680,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6711,28 +6699,28 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4.98</v>
+        <v>4.94</v>
       </c>
       <c r="F72" t="n">
-        <v>1243289462</v>
+        <v>1235200763</v>
       </c>
       <c r="G72" t="n">
         <v>71</v>
       </c>
       <c r="H72" t="n">
-        <v>96086565</v>
+        <v>78427779</v>
       </c>
       <c r="I72" t="n">
-        <v>5.14</v>
+        <v>4.93</v>
       </c>
       <c r="J72" t="n">
-        <v>4.65</v>
+        <v>4.64</v>
       </c>
       <c r="K72" t="n">
-        <v>0.29391</v>
+        <v>0.213891</v>
       </c>
       <c r="L72" t="n">
-        <v>6.2781</v>
+        <v>4.4898</v>
       </c>
       <c r="M72" t="n">
         <v>250000000</v>
@@ -6743,17 +6731,17 @@
       <c r="O72" t="n">
         <v>7.86</v>
       </c>
-      <c r="P72" s="2" t="n">
+      <c r="P72" s="1" t="n">
         <v>46021.04538194444</v>
       </c>
-      <c r="Q72" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q72" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>0.0003653868098873982</v>
+        <v>0.0003513013181921147</v>
       </c>
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
@@ -6767,68 +6755,68 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>polygon-ecosystem-token</t>
+          <t>gatechain-token</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>pol</t>
+          <t>gt</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>POL (ex-MATIC)</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.113591</v>
+        <v>11.07</v>
       </c>
       <c r="F73" t="n">
-        <v>1215803428</v>
+        <v>1183284695</v>
       </c>
       <c r="G73" t="n">
         <v>72</v>
       </c>
       <c r="H73" t="n">
-        <v>183440017</v>
+        <v>3660555</v>
       </c>
       <c r="I73" t="n">
-        <v>0.114508</v>
+        <v>11.26</v>
       </c>
       <c r="J73" t="n">
-        <v>0.104</v>
+        <v>10.77</v>
       </c>
       <c r="K73" t="n">
-        <v>0.0096837</v>
+        <v>-0.168040860000696</v>
       </c>
       <c r="L73" t="n">
-        <v>9.319520000000001</v>
+        <v>-1.49436</v>
       </c>
       <c r="M73" t="n">
-        <v>10718173594.42111</v>
+        <v>106637271.2738255</v>
       </c>
       <c r="N73" t="n">
-        <v>10718173594.42111</v>
+        <v>118888593.6983193</v>
       </c>
       <c r="O73" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P73" s="2" t="n">
-        <v>45364.45493055556</v>
-      </c>
-      <c r="Q73" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>25.38</v>
+      </c>
+      <c r="P73" s="1" t="n">
+        <v>45682.66666666666</v>
+      </c>
+      <c r="Q73" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0.0003494810341841697</v>
+        <v>0.0003213295782226181</v>
       </c>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
@@ -6842,7 +6830,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6861,28 +6849,28 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.052968</v>
+        <v>0.051642</v>
       </c>
       <c r="F74" t="n">
-        <v>1210389596</v>
+        <v>1177171406</v>
       </c>
       <c r="G74" t="n">
         <v>73</v>
       </c>
       <c r="H74" t="n">
-        <v>117071699</v>
+        <v>43908083</v>
       </c>
       <c r="I74" t="n">
-        <v>0.06970899999999999</v>
+        <v>0.06265900000000001</v>
       </c>
       <c r="J74" t="n">
-        <v>0.03148813</v>
+        <v>0.04882322</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.000541111920599274</v>
+        <v>-0.003907926662397344</v>
       </c>
       <c r="L74" t="n">
-        <v>-1.01126</v>
+        <v>-6.42521</v>
       </c>
       <c r="M74" t="n">
         <v>22796250000</v>
@@ -6893,17 +6881,17 @@
       <c r="O74" t="n">
         <v>0.146656</v>
       </c>
-      <c r="P74" s="2" t="n">
+      <c r="P74" s="1" t="n">
         <v>46285.43993055556</v>
       </c>
-      <c r="Q74" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q74" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S74" t="n">
-        <v>0.0003463481268506867</v>
+        <v>0.0003178003065476835</v>
       </c>
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
@@ -6917,68 +6905,68 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>kaspa</t>
+          <t>polygon-ecosystem-token</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>kas</t>
+          <t>pol</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Kaspa</t>
+          <t>POL (ex-MATIC)</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.04256497</v>
+        <v>0.108775</v>
       </c>
       <c r="F75" t="n">
-        <v>1181593079</v>
+        <v>1166941505</v>
       </c>
       <c r="G75" t="n">
         <v>74</v>
       </c>
       <c r="H75" t="n">
-        <v>22251594</v>
+        <v>80978742</v>
       </c>
       <c r="I75" t="n">
-        <v>0.04197595</v>
+        <v>0.112923</v>
       </c>
       <c r="J75" t="n">
-        <v>0.0386518</v>
+        <v>0.106356</v>
       </c>
       <c r="K75" t="n">
-        <v>0.00356807</v>
+        <v>-0.003040010552261871</v>
       </c>
       <c r="L75" t="n">
-        <v>9.149609999999999</v>
+        <v>-2.75053</v>
       </c>
       <c r="M75" t="n">
-        <v>27710766029.85906</v>
+        <v>10718755191.33206</v>
       </c>
       <c r="N75" t="n">
-        <v>27713280689.21</v>
+        <v>10718755191.33206</v>
       </c>
       <c r="O75" t="n">
-        <v>0.207411</v>
-      </c>
-      <c r="P75" s="2" t="n">
-        <v>45504.69498842592</v>
-      </c>
-      <c r="Q75" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>1.29</v>
+      </c>
+      <c r="P75" s="1" t="n">
+        <v>45364.45493055556</v>
+      </c>
+      <c r="Q75" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>0.0003296839933334172</v>
+        <v>0.0003118944676716404</v>
       </c>
       <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr"/>
@@ -6992,68 +6980,68 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>gatechain-token</t>
+          <t>kaspa</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>gt</t>
+          <t>kas</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Kaspa</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>11.04</v>
+        <v>0.04167618</v>
       </c>
       <c r="F76" t="n">
-        <v>1177930690</v>
+        <v>1155383815</v>
       </c>
       <c r="G76" t="n">
         <v>75</v>
       </c>
       <c r="H76" t="n">
-        <v>6827786</v>
+        <v>24976867</v>
       </c>
       <c r="I76" t="n">
-        <v>11.4</v>
+        <v>0.04460429</v>
       </c>
       <c r="J76" t="n">
-        <v>10.34</v>
+        <v>0.04133447</v>
       </c>
       <c r="K76" t="n">
-        <v>0.713846</v>
+        <v>-0.001949097888989622</v>
       </c>
       <c r="L76" t="n">
-        <v>6.91129</v>
+        <v>-4.53567</v>
       </c>
       <c r="M76" t="n">
-        <v>106635883.2020504</v>
+        <v>27714964311.97035</v>
       </c>
       <c r="N76" t="n">
-        <v>118887115.3090956</v>
+        <v>27715665348.36042</v>
       </c>
       <c r="O76" t="n">
-        <v>25.38</v>
-      </c>
-      <c r="P76" s="2" t="n">
-        <v>45682.66666666666</v>
-      </c>
-      <c r="Q76" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>0.207411</v>
+      </c>
+      <c r="P76" s="1" t="n">
+        <v>45504.69498842592</v>
+      </c>
+      <c r="Q76" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R76" t="b">
         <v>1</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0003275646210743284</v>
+        <v>0.0003052220810161631</v>
       </c>
       <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr"/>
@@ -7067,173 +7055,173 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>algorand</t>
+          <t>quant-network</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>algo</t>
+          <t>qnt</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Algorand</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.112858</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="F77" t="n">
-        <v>1018245871</v>
+        <v>1076099999</v>
       </c>
       <c r="G77" t="n">
         <v>76</v>
       </c>
       <c r="H77" t="n">
-        <v>91425780</v>
+        <v>25158205</v>
       </c>
       <c r="I77" t="n">
-        <v>0.117367</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="J77" t="n">
-        <v>0.107695</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>-0.000398156635310759</v>
+        <v>6.39</v>
       </c>
       <c r="L77" t="n">
-        <v>-0.35155</v>
+        <v>9.54158</v>
       </c>
       <c r="M77" t="n">
-        <v>9042435038.282944</v>
+        <v>14544176.16408117</v>
       </c>
       <c r="N77" t="n">
-        <v>9042705520.702909</v>
+        <v>14612493</v>
       </c>
       <c r="O77" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="P77" s="2" t="n">
-        <v>43636.28563657407</v>
-      </c>
-      <c r="Q77" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>427.42</v>
+      </c>
+      <c r="P77" s="1" t="n">
+        <v>44450.05208333334</v>
+      </c>
+      <c r="Q77" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0002351572947127058</v>
+        <v>0.0002594506270427726</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>Plataforma de contratos inteligentes</t>
+          <t>Interoperabilidad</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>Layer 1</t>
+          <t>Infraestructura empresarial</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>Pure Proof of Stake</t>
+          <t>N/A (token ERC-20)</t>
         </is>
       </c>
       <c r="W77" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>algorand.com</t>
+          <t>quant.network</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>Contratos inteligentes de alta eficiencia</t>
+          <t>Interoperabilidad entre redes empresariales</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>Blockchain propia (Layer 1)</t>
+          <t>Token ERC-20 sobre Ethereum</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>Fundada por Silvio Micali, ganador del Premio Turing.</t>
+          <t>Su tecnología Overledger busca conectar múltiples blockchains y redes existentes.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>jupiter-exchange-solana</t>
+          <t>pi-network</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>jup</t>
+          <t>pi</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Pi Network</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.306944</v>
+        <v>0.090235</v>
       </c>
       <c r="F78" t="n">
-        <v>1016626399</v>
+        <v>1014603162</v>
       </c>
       <c r="G78" t="n">
         <v>77</v>
       </c>
       <c r="H78" t="n">
-        <v>126703075</v>
+        <v>12821473</v>
       </c>
       <c r="I78" t="n">
-        <v>0.317727</v>
+        <v>0.094476</v>
       </c>
       <c r="J78" t="n">
-        <v>0.271277</v>
+        <v>0.087199</v>
       </c>
       <c r="K78" t="n">
-        <v>0.03662334</v>
+        <v>0.00027014</v>
       </c>
       <c r="L78" t="n">
-        <v>13.5481</v>
+        <v>0.28909</v>
       </c>
       <c r="M78" t="n">
-        <v>3319369204.37</v>
+        <v>11243022455.381</v>
       </c>
       <c r="N78" t="n">
-        <v>6861486876.193287</v>
+        <v>17296957623.66307</v>
       </c>
       <c r="O78" t="n">
-        <v>2</v>
-      </c>
-      <c r="P78" s="2" t="n">
-        <v>45322.29359953704</v>
-      </c>
-      <c r="Q78" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>2.99</v>
+      </c>
+      <c r="P78" s="1" t="n">
+        <v>45714.36184027778</v>
+      </c>
+      <c r="Q78" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>0.0002342201293730407</v>
+        <v>0.000223947799526819</v>
       </c>
       <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr"/>
@@ -7247,292 +7235,292 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>pi-network</t>
+          <t>kucoin-shares</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>pi</t>
+          <t>kcs</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Pi Network</t>
+          <t>KuCoin</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.089172</v>
+        <v>7.38</v>
       </c>
       <c r="F79" t="n">
-        <v>1000832394</v>
+        <v>1013044584</v>
       </c>
       <c r="G79" t="n">
         <v>78</v>
       </c>
       <c r="H79" t="n">
-        <v>8282429</v>
+        <v>30103529</v>
       </c>
       <c r="I79" t="n">
-        <v>0.090407</v>
+        <v>7.47</v>
       </c>
       <c r="J79" t="n">
-        <v>0.08477800000000001</v>
+        <v>7.28</v>
       </c>
       <c r="K79" t="n">
-        <v>0.00432623</v>
+        <v>0.063027</v>
       </c>
       <c r="L79" t="n">
-        <v>5.09892</v>
+        <v>0.87298</v>
       </c>
       <c r="M79" t="n">
-        <v>11243021168.581</v>
+        <v>137155021.2773955</v>
       </c>
       <c r="N79" t="n">
-        <v>17296955494.70923</v>
+        <v>142155021.2773955</v>
       </c>
       <c r="O79" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="P79" s="2" t="n">
-        <v>45714.36184027778</v>
-      </c>
-      <c r="Q79" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>28.83</v>
+      </c>
+      <c r="P79" s="1" t="n">
+        <v>44531.29832175926</v>
+      </c>
+      <c r="Q79" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R79" t="b">
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0002250803640294603</v>
-      </c>
-      <c r="T79" t="inlineStr"/>
-      <c r="U79" t="inlineStr"/>
-      <c r="V79" t="inlineStr"/>
-      <c r="W79" t="inlineStr"/>
-      <c r="X79" t="inlineStr"/>
-      <c r="Y79" t="inlineStr"/>
-      <c r="Z79" t="inlineStr"/>
-      <c r="AA79" t="inlineStr"/>
+        <v>0.0002230480146174885</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Token de exchange</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Utilidad</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>N/A (token de exchange)</t>
+        </is>
+      </c>
+      <c r="W79" t="n">
+        <v>2017</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>kucoin.com</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>Beneficios en el exchange KuCoin</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>Token ERC-20 sobre Ethereum</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>Otorga descuentos en comisiones dentro del exchange KuCoin.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>kucoin-shares</t>
+          <t>algorand</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>kcs</t>
+          <t>algo</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>KuCoin</t>
+          <t>Algorand</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>7.24</v>
+        <v>0.111659</v>
       </c>
       <c r="F80" t="n">
-        <v>991808381</v>
+        <v>1009834244</v>
       </c>
       <c r="G80" t="n">
         <v>79</v>
       </c>
       <c r="H80" t="n">
-        <v>42457066</v>
+        <v>61193587</v>
       </c>
       <c r="I80" t="n">
-        <v>7.34</v>
+        <v>0.113177</v>
       </c>
       <c r="J80" t="n">
-        <v>7.08</v>
+        <v>0.108049</v>
       </c>
       <c r="K80" t="n">
-        <v>0.123972</v>
+        <v>-0.000111053877648204</v>
       </c>
       <c r="L80" t="n">
-        <v>1.74107</v>
+        <v>-0.07658</v>
       </c>
       <c r="M80" t="n">
-        <v>137155021.2773955</v>
+        <v>9042752944.706263</v>
       </c>
       <c r="N80" t="n">
-        <v>142155021.2773955</v>
+        <v>9055595374.037592</v>
       </c>
       <c r="O80" t="n">
-        <v>28.83</v>
-      </c>
-      <c r="P80" s="2" t="n">
-        <v>44531.29832175926</v>
-      </c>
-      <c r="Q80" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>3.56</v>
+      </c>
+      <c r="P80" s="1" t="n">
+        <v>43636.28563657407</v>
+      </c>
+      <c r="Q80" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R80" t="b">
         <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>0.0002198582964615814</v>
+        <v>0.0002211946486096146</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>Token de exchange</t>
+          <t>Plataforma de contratos inteligentes</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>Utilidad</t>
+          <t>Layer 1</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>N/A (token de exchange)</t>
+          <t>Pure Proof of Stake</t>
         </is>
       </c>
       <c r="W80" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>kucoin.com</t>
+          <t>algorand.com</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>Beneficios en el exchange KuCoin</t>
+          <t>Contratos inteligentes de alta eficiencia</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>Token ERC-20 sobre Ethereum</t>
+          <t>Blockchain propia (Layer 1)</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>Otorga descuentos en comisiones dentro del exchange KuCoin.</t>
+          <t>Fundada por Silvio Micali, ganador del Premio Turing.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>quant-network</t>
+          <t>jupiter-exchange-solana</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>qnt</t>
+          <t>jup</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>67.02</v>
+        <v>0.29984</v>
       </c>
       <c r="F81" t="n">
-        <v>974120723</v>
+        <v>995820975</v>
       </c>
       <c r="G81" t="n">
         <v>80</v>
       </c>
       <c r="H81" t="n">
-        <v>11479032</v>
+        <v>87853850</v>
       </c>
       <c r="I81" t="n">
-        <v>67.93000000000001</v>
+        <v>0.30265</v>
       </c>
       <c r="J81" t="n">
-        <v>63.8</v>
+        <v>0.288725</v>
       </c>
       <c r="K81" t="n">
-        <v>2.88</v>
+        <v>0.00421596</v>
       </c>
       <c r="L81" t="n">
-        <v>4.48507</v>
+        <v>1.43657</v>
       </c>
       <c r="M81" t="n">
-        <v>14544176.16408117</v>
+        <v>3319369204.37</v>
       </c>
       <c r="N81" t="n">
-        <v>14612493</v>
+        <v>6861486746.959235</v>
       </c>
       <c r="O81" t="n">
-        <v>427.42</v>
-      </c>
-      <c r="P81" s="2" t="n">
-        <v>44450.05208333334</v>
-      </c>
-      <c r="Q81" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>2</v>
+      </c>
+      <c r="P81" s="1" t="n">
+        <v>45322.29359953704</v>
+      </c>
+      <c r="Q81" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R81" t="b">
         <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0.0002096227011456687</v>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Interoperabilidad</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Infraestructura empresarial</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>N/A (token ERC-20)</t>
-        </is>
-      </c>
-      <c r="W81" t="n">
-        <v>2018</v>
-      </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>quant.network</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>Interoperabilidad entre redes empresariales</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>Token ERC-20 sobre Ethereum</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>Su tecnología Overledger busca conectar múltiples blockchains y redes existentes.</t>
-        </is>
-      </c>
+        <v>0.0002131046281059314</v>
+      </c>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7551,10 +7539,10 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106.54</v>
+        <v>107.53</v>
       </c>
       <c r="F82" t="n">
-        <v>970804306</v>
+        <v>979825296</v>
       </c>
       <c r="G82" t="n">
         <v>81</v>
@@ -7563,16 +7551,16 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>106.54</v>
+        <v>107.53</v>
       </c>
       <c r="J82" t="n">
         <v>106.54</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>0.92923</v>
       </c>
       <c r="M82" t="n">
         <v>9112111</v>
@@ -7581,19 +7569,19 @@
         <v>9112111</v>
       </c>
       <c r="O82" t="n">
-        <v>106.54</v>
-      </c>
-      <c r="P82" s="2" t="n">
-        <v>46280.14583333334</v>
-      </c>
-      <c r="Q82" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>107.53</v>
+      </c>
+      <c r="P82" s="1" t="n">
+        <v>46287.17361111111</v>
+      </c>
+      <c r="Q82" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R82" t="b">
         <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0.0002077035379466282</v>
+        <v>0.0002038701396307346</v>
       </c>
       <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr"/>
@@ -7607,7 +7595,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7629,13 +7617,13 @@
         <v>1.8</v>
       </c>
       <c r="F83" t="n">
-        <v>957099766</v>
+        <v>959212434</v>
       </c>
       <c r="G83" t="n">
         <v>82</v>
       </c>
       <c r="H83" t="n">
-        <v>77080955</v>
+        <v>70655057</v>
       </c>
       <c r="I83" t="n">
         <v>1.82</v>
@@ -7644,31 +7632,31 @@
         <v>1.73</v>
       </c>
       <c r="K83" t="n">
-        <v>0.06481000000000001</v>
+        <v>-0.001444649463477665</v>
       </c>
       <c r="L83" t="n">
-        <v>3.73722</v>
+        <v>-0.10442</v>
       </c>
       <c r="M83" t="n">
-        <v>531968735.793199</v>
+        <v>532132124.756035</v>
       </c>
       <c r="N83" t="n">
-        <v>531981425.106379</v>
+        <v>532132124.756035</v>
       </c>
       <c r="O83" t="n">
         <v>43.84</v>
       </c>
-      <c r="P83" s="2" t="n">
+      <c r="P83" s="1" t="n">
         <v>44458.66666666666</v>
       </c>
-      <c r="Q83" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q83" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R83" t="b">
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.0001997729161859215</v>
+        <v>0.0001919700985896619</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -7712,68 +7700,68 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>just</t>
+          <t>render-token</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>jst</t>
+          <t>render</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>JUST</t>
+          <t>Render</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.113382</v>
+        <v>1.83</v>
       </c>
       <c r="F84" t="n">
-        <v>928875168</v>
+        <v>948369207</v>
       </c>
       <c r="G84" t="n">
         <v>83</v>
       </c>
       <c r="H84" t="n">
-        <v>41477573</v>
+        <v>88794504</v>
       </c>
       <c r="I84" t="n">
-        <v>0.116713</v>
+        <v>1.9</v>
       </c>
       <c r="J84" t="n">
-        <v>0.111332</v>
+        <v>1.79</v>
       </c>
       <c r="K84" t="n">
-        <v>-0.002727350903736575</v>
+        <v>-0.01793686036568287</v>
       </c>
       <c r="L84" t="n">
-        <v>-2.34894</v>
+        <v>-0.99483</v>
       </c>
       <c r="M84" t="n">
-        <v>8188743036.341737</v>
+        <v>518776241.2826915</v>
       </c>
       <c r="N84" t="n">
-        <v>8188743036.341737</v>
+        <v>533536414.5626915</v>
       </c>
       <c r="O84" t="n">
-        <v>0.193254</v>
-      </c>
-      <c r="P84" s="2" t="n">
-        <v>44290.85721064815</v>
-      </c>
-      <c r="Q84" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>13.53</v>
+      </c>
+      <c r="P84" s="1" t="n">
+        <v>45368.35444444444</v>
+      </c>
+      <c r="Q84" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R84" t="b">
         <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0.0001834397440337735</v>
+        <v>0.0001857101795974489</v>
       </c>
       <c r="T84" t="inlineStr"/>
       <c r="U84" t="inlineStr"/>
@@ -7787,68 +7775,68 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>render-token</t>
+          <t>just</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>render</t>
+          <t>jst</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Render</t>
+          <t>JUST</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1.78</v>
+        <v>0.112577</v>
       </c>
       <c r="F85" t="n">
-        <v>919580013</v>
+        <v>921852139</v>
       </c>
       <c r="G85" t="n">
         <v>84</v>
       </c>
       <c r="H85" t="n">
-        <v>170326835</v>
+        <v>37182180</v>
       </c>
       <c r="I85" t="n">
-        <v>1.83</v>
+        <v>0.117046</v>
       </c>
       <c r="J85" t="n">
-        <v>1.57</v>
+        <v>0.112159</v>
       </c>
       <c r="K85" t="n">
-        <v>0.216485</v>
+        <v>7.262000000000001e-05</v>
       </c>
       <c r="L85" t="n">
-        <v>13.88918</v>
+        <v>0.06308</v>
       </c>
       <c r="M85" t="n">
-        <v>518776241.2826915</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="N85" t="n">
-        <v>533536414.5626915</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="O85" t="n">
-        <v>13.53</v>
-      </c>
-      <c r="P85" s="2" t="n">
-        <v>45368.35444444444</v>
-      </c>
-      <c r="Q85" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>0.193254</v>
+      </c>
+      <c r="P85" s="1" t="n">
+        <v>44290.85721064815</v>
+      </c>
+      <c r="Q85" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>0.0001780607704591667</v>
+        <v>0.000170401572889224</v>
       </c>
       <c r="T85" t="inlineStr"/>
       <c r="U85" t="inlineStr"/>
@@ -7862,7 +7850,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7881,28 +7869,28 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.8806079999999999</v>
+        <v>0.878642</v>
       </c>
       <c r="F86" t="n">
-        <v>879827644</v>
+        <v>879051060</v>
       </c>
       <c r="G86" t="n">
         <v>85</v>
       </c>
       <c r="H86" t="n">
-        <v>7817219</v>
+        <v>5612054</v>
       </c>
       <c r="I86" t="n">
-        <v>0.87577</v>
+        <v>0.896209</v>
       </c>
       <c r="J86" t="n">
-        <v>0.819816</v>
+        <v>0.857331</v>
       </c>
       <c r="K86" t="n">
-        <v>0.060156</v>
+        <v>-0.004406381170605767</v>
       </c>
       <c r="L86" t="n">
-        <v>7.33199</v>
+        <v>-0.56166</v>
       </c>
       <c r="M86" t="n">
         <v>1000000000</v>
@@ -7913,17 +7901,17 @@
       <c r="O86" t="n">
         <v>4.07</v>
       </c>
-      <c r="P86" s="2" t="n">
+      <c r="P86" s="1" t="n">
         <v>44328.27623842593</v>
       </c>
-      <c r="Q86" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q86" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0.0001550566417083263</v>
+        <v>0.0001456920203437215</v>
       </c>
       <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr"/>
@@ -7937,82 +7925,82 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>pancakeswap-token</t>
+          <t>filecoin</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>cake</t>
+          <t>fil</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>PancakeSwap</t>
+          <t>Filecoin</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2.61</v>
+        <v>1.015</v>
       </c>
       <c r="F87" t="n">
-        <v>832854645</v>
+        <v>844623999</v>
       </c>
       <c r="G87" t="n">
         <v>86</v>
       </c>
       <c r="H87" t="n">
-        <v>136695825</v>
+        <v>220605992</v>
       </c>
       <c r="I87" t="n">
-        <v>2.62</v>
+        <v>1.033</v>
       </c>
       <c r="J87" t="n">
-        <v>2.45</v>
+        <v>0.974393</v>
       </c>
       <c r="K87" t="n">
-        <v>0.151086</v>
+        <v>0.03620424</v>
       </c>
       <c r="L87" t="n">
-        <v>6.13663</v>
+        <v>3.72256</v>
       </c>
       <c r="M87" t="n">
-        <v>318981673.778035</v>
+        <v>830751171</v>
       </c>
       <c r="N87" t="n">
-        <v>330627631.6127986</v>
+        <v>1957034255</v>
       </c>
       <c r="O87" t="n">
-        <v>43.96</v>
-      </c>
-      <c r="P87" s="2" t="n">
-        <v>44316.08914351852</v>
-      </c>
-      <c r="Q87" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>236.84</v>
+      </c>
+      <c r="P87" s="1" t="n">
+        <v>44287.22894675926</v>
+      </c>
+      <c r="Q87" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>0.0001278740374009177</v>
+        <v>0.0001258168841873008</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>DeFi</t>
+          <t>Almacenamiento descentralizado</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>Exchange descentralizado</t>
+          <t>Infraestructura Web3</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>N/A (token BEP-20)</t>
+          <t>Proof-of-Replication/Spacetime</t>
         </is>
       </c>
       <c r="W87" t="n">
@@ -8020,345 +8008,375 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>pancakeswap.finance</t>
+          <t>filecoin.io</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>Intercambio descentralizado en BNB Chain</t>
+          <t>Almacenamiento descentralizado de archivos</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>Token BEP-20 sobre BNB Chain</t>
+          <t>Blockchain propia (Layer 1)</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>Principal exchange descentralizado (DEX) del ecosistema BNB Chain.</t>
+          <t>Recompensa a quienes ofrecen espacio de almacenamiento descentralizado.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>filecoin</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>fil</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Filecoin</t>
+          <t>Dash</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.968076</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="F88" t="n">
-        <v>803262272</v>
+        <v>823802913</v>
       </c>
       <c r="G88" t="n">
         <v>87</v>
       </c>
       <c r="H88" t="n">
-        <v>201765623</v>
+        <v>217954738</v>
       </c>
       <c r="I88" t="n">
-        <v>1.015</v>
+        <v>64.89</v>
       </c>
       <c r="J88" t="n">
-        <v>0.926796</v>
+        <v>58.18</v>
       </c>
       <c r="K88" t="n">
-        <v>0.04226669</v>
+        <v>5.44</v>
       </c>
       <c r="L88" t="n">
-        <v>4.56538</v>
+        <v>9.115830000000001</v>
       </c>
       <c r="M88" t="n">
-        <v>830669925</v>
+        <v>12842808.78359296</v>
       </c>
       <c r="N88" t="n">
-        <v>1957036618</v>
+        <v>12842814.69092887</v>
       </c>
       <c r="O88" t="n">
-        <v>236.84</v>
-      </c>
-      <c r="P88" s="2" t="n">
-        <v>44287.22894675926</v>
-      </c>
-      <c r="Q88" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>1493.59</v>
+      </c>
+      <c r="P88" s="1" t="n">
+        <v>43088.66666666666</v>
+      </c>
+      <c r="Q88" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S88" t="n">
-        <v>0.0001107493533717748</v>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>Almacenamiento descentralizado</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>Infraestructura Web3</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>Proof-of-Replication/Spacetime</t>
-        </is>
-      </c>
-      <c r="W88" t="n">
-        <v>2020</v>
-      </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>filecoin.io</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>Almacenamiento descentralizado de archivos</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Layer 1)</t>
-        </is>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>Recompensa a quienes ofrecen espacio de almacenamiento descentralizado.</t>
-        </is>
-      </c>
+        <v>0.0001137966330489725</v>
+      </c>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="inlineStr"/>
+      <c r="X88" t="inlineStr"/>
+      <c r="Y88" t="inlineStr"/>
+      <c r="Z88" t="inlineStr"/>
+      <c r="AA88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>eutbl</t>
+          <t>pancakeswap-token</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>eutbl</t>
+          <t>cake</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Spiko EU T-Bills Money Market Fund</t>
+          <t>PancakeSwap</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1.21</v>
+        <v>2.54</v>
       </c>
       <c r="F89" t="n">
-        <v>784718961</v>
+        <v>812122971</v>
       </c>
       <c r="G89" t="n">
         <v>88</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>91419688</v>
       </c>
       <c r="I89" t="n">
-        <v>1.22</v>
+        <v>2.59</v>
       </c>
       <c r="J89" t="n">
-        <v>1.21</v>
+        <v>2.46</v>
       </c>
       <c r="K89" t="n">
-        <v>-0.000973066503648035</v>
+        <v>0.00034305</v>
       </c>
       <c r="L89" t="n">
-        <v>-0.08003</v>
+        <v>0.02274</v>
       </c>
       <c r="M89" t="n">
-        <v>645949689.8613</v>
+        <v>318995589.2344064</v>
       </c>
       <c r="N89" t="n">
-        <v>645949689.8613</v>
+        <v>330627631.6090779</v>
       </c>
       <c r="O89" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P89" s="2" t="n">
-        <v>46049.54175925926</v>
-      </c>
-      <c r="Q89" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>43.96</v>
+      </c>
+      <c r="P89" s="1" t="n">
+        <v>44316.08914351852</v>
+      </c>
+      <c r="Q89" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R89" t="b">
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>0.0001000186038732764</v>
-      </c>
-      <c r="T89" t="inlineStr"/>
-      <c r="U89" t="inlineStr"/>
-      <c r="V89" t="inlineStr"/>
-      <c r="W89" t="inlineStr"/>
-      <c r="X89" t="inlineStr"/>
-      <c r="Y89" t="inlineStr"/>
-      <c r="Z89" t="inlineStr"/>
-      <c r="AA89" t="inlineStr"/>
+        <v>0.0001070536689153482</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>DeFi</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Exchange descentralizado</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>N/A (token BEP-20)</t>
+        </is>
+      </c>
+      <c r="W89" t="n">
+        <v>2020</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>pancakeswap.finance</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>Intercambio descentralizado en BNB Chain</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>Token BEP-20 sobre BNB Chain</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>Principal exchange descentralizado (DEX) del ecosistema BNB Chain.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>janus-henderson-anemoy-aaa-clo-fund</t>
+          <t>vechain</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>jaaa</t>
+          <t>vet</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy AAA CLO Fund</t>
+          <t>VeChain</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1.05</v>
+        <v>0.0092481</v>
       </c>
       <c r="F90" t="n">
-        <v>776845619</v>
+        <v>796072690</v>
       </c>
       <c r="G90" t="n">
         <v>89</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>16039748</v>
       </c>
       <c r="I90" t="n">
-        <v>1.05</v>
+        <v>0.0093454</v>
       </c>
       <c r="J90" t="n">
-        <v>1.05</v>
+        <v>0.00888102</v>
       </c>
       <c r="K90" t="n">
-        <v>0.000508</v>
+        <v>0.00011927</v>
       </c>
       <c r="L90" t="n">
-        <v>0.04839</v>
+        <v>1.21252</v>
       </c>
       <c r="M90" t="n">
-        <v>739569820.670837</v>
+        <v>85985041177</v>
       </c>
       <c r="N90" t="n">
-        <v>739569820.670837</v>
+        <v>85985041177</v>
       </c>
       <c r="O90" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="P90" s="2" t="n">
-        <v>46286.30578703704</v>
-      </c>
-      <c r="Q90" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>0.280991</v>
+      </c>
+      <c r="P90" s="1" t="n">
+        <v>44304.71413194444</v>
+      </c>
+      <c r="Q90" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R90" t="b">
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>9.546241319524659e-05</v>
-      </c>
-      <c r="T90" t="inlineStr"/>
-      <c r="U90" t="inlineStr"/>
-      <c r="V90" t="inlineStr"/>
-      <c r="W90" t="inlineStr"/>
-      <c r="X90" t="inlineStr"/>
-      <c r="Y90" t="inlineStr"/>
-      <c r="Z90" t="inlineStr"/>
-      <c r="AA90" t="inlineStr"/>
+        <v>9.778765808091152e-05</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Cadena de suministro</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Trazabilidad</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Proof of Authority</t>
+        </is>
+      </c>
+      <c r="W90" t="n">
+        <v>2015</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>vechain.org</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>Trazabilidad de productos y logística</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Layer 1)</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>Enfocada en trazabilidad de cadenas de suministro para empresas.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>injective-protocol</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>inj</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Dash</t>
+          <t>Injective</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>60.37</v>
+        <v>7.8</v>
       </c>
       <c r="F91" t="n">
-        <v>774060503</v>
+        <v>780922158</v>
       </c>
       <c r="G91" t="n">
         <v>90</v>
       </c>
       <c r="H91" t="n">
-        <v>161994185</v>
+        <v>162120178</v>
       </c>
       <c r="I91" t="n">
-        <v>61.42</v>
+        <v>7.99</v>
       </c>
       <c r="J91" t="n">
-        <v>54.89</v>
+        <v>7.5</v>
       </c>
       <c r="K91" t="n">
-        <v>5.44</v>
+        <v>0.04412324</v>
       </c>
       <c r="L91" t="n">
-        <v>9.900130000000001</v>
+        <v>0.52981</v>
       </c>
       <c r="M91" t="n">
-        <v>12841975.17033605</v>
+        <v>100000000</v>
       </c>
       <c r="N91" t="n">
-        <v>12841989.85954539</v>
+        <v>100000000</v>
       </c>
       <c r="O91" t="n">
-        <v>1493.59</v>
-      </c>
-      <c r="P91" s="2" t="n">
-        <v>43088.66666666666</v>
-      </c>
-      <c r="Q91" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>52.62</v>
+      </c>
+      <c r="P91" s="1" t="n">
+        <v>45365.29608796296</v>
+      </c>
+      <c r="Q91" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>9.385070630426795e-05</v>
+        <v>8.904108263718691e-05</v>
       </c>
       <c r="T91" t="inlineStr"/>
       <c r="U91" t="inlineStr"/>
@@ -8372,68 +8390,68 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>injective-protocol</t>
+          <t>eutbl</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>inj</t>
+          <t>eutbl</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Injective</t>
+          <t>Spiko EU T-Bills Money Market Fund</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>7.71</v>
+        <v>1.21</v>
       </c>
       <c r="F92" t="n">
-        <v>769674354</v>
+        <v>779781851</v>
       </c>
       <c r="G92" t="n">
         <v>91</v>
       </c>
       <c r="H92" t="n">
-        <v>187091879</v>
+        <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>8.199999999999999</v>
+        <v>1.22</v>
       </c>
       <c r="J92" t="n">
-        <v>7.58</v>
+        <v>1.21</v>
       </c>
       <c r="K92" t="n">
-        <v>-0.2849914879713022</v>
+        <v>-0.001829979194463149</v>
       </c>
       <c r="L92" t="n">
-        <v>-3.56668</v>
+        <v>-0.15067</v>
       </c>
       <c r="M92" t="n">
-        <v>100000000</v>
+        <v>642998758.0930901</v>
       </c>
       <c r="N92" t="n">
-        <v>100000000</v>
+        <v>642998758.0930901</v>
       </c>
       <c r="O92" t="n">
-        <v>52.62</v>
-      </c>
-      <c r="P92" s="2" t="n">
-        <v>45365.29608796296</v>
-      </c>
-      <c r="Q92" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>1.26</v>
+      </c>
+      <c r="P92" s="1" t="n">
+        <v>46049.54175925926</v>
+      </c>
+      <c r="Q92" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R92" t="b">
         <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>9.131250445983524e-05</v>
+        <v>8.838277036112245e-05</v>
       </c>
       <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr"/>
@@ -8447,173 +8465,143 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>vechain</t>
+          <t>superstate-short-duration-us-government-securities-fund-ustb</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>vet</t>
+          <t>ustb</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VeChain</t>
+          <t>Invesco Short Duration US Government Securities Fund</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.00893233</v>
+        <v>11.22</v>
       </c>
       <c r="F93" t="n">
-        <v>767070561</v>
+        <v>733945028</v>
       </c>
       <c r="G93" t="n">
         <v>92</v>
       </c>
       <c r="H93" t="n">
-        <v>18904924</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>0.00909602</v>
+        <v>11.22</v>
       </c>
       <c r="J93" t="n">
-        <v>0.008248190000000001</v>
+        <v>11.22</v>
       </c>
       <c r="K93" t="n">
-        <v>0.00070602</v>
+        <v>0.003219</v>
       </c>
       <c r="L93" t="n">
-        <v>8.58253</v>
+        <v>0.0287</v>
       </c>
       <c r="M93" t="n">
-        <v>85985041177</v>
+        <v>65413837.965085</v>
       </c>
       <c r="N93" t="n">
-        <v>85985041177</v>
+        <v>65413837.965085</v>
       </c>
       <c r="O93" t="n">
-        <v>0.280991</v>
-      </c>
-      <c r="P93" s="2" t="n">
-        <v>44304.71413194444</v>
-      </c>
-      <c r="Q93" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>11.22</v>
+      </c>
+      <c r="P93" s="1" t="n">
+        <v>46287.57291666666</v>
+      </c>
+      <c r="Q93" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>8.980572660182791e-05</v>
-      </c>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>Cadena de suministro</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>Trazabilidad</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>Proof of Authority</t>
-        </is>
-      </c>
-      <c r="W93" t="n">
-        <v>2015</v>
-      </c>
-      <c r="X93" t="inlineStr">
-        <is>
-          <t>vechain.org</t>
-        </is>
-      </c>
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>Trazabilidad de productos y logística</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Layer 1)</t>
-        </is>
-      </c>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>Enfocada en trazabilidad de cadenas de suministro para empresas.</t>
-        </is>
-      </c>
+        <v>6.192064807590162e-05</v>
+      </c>
+      <c r="T93" t="inlineStr"/>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr"/>
+      <c r="W93" t="inlineStr"/>
+      <c r="X93" t="inlineStr"/>
+      <c r="Y93" t="inlineStr"/>
+      <c r="Z93" t="inlineStr"/>
+      <c r="AA93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>superstate-short-duration-us-government-securities-fund-ustb</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ustb</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Invesco Short Duration US Government Securities Fund</t>
+          <t>GHO</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>11.22</v>
+        <v>0.999159</v>
       </c>
       <c r="F94" t="n">
-        <v>720195294</v>
+        <v>698406630</v>
       </c>
       <c r="G94" t="n">
         <v>93</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>4739386</v>
       </c>
       <c r="I94" t="n">
-        <v>11.22</v>
+        <v>0.999281</v>
       </c>
       <c r="J94" t="n">
-        <v>11.22</v>
+        <v>0.998814</v>
       </c>
       <c r="K94" t="n">
-        <v>0.001094</v>
+        <v>0.00020014</v>
       </c>
       <c r="L94" t="n">
-        <v>0.00975</v>
+        <v>0.02062</v>
       </c>
       <c r="M94" t="n">
-        <v>64206795.204266</v>
+        <v>699000000</v>
       </c>
       <c r="N94" t="n">
-        <v>64206795.204266</v>
+        <v>699000000</v>
       </c>
       <c r="O94" t="n">
-        <v>11.22</v>
-      </c>
-      <c r="P94" s="2" t="n">
-        <v>46286.55219907407</v>
-      </c>
-      <c r="Q94" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>1.03</v>
+      </c>
+      <c r="P94" s="1" t="n">
+        <v>45350.38608796296</v>
+      </c>
+      <c r="Q94" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R94" t="b">
         <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>6.267967840837254e-05</v>
+        <v>4.140392435582949e-05</v>
       </c>
       <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
@@ -8627,143 +8615,173 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ether-fi</t>
+          <t>aptos</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ethfi</t>
+          <t>apt</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Ether.fi</t>
+          <t>Aptos</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.724214</v>
+        <v>0.797092</v>
       </c>
       <c r="F95" t="n">
-        <v>698709596</v>
+        <v>694745959</v>
       </c>
       <c r="G95" t="n">
         <v>94</v>
       </c>
       <c r="H95" t="n">
-        <v>55805811</v>
+        <v>156133688</v>
       </c>
       <c r="I95" t="n">
-        <v>0.769383</v>
+        <v>0.80848</v>
       </c>
       <c r="J95" t="n">
-        <v>0.704524</v>
+        <v>0.748675</v>
       </c>
       <c r="K95" t="n">
-        <v>0.0248904</v>
+        <v>0.01777609</v>
       </c>
       <c r="L95" t="n">
-        <v>3.55921</v>
+        <v>2.38927</v>
       </c>
       <c r="M95" t="n">
-        <v>965350000</v>
+        <v>870646072.2327943</v>
       </c>
       <c r="N95" t="n">
-        <v>965350000</v>
+        <v>1209086276.864642</v>
       </c>
       <c r="O95" t="n">
-        <v>8.529999999999999</v>
-      </c>
-      <c r="P95" s="2" t="n">
-        <v>45378.63525462963</v>
-      </c>
-      <c r="Q95" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>19.92</v>
+      </c>
+      <c r="P95" s="1" t="n">
+        <v>44952.26755787037</v>
+      </c>
+      <c r="Q95" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R95" t="b">
         <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>5.024621153514861e-05</v>
-      </c>
-      <c r="T95" t="inlineStr"/>
-      <c r="U95" t="inlineStr"/>
-      <c r="V95" t="inlineStr"/>
-      <c r="W95" t="inlineStr"/>
-      <c r="X95" t="inlineStr"/>
-      <c r="Y95" t="inlineStr"/>
-      <c r="Z95" t="inlineStr"/>
-      <c r="AA95" t="inlineStr"/>
+        <v>3.929057710992718e-05</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Plataforma de contratos inteligentes</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Layer 1</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Proof of Stake (BFT)</t>
+        </is>
+      </c>
+      <c r="W95" t="n">
+        <v>2022</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>aptosfoundation.org</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>Contratos inteligentes de alto rendimiento</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Layer 1)</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>Desarrollada por exingenieros del proyecto Diem (Meta/Facebook).</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>janus-henderson-anemoy-aaa-clo-fund</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>jaaa</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>GHO</t>
+          <t>Janus Henderson Anemoy AAA CLO Fund</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.999173</v>
+        <v>1.05</v>
       </c>
       <c r="F96" t="n">
-        <v>698438859</v>
+        <v>677692166</v>
       </c>
       <c r="G96" t="n">
         <v>95</v>
       </c>
       <c r="H96" t="n">
-        <v>5302269</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>0.999187</v>
+        <v>1.05</v>
       </c>
       <c r="J96" t="n">
-        <v>0.9988320000000001</v>
+        <v>1.05</v>
       </c>
       <c r="K96" t="n">
-        <v>0.00023127</v>
+        <v>7.4e-05</v>
       </c>
       <c r="L96" t="n">
-        <v>0.02315</v>
+        <v>0.00704</v>
       </c>
       <c r="M96" t="n">
-        <v>699000000</v>
+        <v>645128652.594015</v>
       </c>
       <c r="N96" t="n">
-        <v>699000000</v>
+        <v>645128652.594015</v>
       </c>
       <c r="O96" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="P96" s="2" t="n">
-        <v>45350.38608796296</v>
-      </c>
-      <c r="Q96" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>1.05</v>
+      </c>
+      <c r="P96" s="1" t="n">
+        <v>46287.38530092593</v>
+      </c>
+      <c r="Q96" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R96" t="b">
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>5.008953989614223e-05</v>
+        <v>2.944522731784314e-05</v>
       </c>
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
@@ -8777,7 +8795,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8796,31 +8814,31 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.686856</v>
+        <v>0.681867</v>
       </c>
       <c r="F97" t="n">
-        <v>681820872</v>
+        <v>677295717</v>
       </c>
       <c r="G97" t="n">
         <v>96</v>
       </c>
       <c r="H97" t="n">
-        <v>56831776</v>
+        <v>52560213</v>
       </c>
       <c r="I97" t="n">
-        <v>0.6991810000000001</v>
+        <v>0.717605</v>
       </c>
       <c r="J97" t="n">
-        <v>0.648524</v>
+        <v>0.673687</v>
       </c>
       <c r="K97" t="n">
-        <v>0.02865724</v>
+        <v>-0.006533631426253295</v>
       </c>
       <c r="L97" t="n">
-        <v>4.35389</v>
+        <v>-0.9434</v>
       </c>
       <c r="M97" t="n">
-        <v>992665694.3208704</v>
+        <v>992642375.2273064</v>
       </c>
       <c r="N97" t="n">
         <v>1983240735.576791</v>
@@ -8828,17 +8846,17 @@
       <c r="O97" t="n">
         <v>2.32</v>
       </c>
-      <c r="P97" s="2" t="n">
+      <c r="P97" s="1" t="n">
         <v>45633.25043981482</v>
       </c>
-      <c r="Q97" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q97" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R97" t="b">
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>4.047294792579218e-05</v>
+        <v>2.921635277481791e-05</v>
       </c>
       <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr"/>
@@ -8852,68 +8870,68 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>stable-2</t>
+          <t>ether-fi</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>ethfi</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>​​Stable</t>
+          <t>Ether.fi</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.02539244</v>
+        <v>0.694674</v>
       </c>
       <c r="F98" t="n">
-        <v>673849676</v>
+        <v>670843751</v>
       </c>
       <c r="G98" t="n">
         <v>97</v>
       </c>
       <c r="H98" t="n">
-        <v>10507115</v>
+        <v>51398286</v>
       </c>
       <c r="I98" t="n">
-        <v>0.02655115</v>
+        <v>0.7237980000000001</v>
       </c>
       <c r="J98" t="n">
-        <v>0.02444799</v>
+        <v>0.679153</v>
       </c>
       <c r="K98" t="n">
-        <v>0.0009418299999999999</v>
+        <v>-0.01384730796520994</v>
       </c>
       <c r="L98" t="n">
-        <v>3.85196</v>
+        <v>-1.8656</v>
       </c>
       <c r="M98" t="n">
-        <v>26522995541</v>
+        <v>965350000</v>
       </c>
       <c r="N98" t="n">
-        <v>100000000000</v>
+        <v>965350000</v>
       </c>
       <c r="O98" t="n">
-        <v>0.04323745</v>
-      </c>
-      <c r="P98" s="2" t="n">
-        <v>46156.97986111111</v>
-      </c>
-      <c r="Q98" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>8.529999999999999</v>
+      </c>
+      <c r="P98" s="1" t="n">
+        <v>45378.63525462963</v>
+      </c>
+      <c r="Q98" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R98" t="b">
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>3.586013053414983e-05</v>
+        <v>2.549155899336217e-05</v>
       </c>
       <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr"/>
@@ -8927,112 +8945,82 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>aptos</t>
+          <t>stable-2</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>apt</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Aptos</t>
+          <t>​​Stable</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.771625</v>
+        <v>0.0244496</v>
       </c>
       <c r="F99" t="n">
-        <v>671274865</v>
+        <v>649555722</v>
       </c>
       <c r="G99" t="n">
         <v>98</v>
       </c>
       <c r="H99" t="n">
-        <v>181966908</v>
+        <v>8832998</v>
       </c>
       <c r="I99" t="n">
-        <v>0.790511</v>
+        <v>0.02532359</v>
       </c>
       <c r="J99" t="n">
-        <v>0.721949</v>
+        <v>0.02415728</v>
       </c>
       <c r="K99" t="n">
-        <v>0.050075</v>
+        <v>-0.000240188203144351</v>
       </c>
       <c r="L99" t="n">
-        <v>6.93996</v>
+        <v>-1.00191</v>
       </c>
       <c r="M99" t="n">
-        <v>870586041.4259734</v>
+        <v>26560136831</v>
       </c>
       <c r="N99" t="n">
-        <v>1209026324.181685</v>
+        <v>100000000000</v>
       </c>
       <c r="O99" t="n">
-        <v>19.92</v>
-      </c>
-      <c r="P99" s="2" t="n">
-        <v>44952.26755787037</v>
-      </c>
-      <c r="Q99" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>0.04323745</v>
+      </c>
+      <c r="P99" s="1" t="n">
+        <v>46156.97986111111</v>
+      </c>
+      <c r="Q99" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>3.437012414602539e-05</v>
-      </c>
-      <c r="T99" t="inlineStr">
-        <is>
-          <t>Plataforma de contratos inteligentes</t>
-        </is>
-      </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>Layer 1</t>
-        </is>
-      </c>
-      <c r="V99" t="inlineStr">
-        <is>
-          <t>Proof of Stake (BFT)</t>
-        </is>
-      </c>
-      <c r="W99" t="n">
-        <v>2022</v>
-      </c>
-      <c r="X99" t="inlineStr">
-        <is>
-          <t>aptosfoundation.org</t>
-        </is>
-      </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>Contratos inteligentes de alto rendimiento</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Layer 1)</t>
-        </is>
-      </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>Desarrollada por exingenieros del proyecto Diem (Meta/Facebook).</t>
-        </is>
-      </c>
+        <v>1.320173631936647e-05</v>
+      </c>
+      <c r="T99" t="inlineStr"/>
+      <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr"/>
+      <c r="W99" t="inlineStr"/>
+      <c r="X99" t="inlineStr"/>
+      <c r="Y99" t="inlineStr"/>
+      <c r="Z99" t="inlineStr"/>
+      <c r="AA99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9051,49 +9039,49 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.330374</v>
+        <v>0.335931</v>
       </c>
       <c r="F100" t="n">
-        <v>618216922</v>
+        <v>628228951</v>
       </c>
       <c r="G100" t="n">
         <v>99</v>
       </c>
       <c r="H100" t="n">
-        <v>35672699</v>
+        <v>34548808</v>
       </c>
       <c r="I100" t="n">
-        <v>0.34015</v>
+        <v>0.353654</v>
       </c>
       <c r="J100" t="n">
-        <v>0.30827</v>
+        <v>0.332299</v>
       </c>
       <c r="K100" t="n">
-        <v>0.01942084</v>
+        <v>-0.008535159644705137</v>
       </c>
       <c r="L100" t="n">
-        <v>6.24558</v>
+        <v>-2.52239</v>
       </c>
       <c r="M100" t="n">
-        <v>1868230389.165669</v>
+        <v>1868553460.192209</v>
       </c>
       <c r="N100" t="n">
-        <v>1868230389.165669</v>
+        <v>1868553460.192209</v>
       </c>
       <c r="O100" t="n">
         <v>3.86</v>
       </c>
-      <c r="P100" s="2" t="n">
+      <c r="P100" s="1" t="n">
         <v>45383.19094907407</v>
       </c>
-      <c r="Q100" s="2" t="n">
-        <v>46286.65775462963</v>
+      <c r="Q100" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>3.666249566204706e-06</v>
+        <v>8.895474455673138e-07</v>
       </c>
       <c r="T100" t="inlineStr"/>
       <c r="U100" t="inlineStr"/>
@@ -9107,62 +9095,62 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>official-trump</t>
+          <t>pudgy-penguins</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>trump</t>
+          <t>pengu</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Official Trump</t>
+          <t>Pudgy Penguins</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2.18</v>
+        <v>0.00996264</v>
       </c>
       <c r="F101" t="n">
-        <v>611881446</v>
+        <v>626688106</v>
       </c>
       <c r="G101" t="n">
         <v>100</v>
       </c>
       <c r="H101" t="n">
-        <v>311874452</v>
+        <v>486369273</v>
       </c>
       <c r="I101" t="n">
-        <v>2.19</v>
+        <v>0.01047348</v>
       </c>
       <c r="J101" t="n">
-        <v>2.03</v>
+        <v>0.008669339999999999</v>
       </c>
       <c r="K101" t="n">
-        <v>0.14939</v>
+        <v>0.00129078</v>
       </c>
       <c r="L101" t="n">
-        <v>7.37318</v>
+        <v>14.87479</v>
       </c>
       <c r="M101" t="n">
-        <v>281867936.287634</v>
+        <v>62860396090</v>
       </c>
       <c r="N101" t="n">
-        <v>1000000000</v>
+        <v>76722815225.58829</v>
       </c>
       <c r="O101" t="n">
-        <v>73.43000000000001</v>
-      </c>
-      <c r="P101" s="2" t="n">
-        <v>45676.16011574074</v>
-      </c>
-      <c r="Q101" s="2" t="n">
-        <v>46286.65775462963</v>
+        <v>0.06844699999999999</v>
+      </c>
+      <c r="P101" s="1" t="n">
+        <v>45643.21206018519</v>
+      </c>
+      <c r="Q101" s="1" t="n">
+        <v>46287.91469907408</v>
       </c>
       <c r="R101" t="b">
         <v>1</v>

--- a/src/xlsx/enriched_data.xlsx
+++ b/src/xlsx/enriched_data.xlsx
@@ -560,7 +560,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -579,28 +579,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>86238</v>
+        <v>86091</v>
       </c>
       <c r="F2" t="n">
-        <v>1732793991467</v>
+        <v>1729404845826</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>43485131868</v>
+        <v>43292611645</v>
       </c>
       <c r="I2" t="n">
-        <v>86722</v>
+        <v>86669</v>
       </c>
       <c r="J2" t="n">
         <v>85107</v>
       </c>
       <c r="K2" t="n">
-        <v>-377.4880582667683</v>
+        <v>-493.3569849451887</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.42991</v>
+        <v>-0.5698</v>
       </c>
       <c r="M2" t="n">
         <v>20088034</v>
@@ -615,7 +615,7 @@
         <v>45936.45673611111</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
@@ -665,7 +665,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -684,16 +684,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2748.95</v>
+        <v>2740.68</v>
       </c>
       <c r="F3" t="n">
-        <v>335700394407</v>
+        <v>334532231831</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>16208315503</v>
+        <v>16217849740</v>
       </c>
       <c r="I3" t="n">
         <v>2786.01</v>
@@ -702,10 +702,10 @@
         <v>2716.11</v>
       </c>
       <c r="K3" t="n">
-        <v>-21.36690103358978</v>
+        <v>-33.60544003023369</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.75097</v>
+        <v>-1.21132</v>
       </c>
       <c r="M3" t="n">
         <v>122070499.1930826</v>
@@ -720,13 +720,13 @@
         <v>45893.47295138889</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1934418838473869</v>
+        <v>0.1931470913741057</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -789,16 +789,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999898</v>
+        <v>0.999907</v>
       </c>
       <c r="F4" t="n">
-        <v>183363689877</v>
+        <v>183365485085</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>78958984976</v>
+        <v>78653569988</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -807,10 +807,10 @@
         <v>0.999627</v>
       </c>
       <c r="K4" t="n">
-        <v>6.751e-05</v>
+        <v>0.00010509</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00721</v>
+        <v>0.01051</v>
       </c>
       <c r="M4" t="n">
         <v>183384649781.6938</v>
@@ -825,13 +825,13 @@
         <v>43304.66666666666</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1054961616100404</v>
+        <v>0.1057058956148769</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -894,31 +894,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>784.49</v>
+        <v>783.59</v>
       </c>
       <c r="F5" t="n">
-        <v>104509508003</v>
+        <v>104365737195</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1338733134</v>
+        <v>1332694189</v>
       </c>
       <c r="I5" t="n">
-        <v>806.75</v>
+        <v>803.09</v>
       </c>
       <c r="J5" t="n">
         <v>781.83</v>
       </c>
       <c r="K5" t="n">
-        <v>-20.06454466473849</v>
+        <v>-21.77282668240503</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.48689</v>
+        <v>-2.70348</v>
       </c>
       <c r="M5" t="n">
-        <v>133160045.24</v>
+        <v>133160043.94</v>
       </c>
       <c r="N5" t="n">
         <v>133160043.94</v>
@@ -930,13 +930,13 @@
         <v>45943.02875</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.05997274033254849</v>
+        <v>0.06000912321700162</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -999,16 +999,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="F6" t="n">
-        <v>98935861541</v>
+        <v>97984064776</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>6013941970</v>
+        <v>6102739669</v>
       </c>
       <c r="I6" t="n">
         <v>1.61</v>
@@ -1017,10 +1017,10 @@
         <v>1.49</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02050936</v>
+        <v>-0.003611992187942059</v>
       </c>
       <c r="L6" t="n">
-        <v>1.26594</v>
+        <v>-0.23129</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -1035,13 +1035,13 @@
         <v>45855.82005787037</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R6" t="b">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05675501046824196</v>
+        <v>0.05631769584112064</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1104,34 +1104,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999892</v>
+        <v>0.999896</v>
       </c>
       <c r="F7" t="n">
-        <v>75082614224</v>
+        <v>75083335862</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>20211770616</v>
+        <v>20036837511</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999695</v>
+        <v>0.999744</v>
       </c>
       <c r="K7" t="n">
-        <v>8.51e-06</v>
+        <v>3.21e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00201</v>
+        <v>0.00321</v>
       </c>
       <c r="M7" t="n">
         <v>75091582641.99438</v>
       </c>
       <c r="N7" t="n">
-        <v>75091431783.64163</v>
+        <v>75118327863.70384</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -1140,13 +1140,13 @@
         <v>43418.66666666666</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04298425791407672</v>
+        <v>0.04307095234029781</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1209,16 +1209,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>118.13</v>
+        <v>117.81</v>
       </c>
       <c r="F8" t="n">
-        <v>69442081520</v>
+        <v>69220864144</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>4713073391</v>
+        <v>4526147359</v>
       </c>
       <c r="I8" t="n">
         <v>119.82</v>
@@ -1227,13 +1227,13 @@
         <v>115.58</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.022544647266727</v>
+        <v>-1.566908205533849</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.84705</v>
+        <v>-1.31262</v>
       </c>
       <c r="M8" t="n">
-        <v>587507395.8954812</v>
+        <v>587507355.8515188</v>
       </c>
       <c r="N8" t="n">
         <v>634531021.326126</v>
@@ -1245,13 +1245,13 @@
         <v>45676.13572916666</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R8" t="b">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03972791385709364</v>
+        <v>0.03967985245780897</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1314,16 +1314,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.34165</v>
+        <v>0.341646</v>
       </c>
       <c r="F9" t="n">
-        <v>32442198365</v>
+        <v>32445098179</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>605341752</v>
+        <v>609223370</v>
       </c>
       <c r="I9" t="n">
         <v>0.349178</v>
@@ -1332,10 +1332,10 @@
         <v>0.34041</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.002637683000221824</v>
+        <v>-0.002577573979136272</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.75484</v>
+        <v>-0.74881</v>
       </c>
       <c r="M9" t="n">
         <v>94961729708.24278</v>
@@ -1350,13 +1350,13 @@
         <v>45629.67407407407</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01836745803783905</v>
+        <v>0.01840720473493112</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1419,16 +1419,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1518.81</v>
+        <v>1517.69</v>
       </c>
       <c r="F10" t="n">
-        <v>25756147448</v>
+        <v>25711477168</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>1389815932</v>
+        <v>1293999353</v>
       </c>
       <c r="I10" t="n">
         <v>1562.57</v>
@@ -1437,10 +1437,10 @@
         <v>1445.89</v>
       </c>
       <c r="K10" t="n">
-        <v>56.04</v>
+        <v>51.21</v>
       </c>
       <c r="L10" t="n">
-        <v>3.7356</v>
+        <v>3.49205</v>
       </c>
       <c r="M10" t="n">
         <v>16945106.4155448</v>
@@ -1455,13 +1455,13 @@
         <v>42671.66666666666</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R10" t="b">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01450752435589808</v>
+        <v>0.01451219551057677</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1527,13 +1527,13 @@
         <v>1.039</v>
       </c>
       <c r="F11" t="n">
-        <v>23858934286</v>
+        <v>23851750157</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>83847558</v>
+        <v>84486417</v>
       </c>
       <c r="I11" t="n">
         <v>1.043</v>
@@ -1542,10 +1542,10 @@
         <v>1.006</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0261228</v>
+        <v>0.02578041</v>
       </c>
       <c r="L11" t="n">
-        <v>2.57897</v>
+        <v>2.54554</v>
       </c>
       <c r="M11" t="n">
         <v>22966221270.418</v>
@@ -1560,13 +1560,13 @@
         <v>46237.59675925926</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R11" t="b">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01341224149360253</v>
+        <v>0.01343645129349168</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
@@ -1580,7 +1580,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1599,28 +1599,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>97.31999999999999</v>
+        <v>96.73</v>
       </c>
       <c r="F12" t="n">
-        <v>21655414643</v>
+        <v>21532342792</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1249913907</v>
+        <v>1239088705</v>
       </c>
       <c r="I12" t="n">
-        <v>96.87</v>
+        <v>97.72</v>
       </c>
       <c r="J12" t="n">
         <v>92.19</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>3.56</v>
       </c>
       <c r="L12" t="n">
-        <v>4.26103</v>
+        <v>3.81642</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1635,13 +1635,13 @@
         <v>46287.91296296296</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R12" t="b">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01214012439571919</v>
+        <v>0.01209480865174627</v>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
@@ -1655,7 +1655,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1674,16 +1674,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.100125</v>
+        <v>0.09957199999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>15635492125</v>
+        <v>15542670956</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>2382661626</v>
+        <v>2351774773</v>
       </c>
       <c r="I13" t="n">
         <v>0.105575</v>
@@ -1692,16 +1692,16 @@
         <v>0.097356</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00082386</v>
+        <v>-0.000911816708137669</v>
       </c>
       <c r="L13" t="n">
-        <v>0.82324</v>
+        <v>-0.90742</v>
       </c>
       <c r="M13" t="n">
         <v>156025536383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171737883126.579</v>
+        <v>171738483126.579</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1710,13 +1710,13 @@
         <v>44323.88082175926</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R13" t="b">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.008664754258943556</v>
+        <v>0.00863013087823274</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1779,16 +1779,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>567.3</v>
+        <v>565.58</v>
       </c>
       <c r="F14" t="n">
-        <v>10671971138</v>
+        <v>10647327594</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>163415960</v>
+        <v>162542598</v>
       </c>
       <c r="I14" t="n">
         <v>601.01</v>
@@ -1797,13 +1797,13 @@
         <v>561.65</v>
       </c>
       <c r="K14" t="n">
-        <v>-29.0335298218157</v>
+        <v>-29.14801141764497</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.86632</v>
+        <v>-4.90107</v>
       </c>
       <c r="M14" t="n">
-        <v>18808120.908502</v>
+        <v>18808149.70786505</v>
       </c>
       <c r="N14" t="n">
         <v>18808149.70786505</v>
@@ -1815,13 +1815,13 @@
         <v>46036.48202546296</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R14" t="b">
         <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.005799256811110969</v>
+        <v>0.005798458659047338</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1884,16 +1884,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>86.68000000000001</v>
+        <v>86.51000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>10304856260</v>
+        <v>10282998071</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>148065627</v>
+        <v>147623670</v>
       </c>
       <c r="I15" t="n">
         <v>87.28</v>
@@ -1902,10 +1902,10 @@
         <v>85.56999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4387106662780695</v>
+        <v>-0.6142900680501384</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.49605</v>
+        <v>-0.70508</v>
       </c>
       <c r="M15" t="n">
         <v>118852171</v>
@@ -1920,13 +1920,13 @@
         <v>46286.85358796296</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.005587317192294894</v>
+        <v>0.005587715160048591</v>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
@@ -1940,7 +1940,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1959,16 +1959,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>12.91</v>
+        <v>12.87</v>
       </c>
       <c r="F16" t="n">
-        <v>9671530693</v>
+        <v>9628433562</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>581165005</v>
+        <v>579744023</v>
       </c>
       <c r="I16" t="n">
         <v>13.26</v>
@@ -1977,10 +1977,10 @@
         <v>12.78</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2186754109027937</v>
+        <v>-0.2855421127928377</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.64853</v>
+        <v>-2.17079</v>
       </c>
       <c r="M16" t="n">
         <v>748099970.424884</v>
@@ -1995,13 +1995,13 @@
         <v>44325.67635416667</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R16" t="b">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.005221691097303301</v>
+        <v>0.005209087554437127</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2064,16 +2064,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.999922</v>
+        <v>0.999928</v>
       </c>
       <c r="F17" t="n">
-        <v>9592786193</v>
+        <v>9591907549</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>247011578</v>
+        <v>246657449</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
@@ -2082,16 +2082,16 @@
         <v>0.999729</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.5729221229095e-05</v>
+        <v>-0.000119341335104495</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.00507</v>
+        <v>-0.01193</v>
       </c>
       <c r="M17" t="n">
         <v>9593648553.437454</v>
       </c>
       <c r="N17" t="n">
-        <v>9593648553.437454</v>
+        <v>9595406974.451723</v>
       </c>
       <c r="O17" t="n">
         <v>1.057</v>
@@ -2100,13 +2100,13 @@
         <v>45593.90336805556</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.005176230996626415</v>
+        <v>0.005187959374319553</v>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
@@ -2120,7 +2120,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2139,16 +2139,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.251416</v>
+        <v>0.250084</v>
       </c>
       <c r="F18" t="n">
-        <v>9443905073</v>
+        <v>9387066598</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>878661987</v>
+        <v>878118215</v>
       </c>
       <c r="I18" t="n">
         <v>0.253817</v>
@@ -2157,10 +2157,10 @@
         <v>0.240769</v>
       </c>
       <c r="K18" t="n">
-        <v>0.00659619</v>
+        <v>0.00426462</v>
       </c>
       <c r="L18" t="n">
-        <v>2.72814</v>
+        <v>1.73486</v>
       </c>
       <c r="M18" t="n">
         <v>37529061988.53558</v>
@@ -2175,13 +2175,13 @@
         <v>44440.91678240741</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R18" t="b">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.005090280222869678</v>
+        <v>0.00506947076434772</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.01309167</v>
+        <v>0.01306924</v>
       </c>
       <c r="F19" t="n">
-        <v>9284605249</v>
+        <v>9265634480</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>24775479</v>
+        <v>24665700</v>
       </c>
       <c r="I19" t="n">
         <v>0.01400767</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0130726</v>
+        <v>0.0130548</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.000864517740068033</v>
+        <v>-0.000895503351973326</v>
       </c>
       <c r="L19" t="n">
-        <v>-6.27118</v>
+        <v>-6.4126</v>
       </c>
       <c r="M19" t="n">
-        <v>709239749032.6418</v>
+        <v>709239749688.8101</v>
       </c>
       <c r="N19" t="n">
         <v>1142408526965.963</v>
@@ -2280,13 +2280,13 @@
         <v>46259.82847222222</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R19" t="b">
         <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>0.004998314612105115</v>
+        <v>0.004999229326795736</v>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
@@ -2300,7 +2300,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2322,13 +2322,13 @@
         <v>8.98</v>
       </c>
       <c r="F20" t="n">
-        <v>8260445947</v>
+        <v>8256209354</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>127098</v>
+        <v>122371</v>
       </c>
       <c r="I20" t="n">
         <v>9</v>
@@ -2337,10 +2337,10 @@
         <v>8.880000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.02568804</v>
+        <v>0.02214698</v>
       </c>
       <c r="L20" t="n">
-        <v>0.28873</v>
+        <v>0.24736</v>
       </c>
       <c r="M20" t="n">
         <v>919857851.9</v>
@@ -2355,13 +2355,13 @@
         <v>46146.39930555555</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.004407055730810693</v>
+        <v>0.004415335435137412</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2424,31 +2424,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.215138</v>
+        <v>0.213671</v>
       </c>
       <c r="F21" t="n">
-        <v>7524022577</v>
+        <v>7466217685</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>382146995</v>
+        <v>374469403</v>
       </c>
       <c r="I21" t="n">
-        <v>0.219762</v>
+        <v>0.218266</v>
       </c>
       <c r="J21" t="n">
         <v>0.209091</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.001449679238016699</v>
+        <v>-0.004282575427316249</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.76252</v>
+        <v>-1.9649</v>
       </c>
       <c r="M21" t="n">
-        <v>34931895481.5965</v>
+        <v>34932729791.51797</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70148</v>
@@ -2460,13 +2460,13 @@
         <v>43102.66666666666</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R21" t="b">
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.003981910094721682</v>
+        <v>0.003958371071848852</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2529,16 +2529,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>340.47</v>
+        <v>333.6</v>
       </c>
       <c r="F22" t="n">
-        <v>6849206386</v>
+        <v>6716534493</v>
       </c>
       <c r="G22" t="n">
         <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>1186844804</v>
+        <v>1250678373</v>
       </c>
       <c r="I22" t="n">
         <v>346.9</v>
@@ -2547,10 +2547,10 @@
         <v>261.8</v>
       </c>
       <c r="K22" t="n">
-        <v>72.33</v>
+        <v>62.94</v>
       </c>
       <c r="L22" t="n">
-        <v>26.79209</v>
+        <v>23.25311</v>
       </c>
       <c r="M22" t="n">
         <v>20092971.77165077</v>
@@ -2565,13 +2565,13 @@
         <v>43088.66666666666</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R22" t="b">
         <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0.003592330987847522</v>
+        <v>0.003524722824729912</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2634,16 +2634,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>9.44</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>5869006543</v>
+        <v>5866836849</v>
       </c>
       <c r="G23" t="n">
         <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>1593380024</v>
+        <v>1601168901</v>
       </c>
       <c r="I23" t="n">
         <v>9.699999999999999</v>
@@ -2652,10 +2652,10 @@
         <v>8.68</v>
       </c>
       <c r="K23" t="n">
-        <v>0.672496</v>
+        <v>0.669198</v>
       </c>
       <c r="L23" t="n">
-        <v>7.57425</v>
+        <v>7.61587</v>
       </c>
       <c r="M23" t="n">
         <v>620708422.6104751</v>
@@ -2670,13 +2670,13 @@
         <v>44318.89240740741</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R23" t="b">
         <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>0.00302645040512432</v>
+        <v>0.003033222017677415</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2739,31 +2739,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="F24" t="n">
-        <v>5662458523</v>
+        <v>5650487357</v>
       </c>
       <c r="G24" t="n">
         <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>1682767802</v>
+        <v>1655744565</v>
       </c>
       <c r="I24" t="n">
         <v>4.65</v>
       </c>
       <c r="J24" t="n">
-        <v>4.12</v>
+        <v>4.21</v>
       </c>
       <c r="K24" t="n">
-        <v>0.193685</v>
+        <v>0.164253</v>
       </c>
       <c r="L24" t="n">
-        <v>4.56812</v>
+        <v>3.9499</v>
       </c>
       <c r="M24" t="n">
-        <v>1307027733</v>
+        <v>1307027694</v>
       </c>
       <c r="N24" t="n">
         <v>1307027728</v>
@@ -2775,13 +2775,13 @@
         <v>44577.59010416667</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R24" t="b">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.002907207870295712</v>
+        <v>0.002908076384199116</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2844,31 +2844,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>11.08</v>
+        <v>11.12</v>
       </c>
       <c r="F25" t="n">
-        <v>4909205600</v>
+        <v>4929331368</v>
       </c>
       <c r="G25" t="n">
         <v>24</v>
       </c>
       <c r="H25" t="n">
-        <v>633782095</v>
+        <v>583000115</v>
       </c>
       <c r="I25" t="n">
-        <v>11.35</v>
+        <v>11.27</v>
       </c>
       <c r="J25" t="n">
         <v>10.53</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.2567119165716321</v>
+        <v>-0.09252834473666383</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.2405</v>
+        <v>-0.8249300000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>442927404.050358</v>
+        <v>442929713.9306387</v>
       </c>
       <c r="N25" t="n">
         <v>469596104.050358</v>
@@ -2880,13 +2880,13 @@
         <v>44521.26314814815</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.002472346340731893</v>
+        <v>0.002490929469520555</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2949,16 +2949,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.999824</v>
+        <v>0.999831</v>
       </c>
       <c r="F26" t="n">
-        <v>4898876763</v>
+        <v>4898930130</v>
       </c>
       <c r="G26" t="n">
         <v>25</v>
       </c>
       <c r="H26" t="n">
-        <v>175765816</v>
+        <v>175398799</v>
       </c>
       <c r="I26" t="n">
         <v>0.999931</v>
@@ -2967,10 +2967,10 @@
         <v>0.998631</v>
       </c>
       <c r="K26" t="n">
-        <v>2.905e-05</v>
+        <v>4.747e-05</v>
       </c>
       <c r="L26" t="n">
-        <v>0.00317</v>
+        <v>0.00475</v>
       </c>
       <c r="M26" t="n">
         <v>4899806603.894896</v>
@@ -2985,13 +2985,13 @@
         <v>46000.38208333333</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R26" t="b">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.002466383384971235</v>
+        <v>0.002473344116521277</v>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
@@ -3005,7 +3005,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3024,16 +3024,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>62.62</v>
+        <v>62.39</v>
       </c>
       <c r="F27" t="n">
-        <v>4864663052</v>
+        <v>4845618269</v>
       </c>
       <c r="G27" t="n">
         <v>26</v>
       </c>
       <c r="H27" t="n">
-        <v>500958406</v>
+        <v>494519336</v>
       </c>
       <c r="I27" t="n">
         <v>63.44</v>
@@ -3042,13 +3042,13 @@
         <v>59.82</v>
       </c>
       <c r="K27" t="n">
-        <v>0.593382</v>
+        <v>0.509826</v>
       </c>
       <c r="L27" t="n">
-        <v>0.98769</v>
+        <v>0.82386</v>
       </c>
       <c r="M27" t="n">
-        <v>77636779.47670597</v>
+        <v>77636991.97696769</v>
       </c>
       <c r="N27" t="n">
         <v>77639516.98369066</v>
@@ -3060,13 +3060,13 @@
         <v>44325.80077546297</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R27" t="b">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.002446631418210511</v>
+        <v>0.002442506296866253</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3129,16 +3129,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.999915</v>
+        <v>0.999827</v>
       </c>
       <c r="F28" t="n">
-        <v>4575720883</v>
+        <v>4592048687</v>
       </c>
       <c r="G28" t="n">
         <v>27</v>
       </c>
       <c r="H28" t="n">
-        <v>235945685</v>
+        <v>238631706</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
@@ -3147,16 +3147,16 @@
         <v>0.998871</v>
       </c>
       <c r="K28" t="n">
-        <v>3.684e-05</v>
+        <v>-6.672678711572299e-05</v>
       </c>
       <c r="L28" t="n">
-        <v>0.00452</v>
+        <v>-0.00667</v>
       </c>
       <c r="M28" t="n">
-        <v>4575753580.16673</v>
+        <v>4592088883.495623</v>
       </c>
       <c r="N28" t="n">
-        <v>4592088883.495623</v>
+        <v>4607756201.823016</v>
       </c>
       <c r="O28" t="n">
         <v>1.22</v>
@@ -3165,13 +3165,13 @@
         <v>43902.79363425926</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R28" t="b">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.002279821798585806</v>
+        <v>0.002295830999980336</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3234,16 +3234,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.114167</v>
+        <v>0.113361</v>
       </c>
       <c r="F29" t="n">
-        <v>4528241072</v>
+        <v>4495985229</v>
       </c>
       <c r="G29" t="n">
         <v>28</v>
       </c>
       <c r="H29" t="n">
-        <v>17809362</v>
+        <v>17648343</v>
       </c>
       <c r="I29" t="n">
         <v>0.119967</v>
@@ -3252,16 +3252,16 @@
         <v>0.111864</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.001610986985493751</v>
+        <v>-0.001888689596183116</v>
       </c>
       <c r="L29" t="n">
-        <v>-1.38068</v>
+        <v>-1.63877</v>
       </c>
       <c r="M29" t="n">
         <v>39662232770.86527</v>
       </c>
       <c r="N29" t="n">
-        <v>39662232770.86527</v>
+        <v>39663044281.77826</v>
       </c>
       <c r="O29" t="n">
         <v>0.194152</v>
@@ -3270,13 +3270,13 @@
         <v>46056.00148148148</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R29" t="b">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.002252411160532615</v>
+        <v>0.002240263860929573</v>
       </c>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
@@ -3290,7 +3290,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3309,16 +3309,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.999344</v>
+        <v>0.999353</v>
       </c>
       <c r="F30" t="n">
-        <v>4392803585</v>
+        <v>4392965697</v>
       </c>
       <c r="G30" t="n">
         <v>29</v>
       </c>
       <c r="H30" t="n">
-        <v>1317635380</v>
+        <v>1314867446</v>
       </c>
       <c r="I30" t="n">
         <v>0.999651</v>
@@ -3327,10 +3327,10 @@
         <v>0.999131</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.000230891299258684</v>
+        <v>-0.000189665058792587</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.0249</v>
+        <v>-0.01898</v>
       </c>
       <c r="M30" t="n">
         <v>4395796475.062263</v>
@@ -3345,13 +3345,13 @@
         <v>46212.42696759259</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R30" t="b">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.002174221549900198</v>
+        <v>0.002180673036501948</v>
       </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
@@ -3365,7 +3365,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3384,16 +3384,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.099762</v>
+        <v>0.098964</v>
       </c>
       <c r="F31" t="n">
-        <v>4381497354</v>
+        <v>4338046552</v>
       </c>
       <c r="G31" t="n">
         <v>30</v>
       </c>
       <c r="H31" t="n">
-        <v>253199661</v>
+        <v>248233542</v>
       </c>
       <c r="I31" t="n">
         <v>0.100667</v>
@@ -3402,13 +3402,13 @@
         <v>0.091183</v>
       </c>
       <c r="K31" t="n">
-        <v>0.007907839999999999</v>
+        <v>0.00616817</v>
       </c>
       <c r="L31" t="n">
-        <v>8.63801</v>
+        <v>6.64701</v>
       </c>
       <c r="M31" t="n">
-        <v>43831706400.35046</v>
+        <v>43831706400.35147</v>
       </c>
       <c r="N31" t="n">
         <v>50000000000</v>
@@ -3420,13 +3420,13 @@
         <v>44454.11143518519</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R31" t="b">
         <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>0.002167694333402079</v>
+        <v>0.002148905496270739</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3489,16 +3489,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1.011</v>
+        <v>1.008</v>
       </c>
       <c r="F32" t="n">
-        <v>4147213010</v>
+        <v>4130999814</v>
       </c>
       <c r="G32" t="n">
         <v>31</v>
       </c>
       <c r="H32" t="n">
-        <v>1118620738</v>
+        <v>1120008041</v>
       </c>
       <c r="I32" t="n">
         <v>1.079</v>
@@ -3507,10 +3507,10 @@
         <v>0.988259</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.008432258001915161</v>
+        <v>-0.01936280268045532</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.78915</v>
+        <v>-1.88384</v>
       </c>
       <c r="M32" t="n">
         <v>4096537146.540959</v>
@@ -3525,13 +3525,13 @@
         <v>45661.62243055556</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R32" t="b">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.002032439301428316</v>
+        <v>0.002029140966448662</v>
       </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
@@ -3545,7 +3545,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3567,13 +3567,13 @@
         <v>1.45</v>
       </c>
       <c r="F33" t="n">
-        <v>4086969910</v>
+        <v>4077642836</v>
       </c>
       <c r="G33" t="n">
         <v>32</v>
       </c>
       <c r="H33" t="n">
-        <v>52837490</v>
+        <v>53122958</v>
       </c>
       <c r="I33" t="n">
         <v>1.47</v>
@@ -3582,16 +3582,16 @@
         <v>1.41</v>
       </c>
       <c r="K33" t="n">
-        <v>0.00408983</v>
+        <v>0.00133977</v>
       </c>
       <c r="L33" t="n">
-        <v>0.24221</v>
+        <v>0.09245</v>
       </c>
       <c r="M33" t="n">
         <v>2810942525.236758</v>
       </c>
       <c r="N33" t="n">
-        <v>5253728562.764504</v>
+        <v>5253752609.789647</v>
       </c>
       <c r="O33" t="n">
         <v>8.25</v>
@@ -3600,13 +3600,13 @@
         <v>45457.69225694444</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R33" t="b">
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.001997660270625051</v>
+        <v>0.001998277049225793</v>
       </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
@@ -3620,7 +3620,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3639,16 +3639,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6.05e-06</v>
+        <v>6.01e-06</v>
       </c>
       <c r="F34" t="n">
-        <v>3567256021</v>
+        <v>3541226044</v>
       </c>
       <c r="G34" t="n">
         <v>33</v>
       </c>
       <c r="H34" t="n">
-        <v>213804939</v>
+        <v>211376302</v>
       </c>
       <c r="I34" t="n">
         <v>6.25e-06</v>
@@ -3657,10 +3657,10 @@
         <v>5.9e-06</v>
       </c>
       <c r="K34" t="n">
-        <v>8.1711e-08</v>
+        <v>-3.5306998336e-08</v>
       </c>
       <c r="L34" t="n">
-        <v>1.4441</v>
+        <v>-0.58435</v>
       </c>
       <c r="M34" t="n">
         <v>589238968628246.4</v>
@@ -3675,13 +3675,13 @@
         <v>44496.82980324074</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R34" t="b">
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0.001697623497045746</v>
+        <v>0.001687991045673556</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3744,28 +3744,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>309.22</v>
+        <v>308.56</v>
       </c>
       <c r="F35" t="n">
-        <v>3508186486</v>
+        <v>3499419828</v>
       </c>
       <c r="G35" t="n">
         <v>34</v>
       </c>
       <c r="H35" t="n">
-        <v>545675077</v>
+        <v>537476536</v>
       </c>
       <c r="I35" t="n">
         <v>325.76</v>
       </c>
       <c r="J35" t="n">
-        <v>302.22</v>
+        <v>306.69</v>
       </c>
       <c r="K35" t="n">
-        <v>1.068</v>
+        <v>4.6</v>
       </c>
       <c r="L35" t="n">
-        <v>0.49825</v>
+        <v>1.51283</v>
       </c>
       <c r="M35" t="n">
         <v>11339645.9251</v>
@@ -3780,13 +3780,13 @@
         <v>45358.44833333333</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R35" t="b">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.001663521978742413</v>
+        <v>0.001663808574356958</v>
       </c>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
@@ -3800,7 +3800,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3819,16 +3819,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.06623999999999999</v>
+        <v>0.065981</v>
       </c>
       <c r="F36" t="n">
-        <v>3294501272</v>
+        <v>3281617349</v>
       </c>
       <c r="G36" t="n">
         <v>35</v>
       </c>
       <c r="H36" t="n">
-        <v>16354864</v>
+        <v>18457889</v>
       </c>
       <c r="I36" t="n">
         <v>0.068842</v>
@@ -3837,16 +3837,16 @@
         <v>0.06461500000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>0.0008701</v>
+        <v>0.00060393</v>
       </c>
       <c r="L36" t="n">
-        <v>1.33228</v>
+        <v>0.92376</v>
       </c>
       <c r="M36" t="n">
-        <v>49737707457.07803</v>
+        <v>49737789509.91389</v>
       </c>
       <c r="N36" t="n">
-        <v>98937691623.08702</v>
+        <v>98937800399.94398</v>
       </c>
       <c r="O36" t="n">
         <v>0.891544</v>
@@ -3855,13 +3855,13 @@
         <v>44523.66666666666</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R36" t="b">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.001540159060169029</v>
+        <v>0.001537822472168195</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3927,13 +3927,13 @@
         <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>3258615171</v>
+        <v>3258614301</v>
       </c>
       <c r="G37" t="n">
         <v>36</v>
       </c>
       <c r="H37" t="n">
-        <v>916316571</v>
+        <v>920617922</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
@@ -3942,10 +3942,10 @@
         <v>0.999787</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.5706744024069e-05</v>
+        <v>7.24e-05</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.00083</v>
+        <v>0.00724</v>
       </c>
       <c r="M37" t="n">
         <v>3258647890.048256</v>
@@ -3960,13 +3960,13 @@
         <v>45686.67436342593</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R37" t="b">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.00151944160352938</v>
+        <v>0.001524516543010332</v>
       </c>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
@@ -3980,7 +3980,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4002,13 +4002,13 @@
         <v>1.31</v>
       </c>
       <c r="F38" t="n">
-        <v>2977606566</v>
+        <v>2977708940</v>
       </c>
       <c r="G38" t="n">
         <v>37</v>
       </c>
       <c r="H38" t="n">
-        <v>1787037</v>
+        <v>1772456</v>
       </c>
       <c r="I38" t="n">
         <v>1.48</v>
@@ -4017,10 +4017,10 @@
         <v>1.29</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.1573793546544873</v>
+        <v>-0.1590208969476814</v>
       </c>
       <c r="L38" t="n">
-        <v>-10.74441</v>
+        <v>-10.8441</v>
       </c>
       <c r="M38" t="n">
         <v>2277592661.72997</v>
@@ -4035,13 +4035,13 @@
         <v>46205.17638888889</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R38" t="b">
         <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>0.00135721212116082</v>
+        <v>0.001362029083368896</v>
       </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
@@ -4055,7 +4055,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4077,13 +4077,13 @@
         <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>2823592224</v>
+        <v>2823457383</v>
       </c>
       <c r="G39" t="n">
         <v>38</v>
       </c>
       <c r="H39" t="n">
-        <v>157981743</v>
+        <v>158036998</v>
       </c>
       <c r="I39" t="n">
         <v>1</v>
@@ -4092,10 +4092,10 @@
         <v>0.99978</v>
       </c>
       <c r="K39" t="n">
-        <v>6.4e-06</v>
+        <v>3.783e-05</v>
       </c>
       <c r="L39" t="n">
-        <v>0.00118</v>
+        <v>0.00378</v>
       </c>
       <c r="M39" t="n">
         <v>2823558770.164367</v>
@@ -4110,13 +4110,13 @@
         <v>45222.61454861111</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001268297879620087</v>
+        <v>0.001272803503787785</v>
       </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
@@ -4130,7 +4130,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4149,16 +4149,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4355.93</v>
+        <v>4360.49</v>
       </c>
       <c r="F40" t="n">
-        <v>2712967630</v>
+        <v>2715915538</v>
       </c>
       <c r="G40" t="n">
         <v>39</v>
       </c>
       <c r="H40" t="n">
-        <v>209976775</v>
+        <v>212911419</v>
       </c>
       <c r="I40" t="n">
         <v>4372.67</v>
@@ -4167,10 +4167,10 @@
         <v>4295.64</v>
       </c>
       <c r="K40" t="n">
-        <v>15.59</v>
+        <v>11.22</v>
       </c>
       <c r="L40" t="n">
-        <v>0.34468</v>
+        <v>0.25796</v>
       </c>
       <c r="M40" t="n">
         <v>622823.6595320001</v>
@@ -4185,13 +4185,13 @@
         <v>46050.66666666666</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R40" t="b">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.001204433035972854</v>
+        <v>0.001210596783570712</v>
       </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
@@ -4205,7 +4205,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4224,16 +4224,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>123.13</v>
+        <v>122.42</v>
       </c>
       <c r="F41" t="n">
-        <v>2587013448</v>
+        <v>2571444715</v>
       </c>
       <c r="G41" t="n">
         <v>40</v>
       </c>
       <c r="H41" t="n">
-        <v>40188551</v>
+        <v>39775410</v>
       </c>
       <c r="I41" t="n">
         <v>126.4</v>
@@ -4242,10 +4242,10 @@
         <v>120.48</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.1176173684437742</v>
+        <v>-0.5971208906714907</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.16008</v>
+        <v>-0.48539</v>
       </c>
       <c r="M41" t="n">
         <v>21000000</v>
@@ -4260,13 +4260,13 @@
         <v>45934.66666666666</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R41" t="b">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.001131718245804718</v>
+        <v>0.001127028791354367</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4365,13 +4365,13 @@
         <v>46287.53819444445</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R42" t="b">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.001086579481871068</v>
+        <v>0.001090807240181103</v>
       </c>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
@@ -4385,68 +4385,68 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ripple-usd</t>
+          <t>bitway</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>rlusd</t>
+          <t>btw</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Ripple USD</t>
+          <t>Bitway</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>0.894261</v>
       </c>
       <c r="F43" t="n">
-        <v>2414668604</v>
+        <v>2420235968</v>
       </c>
       <c r="G43" t="n">
         <v>42</v>
       </c>
       <c r="H43" t="n">
-        <v>423709547</v>
+        <v>14031928</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0.886543</v>
       </c>
       <c r="J43" t="n">
-        <v>0.9997740000000001</v>
+        <v>0.717963</v>
       </c>
       <c r="K43" t="n">
-        <v>9.699e-05</v>
+        <v>0.02319291</v>
       </c>
       <c r="L43" t="n">
-        <v>0.00021</v>
+        <v>2.66258</v>
       </c>
       <c r="M43" t="n">
-        <v>2414682344.087236</v>
+        <v>2708142280.000001</v>
       </c>
       <c r="N43" t="n">
-        <v>2417586212.607235</v>
+        <v>10000000000</v>
       </c>
       <c r="O43" t="n">
-        <v>1.073</v>
+        <v>0.972034</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>45652.11518518518</v>
+        <v>46286.79398148148</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R43" t="b">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.001032221595760816</v>
+        <v>0.001039563300884092</v>
       </c>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
@@ -4460,68 +4460,68 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>bitway</t>
+          <t>ripple-usd</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>btw</t>
+          <t>rlusd</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Bitway</t>
+          <t>Ripple USD</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.882043</v>
+        <v>0.999978</v>
       </c>
       <c r="F44" t="n">
-        <v>2386426149</v>
+        <v>2417505676</v>
       </c>
       <c r="G44" t="n">
         <v>43</v>
       </c>
       <c r="H44" t="n">
-        <v>13777728</v>
+        <v>431971136</v>
       </c>
       <c r="I44" t="n">
-        <v>0.885736</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>0.717963</v>
+        <v>0.9997740000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>0.01416612</v>
+        <v>-0.000173738122698608</v>
       </c>
       <c r="L44" t="n">
-        <v>1.3311</v>
+        <v>-0.01737</v>
       </c>
       <c r="M44" t="n">
-        <v>2708142280.000001</v>
+        <v>2417586212.607235</v>
       </c>
       <c r="N44" t="n">
-        <v>10000000000</v>
+        <v>2417586212.607235</v>
       </c>
       <c r="O44" t="n">
-        <v>0.972034</v>
+        <v>1.073</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>46286.79398148148</v>
+        <v>45652.11518518518</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R44" t="b">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.001015916903399287</v>
+        <v>0.001037983985311118</v>
       </c>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
@@ -4535,7 +4535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4572,7 +4572,7 @@
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>-1.11e-16</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -4590,13 +4590,13 @@
         <v>45699.87511574074</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R45" t="b">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.0009549918306333762</v>
+        <v>0.0009589618976471764</v>
       </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
@@ -4610,7 +4610,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4629,16 +4629,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="F46" t="n">
-        <v>2246400476</v>
+        <v>2245147219</v>
       </c>
       <c r="G46" t="n">
         <v>45</v>
       </c>
       <c r="H46" t="n">
-        <v>2779332</v>
+        <v>5601491</v>
       </c>
       <c r="I46" t="n">
         <v>1.15</v>
@@ -4647,10 +4647,10 @@
         <v>1.13</v>
       </c>
       <c r="K46" t="n">
-        <v>0.0046907</v>
+        <v>-0.003195321708100662</v>
       </c>
       <c r="L46" t="n">
-        <v>0.42566</v>
+        <v>-0.27872</v>
       </c>
       <c r="M46" t="n">
         <v>1963554625.495198</v>
@@ -4665,13 +4665,13 @@
         <v>45377.89175925926</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R46" t="b">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.0009350784805008161</v>
+        <v>0.0009382846142277451</v>
       </c>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
@@ -4685,7 +4685,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4704,16 +4704,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>144.82</v>
+        <v>144.35</v>
       </c>
       <c r="F47" t="n">
-        <v>2236997529</v>
+        <v>2227832718</v>
       </c>
       <c r="G47" t="n">
         <v>46</v>
       </c>
       <c r="H47" t="n">
-        <v>267338061</v>
+        <v>267445253</v>
       </c>
       <c r="I47" t="n">
         <v>146.7</v>
@@ -4722,13 +4722,13 @@
         <v>140.18</v>
       </c>
       <c r="K47" t="n">
-        <v>1.28</v>
+        <v>0.224976</v>
       </c>
       <c r="L47" t="n">
-        <v>0.85148</v>
+        <v>0.15609</v>
       </c>
       <c r="M47" t="n">
-        <v>15428919.91855954</v>
+        <v>15428920.67059255</v>
       </c>
       <c r="N47" t="n">
         <v>16000000</v>
@@ -4740,13 +4740,13 @@
         <v>44334.55554398148</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R47" t="b">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0.0009296500516292197</v>
+        <v>0.0009282691795901374</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4809,16 +4809,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.668858</v>
+        <v>0.667385</v>
       </c>
       <c r="F48" t="n">
-        <v>2210124703</v>
+        <v>2204088910</v>
       </c>
       <c r="G48" t="n">
         <v>47</v>
       </c>
       <c r="H48" t="n">
-        <v>56060834</v>
+        <v>53749791</v>
       </c>
       <c r="I48" t="n">
         <v>0.671764</v>
@@ -4827,10 +4827,10 @@
         <v>0.636514</v>
       </c>
       <c r="K48" t="n">
-        <v>0.02171301</v>
+        <v>0.01742403</v>
       </c>
       <c r="L48" t="n">
-        <v>3.34798</v>
+        <v>2.68078</v>
       </c>
       <c r="M48" t="n">
         <v>3302294382.53684</v>
@@ -4845,13 +4845,13 @@
         <v>45938.71164351852</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R48" t="b">
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0.0009141360617577694</v>
+        <v>0.0009145347637342079</v>
       </c>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
@@ -4865,68 +4865,68 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ondo-finance</t>
+          <t>ethena</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ondo</t>
+          <t>ena</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Ondo</t>
+          <t>Ethena</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.435294</v>
+        <v>0.208813</v>
       </c>
       <c r="F49" t="n">
-        <v>2121311587</v>
+        <v>2110538729</v>
       </c>
       <c r="G49" t="n">
         <v>48</v>
       </c>
       <c r="H49" t="n">
-        <v>252008569</v>
+        <v>462953450</v>
       </c>
       <c r="I49" t="n">
-        <v>0.463533</v>
+        <v>0.218605</v>
       </c>
       <c r="J49" t="n">
-        <v>0.422514</v>
+        <v>0.203656</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.01531617904591515</v>
+        <v>-0.000232921066841418</v>
       </c>
       <c r="L49" t="n">
-        <v>-3.43312</v>
+        <v>-0.11142</v>
       </c>
       <c r="M49" t="n">
-        <v>4869330647</v>
+        <v>10095312500</v>
       </c>
       <c r="N49" t="n">
-        <v>10000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="O49" t="n">
-        <v>2.14</v>
+        <v>1.52</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>45641.69166666667</v>
+        <v>45393.21892361111</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R49" t="b">
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>0.0008628632338804206</v>
+        <v>0.0008604214096651606</v>
       </c>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
@@ -4940,68 +4940,68 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ethena</t>
+          <t>ondo-finance</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ena</t>
+          <t>ondo</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Ethena</t>
+          <t>Ondo</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.208918</v>
+        <v>0.432797</v>
       </c>
       <c r="F50" t="n">
-        <v>2112989817</v>
+        <v>2108132110</v>
       </c>
       <c r="G50" t="n">
         <v>49</v>
       </c>
       <c r="H50" t="n">
-        <v>443685103</v>
+        <v>261671080</v>
       </c>
       <c r="I50" t="n">
-        <v>0.218605</v>
+        <v>0.463533</v>
       </c>
       <c r="J50" t="n">
-        <v>0.203656</v>
+        <v>0.422514</v>
       </c>
       <c r="K50" t="n">
-        <v>0.00058719</v>
+        <v>-0.02050550131691564</v>
       </c>
       <c r="L50" t="n">
-        <v>0.33878</v>
+        <v>-4.52358</v>
       </c>
       <c r="M50" t="n">
-        <v>10095312500</v>
+        <v>4869330647</v>
       </c>
       <c r="N50" t="n">
-        <v>15000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="O50" t="n">
-        <v>1.52</v>
+        <v>2.14</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>45393.21892361111</v>
+        <v>45641.69166666667</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S50" t="n">
-        <v>0.0008580589808594492</v>
+        <v>0.0008590293201505898</v>
       </c>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
@@ -5015,7 +5015,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5034,28 +5034,28 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.00445687</v>
+        <v>0.00445567</v>
       </c>
       <c r="F51" t="n">
-        <v>2083585191</v>
+        <v>2080692809</v>
       </c>
       <c r="G51" t="n">
         <v>50</v>
       </c>
       <c r="H51" t="n">
-        <v>226448298</v>
+        <v>227181607</v>
       </c>
       <c r="I51" t="n">
         <v>0.00469623</v>
       </c>
       <c r="J51" t="n">
-        <v>0.00431196</v>
+        <v>0.00434625</v>
       </c>
       <c r="K51" t="n">
-        <v>0.00013924</v>
+        <v>0.00014213</v>
       </c>
       <c r="L51" t="n">
-        <v>3.18771</v>
+        <v>3.29489</v>
       </c>
       <c r="M51" t="n">
         <v>467008882120.3215</v>
@@ -5070,13 +5070,13 @@
         <v>45914.36296296296</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R51" t="b">
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0.0008410833538845346</v>
+        <v>0.0008431572759220473</v>
       </c>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
@@ -5090,7 +5090,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5109,16 +5109,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4.91e-06</v>
+        <v>4.9e-06</v>
       </c>
       <c r="F52" t="n">
-        <v>2067006553</v>
+        <v>2062795678</v>
       </c>
       <c r="G52" t="n">
         <v>51</v>
       </c>
       <c r="H52" t="n">
-        <v>961220641</v>
+        <v>936446984</v>
       </c>
       <c r="I52" t="n">
         <v>5.34e-06</v>
@@ -5127,10 +5127,10 @@
         <v>4.71e-06</v>
       </c>
       <c r="K52" t="n">
-        <v>9.7696e-08</v>
+        <v>4.9565e-08</v>
       </c>
       <c r="L52" t="n">
-        <v>1.97647</v>
+        <v>1.02125</v>
       </c>
       <c r="M52" t="n">
         <v>420690000000000</v>
@@ -5145,13 +5145,13 @@
         <v>45635.35457175926</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R52" t="b">
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0.0008315123165096623</v>
+        <v>0.0008328048236202915</v>
       </c>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
@@ -5165,7 +5165,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5184,16 +5184,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="F53" t="n">
-        <v>2039692689</v>
+        <v>2029369315</v>
       </c>
       <c r="G53" t="n">
         <v>52</v>
       </c>
       <c r="H53" t="n">
-        <v>176420599</v>
+        <v>173566728</v>
       </c>
       <c r="I53" t="n">
         <v>1.22</v>
@@ -5202,13 +5202,13 @@
         <v>1.15</v>
       </c>
       <c r="K53" t="n">
-        <v>0.00602479</v>
+        <v>-0.003513831894498276</v>
       </c>
       <c r="L53" t="n">
-        <v>0.45589</v>
+        <v>-0.2943</v>
       </c>
       <c r="M53" t="n">
-        <v>1704000796.081443</v>
+        <v>1704007261.631945</v>
       </c>
       <c r="N53" t="n">
         <v>1704007261.631945</v>
@@ -5220,13 +5220,13 @@
         <v>44504.25704861111</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R53" t="b">
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0.0008157437103553943</v>
+        <v>0.0008134696112569985</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5289,16 +5289,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.727623</v>
+        <v>0.7260450000000001</v>
       </c>
       <c r="F54" t="n">
-        <v>1974213251</v>
+        <v>1967105995</v>
       </c>
       <c r="G54" t="n">
         <v>53</v>
       </c>
       <c r="H54" t="n">
-        <v>165809899</v>
+        <v>165661199</v>
       </c>
       <c r="I54" t="n">
         <v>0.748964</v>
@@ -5307,10 +5307,10 @@
         <v>0.7117059999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.01163590523736624</v>
+        <v>-0.01247816815186487</v>
       </c>
       <c r="L54" t="n">
-        <v>-1.59472</v>
+        <v>-1.68961</v>
       </c>
       <c r="M54" t="n">
         <v>2710487455.649731</v>
@@ -5325,13 +5325,13 @@
         <v>45924.13766203704</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R54" t="b">
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>0.0007779416817217009</v>
+        <v>0.0007774538917291614</v>
       </c>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
@@ -5345,7 +5345,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5364,16 +5364,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4355.91</v>
+        <v>4359.73</v>
       </c>
       <c r="F55" t="n">
-        <v>1894407221</v>
+        <v>1896162989</v>
       </c>
       <c r="G55" t="n">
         <v>54</v>
       </c>
       <c r="H55" t="n">
-        <v>199072964</v>
+        <v>197750904</v>
       </c>
       <c r="I55" t="n">
         <v>4369.08</v>
@@ -5382,10 +5382,10 @@
         <v>4295.5</v>
       </c>
       <c r="K55" t="n">
-        <v>18.53</v>
+        <v>14.74</v>
       </c>
       <c r="L55" t="n">
-        <v>0.41116</v>
+        <v>0.33933</v>
       </c>
       <c r="M55" t="n">
         <v>434903.623539</v>
@@ -5400,13 +5400,13 @@
         <v>46050.93814814815</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R55" t="b">
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0007318687476320498</v>
+        <v>0.0007364174772469646</v>
       </c>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
@@ -5420,7 +5420,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5439,16 +5439,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.058378</v>
+        <v>0.058183</v>
       </c>
       <c r="F56" t="n">
-        <v>1855309470</v>
+        <v>1848705508</v>
       </c>
       <c r="G56" t="n">
         <v>55</v>
       </c>
       <c r="H56" t="n">
-        <v>57287055</v>
+        <v>61134963</v>
       </c>
       <c r="I56" t="n">
         <v>0.058528</v>
@@ -5457,10 +5457,10 @@
         <v>0.056703</v>
       </c>
       <c r="K56" t="n">
-        <v>0.00125043</v>
+        <v>0.00104893</v>
       </c>
       <c r="L56" t="n">
-        <v>2.19569</v>
+        <v>1.83592</v>
       </c>
       <c r="M56" t="n">
         <v>31777768006</v>
@@ -5475,13 +5475,13 @@
         <v>45901.18065972222</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R56" t="b">
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0.0007092971687065402</v>
+        <v>0.0007089660768848628</v>
       </c>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
@@ -5495,7 +5495,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5514,16 +5514,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="F57" t="n">
-        <v>1807976374</v>
+        <v>1805505796</v>
       </c>
       <c r="G57" t="n">
         <v>56</v>
       </c>
       <c r="H57" t="n">
-        <v>33520122</v>
+        <v>33427436</v>
       </c>
       <c r="I57" t="n">
         <v>2.67</v>
@@ -5532,13 +5532,13 @@
         <v>2.56</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.0698690106453359</v>
+        <v>-0.0655068506491947</v>
       </c>
       <c r="L57" t="n">
-        <v>-2.64098</v>
+        <v>-2.4746</v>
       </c>
       <c r="M57" t="n">
-        <v>699288962.8606994</v>
+        <v>699291024.8718739</v>
       </c>
       <c r="N57" t="n">
         <v>1000000000</v>
@@ -5550,13 +5550,13 @@
         <v>45674.19883101852</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R57" t="b">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0.0006819712309012499</v>
+        <v>0.0006839775489509952</v>
       </c>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
@@ -5570,7 +5570,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5589,16 +5589,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.460206</v>
+        <v>0.457343</v>
       </c>
       <c r="F58" t="n">
-        <v>1680569073</v>
+        <v>1668410444</v>
       </c>
       <c r="G58" t="n">
         <v>57</v>
       </c>
       <c r="H58" t="n">
-        <v>249743884</v>
+        <v>250281011</v>
       </c>
       <c r="I58" t="n">
         <v>0.476706</v>
@@ -5607,10 +5607,10 @@
         <v>0.441742</v>
       </c>
       <c r="K58" t="n">
-        <v>0.00849258</v>
+        <v>0.00015672</v>
       </c>
       <c r="L58" t="n">
-        <v>1.89246</v>
+        <v>0.03428</v>
       </c>
       <c r="M58" t="n">
         <v>3646959224.069938</v>
@@ -5625,13 +5625,13 @@
         <v>45360.67409722223</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R58" t="b">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0006084175385109214</v>
+        <v>0.0006046758389522016</v>
       </c>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
@@ -5645,7 +5645,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5664,16 +5664,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="F59" t="n">
-        <v>1662258969</v>
+        <v>1653855828</v>
       </c>
       <c r="G59" t="n">
         <v>58</v>
       </c>
       <c r="H59" t="n">
-        <v>71912870</v>
+        <v>74592682</v>
       </c>
       <c r="I59" t="n">
         <v>3.07</v>
@@ -5682,13 +5682,13 @@
         <v>2.89</v>
       </c>
       <c r="K59" t="n">
-        <v>0.01167413</v>
+        <v>-0.02078629846631808</v>
       </c>
       <c r="L59" t="n">
-        <v>0.40321</v>
+        <v>-0.69573</v>
       </c>
       <c r="M59" t="n">
-        <v>556905624.1128303</v>
+        <v>556905641.1775453</v>
       </c>
       <c r="N59" t="n">
         <v>556905641.1775453</v>
@@ -5700,13 +5700,13 @@
         <v>44326.33741898148</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R59" t="b">
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>0.0005978469060065021</v>
+        <v>0.0005962568377217601</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5769,31 +5769,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.069689</v>
+        <v>0.069221</v>
       </c>
       <c r="F60" t="n">
-        <v>1632669937</v>
+        <v>1621385060</v>
       </c>
       <c r="G60" t="n">
         <v>59</v>
       </c>
       <c r="H60" t="n">
-        <v>18938739</v>
+        <v>20185480</v>
       </c>
       <c r="I60" t="n">
-        <v>0.072129</v>
+        <v>0.07128</v>
       </c>
       <c r="J60" t="n">
         <v>0.066889</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.002276997225677535</v>
+        <v>-0.002525909363693277</v>
       </c>
       <c r="L60" t="n">
-        <v>-3.19928</v>
+        <v>-3.52059</v>
       </c>
       <c r="M60" t="n">
-        <v>23425011020.63758</v>
+        <v>23424963409.60133</v>
       </c>
       <c r="N60" t="n">
         <v>23459804203.60596</v>
@@ -5805,13 +5805,13 @@
         <v>45630.09302083333</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R60" t="b">
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0.0005807648193382068</v>
+        <v>0.0005774743816442258</v>
       </c>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
@@ -5825,7 +5825,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5847,13 +5847,13 @@
         <v>1.73e-06</v>
       </c>
       <c r="F61" t="n">
-        <v>1554986701</v>
+        <v>1554988430</v>
       </c>
       <c r="G61" t="n">
         <v>60</v>
       </c>
       <c r="H61" t="n">
-        <v>6629811</v>
+        <v>6619750</v>
       </c>
       <c r="I61" t="n">
         <v>1.75e-06</v>
@@ -5862,10 +5862,10 @@
         <v>1.71e-06</v>
       </c>
       <c r="K61" t="n">
-        <v>4.177e-09</v>
+        <v>5.388e-09</v>
       </c>
       <c r="L61" t="n">
-        <v>0.28796</v>
+        <v>0.31221</v>
       </c>
       <c r="M61" t="n">
         <v>898232728634017.2</v>
@@ -5880,13 +5880,13 @@
         <v>45629.67800925926</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R61" t="b">
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>0.0005359173985092443</v>
+        <v>0.0005390677820013932</v>
       </c>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
@@ -5900,7 +5900,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5919,31 +5919,31 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>31.94</v>
+        <v>32.04</v>
       </c>
       <c r="F62" t="n">
-        <v>1538893470</v>
+        <v>1541580321</v>
       </c>
       <c r="G62" t="n">
         <v>61</v>
       </c>
       <c r="H62" t="n">
-        <v>78339005</v>
+        <v>77002315</v>
       </c>
       <c r="I62" t="n">
-        <v>32.8</v>
+        <v>32.76</v>
       </c>
       <c r="J62" t="n">
         <v>30.32</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.5217021934352672</v>
+        <v>-0.5387525065471479</v>
       </c>
       <c r="L62" t="n">
-        <v>-1.64228</v>
+        <v>-1.65352</v>
       </c>
       <c r="M62" t="n">
-        <v>48110483.86115634</v>
+        <v>48113678.9569875</v>
       </c>
       <c r="N62" t="n">
         <v>81028467.06059173</v>
@@ -5955,13 +5955,13 @@
         <v>46286.34548611111</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R62" t="b">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0.0005266265921484651</v>
+        <v>0.0005313119685763676</v>
       </c>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
@@ -5975,7 +5975,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5994,16 +5994,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.998385</v>
+        <v>0.998397</v>
       </c>
       <c r="F63" t="n">
-        <v>1514650093</v>
+        <v>1524481541</v>
       </c>
       <c r="G63" t="n">
         <v>62</v>
       </c>
       <c r="H63" t="n">
-        <v>2022187</v>
+        <v>2022787</v>
       </c>
       <c r="I63" t="n">
         <v>0.999239</v>
@@ -6012,13 +6012,13 @@
         <v>0.998009</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.000319527799870545</v>
+        <v>-0.000216429162676612</v>
       </c>
       <c r="L63" t="n">
-        <v>-0.03532</v>
+        <v>-0.02167</v>
       </c>
       <c r="M63" t="n">
-        <v>1517125649</v>
+        <v>1526944779</v>
       </c>
       <c r="N63" t="n">
         <v>1527073089</v>
@@ -6030,13 +6030,13 @@
         <v>46212.39942129629</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R63" t="b">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0.000512630613265271</v>
+        <v>0.0005214213160260669</v>
       </c>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
@@ -6050,7 +6050,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6069,16 +6069,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.217939</v>
+        <v>0.217408</v>
       </c>
       <c r="F64" t="n">
-        <v>1479790029</v>
+        <v>1475125489</v>
       </c>
       <c r="G64" t="n">
         <v>63</v>
       </c>
       <c r="H64" t="n">
-        <v>312111878</v>
+        <v>310619951</v>
       </c>
       <c r="I64" t="n">
         <v>0.230082</v>
@@ -6087,10 +6087,10 @@
         <v>0.211434</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.003795146315592746</v>
+        <v>-0.005521648076855873</v>
       </c>
       <c r="L64" t="n">
-        <v>-1.6999</v>
+        <v>-2.47685</v>
       </c>
       <c r="M64" t="n">
         <v>6785574605</v>
@@ -6105,13 +6105,13 @@
         <v>45303.18748842592</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R64" t="b">
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0.000492505499523452</v>
+        <v>0.0004928717024520824</v>
       </c>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
@@ -6125,187 +6125,187 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ethereum-classic</t>
+          <t>bitget-token</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>bgb</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Ethereum Classic</t>
+          <t>Bitget Token</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>9.34</v>
+        <v>2.11</v>
       </c>
       <c r="F65" t="n">
-        <v>1478692181</v>
+        <v>1474990424</v>
       </c>
       <c r="G65" t="n">
         <v>64</v>
       </c>
       <c r="H65" t="n">
-        <v>105301995</v>
+        <v>16540237</v>
       </c>
       <c r="I65" t="n">
-        <v>9.369999999999999</v>
+        <v>2.18</v>
       </c>
       <c r="J65" t="n">
-        <v>8.56</v>
+        <v>2.08</v>
       </c>
       <c r="K65" t="n">
-        <v>0.556522</v>
+        <v>-0.04615182268589679</v>
       </c>
       <c r="L65" t="n">
-        <v>6.33342</v>
+        <v>-2.14338</v>
       </c>
       <c r="M65" t="n">
-        <v>158251635.651071</v>
+        <v>699992029.6481038</v>
       </c>
       <c r="N65" t="n">
-        <v>158251635.651071</v>
+        <v>910920874.6481038</v>
       </c>
       <c r="O65" t="n">
-        <v>167.09</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="P65" s="1" t="n">
-        <v>44322.44053240741</v>
+        <v>45653.15375</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0.000491871699313813</v>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Plataforma de contratos inteligentes</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Layer 1</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Proof of Work</t>
-        </is>
-      </c>
-      <c r="W65" t="n">
-        <v>2016</v>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>ethereumclassic.org</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>Contratos inteligentes (cadena original)</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>Blockchain propia (fork de Ethereum)</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>Mantiene la cadena original de Ethereum tras la bifurcación de 2016.</t>
-        </is>
-      </c>
+        <v>0.000492793575182961</v>
+      </c>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr"/>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>bitget-token</t>
+          <t>ethereum-classic</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>bgb</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Bitget Token</t>
+          <t>Ethereum Classic</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2.11</v>
+        <v>9.25</v>
       </c>
       <c r="F66" t="n">
-        <v>1475117403</v>
+        <v>1463504601</v>
       </c>
       <c r="G66" t="n">
         <v>65</v>
       </c>
       <c r="H66" t="n">
-        <v>16504894</v>
+        <v>117262670</v>
       </c>
       <c r="I66" t="n">
-        <v>2.18</v>
+        <v>9.41</v>
       </c>
       <c r="J66" t="n">
-        <v>2.08</v>
+        <v>8.56</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.04551146207062784</v>
+        <v>0.381459</v>
       </c>
       <c r="L66" t="n">
-        <v>-2.09981</v>
+        <v>4.30343</v>
       </c>
       <c r="M66" t="n">
-        <v>699992029.6481038</v>
+        <v>158251635.651071</v>
       </c>
       <c r="N66" t="n">
-        <v>910920874.6481038</v>
+        <v>158252729.1806711</v>
       </c>
       <c r="O66" t="n">
-        <v>8.449999999999999</v>
+        <v>167.09</v>
       </c>
       <c r="P66" s="1" t="n">
-        <v>45653.15375</v>
+        <v>44322.44053240741</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R66" t="b">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0.0004898079390794154</v>
-      </c>
-      <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr"/>
-      <c r="X66" t="inlineStr"/>
-      <c r="Y66" t="inlineStr"/>
-      <c r="Z66" t="inlineStr"/>
-      <c r="AA66" t="inlineStr"/>
+        <v>0.0004861496927219168</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Plataforma de contratos inteligentes</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Layer 1</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Proof of Work</t>
+        </is>
+      </c>
+      <c r="W66" t="n">
+        <v>2016</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>ethereumclassic.org</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>Contratos inteligentes (cadena original)</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>Blockchain propia (fork de Ethereum)</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>Mantiene la cadena original de Ethereum tras la bifurcación de 2016.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6342,10 +6342,10 @@
         <v>1.16</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.001720484800925348</v>
+        <v>-0.001443504240429272</v>
       </c>
       <c r="L67" t="n">
-        <v>-0.14811</v>
+        <v>-0.1243</v>
       </c>
       <c r="M67" t="n">
         <v>1249985019.14243</v>
@@ -6360,13 +6360,13 @@
         <v>46255.48263888889</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R67" t="b">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.0004752252022092601</v>
+        <v>0.0004782557305717813</v>
       </c>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
@@ -6380,7 +6380,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6399,28 +6399,28 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.999519</v>
+        <v>0.999359</v>
       </c>
       <c r="F68" t="n">
-        <v>1418612169</v>
+        <v>1418627552</v>
       </c>
       <c r="G68" t="n">
         <v>67</v>
       </c>
       <c r="H68" t="n">
-        <v>160832716</v>
+        <v>163399353</v>
       </c>
       <c r="I68" t="n">
-        <v>0.999923</v>
+        <v>0.9999</v>
       </c>
       <c r="J68" t="n">
         <v>0.999328</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.000312985174393487</v>
+        <v>-0.000450917662056738</v>
       </c>
       <c r="L68" t="n">
-        <v>-0.03296</v>
+        <v>-0.0451</v>
       </c>
       <c r="M68" t="n">
         <v>1419429007.8</v>
@@ -6435,13 +6435,13 @@
         <v>46058.54591435185</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R68" t="b">
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0.000457186821078654</v>
+        <v>0.0004601909226142355</v>
       </c>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
@@ -6455,7 +6455,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6474,28 +6474,28 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9997819999999999</v>
+        <v>0.999784</v>
       </c>
       <c r="F69" t="n">
-        <v>1403486151</v>
+        <v>1404230861</v>
       </c>
       <c r="G69" t="n">
         <v>68</v>
       </c>
       <c r="H69" t="n">
-        <v>81824505</v>
+        <v>81320776</v>
       </c>
       <c r="I69" t="n">
         <v>1.001</v>
       </c>
       <c r="J69" t="n">
-        <v>0.999711</v>
+        <v>0.999712</v>
       </c>
       <c r="K69" t="n">
-        <v>6.707000000000001e-05</v>
+        <v>4.143e-05</v>
       </c>
       <c r="L69" t="n">
-        <v>-0.05448</v>
+        <v>0.00414</v>
       </c>
       <c r="M69" t="n">
         <v>1403784805.97</v>
@@ -6510,13 +6510,13 @@
         <v>46092.00303240741</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R69" t="b">
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>0.0004484543978475663</v>
+        <v>0.0004518632718371016</v>
       </c>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
@@ -6530,7 +6530,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6549,16 +6549,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.995766</v>
+        <v>0.99577</v>
       </c>
       <c r="F70" t="n">
-        <v>1371171784</v>
+        <v>1371196287</v>
       </c>
       <c r="G70" t="n">
         <v>69</v>
       </c>
       <c r="H70" t="n">
-        <v>346364</v>
+        <v>346913</v>
       </c>
       <c r="I70" t="n">
         <v>0.996614</v>
@@ -6567,10 +6567,10 @@
         <v>0.995093</v>
       </c>
       <c r="K70" t="n">
-        <v>-0.000223555758983696</v>
+        <v>-0.000187773526380997</v>
       </c>
       <c r="L70" t="n">
-        <v>-0.02179</v>
+        <v>-0.01885</v>
       </c>
       <c r="M70" t="n">
         <v>1377035569.737884</v>
@@ -6585,13 +6585,13 @@
         <v>45785.55951388889</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R70" t="b">
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>0.0004297989441062914</v>
+        <v>0.0004327546866876817</v>
       </c>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
@@ -6605,7 +6605,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6624,16 +6624,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.999819</v>
+        <v>0.999826</v>
       </c>
       <c r="F71" t="n">
-        <v>1319746233</v>
+        <v>1319756381</v>
       </c>
       <c r="G71" t="n">
         <v>70</v>
       </c>
       <c r="H71" t="n">
-        <v>9371061</v>
+        <v>9371282</v>
       </c>
       <c r="I71" t="n">
         <v>0.999993</v>
@@ -6642,10 +6642,10 @@
         <v>0.999553</v>
       </c>
       <c r="K71" t="n">
-        <v>4.122e-05</v>
+        <v>7.813999999999999e-05</v>
       </c>
       <c r="L71" t="n">
-        <v>0.00457</v>
+        <v>0.007820000000000001</v>
       </c>
       <c r="M71" t="n">
         <v>1320000000</v>
@@ -6660,13 +6660,13 @@
         <v>45940.56990740741</v>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R71" t="b">
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>0.0004001103852123458</v>
+        <v>0.0004029996844321916</v>
       </c>
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
@@ -6680,7 +6680,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6699,28 +6699,28 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4.94</v>
+        <v>4.93</v>
       </c>
       <c r="F72" t="n">
-        <v>1235200763</v>
+        <v>1232242620</v>
       </c>
       <c r="G72" t="n">
         <v>71</v>
       </c>
       <c r="H72" t="n">
-        <v>78427779</v>
+        <v>79001451</v>
       </c>
       <c r="I72" t="n">
-        <v>4.93</v>
+        <v>4.95</v>
       </c>
       <c r="J72" t="n">
         <v>4.64</v>
       </c>
       <c r="K72" t="n">
-        <v>0.213891</v>
+        <v>0.209943</v>
       </c>
       <c r="L72" t="n">
-        <v>4.4898</v>
+        <v>4.45258</v>
       </c>
       <c r="M72" t="n">
         <v>250000000</v>
@@ -6735,13 +6735,13 @@
         <v>46021.04538194444</v>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R72" t="b">
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>0.0003513013181921147</v>
+        <v>0.0003523780492382739</v>
       </c>
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
@@ -6755,68 +6755,68 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>gatechain-token</t>
+          <t>akedo</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>gt</t>
+          <t>ake</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Akedo</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>11.07</v>
+        <v>0.052399</v>
       </c>
       <c r="F73" t="n">
-        <v>1183284695</v>
+        <v>1196782097</v>
       </c>
       <c r="G73" t="n">
         <v>72</v>
       </c>
       <c r="H73" t="n">
-        <v>3660555</v>
+        <v>44626179</v>
       </c>
       <c r="I73" t="n">
-        <v>11.26</v>
+        <v>0.06265900000000001</v>
       </c>
       <c r="J73" t="n">
-        <v>10.77</v>
+        <v>0.04882322</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.168040860000696</v>
+        <v>-0.003079557998142114</v>
       </c>
       <c r="L73" t="n">
-        <v>-1.49436</v>
+        <v>-5.55094</v>
       </c>
       <c r="M73" t="n">
-        <v>106637271.2738255</v>
+        <v>22796250000</v>
       </c>
       <c r="N73" t="n">
-        <v>118888593.6983193</v>
+        <v>100000000000</v>
       </c>
       <c r="O73" t="n">
-        <v>25.38</v>
+        <v>0.146656</v>
       </c>
       <c r="P73" s="1" t="n">
-        <v>45682.66666666666</v>
+        <v>46285.43993055556</v>
       </c>
       <c r="Q73" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S73" t="n">
-        <v>0.0003213295782226181</v>
+        <v>0.0003318661932903672</v>
       </c>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
@@ -6830,68 +6830,68 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>akedo</t>
+          <t>gatechain-token</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ake</t>
+          <t>gt</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Akedo</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.051642</v>
+        <v>11.08</v>
       </c>
       <c r="F74" t="n">
-        <v>1177171406</v>
+        <v>1181113565</v>
       </c>
       <c r="G74" t="n">
         <v>73</v>
       </c>
       <c r="H74" t="n">
-        <v>43908083</v>
+        <v>2167755</v>
       </c>
       <c r="I74" t="n">
-        <v>0.06265900000000001</v>
+        <v>11.23</v>
       </c>
       <c r="J74" t="n">
-        <v>0.04882322</v>
+        <v>10.77</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.003907926662397344</v>
+        <v>-0.1686314408443543</v>
       </c>
       <c r="L74" t="n">
-        <v>-6.42521</v>
+        <v>-1.49965</v>
       </c>
       <c r="M74" t="n">
-        <v>22796250000</v>
+        <v>106637326.4685546</v>
       </c>
       <c r="N74" t="n">
-        <v>100000000000</v>
+        <v>118888593.6983193</v>
       </c>
       <c r="O74" t="n">
-        <v>0.146656</v>
+        <v>25.38</v>
       </c>
       <c r="P74" s="1" t="n">
-        <v>46285.43993055556</v>
+        <v>45682.66666666666</v>
       </c>
       <c r="Q74" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>0.0003178003065476835</v>
+        <v>0.0003228028562578264</v>
       </c>
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
@@ -6905,7 +6905,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6924,28 +6924,28 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.108775</v>
+        <v>0.108006</v>
       </c>
       <c r="F75" t="n">
-        <v>1166941505</v>
+        <v>1158178709</v>
       </c>
       <c r="G75" t="n">
         <v>74</v>
       </c>
       <c r="H75" t="n">
-        <v>80978742</v>
+        <v>80988029</v>
       </c>
       <c r="I75" t="n">
-        <v>0.112923</v>
+        <v>0.11281</v>
       </c>
       <c r="J75" t="n">
         <v>0.106356</v>
       </c>
       <c r="K75" t="n">
-        <v>-0.003040010552261871</v>
+        <v>-0.003967526668272978</v>
       </c>
       <c r="L75" t="n">
-        <v>-2.75053</v>
+        <v>-3.54326</v>
       </c>
       <c r="M75" t="n">
         <v>10718755191.33206</v>
@@ -6960,13 +6960,13 @@
         <v>45364.45493055556</v>
       </c>
       <c r="Q75" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R75" t="b">
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>0.0003118944676716404</v>
+        <v>0.0003095363722170247</v>
       </c>
       <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr"/>
@@ -6980,7 +6980,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6999,16 +6999,16 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.04167618</v>
+        <v>0.04145009</v>
       </c>
       <c r="F76" t="n">
-        <v>1155383815</v>
+        <v>1148755487</v>
       </c>
       <c r="G76" t="n">
         <v>75</v>
       </c>
       <c r="H76" t="n">
-        <v>24976867</v>
+        <v>24901024</v>
       </c>
       <c r="I76" t="n">
         <v>0.04460429</v>
@@ -7017,10 +7017,10 @@
         <v>0.04133447</v>
       </c>
       <c r="K76" t="n">
-        <v>-0.001949097888989622</v>
+        <v>-0.002310381704365191</v>
       </c>
       <c r="L76" t="n">
-        <v>-4.53567</v>
+        <v>-5.27961</v>
       </c>
       <c r="M76" t="n">
         <v>27714964311.97035</v>
@@ -7035,13 +7035,13 @@
         <v>45504.69498842592</v>
       </c>
       <c r="Q76" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R76" t="b">
         <v>1</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0003052220810161631</v>
+        <v>0.0003040855848095985</v>
       </c>
       <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr"/>
@@ -7055,7 +7055,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7074,28 +7074,28 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>73.95999999999999</v>
+        <v>73.51000000000001</v>
       </c>
       <c r="F77" t="n">
-        <v>1076099999</v>
+        <v>1069014351</v>
       </c>
       <c r="G77" t="n">
         <v>76</v>
       </c>
       <c r="H77" t="n">
-        <v>25158205</v>
+        <v>25197522</v>
       </c>
       <c r="I77" t="n">
-        <v>74.48999999999999</v>
+        <v>75.02</v>
       </c>
       <c r="J77" t="n">
         <v>65.90000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>6.39</v>
+        <v>5.85</v>
       </c>
       <c r="L77" t="n">
-        <v>9.54158</v>
+        <v>8.647360000000001</v>
       </c>
       <c r="M77" t="n">
         <v>14544176.16408117</v>
@@ -7110,13 +7110,13 @@
         <v>44450.05208333334</v>
       </c>
       <c r="Q77" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R77" t="b">
         <v>1</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0002594506270427726</v>
+        <v>0.0002579599623884506</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7179,16 +7179,16 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.090235</v>
+        <v>0.090155</v>
       </c>
       <c r="F78" t="n">
-        <v>1014603162</v>
+        <v>1013630058</v>
       </c>
       <c r="G78" t="n">
         <v>77</v>
       </c>
       <c r="H78" t="n">
-        <v>12821473</v>
+        <v>12821802</v>
       </c>
       <c r="I78" t="n">
         <v>0.094476</v>
@@ -7197,10 +7197,10 @@
         <v>0.087199</v>
       </c>
       <c r="K78" t="n">
-        <v>0.00027014</v>
+        <v>0.00023575</v>
       </c>
       <c r="L78" t="n">
-        <v>0.28909</v>
+        <v>0.26218</v>
       </c>
       <c r="M78" t="n">
         <v>11243022455.381</v>
@@ -7215,13 +7215,13 @@
         <v>45714.36184027778</v>
       </c>
       <c r="Q78" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R78" t="b">
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>0.000223947799526819</v>
+        <v>0.0002259233610164783</v>
       </c>
       <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr"/>
@@ -7235,7 +7235,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7257,13 +7257,13 @@
         <v>7.38</v>
       </c>
       <c r="F79" t="n">
-        <v>1013044584</v>
+        <v>1011903588</v>
       </c>
       <c r="G79" t="n">
         <v>78</v>
       </c>
       <c r="H79" t="n">
-        <v>30103529</v>
+        <v>30162316</v>
       </c>
       <c r="I79" t="n">
         <v>7.47</v>
@@ -7272,10 +7272,10 @@
         <v>7.28</v>
       </c>
       <c r="K79" t="n">
-        <v>0.063027</v>
+        <v>0.059278</v>
       </c>
       <c r="L79" t="n">
-        <v>0.87298</v>
+        <v>0.80992</v>
       </c>
       <c r="M79" t="n">
         <v>137155021.2773955</v>
@@ -7290,13 +7290,13 @@
         <v>44531.29832175926</v>
       </c>
       <c r="Q79" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R79" t="b">
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0002230480146174885</v>
+        <v>0.0002249246982517362</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7359,16 +7359,16 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.111659</v>
+        <v>0.111028</v>
       </c>
       <c r="F80" t="n">
-        <v>1009834244</v>
+        <v>1004021390</v>
       </c>
       <c r="G80" t="n">
         <v>79</v>
       </c>
       <c r="H80" t="n">
-        <v>61193587</v>
+        <v>60317321</v>
       </c>
       <c r="I80" t="n">
         <v>0.113177</v>
@@ -7377,10 +7377,10 @@
         <v>0.108049</v>
       </c>
       <c r="K80" t="n">
-        <v>-0.000111053877648204</v>
+        <v>-0.000907045263806736</v>
       </c>
       <c r="L80" t="n">
-        <v>-0.07658</v>
+        <v>-0.81033</v>
       </c>
       <c r="M80" t="n">
         <v>9042752944.706263</v>
@@ -7395,13 +7395,13 @@
         <v>43636.28563657407</v>
       </c>
       <c r="Q80" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R80" t="b">
         <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>0.0002211946486096146</v>
+        <v>0.0002203653038533829</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7464,16 +7464,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.29984</v>
+        <v>0.297261</v>
       </c>
       <c r="F81" t="n">
-        <v>995820975</v>
+        <v>987368378</v>
       </c>
       <c r="G81" t="n">
         <v>80</v>
       </c>
       <c r="H81" t="n">
-        <v>87853850</v>
+        <v>89403138</v>
       </c>
       <c r="I81" t="n">
         <v>0.30265</v>
@@ -7482,10 +7482,10 @@
         <v>0.288725</v>
       </c>
       <c r="K81" t="n">
-        <v>0.00421596</v>
+        <v>0.0020476</v>
       </c>
       <c r="L81" t="n">
-        <v>1.43657</v>
+        <v>0.6936</v>
       </c>
       <c r="M81" t="n">
         <v>3319369204.37</v>
@@ -7500,13 +7500,13 @@
         <v>45322.29359953704</v>
       </c>
       <c r="Q81" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R81" t="b">
         <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0.0002131046281059314</v>
+        <v>0.0002107325022378297</v>
       </c>
       <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr"/>
@@ -7520,7 +7520,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7575,13 +7575,13 @@
         <v>46287.17361111111</v>
       </c>
       <c r="Q82" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R82" t="b">
         <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0.0002038701396307346</v>
+        <v>0.000206369266777731</v>
       </c>
       <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr"/>
@@ -7595,7 +7595,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7614,16 +7614,16 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="F83" t="n">
-        <v>959212434</v>
+        <v>953590068</v>
       </c>
       <c r="G83" t="n">
         <v>82</v>
       </c>
       <c r="H83" t="n">
-        <v>70655057</v>
+        <v>69764701</v>
       </c>
       <c r="I83" t="n">
         <v>1.82</v>
@@ -7632,10 +7632,10 @@
         <v>1.73</v>
       </c>
       <c r="K83" t="n">
-        <v>-0.001444649463477665</v>
+        <v>-0.01942424605047477</v>
       </c>
       <c r="L83" t="n">
-        <v>-0.10442</v>
+        <v>-1.07234</v>
       </c>
       <c r="M83" t="n">
         <v>532132124.756035</v>
@@ -7650,13 +7650,13 @@
         <v>44458.66666666666</v>
       </c>
       <c r="Q83" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R83" t="b">
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.0001919700985896619</v>
+        <v>0.000191193708946943</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7719,16 +7719,16 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="F84" t="n">
-        <v>948369207</v>
+        <v>944144256</v>
       </c>
       <c r="G84" t="n">
         <v>83</v>
       </c>
       <c r="H84" t="n">
-        <v>88794504</v>
+        <v>88805898</v>
       </c>
       <c r="I84" t="n">
         <v>1.9</v>
@@ -7737,10 +7737,10 @@
         <v>1.79</v>
       </c>
       <c r="K84" t="n">
-        <v>-0.01793686036568287</v>
+        <v>-0.02020480614472042</v>
       </c>
       <c r="L84" t="n">
-        <v>-0.99483</v>
+        <v>-1.09889</v>
       </c>
       <c r="M84" t="n">
         <v>518776241.2826915</v>
@@ -7755,13 +7755,13 @@
         <v>45368.35444444444</v>
       </c>
       <c r="Q84" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R84" t="b">
         <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0.0001857101795974489</v>
+        <v>0.0001857298545346714</v>
       </c>
       <c r="T84" t="inlineStr"/>
       <c r="U84" t="inlineStr"/>
@@ -7775,7 +7775,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7794,28 +7794,28 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.112577</v>
+        <v>0.112712</v>
       </c>
       <c r="F85" t="n">
-        <v>921852139</v>
+        <v>922930974</v>
       </c>
       <c r="G85" t="n">
         <v>84</v>
       </c>
       <c r="H85" t="n">
-        <v>37182180</v>
+        <v>40948327</v>
       </c>
       <c r="I85" t="n">
         <v>0.117046</v>
       </c>
       <c r="J85" t="n">
-        <v>0.112159</v>
+        <v>0.112475</v>
       </c>
       <c r="K85" t="n">
-        <v>7.262000000000001e-05</v>
+        <v>0.00048579</v>
       </c>
       <c r="L85" t="n">
-        <v>0.06308</v>
+        <v>0.43286</v>
       </c>
       <c r="M85" t="n">
         <v>8188743036.341737</v>
@@ -7830,13 +7830,13 @@
         <v>44290.85721064815</v>
       </c>
       <c r="Q85" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R85" t="b">
         <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>0.000170401572889224</v>
+        <v>0.0001734592012065657</v>
       </c>
       <c r="T85" t="inlineStr"/>
       <c r="U85" t="inlineStr"/>
@@ -7850,7 +7850,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7869,16 +7869,16 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.878642</v>
+        <v>0.879281</v>
       </c>
       <c r="F86" t="n">
-        <v>879051060</v>
+        <v>879412431</v>
       </c>
       <c r="G86" t="n">
         <v>85</v>
       </c>
       <c r="H86" t="n">
-        <v>5612054</v>
+        <v>5098330</v>
       </c>
       <c r="I86" t="n">
         <v>0.896209</v>
@@ -7887,10 +7887,10 @@
         <v>0.857331</v>
       </c>
       <c r="K86" t="n">
-        <v>-0.004406381170605767</v>
+        <v>-0.000805513845757888</v>
       </c>
       <c r="L86" t="n">
-        <v>-0.56166</v>
+        <v>-0.09153</v>
       </c>
       <c r="M86" t="n">
         <v>1000000000</v>
@@ -7905,13 +7905,13 @@
         <v>44328.27623842593</v>
       </c>
       <c r="Q86" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R86" t="b">
         <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0.0001456920203437215</v>
+        <v>0.0001482862480304724</v>
       </c>
       <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr"/>
@@ -7925,7 +7925,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7944,16 +7944,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1.015</v>
+        <v>1.014</v>
       </c>
       <c r="F87" t="n">
-        <v>844623999</v>
+        <v>842021201</v>
       </c>
       <c r="G87" t="n">
         <v>86</v>
       </c>
       <c r="H87" t="n">
-        <v>220605992</v>
+        <v>210499976</v>
       </c>
       <c r="I87" t="n">
         <v>1.033</v>
@@ -7962,13 +7962,13 @@
         <v>0.974393</v>
       </c>
       <c r="K87" t="n">
-        <v>0.03620424</v>
+        <v>0.02573698</v>
       </c>
       <c r="L87" t="n">
-        <v>3.72256</v>
+        <v>2.60493</v>
       </c>
       <c r="M87" t="n">
-        <v>830751171</v>
+        <v>830752086</v>
       </c>
       <c r="N87" t="n">
         <v>1957034255</v>
@@ -7980,13 +7980,13 @@
         <v>44287.22894675926</v>
       </c>
       <c r="Q87" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R87" t="b">
         <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>0.0001258168841873008</v>
+        <v>0.0001266575900584778</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8049,16 +8049,16 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>64.04000000000001</v>
+        <v>63.62</v>
       </c>
       <c r="F88" t="n">
-        <v>823802913</v>
+        <v>816756952</v>
       </c>
       <c r="G88" t="n">
         <v>87</v>
       </c>
       <c r="H88" t="n">
-        <v>217954738</v>
+        <v>216929174</v>
       </c>
       <c r="I88" t="n">
         <v>64.89</v>
@@ -8067,16 +8067,16 @@
         <v>58.18</v>
       </c>
       <c r="K88" t="n">
-        <v>5.44</v>
+        <v>4.75</v>
       </c>
       <c r="L88" t="n">
-        <v>9.115830000000001</v>
+        <v>8.06732</v>
       </c>
       <c r="M88" t="n">
         <v>12842808.78359296</v>
       </c>
       <c r="N88" t="n">
-        <v>12842814.69092887</v>
+        <v>12842844.19760836</v>
       </c>
       <c r="O88" t="n">
         <v>1493.59</v>
@@ -8085,13 +8085,13 @@
         <v>43088.66666666666</v>
       </c>
       <c r="Q88" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R88" t="b">
         <v>1</v>
       </c>
       <c r="S88" t="n">
-        <v>0.0001137966330489725</v>
+        <v>0.0001120436872652211</v>
       </c>
       <c r="T88" t="inlineStr"/>
       <c r="U88" t="inlineStr"/>
@@ -8105,7 +8105,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8127,13 +8127,13 @@
         <v>2.54</v>
       </c>
       <c r="F89" t="n">
-        <v>812122971</v>
+        <v>811500600</v>
       </c>
       <c r="G89" t="n">
         <v>88</v>
       </c>
       <c r="H89" t="n">
-        <v>91419688</v>
+        <v>91997476</v>
       </c>
       <c r="I89" t="n">
         <v>2.59</v>
@@ -8142,10 +8142,10 @@
         <v>2.46</v>
       </c>
       <c r="K89" t="n">
-        <v>0.00034305</v>
+        <v>-0.002035382228805283</v>
       </c>
       <c r="L89" t="n">
-        <v>0.02274</v>
+        <v>-0.07997</v>
       </c>
       <c r="M89" t="n">
         <v>318995589.2344064</v>
@@ -8160,13 +8160,13 @@
         <v>44316.08914351852</v>
       </c>
       <c r="Q89" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R89" t="b">
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>0.0001070536689153482</v>
+        <v>0.0001090031924864077</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8229,16 +8229,16 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.0092481</v>
+        <v>0.00918296</v>
       </c>
       <c r="F90" t="n">
-        <v>796072690</v>
+        <v>789620256</v>
       </c>
       <c r="G90" t="n">
         <v>89</v>
       </c>
       <c r="H90" t="n">
-        <v>16039748</v>
+        <v>16654905</v>
       </c>
       <c r="I90" t="n">
         <v>0.0093454</v>
@@ -8247,10 +8247,10 @@
         <v>0.00888102</v>
       </c>
       <c r="K90" t="n">
-        <v>0.00011927</v>
+        <v>-5.874247927338e-06</v>
       </c>
       <c r="L90" t="n">
-        <v>1.21252</v>
+        <v>-0.06393</v>
       </c>
       <c r="M90" t="n">
         <v>85985041177</v>
@@ -8265,13 +8265,13 @@
         <v>44304.71413194444</v>
       </c>
       <c r="Q90" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R90" t="b">
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>9.778765808091152e-05</v>
+        <v>9.634668247896528e-05</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8337,13 +8337,13 @@
         <v>7.8</v>
       </c>
       <c r="F91" t="n">
-        <v>780922158</v>
+        <v>779786046</v>
       </c>
       <c r="G91" t="n">
         <v>90</v>
       </c>
       <c r="H91" t="n">
-        <v>162120178</v>
+        <v>157009128</v>
       </c>
       <c r="I91" t="n">
         <v>7.99</v>
@@ -8352,10 +8352,10 @@
         <v>7.5</v>
       </c>
       <c r="K91" t="n">
-        <v>0.04412324</v>
+        <v>0.01423484</v>
       </c>
       <c r="L91" t="n">
-        <v>0.52981</v>
+        <v>0.18285</v>
       </c>
       <c r="M91" t="n">
         <v>100000000</v>
@@ -8370,13 +8370,13 @@
         <v>45365.29608796296</v>
       </c>
       <c r="Q91" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R91" t="b">
         <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>8.904108263718691e-05</v>
+        <v>9.065816234965238e-05</v>
       </c>
       <c r="T91" t="inlineStr"/>
       <c r="U91" t="inlineStr"/>
@@ -8390,7 +8390,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8427,10 +8427,10 @@
         <v>1.21</v>
       </c>
       <c r="K92" t="n">
-        <v>-0.001829979194463149</v>
+        <v>-0.001516706866147688</v>
       </c>
       <c r="L92" t="n">
-        <v>-0.15067</v>
+        <v>-0.12491</v>
       </c>
       <c r="M92" t="n">
         <v>642998758.0930901</v>
@@ -8445,13 +8445,13 @@
         <v>46049.54175925926</v>
       </c>
       <c r="Q92" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R92" t="b">
         <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>8.838277036112245e-05</v>
+        <v>9.065573578545023e-05</v>
       </c>
       <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr"/>
@@ -8465,7 +8465,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8511,7 +8511,7 @@
         <v>65413837.965085</v>
       </c>
       <c r="N93" t="n">
-        <v>65413837.965085</v>
+        <v>65373552.035848</v>
       </c>
       <c r="O93" t="n">
         <v>11.22</v>
@@ -8520,13 +8520,13 @@
         <v>46287.57291666666</v>
       </c>
       <c r="Q93" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R93" t="b">
         <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>6.192064807590162e-05</v>
+        <v>6.414179208288009e-05</v>
       </c>
       <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr"/>
@@ -8540,7 +8540,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8559,16 +8559,16 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.999159</v>
+        <v>0.999162</v>
       </c>
       <c r="F94" t="n">
-        <v>698406630</v>
+        <v>698406791</v>
       </c>
       <c r="G94" t="n">
         <v>93</v>
       </c>
       <c r="H94" t="n">
-        <v>4739386</v>
+        <v>4746550</v>
       </c>
       <c r="I94" t="n">
         <v>0.999281</v>
@@ -8577,10 +8577,10 @@
         <v>0.998814</v>
       </c>
       <c r="K94" t="n">
-        <v>0.00020014</v>
+        <v>0.00022591</v>
       </c>
       <c r="L94" t="n">
-        <v>0.02062</v>
+        <v>0.02261</v>
       </c>
       <c r="M94" t="n">
         <v>699000000</v>
@@ -8595,13 +8595,13 @@
         <v>45350.38608796296</v>
       </c>
       <c r="Q94" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R94" t="b">
         <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>4.140392435582949e-05</v>
+        <v>4.358498309316028e-05</v>
       </c>
       <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
@@ -8615,7 +8615,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8634,16 +8634,16 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.797092</v>
+        <v>0.792002</v>
       </c>
       <c r="F95" t="n">
-        <v>694745959</v>
+        <v>690250378</v>
       </c>
       <c r="G95" t="n">
         <v>94</v>
       </c>
       <c r="H95" t="n">
-        <v>156133688</v>
+        <v>152849727</v>
       </c>
       <c r="I95" t="n">
         <v>0.80848</v>
@@ -8652,13 +8652,13 @@
         <v>0.748675</v>
       </c>
       <c r="K95" t="n">
-        <v>0.01777609</v>
+        <v>0.01030098</v>
       </c>
       <c r="L95" t="n">
-        <v>2.38927</v>
+        <v>1.31776</v>
       </c>
       <c r="M95" t="n">
-        <v>870646072.2327943</v>
+        <v>870645897.0627604</v>
       </c>
       <c r="N95" t="n">
         <v>1209086276.864642</v>
@@ -8670,13 +8670,13 @@
         <v>44952.26755787037</v>
       </c>
       <c r="Q95" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R95" t="b">
         <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>3.929057710992718e-05</v>
+        <v>3.886697122098251e-05</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8775,13 +8775,13 @@
         <v>46287.38530092593</v>
       </c>
       <c r="Q96" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R96" t="b">
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>2.944522731784314e-05</v>
+        <v>3.160277391889329e-05</v>
       </c>
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
@@ -8795,7 +8795,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8814,16 +8814,16 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.681867</v>
+        <v>0.680061</v>
       </c>
       <c r="F97" t="n">
-        <v>677295717</v>
+        <v>675050792</v>
       </c>
       <c r="G97" t="n">
         <v>96</v>
       </c>
       <c r="H97" t="n">
-        <v>52560213</v>
+        <v>51710166</v>
       </c>
       <c r="I97" t="n">
         <v>0.717605</v>
@@ -8832,13 +8832,13 @@
         <v>0.673687</v>
       </c>
       <c r="K97" t="n">
-        <v>-0.006533631426253295</v>
+        <v>-0.00846509180192645</v>
       </c>
       <c r="L97" t="n">
-        <v>-0.9434</v>
+        <v>-1.22945</v>
       </c>
       <c r="M97" t="n">
-        <v>992642375.2273064</v>
+        <v>992641877.0384015</v>
       </c>
       <c r="N97" t="n">
         <v>1983240735.576791</v>
@@ -8850,13 +8850,13 @@
         <v>45633.25043981482</v>
       </c>
       <c r="Q97" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R97" t="b">
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>2.921635277481791e-05</v>
+        <v>3.007489225193237e-05</v>
       </c>
       <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr"/>
@@ -8870,7 +8870,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8889,16 +8889,16 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.694674</v>
+        <v>0.693433</v>
       </c>
       <c r="F98" t="n">
-        <v>670843751</v>
+        <v>669586560</v>
       </c>
       <c r="G98" t="n">
         <v>97</v>
       </c>
       <c r="H98" t="n">
-        <v>51398286</v>
+        <v>50159691</v>
       </c>
       <c r="I98" t="n">
         <v>0.7237980000000001</v>
@@ -8907,10 +8907,10 @@
         <v>0.679153</v>
       </c>
       <c r="K98" t="n">
-        <v>-0.01384730796520994</v>
+        <v>-0.01990448344609985</v>
       </c>
       <c r="L98" t="n">
-        <v>-1.8656</v>
+        <v>-2.79033</v>
       </c>
       <c r="M98" t="n">
         <v>965350000</v>
@@ -8925,13 +8925,13 @@
         <v>45378.63525462963</v>
       </c>
       <c r="Q98" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R98" t="b">
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>2.549155899336217e-05</v>
+        <v>2.691415094955672e-05</v>
       </c>
       <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr"/>
@@ -8945,7 +8945,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8964,16 +8964,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.0244496</v>
+        <v>0.02442636</v>
       </c>
       <c r="F99" t="n">
-        <v>649555722</v>
+        <v>648559721</v>
       </c>
       <c r="G99" t="n">
         <v>98</v>
       </c>
       <c r="H99" t="n">
-        <v>8832998</v>
+        <v>8673652</v>
       </c>
       <c r="I99" t="n">
         <v>0.02532359</v>
@@ -8982,13 +8982,13 @@
         <v>0.02415728</v>
       </c>
       <c r="K99" t="n">
-        <v>-0.000240188203144351</v>
+        <v>-0.000249403786291184</v>
       </c>
       <c r="L99" t="n">
-        <v>-1.00191</v>
+        <v>-1.01072</v>
       </c>
       <c r="M99" t="n">
-        <v>26560136831</v>
+        <v>26560449245</v>
       </c>
       <c r="N99" t="n">
         <v>100000000000</v>
@@ -9000,13 +9000,13 @@
         <v>46156.97986111111</v>
       </c>
       <c r="Q99" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R99" t="b">
         <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>1.320173631936647e-05</v>
+        <v>1.475134408379715e-05</v>
       </c>
       <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr"/>
@@ -9020,7 +9020,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9039,16 +9039,16 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.335931</v>
+        <v>0.335613</v>
       </c>
       <c r="F100" t="n">
-        <v>628228951</v>
+        <v>627121537</v>
       </c>
       <c r="G100" t="n">
         <v>99</v>
       </c>
       <c r="H100" t="n">
-        <v>34548808</v>
+        <v>34440364</v>
       </c>
       <c r="I100" t="n">
         <v>0.353654</v>
@@ -9057,10 +9057,10 @@
         <v>0.332299</v>
       </c>
       <c r="K100" t="n">
-        <v>-0.008535159644705137</v>
+        <v>-0.009784445667260777</v>
       </c>
       <c r="L100" t="n">
-        <v>-2.52239</v>
+        <v>-2.8328</v>
       </c>
       <c r="M100" t="n">
         <v>1868553460.192209</v>
@@ -9075,13 +9075,13 @@
         <v>45383.19094907407</v>
       </c>
       <c r="Q100" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R100" t="b">
         <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>8.895474455673138e-07</v>
+        <v>2.350597992355773e-06</v>
       </c>
       <c r="T100" t="inlineStr"/>
       <c r="U100" t="inlineStr"/>
@@ -9095,7 +9095,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9114,28 +9114,28 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.00996264</v>
+        <v>0.00991273</v>
       </c>
       <c r="F101" t="n">
-        <v>626688106</v>
+        <v>623057866</v>
       </c>
       <c r="G101" t="n">
         <v>100</v>
       </c>
       <c r="H101" t="n">
-        <v>486369273</v>
+        <v>482275460</v>
       </c>
       <c r="I101" t="n">
         <v>0.01047348</v>
       </c>
       <c r="J101" t="n">
-        <v>0.008669339999999999</v>
+        <v>0.00867449</v>
       </c>
       <c r="K101" t="n">
-        <v>0.00129078</v>
+        <v>0.00112527</v>
       </c>
       <c r="L101" t="n">
-        <v>14.87479</v>
+        <v>12.80544</v>
       </c>
       <c r="M101" t="n">
         <v>62860396090</v>
@@ -9150,7 +9150,7 @@
         <v>45643.21206018519</v>
       </c>
       <c r="Q101" s="1" t="n">
-        <v>46287.91469907408</v>
+        <v>46287.92372685186</v>
       </c>
       <c r="R101" t="b">
         <v>1</v>

--- a/src/xlsx/enriched_data.xlsx
+++ b/src/xlsx/enriched_data.xlsx
@@ -560,7 +560,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -579,34 +579,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>86091</v>
+        <v>85660</v>
       </c>
       <c r="F2" t="n">
-        <v>1729404845826</v>
+        <v>1720796656545</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>43292611645</v>
+        <v>40475457238</v>
       </c>
       <c r="I2" t="n">
-        <v>86669</v>
+        <v>87251</v>
       </c>
       <c r="J2" t="n">
-        <v>85107</v>
+        <v>85266</v>
       </c>
       <c r="K2" t="n">
-        <v>-493.3569849451887</v>
+        <v>-433.6906185361877</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.5698</v>
+        <v>-0.50375</v>
       </c>
       <c r="M2" t="n">
-        <v>20088034</v>
+        <v>20088325</v>
       </c>
       <c r="N2" t="n">
-        <v>20088056</v>
+        <v>20088325</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -615,7 +615,7 @@
         <v>45936.45673611111</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
@@ -665,7 +665,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -684,34 +684,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2740.68</v>
+        <v>2713.74</v>
       </c>
       <c r="F3" t="n">
-        <v>334532231831</v>
+        <v>331259670445</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>16217849740</v>
+        <v>16541219556</v>
       </c>
       <c r="I3" t="n">
-        <v>2786.01</v>
+        <v>2786.6</v>
       </c>
       <c r="J3" t="n">
-        <v>2716.11</v>
+        <v>2714.35</v>
       </c>
       <c r="K3" t="n">
-        <v>-33.60544003023369</v>
+        <v>-38.06506006067275</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.21132</v>
+        <v>-1.38328</v>
       </c>
       <c r="M3" t="n">
-        <v>122070499.1930826</v>
+        <v>122073393.4861459</v>
       </c>
       <c r="N3" t="n">
-        <v>122070499.1930825</v>
+        <v>122073393.4861459</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -720,13 +720,13 @@
         <v>45893.47295138889</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1931470913741057</v>
+        <v>0.192208483399482</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -789,34 +789,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999907</v>
+        <v>0.9997239999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>183365485085</v>
+        <v>183423662761</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>78653569988</v>
+        <v>77641044569</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999627</v>
+        <v>0.9996159999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00010509</v>
+        <v>-1.3375693649009e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01051</v>
+        <v>-0.00134</v>
       </c>
       <c r="M4" t="n">
-        <v>183384649781.6938</v>
+        <v>183470116796.0007</v>
       </c>
       <c r="N4" t="n">
-        <v>188851595759.0362</v>
+        <v>188937062885.4362</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -825,13 +825,13 @@
         <v>43304.66666666666</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1057058956148769</v>
+        <v>0.1062657024229202</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -894,34 +894,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>783.59</v>
+        <v>780.89</v>
       </c>
       <c r="F5" t="n">
-        <v>104365737195</v>
+        <v>103989325404</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1332694189</v>
+        <v>1153867414</v>
       </c>
       <c r="I5" t="n">
-        <v>803.09</v>
+        <v>798.34</v>
       </c>
       <c r="J5" t="n">
-        <v>781.83</v>
+        <v>777.16</v>
       </c>
       <c r="K5" t="n">
-        <v>-21.77282668240503</v>
+        <v>-8.973599075082916</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.70348</v>
+        <v>-1.1361</v>
       </c>
       <c r="M5" t="n">
-        <v>133160043.94</v>
+        <v>133159986.57</v>
       </c>
       <c r="N5" t="n">
-        <v>133160043.94</v>
+        <v>133159986.57</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -930,13 +930,13 @@
         <v>45943.02875</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06000912321700162</v>
+        <v>0.06008745421100078</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -999,28 +999,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="F6" t="n">
-        <v>97984064776</v>
+        <v>98975003054</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>6102739669</v>
+        <v>6721150870</v>
       </c>
       <c r="I6" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="J6" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.003611992187942059</v>
+        <v>0.00486281</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.23129</v>
+        <v>0.30987</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -1035,13 +1035,13 @@
         <v>45855.82005787037</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R6" t="b">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05631769584112064</v>
+        <v>0.05717243496620979</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1104,34 +1104,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999896</v>
+        <v>0.9998</v>
       </c>
       <c r="F7" t="n">
-        <v>75083335862</v>
+        <v>75112332603</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>20036837511</v>
+        <v>20985936797</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999744</v>
+        <v>0.999641</v>
       </c>
       <c r="K7" t="n">
-        <v>3.21e-05</v>
+        <v>-2.9422490854358e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00321</v>
+        <v>-0.00294</v>
       </c>
       <c r="M7" t="n">
-        <v>75091582641.99438</v>
+        <v>75125433963.32286</v>
       </c>
       <c r="N7" t="n">
-        <v>75118327863.70384</v>
+        <v>75154585345.82596</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -1140,13 +1140,13 @@
         <v>43418.66666666666</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04307095234029781</v>
+        <v>0.04330014301099269</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1209,34 +1209,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>117.81</v>
+        <v>116.72</v>
       </c>
       <c r="F8" t="n">
-        <v>69220864144</v>
+        <v>68558658494</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>4526147359</v>
+        <v>4497356714</v>
       </c>
       <c r="I8" t="n">
-        <v>119.82</v>
+        <v>119.66</v>
       </c>
       <c r="J8" t="n">
-        <v>115.58</v>
+        <v>116.08</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.566908205533849</v>
+        <v>-0.8052274963640826</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.31262</v>
+        <v>-0.68515</v>
       </c>
       <c r="M8" t="n">
-        <v>587507355.8515188</v>
+        <v>587506755.615492</v>
       </c>
       <c r="N8" t="n">
-        <v>634531021.326126</v>
+        <v>634530393.8774225</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -1245,13 +1245,13 @@
         <v>45676.13572916666</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R8" t="b">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03967985245780897</v>
+        <v>0.03949023913598085</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1314,34 +1314,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.341646</v>
+        <v>0.34171</v>
       </c>
       <c r="F9" t="n">
-        <v>32445098179</v>
+        <v>32452956079</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>609223370</v>
+        <v>464108235</v>
       </c>
       <c r="I9" t="n">
-        <v>0.349178</v>
+        <v>0.345004</v>
       </c>
       <c r="J9" t="n">
         <v>0.34041</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.002577573979136272</v>
+        <v>-0.001158784293061932</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.74881</v>
+        <v>-0.33797</v>
       </c>
       <c r="M9" t="n">
         <v>94961729708.24278</v>
       </c>
       <c r="N9" t="n">
-        <v>94962102587.18929</v>
+        <v>94963358525.63339</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1350,13 +1350,13 @@
         <v>45629.67407407407</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01840720473493112</v>
+        <v>0.01850059985073993</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1419,34 +1419,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1517.69</v>
+        <v>1634.87</v>
       </c>
       <c r="F10" t="n">
-        <v>25711477168</v>
+        <v>27693853314</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>1293999353</v>
+        <v>2062081097</v>
       </c>
       <c r="I10" t="n">
-        <v>1562.57</v>
+        <v>1658.86</v>
       </c>
       <c r="J10" t="n">
-        <v>1445.89</v>
+        <v>1501.2</v>
       </c>
       <c r="K10" t="n">
-        <v>51.21</v>
+        <v>119.98</v>
       </c>
       <c r="L10" t="n">
-        <v>3.49205</v>
+        <v>7.92037</v>
       </c>
       <c r="M10" t="n">
         <v>16945106.4155448</v>
       </c>
       <c r="N10" t="n">
-        <v>16946950.1655448</v>
+        <v>16948106.4155448</v>
       </c>
       <c r="O10" t="n">
         <v>3191.93</v>
@@ -1455,13 +1455,13 @@
         <v>42671.66666666666</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01451219551057677</v>
+        <v>0.01573394960777878</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1524,16 +1524,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.039</v>
+        <v>1.031</v>
       </c>
       <c r="F11" t="n">
-        <v>23851750157</v>
+        <v>23674581041</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>84486417</v>
+        <v>189366594</v>
       </c>
       <c r="I11" t="n">
         <v>1.043</v>
@@ -1542,10 +1542,10 @@
         <v>1.006</v>
       </c>
       <c r="K11" t="n">
-        <v>0.02578041</v>
+        <v>0.01784585</v>
       </c>
       <c r="L11" t="n">
-        <v>2.54554</v>
+        <v>1.76152</v>
       </c>
       <c r="M11" t="n">
         <v>22966221270.418</v>
@@ -1560,13 +1560,13 @@
         <v>46237.59675925926</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R11" t="b">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01343645129349168</v>
+        <v>0.01339739140348825</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
@@ -1580,7 +1580,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1599,28 +1599,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>96.73</v>
+        <v>95.42</v>
       </c>
       <c r="F12" t="n">
-        <v>21532342792</v>
+        <v>21227739049</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1239088705</v>
+        <v>1156045775</v>
       </c>
       <c r="I12" t="n">
-        <v>97.72</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>92.19</v>
+        <v>93.83</v>
       </c>
       <c r="K12" t="n">
-        <v>3.56</v>
+        <v>0.102821</v>
       </c>
       <c r="L12" t="n">
-        <v>3.81642</v>
+        <v>0.10787</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1629,19 +1629,19 @@
         <v>955307079.4341414</v>
       </c>
       <c r="O12" t="n">
-        <v>97.72</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>46287.91296296296</v>
+        <v>46288.22002314815</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R12" t="b">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01209480865174627</v>
+        <v>0.01197494765181307</v>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
@@ -1655,7 +1655,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1674,34 +1674,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.09957199999999999</v>
+        <v>0.09939099999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>15542670956</v>
+        <v>15510961595</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>2351774773</v>
+        <v>1716316067</v>
       </c>
       <c r="I13" t="n">
-        <v>0.105575</v>
+        <v>0.104229</v>
       </c>
       <c r="J13" t="n">
-        <v>0.097356</v>
+        <v>0.098667</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.000911816708137669</v>
+        <v>-0.001316097675634703</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.90742</v>
+        <v>-1.30685</v>
       </c>
       <c r="M13" t="n">
-        <v>156025536383.7052</v>
+        <v>156034686383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171738483126.579</v>
+        <v>156034696383.7052</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1710,13 +1710,13 @@
         <v>44323.88082175926</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R13" t="b">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.00863013087823274</v>
+        <v>0.008651564124904941</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1779,34 +1779,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>565.58</v>
+        <v>563.9299999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>10647327594</v>
+        <v>10598490531</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>162542598</v>
+        <v>147373493</v>
       </c>
       <c r="I14" t="n">
-        <v>601.01</v>
+        <v>577.02</v>
       </c>
       <c r="J14" t="n">
-        <v>561.65</v>
+        <v>555.9400000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-29.14801141764497</v>
+        <v>-10.32139536398063</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.90107</v>
+        <v>-1.79737</v>
       </c>
       <c r="M14" t="n">
-        <v>18808149.70786505</v>
+        <v>18808405.30238605</v>
       </c>
       <c r="N14" t="n">
-        <v>18808149.70786505</v>
+        <v>18808438.90178666</v>
       </c>
       <c r="O14" t="n">
         <v>797.73</v>
@@ -1815,13 +1815,13 @@
         <v>46036.48202546296</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.005798458659047338</v>
+        <v>0.00579575496635755</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1884,28 +1884,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>86.51000000000001</v>
+        <v>85.92</v>
       </c>
       <c r="F15" t="n">
-        <v>10282998071</v>
+        <v>10212986508</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>147623670</v>
+        <v>120844109</v>
       </c>
       <c r="I15" t="n">
-        <v>87.28</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>85.56999999999999</v>
+        <v>85.67</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6142900680501384</v>
+        <v>-0.6889404075766237</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.70508</v>
+        <v>-0.7954599999999999</v>
       </c>
       <c r="M15" t="n">
         <v>118852171</v>
@@ -1920,13 +1920,13 @@
         <v>46286.85358796296</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.005587715160048591</v>
+        <v>0.005571646588883702</v>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
@@ -1940,187 +1940,187 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>USDS</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>12.87</v>
+        <v>0.999889</v>
       </c>
       <c r="F16" t="n">
-        <v>9628433562</v>
+        <v>9604357137</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>579744023</v>
+        <v>213968809</v>
       </c>
       <c r="I16" t="n">
-        <v>13.26</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>12.78</v>
+        <v>0.999631</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2855421127928377</v>
+        <v>-5.6344570002698e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.17079</v>
+        <v>-0.00563</v>
       </c>
       <c r="M16" t="n">
-        <v>748099970.424884</v>
+        <v>9604704100.806463</v>
       </c>
       <c r="N16" t="n">
-        <v>1000000000</v>
+        <v>9607472753.612017</v>
       </c>
       <c r="O16" t="n">
-        <v>52.7</v>
+        <v>1.057</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>44325.67635416667</v>
+        <v>45593.90336805556</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R16" t="b">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.005209087554437127</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Oráculo</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Infraestructura Web3</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>N/A (token ERC-20, red de oráculos)</t>
-        </is>
-      </c>
-      <c r="W16" t="n">
-        <v>2017</v>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>chain.link</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Conexión de datos externos a contratos inteligentes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Token ERC-20 sobre Ethereum</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Provee datos del mundo real (oráculos) a contratos inteligentes.</t>
-        </is>
-      </c>
+        <v>0.005217826829089034</v>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>chainlink</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>USDS</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.999928</v>
+        <v>12.67</v>
       </c>
       <c r="F17" t="n">
-        <v>9591907549</v>
+        <v>9479889414</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>246657449</v>
+        <v>562753051</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>13.21</v>
       </c>
       <c r="J17" t="n">
-        <v>0.999729</v>
+        <v>12.68</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.000119341335104495</v>
+        <v>-0.3822432461842418</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.01193</v>
+        <v>-2.92782</v>
       </c>
       <c r="M17" t="n">
-        <v>9593648553.437454</v>
+        <v>748099970.424884</v>
       </c>
       <c r="N17" t="n">
-        <v>9595406974.451723</v>
+        <v>1000000000</v>
       </c>
       <c r="O17" t="n">
-        <v>1.057</v>
+        <v>52.7</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>45593.90336805556</v>
+        <v>44325.67635416667</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.005187959374319553</v>
-      </c>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
+        <v>0.005145468934527207</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Oráculo</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Infraestructura Web3</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>N/A (token ERC-20, red de oráculos)</t>
+        </is>
+      </c>
+      <c r="W17" t="n">
+        <v>2017</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>chain.link</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Conexión de datos externos a contratos inteligentes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Token ERC-20 sobre Ethereum</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Provee datos del mundo real (oráculos) a contratos inteligentes.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2139,28 +2139,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.250084</v>
+        <v>0.248372</v>
       </c>
       <c r="F18" t="n">
-        <v>9387066598</v>
+        <v>9320073154</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>878118215</v>
+        <v>864974645</v>
       </c>
       <c r="I18" t="n">
-        <v>0.253817</v>
+        <v>0.261886</v>
       </c>
       <c r="J18" t="n">
-        <v>0.240769</v>
+        <v>0.246132</v>
       </c>
       <c r="K18" t="n">
-        <v>0.00426462</v>
+        <v>-0.004014587718880164</v>
       </c>
       <c r="L18" t="n">
-        <v>1.73486</v>
+        <v>-1.59065</v>
       </c>
       <c r="M18" t="n">
         <v>37529061988.53558</v>
@@ -2175,13 +2175,13 @@
         <v>44440.91678240741</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R18" t="b">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.00506947076434772</v>
+        <v>0.005052561570179056</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.01306924</v>
+        <v>0.01268255</v>
       </c>
       <c r="F19" t="n">
-        <v>9265634480</v>
+        <v>8997710190</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>24665700</v>
+        <v>25047308</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01400767</v>
+        <v>0.01348598</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0130548</v>
+        <v>0.01270828</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.000895503351973326</v>
+        <v>-0.000786568705675847</v>
       </c>
       <c r="L19" t="n">
-        <v>-6.4126</v>
+        <v>-5.8398</v>
       </c>
       <c r="M19" t="n">
-        <v>709239749688.8101</v>
+        <v>709240042765.4675</v>
       </c>
       <c r="N19" t="n">
         <v>1142408526965.963</v>
@@ -2280,13 +2280,13 @@
         <v>46259.82847222222</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R19" t="b">
         <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>0.004999229326795736</v>
+        <v>0.004865159528930578</v>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
@@ -2300,7 +2300,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2322,25 +2322,25 @@
         <v>8.98</v>
       </c>
       <c r="F20" t="n">
-        <v>8256209354</v>
+        <v>8264196225</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>122371</v>
+        <v>174153</v>
       </c>
       <c r="I20" t="n">
         <v>9</v>
       </c>
       <c r="J20" t="n">
-        <v>8.880000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.02214698</v>
+        <v>0.01392138</v>
       </c>
       <c r="L20" t="n">
-        <v>0.24736</v>
+        <v>0.1552</v>
       </c>
       <c r="M20" t="n">
         <v>919857851.9</v>
@@ -2355,13 +2355,13 @@
         <v>46146.39930555555</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.004415335435137412</v>
+        <v>0.004438739531361426</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2424,31 +2424,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.213671</v>
+        <v>0.212671</v>
       </c>
       <c r="F21" t="n">
-        <v>7466217685</v>
+        <v>7429479507</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>374469403</v>
+        <v>393742905</v>
       </c>
       <c r="I21" t="n">
-        <v>0.218266</v>
+        <v>0.224502</v>
       </c>
       <c r="J21" t="n">
-        <v>0.209091</v>
+        <v>0.210057</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.004282575427316249</v>
+        <v>-0.001867059350335182</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.9649</v>
+        <v>-0.87027</v>
       </c>
       <c r="M21" t="n">
-        <v>34932729791.51797</v>
+        <v>34932724603.07527</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70148</v>
@@ -2460,13 +2460,13 @@
         <v>43102.66666666666</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R21" t="b">
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.003958371071848852</v>
+        <v>0.00395348646482916</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2529,34 +2529,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>333.6</v>
+        <v>353.73</v>
       </c>
       <c r="F22" t="n">
-        <v>6716534493</v>
+        <v>7104701843</v>
       </c>
       <c r="G22" t="n">
         <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>1250678373</v>
+        <v>1522885394</v>
       </c>
       <c r="I22" t="n">
-        <v>346.9</v>
+        <v>365.1</v>
       </c>
       <c r="J22" t="n">
-        <v>261.8</v>
+        <v>315.1</v>
       </c>
       <c r="K22" t="n">
-        <v>62.94</v>
+        <v>33.15</v>
       </c>
       <c r="L22" t="n">
-        <v>23.25311</v>
+        <v>10.34023</v>
       </c>
       <c r="M22" t="n">
-        <v>20092971.77165077</v>
+        <v>20093343.64665077</v>
       </c>
       <c r="N22" t="n">
-        <v>20092968.64665077</v>
+        <v>20093340.52165077</v>
       </c>
       <c r="O22" t="n">
         <v>3785.82</v>
@@ -2565,13 +2565,13 @@
         <v>43088.66666666666</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R22" t="b">
         <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0.003524722824729912</v>
+        <v>0.003764680665210342</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2615,485 +2615,485 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>uniswap</t>
+          <t>near</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>uni</t>
+          <t>near</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Uniswap</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>9.460000000000001</v>
+        <v>4.74</v>
       </c>
       <c r="F23" t="n">
-        <v>5866836849</v>
+        <v>6192679700</v>
       </c>
       <c r="G23" t="n">
         <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>1601168901</v>
+        <v>2285905002</v>
       </c>
       <c r="I23" t="n">
-        <v>9.699999999999999</v>
+        <v>4.79</v>
       </c>
       <c r="J23" t="n">
-        <v>8.68</v>
+        <v>4.25</v>
       </c>
       <c r="K23" t="n">
-        <v>0.669198</v>
+        <v>0.270313</v>
       </c>
       <c r="L23" t="n">
-        <v>7.61587</v>
+        <v>6.04429</v>
       </c>
       <c r="M23" t="n">
-        <v>620708422.6104751</v>
+        <v>1307081067</v>
       </c>
       <c r="N23" t="n">
-        <v>887956418.9163101</v>
+        <v>1307081081</v>
       </c>
       <c r="O23" t="n">
-        <v>44.92</v>
+        <v>20.44</v>
       </c>
       <c r="P23" s="1" t="n">
-        <v>44318.89240740741</v>
+        <v>44577.59010416667</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R23" t="b">
         <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>0.003033222017677415</v>
+        <v>0.003234486969441955</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>DeFi</t>
+          <t>Plataforma de contratos inteligentes</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>Exchange descentralizado</t>
+          <t>Layer 1</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>N/A (token ERC-20)</t>
+          <t>Proof of Stake (sharding)</t>
         </is>
       </c>
       <c r="W23" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>uniswap.org</t>
+          <t>near.org</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>Intercambio descentralizado de tokens</t>
+          <t>dApps escalables mediante sharding</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>Token ERC-20 sobre Ethereum</t>
+          <t>Blockchain propia (Layer 1)</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Uno de los mayores exchanges descentralizados (DEX) del ecosistema Ethereum.</t>
+          <t>Usa sharding para escalar el procesamiento de transacciones.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>uniswap</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>uni</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NEAR Protocol</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4.32</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>5650487357</v>
+        <v>5923296357</v>
       </c>
       <c r="G24" t="n">
         <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>1655744565</v>
+        <v>2063905504</v>
       </c>
       <c r="I24" t="n">
-        <v>4.65</v>
+        <v>10.89</v>
       </c>
       <c r="J24" t="n">
-        <v>4.21</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.164253</v>
+        <v>0.460594</v>
       </c>
       <c r="L24" t="n">
-        <v>3.9499</v>
+        <v>5.07712</v>
       </c>
       <c r="M24" t="n">
-        <v>1307027694</v>
+        <v>620668422.6104751</v>
       </c>
       <c r="N24" t="n">
-        <v>1307027728</v>
+        <v>887916418.9163101</v>
       </c>
       <c r="O24" t="n">
-        <v>20.44</v>
+        <v>44.92</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>44577.59010416667</v>
+        <v>44318.89240740741</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R24" t="b">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.002908076384199116</v>
+        <v>0.003077884028055243</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>Plataforma de contratos inteligentes</t>
+          <t>DeFi</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>Layer 1</t>
+          <t>Exchange descentralizado</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Proof of Stake (sharding)</t>
+          <t>N/A (token ERC-20)</t>
         </is>
       </c>
       <c r="W24" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>near.org</t>
+          <t>uniswap.org</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>dApps escalables mediante sharding</t>
+          <t>Intercambio descentralizado de tokens</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>Blockchain propia (Layer 1)</t>
+          <t>Token ERC-20 sobre Ethereum</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Usa sharding para escalar el procesamiento de transacciones.</t>
+          <t>Uno de los mayores exchanges descentralizados (DEX) del ecosistema Ethereum.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>avalanche-2</t>
+          <t>ethena-usde</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>avax</t>
+          <t>usde</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Ethena USDe</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>11.12</v>
+        <v>0.999671</v>
       </c>
       <c r="F25" t="n">
-        <v>4929331368</v>
+        <v>4892747442</v>
       </c>
       <c r="G25" t="n">
         <v>24</v>
       </c>
       <c r="H25" t="n">
-        <v>583000115</v>
+        <v>42655456</v>
       </c>
       <c r="I25" t="n">
-        <v>11.27</v>
+        <v>0.9999169999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>10.53</v>
+        <v>0.999505</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.09252834473666383</v>
+        <v>9.504e-05</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.8249300000000001</v>
+        <v>0.009509999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>442929713.9306387</v>
+        <v>4894216226.655697</v>
       </c>
       <c r="N25" t="n">
-        <v>469596104.050358</v>
+        <v>4897760252.030897</v>
       </c>
       <c r="O25" t="n">
-        <v>144.96</v>
+        <v>1.034</v>
       </c>
       <c r="P25" s="1" t="n">
-        <v>44521.26314814815</v>
+        <v>46000.38208333333</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.002490929469520555</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Plataforma de contratos inteligentes</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Layer 1</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Proof of Stake (Avalanche consensus)</t>
-        </is>
-      </c>
-      <c r="W25" t="n">
-        <v>2020</v>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>avax.network</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>Subredes personalizadas para empresas</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Layer 1)</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>Permite crear subredes (subnets) personalizadas para casos de uso específicos.</t>
-        </is>
-      </c>
+        <v>0.002478786141992239</v>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ethena-usde</t>
+          <t>litecoin</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>usde</t>
+          <t>ltc</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ethena USDe</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.999831</v>
+        <v>62.54</v>
       </c>
       <c r="F26" t="n">
-        <v>4898930130</v>
+        <v>4855138861</v>
       </c>
       <c r="G26" t="n">
         <v>25</v>
       </c>
       <c r="H26" t="n">
-        <v>175398799</v>
+        <v>599111390</v>
       </c>
       <c r="I26" t="n">
-        <v>0.999931</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>0.998631</v>
+        <v>60.79</v>
       </c>
       <c r="K26" t="n">
-        <v>4.747e-05</v>
+        <v>0.599789</v>
       </c>
       <c r="L26" t="n">
-        <v>0.00475</v>
+        <v>0.9684</v>
       </c>
       <c r="M26" t="n">
-        <v>4899806603.894896</v>
+        <v>77639204.48411152</v>
       </c>
       <c r="N26" t="n">
-        <v>4897763014.332197</v>
+        <v>77639154.48411152</v>
       </c>
       <c r="O26" t="n">
-        <v>1.034</v>
+        <v>410.26</v>
       </c>
       <c r="P26" s="1" t="n">
-        <v>46000.38208333333</v>
+        <v>44325.80077546297</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R26" t="b">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.002473344116521277</v>
-      </c>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr"/>
+        <v>0.002456922821341487</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Pagos</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Store of value ligero</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Proof of Work</t>
+        </is>
+      </c>
+      <c r="W26" t="n">
+        <v>2011</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>litecoin.org</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Pagos rápidos de bajo costo</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Layer 1)</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Fue diseñada como complemento más rápido y liviano de Bitcoin.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>litecoin</t>
+          <t>avalanche-2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ltc</t>
+          <t>avax</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Litecoin</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>62.39</v>
+        <v>10.72</v>
       </c>
       <c r="F27" t="n">
-        <v>4845618269</v>
+        <v>4738703503</v>
       </c>
       <c r="G27" t="n">
         <v>26</v>
       </c>
       <c r="H27" t="n">
-        <v>494519336</v>
+        <v>645833105</v>
       </c>
       <c r="I27" t="n">
-        <v>63.44</v>
+        <v>11.38</v>
       </c>
       <c r="J27" t="n">
-        <v>59.82</v>
+        <v>10.73</v>
       </c>
       <c r="K27" t="n">
-        <v>0.509826</v>
+        <v>-0.2624415949471288</v>
       </c>
       <c r="L27" t="n">
-        <v>0.82386</v>
+        <v>-2.39036</v>
       </c>
       <c r="M27" t="n">
-        <v>77636991.97696769</v>
+        <v>443045723.4029999</v>
       </c>
       <c r="N27" t="n">
-        <v>77639516.98369066</v>
+        <v>469714532.4028373</v>
       </c>
       <c r="O27" t="n">
-        <v>410.26</v>
+        <v>144.96</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>44325.80077546297</v>
+        <v>44521.26314814815</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R27" t="b">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.002442506296866253</v>
+        <v>0.002389234450779485</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Plataforma de contratos inteligentes</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>Store of value ligero</t>
+          <t>Layer 1</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Proof of Work</t>
+          <t>Proof of Stake (Avalanche consensus)</t>
         </is>
       </c>
       <c r="W27" t="n">
-        <v>2011</v>
+        <v>2020</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>litecoin.org</t>
+          <t>avax.network</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>Pagos rápidos de bajo costo</t>
+          <t>Subredes personalizadas para empresas</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -3103,14 +3103,14 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>Fue diseñada como complemento más rápido y liviano de Bitcoin.</t>
+          <t>Permite crear subredes (subnets) personalizadas para casos de uso específicos.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3129,16 +3129,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.999827</v>
+        <v>0.999841</v>
       </c>
       <c r="F28" t="n">
-        <v>4592048687</v>
+        <v>4582808900</v>
       </c>
       <c r="G28" t="n">
         <v>27</v>
       </c>
       <c r="H28" t="n">
-        <v>238631706</v>
+        <v>237165850</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
@@ -3147,16 +3147,16 @@
         <v>0.998871</v>
       </c>
       <c r="K28" t="n">
-        <v>-6.672678711572299e-05</v>
+        <v>-0.000156011346180596</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.00667</v>
+        <v>-0.0156</v>
       </c>
       <c r="M28" t="n">
-        <v>4592088883.495623</v>
+        <v>4583830468.504778</v>
       </c>
       <c r="N28" t="n">
-        <v>4607756201.823016</v>
+        <v>4584121642.59938</v>
       </c>
       <c r="O28" t="n">
         <v>1.22</v>
@@ -3165,13 +3165,13 @@
         <v>43902.79363425926</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R28" t="b">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.002295830999980336</v>
+        <v>0.002298606897107342</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3234,34 +3234,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.113361</v>
+        <v>0.111645</v>
       </c>
       <c r="F29" t="n">
-        <v>4495985229</v>
+        <v>4426803854</v>
       </c>
       <c r="G29" t="n">
         <v>28</v>
       </c>
       <c r="H29" t="n">
-        <v>17648343</v>
+        <v>18675067</v>
       </c>
       <c r="I29" t="n">
-        <v>0.119967</v>
+        <v>0.117565</v>
       </c>
       <c r="J29" t="n">
-        <v>0.111864</v>
+        <v>0.111573</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.001888689596183116</v>
+        <v>-0.005249514732099017</v>
       </c>
       <c r="L29" t="n">
-        <v>-1.63877</v>
+        <v>-4.49082</v>
       </c>
       <c r="M29" t="n">
-        <v>39662232770.86527</v>
+        <v>39666257608.93535</v>
       </c>
       <c r="N29" t="n">
-        <v>39663044281.77826</v>
+        <v>39667085270.89719</v>
       </c>
       <c r="O29" t="n">
         <v>0.194152</v>
@@ -3270,13 +3270,13 @@
         <v>46056.00148148148</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
-        <v>0.002240263860929573</v>
+        <v>0.002207915138653779</v>
       </c>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
@@ -3290,7 +3290,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3309,34 +3309,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.999353</v>
+        <v>0.999242</v>
       </c>
       <c r="F30" t="n">
-        <v>4392965697</v>
+        <v>4392540758</v>
       </c>
       <c r="G30" t="n">
         <v>29</v>
       </c>
       <c r="H30" t="n">
-        <v>1314867446</v>
+        <v>1208321949</v>
       </c>
       <c r="I30" t="n">
-        <v>0.999651</v>
+        <v>0.99961</v>
       </c>
       <c r="J30" t="n">
-        <v>0.999131</v>
+        <v>0.999139</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.000189665058792587</v>
+        <v>-8.6097787802997e-05</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.01898</v>
+        <v>-0.008619999999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>4395796475.062263</v>
+        <v>4395796480.061099</v>
       </c>
       <c r="N30" t="n">
-        <v>4395796475.062263</v>
+        <v>4398506663.061099</v>
       </c>
       <c r="O30" t="n">
         <v>1.048</v>
@@ -3345,13 +3345,13 @@
         <v>46212.42696759259</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R30" t="b">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.002180673036501948</v>
+        <v>0.002187996677642567</v>
       </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
@@ -3365,7 +3365,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3384,31 +3384,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.098964</v>
+        <v>0.094085</v>
       </c>
       <c r="F31" t="n">
-        <v>4338046552</v>
+        <v>4123048732</v>
       </c>
       <c r="G31" t="n">
         <v>30</v>
       </c>
       <c r="H31" t="n">
-        <v>248233542</v>
+        <v>240085946</v>
       </c>
       <c r="I31" t="n">
-        <v>0.100667</v>
+        <v>0.101256</v>
       </c>
       <c r="J31" t="n">
-        <v>0.091183</v>
+        <v>0.09447800000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.00616817</v>
+        <v>-0.002485756545079959</v>
       </c>
       <c r="L31" t="n">
-        <v>6.64701</v>
+        <v>-2.57402</v>
       </c>
       <c r="M31" t="n">
-        <v>43831706400.35147</v>
+        <v>43831706399.65635</v>
       </c>
       <c r="N31" t="n">
         <v>50000000000</v>
@@ -3420,13 +3420,13 @@
         <v>44454.11143518519</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0.002148905496270739</v>
+        <v>0.002031330554630409</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3489,28 +3489,28 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1.008</v>
+        <v>1.007</v>
       </c>
       <c r="F32" t="n">
-        <v>4130999814</v>
+        <v>4124856473</v>
       </c>
       <c r="G32" t="n">
         <v>31</v>
       </c>
       <c r="H32" t="n">
-        <v>1120008041</v>
+        <v>971487150</v>
       </c>
       <c r="I32" t="n">
-        <v>1.079</v>
+        <v>1.036</v>
       </c>
       <c r="J32" t="n">
         <v>0.988259</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.01936280268045532</v>
+        <v>-0.007936769969634438</v>
       </c>
       <c r="L32" t="n">
-        <v>-1.88384</v>
+        <v>-0.78184</v>
       </c>
       <c r="M32" t="n">
         <v>4096537146.540959</v>
@@ -3525,13 +3525,13 @@
         <v>45661.62243055556</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R32" t="b">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.002029140966448662</v>
+        <v>0.00203238146429213</v>
       </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
@@ -3545,7 +3545,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3564,34 +3564,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="F33" t="n">
-        <v>4077642836</v>
+        <v>4049207563</v>
       </c>
       <c r="G33" t="n">
         <v>32</v>
       </c>
       <c r="H33" t="n">
-        <v>53122958</v>
+        <v>54086270</v>
       </c>
       <c r="I33" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="J33" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="K33" t="n">
-        <v>0.00133977</v>
+        <v>0.00905706</v>
       </c>
       <c r="L33" t="n">
-        <v>0.09245</v>
+        <v>0.6329</v>
       </c>
       <c r="M33" t="n">
-        <v>2810942525.236758</v>
+        <v>2811563721.089555</v>
       </c>
       <c r="N33" t="n">
-        <v>5253752609.789647</v>
+        <v>5254127987.90229</v>
       </c>
       <c r="O33" t="n">
         <v>8.25</v>
@@ -3600,13 +3600,13 @@
         <v>45457.69225694444</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R33" t="b">
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.001998277049225793</v>
+        <v>0.001988403831203291</v>
       </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
@@ -3620,367 +3620,367 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>shiba-inu</t>
+          <t>bittensor</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>shib</t>
+          <t>tao</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Shiba Inu</t>
+          <t>Bittensor</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6.01e-06</v>
+        <v>311.83</v>
       </c>
       <c r="F34" t="n">
-        <v>3541226044</v>
+        <v>3527202635</v>
       </c>
       <c r="G34" t="n">
         <v>33</v>
       </c>
       <c r="H34" t="n">
-        <v>211376302</v>
+        <v>339297374</v>
       </c>
       <c r="I34" t="n">
-        <v>6.25e-06</v>
+        <v>325.4</v>
       </c>
       <c r="J34" t="n">
-        <v>5.9e-06</v>
+        <v>300.88</v>
       </c>
       <c r="K34" t="n">
-        <v>-3.5306998336e-08</v>
+        <v>-7.60569083252318</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.58435</v>
+        <v>-2.38101</v>
       </c>
       <c r="M34" t="n">
-        <v>589238968628246.4</v>
+        <v>11339645.9251</v>
       </c>
       <c r="N34" t="n">
-        <v>589496070402766.1</v>
+        <v>21000000</v>
       </c>
       <c r="O34" t="n">
-        <v>8.616e-05</v>
+        <v>757.6</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>44496.82980324074</v>
+        <v>45358.44833333333</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R34" t="b">
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0.001687991045673556</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Meme coin</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Ecosistema DeFi</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>N/A (token ERC-20)</t>
-        </is>
-      </c>
-      <c r="W34" t="n">
-        <v>2020</v>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>shibatoken.com</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>Ecosistema meme y DeFi comunitario</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>Token ERC-20 sobre Ethereum</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>Token meme inspirado en Dogecoin, con ecosistema DeFi propio (ShibaSwap).</t>
-        </is>
-      </c>
+        <v>0.001684942205726474</v>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>bittensor</t>
+          <t>shiba-inu</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>tao</t>
+          <t>shib</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Bittensor</t>
+          <t>Shiba Inu</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>308.56</v>
+        <v>5.96e-06</v>
       </c>
       <c r="F35" t="n">
-        <v>3499419828</v>
+        <v>3515289498</v>
       </c>
       <c r="G35" t="n">
         <v>34</v>
       </c>
       <c r="H35" t="n">
-        <v>537476536</v>
+        <v>135254168</v>
       </c>
       <c r="I35" t="n">
-        <v>325.76</v>
+        <v>6.23e-06</v>
       </c>
       <c r="J35" t="n">
-        <v>306.69</v>
+        <v>5.92e-06</v>
       </c>
       <c r="K35" t="n">
-        <v>4.6</v>
+        <v>-5.4928049595e-08</v>
       </c>
       <c r="L35" t="n">
-        <v>1.51283</v>
+        <v>-0.91248</v>
       </c>
       <c r="M35" t="n">
-        <v>11339645.9251</v>
+        <v>589238968295838.6</v>
       </c>
       <c r="N35" t="n">
-        <v>21000000</v>
+        <v>589496070070358.4</v>
       </c>
       <c r="O35" t="n">
-        <v>757.6</v>
+        <v>8.616e-05</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>45358.44833333333</v>
+        <v>44496.82980324074</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R35" t="b">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.001663808574356958</v>
-      </c>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr"/>
+        <v>0.001678016639080199</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Meme coin</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ecosistema DeFi</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>N/A (token ERC-20)</t>
+        </is>
+      </c>
+      <c r="W35" t="n">
+        <v>2020</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>shibatoken.com</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>Ecosistema meme y DeFi comunitario</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>Token ERC-20 sobre Ethereum</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>Token meme inspirado en Dogecoin, con ecosistema DeFi propio (ShibaSwap).</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>crypto-com-chain</t>
+          <t>global-dollar</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>cro</t>
+          <t>usdg</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cronos</t>
+          <t>Global Dollar</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.065981</v>
+        <v>0.999939</v>
       </c>
       <c r="F36" t="n">
-        <v>3281617349</v>
+        <v>3267611043</v>
       </c>
       <c r="G36" t="n">
         <v>35</v>
       </c>
       <c r="H36" t="n">
-        <v>18457889</v>
+        <v>892621912</v>
       </c>
       <c r="I36" t="n">
-        <v>0.068842</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>0.06461500000000001</v>
+        <v>0.999742</v>
       </c>
       <c r="K36" t="n">
-        <v>0.00060393</v>
+        <v>-0.000111259712300082</v>
       </c>
       <c r="L36" t="n">
-        <v>0.92376</v>
+        <v>-0.01113</v>
       </c>
       <c r="M36" t="n">
-        <v>49737789509.91389</v>
+        <v>3267748267.80673</v>
       </c>
       <c r="N36" t="n">
-        <v>98937800399.94398</v>
+        <v>3256747890.046524</v>
       </c>
       <c r="O36" t="n">
-        <v>0.891544</v>
+        <v>1.65</v>
       </c>
       <c r="P36" s="1" t="n">
-        <v>44523.66666666666</v>
+        <v>45686.67436342593</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R36" t="b">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.001537822472168195</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Token de exchange</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Layer 1 (Cronos)</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Proof of Stake</t>
-        </is>
-      </c>
-      <c r="W36" t="n">
-        <v>2018</v>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>cronos.org</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>Pagos y DeFi en el ecosistema Crypto.com</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Cronos, EVM-compatible)</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>Token nativo del ecosistema Crypto.com y su red Cronos.</t>
-        </is>
-      </c>
+        <v>0.001534031587372245</v>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>global-dollar</t>
+          <t>crypto-com-chain</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>usdg</t>
+          <t>cro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Global Dollar</t>
+          <t>Cronos</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>0.06514499999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>3258614301</v>
+        <v>3237405170</v>
       </c>
       <c r="G37" t="n">
         <v>36</v>
       </c>
       <c r="H37" t="n">
-        <v>920617922</v>
+        <v>13111871</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0.068983</v>
       </c>
       <c r="J37" t="n">
-        <v>0.999787</v>
+        <v>0.06469900000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>7.24e-05</v>
+        <v>-0.001562254340246122</v>
       </c>
       <c r="L37" t="n">
-        <v>0.00724</v>
+        <v>-2.34195</v>
       </c>
       <c r="M37" t="n">
-        <v>3258647890.048256</v>
+        <v>49739045371.25254</v>
       </c>
       <c r="N37" t="n">
-        <v>3258647890.048256</v>
+        <v>98939055665.36623</v>
       </c>
       <c r="O37" t="n">
-        <v>1.65</v>
+        <v>0.891544</v>
       </c>
       <c r="P37" s="1" t="n">
-        <v>45686.67436342593</v>
+        <v>44523.66666666666</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R37" t="b">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.001524516543010332</v>
-      </c>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr"/>
+        <v>0.001516471746788659</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Token de exchange</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Layer 1 (Cronos)</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Proof of Stake</t>
+        </is>
+      </c>
+      <c r="W37" t="n">
+        <v>2018</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>cronos.org</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>Pagos y DeFi en el ecosistema Crypto.com</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Cronos, EVM-compatible)</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>Token nativo del ecosistema Crypto.com y su red Cronos.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3999,34 +3999,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="F38" t="n">
-        <v>2977708940</v>
+        <v>2855695265</v>
       </c>
       <c r="G38" t="n">
         <v>37</v>
       </c>
       <c r="H38" t="n">
-        <v>1772456</v>
+        <v>893698</v>
       </c>
       <c r="I38" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="J38" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.1590208969476814</v>
+        <v>-0.0662498015158246</v>
       </c>
       <c r="L38" t="n">
-        <v>-10.8441</v>
+        <v>-5.02005</v>
       </c>
       <c r="M38" t="n">
-        <v>2277592661.72997</v>
+        <v>2277839497.199591</v>
       </c>
       <c r="N38" t="n">
-        <v>5417166988.519834</v>
+        <v>5417413823.773819</v>
       </c>
       <c r="O38" t="n">
         <v>5.64</v>
@@ -4035,13 +4035,13 @@
         <v>46205.17638888889</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R38" t="b">
         <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>0.001362029083368896</v>
+        <v>0.001294569036644318</v>
       </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
@@ -4055,7 +4055,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4074,34 +4074,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>0.999876</v>
       </c>
       <c r="F39" t="n">
-        <v>2823457383</v>
+        <v>2817767263</v>
       </c>
       <c r="G39" t="n">
         <v>38</v>
       </c>
       <c r="H39" t="n">
-        <v>158036998</v>
+        <v>117187480</v>
       </c>
       <c r="I39" t="n">
         <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>0.99978</v>
+        <v>0.99975</v>
       </c>
       <c r="K39" t="n">
-        <v>3.783e-05</v>
+        <v>-6.1017185474577e-05</v>
       </c>
       <c r="L39" t="n">
-        <v>0.00378</v>
+        <v>-0.0061</v>
       </c>
       <c r="M39" t="n">
-        <v>2823558770.164367</v>
+        <v>2817932111.158792</v>
       </c>
       <c r="N39" t="n">
-        <v>2823558770.164366</v>
+        <v>2817930847.468791</v>
       </c>
       <c r="O39" t="n">
         <v>1.021</v>
@@ -4110,13 +4110,13 @@
         <v>45222.61454861111</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001272803503787785</v>
+        <v>0.001272520024229615</v>
       </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
@@ -4130,7 +4130,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4149,28 +4149,28 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4360.49</v>
+        <v>4288.64</v>
       </c>
       <c r="F40" t="n">
-        <v>2715915538</v>
+        <v>2671159184</v>
       </c>
       <c r="G40" t="n">
         <v>39</v>
       </c>
       <c r="H40" t="n">
-        <v>212911419</v>
+        <v>170212198</v>
       </c>
       <c r="I40" t="n">
-        <v>4372.67</v>
+        <v>4368.27</v>
       </c>
       <c r="J40" t="n">
-        <v>4295.64</v>
+        <v>4301.09</v>
       </c>
       <c r="K40" t="n">
-        <v>11.22</v>
+        <v>-45.86152627207593</v>
       </c>
       <c r="L40" t="n">
-        <v>0.25796</v>
+        <v>-1.05806</v>
       </c>
       <c r="M40" t="n">
         <v>622823.6595320001</v>
@@ -4185,13 +4185,13 @@
         <v>46050.66666666666</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R40" t="b">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.001210596783570712</v>
+        <v>0.00118729108562202</v>
       </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
@@ -4205,248 +4205,248 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>okb</t>
+          <t>bitway</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>okb</t>
+          <t>btw</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>OKB</t>
+          <t>Bitway</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>122.42</v>
+        <v>0.9601150000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>2571444715</v>
+        <v>2599451132</v>
       </c>
       <c r="G41" t="n">
         <v>40</v>
       </c>
       <c r="H41" t="n">
-        <v>39775410</v>
+        <v>21262194</v>
       </c>
       <c r="I41" t="n">
-        <v>126.4</v>
+        <v>0.96234</v>
       </c>
       <c r="J41" t="n">
-        <v>120.48</v>
+        <v>0.844931</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.5971208906714907</v>
+        <v>0.091182</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.48539</v>
+        <v>10.49359</v>
       </c>
       <c r="M41" t="n">
-        <v>21000000</v>
+        <v>2708142280.000001</v>
       </c>
       <c r="N41" t="n">
-        <v>21000000</v>
+        <v>10000000000</v>
       </c>
       <c r="O41" t="n">
-        <v>228.74</v>
+        <v>0.972034</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>45934.66666666666</v>
+        <v>46286.79398148148</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
-        <v>0.001127028791354367</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Token de exchange</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Utilidad</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>N/A (token de exchange)</t>
-        </is>
-      </c>
-      <c r="W41" t="n">
-        <v>2019</v>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>okx.com</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>Beneficios dentro del exchange OKX</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>Token ERC-20 sobre Ethereum</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>Token nativo del exchange OKX, usado para descuentos y beneficios.</t>
-        </is>
-      </c>
+        <v>0.001145604425492068</v>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>hashnote-usyc</t>
+          <t>okb</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>usyc</t>
+          <t>okb</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Circle USYC</t>
+          <t>OKB</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1.14</v>
+        <v>121.4</v>
       </c>
       <c r="F42" t="n">
-        <v>2508825557</v>
+        <v>2550230189</v>
       </c>
       <c r="G42" t="n">
         <v>41</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>32411824</v>
       </c>
       <c r="I42" t="n">
-        <v>1.14</v>
+        <v>125.52</v>
       </c>
       <c r="J42" t="n">
-        <v>1.14</v>
+        <v>120.82</v>
       </c>
       <c r="K42" t="n">
-        <v>0.00010508</v>
+        <v>-0.9404539534214251</v>
       </c>
       <c r="L42" t="n">
-        <v>0.00923</v>
+        <v>-0.76872</v>
       </c>
       <c r="M42" t="n">
-        <v>2204477317.470919</v>
+        <v>21000000</v>
       </c>
       <c r="N42" t="n">
-        <v>2204477317.470919</v>
+        <v>21000000</v>
       </c>
       <c r="O42" t="n">
-        <v>1.14</v>
+        <v>228.74</v>
       </c>
       <c r="P42" s="1" t="n">
-        <v>46287.53819444445</v>
+        <v>45934.66666666666</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R42" t="b">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.001090807240181103</v>
-      </c>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr"/>
+        <v>0.001116990390319048</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Token de exchange</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Utilidad</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>N/A (token de exchange)</t>
+        </is>
+      </c>
+      <c r="W42" t="n">
+        <v>2019</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>okx.com</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>Beneficios dentro del exchange OKX</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>Token ERC-20 sobre Ethereum</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>Token nativo del exchange OKX, usado para descuentos y beneficios.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>bitway</t>
+          <t>hashnote-usyc</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>btw</t>
+          <t>usyc</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Bitway</t>
+          <t>Circle USYC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.894261</v>
+        <v>1.14</v>
       </c>
       <c r="F43" t="n">
-        <v>2420235968</v>
+        <v>2509066381</v>
       </c>
       <c r="G43" t="n">
         <v>42</v>
       </c>
       <c r="H43" t="n">
-        <v>14031928</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0.886543</v>
+        <v>1.14</v>
       </c>
       <c r="J43" t="n">
-        <v>0.717963</v>
+        <v>1.14</v>
       </c>
       <c r="K43" t="n">
-        <v>0.02319291</v>
+        <v>0.00010924</v>
       </c>
       <c r="L43" t="n">
-        <v>2.66258</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="M43" t="n">
-        <v>2708142280.000001</v>
+        <v>2204477317.470919</v>
       </c>
       <c r="N43" t="n">
-        <v>10000000000</v>
+        <v>2204477317.470919</v>
       </c>
       <c r="O43" t="n">
-        <v>0.972034</v>
+        <v>1.14</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>46286.79398148148</v>
+        <v>46288.5349537037</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R43" t="b">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.001039563300884092</v>
+        <v>0.001093060278903518</v>
       </c>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
@@ -4460,7 +4460,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4479,34 +4479,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.999978</v>
+        <v>0.999987</v>
       </c>
       <c r="F44" t="n">
-        <v>2417505676</v>
+        <v>2430566971</v>
       </c>
       <c r="G44" t="n">
         <v>43</v>
       </c>
       <c r="H44" t="n">
-        <v>431971136</v>
+        <v>408722228</v>
       </c>
       <c r="I44" t="n">
         <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>0.9997740000000001</v>
+        <v>0.999723</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.000173738122698608</v>
+        <v>-8.6788943180593e-05</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.01737</v>
+        <v>-0.00868</v>
       </c>
       <c r="M44" t="n">
-        <v>2417586212.607235</v>
+        <v>2430586212.607239</v>
       </c>
       <c r="N44" t="n">
-        <v>2417586212.607235</v>
+        <v>2420586212.607235</v>
       </c>
       <c r="O44" t="n">
         <v>1.073</v>
@@ -4515,13 +4515,13 @@
         <v>45652.11518518518</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R44" t="b">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.001037983985311118</v>
+        <v>0.001047425540072909</v>
       </c>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
@@ -4535,7 +4535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4572,7 +4572,7 @@
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>-1.11e-16</v>
+        <v>1.11e-16</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -4590,13 +4590,13 @@
         <v>45699.87511574074</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R45" t="b">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.0009589618976471764</v>
+        <v>0.0009604147044122856</v>
       </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
@@ -4610,7 +4610,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4629,34 +4629,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="F46" t="n">
-        <v>2245147219</v>
+        <v>2265296346</v>
       </c>
       <c r="G46" t="n">
         <v>45</v>
       </c>
       <c r="H46" t="n">
-        <v>5601491</v>
+        <v>2784598</v>
       </c>
       <c r="I46" t="n">
         <v>1.15</v>
       </c>
       <c r="J46" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.003195321708100662</v>
+        <v>-0.000589271372547939</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.27872</v>
+        <v>-0.05139</v>
       </c>
       <c r="M46" t="n">
-        <v>1963554625.495198</v>
+        <v>1977425342.111264</v>
       </c>
       <c r="N46" t="n">
-        <v>1963554625.495198</v>
+        <v>1977437874.141553</v>
       </c>
       <c r="O46" t="n">
         <v>1.26</v>
@@ -4665,13 +4665,13 @@
         <v>45377.89175925926</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R46" t="b">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.0009382846142277451</v>
+        <v>0.0009513473426922327</v>
       </c>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
@@ -4685,7 +4685,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4704,31 +4704,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>144.35</v>
+        <v>145.91</v>
       </c>
       <c r="F47" t="n">
-        <v>2227832718</v>
+        <v>2250997512</v>
       </c>
       <c r="G47" t="n">
         <v>46</v>
       </c>
       <c r="H47" t="n">
-        <v>267445253</v>
+        <v>379773417</v>
       </c>
       <c r="I47" t="n">
-        <v>146.7</v>
+        <v>154.8</v>
       </c>
       <c r="J47" t="n">
-        <v>140.18</v>
+        <v>140.89</v>
       </c>
       <c r="K47" t="n">
-        <v>0.224976</v>
+        <v>1.81</v>
       </c>
       <c r="L47" t="n">
-        <v>0.15609</v>
+        <v>1.25921</v>
       </c>
       <c r="M47" t="n">
-        <v>15428920.67059255</v>
+        <v>15429000.22800938</v>
       </c>
       <c r="N47" t="n">
         <v>16000000</v>
@@ -4740,13 +4740,13 @@
         <v>44334.55554398148</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R47" t="b">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0.0009282691795901374</v>
+        <v>0.0009430348782396689</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4809,28 +4809,28 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.667385</v>
+        <v>0.6676609999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>2204088910</v>
+        <v>2203402046</v>
       </c>
       <c r="G48" t="n">
         <v>47</v>
       </c>
       <c r="H48" t="n">
-        <v>53749791</v>
+        <v>54032578</v>
       </c>
       <c r="I48" t="n">
-        <v>0.671764</v>
+        <v>0.696315</v>
       </c>
       <c r="J48" t="n">
-        <v>0.636514</v>
+        <v>0.650689</v>
       </c>
       <c r="K48" t="n">
-        <v>0.01742403</v>
+        <v>0.00460571</v>
       </c>
       <c r="L48" t="n">
-        <v>2.68078</v>
+        <v>0.69462</v>
       </c>
       <c r="M48" t="n">
         <v>3302294382.53684</v>
@@ -4845,13 +4845,13 @@
         <v>45938.71164351852</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R48" t="b">
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0.0009145347637342079</v>
+        <v>0.0009153657956257848</v>
       </c>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
@@ -4865,7 +4865,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4884,28 +4884,28 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.208813</v>
+        <v>0.210498</v>
       </c>
       <c r="F49" t="n">
-        <v>2110538729</v>
+        <v>2124853632</v>
       </c>
       <c r="G49" t="n">
         <v>48</v>
       </c>
       <c r="H49" t="n">
-        <v>462953450</v>
+        <v>427826210</v>
       </c>
       <c r="I49" t="n">
-        <v>0.218605</v>
+        <v>0.220878</v>
       </c>
       <c r="J49" t="n">
         <v>0.203656</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.000232921066841418</v>
+        <v>-0.00015034861664584</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.11142</v>
+        <v>-0.07137</v>
       </c>
       <c r="M49" t="n">
         <v>10095312500</v>
@@ -4920,13 +4920,13 @@
         <v>45393.21892361111</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R49" t="b">
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>0.0008604214096651606</v>
+        <v>0.0008697025688773468</v>
       </c>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
@@ -4940,7 +4940,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4959,28 +4959,28 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.432797</v>
+        <v>0.430371</v>
       </c>
       <c r="F50" t="n">
-        <v>2108132110</v>
+        <v>2094725216</v>
       </c>
       <c r="G50" t="n">
         <v>49</v>
       </c>
       <c r="H50" t="n">
-        <v>261671080</v>
+        <v>240491377</v>
       </c>
       <c r="I50" t="n">
-        <v>0.463533</v>
+        <v>0.446916</v>
       </c>
       <c r="J50" t="n">
         <v>0.422514</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.02050550131691564</v>
+        <v>-0.002795556637051055</v>
       </c>
       <c r="L50" t="n">
-        <v>-4.52358</v>
+        <v>-0.64538</v>
       </c>
       <c r="M50" t="n">
         <v>4869330647</v>
@@ -4995,13 +4995,13 @@
         <v>45641.69166666667</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0.0008590293201505898</v>
+        <v>0.0008521877570393985</v>
       </c>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
@@ -5015,68 +5015,68 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>pump-fun</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Pump.fun</t>
+          <t>Pepe</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.00445567</v>
+        <v>4.72e-06</v>
       </c>
       <c r="F51" t="n">
-        <v>2080692809</v>
+        <v>1986740277</v>
       </c>
       <c r="G51" t="n">
         <v>50</v>
       </c>
       <c r="H51" t="n">
-        <v>227181607</v>
+        <v>549261212</v>
       </c>
       <c r="I51" t="n">
-        <v>0.00469623</v>
+        <v>5.06e-06</v>
       </c>
       <c r="J51" t="n">
-        <v>0.00434625</v>
+        <v>4.68e-06</v>
       </c>
       <c r="K51" t="n">
-        <v>0.00014213</v>
+        <v>-2.10276760423e-07</v>
       </c>
       <c r="L51" t="n">
-        <v>3.29489</v>
+        <v>-4.26256</v>
       </c>
       <c r="M51" t="n">
-        <v>467008882120.3215</v>
+        <v>420690000000000</v>
       </c>
       <c r="N51" t="n">
-        <v>832520702375.5927</v>
+        <v>420690000000000</v>
       </c>
       <c r="O51" t="n">
-        <v>0.00881908</v>
+        <v>2.803e-05</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>45914.36296296296</v>
+        <v>45635.35457175926</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R51" t="b">
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0.0008431572759220473</v>
+        <v>0.0007894119414134683</v>
       </c>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
@@ -5090,68 +5090,68 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>pump-fun</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Pepe</t>
+          <t>Pump.fun</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4.9e-06</v>
+        <v>0.00420158</v>
       </c>
       <c r="F52" t="n">
-        <v>2062795678</v>
+        <v>1960143679</v>
       </c>
       <c r="G52" t="n">
         <v>51</v>
       </c>
       <c r="H52" t="n">
-        <v>936446984</v>
+        <v>178269348</v>
       </c>
       <c r="I52" t="n">
-        <v>5.34e-06</v>
+        <v>0.00454506</v>
       </c>
       <c r="J52" t="n">
-        <v>4.71e-06</v>
+        <v>0.0041635</v>
       </c>
       <c r="K52" t="n">
-        <v>4.9565e-08</v>
+        <v>-0.000320287581018032</v>
       </c>
       <c r="L52" t="n">
-        <v>1.02125</v>
+        <v>-7.08308</v>
       </c>
       <c r="M52" t="n">
-        <v>420690000000000</v>
+        <v>466901904548.8473</v>
       </c>
       <c r="N52" t="n">
-        <v>420690000000000</v>
+        <v>832406681537.3623</v>
       </c>
       <c r="O52" t="n">
-        <v>2.803e-05</v>
+        <v>0.00881908</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>45635.35457175926</v>
+        <v>45914.36296296296</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S52" t="n">
-        <v>0.0008328048236202915</v>
+        <v>0.0007739503117844977</v>
       </c>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
@@ -5165,7 +5165,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5184,34 +5184,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="F53" t="n">
-        <v>2029369315</v>
+        <v>1961844140</v>
       </c>
       <c r="G53" t="n">
         <v>52</v>
       </c>
       <c r="H53" t="n">
-        <v>173566728</v>
+        <v>207619063</v>
       </c>
       <c r="I53" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="J53" t="n">
         <v>1.15</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.003513831894498276</v>
+        <v>-0.02755527188789175</v>
       </c>
       <c r="L53" t="n">
-        <v>-0.2943</v>
+        <v>-2.33799</v>
       </c>
       <c r="M53" t="n">
-        <v>1704007261.631945</v>
+        <v>1704102123.743917</v>
       </c>
       <c r="N53" t="n">
-        <v>1704007261.631945</v>
+        <v>1704107015.451853</v>
       </c>
       <c r="O53" t="n">
         <v>54.98</v>
@@ -5220,13 +5220,13 @@
         <v>44504.25704861111</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R53" t="b">
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0.0008134696112569985</v>
+        <v>0.0007749388554388594</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5289,34 +5289,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.7260450000000001</v>
+        <v>0.712658</v>
       </c>
       <c r="F54" t="n">
-        <v>1967105995</v>
+        <v>1930613228</v>
       </c>
       <c r="G54" t="n">
         <v>53</v>
       </c>
       <c r="H54" t="n">
-        <v>165661199</v>
+        <v>143167311</v>
       </c>
       <c r="I54" t="n">
-        <v>0.748964</v>
+        <v>0.740887</v>
       </c>
       <c r="J54" t="n">
-        <v>0.7117059999999999</v>
+        <v>0.708005</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.01247816815186487</v>
+        <v>-0.01116442953006569</v>
       </c>
       <c r="L54" t="n">
-        <v>-1.68961</v>
+        <v>-1.54243</v>
       </c>
       <c r="M54" t="n">
         <v>2710487455.649731</v>
       </c>
       <c r="N54" t="n">
-        <v>7795741639.279952</v>
+        <v>7795741639.279309</v>
       </c>
       <c r="O54" t="n">
         <v>2.41</v>
@@ -5325,13 +5325,13 @@
         <v>45924.13766203704</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R54" t="b">
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>0.0007774538917291614</v>
+        <v>0.0007567831200956033</v>
       </c>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
@@ -5345,7 +5345,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5364,28 +5364,28 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4359.73</v>
+        <v>4287.67</v>
       </c>
       <c r="F55" t="n">
-        <v>1896162989</v>
+        <v>1864921106</v>
       </c>
       <c r="G55" t="n">
         <v>54</v>
       </c>
       <c r="H55" t="n">
-        <v>197750904</v>
+        <v>156503064</v>
       </c>
       <c r="I55" t="n">
-        <v>4369.08</v>
+        <v>4366.45</v>
       </c>
       <c r="J55" t="n">
-        <v>4295.5</v>
+        <v>4298.37</v>
       </c>
       <c r="K55" t="n">
-        <v>14.74</v>
+        <v>-45.91542975439643</v>
       </c>
       <c r="L55" t="n">
-        <v>0.33933</v>
+        <v>-1.05952</v>
       </c>
       <c r="M55" t="n">
         <v>434903.623539</v>
@@ -5400,13 +5400,13 @@
         <v>46050.93814814815</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R55" t="b">
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0007364174772469646</v>
+        <v>0.0007185937524213934</v>
       </c>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
@@ -5420,7 +5420,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5439,31 +5439,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.058183</v>
+        <v>0.057758</v>
       </c>
       <c r="F56" t="n">
-        <v>1848705508</v>
+        <v>1833651673</v>
       </c>
       <c r="G56" t="n">
         <v>55</v>
       </c>
       <c r="H56" t="n">
-        <v>61134963</v>
+        <v>43170388</v>
       </c>
       <c r="I56" t="n">
-        <v>0.058528</v>
+        <v>0.05854</v>
       </c>
       <c r="J56" t="n">
-        <v>0.056703</v>
+        <v>0.057097</v>
       </c>
       <c r="K56" t="n">
-        <v>0.00104893</v>
+        <v>-6.534036778634001e-05</v>
       </c>
       <c r="L56" t="n">
-        <v>1.83592</v>
+        <v>-0.113</v>
       </c>
       <c r="M56" t="n">
-        <v>31777768006</v>
+        <v>31777806194</v>
       </c>
       <c r="N56" t="n">
         <v>100000000000</v>
@@ -5475,13 +5475,13 @@
         <v>45901.18065972222</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R56" t="b">
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0.0007089660768848628</v>
+        <v>0.0007004156233330825</v>
       </c>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
@@ -5495,7 +5495,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5514,31 +5514,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="F57" t="n">
-        <v>1805505796</v>
+        <v>1815703875</v>
       </c>
       <c r="G57" t="n">
         <v>56</v>
       </c>
       <c r="H57" t="n">
-        <v>33427436</v>
+        <v>38070094</v>
       </c>
       <c r="I57" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="J57" t="n">
         <v>2.56</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.0655068506491947</v>
+        <v>-0.01474188022210354</v>
       </c>
       <c r="L57" t="n">
-        <v>-2.4746</v>
+        <v>-0.56476</v>
       </c>
       <c r="M57" t="n">
-        <v>699291024.8718739</v>
+        <v>699322574.1099297</v>
       </c>
       <c r="N57" t="n">
         <v>1000000000</v>
@@ -5550,13 +5550,13 @@
         <v>45674.19883101852</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R57" t="b">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0.0006839775489509952</v>
+        <v>0.0006899818751773379</v>
       </c>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
@@ -5570,68 +5570,68 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>worldcoin-wld</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>wld</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Worldcoin</t>
+          <t>Sky</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.457343</v>
+        <v>0.074221</v>
       </c>
       <c r="F58" t="n">
-        <v>1668410444</v>
+        <v>1739729959</v>
       </c>
       <c r="G58" t="n">
         <v>57</v>
       </c>
       <c r="H58" t="n">
-        <v>250281011</v>
+        <v>32498053</v>
       </c>
       <c r="I58" t="n">
-        <v>0.476706</v>
+        <v>0.075257</v>
       </c>
       <c r="J58" t="n">
-        <v>0.441742</v>
+        <v>0.066938</v>
       </c>
       <c r="K58" t="n">
-        <v>0.00015672</v>
+        <v>0.00621626</v>
       </c>
       <c r="L58" t="n">
-        <v>0.03428</v>
+        <v>9.14096</v>
       </c>
       <c r="M58" t="n">
-        <v>3646959224.069938</v>
+        <v>23423997285.19598</v>
       </c>
       <c r="N58" t="n">
-        <v>10000000000</v>
+        <v>23459804203.60596</v>
       </c>
       <c r="O58" t="n">
-        <v>11.74</v>
+        <v>0.100535</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>45360.67409722223</v>
+        <v>45630.09302083333</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0006046758389522016</v>
+        <v>0.0006458153035483452</v>
       </c>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
@@ -5645,7 +5645,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5664,34 +5664,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="F59" t="n">
-        <v>1653855828</v>
+        <v>1728332299</v>
       </c>
       <c r="G59" t="n">
         <v>58</v>
       </c>
       <c r="H59" t="n">
-        <v>74592682</v>
+        <v>90090819</v>
       </c>
       <c r="I59" t="n">
-        <v>3.07</v>
+        <v>3.17</v>
       </c>
       <c r="J59" t="n">
         <v>2.89</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.02078629846631808</v>
+        <v>0.148767</v>
       </c>
       <c r="L59" t="n">
-        <v>-0.69573</v>
+        <v>5.0332</v>
       </c>
       <c r="M59" t="n">
-        <v>556905641.1775453</v>
+        <v>556906568.8330376</v>
       </c>
       <c r="N59" t="n">
-        <v>556905641.1775453</v>
+        <v>556906568.8330376</v>
       </c>
       <c r="O59" t="n">
         <v>700.65</v>
@@ -5700,13 +5700,13 @@
         <v>44326.33741898148</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R59" t="b">
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>0.0005962568377217601</v>
+        <v>0.0006391894035908794</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -5750,68 +5750,68 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>worldcoin-wld</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>wld</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Sky</t>
+          <t>Worldcoin</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.069221</v>
+        <v>0.447125</v>
       </c>
       <c r="F60" t="n">
-        <v>1621385060</v>
+        <v>1630975252</v>
       </c>
       <c r="G60" t="n">
         <v>59</v>
       </c>
       <c r="H60" t="n">
-        <v>20185480</v>
+        <v>368038301</v>
       </c>
       <c r="I60" t="n">
-        <v>0.07128</v>
+        <v>0.478425</v>
       </c>
       <c r="J60" t="n">
-        <v>0.066889</v>
+        <v>0.444828</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.002525909363693277</v>
+        <v>-0.01147458947688723</v>
       </c>
       <c r="L60" t="n">
-        <v>-3.52059</v>
+        <v>-2.5021</v>
       </c>
       <c r="M60" t="n">
-        <v>23424963409.60133</v>
+        <v>3648371573.354076</v>
       </c>
       <c r="N60" t="n">
-        <v>23459804203.60596</v>
+        <v>10000000000</v>
       </c>
       <c r="O60" t="n">
-        <v>0.100535</v>
+        <v>11.74</v>
       </c>
       <c r="P60" s="1" t="n">
-        <v>45630.09302083333</v>
+        <v>45360.67409722223</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R60" t="b">
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0.0005774743816442258</v>
+        <v>0.0005825919920541</v>
       </c>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
@@ -5825,7 +5825,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5847,25 +5847,25 @@
         <v>1.73e-06</v>
       </c>
       <c r="F61" t="n">
-        <v>1554988430</v>
+        <v>1552311309</v>
       </c>
       <c r="G61" t="n">
         <v>60</v>
       </c>
       <c r="H61" t="n">
-        <v>6619750</v>
+        <v>10763223</v>
       </c>
       <c r="I61" t="n">
-        <v>1.75e-06</v>
+        <v>1.74e-06</v>
       </c>
       <c r="J61" t="n">
         <v>1.71e-06</v>
       </c>
       <c r="K61" t="n">
-        <v>5.388e-09</v>
+        <v>-1.110989529e-09</v>
       </c>
       <c r="L61" t="n">
-        <v>0.31221</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="M61" t="n">
         <v>898232728634017.2</v>
@@ -5880,13 +5880,13 @@
         <v>45629.67800925926</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R61" t="b">
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>0.0005390677820013932</v>
+        <v>0.0005368616038360107</v>
       </c>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
@@ -5900,68 +5900,68 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>venice-token</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>vvv</t>
+          <t>arb</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Venice Token</t>
+          <t>Arbitrum</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>32.04</v>
+        <v>0.229164</v>
       </c>
       <c r="F62" t="n">
-        <v>1541580321</v>
+        <v>1554187273</v>
       </c>
       <c r="G62" t="n">
         <v>61</v>
       </c>
       <c r="H62" t="n">
-        <v>77002315</v>
+        <v>530985295</v>
       </c>
       <c r="I62" t="n">
-        <v>32.76</v>
+        <v>0.254366</v>
       </c>
       <c r="J62" t="n">
-        <v>30.32</v>
+        <v>0.211434</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.5387525065471479</v>
+        <v>0.01161925</v>
       </c>
       <c r="L62" t="n">
-        <v>-1.65352</v>
+        <v>5.34108</v>
       </c>
       <c r="M62" t="n">
-        <v>48113678.9569875</v>
+        <v>6785574605</v>
       </c>
       <c r="N62" t="n">
-        <v>81028467.06059173</v>
+        <v>10000000000</v>
       </c>
       <c r="O62" t="n">
-        <v>34.53</v>
+        <v>2.39</v>
       </c>
       <c r="P62" s="1" t="n">
-        <v>46286.34548611111</v>
+        <v>45303.18748842592</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R62" t="b">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0.0005313119685763676</v>
+        <v>0.0005379521741625345</v>
       </c>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
@@ -5975,68 +5975,68 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>venice-token</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>vvv</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>USDD</t>
+          <t>Venice Token</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.998397</v>
+        <v>32.03</v>
       </c>
       <c r="F63" t="n">
-        <v>1524481541</v>
+        <v>1541518983</v>
       </c>
       <c r="G63" t="n">
         <v>62</v>
       </c>
       <c r="H63" t="n">
-        <v>2022787</v>
+        <v>66835175</v>
       </c>
       <c r="I63" t="n">
-        <v>0.999239</v>
+        <v>33.44</v>
       </c>
       <c r="J63" t="n">
-        <v>0.998009</v>
+        <v>30.93</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.000216429162676612</v>
+        <v>0.3302</v>
       </c>
       <c r="L63" t="n">
-        <v>-0.02167</v>
+        <v>1.04149</v>
       </c>
       <c r="M63" t="n">
-        <v>1526944779</v>
+        <v>48125289.11596377</v>
       </c>
       <c r="N63" t="n">
-        <v>1527073089</v>
+        <v>81032627.41462347</v>
       </c>
       <c r="O63" t="n">
-        <v>1.24</v>
+        <v>34.53</v>
       </c>
       <c r="P63" s="1" t="n">
-        <v>46212.39942129629</v>
+        <v>46286.34548611111</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R63" t="b">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0.0005214213160260669</v>
+        <v>0.0005305876079119039</v>
       </c>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
@@ -6050,68 +6050,68 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>arb</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Arbitrum</t>
+          <t>USDD</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.217408</v>
+        <v>0.998815</v>
       </c>
       <c r="F64" t="n">
-        <v>1475125489</v>
+        <v>1511831977</v>
       </c>
       <c r="G64" t="n">
         <v>63</v>
       </c>
       <c r="H64" t="n">
-        <v>310619951</v>
+        <v>2346046</v>
       </c>
       <c r="I64" t="n">
-        <v>0.230082</v>
+        <v>0.999157</v>
       </c>
       <c r="J64" t="n">
-        <v>0.211434</v>
+        <v>0.997605</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.005521648076855873</v>
+        <v>-2.1427141663977e-05</v>
       </c>
       <c r="L64" t="n">
-        <v>-2.47685</v>
+        <v>-0.00215</v>
       </c>
       <c r="M64" t="n">
-        <v>6785574605</v>
+        <v>1513617332</v>
       </c>
       <c r="N64" t="n">
-        <v>10000000000</v>
+        <v>1513617332</v>
       </c>
       <c r="O64" t="n">
-        <v>2.39</v>
+        <v>1.24</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>45303.18748842592</v>
+        <v>46212.39942129629</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R64" t="b">
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0004928717024520824</v>
+        <v>0.0005133294047550554</v>
       </c>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
@@ -6125,187 +6125,187 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>bitget-token</t>
+          <t>ethereum-classic</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>bgb</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Bitget Token</t>
+          <t>Ethereum Classic</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2.11</v>
+        <v>9.42</v>
       </c>
       <c r="F65" t="n">
-        <v>1474990424</v>
+        <v>1491549131</v>
       </c>
       <c r="G65" t="n">
         <v>64</v>
       </c>
       <c r="H65" t="n">
-        <v>16540237</v>
+        <v>135241381</v>
       </c>
       <c r="I65" t="n">
-        <v>2.18</v>
+        <v>9.66</v>
       </c>
       <c r="J65" t="n">
-        <v>2.08</v>
+        <v>8.84</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.04615182268589679</v>
+        <v>0.368</v>
       </c>
       <c r="L65" t="n">
-        <v>-2.14338</v>
+        <v>4.06515</v>
       </c>
       <c r="M65" t="n">
-        <v>699992029.6481038</v>
+        <v>158258655.0495532</v>
       </c>
       <c r="N65" t="n">
-        <v>910920874.6481038</v>
+        <v>158259070.0255532</v>
       </c>
       <c r="O65" t="n">
-        <v>8.449999999999999</v>
+        <v>167.09</v>
       </c>
       <c r="P65" s="1" t="n">
-        <v>45653.15375</v>
+        <v>44322.44053240741</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R65" t="b">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0.000492793575182961</v>
-      </c>
-      <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr"/>
-      <c r="X65" t="inlineStr"/>
-      <c r="Y65" t="inlineStr"/>
-      <c r="Z65" t="inlineStr"/>
-      <c r="AA65" t="inlineStr"/>
+        <v>0.0005015382030128835</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Plataforma de contratos inteligentes</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Layer 1</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Proof of Work</t>
+        </is>
+      </c>
+      <c r="W65" t="n">
+        <v>2016</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>ethereumclassic.org</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>Contratos inteligentes (cadena original)</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>Blockchain propia (fork de Ethereum)</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>Mantiene la cadena original de Ethereum tras la bifurcación de 2016.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ethereum-classic</t>
+          <t>bitget-token</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>bgb</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Ethereum Classic</t>
+          <t>Bitget Token</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>9.25</v>
+        <v>2.08</v>
       </c>
       <c r="F66" t="n">
-        <v>1463504601</v>
+        <v>1453173800</v>
       </c>
       <c r="G66" t="n">
         <v>65</v>
       </c>
       <c r="H66" t="n">
-        <v>117262670</v>
+        <v>14819720</v>
       </c>
       <c r="I66" t="n">
-        <v>9.41</v>
+        <v>2.14</v>
       </c>
       <c r="J66" t="n">
-        <v>8.56</v>
+        <v>2.06</v>
       </c>
       <c r="K66" t="n">
-        <v>0.381459</v>
+        <v>-0.02948212635753444</v>
       </c>
       <c r="L66" t="n">
-        <v>4.30343</v>
+        <v>-1.4001</v>
       </c>
       <c r="M66" t="n">
-        <v>158251635.651071</v>
+        <v>699992029.6481038</v>
       </c>
       <c r="N66" t="n">
-        <v>158252729.1806711</v>
+        <v>910920874.6481038</v>
       </c>
       <c r="O66" t="n">
-        <v>167.09</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="P66" s="1" t="n">
-        <v>44322.44053240741</v>
+        <v>45653.15375</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R66" t="b">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0.0004861496927219168</v>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Plataforma de contratos inteligentes</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Layer 1</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Proof of Work</t>
-        </is>
-      </c>
-      <c r="W66" t="n">
-        <v>2016</v>
-      </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>ethereumclassic.org</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>Contratos inteligentes (cadena original)</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>Blockchain propia (fork de Ethereum)</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>Mantiene la cadena original de Ethereum tras la bifurcación de 2016.</t>
-        </is>
-      </c>
+        <v>0.0004792291409737777</v>
+      </c>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6327,7 +6327,7 @@
         <v>1.16</v>
       </c>
       <c r="F67" t="n">
-        <v>1449857663</v>
+        <v>1444759933</v>
       </c>
       <c r="G67" t="n">
         <v>66</v>
@@ -6342,10 +6342,10 @@
         <v>1.16</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.001443504240429272</v>
+        <v>-0.004910982889112736</v>
       </c>
       <c r="L67" t="n">
-        <v>-0.1243</v>
+        <v>-0.42309</v>
       </c>
       <c r="M67" t="n">
         <v>1249985019.14243</v>
@@ -6360,13 +6360,13 @@
         <v>46255.48263888889</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R67" t="b">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.0004782557305717813</v>
+        <v>0.0004743378351270142</v>
       </c>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
@@ -6380,7 +6380,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6399,28 +6399,28 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.999359</v>
+        <v>0.999157</v>
       </c>
       <c r="F68" t="n">
-        <v>1418627552</v>
+        <v>1418449542</v>
       </c>
       <c r="G68" t="n">
         <v>67</v>
       </c>
       <c r="H68" t="n">
-        <v>163399353</v>
+        <v>186741192</v>
       </c>
       <c r="I68" t="n">
-        <v>0.9999</v>
+        <v>0.999781</v>
       </c>
       <c r="J68" t="n">
-        <v>0.999328</v>
+        <v>0.999009</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.000450917662056738</v>
+        <v>-0.000303821891072142</v>
       </c>
       <c r="L68" t="n">
-        <v>-0.0451</v>
+        <v>-0.0304</v>
       </c>
       <c r="M68" t="n">
         <v>1419429007.8</v>
@@ -6435,13 +6435,13 @@
         <v>46058.54591435185</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R68" t="b">
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0.0004601909226142355</v>
+        <v>0.0004590425886810063</v>
       </c>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
@@ -6455,7 +6455,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6474,34 +6474,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.999784</v>
+        <v>0.999945</v>
       </c>
       <c r="F69" t="n">
-        <v>1404230861</v>
+        <v>1417710803</v>
       </c>
       <c r="G69" t="n">
         <v>68</v>
       </c>
       <c r="H69" t="n">
-        <v>81320776</v>
+        <v>74197974</v>
       </c>
       <c r="I69" t="n">
         <v>1.001</v>
       </c>
       <c r="J69" t="n">
-        <v>0.999712</v>
+        <v>0.999722</v>
       </c>
       <c r="K69" t="n">
-        <v>4.143e-05</v>
+        <v>3.166e-05</v>
       </c>
       <c r="L69" t="n">
-        <v>0.00414</v>
+        <v>0.00317</v>
       </c>
       <c r="M69" t="n">
-        <v>1403784805.97</v>
+        <v>1417780805.97</v>
       </c>
       <c r="N69" t="n">
-        <v>1403784805.97</v>
+        <v>1417780805.97</v>
       </c>
       <c r="O69" t="n">
         <v>1.002</v>
@@ -6510,13 +6510,13 @@
         <v>46092.00303240741</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R69" t="b">
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>0.0004518632718371016</v>
+        <v>0.0004586131311687907</v>
       </c>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
@@ -6530,7 +6530,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6549,34 +6549,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.99577</v>
+        <v>0.995795</v>
       </c>
       <c r="F70" t="n">
-        <v>1371196287</v>
+        <v>1371639437</v>
       </c>
       <c r="G70" t="n">
         <v>69</v>
       </c>
       <c r="H70" t="n">
-        <v>346913</v>
+        <v>323560</v>
       </c>
       <c r="I70" t="n">
-        <v>0.996614</v>
+        <v>0.9963649999999999</v>
       </c>
       <c r="J70" t="n">
         <v>0.995093</v>
       </c>
       <c r="K70" t="n">
-        <v>-0.000187773526380997</v>
+        <v>0.00026005</v>
       </c>
       <c r="L70" t="n">
-        <v>-0.01885</v>
+        <v>0.02612</v>
       </c>
       <c r="M70" t="n">
-        <v>1377035569.737884</v>
+        <v>1377398957.226253</v>
       </c>
       <c r="N70" t="n">
-        <v>1377035569.737884</v>
+        <v>1377398957.226253</v>
       </c>
       <c r="O70" t="n">
         <v>1.075</v>
@@ -6585,13 +6585,13 @@
         <v>45785.55951388889</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R70" t="b">
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>0.0004327546866876817</v>
+        <v>0.0004318300667485687</v>
       </c>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
@@ -6605,68 +6605,68 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>bfusd</t>
+          <t>lighter</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>bfusd</t>
+          <t>lit</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>BFUSD</t>
+          <t>Lighter</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.999826</v>
+        <v>5.4</v>
       </c>
       <c r="F71" t="n">
-        <v>1319756381</v>
+        <v>1347735457</v>
       </c>
       <c r="G71" t="n">
         <v>70</v>
       </c>
       <c r="H71" t="n">
-        <v>9371282</v>
+        <v>124167092</v>
       </c>
       <c r="I71" t="n">
-        <v>0.999993</v>
+        <v>5.31</v>
       </c>
       <c r="J71" t="n">
-        <v>0.999553</v>
+        <v>4.64</v>
       </c>
       <c r="K71" t="n">
-        <v>7.813999999999999e-05</v>
+        <v>0.666084</v>
       </c>
       <c r="L71" t="n">
-        <v>0.007820000000000001</v>
+        <v>14.07638</v>
       </c>
       <c r="M71" t="n">
-        <v>1320000000</v>
+        <v>250000000</v>
       </c>
       <c r="N71" t="n">
-        <v>1320000000</v>
+        <v>1000000000</v>
       </c>
       <c r="O71" t="n">
-        <v>1.007</v>
+        <v>7.86</v>
       </c>
       <c r="P71" s="1" t="n">
-        <v>45940.56990740741</v>
+        <v>46021.04538194444</v>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S71" t="n">
-        <v>0.0004029996844321916</v>
+        <v>0.0004179337599570639</v>
       </c>
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
@@ -6680,68 +6680,68 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>lighter</t>
+          <t>bfusd</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>lit</t>
+          <t>bfusd</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Lighter</t>
+          <t>BFUSD</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4.93</v>
+        <v>0.9996390000000001</v>
       </c>
       <c r="F72" t="n">
-        <v>1232242620</v>
+        <v>1319687604</v>
       </c>
       <c r="G72" t="n">
         <v>71</v>
       </c>
       <c r="H72" t="n">
-        <v>79001451</v>
+        <v>8670377</v>
       </c>
       <c r="I72" t="n">
-        <v>4.95</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
-        <v>4.64</v>
+        <v>0.9995849999999999</v>
       </c>
       <c r="K72" t="n">
-        <v>0.209943</v>
+        <v>-0.00010823724121567</v>
       </c>
       <c r="L72" t="n">
-        <v>4.45258</v>
+        <v>-0.01083</v>
       </c>
       <c r="M72" t="n">
-        <v>250000000</v>
+        <v>1320000000</v>
       </c>
       <c r="N72" t="n">
-        <v>1000000000</v>
+        <v>1320000000</v>
       </c>
       <c r="O72" t="n">
-        <v>7.86</v>
+        <v>1.007</v>
       </c>
       <c r="P72" s="1" t="n">
-        <v>46021.04538194444</v>
+        <v>45940.56990740741</v>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R72" t="b">
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>0.0003523780492382739</v>
+        <v>0.0004016284597463448</v>
       </c>
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
@@ -6755,68 +6755,68 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>akedo</t>
+          <t>gatechain-token</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ake</t>
+          <t>gt</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Akedo</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.052399</v>
+        <v>10.84</v>
       </c>
       <c r="F73" t="n">
-        <v>1196782097</v>
+        <v>1155932691</v>
       </c>
       <c r="G73" t="n">
         <v>72</v>
       </c>
       <c r="H73" t="n">
-        <v>44626179</v>
+        <v>1638378</v>
       </c>
       <c r="I73" t="n">
-        <v>0.06265900000000001</v>
+        <v>11.23</v>
       </c>
       <c r="J73" t="n">
-        <v>0.04882322</v>
+        <v>10.82</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.003079557998142114</v>
+        <v>-0.1133170312000562</v>
       </c>
       <c r="L73" t="n">
-        <v>-5.55094</v>
+        <v>-1.03465</v>
       </c>
       <c r="M73" t="n">
-        <v>22796250000</v>
+        <v>106638072.8025264</v>
       </c>
       <c r="N73" t="n">
-        <v>100000000000</v>
+        <v>118889344.1049307</v>
       </c>
       <c r="O73" t="n">
-        <v>0.146656</v>
+        <v>25.38</v>
       </c>
       <c r="P73" s="1" t="n">
-        <v>46285.43993055556</v>
+        <v>45682.66666666666</v>
       </c>
       <c r="Q73" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0.0003318661932903672</v>
+        <v>0.0003064314042909701</v>
       </c>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
@@ -6830,68 +6830,68 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>gatechain-token</t>
+          <t>akedo</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>gt</t>
+          <t>ake</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Akedo</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>11.08</v>
+        <v>0.050532</v>
       </c>
       <c r="F74" t="n">
-        <v>1181113565</v>
+        <v>1144411799</v>
       </c>
       <c r="G74" t="n">
         <v>73</v>
       </c>
       <c r="H74" t="n">
-        <v>2167755</v>
+        <v>47864165</v>
       </c>
       <c r="I74" t="n">
-        <v>11.23</v>
+        <v>0.053668</v>
       </c>
       <c r="J74" t="n">
-        <v>10.77</v>
+        <v>0.04016857</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.1686314408443543</v>
+        <v>-0.002711219477506105</v>
       </c>
       <c r="L74" t="n">
-        <v>-1.49965</v>
+        <v>-5.09217</v>
       </c>
       <c r="M74" t="n">
-        <v>106637326.4685546</v>
+        <v>22796250000</v>
       </c>
       <c r="N74" t="n">
-        <v>118888593.6983193</v>
+        <v>100000000000</v>
       </c>
       <c r="O74" t="n">
-        <v>25.38</v>
+        <v>0.146656</v>
       </c>
       <c r="P74" s="1" t="n">
-        <v>45682.66666666666</v>
+        <v>46285.43993055556</v>
       </c>
       <c r="Q74" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S74" t="n">
-        <v>0.0003228028562578264</v>
+        <v>0.0002997338648124484</v>
       </c>
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
@@ -6905,7 +6905,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6924,34 +6924,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.108006</v>
+        <v>0.106738</v>
       </c>
       <c r="F75" t="n">
-        <v>1158178709</v>
+        <v>1144285758</v>
       </c>
       <c r="G75" t="n">
         <v>74</v>
       </c>
       <c r="H75" t="n">
-        <v>80988029</v>
+        <v>107188421</v>
       </c>
       <c r="I75" t="n">
-        <v>0.11281</v>
+        <v>0.11333</v>
       </c>
       <c r="J75" t="n">
         <v>0.106356</v>
       </c>
       <c r="K75" t="n">
-        <v>-0.003967526668272978</v>
+        <v>-0.00185853209138287</v>
       </c>
       <c r="L75" t="n">
-        <v>-3.54326</v>
+        <v>-1.7114</v>
       </c>
       <c r="M75" t="n">
-        <v>10718755191.33206</v>
+        <v>10719336659.25645</v>
       </c>
       <c r="N75" t="n">
-        <v>10718755191.33206</v>
+        <v>10719336659.25645</v>
       </c>
       <c r="O75" t="n">
         <v>1.29</v>
@@ -6960,13 +6960,13 @@
         <v>45364.45493055556</v>
       </c>
       <c r="Q75" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R75" t="b">
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>0.0003095363722170247</v>
+        <v>0.0002996605923112035</v>
       </c>
       <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr"/>
@@ -6980,7 +6980,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6999,34 +6999,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.04145009</v>
+        <v>0.04096166</v>
       </c>
       <c r="F76" t="n">
-        <v>1148755487</v>
+        <v>1135099777</v>
       </c>
       <c r="G76" t="n">
         <v>75</v>
       </c>
       <c r="H76" t="n">
-        <v>24901024</v>
+        <v>16983891</v>
       </c>
       <c r="I76" t="n">
-        <v>0.04460429</v>
+        <v>0.04277877</v>
       </c>
       <c r="J76" t="n">
-        <v>0.04133447</v>
+        <v>0.04091753</v>
       </c>
       <c r="K76" t="n">
-        <v>-0.002310381704365191</v>
+        <v>-0.000935338803778413</v>
       </c>
       <c r="L76" t="n">
-        <v>-5.27961</v>
+        <v>-2.23247</v>
       </c>
       <c r="M76" t="n">
-        <v>27714964311.97035</v>
+        <v>27715909912.88878</v>
       </c>
       <c r="N76" t="n">
-        <v>27715665348.36042</v>
+        <v>27716892547.28106</v>
       </c>
       <c r="O76" t="n">
         <v>0.207411</v>
@@ -7035,13 +7035,13 @@
         <v>45504.69498842592</v>
       </c>
       <c r="Q76" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0003040855848095985</v>
+        <v>0.0002943204267757181</v>
       </c>
       <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr"/>
@@ -7055,7 +7055,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7074,28 +7074,28 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>73.51000000000001</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F77" t="n">
-        <v>1069014351</v>
+        <v>1075963068</v>
       </c>
       <c r="G77" t="n">
         <v>76</v>
       </c>
       <c r="H77" t="n">
-        <v>25197522</v>
+        <v>16743469</v>
       </c>
       <c r="I77" t="n">
-        <v>75.02</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="J77" t="n">
-        <v>65.90000000000001</v>
+        <v>71.09</v>
       </c>
       <c r="K77" t="n">
-        <v>5.85</v>
+        <v>1.53</v>
       </c>
       <c r="L77" t="n">
-        <v>8.647360000000001</v>
+        <v>2.10929</v>
       </c>
       <c r="M77" t="n">
         <v>14544176.16408117</v>
@@ -7110,13 +7110,13 @@
         <v>44450.05208333334</v>
       </c>
       <c r="Q77" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0002579599623884506</v>
+        <v>0.0002599419738610177</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7179,28 +7179,28 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.090155</v>
+        <v>0.090327</v>
       </c>
       <c r="F78" t="n">
-        <v>1013630058</v>
+        <v>1015710229</v>
       </c>
       <c r="G78" t="n">
         <v>77</v>
       </c>
       <c r="H78" t="n">
-        <v>12821802</v>
+        <v>7674560</v>
       </c>
       <c r="I78" t="n">
-        <v>0.094476</v>
+        <v>0.092358</v>
       </c>
       <c r="J78" t="n">
-        <v>0.087199</v>
+        <v>0.088785</v>
       </c>
       <c r="K78" t="n">
-        <v>0.00023575</v>
+        <v>0.00033866</v>
       </c>
       <c r="L78" t="n">
-        <v>0.26218</v>
+        <v>0.37634</v>
       </c>
       <c r="M78" t="n">
         <v>11243022455.381</v>
@@ -7215,13 +7215,13 @@
         <v>45714.36184027778</v>
       </c>
       <c r="Q78" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R78" t="b">
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>0.0002259233610164783</v>
+        <v>0.0002249146714702384</v>
       </c>
       <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr"/>
@@ -7235,292 +7235,292 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>kucoin-shares</t>
+          <t>jupiter-exchange-solana</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>kcs</t>
+          <t>jup</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>KuCoin</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>7.38</v>
+        <v>0.299981</v>
       </c>
       <c r="F79" t="n">
-        <v>1011903588</v>
+        <v>995497410</v>
       </c>
       <c r="G79" t="n">
         <v>78</v>
       </c>
       <c r="H79" t="n">
-        <v>30162316</v>
+        <v>88093803</v>
       </c>
       <c r="I79" t="n">
-        <v>7.47</v>
+        <v>0.305864</v>
       </c>
       <c r="J79" t="n">
-        <v>7.28</v>
+        <v>0.288725</v>
       </c>
       <c r="K79" t="n">
-        <v>0.059278</v>
+        <v>0.00581027</v>
       </c>
       <c r="L79" t="n">
-        <v>0.80992</v>
+        <v>1.97514</v>
       </c>
       <c r="M79" t="n">
-        <v>137155021.2773955</v>
+        <v>3319369204.37</v>
       </c>
       <c r="N79" t="n">
-        <v>142155021.2773955</v>
+        <v>6861486697.52717</v>
       </c>
       <c r="O79" t="n">
-        <v>28.83</v>
+        <v>2</v>
       </c>
       <c r="P79" s="1" t="n">
-        <v>44531.29832175926</v>
+        <v>45322.29359953704</v>
       </c>
       <c r="Q79" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R79" t="b">
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0002249246982517362</v>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>Token de exchange</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>Utilidad</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>N/A (token de exchange)</t>
-        </is>
-      </c>
-      <c r="W79" t="n">
-        <v>2017</v>
-      </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>kucoin.com</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>Beneficios en el exchange KuCoin</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>Token ERC-20 sobre Ethereum</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>Otorga descuentos en comisiones dentro del exchange KuCoin.</t>
-        </is>
-      </c>
+        <v>0.0002131641791277433</v>
+      </c>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr"/>
+      <c r="X79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>algorand</t>
+          <t>kucoin-shares</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>algo</t>
+          <t>kcs</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Algorand</t>
+          <t>KuCoin</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.111028</v>
+        <v>7.25</v>
       </c>
       <c r="F80" t="n">
-        <v>1004021390</v>
+        <v>994089775</v>
       </c>
       <c r="G80" t="n">
         <v>79</v>
       </c>
       <c r="H80" t="n">
-        <v>60317321</v>
+        <v>29298412</v>
       </c>
       <c r="I80" t="n">
-        <v>0.113177</v>
+        <v>7.48</v>
       </c>
       <c r="J80" t="n">
-        <v>0.108049</v>
+        <v>7.18</v>
       </c>
       <c r="K80" t="n">
-        <v>-0.000907045263806736</v>
+        <v>-0.1272167778339623</v>
       </c>
       <c r="L80" t="n">
-        <v>-0.81033</v>
+        <v>-1.72493</v>
       </c>
       <c r="M80" t="n">
-        <v>9042752944.706263</v>
+        <v>137155021.2773955</v>
       </c>
       <c r="N80" t="n">
-        <v>9055595374.037592</v>
+        <v>142155021.2773955</v>
       </c>
       <c r="O80" t="n">
-        <v>3.56</v>
+        <v>28.83</v>
       </c>
       <c r="P80" s="1" t="n">
-        <v>43636.28563657407</v>
+        <v>44531.29832175926</v>
       </c>
       <c r="Q80" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R80" t="b">
         <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>0.0002203653038533829</v>
+        <v>0.0002123458665366828</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>Plataforma de contratos inteligentes</t>
+          <t>Token de exchange</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>Layer 1</t>
+          <t>Utilidad</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>Pure Proof of Stake</t>
+          <t>N/A (token de exchange)</t>
         </is>
       </c>
       <c r="W80" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>algorand.com</t>
+          <t>kucoin.com</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>Contratos inteligentes de alta eficiencia</t>
+          <t>Beneficios en el exchange KuCoin</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>Blockchain propia (Layer 1)</t>
+          <t>Token ERC-20 sobre Ethereum</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>Fundada por Silvio Micali, ganador del Premio Turing.</t>
+          <t>Otorga descuentos en comisiones dentro del exchange KuCoin.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>jupiter-exchange-solana</t>
+          <t>algorand</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>jup</t>
+          <t>algo</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Algorand</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.297261</v>
+        <v>0.108912</v>
       </c>
       <c r="F81" t="n">
-        <v>987368378</v>
+        <v>983516897</v>
       </c>
       <c r="G81" t="n">
         <v>80</v>
       </c>
       <c r="H81" t="n">
-        <v>89403138</v>
+        <v>54321051</v>
       </c>
       <c r="I81" t="n">
-        <v>0.30265</v>
+        <v>0.114624</v>
       </c>
       <c r="J81" t="n">
-        <v>0.288725</v>
+        <v>0.108881</v>
       </c>
       <c r="K81" t="n">
-        <v>0.0020476</v>
+        <v>-0.001904373624831854</v>
       </c>
       <c r="L81" t="n">
-        <v>0.6936</v>
+        <v>-1.7185</v>
       </c>
       <c r="M81" t="n">
-        <v>3319369204.37</v>
+        <v>9042752944.706263</v>
       </c>
       <c r="N81" t="n">
-        <v>6861486746.959235</v>
+        <v>9055738958.909975</v>
       </c>
       <c r="O81" t="n">
-        <v>2</v>
+        <v>3.56</v>
       </c>
       <c r="P81" s="1" t="n">
-        <v>45322.29359953704</v>
+        <v>43636.28563657407</v>
       </c>
       <c r="Q81" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R81" t="b">
         <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0.0002107325022378297</v>
-      </c>
-      <c r="T81" t="inlineStr"/>
-      <c r="U81" t="inlineStr"/>
-      <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
-      <c r="X81" t="inlineStr"/>
-      <c r="Y81" t="inlineStr"/>
-      <c r="Z81" t="inlineStr"/>
-      <c r="AA81" t="inlineStr"/>
+        <v>0.000206199444210478</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Plataforma de contratos inteligentes</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Layer 1</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Pure Proof of Stake</t>
+        </is>
+      </c>
+      <c r="W81" t="n">
+        <v>2019</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>algorand.com</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>Contratos inteligentes de alta eficiencia</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Layer 1)</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>Fundada por Silvio Micali, ganador del Premio Turing.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7542,7 +7542,7 @@
         <v>107.53</v>
       </c>
       <c r="F82" t="n">
-        <v>979825296</v>
+        <v>977656523</v>
       </c>
       <c r="G82" t="n">
         <v>81</v>
@@ -7554,19 +7554,19 @@
         <v>107.53</v>
       </c>
       <c r="J82" t="n">
-        <v>106.54</v>
+        <v>107.53</v>
       </c>
       <c r="K82" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>0.92923</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>9112111</v>
+        <v>9091942</v>
       </c>
       <c r="N82" t="n">
-        <v>9112111</v>
+        <v>9091942</v>
       </c>
       <c r="O82" t="n">
         <v>107.53</v>
@@ -7575,13 +7575,13 @@
         <v>46287.17361111111</v>
       </c>
       <c r="Q82" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R82" t="b">
         <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0.000206369266777731</v>
+        <v>0.0002027925824654064</v>
       </c>
       <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr"/>
@@ -7595,7 +7595,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7614,34 +7614,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="F83" t="n">
-        <v>953590068</v>
+        <v>957085224</v>
       </c>
       <c r="G83" t="n">
         <v>82</v>
       </c>
       <c r="H83" t="n">
-        <v>69764701</v>
+        <v>63768684</v>
       </c>
       <c r="I83" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="J83" t="n">
         <v>1.73</v>
       </c>
       <c r="K83" t="n">
-        <v>-0.01942424605047477</v>
+        <v>0.03481011</v>
       </c>
       <c r="L83" t="n">
-        <v>-1.07234</v>
+        <v>1.97262</v>
       </c>
       <c r="M83" t="n">
         <v>532132124.756035</v>
       </c>
       <c r="N83" t="n">
-        <v>532132124.756035</v>
+        <v>532137677.998407</v>
       </c>
       <c r="O83" t="n">
         <v>43.84</v>
@@ -7650,13 +7650,13 @@
         <v>44458.66666666666</v>
       </c>
       <c r="Q83" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R83" t="b">
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.000191193708946943</v>
+        <v>0.0001908336918537269</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -7700,68 +7700,68 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>render-token</t>
+          <t>just</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>render</t>
+          <t>jst</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Render</t>
+          <t>JUST</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1.82</v>
+        <v>0.112383</v>
       </c>
       <c r="F84" t="n">
-        <v>944144256</v>
+        <v>920300064</v>
       </c>
       <c r="G84" t="n">
         <v>83</v>
       </c>
       <c r="H84" t="n">
-        <v>88805898</v>
+        <v>25632519</v>
       </c>
       <c r="I84" t="n">
-        <v>1.9</v>
+        <v>0.115786</v>
       </c>
       <c r="J84" t="n">
-        <v>1.79</v>
+        <v>0.111845</v>
       </c>
       <c r="K84" t="n">
-        <v>-0.02020480614472042</v>
+        <v>-0.003271375287102293</v>
       </c>
       <c r="L84" t="n">
-        <v>-1.09889</v>
+        <v>-2.82858</v>
       </c>
       <c r="M84" t="n">
-        <v>518776241.2826915</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="N84" t="n">
-        <v>533536414.5626915</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="O84" t="n">
-        <v>13.53</v>
+        <v>0.193254</v>
       </c>
       <c r="P84" s="1" t="n">
-        <v>45368.35444444444</v>
+        <v>44290.85721064815</v>
       </c>
       <c r="Q84" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R84" t="b">
         <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0.0001857298545346714</v>
+        <v>0.0001694490576323718</v>
       </c>
       <c r="T84" t="inlineStr"/>
       <c r="U84" t="inlineStr"/>
@@ -7775,68 +7775,68 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>just</t>
+          <t>render-token</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>jst</t>
+          <t>render</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>JUST</t>
+          <t>Render</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.112712</v>
+        <v>1.77</v>
       </c>
       <c r="F85" t="n">
-        <v>922930974</v>
+        <v>919142956</v>
       </c>
       <c r="G85" t="n">
         <v>84</v>
       </c>
       <c r="H85" t="n">
-        <v>40948327</v>
+        <v>69728211</v>
       </c>
       <c r="I85" t="n">
-        <v>0.117046</v>
+        <v>1.88</v>
       </c>
       <c r="J85" t="n">
-        <v>0.112475</v>
+        <v>1.77</v>
       </c>
       <c r="K85" t="n">
-        <v>0.00048579</v>
+        <v>-0.07681907152692014</v>
       </c>
       <c r="L85" t="n">
-        <v>0.43286</v>
+        <v>-4.15402</v>
       </c>
       <c r="M85" t="n">
-        <v>8188743036.341737</v>
+        <v>518776241.2826915</v>
       </c>
       <c r="N85" t="n">
-        <v>8188743036.341737</v>
+        <v>533536414.5626915</v>
       </c>
       <c r="O85" t="n">
-        <v>0.193254</v>
+        <v>13.53</v>
       </c>
       <c r="P85" s="1" t="n">
-        <v>44290.85721064815</v>
+        <v>45368.35444444444</v>
       </c>
       <c r="Q85" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R85" t="b">
         <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>0.0001734592012065657</v>
+        <v>0.0001687763860622439</v>
       </c>
       <c r="T85" t="inlineStr"/>
       <c r="U85" t="inlineStr"/>
@@ -7850,7 +7850,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7869,28 +7869,28 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.879281</v>
+        <v>0.869165</v>
       </c>
       <c r="F86" t="n">
-        <v>879412431</v>
+        <v>869403190</v>
       </c>
       <c r="G86" t="n">
         <v>85</v>
       </c>
       <c r="H86" t="n">
-        <v>5098330</v>
+        <v>5535412</v>
       </c>
       <c r="I86" t="n">
-        <v>0.896209</v>
+        <v>0.89935</v>
       </c>
       <c r="J86" t="n">
-        <v>0.857331</v>
+        <v>0.871714</v>
       </c>
       <c r="K86" t="n">
-        <v>-0.000805513845757888</v>
+        <v>-0.01375341783522532</v>
       </c>
       <c r="L86" t="n">
-        <v>-0.09153</v>
+        <v>-1.55772</v>
       </c>
       <c r="M86" t="n">
         <v>1000000000</v>
@@ -7905,13 +7905,13 @@
         <v>44328.27623842593</v>
       </c>
       <c r="Q86" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R86" t="b">
         <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0.0001482862480304724</v>
+        <v>0.0001398607390413856</v>
       </c>
       <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr"/>
@@ -7925,7 +7925,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7944,34 +7944,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1.014</v>
+        <v>1.016</v>
       </c>
       <c r="F87" t="n">
-        <v>842021201</v>
+        <v>844421380</v>
       </c>
       <c r="G87" t="n">
         <v>86</v>
       </c>
       <c r="H87" t="n">
-        <v>210499976</v>
+        <v>195620051</v>
       </c>
       <c r="I87" t="n">
-        <v>1.033</v>
+        <v>1.064</v>
       </c>
       <c r="J87" t="n">
-        <v>0.974393</v>
+        <v>0.9855390000000001</v>
       </c>
       <c r="K87" t="n">
-        <v>0.02573698</v>
+        <v>-0.001571817332436831</v>
       </c>
       <c r="L87" t="n">
-        <v>2.60493</v>
+        <v>-0.15447</v>
       </c>
       <c r="M87" t="n">
-        <v>830752086</v>
+        <v>830787126</v>
       </c>
       <c r="N87" t="n">
-        <v>1957034255</v>
+        <v>1957033216</v>
       </c>
       <c r="O87" t="n">
         <v>236.84</v>
@@ -7980,13 +7980,13 @@
         <v>44287.22894675926</v>
       </c>
       <c r="Q87" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R87" t="b">
         <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>0.0001266575900584778</v>
+        <v>0.0001253378480430213</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -8030,187 +8030,187 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>pancakeswap-token</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>cake</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Dash</t>
+          <t>PancakeSwap</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>63.62</v>
+        <v>2.6</v>
       </c>
       <c r="F88" t="n">
-        <v>816756952</v>
+        <v>828522048</v>
       </c>
       <c r="G88" t="n">
         <v>87</v>
       </c>
       <c r="H88" t="n">
-        <v>216929174</v>
+        <v>117790690</v>
       </c>
       <c r="I88" t="n">
-        <v>64.89</v>
+        <v>2.72</v>
       </c>
       <c r="J88" t="n">
-        <v>58.18</v>
+        <v>2.5</v>
       </c>
       <c r="K88" t="n">
-        <v>4.75</v>
+        <v>0.06571100000000001</v>
       </c>
       <c r="L88" t="n">
-        <v>8.06732</v>
+        <v>2.59574</v>
       </c>
       <c r="M88" t="n">
-        <v>12842808.78359296</v>
+        <v>318995668.0660263</v>
       </c>
       <c r="N88" t="n">
-        <v>12842844.19760836</v>
+        <v>330627631.6090779</v>
       </c>
       <c r="O88" t="n">
-        <v>1493.59</v>
+        <v>43.96</v>
       </c>
       <c r="P88" s="1" t="n">
-        <v>43088.66666666666</v>
+        <v>44316.08914351852</v>
       </c>
       <c r="Q88" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>0.0001120436872652211</v>
-      </c>
-      <c r="T88" t="inlineStr"/>
-      <c r="U88" t="inlineStr"/>
-      <c r="V88" t="inlineStr"/>
-      <c r="W88" t="inlineStr"/>
-      <c r="X88" t="inlineStr"/>
-      <c r="Y88" t="inlineStr"/>
-      <c r="Z88" t="inlineStr"/>
-      <c r="AA88" t="inlineStr"/>
+        <v>0.0001160949522887583</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>DeFi</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Exchange descentralizado</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>N/A (token BEP-20)</t>
+        </is>
+      </c>
+      <c r="W88" t="n">
+        <v>2020</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>pancakeswap.finance</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>Intercambio descentralizado en BNB Chain</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>Token BEP-20 sobre BNB Chain</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>Principal exchange descentralizado (DEX) del ecosistema BNB Chain.</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>pancakeswap-token</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>cake</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>PancakeSwap</t>
+          <t>Dash</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2.54</v>
+        <v>64.44</v>
       </c>
       <c r="F89" t="n">
-        <v>811500600</v>
+        <v>828395976</v>
       </c>
       <c r="G89" t="n">
         <v>88</v>
       </c>
       <c r="H89" t="n">
-        <v>91997476</v>
+        <v>243663635</v>
       </c>
       <c r="I89" t="n">
-        <v>2.59</v>
+        <v>65.53</v>
       </c>
       <c r="J89" t="n">
-        <v>2.46</v>
+        <v>58.18</v>
       </c>
       <c r="K89" t="n">
-        <v>-0.002035382228805283</v>
+        <v>4.86</v>
       </c>
       <c r="L89" t="n">
-        <v>-0.07997</v>
+        <v>8.148160000000001</v>
       </c>
       <c r="M89" t="n">
-        <v>318995589.2344064</v>
+        <v>12841073.33258205</v>
       </c>
       <c r="N89" t="n">
-        <v>330627631.6090779</v>
+        <v>12841268.89159301</v>
       </c>
       <c r="O89" t="n">
-        <v>43.96</v>
+        <v>1493.59</v>
       </c>
       <c r="P89" s="1" t="n">
-        <v>44316.08914351852</v>
+        <v>43088.66666666666</v>
       </c>
       <c r="Q89" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S89" t="n">
-        <v>0.0001090031924864077</v>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>DeFi</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>Exchange descentralizado</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>N/A (token BEP-20)</t>
-        </is>
-      </c>
-      <c r="W89" t="n">
-        <v>2020</v>
-      </c>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>pancakeswap.finance</t>
-        </is>
-      </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>Intercambio descentralizado en BNB Chain</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>Token BEP-20 sobre BNB Chain</t>
-        </is>
-      </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>Principal exchange descentralizado (DEX) del ecosistema BNB Chain.</t>
-        </is>
-      </c>
+        <v>0.0001160216617660161</v>
+      </c>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr"/>
+      <c r="W89" t="inlineStr"/>
+      <c r="X89" t="inlineStr"/>
+      <c r="Y89" t="inlineStr"/>
+      <c r="Z89" t="inlineStr"/>
+      <c r="AA89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8229,28 +8229,28 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.00918296</v>
+        <v>0.00945007</v>
       </c>
       <c r="F90" t="n">
-        <v>789620256</v>
+        <v>812856826</v>
       </c>
       <c r="G90" t="n">
         <v>89</v>
       </c>
       <c r="H90" t="n">
-        <v>16654905</v>
+        <v>23445125</v>
       </c>
       <c r="I90" t="n">
-        <v>0.0093454</v>
+        <v>0.00988909</v>
       </c>
       <c r="J90" t="n">
-        <v>0.00888102</v>
+        <v>0.008951300000000001</v>
       </c>
       <c r="K90" t="n">
-        <v>-5.874247927338e-06</v>
+        <v>0.00027041</v>
       </c>
       <c r="L90" t="n">
-        <v>-0.06393</v>
+        <v>2.94573</v>
       </c>
       <c r="M90" t="n">
         <v>85985041177</v>
@@ -8265,13 +8265,13 @@
         <v>44304.71413194444</v>
       </c>
       <c r="Q90" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R90" t="b">
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>9.634668247896528e-05</v>
+        <v>0.000106988153719272</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8334,28 +8334,28 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>7.8</v>
+        <v>8.08</v>
       </c>
       <c r="F91" t="n">
-        <v>779786046</v>
+        <v>808076123</v>
       </c>
       <c r="G91" t="n">
         <v>90</v>
       </c>
       <c r="H91" t="n">
-        <v>157009128</v>
+        <v>199910565</v>
       </c>
       <c r="I91" t="n">
-        <v>7.99</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="J91" t="n">
-        <v>7.5</v>
+        <v>7.59</v>
       </c>
       <c r="K91" t="n">
-        <v>0.01423484</v>
+        <v>0.271737</v>
       </c>
       <c r="L91" t="n">
-        <v>0.18285</v>
+        <v>3.47926</v>
       </c>
       <c r="M91" t="n">
         <v>100000000</v>
@@ -8370,13 +8370,13 @@
         <v>45365.29608796296</v>
       </c>
       <c r="Q91" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R91" t="b">
         <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>9.065816234965238e-05</v>
+        <v>0.0001042089464254629</v>
       </c>
       <c r="T91" t="inlineStr"/>
       <c r="U91" t="inlineStr"/>
@@ -8390,7 +8390,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8412,7 +8412,7 @@
         <v>1.21</v>
       </c>
       <c r="F92" t="n">
-        <v>779781851</v>
+        <v>767684870</v>
       </c>
       <c r="G92" t="n">
         <v>91</v>
@@ -8421,22 +8421,22 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="J92" t="n">
         <v>1.21</v>
       </c>
       <c r="K92" t="n">
-        <v>-0.001516706866147688</v>
+        <v>-0.005142105392973884</v>
       </c>
       <c r="L92" t="n">
-        <v>-0.12491</v>
+        <v>-0.42371</v>
       </c>
       <c r="M92" t="n">
-        <v>642998758.0930901</v>
+        <v>635257311.01475</v>
       </c>
       <c r="N92" t="n">
-        <v>642998758.0930901</v>
+        <v>635257311.01475</v>
       </c>
       <c r="O92" t="n">
         <v>1.26</v>
@@ -8445,13 +8445,13 @@
         <v>46049.54175925926</v>
       </c>
       <c r="Q92" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R92" t="b">
         <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>9.065573578545023e-05</v>
+        <v>8.072795106898724e-05</v>
       </c>
       <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr"/>
@@ -8465,7 +8465,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8487,7 +8487,7 @@
         <v>11.22</v>
       </c>
       <c r="F93" t="n">
-        <v>733945028</v>
+        <v>736700070</v>
       </c>
       <c r="G93" t="n">
         <v>92</v>
@@ -8502,31 +8502,31 @@
         <v>11.22</v>
       </c>
       <c r="K93" t="n">
-        <v>0.003219</v>
+        <v>0.001098</v>
       </c>
       <c r="L93" t="n">
-        <v>0.0287</v>
+        <v>0.00979</v>
       </c>
       <c r="M93" t="n">
-        <v>65413837.965085</v>
+        <v>65652959.922754</v>
       </c>
       <c r="N93" t="n">
-        <v>65373552.035848</v>
+        <v>65653772.677143</v>
       </c>
       <c r="O93" t="n">
         <v>11.22</v>
       </c>
       <c r="P93" s="1" t="n">
-        <v>46287.57291666666</v>
+        <v>46288.55590277778</v>
       </c>
       <c r="Q93" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R93" t="b">
         <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>6.414179208288009e-05</v>
+        <v>6.27152901366481e-05</v>
       </c>
       <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr"/>
@@ -8540,248 +8540,248 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>aptos</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>apt</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>GHO</t>
+          <t>Aptos</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.999162</v>
+        <v>0.8195210000000001</v>
       </c>
       <c r="F94" t="n">
-        <v>698406791</v>
+        <v>713656348</v>
       </c>
       <c r="G94" t="n">
         <v>93</v>
       </c>
       <c r="H94" t="n">
-        <v>4746550</v>
+        <v>175330693</v>
       </c>
       <c r="I94" t="n">
-        <v>0.999281</v>
+        <v>0.857235</v>
       </c>
       <c r="J94" t="n">
-        <v>0.998814</v>
+        <v>0.7566310000000001</v>
       </c>
       <c r="K94" t="n">
-        <v>0.00022591</v>
+        <v>0.050185</v>
       </c>
       <c r="L94" t="n">
-        <v>0.02261</v>
+        <v>6.52315</v>
       </c>
       <c r="M94" t="n">
-        <v>699000000</v>
+        <v>870678378.6642992</v>
       </c>
       <c r="N94" t="n">
-        <v>699000000</v>
+        <v>1209118421.186413</v>
       </c>
       <c r="O94" t="n">
-        <v>1.03</v>
+        <v>19.92</v>
       </c>
       <c r="P94" s="1" t="n">
-        <v>45350.38608796296</v>
+        <v>44952.26755787037</v>
       </c>
       <c r="Q94" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S94" t="n">
-        <v>4.358498309316028e-05</v>
-      </c>
-      <c r="T94" t="inlineStr"/>
-      <c r="U94" t="inlineStr"/>
-      <c r="V94" t="inlineStr"/>
-      <c r="W94" t="inlineStr"/>
-      <c r="X94" t="inlineStr"/>
-      <c r="Y94" t="inlineStr"/>
-      <c r="Z94" t="inlineStr"/>
-      <c r="AA94" t="inlineStr"/>
+        <v>4.931908454535548e-05</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Plataforma de contratos inteligentes</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Layer 1</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Proof of Stake (BFT)</t>
+        </is>
+      </c>
+      <c r="W94" t="n">
+        <v>2022</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>aptosfoundation.org</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>Contratos inteligentes de alto rendimiento</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Layer 1)</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>Desarrollada por exingenieros del proyecto Diem (Meta/Facebook).</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>aptos</t>
+          <t>aerodrome-finance</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>apt</t>
+          <t>aero</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Aptos</t>
+          <t>Aerodrome Finance</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.792002</v>
+        <v>0.713074</v>
       </c>
       <c r="F95" t="n">
-        <v>690250378</v>
+        <v>707608773</v>
       </c>
       <c r="G95" t="n">
         <v>94</v>
       </c>
       <c r="H95" t="n">
-        <v>152849727</v>
+        <v>71562123</v>
       </c>
       <c r="I95" t="n">
-        <v>0.80848</v>
+        <v>0.7368209999999999</v>
       </c>
       <c r="J95" t="n">
-        <v>0.748675</v>
+        <v>0.673687</v>
       </c>
       <c r="K95" t="n">
-        <v>0.01030098</v>
+        <v>0.01988293</v>
       </c>
       <c r="L95" t="n">
-        <v>1.31776</v>
+        <v>2.86832</v>
       </c>
       <c r="M95" t="n">
-        <v>870645897.0627604</v>
+        <v>992612383.1289241</v>
       </c>
       <c r="N95" t="n">
-        <v>1209086276.864642</v>
+        <v>1983240735.576791</v>
       </c>
       <c r="O95" t="n">
-        <v>19.92</v>
+        <v>2.32</v>
       </c>
       <c r="P95" s="1" t="n">
-        <v>44952.26755787037</v>
+        <v>45633.25043981482</v>
       </c>
       <c r="Q95" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R95" t="b">
         <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>3.886697122098251e-05</v>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>Plataforma de contratos inteligentes</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>Layer 1</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>Proof of Stake (BFT)</t>
-        </is>
-      </c>
-      <c r="W95" t="n">
-        <v>2022</v>
-      </c>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>aptosfoundation.org</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>Contratos inteligentes de alto rendimiento</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Layer 1)</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>Desarrollada por exingenieros del proyecto Diem (Meta/Facebook).</t>
-        </is>
-      </c>
+        <v>4.580339562892256e-05</v>
+      </c>
+      <c r="T95" t="inlineStr"/>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr"/>
+      <c r="W95" t="inlineStr"/>
+      <c r="X95" t="inlineStr"/>
+      <c r="Y95" t="inlineStr"/>
+      <c r="Z95" t="inlineStr"/>
+      <c r="AA95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>janus-henderson-anemoy-aaa-clo-fund</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>jaaa</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy AAA CLO Fund</t>
+          <t>GHO</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1.05</v>
+        <v>0.998898</v>
       </c>
       <c r="F96" t="n">
-        <v>677692166</v>
+        <v>698246801</v>
       </c>
       <c r="G96" t="n">
         <v>95</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>6795088</v>
       </c>
       <c r="I96" t="n">
-        <v>1.05</v>
+        <v>0.999282</v>
       </c>
       <c r="J96" t="n">
-        <v>1.05</v>
+        <v>0.998801</v>
       </c>
       <c r="K96" t="n">
-        <v>7.4e-05</v>
+        <v>-0.000139018097914612</v>
       </c>
       <c r="L96" t="n">
-        <v>0.00704</v>
+        <v>-0.01392</v>
       </c>
       <c r="M96" t="n">
-        <v>645128652.594015</v>
+        <v>699000000</v>
       </c>
       <c r="N96" t="n">
-        <v>645128652.594015</v>
+        <v>699000000</v>
       </c>
       <c r="O96" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="P96" s="1" t="n">
-        <v>46287.38530092593</v>
+        <v>45350.38608796296</v>
       </c>
       <c r="Q96" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R96" t="b">
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>3.160277391889329e-05</v>
+        <v>4.036091972802752e-05</v>
       </c>
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
@@ -8795,68 +8795,68 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>aerodrome-finance</t>
+          <t>janus-henderson-anemoy-aaa-clo-fund</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>aero</t>
+          <t>jaaa</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Aerodrome Finance</t>
+          <t>Janus Henderson Anemoy AAA CLO Fund</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.680061</v>
+        <v>1.05</v>
       </c>
       <c r="F97" t="n">
-        <v>675050792</v>
+        <v>677692166</v>
       </c>
       <c r="G97" t="n">
         <v>96</v>
       </c>
       <c r="H97" t="n">
-        <v>51710166</v>
+        <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>0.717605</v>
+        <v>1.05</v>
       </c>
       <c r="J97" t="n">
-        <v>0.673687</v>
+        <v>1.05</v>
       </c>
       <c r="K97" t="n">
-        <v>-0.00846509180192645</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>-1.22945</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>992641877.0384015</v>
+        <v>645128652.594015</v>
       </c>
       <c r="N97" t="n">
-        <v>1983240735.576791</v>
+        <v>645128652.594015</v>
       </c>
       <c r="O97" t="n">
-        <v>2.32</v>
+        <v>1.05</v>
       </c>
       <c r="P97" s="1" t="n">
-        <v>45633.25043981482</v>
+        <v>46287.38530092593</v>
       </c>
       <c r="Q97" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R97" t="b">
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>3.007489225193237e-05</v>
+        <v>2.841171654314362e-05</v>
       </c>
       <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr"/>
@@ -8870,68 +8870,68 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ether-fi</t>
+          <t>stable-2</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ethfi</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Ether.fi</t>
+          <t>​​Stable</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.693433</v>
+        <v>0.02542602</v>
       </c>
       <c r="F98" t="n">
-        <v>669586560</v>
+        <v>676294745</v>
       </c>
       <c r="G98" t="n">
         <v>97</v>
       </c>
       <c r="H98" t="n">
-        <v>50159691</v>
+        <v>8812550</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7237980000000001</v>
+        <v>0.02547868</v>
       </c>
       <c r="J98" t="n">
-        <v>0.679153</v>
+        <v>0.02415728</v>
       </c>
       <c r="K98" t="n">
-        <v>-0.01990448344609985</v>
+        <v>0.00102938</v>
       </c>
       <c r="L98" t="n">
-        <v>-2.79033</v>
+        <v>4.21934</v>
       </c>
       <c r="M98" t="n">
-        <v>965350000</v>
+        <v>26579350137</v>
       </c>
       <c r="N98" t="n">
-        <v>965350000</v>
+        <v>100000000000</v>
       </c>
       <c r="O98" t="n">
-        <v>8.529999999999999</v>
+        <v>0.04323745</v>
       </c>
       <c r="P98" s="1" t="n">
-        <v>45378.63525462963</v>
+        <v>46156.97986111111</v>
       </c>
       <c r="Q98" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R98" t="b">
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>2.691415094955672e-05</v>
+        <v>2.759934174476732e-05</v>
       </c>
       <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr"/>
@@ -8945,68 +8945,68 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>stable-2</t>
+          <t>ether-fi</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>ethfi</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>​​Stable</t>
+          <t>Ether.fi</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.02442636</v>
+        <v>0.691782</v>
       </c>
       <c r="F99" t="n">
-        <v>648559721</v>
+        <v>666968076</v>
       </c>
       <c r="G99" t="n">
         <v>98</v>
       </c>
       <c r="H99" t="n">
-        <v>8673652</v>
+        <v>54243778</v>
       </c>
       <c r="I99" t="n">
-        <v>0.02532359</v>
+        <v>0.727727</v>
       </c>
       <c r="J99" t="n">
-        <v>0.02415728</v>
+        <v>0.679153</v>
       </c>
       <c r="K99" t="n">
-        <v>-0.000249403786291184</v>
+        <v>-0.01626979708185095</v>
       </c>
       <c r="L99" t="n">
-        <v>-1.01072</v>
+        <v>-2.29783</v>
       </c>
       <c r="M99" t="n">
-        <v>26560449245</v>
+        <v>965350000</v>
       </c>
       <c r="N99" t="n">
-        <v>100000000000</v>
+        <v>965350000</v>
       </c>
       <c r="O99" t="n">
-        <v>0.04323745</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="P99" s="1" t="n">
-        <v>46156.97986111111</v>
+        <v>45378.63525462963</v>
       </c>
       <c r="Q99" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R99" t="b">
         <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>1.475134408379715e-05</v>
+        <v>2.217738884124177e-05</v>
       </c>
       <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr"/>
@@ -9020,68 +9020,68 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>blockstack</t>
+          <t>pudgy-penguins</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>stx</t>
+          <t>pengu</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Stacks</t>
+          <t>Pudgy Penguins</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.335613</v>
+        <v>0.01031779</v>
       </c>
       <c r="F100" t="n">
-        <v>627121537</v>
+        <v>648368859</v>
       </c>
       <c r="G100" t="n">
         <v>99</v>
       </c>
       <c r="H100" t="n">
-        <v>34440364</v>
+        <v>531306847</v>
       </c>
       <c r="I100" t="n">
-        <v>0.353654</v>
+        <v>0.01111058</v>
       </c>
       <c r="J100" t="n">
-        <v>0.332299</v>
+        <v>0.008808359999999999</v>
       </c>
       <c r="K100" t="n">
-        <v>-0.009784445667260777</v>
+        <v>0.00119626</v>
       </c>
       <c r="L100" t="n">
-        <v>-2.8328</v>
+        <v>13.1147</v>
       </c>
       <c r="M100" t="n">
-        <v>1868553460.192209</v>
+        <v>62860396090</v>
       </c>
       <c r="N100" t="n">
-        <v>1868553460.192209</v>
+        <v>76722811726.78036</v>
       </c>
       <c r="O100" t="n">
-        <v>3.86</v>
+        <v>0.06844699999999999</v>
       </c>
       <c r="P100" s="1" t="n">
-        <v>45383.19094907407</v>
+        <v>45643.21206018519</v>
       </c>
       <c r="Q100" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S100" t="n">
-        <v>2.350597992355773e-06</v>
+        <v>1.136494566174738e-05</v>
       </c>
       <c r="T100" t="inlineStr"/>
       <c r="U100" t="inlineStr"/>
@@ -9095,65 +9095,65 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>pudgy-penguins</t>
+          <t>flare-networks</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>pengu</t>
+          <t>flr</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Pudgy Penguins</t>
+          <t>Flare</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.00991273</v>
+        <v>0.00723778</v>
       </c>
       <c r="F101" t="n">
-        <v>623057866</v>
+        <v>628819245</v>
       </c>
       <c r="G101" t="n">
         <v>100</v>
       </c>
       <c r="H101" t="n">
-        <v>482275460</v>
+        <v>6889701</v>
       </c>
       <c r="I101" t="n">
-        <v>0.01047348</v>
+        <v>0.00760419</v>
       </c>
       <c r="J101" t="n">
-        <v>0.00867449</v>
+        <v>0.00692082</v>
       </c>
       <c r="K101" t="n">
-        <v>0.00112527</v>
+        <v>0.00027627</v>
       </c>
       <c r="L101" t="n">
-        <v>12.80544</v>
+        <v>3.96854</v>
       </c>
       <c r="M101" t="n">
-        <v>62860396090</v>
+        <v>86880791700.73494</v>
       </c>
       <c r="N101" t="n">
-        <v>76722815225.58829</v>
+        <v>106608975509.8958</v>
       </c>
       <c r="O101" t="n">
-        <v>0.06844699999999999</v>
+        <v>0.150073</v>
       </c>
       <c r="P101" s="1" t="n">
-        <v>45643.21206018519</v>
+        <v>44935.80144675926</v>
       </c>
       <c r="Q101" s="1" t="n">
-        <v>46287.92372685186</v>
+        <v>46288.57835648148</v>
       </c>
       <c r="R101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>

--- a/src/xlsx/enriched_data.xlsx
+++ b/src/xlsx/enriched_data.xlsx
@@ -560,7 +560,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -579,34 +579,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>85660</v>
+        <v>83978</v>
       </c>
       <c r="F2" t="n">
-        <v>1720796656545</v>
+        <v>1687012220721</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>40475457238</v>
+        <v>44006821718</v>
       </c>
       <c r="I2" t="n">
-        <v>87251</v>
+        <v>85876</v>
       </c>
       <c r="J2" t="n">
-        <v>85266</v>
+        <v>82941</v>
       </c>
       <c r="K2" t="n">
-        <v>-433.6906185361877</v>
+        <v>-1701.113919286392</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.50375</v>
+        <v>-1.97836</v>
       </c>
       <c r="M2" t="n">
-        <v>20088325</v>
+        <v>20088671</v>
       </c>
       <c r="N2" t="n">
-        <v>20088325</v>
+        <v>20088728</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -615,7 +615,7 @@
         <v>45936.45673611111</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
@@ -665,7 +665,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -684,34 +684,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2713.74</v>
+        <v>2664.09</v>
       </c>
       <c r="F3" t="n">
-        <v>331259670445</v>
+        <v>325222379231</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>16541219556</v>
+        <v>16572408474</v>
       </c>
       <c r="I3" t="n">
-        <v>2786.6</v>
+        <v>2720.31</v>
       </c>
       <c r="J3" t="n">
-        <v>2714.35</v>
+        <v>2634.74</v>
       </c>
       <c r="K3" t="n">
-        <v>-38.06506006067275</v>
+        <v>-49.80841626912115</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.38328</v>
+        <v>-1.81017</v>
       </c>
       <c r="M3" t="n">
-        <v>122073393.4861459</v>
+        <v>122076229.2680794</v>
       </c>
       <c r="N3" t="n">
-        <v>122073393.4861459</v>
+        <v>122076229.2680793</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -720,13 +720,13 @@
         <v>45893.47295138889</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.192208483399482</v>
+        <v>0.1924917898202895</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -789,34 +789,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9997239999999999</v>
+        <v>0.999744</v>
       </c>
       <c r="F4" t="n">
-        <v>183423662761</v>
+        <v>183495697334</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>77641044569</v>
+        <v>77473994732</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0.999937</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9996159999999999</v>
+        <v>0.999652</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.3375693649009e-05</v>
+        <v>-8.90247621177e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.00134</v>
+        <v>-0.00043</v>
       </c>
       <c r="M4" t="n">
-        <v>183470116796.0007</v>
+        <v>183542716766.929</v>
       </c>
       <c r="N4" t="n">
-        <v>188937062885.4362</v>
+        <v>189009662872.4462</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -825,13 +825,13 @@
         <v>43304.66666666666</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1062657024229202</v>
+        <v>0.1084513191496202</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -894,34 +894,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>780.89</v>
+        <v>775.11</v>
       </c>
       <c r="F5" t="n">
-        <v>103989325404</v>
+        <v>103213855578</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1153867414</v>
+        <v>1197659217</v>
       </c>
       <c r="I5" t="n">
-        <v>798.34</v>
+        <v>781.95</v>
       </c>
       <c r="J5" t="n">
-        <v>777.16</v>
+        <v>758.22</v>
       </c>
       <c r="K5" t="n">
-        <v>-8.973599075082916</v>
+        <v>-5.754073065851458</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.1361</v>
+        <v>-0.70514</v>
       </c>
       <c r="M5" t="n">
-        <v>133159986.57</v>
+        <v>133159906.26</v>
       </c>
       <c r="N5" t="n">
-        <v>133159986.57</v>
+        <v>133159906.26</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -930,13 +930,13 @@
         <v>45943.02875</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06008745421100078</v>
+        <v>0.0608461422190987</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -999,28 +999,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="F6" t="n">
-        <v>98975003054</v>
+        <v>94214439065</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>6721150870</v>
+        <v>4658671923</v>
       </c>
       <c r="I6" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="J6" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00486281</v>
+        <v>-0.07669192306231665</v>
       </c>
       <c r="L6" t="n">
-        <v>0.30987</v>
+        <v>-4.8361</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -1035,13 +1035,13 @@
         <v>45855.82005787037</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05717243496620979</v>
+        <v>0.05550970740392702</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1104,34 +1104,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9998</v>
+        <v>0.99982</v>
       </c>
       <c r="F7" t="n">
-        <v>75112332603</v>
+        <v>75208946184</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>20985936797</v>
+        <v>21520943946</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>1.002</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999641</v>
+        <v>0.999305</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.9422490854358e-05</v>
+        <v>5.7299e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.00294</v>
+        <v>0.00027</v>
       </c>
       <c r="M7" t="n">
-        <v>75125433963.32286</v>
+        <v>75222489862.57661</v>
       </c>
       <c r="N7" t="n">
-        <v>75154585345.82596</v>
+        <v>75208587556.4671</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -1140,13 +1140,13 @@
         <v>43418.66666666666</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04330014301099269</v>
+        <v>0.04423991299634975</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1209,34 +1209,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>116.72</v>
+        <v>114.78</v>
       </c>
       <c r="F8" t="n">
-        <v>68558658494</v>
+        <v>67442627183</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>4497356714</v>
+        <v>4787195372</v>
       </c>
       <c r="I8" t="n">
-        <v>119.66</v>
+        <v>116.94</v>
       </c>
       <c r="J8" t="n">
-        <v>116.08</v>
+        <v>112.72</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8052274963640826</v>
+        <v>-1.945020311639823</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.68515</v>
+        <v>-1.62052</v>
       </c>
       <c r="M8" t="n">
-        <v>587506755.615492</v>
+        <v>587577149.9029876</v>
       </c>
       <c r="N8" t="n">
-        <v>634530393.8774225</v>
+        <v>634608286.6592437</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -1245,13 +1245,13 @@
         <v>45676.13572916666</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R8" t="b">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03949023913598085</v>
+        <v>0.03963467497421824</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1314,34 +1314,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.34171</v>
+        <v>0.339884</v>
       </c>
       <c r="F9" t="n">
-        <v>32452956079</v>
+        <v>32277074717</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>464108235</v>
+        <v>508747370</v>
       </c>
       <c r="I9" t="n">
-        <v>0.345004</v>
+        <v>0.343877</v>
       </c>
       <c r="J9" t="n">
-        <v>0.34041</v>
+        <v>0.338585</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.001158784293061932</v>
+        <v>-0.001792421662365318</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.33797</v>
+        <v>-0.53525</v>
       </c>
       <c r="M9" t="n">
-        <v>94961729708.24278</v>
+        <v>94964948406.9399</v>
       </c>
       <c r="N9" t="n">
-        <v>94963358525.63339</v>
+        <v>94965004918.81999</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1350,13 +1350,13 @@
         <v>45629.67407407407</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01850059985073993</v>
+        <v>0.01878235880425004</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1419,34 +1419,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1634.87</v>
+        <v>1514.5</v>
       </c>
       <c r="F10" t="n">
-        <v>27693853314</v>
+        <v>25670307558</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>2062081097</v>
+        <v>1530755188</v>
       </c>
       <c r="I10" t="n">
-        <v>1658.86</v>
+        <v>1638.23</v>
       </c>
       <c r="J10" t="n">
-        <v>1501.2</v>
+        <v>1461.52</v>
       </c>
       <c r="K10" t="n">
-        <v>119.98</v>
+        <v>-120.5149810899129</v>
       </c>
       <c r="L10" t="n">
-        <v>7.92037</v>
+        <v>-7.53144</v>
       </c>
       <c r="M10" t="n">
-        <v>16945106.4155448</v>
+        <v>16949703.2905448</v>
       </c>
       <c r="N10" t="n">
-        <v>16948106.4155448</v>
+        <v>16949931.4155448</v>
       </c>
       <c r="O10" t="n">
         <v>3191.93</v>
@@ -1455,13 +1455,13 @@
         <v>42671.66666666666</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01573394960777878</v>
+        <v>0.01486470678402283</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1524,34 +1524,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.031</v>
+        <v>1.037</v>
       </c>
       <c r="F11" t="n">
-        <v>23674581041</v>
+        <v>23885874146</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>189366594</v>
+        <v>30426403</v>
       </c>
       <c r="I11" t="n">
-        <v>1.043</v>
+        <v>1.037</v>
       </c>
       <c r="J11" t="n">
-        <v>1.006</v>
+        <v>1.022</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01784585</v>
+        <v>0.00575091</v>
       </c>
       <c r="L11" t="n">
-        <v>1.76152</v>
+        <v>0.55813</v>
       </c>
       <c r="M11" t="n">
-        <v>22966221270.418</v>
+        <v>23042572971.368</v>
       </c>
       <c r="N11" t="n">
-        <v>22966221270.418</v>
+        <v>23042572971.368</v>
       </c>
       <c r="O11" t="n">
         <v>1.061</v>
@@ -1560,13 +1560,13 @@
         <v>46237.59675925926</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R11" t="b">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01339739140348825</v>
+        <v>0.01380658122983865</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
@@ -1580,7 +1580,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1599,28 +1599,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>95.42</v>
+        <v>92.52</v>
       </c>
       <c r="F12" t="n">
-        <v>21227739049</v>
+        <v>20581429395</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1156045775</v>
+        <v>1338426068</v>
       </c>
       <c r="I12" t="n">
-        <v>97.95999999999999</v>
+        <v>95.77</v>
       </c>
       <c r="J12" t="n">
-        <v>93.83</v>
+        <v>89.91</v>
       </c>
       <c r="K12" t="n">
-        <v>0.102821</v>
+        <v>-2.957293932139351</v>
       </c>
       <c r="L12" t="n">
-        <v>0.10787</v>
+        <v>-3.12298</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1635,13 +1635,13 @@
         <v>46288.22002314815</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R12" t="b">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01197494765181307</v>
+        <v>0.01184712597086994</v>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
@@ -1655,7 +1655,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1674,34 +1674,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.09939099999999999</v>
+        <v>0.093919</v>
       </c>
       <c r="F13" t="n">
-        <v>15510961595</v>
+        <v>14655932118</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>1716316067</v>
+        <v>1578915177</v>
       </c>
       <c r="I13" t="n">
-        <v>0.104229</v>
+        <v>0.099772</v>
       </c>
       <c r="J13" t="n">
-        <v>0.098667</v>
+        <v>0.091664</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.001316097675634703</v>
+        <v>-0.005505030732556204</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.30685</v>
+        <v>-5.47073</v>
       </c>
       <c r="M13" t="n">
-        <v>156034686383.7052</v>
+        <v>156048806383.7053</v>
       </c>
       <c r="N13" t="n">
-        <v>156034696383.7052</v>
+        <v>156048456383.7052</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1710,13 +1710,13 @@
         <v>44323.88082175926</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>0.008651564124904941</v>
+        <v>0.008333450398624783</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1779,34 +1779,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>563.9299999999999</v>
+        <v>549.51</v>
       </c>
       <c r="F14" t="n">
-        <v>10598490531</v>
+        <v>10335646084</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>147373493</v>
+        <v>131877115</v>
       </c>
       <c r="I14" t="n">
-        <v>577.02</v>
+        <v>566.0700000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>555.9400000000001</v>
+        <v>542.46</v>
       </c>
       <c r="K14" t="n">
-        <v>-10.32139536398063</v>
+        <v>-13.80552932081468</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.79737</v>
+        <v>-2.47342</v>
       </c>
       <c r="M14" t="n">
-        <v>18808405.30238605</v>
+        <v>18808857.69615291</v>
       </c>
       <c r="N14" t="n">
-        <v>18808438.90178666</v>
+        <v>18808888.29599696</v>
       </c>
       <c r="O14" t="n">
         <v>797.73</v>
@@ -1815,13 +1815,13 @@
         <v>46036.48202546296</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R14" t="b">
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.00579575496635755</v>
+        <v>0.005771625999228014</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1884,28 +1884,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>85.92</v>
+        <v>83.98999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>10212986508</v>
+        <v>9982633074</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>120844109</v>
+        <v>140612680</v>
       </c>
       <c r="I15" t="n">
-        <v>87.68000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>85.67</v>
+        <v>82.98</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6889404075766237</v>
+        <v>-1.943211609221805</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.7954599999999999</v>
+        <v>-2.22567</v>
       </c>
       <c r="M15" t="n">
         <v>118852171</v>
@@ -1920,13 +1920,13 @@
         <v>46286.85358796296</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.005571646588883702</v>
+        <v>0.005562297881782702</v>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
@@ -1940,7 +1940,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1959,34 +1959,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.999889</v>
+        <v>0.999883</v>
       </c>
       <c r="F16" t="n">
-        <v>9604357137</v>
+        <v>9686691626</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>213968809</v>
+        <v>141654011</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.999631</v>
+        <v>0.999647</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.6344570002698e-05</v>
+        <v>-2.8205541120485e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.00563</v>
+        <v>-0.009090000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>9604704100.806463</v>
+        <v>9687827058.865</v>
       </c>
       <c r="N16" t="n">
-        <v>9607472753.612017</v>
+        <v>9697547815.27993</v>
       </c>
       <c r="O16" t="n">
         <v>1.057</v>
@@ -1995,13 +1995,13 @@
         <v>45593.90336805556</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R16" t="b">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.005217826829089034</v>
+        <v>0.00538681181064929</v>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2034,28 +2034,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>12.67</v>
+        <v>12.46</v>
       </c>
       <c r="F17" t="n">
-        <v>9479889414</v>
+        <v>9317677595</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>562753051</v>
+        <v>522257174</v>
       </c>
       <c r="I17" t="n">
-        <v>13.21</v>
+        <v>12.75</v>
       </c>
       <c r="J17" t="n">
-        <v>12.68</v>
+        <v>12.1</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3822432461842418</v>
+        <v>-0.2108202456293533</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.92782</v>
+        <v>-1.59865</v>
       </c>
       <c r="M17" t="n">
         <v>748099970.424884</v>
@@ -2070,13 +2070,13 @@
         <v>44325.67635416667</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.005145468934527207</v>
+        <v>0.005167995477449173</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2139,28 +2139,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.248372</v>
+        <v>0.240627</v>
       </c>
       <c r="F18" t="n">
-        <v>9320073154</v>
+        <v>9030496797</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>864974645</v>
+        <v>592604878</v>
       </c>
       <c r="I18" t="n">
-        <v>0.261886</v>
+        <v>0.249431</v>
       </c>
       <c r="J18" t="n">
-        <v>0.246132</v>
+        <v>0.233288</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.004014587718880164</v>
+        <v>-0.007681261816755242</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.59065</v>
+        <v>-3.03354</v>
       </c>
       <c r="M18" t="n">
         <v>37529061988.53558</v>
@@ -2175,13 +2175,13 @@
         <v>44440.91678240741</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R18" t="b">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.005052561570179056</v>
+        <v>0.004997704258403783</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.01268255</v>
+        <v>0.01204162</v>
       </c>
       <c r="F19" t="n">
-        <v>8997710190</v>
+        <v>8540399072</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>25047308</v>
+        <v>19988680</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01348598</v>
+        <v>0.01271105</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01270828</v>
+        <v>0.01195719</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.000786568705675847</v>
+        <v>-0.0006301626399832819</v>
       </c>
       <c r="L19" t="n">
-        <v>-5.8398</v>
+        <v>-5.2628</v>
       </c>
       <c r="M19" t="n">
-        <v>709240042765.4675</v>
+        <v>709240298301.3969</v>
       </c>
       <c r="N19" t="n">
         <v>1142408526965.963</v>
@@ -2280,13 +2280,13 @@
         <v>46259.82847222222</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R19" t="b">
         <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>0.004865159528930578</v>
+        <v>0.004707088243604554</v>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
@@ -2300,7 +2300,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2319,28 +2319,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8.98</v>
+        <v>8.9</v>
       </c>
       <c r="F20" t="n">
-        <v>8264196225</v>
+        <v>8187966753</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>174153</v>
+        <v>399230</v>
       </c>
       <c r="I20" t="n">
-        <v>9</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>8.949999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.01392138</v>
+        <v>-0.08439936080502441</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1552</v>
+        <v>-0.93935</v>
       </c>
       <c r="M20" t="n">
         <v>919857851.9</v>
@@ -2355,13 +2355,13 @@
         <v>46146.39930555555</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.004438739531361426</v>
+        <v>0.004498104461779753</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2424,34 +2424,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.212671</v>
+        <v>0.20324</v>
       </c>
       <c r="F21" t="n">
-        <v>7429479507</v>
+        <v>7100935549</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>393742905</v>
+        <v>321290636</v>
       </c>
       <c r="I21" t="n">
-        <v>0.224502</v>
+        <v>0.213122</v>
       </c>
       <c r="J21" t="n">
-        <v>0.210057</v>
+        <v>0.197178</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.001867059350335182</v>
+        <v>-0.009336099321796909</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.87027</v>
+        <v>-4.38715</v>
       </c>
       <c r="M21" t="n">
-        <v>34932724603.07527</v>
+        <v>34938629825.38779</v>
       </c>
       <c r="N21" t="n">
-        <v>50001786839.70148</v>
+        <v>50001786839.70147</v>
       </c>
       <c r="O21" t="n">
         <v>0.875563</v>
@@ -2460,13 +2460,13 @@
         <v>43102.66666666666</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R21" t="b">
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.00395348646482916</v>
+        <v>0.003853521431999544</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2529,34 +2529,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353.73</v>
+        <v>335.52</v>
       </c>
       <c r="F22" t="n">
-        <v>7104701843</v>
+        <v>6741819960</v>
       </c>
       <c r="G22" t="n">
         <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>1522885394</v>
+        <v>755674102</v>
       </c>
       <c r="I22" t="n">
-        <v>365.1</v>
+        <v>354.07</v>
       </c>
       <c r="J22" t="n">
-        <v>315.1</v>
+        <v>325.6</v>
       </c>
       <c r="K22" t="n">
-        <v>33.15</v>
+        <v>-19.23857209004734</v>
       </c>
       <c r="L22" t="n">
-        <v>10.34023</v>
+        <v>-5.41248</v>
       </c>
       <c r="M22" t="n">
-        <v>20093343.64665077</v>
+        <v>20093784.27165077</v>
       </c>
       <c r="N22" t="n">
-        <v>20093340.52165077</v>
+        <v>20093796.77165077</v>
       </c>
       <c r="O22" t="n">
         <v>3785.82</v>
@@ -2565,13 +2565,13 @@
         <v>43088.66666666666</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R22" t="b">
         <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0.003764680665210342</v>
+        <v>0.003640574633832999</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2634,34 +2634,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4.74</v>
+        <v>4.5</v>
       </c>
       <c r="F23" t="n">
-        <v>6192679700</v>
+        <v>5881404513</v>
       </c>
       <c r="G23" t="n">
         <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>2285905002</v>
+        <v>1941085414</v>
       </c>
       <c r="I23" t="n">
-        <v>4.79</v>
+        <v>4.76</v>
       </c>
       <c r="J23" t="n">
-        <v>4.25</v>
+        <v>4.09</v>
       </c>
       <c r="K23" t="n">
-        <v>0.270313</v>
+        <v>-0.2306575718520847</v>
       </c>
       <c r="L23" t="n">
-        <v>6.04429</v>
+        <v>-4.60616</v>
       </c>
       <c r="M23" t="n">
-        <v>1307081067</v>
+        <v>1307188691</v>
       </c>
       <c r="N23" t="n">
-        <v>1307081081</v>
+        <v>1307188713</v>
       </c>
       <c r="O23" t="n">
         <v>20.44</v>
@@ -2670,13 +2670,13 @@
         <v>44577.59010416667</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.003234486969441955</v>
+        <v>0.003130369228821503</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2739,34 +2739,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>9.529999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="F24" t="n">
-        <v>5923296357</v>
+        <v>5703573466</v>
       </c>
       <c r="G24" t="n">
         <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>2063905504</v>
+        <v>1293846620</v>
       </c>
       <c r="I24" t="n">
-        <v>10.89</v>
+        <v>9.58</v>
       </c>
       <c r="J24" t="n">
-        <v>8.800000000000001</v>
+        <v>8.81</v>
       </c>
       <c r="K24" t="n">
-        <v>0.460594</v>
+        <v>-0.3608256045277365</v>
       </c>
       <c r="L24" t="n">
-        <v>5.07712</v>
+        <v>-3.73341</v>
       </c>
       <c r="M24" t="n">
-        <v>620668422.6104751</v>
+        <v>620592422.6104751</v>
       </c>
       <c r="N24" t="n">
-        <v>887916418.9163101</v>
+        <v>887840418.9163101</v>
       </c>
       <c r="O24" t="n">
         <v>44.92</v>
@@ -2775,13 +2775,13 @@
         <v>44318.89240740741</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R24" t="b">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.003077884028055243</v>
+        <v>0.003024919748951515</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2825,458 +2825,458 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ethena-usde</t>
+          <t>litecoin</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>usde</t>
+          <t>ltc</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ethena USDe</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.999671</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>4892747442</v>
+        <v>5364962731</v>
       </c>
       <c r="G25" t="n">
         <v>24</v>
       </c>
       <c r="H25" t="n">
-        <v>42655456</v>
+        <v>1161909033</v>
       </c>
       <c r="I25" t="n">
-        <v>0.9999169999999999</v>
+        <v>69.45</v>
       </c>
       <c r="J25" t="n">
-        <v>0.999505</v>
+        <v>59.11</v>
       </c>
       <c r="K25" t="n">
-        <v>9.504e-05</v>
+        <v>6.56</v>
       </c>
       <c r="L25" t="n">
-        <v>0.009509999999999999</v>
+        <v>10.72198</v>
       </c>
       <c r="M25" t="n">
-        <v>4894216226.655697</v>
+        <v>77644854.4984657</v>
       </c>
       <c r="N25" t="n">
-        <v>4897760252.030897</v>
+        <v>77642716.99309745</v>
       </c>
       <c r="O25" t="n">
-        <v>1.034</v>
+        <v>410.26</v>
       </c>
       <c r="P25" s="1" t="n">
-        <v>46000.38208333333</v>
+        <v>44325.80077546297</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>0.002478786141992239</v>
-      </c>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
+        <v>0.002824131829819799</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Pagos</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Store of value ligero</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Proof of Work</t>
+        </is>
+      </c>
+      <c r="W25" t="n">
+        <v>2011</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>litecoin.org</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Pagos rápidos de bajo costo</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Layer 1)</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>Fue diseñada como complemento más rápido y liviano de Bitcoin.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>litecoin</t>
+          <t>ethena-usde</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ltc</t>
+          <t>usde</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Litecoin</t>
+          <t>Ethena USDe</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>62.54</v>
+        <v>0.999875</v>
       </c>
       <c r="F26" t="n">
-        <v>4855138861</v>
+        <v>4896232481</v>
       </c>
       <c r="G26" t="n">
         <v>25</v>
       </c>
       <c r="H26" t="n">
-        <v>599111390</v>
+        <v>75530601</v>
       </c>
       <c r="I26" t="n">
-        <v>64.56999999999999</v>
+        <v>1.001</v>
       </c>
       <c r="J26" t="n">
-        <v>60.79</v>
+        <v>0.999507</v>
       </c>
       <c r="K26" t="n">
-        <v>0.599789</v>
+        <v>0.00017841</v>
       </c>
       <c r="L26" t="n">
-        <v>0.9684</v>
+        <v>0.01751</v>
       </c>
       <c r="M26" t="n">
-        <v>77639204.48411152</v>
+        <v>4896842976.860238</v>
       </c>
       <c r="N26" t="n">
-        <v>77639154.48411152</v>
+        <v>4898170210.675478</v>
       </c>
       <c r="O26" t="n">
-        <v>410.26</v>
+        <v>1.034</v>
       </c>
       <c r="P26" s="1" t="n">
-        <v>44325.80077546297</v>
+        <v>46000.38208333333</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R26" t="b">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.002456922821341487</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Pagos</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Store of value ligero</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Proof of Work</t>
-        </is>
-      </c>
-      <c r="W26" t="n">
-        <v>2011</v>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>litecoin.org</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>Pagos rápidos de bajo costo</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Layer 1)</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>Fue diseñada como complemento más rápido y liviano de Bitcoin.</t>
-        </is>
-      </c>
+        <v>0.002546186207299625</v>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>avalanche-2</t>
+          <t>dai</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>avax</t>
+          <t>dai</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Dai</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>10.72</v>
+        <v>0.99993</v>
       </c>
       <c r="F27" t="n">
-        <v>4738703503</v>
+        <v>4600156531</v>
       </c>
       <c r="G27" t="n">
         <v>26</v>
       </c>
       <c r="H27" t="n">
-        <v>645833105</v>
+        <v>237007676</v>
       </c>
       <c r="I27" t="n">
-        <v>11.38</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>10.73</v>
+        <v>0.999552</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.2624415949471288</v>
+        <v>-3.1086359221111e-05</v>
       </c>
       <c r="L27" t="n">
-        <v>-2.39036</v>
+        <v>0.0058</v>
       </c>
       <c r="M27" t="n">
-        <v>443045723.4029999</v>
+        <v>4600480382.490121</v>
       </c>
       <c r="N27" t="n">
-        <v>469714532.4028373</v>
+        <v>4600480382.490121</v>
       </c>
       <c r="O27" t="n">
-        <v>144.96</v>
+        <v>1.22</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>44521.26314814815</v>
+        <v>43902.79363425926</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R27" t="b">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.002389234450779485</v>
+        <v>0.002370620379755953</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>Plataforma de contratos inteligentes</t>
+          <t>Stablecoin</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>Layer 1</t>
+          <t>Colateralizada por cripto</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Proof of Stake (Avalanche consensus)</t>
+          <t>N/A (token, colateral cripto)</t>
         </is>
       </c>
       <c r="W27" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>avax.network</t>
+          <t>makerdao.com</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>Subredes personalizadas para empresas</t>
+          <t>Estabilidad de valor descentralizada</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>Blockchain propia (Layer 1)</t>
+          <t>Token ERC-20 sobre Ethereum</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>Permite crear subredes (subnets) personalizadas para casos de uso específicos.</t>
+          <t>Stablecoin descentralizada, generada mediante colateral cripto sobrecolateralizado.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>dai</t>
+          <t>avalanche-2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>dai</t>
+          <t>avax</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Dai</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.999841</v>
+        <v>10.24</v>
       </c>
       <c r="F28" t="n">
-        <v>4582808900</v>
+        <v>4534909728</v>
       </c>
       <c r="G28" t="n">
         <v>27</v>
       </c>
       <c r="H28" t="n">
-        <v>237165850</v>
+        <v>543789681</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>10.81</v>
       </c>
       <c r="J28" t="n">
-        <v>0.998871</v>
+        <v>9.98</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.000156011346180596</v>
+        <v>-0.4021845510378839</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.0156</v>
+        <v>-3.71833</v>
       </c>
       <c r="M28" t="n">
-        <v>4583830468.504778</v>
+        <v>443057691.2148384</v>
       </c>
       <c r="N28" t="n">
-        <v>4584121642.59938</v>
+        <v>469726458.1779858</v>
       </c>
       <c r="O28" t="n">
-        <v>1.22</v>
+        <v>144.96</v>
       </c>
       <c r="P28" s="1" t="n">
-        <v>43902.79363425926</v>
+        <v>44521.26314814815</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R28" t="b">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.002298606897107342</v>
+        <v>0.002331930614635639</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>Stablecoin</t>
+          <t>Plataforma de contratos inteligentes</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>Colateralizada por cripto</t>
+          <t>Layer 1</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>N/A (token, colateral cripto)</t>
+          <t>Proof of Stake (Avalanche consensus)</t>
         </is>
       </c>
       <c r="W28" t="n">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>makerdao.com</t>
+          <t>avax.network</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>Estabilidad de valor descentralizada</t>
+          <t>Subredes personalizadas para empresas</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>Token ERC-20 sobre Ethereum</t>
+          <t>Blockchain propia (Layer 1)</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Stablecoin descentralizada, generada mediante colateral cripto sobrecolateralizado.</t>
+          <t>Permite crear subredes (subnets) personalizadas para casos de uso específicos.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>canton-network</t>
+          <t>usd1-wlfi</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>usd1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Canton</t>
+          <t>USD1</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.111645</v>
+        <v>0.999229</v>
       </c>
       <c r="F29" t="n">
-        <v>4426803854</v>
+        <v>4405106258</v>
       </c>
       <c r="G29" t="n">
         <v>28</v>
       </c>
       <c r="H29" t="n">
-        <v>18675067</v>
+        <v>1238503775</v>
       </c>
       <c r="I29" t="n">
-        <v>0.117565</v>
+        <v>0.9995810000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>0.111573</v>
+        <v>0.999151</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.005249514732099017</v>
+        <v>-3.1375902725284e-05</v>
       </c>
       <c r="L29" t="n">
-        <v>-4.49082</v>
+        <v>0.00131</v>
       </c>
       <c r="M29" t="n">
-        <v>39666257608.93535</v>
+        <v>4408506663.047887</v>
       </c>
       <c r="N29" t="n">
-        <v>39667085270.89719</v>
+        <v>4408506663.047887</v>
       </c>
       <c r="O29" t="n">
-        <v>0.194152</v>
+        <v>1.048</v>
       </c>
       <c r="P29" s="1" t="n">
-        <v>46056.00148148148</v>
+        <v>46212.42696759259</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.002207915138653779</v>
+        <v>0.002254960318235035</v>
       </c>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
@@ -3290,68 +3290,68 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>usd1-wlfi</t>
+          <t>canton-network</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>usd1</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>USD1</t>
+          <t>Canton</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.999242</v>
+        <v>0.109057</v>
       </c>
       <c r="F30" t="n">
-        <v>4392540758</v>
+        <v>4326760553</v>
       </c>
       <c r="G30" t="n">
         <v>29</v>
       </c>
       <c r="H30" t="n">
-        <v>1208321949</v>
+        <v>18129687</v>
       </c>
       <c r="I30" t="n">
-        <v>0.99961</v>
+        <v>0.111695</v>
       </c>
       <c r="J30" t="n">
-        <v>0.999139</v>
+        <v>0.106336</v>
       </c>
       <c r="K30" t="n">
-        <v>-8.6097787802997e-05</v>
+        <v>-0.002755490892089763</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.008619999999999999</v>
+        <v>-2.56513</v>
       </c>
       <c r="M30" t="n">
-        <v>4395796480.061099</v>
+        <v>39674466050.23323</v>
       </c>
       <c r="N30" t="n">
-        <v>4398506663.061099</v>
+        <v>39674466050.23323</v>
       </c>
       <c r="O30" t="n">
-        <v>1.048</v>
+        <v>0.194152</v>
       </c>
       <c r="P30" s="1" t="n">
-        <v>46212.42696759259</v>
+        <v>46056.00148148148</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R30" t="b">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.002187996677642567</v>
+        <v>0.002208503223247018</v>
       </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
@@ -3365,7 +3365,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3384,31 +3384,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.094085</v>
+        <v>0.091989</v>
       </c>
       <c r="F31" t="n">
-        <v>4123048732</v>
+        <v>4032020194</v>
       </c>
       <c r="G31" t="n">
         <v>30</v>
       </c>
       <c r="H31" t="n">
-        <v>240085946</v>
+        <v>141640161</v>
       </c>
       <c r="I31" t="n">
-        <v>0.101256</v>
+        <v>0.09438000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>0.09447800000000001</v>
+        <v>0.08828999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.002485756545079959</v>
+        <v>-0.002055540979405135</v>
       </c>
       <c r="L31" t="n">
-        <v>-2.57402</v>
+        <v>-2.06873</v>
       </c>
       <c r="M31" t="n">
-        <v>43831706399.65635</v>
+        <v>43831706399.39579</v>
       </c>
       <c r="N31" t="n">
         <v>50000000000</v>
@@ -3420,13 +3420,13 @@
         <v>44454.11143518519</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R31" t="b">
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0.002031330554630409</v>
+        <v>0.002033729368638585</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3489,28 +3489,28 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1.007</v>
+        <v>0.983869</v>
       </c>
       <c r="F32" t="n">
-        <v>4124856473</v>
+        <v>4030455436</v>
       </c>
       <c r="G32" t="n">
         <v>31</v>
       </c>
       <c r="H32" t="n">
-        <v>971487150</v>
+        <v>871339503</v>
       </c>
       <c r="I32" t="n">
-        <v>1.036</v>
+        <v>1.011</v>
       </c>
       <c r="J32" t="n">
-        <v>0.988259</v>
+        <v>0.936868</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.007936769969634438</v>
+        <v>-0.0218399751267605</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.78184</v>
+        <v>-2.13748</v>
       </c>
       <c r="M32" t="n">
         <v>4096537146.540959</v>
@@ -3525,13 +3525,13 @@
         <v>45661.62243055556</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R32" t="b">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.00203238146429213</v>
+        <v>0.002032801505253614</v>
       </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
@@ -3545,7 +3545,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3564,34 +3564,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="F33" t="n">
-        <v>4049207563</v>
+        <v>3956280213</v>
       </c>
       <c r="G33" t="n">
         <v>32</v>
       </c>
       <c r="H33" t="n">
-        <v>54086270</v>
+        <v>59204372</v>
       </c>
       <c r="I33" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="J33" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="K33" t="n">
-        <v>0.00905706</v>
+        <v>-0.03317149284147103</v>
       </c>
       <c r="L33" t="n">
-        <v>0.6329</v>
+        <v>-2.33833</v>
       </c>
       <c r="M33" t="n">
-        <v>2811563721.089555</v>
+        <v>2812142972.624207</v>
       </c>
       <c r="N33" t="n">
-        <v>5254127987.90229</v>
+        <v>5254679247.355583</v>
       </c>
       <c r="O33" t="n">
         <v>8.25</v>
@@ -3600,13 +3600,13 @@
         <v>45457.69225694444</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R33" t="b">
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.001988403831203291</v>
+        <v>0.001988817404521246</v>
       </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
@@ -3620,187 +3620,187 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>bittensor</t>
+          <t>shiba-inu</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>tao</t>
+          <t>shib</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Bittensor</t>
+          <t>Shiba Inu</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>311.83</v>
+        <v>5.69e-06</v>
       </c>
       <c r="F34" t="n">
-        <v>3527202635</v>
+        <v>3351592860</v>
       </c>
       <c r="G34" t="n">
         <v>33</v>
       </c>
       <c r="H34" t="n">
-        <v>339297374</v>
+        <v>144176003</v>
       </c>
       <c r="I34" t="n">
-        <v>325.4</v>
+        <v>5.98e-06</v>
       </c>
       <c r="J34" t="n">
-        <v>300.88</v>
+        <v>5.56e-06</v>
       </c>
       <c r="K34" t="n">
-        <v>-7.60569083252318</v>
+        <v>-2.77763758295e-07</v>
       </c>
       <c r="L34" t="n">
-        <v>-2.38101</v>
+        <v>-4.60362</v>
       </c>
       <c r="M34" t="n">
-        <v>11339645.9251</v>
+        <v>589238967875888.2</v>
       </c>
       <c r="N34" t="n">
-        <v>21000000</v>
+        <v>589496069650408</v>
       </c>
       <c r="O34" t="n">
-        <v>757.6</v>
+        <v>8.616e-05</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>45358.44833333333</v>
+        <v>44496.82980324074</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R34" t="b">
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0.001684942205726474</v>
-      </c>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr"/>
+        <v>0.001630252531100634</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Meme coin</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ecosistema DeFi</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>N/A (token ERC-20)</t>
+        </is>
+      </c>
+      <c r="W34" t="n">
+        <v>2020</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>shibatoken.com</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>Ecosistema meme y DeFi comunitario</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>Token ERC-20 sobre Ethereum</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>Token meme inspirado en Dogecoin, con ecosistema DeFi propio (ShibaSwap).</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>shiba-inu</t>
+          <t>bittensor</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>shib</t>
+          <t>tao</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Shiba Inu</t>
+          <t>Bittensor</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5.96e-06</v>
+        <v>288.23</v>
       </c>
       <c r="F35" t="n">
-        <v>3515289498</v>
+        <v>3268453797</v>
       </c>
       <c r="G35" t="n">
         <v>34</v>
       </c>
       <c r="H35" t="n">
-        <v>135254168</v>
+        <v>348005096</v>
       </c>
       <c r="I35" t="n">
-        <v>6.23e-06</v>
+        <v>311.88</v>
       </c>
       <c r="J35" t="n">
-        <v>5.92e-06</v>
+        <v>278.69</v>
       </c>
       <c r="K35" t="n">
-        <v>-5.4928049595e-08</v>
+        <v>-21.06650862142038</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.91248</v>
+        <v>-6.79133</v>
       </c>
       <c r="M35" t="n">
-        <v>589238968295838.6</v>
+        <v>11339645.9251</v>
       </c>
       <c r="N35" t="n">
-        <v>589496070070358.4</v>
+        <v>21000000</v>
       </c>
       <c r="O35" t="n">
-        <v>8.616e-05</v>
+        <v>757.6</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>44496.82980324074</v>
+        <v>45358.44833333333</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
-        <v>0.001678016639080199</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Meme coin</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Ecosistema DeFi</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>N/A (token ERC-20)</t>
-        </is>
-      </c>
-      <c r="W35" t="n">
-        <v>2020</v>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>shibatoken.com</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>Ecosistema meme y DeFi comunitario</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>Token ERC-20 sobre Ethereum</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>Token meme inspirado en Dogecoin, con ecosistema DeFi propio (ShibaSwap).</t>
-        </is>
-      </c>
+        <v>0.001580953091558853</v>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3819,34 +3819,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.999939</v>
+        <v>0.999923</v>
       </c>
       <c r="F36" t="n">
-        <v>3267611043</v>
+        <v>3254497247</v>
       </c>
       <c r="G36" t="n">
         <v>35</v>
       </c>
       <c r="H36" t="n">
-        <v>892621912</v>
+        <v>945084427</v>
       </c>
       <c r="I36" t="n">
         <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>0.999742</v>
+        <v>0.999736</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.000111259712300082</v>
+        <v>-4.532150067571e-05</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.01113</v>
+        <v>-0.00792</v>
       </c>
       <c r="M36" t="n">
-        <v>3267748267.80673</v>
+        <v>3254747890.046411</v>
       </c>
       <c r="N36" t="n">
-        <v>3256747890.046524</v>
+        <v>3254747890.046411</v>
       </c>
       <c r="O36" t="n">
         <v>1.65</v>
@@ -3855,13 +3855,13 @@
         <v>45686.67436342593</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R36" t="b">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.001534031587372245</v>
+        <v>0.00157267719731481</v>
       </c>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
@@ -3875,7 +3875,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3894,34 +3894,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.06514499999999999</v>
+        <v>0.061385</v>
       </c>
       <c r="F37" t="n">
-        <v>3237405170</v>
+        <v>3053335366</v>
       </c>
       <c r="G37" t="n">
         <v>36</v>
       </c>
       <c r="H37" t="n">
-        <v>13111871</v>
+        <v>13823496</v>
       </c>
       <c r="I37" t="n">
-        <v>0.068983</v>
+        <v>0.06524199999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>0.06469900000000001</v>
+        <v>0.060291</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.001562254340246122</v>
+        <v>-0.003689313612499391</v>
       </c>
       <c r="L37" t="n">
-        <v>-2.34195</v>
+        <v>-5.73558</v>
       </c>
       <c r="M37" t="n">
-        <v>49739045371.25254</v>
+        <v>49741083117.23193</v>
       </c>
       <c r="N37" t="n">
-        <v>98939055665.36623</v>
+        <v>98941038276.2905</v>
       </c>
       <c r="O37" t="n">
         <v>0.891544</v>
@@ -3930,13 +3930,13 @@
         <v>44523.66666666666</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S37" t="n">
-        <v>0.001516471746788659</v>
+        <v>0.001453393101095557</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -3980,68 +3980,68 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>memecore</t>
+          <t>bitway</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>btw</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>MemeCore</t>
+          <t>Bitway</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1.25</v>
+        <v>1.048</v>
       </c>
       <c r="F38" t="n">
-        <v>2855695265</v>
+        <v>2838641352</v>
       </c>
       <c r="G38" t="n">
         <v>37</v>
       </c>
       <c r="H38" t="n">
-        <v>893698</v>
+        <v>23569633</v>
       </c>
       <c r="I38" t="n">
-        <v>1.33</v>
+        <v>1.094</v>
       </c>
       <c r="J38" t="n">
-        <v>1.26</v>
+        <v>0.935707</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.0662498015158246</v>
+        <v>0.087975</v>
       </c>
       <c r="L38" t="n">
-        <v>-5.02005</v>
+        <v>9.20782</v>
       </c>
       <c r="M38" t="n">
-        <v>2277839497.199591</v>
+        <v>2708142280.000001</v>
       </c>
       <c r="N38" t="n">
-        <v>5417413823.773819</v>
+        <v>10000000000</v>
       </c>
       <c r="O38" t="n">
-        <v>5.64</v>
+        <v>1.094</v>
       </c>
       <c r="P38" s="1" t="n">
-        <v>46205.17638888889</v>
+        <v>46289.21423611111</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R38" t="b">
         <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>0.001294569036644318</v>
+        <v>0.001326084779576762</v>
       </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
@@ -4055,68 +4055,68 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>paypal-usd</t>
+          <t>memecore</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>pyusd</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>PayPal USD</t>
+          <t>MemeCore</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.999876</v>
+        <v>1.22</v>
       </c>
       <c r="F39" t="n">
-        <v>2817767263</v>
+        <v>2768666425</v>
       </c>
       <c r="G39" t="n">
         <v>38</v>
       </c>
       <c r="H39" t="n">
-        <v>117187480</v>
+        <v>1077781</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>1.27</v>
       </c>
       <c r="J39" t="n">
-        <v>0.99975</v>
+        <v>1.19</v>
       </c>
       <c r="K39" t="n">
-        <v>-6.1017185474577e-05</v>
+        <v>-0.04265830950945704</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.0061</v>
+        <v>-3.33534</v>
       </c>
       <c r="M39" t="n">
-        <v>2817932111.158792</v>
+        <v>2278209780.488189</v>
       </c>
       <c r="N39" t="n">
-        <v>2817930847.468791</v>
+        <v>5417784107.057606</v>
       </c>
       <c r="O39" t="n">
-        <v>1.021</v>
+        <v>5.64</v>
       </c>
       <c r="P39" s="1" t="n">
-        <v>45222.61454861111</v>
+        <v>46205.17638888889</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001272520024229615</v>
+        <v>0.001284591352075937</v>
       </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
@@ -4130,68 +4130,68 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>tether-gold</t>
+          <t>paypal-usd</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>xaut</t>
+          <t>pyusd</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tether Gold</t>
+          <t>PayPal USD</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4288.64</v>
+        <v>0.999952</v>
       </c>
       <c r="F40" t="n">
-        <v>2671159184</v>
+        <v>2681333732</v>
       </c>
       <c r="G40" t="n">
         <v>39</v>
       </c>
       <c r="H40" t="n">
-        <v>170212198</v>
+        <v>59767782</v>
       </c>
       <c r="I40" t="n">
-        <v>4368.27</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
-        <v>4301.09</v>
+        <v>0.999715</v>
       </c>
       <c r="K40" t="n">
-        <v>-45.86152627207593</v>
+        <v>4.323e-05</v>
       </c>
       <c r="L40" t="n">
-        <v>-1.05806</v>
+        <v>0.00223</v>
       </c>
       <c r="M40" t="n">
-        <v>622823.6595320001</v>
+        <v>2681462176.707304</v>
       </c>
       <c r="N40" t="n">
-        <v>707747.089</v>
+        <v>2681462176.707304</v>
       </c>
       <c r="O40" t="n">
-        <v>5504.62</v>
+        <v>1.021</v>
       </c>
       <c r="P40" s="1" t="n">
-        <v>46050.66666666666</v>
+        <v>45222.61454861111</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R40" t="b">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.00118729108562202</v>
+        <v>0.001232805192078266</v>
       </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
@@ -4205,68 +4205,68 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>bitway</t>
+          <t>tether-gold</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>btw</t>
+          <t>xaut</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Bitway</t>
+          <t>Tether Gold</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.9601150000000001</v>
+        <v>4271.37</v>
       </c>
       <c r="F41" t="n">
-        <v>2599451132</v>
+        <v>2660311611</v>
       </c>
       <c r="G41" t="n">
         <v>40</v>
       </c>
       <c r="H41" t="n">
-        <v>21262194</v>
+        <v>217328082</v>
       </c>
       <c r="I41" t="n">
-        <v>0.96234</v>
+        <v>4301.85</v>
       </c>
       <c r="J41" t="n">
-        <v>0.844931</v>
+        <v>4248.02</v>
       </c>
       <c r="K41" t="n">
-        <v>0.091182</v>
+        <v>-18.37164533468513</v>
       </c>
       <c r="L41" t="n">
-        <v>10.49359</v>
+        <v>-0.43368</v>
       </c>
       <c r="M41" t="n">
-        <v>2708142280.000001</v>
+        <v>622823.6595320001</v>
       </c>
       <c r="N41" t="n">
-        <v>10000000000</v>
+        <v>707747.089</v>
       </c>
       <c r="O41" t="n">
-        <v>0.972034</v>
+        <v>5504.62</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>46286.79398148148</v>
+        <v>46050.66666666666</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.001145604425492068</v>
+        <v>0.001220339586310258</v>
       </c>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
@@ -4280,7 +4280,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4299,28 +4299,28 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>121.4</v>
+        <v>119.04</v>
       </c>
       <c r="F42" t="n">
-        <v>2550230189</v>
+        <v>2499814238</v>
       </c>
       <c r="G42" t="n">
         <v>41</v>
       </c>
       <c r="H42" t="n">
-        <v>32411824</v>
+        <v>39652791</v>
       </c>
       <c r="I42" t="n">
-        <v>125.52</v>
+        <v>121.52</v>
       </c>
       <c r="J42" t="n">
-        <v>120.82</v>
+        <v>117.52</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.9404539534214251</v>
+        <v>-2.843280796039352</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.76872</v>
+        <v>-2.29673</v>
       </c>
       <c r="M42" t="n">
         <v>21000000</v>
@@ -4335,13 +4335,13 @@
         <v>45934.66666666666</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R42" t="b">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.001116990390319048</v>
+        <v>0.001125168552967867</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4407,7 +4407,7 @@
         <v>1.14</v>
       </c>
       <c r="F43" t="n">
-        <v>2509066381</v>
+        <v>2432956202</v>
       </c>
       <c r="G43" t="n">
         <v>42</v>
@@ -4422,31 +4422,31 @@
         <v>1.14</v>
       </c>
       <c r="K43" t="n">
-        <v>0.00010924</v>
+        <v>0.00010526</v>
       </c>
       <c r="L43" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.00925</v>
       </c>
       <c r="M43" t="n">
-        <v>2204477317.470919</v>
+        <v>2137408897.697903</v>
       </c>
       <c r="N43" t="n">
-        <v>2204477317.470919</v>
+        <v>2137408897.697903</v>
       </c>
       <c r="O43" t="n">
         <v>1.14</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>46288.5349537037</v>
+        <v>46289.54166666666</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R43" t="b">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.001093060278903518</v>
+        <v>0.00108552336591946</v>
       </c>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
@@ -4460,7 +4460,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4479,34 +4479,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.999987</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>2430566971</v>
+        <v>2373693267</v>
       </c>
       <c r="G44" t="n">
         <v>43</v>
       </c>
       <c r="H44" t="n">
-        <v>408722228</v>
+        <v>326252990</v>
       </c>
       <c r="I44" t="n">
         <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>0.999723</v>
+        <v>0.999799</v>
       </c>
       <c r="K44" t="n">
-        <v>-8.6788943180593e-05</v>
+        <v>0.00010926</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.00868</v>
+        <v>0.01618</v>
       </c>
       <c r="M44" t="n">
-        <v>2430586212.607239</v>
+        <v>2373469066.207216</v>
       </c>
       <c r="N44" t="n">
-        <v>2420586212.607235</v>
+        <v>2373469066.207212</v>
       </c>
       <c r="O44" t="n">
         <v>1.073</v>
@@ -4515,13 +4515,13 @@
         <v>45652.11518518518</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R44" t="b">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.001047425540072909</v>
+        <v>0.001050381888788535</v>
       </c>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
@@ -4535,68 +4535,68 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>blackrock-usd-institutional-digital-liquidity-fund</t>
+          <t>ondo-finance</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>buidl</t>
+          <t>ondo</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>BlackRock USD Institutional Digital Liquidity Fund</t>
+          <t>Ondo</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>0.484279</v>
       </c>
       <c r="F45" t="n">
-        <v>2280893730</v>
+        <v>2358114181</v>
       </c>
       <c r="G45" t="n">
         <v>44</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>593027601</v>
       </c>
       <c r="I45" t="n">
+        <v>0.470252</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.406139</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.054809</v>
+      </c>
+      <c r="L45" t="n">
+        <v>12.54924</v>
+      </c>
+      <c r="M45" t="n">
+        <v>4869330647</v>
+      </c>
+      <c r="N45" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="P45" s="1" t="n">
+        <v>45641.69166666667</v>
+      </c>
+      <c r="Q45" s="1" t="n">
+        <v>46289.57523148148</v>
+      </c>
+      <c r="R45" t="b">
         <v>1</v>
       </c>
-      <c r="J45" t="n">
-        <v>1</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1.11e-16</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>2280893730.007649</v>
-      </c>
-      <c r="N45" t="n">
-        <v>2280893730.007649</v>
-      </c>
-      <c r="O45" t="n">
-        <v>1</v>
-      </c>
-      <c r="P45" s="1" t="n">
-        <v>45699.87511574074</v>
-      </c>
-      <c r="Q45" s="1" t="n">
-        <v>46288.57835648148</v>
-      </c>
-      <c r="R45" t="b">
-        <v>0</v>
-      </c>
       <c r="S45" t="n">
-        <v>0.0009604147044122856</v>
+        <v>0.00104114387021268</v>
       </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
@@ -4610,68 +4610,68 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ondo-us-dollar-yield</t>
+          <t>blackrock-usd-institutional-digital-liquidity-fund</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>usdy</t>
+          <t>buidl</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Ondo US Dollar Yield</t>
+          <t>BlackRock USD Institutional Digital Liquidity Fund</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>2265296346</v>
+        <v>2290219820</v>
       </c>
       <c r="G46" t="n">
         <v>45</v>
       </c>
       <c r="H46" t="n">
-        <v>2784598</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.000589271372547939</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.05139</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1977425342.111264</v>
+        <v>2290219819.817649</v>
       </c>
       <c r="N46" t="n">
-        <v>1977437874.141553</v>
+        <v>2290219819.817649</v>
       </c>
       <c r="O46" t="n">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>45377.89175925926</v>
+        <v>45699.87511574074</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R46" t="b">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.0009513473426922327</v>
+        <v>0.001000884167678537</v>
       </c>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
@@ -4685,112 +4685,82 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>ondo-us-dollar-yield</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>usdy</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Aave</t>
+          <t>Ondo US Dollar Yield</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>145.91</v>
+        <v>1.15</v>
       </c>
       <c r="F47" t="n">
-        <v>2250997512</v>
+        <v>2268846569</v>
       </c>
       <c r="G47" t="n">
         <v>46</v>
       </c>
       <c r="H47" t="n">
-        <v>379773417</v>
+        <v>5646269</v>
       </c>
       <c r="I47" t="n">
-        <v>154.8</v>
+        <v>1.15</v>
       </c>
       <c r="J47" t="n">
-        <v>140.89</v>
+        <v>1.14</v>
       </c>
       <c r="K47" t="n">
-        <v>1.81</v>
+        <v>-0.000774468384536986</v>
       </c>
       <c r="L47" t="n">
-        <v>1.25921</v>
+        <v>0.03233</v>
       </c>
       <c r="M47" t="n">
-        <v>15429000.22800938</v>
+        <v>1980718587.224123</v>
       </c>
       <c r="N47" t="n">
-        <v>16000000</v>
+        <v>1980723621.969325</v>
       </c>
       <c r="O47" t="n">
-        <v>661.6900000000001</v>
+        <v>1.26</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>44334.55554398148</v>
+        <v>45377.89175925926</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R47" t="b">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0.0009430348782396689</v>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>DeFi</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Préstamos</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>N/A (token de gobernanza)</t>
-        </is>
-      </c>
-      <c r="W47" t="n">
-        <v>2017</v>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>aave.com</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>Préstamos y créditos descentralizados</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>Token ERC-20 sobre Ethereum</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>Pionero en préstamos y créditos flash (flash loans) dentro de DeFi.</t>
-        </is>
-      </c>
+        <v>0.0009882103503721547</v>
+      </c>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4809,28 +4779,28 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.6676609999999999</v>
+        <v>0.684297</v>
       </c>
       <c r="F48" t="n">
-        <v>2203402046</v>
+        <v>2259748669</v>
       </c>
       <c r="G48" t="n">
         <v>47</v>
       </c>
       <c r="H48" t="n">
-        <v>54032578</v>
+        <v>65324506</v>
       </c>
       <c r="I48" t="n">
-        <v>0.696315</v>
+        <v>0.697646</v>
       </c>
       <c r="J48" t="n">
-        <v>0.650689</v>
+        <v>0.644684</v>
       </c>
       <c r="K48" t="n">
-        <v>0.00460571</v>
+        <v>0.01729176</v>
       </c>
       <c r="L48" t="n">
-        <v>0.69462</v>
+        <v>2.50488</v>
       </c>
       <c r="M48" t="n">
         <v>3302294382.53684</v>
@@ -4845,13 +4815,13 @@
         <v>45938.71164351852</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R48" t="b">
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0.0009153657956257848</v>
+        <v>0.0009828155172477162</v>
       </c>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
@@ -4865,7 +4835,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4884,28 +4854,28 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.210498</v>
+        <v>0.21651</v>
       </c>
       <c r="F49" t="n">
-        <v>2124853632</v>
+        <v>2185736780</v>
       </c>
       <c r="G49" t="n">
         <v>48</v>
       </c>
       <c r="H49" t="n">
-        <v>427826210</v>
+        <v>457659961</v>
       </c>
       <c r="I49" t="n">
-        <v>0.220878</v>
+        <v>0.214238</v>
       </c>
       <c r="J49" t="n">
-        <v>0.203656</v>
+        <v>0.199436</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.00015034861664584</v>
+        <v>0.00608209</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.07137</v>
+        <v>3.21791</v>
       </c>
       <c r="M49" t="n">
         <v>10095312500</v>
@@ -4920,13 +4890,13 @@
         <v>45393.21892361111</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R49" t="b">
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>0.0008697025688773468</v>
+        <v>0.0009389282695994172</v>
       </c>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
@@ -4940,143 +4910,173 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ondo-finance</t>
+          <t>aave</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ondo</t>
+          <t>aave</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Ondo</t>
+          <t>Aave</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.430371</v>
+        <v>140.97</v>
       </c>
       <c r="F50" t="n">
-        <v>2094725216</v>
+        <v>2174986020</v>
       </c>
       <c r="G50" t="n">
         <v>49</v>
       </c>
       <c r="H50" t="n">
-        <v>240491377</v>
+        <v>326267479</v>
       </c>
       <c r="I50" t="n">
-        <v>0.446916</v>
+        <v>146.9</v>
       </c>
       <c r="J50" t="n">
-        <v>0.422514</v>
+        <v>135.12</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.002795556637051055</v>
+        <v>-4.943278722712705</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.64538</v>
+        <v>-3.28341</v>
       </c>
       <c r="M50" t="n">
-        <v>4869330647</v>
+        <v>15429020.74517355</v>
       </c>
       <c r="N50" t="n">
-        <v>10000000000</v>
+        <v>16000000</v>
       </c>
       <c r="O50" t="n">
-        <v>2.14</v>
+        <v>661.6900000000001</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>45641.69166666667</v>
+        <v>44334.55554398148</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R50" t="b">
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0.0008521877570393985</v>
-      </c>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
-      <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr"/>
-      <c r="AA50" t="inlineStr"/>
+        <v>0.000932553330749695</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>DeFi</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Préstamos</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>N/A (token de gobernanza)</t>
+        </is>
+      </c>
+      <c r="W50" t="n">
+        <v>2017</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>aave.com</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>Préstamos y créditos descentralizados</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>Token ERC-20 sobre Ethereum</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>Pionero en préstamos y créditos flash (flash loans) dentro de DeFi.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Pepe</t>
+          <t>Morpho</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4.72e-06</v>
+        <v>2.91</v>
       </c>
       <c r="F51" t="n">
-        <v>1986740277</v>
+        <v>2037269448</v>
       </c>
       <c r="G51" t="n">
         <v>50</v>
       </c>
       <c r="H51" t="n">
-        <v>549261212</v>
+        <v>64550994</v>
       </c>
       <c r="I51" t="n">
-        <v>5.06e-06</v>
+        <v>2.75</v>
       </c>
       <c r="J51" t="n">
-        <v>4.68e-06</v>
+        <v>2.49</v>
       </c>
       <c r="K51" t="n">
-        <v>-2.10276760423e-07</v>
+        <v>0.313299</v>
       </c>
       <c r="L51" t="n">
-        <v>-4.26256</v>
+        <v>11.89216</v>
       </c>
       <c r="M51" t="n">
-        <v>420690000000000</v>
+        <v>699408032.7999195</v>
       </c>
       <c r="N51" t="n">
-        <v>420690000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="O51" t="n">
-        <v>2.803e-05</v>
+        <v>4.17</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>45635.35457175926</v>
+        <v>45674.19883101852</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S51" t="n">
-        <v>0.0007894119414134683</v>
+        <v>0.000850890757583392</v>
       </c>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
@@ -5090,248 +5090,248 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>pump-fun</t>
+          <t>polkadot</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>dot</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Pump.fun</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.00420158</v>
+        <v>1.14</v>
       </c>
       <c r="F52" t="n">
-        <v>1960143679</v>
+        <v>1948735881</v>
       </c>
       <c r="G52" t="n">
         <v>51</v>
       </c>
       <c r="H52" t="n">
-        <v>178269348</v>
+        <v>192569027</v>
       </c>
       <c r="I52" t="n">
-        <v>0.00454506</v>
+        <v>1.15</v>
       </c>
       <c r="J52" t="n">
-        <v>0.0041635</v>
+        <v>1.083</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.000320287581018032</v>
+        <v>-0.005984068202869786</v>
       </c>
       <c r="L52" t="n">
-        <v>-7.08308</v>
+        <v>-0.45445</v>
       </c>
       <c r="M52" t="n">
-        <v>466901904548.8473</v>
+        <v>1704257813.2567</v>
       </c>
       <c r="N52" t="n">
-        <v>832406681537.3623</v>
+        <v>1704264406.430411</v>
       </c>
       <c r="O52" t="n">
-        <v>0.00881908</v>
+        <v>54.98</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>45914.36296296296</v>
+        <v>44504.25704861111</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0.0007739503117844977</v>
-      </c>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr"/>
-      <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr"/>
-      <c r="AA52" t="inlineStr"/>
+        <v>0.0007983925085505067</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Layer 0</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Proof of Stake (NPoS)</t>
+        </is>
+      </c>
+      <c r="W52" t="n">
+        <v>2020</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>polkadot.network</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>Interoperabilidad entre blockchains</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Layer 0, relay chain)</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>Permite que blockchains distintas (parachains) se comuniquen entre sí.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>polkadot</t>
+          <t>aster-2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>dot</t>
+          <t>aster</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1.15</v>
+        <v>0.70549</v>
       </c>
       <c r="F53" t="n">
-        <v>1961844140</v>
+        <v>1912221350</v>
       </c>
       <c r="G53" t="n">
         <v>52</v>
       </c>
       <c r="H53" t="n">
-        <v>207619063</v>
+        <v>146322990</v>
       </c>
       <c r="I53" t="n">
-        <v>1.23</v>
+        <v>0.7152579999999999</v>
       </c>
       <c r="J53" t="n">
-        <v>1.15</v>
+        <v>0.6801</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.02755527188789175</v>
+        <v>-0.006181647943094393</v>
       </c>
       <c r="L53" t="n">
-        <v>-2.33799</v>
+        <v>-0.88759</v>
       </c>
       <c r="M53" t="n">
-        <v>1704102123.743917</v>
+        <v>2710487455.649731</v>
       </c>
       <c r="N53" t="n">
-        <v>1704107015.451853</v>
+        <v>7795741639.279309</v>
       </c>
       <c r="O53" t="n">
-        <v>54.98</v>
+        <v>2.41</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>44504.25704861111</v>
+        <v>45924.13766203704</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R53" t="b">
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0.0007749388554388594</v>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>Interoperabilidad</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>Layer 0</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Proof of Stake (NPoS)</t>
-        </is>
-      </c>
-      <c r="W53" t="n">
-        <v>2020</v>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>polkadot.network</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>Interoperabilidad entre blockchains</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Layer 0, relay chain)</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>Permite que blockchains distintas (parachains) se comuniquen entre sí.</t>
-        </is>
-      </c>
+        <v>0.0007767402809636864</v>
+      </c>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>aster-2</t>
+          <t>pax-gold</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>aster</t>
+          <t>paxg</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>PAX Gold</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.712658</v>
+        <v>4267.7</v>
       </c>
       <c r="F54" t="n">
-        <v>1930613228</v>
+        <v>1856037392</v>
       </c>
       <c r="G54" t="n">
         <v>53</v>
       </c>
       <c r="H54" t="n">
-        <v>143167311</v>
+        <v>227214239</v>
       </c>
       <c r="I54" t="n">
-        <v>0.740887</v>
+        <v>4300.04</v>
       </c>
       <c r="J54" t="n">
-        <v>0.708005</v>
+        <v>4242.49</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.01116442953006569</v>
+        <v>-21.90785163517194</v>
       </c>
       <c r="L54" t="n">
-        <v>-1.54243</v>
+        <v>-0.50476</v>
       </c>
       <c r="M54" t="n">
-        <v>2710487455.649731</v>
+        <v>434903.623539</v>
       </c>
       <c r="N54" t="n">
-        <v>7795741639.279309</v>
+        <v>434903.623539</v>
       </c>
       <c r="O54" t="n">
-        <v>2.41</v>
+        <v>5619.09</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>45924.13766203704</v>
+        <v>46050.93814814815</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R54" t="b">
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>0.0007567831200956033</v>
+        <v>0.0007434245622065604</v>
       </c>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
@@ -5345,68 +5345,68 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>pax-gold</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>paxg</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>PAX Gold</t>
+          <t>Pepe</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4287.67</v>
+        <v>4.37e-06</v>
       </c>
       <c r="F55" t="n">
-        <v>1864921106</v>
+        <v>1840327966</v>
       </c>
       <c r="G55" t="n">
         <v>54</v>
       </c>
       <c r="H55" t="n">
-        <v>156503064</v>
+        <v>496628766</v>
       </c>
       <c r="I55" t="n">
-        <v>4366.45</v>
+        <v>4.73e-06</v>
       </c>
       <c r="J55" t="n">
-        <v>4298.37</v>
+        <v>4.22e-06</v>
       </c>
       <c r="K55" t="n">
-        <v>-45.91542975439643</v>
+        <v>-3.52898805786e-07</v>
       </c>
       <c r="L55" t="n">
-        <v>-1.05952</v>
+        <v>-7.4038</v>
       </c>
       <c r="M55" t="n">
-        <v>434903.623539</v>
+        <v>420690000000000</v>
       </c>
       <c r="N55" t="n">
-        <v>434903.623539</v>
+        <v>420690000000000</v>
       </c>
       <c r="O55" t="n">
-        <v>5619.09</v>
+        <v>2.803e-05</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>46050.93814814815</v>
+        <v>45635.35457175926</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0007185937524213934</v>
+        <v>0.0007341092551850813</v>
       </c>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
@@ -5420,68 +5420,68 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>world-liberty-financial</t>
+          <t>pump-fun</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>wlfi</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>World Liberty Financial</t>
+          <t>Pump.fun</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.057758</v>
+        <v>0.00385277</v>
       </c>
       <c r="F56" t="n">
-        <v>1833651673</v>
+        <v>1798093331</v>
       </c>
       <c r="G56" t="n">
         <v>55</v>
       </c>
       <c r="H56" t="n">
-        <v>43170388</v>
+        <v>148366653</v>
       </c>
       <c r="I56" t="n">
-        <v>0.05854</v>
+        <v>0.00420914</v>
       </c>
       <c r="J56" t="n">
-        <v>0.057097</v>
+        <v>0.0037575</v>
       </c>
       <c r="K56" t="n">
-        <v>-6.534036778634001e-05</v>
+        <v>-0.000346574342933239</v>
       </c>
       <c r="L56" t="n">
-        <v>-0.113</v>
+        <v>-8.292</v>
       </c>
       <c r="M56" t="n">
-        <v>31777806194</v>
+        <v>466700999693.5743</v>
       </c>
       <c r="N56" t="n">
-        <v>100000000000</v>
+        <v>832207673323.2832</v>
       </c>
       <c r="O56" t="n">
-        <v>0.331336</v>
+        <v>0.00881908</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>45901.18065972222</v>
+        <v>45914.36296296296</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S56" t="n">
-        <v>0.0007004156233330825</v>
+        <v>0.0007090651452370091</v>
       </c>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
@@ -5495,68 +5495,68 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>world-liberty-financial</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>wlfi</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Morpho</t>
+          <t>World Liberty Financial</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2.6</v>
+        <v>0.054942</v>
       </c>
       <c r="F57" t="n">
-        <v>1815703875</v>
+        <v>1745921284</v>
       </c>
       <c r="G57" t="n">
         <v>56</v>
       </c>
       <c r="H57" t="n">
-        <v>38070094</v>
+        <v>53692296</v>
       </c>
       <c r="I57" t="n">
-        <v>2.71</v>
+        <v>0.057932</v>
       </c>
       <c r="J57" t="n">
-        <v>2.56</v>
+        <v>0.053389</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.01474188022210354</v>
+        <v>-0.002857573217483492</v>
       </c>
       <c r="L57" t="n">
-        <v>-0.56476</v>
+        <v>-4.96231</v>
       </c>
       <c r="M57" t="n">
-        <v>699322574.1099297</v>
+        <v>31777818012</v>
       </c>
       <c r="N57" t="n">
-        <v>1000000000</v>
+        <v>100000000000</v>
       </c>
       <c r="O57" t="n">
-        <v>4.17</v>
+        <v>0.331336</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>45674.19883101852</v>
+        <v>45901.18065972222</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S57" t="n">
-        <v>0.0006899818751773379</v>
+        <v>0.0006781283919944633</v>
       </c>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
@@ -5570,187 +5570,187 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>internet-computer</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>icp</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Sky</t>
+          <t>Internet Computer</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.074221</v>
+        <v>3.05</v>
       </c>
       <c r="F58" t="n">
-        <v>1739729959</v>
+        <v>1698964503</v>
       </c>
       <c r="G58" t="n">
         <v>57</v>
       </c>
       <c r="H58" t="n">
-        <v>32498053</v>
+        <v>104738488</v>
       </c>
       <c r="I58" t="n">
-        <v>0.075257</v>
+        <v>3.14</v>
       </c>
       <c r="J58" t="n">
-        <v>0.066938</v>
+        <v>2.84</v>
       </c>
       <c r="K58" t="n">
-        <v>0.00621626</v>
+        <v>-0.04820574080413698</v>
       </c>
       <c r="L58" t="n">
-        <v>9.14096</v>
+        <v>-1.54971</v>
       </c>
       <c r="M58" t="n">
-        <v>23423997285.19598</v>
+        <v>556899104.8894781</v>
       </c>
       <c r="N58" t="n">
-        <v>23459804203.60596</v>
+        <v>556899104.8894781</v>
       </c>
       <c r="O58" t="n">
-        <v>0.100535</v>
+        <v>700.65</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>45630.09302083333</v>
+        <v>44326.33741898148</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0006458153035483452</v>
-      </c>
-      <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
-      <c r="X58" t="inlineStr"/>
-      <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr"/>
-      <c r="AA58" t="inlineStr"/>
+        <v>0.0006502841644742882</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Infraestructura descentralizada</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Hosting</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Proof of Stake (Chain Key)</t>
+        </is>
+      </c>
+      <c r="W58" t="n">
+        <v>2021</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>internetcomputer.org</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>Hosting descentralizado de aplicaciones</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Layer 1)</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>Busca reemplazar servidores tradicionales con "canisters" en cadena.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>internet-computer</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>icp</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Internet Computer</t>
+          <t>Sky</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3.1</v>
+        <v>0.07137499999999999</v>
       </c>
       <c r="F59" t="n">
-        <v>1728332299</v>
+        <v>1671792596</v>
       </c>
       <c r="G59" t="n">
         <v>58</v>
       </c>
       <c r="H59" t="n">
-        <v>90090819</v>
+        <v>37387940</v>
       </c>
       <c r="I59" t="n">
-        <v>3.17</v>
+        <v>0.07593</v>
       </c>
       <c r="J59" t="n">
-        <v>2.89</v>
+        <v>0.068749</v>
       </c>
       <c r="K59" t="n">
-        <v>0.148767</v>
+        <v>-0.002659009276291313</v>
       </c>
       <c r="L59" t="n">
-        <v>5.0332</v>
+        <v>-3.91437</v>
       </c>
       <c r="M59" t="n">
-        <v>556906568.8330376</v>
+        <v>23422655415.78843</v>
       </c>
       <c r="N59" t="n">
-        <v>556906568.8330376</v>
+        <v>23459804203.60596</v>
       </c>
       <c r="O59" t="n">
-        <v>700.65</v>
+        <v>0.100535</v>
       </c>
       <c r="P59" s="1" t="n">
-        <v>44326.33741898148</v>
+        <v>45630.09302083333</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R59" t="b">
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>0.0006391894035908794</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Infraestructura descentralizada</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Hosting</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Proof of Stake (Chain Key)</t>
-        </is>
-      </c>
-      <c r="W59" t="n">
-        <v>2021</v>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>internetcomputer.org</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>Hosting descentralizado de aplicaciones</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Layer 1)</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>Busca reemplazar servidores tradicionales con "canisters" en cadena.</t>
-        </is>
-      </c>
+        <v>0.0006341718853837553</v>
+      </c>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5769,31 +5769,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.447125</v>
+        <v>0.423671</v>
       </c>
       <c r="F60" t="n">
-        <v>1630975252</v>
+        <v>1546541856</v>
       </c>
       <c r="G60" t="n">
         <v>59</v>
       </c>
       <c r="H60" t="n">
-        <v>368038301</v>
+        <v>442319003</v>
       </c>
       <c r="I60" t="n">
-        <v>0.478425</v>
+        <v>0.448592</v>
       </c>
       <c r="J60" t="n">
-        <v>0.444828</v>
+        <v>0.400932</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.01147458947688723</v>
+        <v>-0.02246015873684787</v>
       </c>
       <c r="L60" t="n">
-        <v>-2.5021</v>
+        <v>-4.94776</v>
       </c>
       <c r="M60" t="n">
-        <v>3648371573.354076</v>
+        <v>3650340456.196745</v>
       </c>
       <c r="N60" t="n">
         <v>10000000000</v>
@@ -5805,13 +5805,13 @@
         <v>45360.67409722223</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S60" t="n">
-        <v>0.0005825919920541</v>
+        <v>0.000559901246993311</v>
       </c>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
@@ -5825,7 +5825,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5844,28 +5844,28 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1.73e-06</v>
+        <v>1.71e-06</v>
       </c>
       <c r="F61" t="n">
-        <v>1552311309</v>
+        <v>1537643253</v>
       </c>
       <c r="G61" t="n">
         <v>60</v>
       </c>
       <c r="H61" t="n">
-        <v>10763223</v>
+        <v>11872337</v>
       </c>
       <c r="I61" t="n">
-        <v>1.74e-06</v>
+        <v>1.73e-06</v>
       </c>
       <c r="J61" t="n">
-        <v>1.71e-06</v>
+        <v>1.7e-06</v>
       </c>
       <c r="K61" t="n">
-        <v>-1.110989529e-09</v>
+        <v>-1.6416876349e-08</v>
       </c>
       <c r="L61" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-1.00637</v>
       </c>
       <c r="M61" t="n">
         <v>898232728634017.2</v>
@@ -5880,13 +5880,13 @@
         <v>45629.67800925926</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R61" t="b">
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>0.0005368616038360107</v>
+        <v>0.0005546245921360772</v>
       </c>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
@@ -5900,68 +5900,68 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>arb</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Arbitrum</t>
+          <t>USDD</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.229164</v>
+        <v>0.999234</v>
       </c>
       <c r="F62" t="n">
-        <v>1554187273</v>
+        <v>1521430844</v>
       </c>
       <c r="G62" t="n">
         <v>61</v>
       </c>
       <c r="H62" t="n">
-        <v>530985295</v>
+        <v>1396580</v>
       </c>
       <c r="I62" t="n">
-        <v>0.254366</v>
+        <v>0.9995309999999999</v>
       </c>
       <c r="J62" t="n">
-        <v>0.211434</v>
+        <v>0.997431</v>
       </c>
       <c r="K62" t="n">
-        <v>0.01161925</v>
+        <v>0.00040721</v>
       </c>
       <c r="L62" t="n">
-        <v>5.34108</v>
+        <v>0.04515</v>
       </c>
       <c r="M62" t="n">
-        <v>6785574605</v>
+        <v>1522596897</v>
       </c>
       <c r="N62" t="n">
-        <v>10000000000</v>
+        <v>1530643977</v>
       </c>
       <c r="O62" t="n">
-        <v>2.39</v>
+        <v>1.24</v>
       </c>
       <c r="P62" s="1" t="n">
-        <v>45303.18748842592</v>
+        <v>46212.39942129629</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R62" t="b">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0.0005379521741625345</v>
+        <v>0.0005450110284455394</v>
       </c>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
@@ -5975,143 +5975,173 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>venice-token</t>
+          <t>ethereum-classic</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>vvv</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Venice Token</t>
+          <t>Ethereum Classic</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>32.03</v>
+        <v>9.51</v>
       </c>
       <c r="F63" t="n">
-        <v>1541518983</v>
+        <v>1504422259</v>
       </c>
       <c r="G63" t="n">
         <v>62</v>
       </c>
       <c r="H63" t="n">
-        <v>66835175</v>
+        <v>163869086</v>
       </c>
       <c r="I63" t="n">
-        <v>33.44</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J63" t="n">
-        <v>30.93</v>
+        <v>8.65</v>
       </c>
       <c r="K63" t="n">
-        <v>0.3302</v>
+        <v>0.09289</v>
       </c>
       <c r="L63" t="n">
-        <v>1.04149</v>
+        <v>0.9805199999999999</v>
       </c>
       <c r="M63" t="n">
-        <v>48125289.11596377</v>
+        <v>158269190.6970681</v>
       </c>
       <c r="N63" t="n">
-        <v>81032627.41462347</v>
+        <v>158269579.3562681</v>
       </c>
       <c r="O63" t="n">
-        <v>34.53</v>
+        <v>167.09</v>
       </c>
       <c r="P63" s="1" t="n">
-        <v>46286.34548611111</v>
+        <v>44322.44053240741</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R63" t="b">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0.0005305876079119039</v>
-      </c>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
-      <c r="X63" t="inlineStr"/>
-      <c r="Y63" t="inlineStr"/>
-      <c r="Z63" t="inlineStr"/>
-      <c r="AA63" t="inlineStr"/>
+        <v>0.0005349253517775363</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Plataforma de contratos inteligentes</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Layer 1</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Proof of Work</t>
+        </is>
+      </c>
+      <c r="W63" t="n">
+        <v>2016</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>ethereumclassic.org</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>Contratos inteligentes (cadena original)</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>Blockchain propia (fork de Ethereum)</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>Mantiene la cadena original de Ethereum tras la bifurcación de 2016.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>arb</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>USDD</t>
+          <t>Arbitrum</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.998815</v>
+        <v>0.218005</v>
       </c>
       <c r="F64" t="n">
-        <v>1511831977</v>
+        <v>1479287884</v>
       </c>
       <c r="G64" t="n">
         <v>63</v>
       </c>
       <c r="H64" t="n">
-        <v>2346046</v>
+        <v>325788139</v>
       </c>
       <c r="I64" t="n">
-        <v>0.999157</v>
+        <v>0.229675</v>
       </c>
       <c r="J64" t="n">
-        <v>0.997605</v>
+        <v>0.210805</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.1427141663977e-05</v>
+        <v>-0.01116477426095458</v>
       </c>
       <c r="L64" t="n">
-        <v>-0.00215</v>
+        <v>-4.93658</v>
       </c>
       <c r="M64" t="n">
-        <v>1513617332</v>
+        <v>6785574605</v>
       </c>
       <c r="N64" t="n">
-        <v>1513617332</v>
+        <v>10000000000</v>
       </c>
       <c r="O64" t="n">
-        <v>1.24</v>
+        <v>2.39</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>46212.39942129629</v>
+        <v>45303.18748842592</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0005133294047550554</v>
+        <v>0.0005200212795397609</v>
       </c>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
@@ -6125,173 +6155,143 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ethereum-classic</t>
+          <t>united-stables</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>u</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Ethereum Classic</t>
+          <t>United Stables</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>9.42</v>
+        <v>0.999204</v>
       </c>
       <c r="F65" t="n">
-        <v>1491549131</v>
+        <v>1465742252</v>
       </c>
       <c r="G65" t="n">
         <v>64</v>
       </c>
       <c r="H65" t="n">
-        <v>135241381</v>
+        <v>192240310</v>
       </c>
       <c r="I65" t="n">
-        <v>9.66</v>
+        <v>0.999577</v>
       </c>
       <c r="J65" t="n">
-        <v>8.84</v>
+        <v>0.998874</v>
       </c>
       <c r="K65" t="n">
-        <v>0.368</v>
+        <v>-7.0129395513e-07</v>
       </c>
       <c r="L65" t="n">
-        <v>4.06515</v>
+        <v>-0.00393</v>
       </c>
       <c r="M65" t="n">
-        <v>158258655.0495532</v>
+        <v>1466909391.63</v>
       </c>
       <c r="N65" t="n">
-        <v>158259070.0255532</v>
+        <v>1466909391.63</v>
       </c>
       <c r="O65" t="n">
-        <v>167.09</v>
+        <v>1.008</v>
       </c>
       <c r="P65" s="1" t="n">
-        <v>44322.44053240741</v>
+        <v>46058.54591435185</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R65" t="b">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0.0005015382030128835</v>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Plataforma de contratos inteligentes</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Layer 1</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Proof of Work</t>
-        </is>
-      </c>
-      <c r="W65" t="n">
-        <v>2016</v>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>ethereumclassic.org</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>Contratos inteligentes (cadena original)</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>Blockchain propia (fork de Ethereum)</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>Mantiene la cadena original de Ethereum tras la bifurcación de 2016.</t>
-        </is>
-      </c>
+        <v>0.000511989049661981</v>
+      </c>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr"/>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>bitget-token</t>
+          <t>spiko-amundi-overnight-swap-fund-eur</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>bgb</t>
+          <t>eursafo</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Bitget Token</t>
+          <t>Spiko Amundi Overnight Swap Fund (EUR)</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2.08</v>
+        <v>1.15</v>
       </c>
       <c r="F66" t="n">
-        <v>1453173800</v>
+        <v>1455025954</v>
       </c>
       <c r="G66" t="n">
         <v>65</v>
       </c>
       <c r="H66" t="n">
-        <v>14819720</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>2.14</v>
+        <v>1.16</v>
       </c>
       <c r="J66" t="n">
-        <v>2.06</v>
+        <v>1.15</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.02948212635753444</v>
+        <v>-0.003791863830702846</v>
       </c>
       <c r="L66" t="n">
-        <v>-1.4001</v>
+        <v>-0.32807</v>
       </c>
       <c r="M66" t="n">
-        <v>699992029.6481038</v>
+        <v>1263010543.63882</v>
       </c>
       <c r="N66" t="n">
-        <v>910920874.6481038</v>
+        <v>1263010543.63882</v>
       </c>
       <c r="O66" t="n">
-        <v>8.449999999999999</v>
+        <v>1.18</v>
       </c>
       <c r="P66" s="1" t="n">
-        <v>45653.15375</v>
+        <v>46255.48263888889</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R66" t="b">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0.0004792291409737777</v>
+        <v>0.0005056345459389512</v>
       </c>
       <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr"/>
@@ -6305,68 +6305,68 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>spiko-amundi-overnight-swap-fund-eur</t>
+          <t>venice-token</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>eursafo</t>
+          <t>vvv</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Spiko Amundi Overnight Swap Fund (EUR)</t>
+          <t>Venice Token</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1.16</v>
+        <v>29.75</v>
       </c>
       <c r="F67" t="n">
-        <v>1444759933</v>
+        <v>1431958745</v>
       </c>
       <c r="G67" t="n">
         <v>66</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>68957545</v>
       </c>
       <c r="I67" t="n">
-        <v>1.16</v>
+        <v>31.78</v>
       </c>
       <c r="J67" t="n">
-        <v>1.16</v>
+        <v>28.51</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.004910982889112736</v>
+        <v>-2.290645359558955</v>
       </c>
       <c r="L67" t="n">
-        <v>-0.42309</v>
+        <v>-7.17827</v>
       </c>
       <c r="M67" t="n">
-        <v>1249985019.14243</v>
+        <v>48134255.57614676</v>
       </c>
       <c r="N67" t="n">
-        <v>1249985019.14243</v>
+        <v>81038958.6290253</v>
       </c>
       <c r="O67" t="n">
-        <v>1.18</v>
+        <v>34.53</v>
       </c>
       <c r="P67" s="1" t="n">
-        <v>46255.48263888889</v>
+        <v>46286.34548611111</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S67" t="n">
-        <v>0.0004743378351270142</v>
+        <v>0.0004919562527942097</v>
       </c>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
@@ -6380,68 +6380,68 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>united-stables</t>
+          <t>bitget-token</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>bgb</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>United Stables</t>
+          <t>Bitget Token</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.999157</v>
+        <v>2.04</v>
       </c>
       <c r="F68" t="n">
-        <v>1418449542</v>
+        <v>1431359067</v>
       </c>
       <c r="G68" t="n">
         <v>67</v>
       </c>
       <c r="H68" t="n">
-        <v>186741192</v>
+        <v>14513852</v>
       </c>
       <c r="I68" t="n">
-        <v>0.999781</v>
+        <v>2.08</v>
       </c>
       <c r="J68" t="n">
-        <v>0.999009</v>
+        <v>2</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.000303821891072142</v>
+        <v>-0.03152185663063145</v>
       </c>
       <c r="L68" t="n">
-        <v>-0.0304</v>
+        <v>-1.51287</v>
       </c>
       <c r="M68" t="n">
-        <v>1419429007.8</v>
+        <v>699992029.6481038</v>
       </c>
       <c r="N68" t="n">
-        <v>1419429007.8</v>
+        <v>910920874.6481038</v>
       </c>
       <c r="O68" t="n">
-        <v>1.008</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="P68" s="1" t="n">
-        <v>46058.54591435185</v>
+        <v>45653.15375</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R68" t="b">
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0.0004590425886810063</v>
+        <v>0.0004916006583451174</v>
       </c>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
@@ -6455,7 +6455,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6474,28 +6474,28 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.999945</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>1417710803</v>
+        <v>1418449056</v>
       </c>
       <c r="G69" t="n">
         <v>68</v>
       </c>
       <c r="H69" t="n">
-        <v>74197974</v>
+        <v>20026880</v>
       </c>
       <c r="I69" t="n">
         <v>1.001</v>
       </c>
       <c r="J69" t="n">
-        <v>0.999722</v>
+        <v>0.999789</v>
       </c>
       <c r="K69" t="n">
-        <v>3.166e-05</v>
+        <v>7.656999999999999e-05</v>
       </c>
       <c r="L69" t="n">
-        <v>0.00317</v>
+        <v>0.01655</v>
       </c>
       <c r="M69" t="n">
         <v>1417780805.97</v>
@@ -6510,13 +6510,13 @@
         <v>46092.00303240741</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R69" t="b">
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>0.0004586131311687907</v>
+        <v>0.0004839453362400531</v>
       </c>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
@@ -6530,7 +6530,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6549,28 +6549,28 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.995795</v>
+        <v>0.995592</v>
       </c>
       <c r="F70" t="n">
-        <v>1371639437</v>
+        <v>1371327861</v>
       </c>
       <c r="G70" t="n">
         <v>69</v>
       </c>
       <c r="H70" t="n">
-        <v>323560</v>
+        <v>412081</v>
       </c>
       <c r="I70" t="n">
-        <v>0.9963649999999999</v>
+        <v>0.996672</v>
       </c>
       <c r="J70" t="n">
-        <v>0.995093</v>
+        <v>0.993875</v>
       </c>
       <c r="K70" t="n">
-        <v>0.00026005</v>
+        <v>-0.000222884782159927</v>
       </c>
       <c r="L70" t="n">
-        <v>0.02612</v>
+        <v>-0.02264</v>
       </c>
       <c r="M70" t="n">
         <v>1377398957.226253</v>
@@ -6585,13 +6585,13 @@
         <v>45785.55951388889</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R70" t="b">
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>0.0004318300667485687</v>
+        <v>0.0004560036152221125</v>
       </c>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
@@ -6605,68 +6605,68 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>lighter</t>
+          <t>bfusd</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>lit</t>
+          <t>bfusd</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Lighter</t>
+          <t>BFUSD</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5.4</v>
+        <v>0.999628</v>
       </c>
       <c r="F71" t="n">
-        <v>1347735457</v>
+        <v>1319508692</v>
       </c>
       <c r="G71" t="n">
         <v>70</v>
       </c>
       <c r="H71" t="n">
-        <v>124167092</v>
+        <v>4065721</v>
       </c>
       <c r="I71" t="n">
-        <v>5.31</v>
+        <v>0.9999209999999999</v>
       </c>
       <c r="J71" t="n">
-        <v>4.64</v>
+        <v>0.999528</v>
       </c>
       <c r="K71" t="n">
-        <v>0.666084</v>
+        <v>-0.000132570629598927</v>
       </c>
       <c r="L71" t="n">
-        <v>14.07638</v>
+        <v>-0.00352</v>
       </c>
       <c r="M71" t="n">
-        <v>250000000</v>
+        <v>1320000000</v>
       </c>
       <c r="N71" t="n">
-        <v>1000000000</v>
+        <v>1320000000</v>
       </c>
       <c r="O71" t="n">
-        <v>7.86</v>
+        <v>1.007</v>
       </c>
       <c r="P71" s="1" t="n">
-        <v>46021.04538194444</v>
+        <v>45940.56990740741</v>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>0.0004179337599570639</v>
+        <v>0.0004252761100393701</v>
       </c>
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
@@ -6680,68 +6680,68 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>bfusd</t>
+          <t>lighter</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>bfusd</t>
+          <t>lit</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>BFUSD</t>
+          <t>Lighter</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9996390000000001</v>
+        <v>5.21</v>
       </c>
       <c r="F72" t="n">
-        <v>1319687604</v>
+        <v>1302813360</v>
       </c>
       <c r="G72" t="n">
         <v>71</v>
       </c>
       <c r="H72" t="n">
-        <v>8670377</v>
+        <v>149894014</v>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>5.54</v>
       </c>
       <c r="J72" t="n">
-        <v>0.9995849999999999</v>
+        <v>4.92</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.00010823724121567</v>
+        <v>-0.114789701572211</v>
       </c>
       <c r="L72" t="n">
-        <v>-0.01083</v>
+        <v>-2.44837</v>
       </c>
       <c r="M72" t="n">
-        <v>1320000000</v>
+        <v>250000000</v>
       </c>
       <c r="N72" t="n">
-        <v>1320000000</v>
+        <v>1000000000</v>
       </c>
       <c r="O72" t="n">
-        <v>1.007</v>
+        <v>7.86</v>
       </c>
       <c r="P72" s="1" t="n">
-        <v>45940.56990740741</v>
+        <v>46021.04538194444</v>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R72" t="b">
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>0.0004016284597463448</v>
+        <v>0.0004153761847712207</v>
       </c>
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
@@ -6755,143 +6755,173 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>gatechain-token</t>
+          <t>quant-network</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>gt</t>
+          <t>qnt</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>10.84</v>
+        <v>77.31</v>
       </c>
       <c r="F73" t="n">
-        <v>1155932691</v>
+        <v>1124461003</v>
       </c>
       <c r="G73" t="n">
         <v>72</v>
       </c>
       <c r="H73" t="n">
-        <v>1638378</v>
+        <v>14349702</v>
       </c>
       <c r="I73" t="n">
-        <v>11.23</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="J73" t="n">
-        <v>10.82</v>
+        <v>69.78</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.1133170312000562</v>
+        <v>3.41</v>
       </c>
       <c r="L73" t="n">
-        <v>-1.03465</v>
+        <v>4.85594</v>
       </c>
       <c r="M73" t="n">
-        <v>106638072.8025264</v>
+        <v>14544176.16408117</v>
       </c>
       <c r="N73" t="n">
-        <v>118889344.1049307</v>
+        <v>14612493</v>
       </c>
       <c r="O73" t="n">
-        <v>25.38</v>
+        <v>427.42</v>
       </c>
       <c r="P73" s="1" t="n">
-        <v>45682.66666666666</v>
+        <v>44450.05208333334</v>
       </c>
       <c r="Q73" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R73" t="b">
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0.0003064314042909701</v>
-      </c>
-      <c r="T73" t="inlineStr"/>
-      <c r="U73" t="inlineStr"/>
-      <c r="V73" t="inlineStr"/>
-      <c r="W73" t="inlineStr"/>
-      <c r="X73" t="inlineStr"/>
-      <c r="Y73" t="inlineStr"/>
-      <c r="Z73" t="inlineStr"/>
-      <c r="AA73" t="inlineStr"/>
+        <v>0.0003096175807675203</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Infraestructura empresarial</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>N/A (token ERC-20)</t>
+        </is>
+      </c>
+      <c r="W73" t="n">
+        <v>2018</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>quant.network</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>Interoperabilidad entre redes empresariales</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>Token ERC-20 sobre Ethereum</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>Su tecnología Overledger busca conectar múltiples blockchains y redes existentes.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>akedo</t>
+          <t>gatechain-token</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ake</t>
+          <t>gt</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Akedo</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.050532</v>
+        <v>10.56</v>
       </c>
       <c r="F74" t="n">
-        <v>1144411799</v>
+        <v>1125588745</v>
       </c>
       <c r="G74" t="n">
         <v>73</v>
       </c>
       <c r="H74" t="n">
-        <v>47864165</v>
+        <v>3793329</v>
       </c>
       <c r="I74" t="n">
-        <v>0.053668</v>
+        <v>10.9</v>
       </c>
       <c r="J74" t="n">
-        <v>0.04016857</v>
+        <v>10.38</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.002711219477506105</v>
+        <v>-0.2992864443187386</v>
       </c>
       <c r="L74" t="n">
-        <v>-5.09217</v>
+        <v>-2.71405</v>
       </c>
       <c r="M74" t="n">
-        <v>22796250000</v>
+        <v>106639170.2071135</v>
       </c>
       <c r="N74" t="n">
-        <v>100000000000</v>
+        <v>118890463.1038794</v>
       </c>
       <c r="O74" t="n">
-        <v>0.146656</v>
+        <v>25.38</v>
       </c>
       <c r="P74" s="1" t="n">
-        <v>46285.43993055556</v>
+        <v>45682.66666666666</v>
       </c>
       <c r="Q74" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>0.0002997338648124484</v>
+        <v>0.0003102863043078341</v>
       </c>
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
@@ -6905,7 +6935,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6924,34 +6954,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.106738</v>
+        <v>0.104148</v>
       </c>
       <c r="F75" t="n">
-        <v>1144285758</v>
+        <v>1106038183</v>
       </c>
       <c r="G75" t="n">
         <v>74</v>
       </c>
       <c r="H75" t="n">
-        <v>107188421</v>
+        <v>93832289</v>
       </c>
       <c r="I75" t="n">
-        <v>0.11333</v>
+        <v>0.107051</v>
       </c>
       <c r="J75" t="n">
-        <v>0.106356</v>
+        <v>0.100043</v>
       </c>
       <c r="K75" t="n">
-        <v>-0.00185853209138287</v>
+        <v>-0.002443803701124916</v>
       </c>
       <c r="L75" t="n">
-        <v>-1.7114</v>
+        <v>-2.15828</v>
       </c>
       <c r="M75" t="n">
-        <v>10719336659.25645</v>
+        <v>10619918238.50136</v>
       </c>
       <c r="N75" t="n">
-        <v>10719336659.25645</v>
+        <v>10619918238.50136</v>
       </c>
       <c r="O75" t="n">
         <v>1.29</v>
@@ -6960,13 +6990,13 @@
         <v>45364.45493055556</v>
       </c>
       <c r="Q75" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R75" t="b">
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>0.0002996605923112035</v>
+        <v>0.000298693297187621</v>
       </c>
       <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr"/>
@@ -6980,7 +7010,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6999,34 +7029,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.04096166</v>
+        <v>0.03898802</v>
       </c>
       <c r="F76" t="n">
-        <v>1135099777</v>
+        <v>1080689406</v>
       </c>
       <c r="G76" t="n">
         <v>75</v>
       </c>
       <c r="H76" t="n">
-        <v>16983891</v>
+        <v>18606938</v>
       </c>
       <c r="I76" t="n">
-        <v>0.04277877</v>
+        <v>0.04100133</v>
       </c>
       <c r="J76" t="n">
-        <v>0.04091753</v>
+        <v>0.03807561</v>
       </c>
       <c r="K76" t="n">
-        <v>-0.000935338803778413</v>
+        <v>-0.001977854268385787</v>
       </c>
       <c r="L76" t="n">
-        <v>-2.23247</v>
+        <v>-4.83024</v>
       </c>
       <c r="M76" t="n">
-        <v>27715909912.88878</v>
+        <v>27718500422.43598</v>
       </c>
       <c r="N76" t="n">
-        <v>27716892547.28106</v>
+        <v>27718779366.30129</v>
       </c>
       <c r="O76" t="n">
         <v>0.207411</v>
@@ -7035,13 +7065,13 @@
         <v>45504.69498842592</v>
       </c>
       <c r="Q76" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0002943204267757181</v>
+        <v>0.0002836620897855169</v>
       </c>
       <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr"/>
@@ -7055,95 +7085,95 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>quant-network</t>
+          <t>kucoin-shares</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>qnt</t>
+          <t>kcs</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>KuCoin</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>73.90000000000001</v>
+        <v>7.22</v>
       </c>
       <c r="F77" t="n">
-        <v>1075963068</v>
+        <v>990443671</v>
       </c>
       <c r="G77" t="n">
         <v>76</v>
       </c>
       <c r="H77" t="n">
-        <v>16743469</v>
+        <v>9745795</v>
       </c>
       <c r="I77" t="n">
-        <v>76.31999999999999</v>
+        <v>7.28</v>
       </c>
       <c r="J77" t="n">
-        <v>71.09</v>
+        <v>7.1</v>
       </c>
       <c r="K77" t="n">
-        <v>1.53</v>
+        <v>-0.03072494057700936</v>
       </c>
       <c r="L77" t="n">
-        <v>2.10929</v>
+        <v>-0.30756</v>
       </c>
       <c r="M77" t="n">
-        <v>14544176.16408117</v>
+        <v>137155021.2773955</v>
       </c>
       <c r="N77" t="n">
-        <v>14612493</v>
+        <v>142155021.2773955</v>
       </c>
       <c r="O77" t="n">
-        <v>427.42</v>
+        <v>28.83</v>
       </c>
       <c r="P77" s="1" t="n">
-        <v>44450.05208333334</v>
+        <v>44531.29832175926</v>
       </c>
       <c r="Q77" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R77" t="b">
         <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0002599419738610177</v>
+        <v>0.0002301485668277694</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>Interoperabilidad</t>
+          <t>Token de exchange</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>Infraestructura empresarial</t>
+          <t>Utilidad</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>N/A (token ERC-20)</t>
+          <t>N/A (token de exchange)</t>
         </is>
       </c>
       <c r="W77" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>quant.network</t>
+          <t>kucoin.com</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>Interoperabilidad entre redes empresariales</t>
+          <t>Beneficios en el exchange KuCoin</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
@@ -7153,75 +7183,75 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>Su tecnología Overledger busca conectar múltiples blockchains y redes existentes.</t>
+          <t>Otorga descuentos en comisiones dentro del exchange KuCoin.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>pi-network</t>
+          <t>blockchain-capital</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>pi</t>
+          <t>bcap</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Pi Network</t>
+          <t>Blockchain Capital</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.090327</v>
+        <v>107.53</v>
       </c>
       <c r="F78" t="n">
-        <v>1015710229</v>
+        <v>979825296</v>
       </c>
       <c r="G78" t="n">
         <v>77</v>
       </c>
       <c r="H78" t="n">
-        <v>7674560</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>0.092358</v>
+        <v>107.53</v>
       </c>
       <c r="J78" t="n">
-        <v>0.088785</v>
+        <v>107.53</v>
       </c>
       <c r="K78" t="n">
-        <v>0.00033866</v>
+        <v>1.4211e-14</v>
       </c>
       <c r="L78" t="n">
-        <v>0.37634</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>11243022455.381</v>
+        <v>9112111</v>
       </c>
       <c r="N78" t="n">
-        <v>17296957623.66307</v>
+        <v>9112111</v>
       </c>
       <c r="O78" t="n">
-        <v>2.99</v>
+        <v>107.53</v>
       </c>
       <c r="P78" s="1" t="n">
-        <v>45714.36184027778</v>
+        <v>46287.17361111111</v>
       </c>
       <c r="Q78" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R78" t="b">
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>0.0002249146714702384</v>
+        <v>0.0002238521290588657</v>
       </c>
       <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr"/>
@@ -7235,7 +7265,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7254,34 +7284,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.299981</v>
+        <v>0.294776</v>
       </c>
       <c r="F79" t="n">
-        <v>995497410</v>
+        <v>978471567</v>
       </c>
       <c r="G79" t="n">
         <v>78</v>
       </c>
       <c r="H79" t="n">
-        <v>88093803</v>
+        <v>101687450</v>
       </c>
       <c r="I79" t="n">
-        <v>0.305864</v>
+        <v>0.300785</v>
       </c>
       <c r="J79" t="n">
-        <v>0.288725</v>
+        <v>0.276615</v>
       </c>
       <c r="K79" t="n">
-        <v>0.00581027</v>
+        <v>-0.005983646650502994</v>
       </c>
       <c r="L79" t="n">
-        <v>1.97514</v>
+        <v>-1.95707</v>
       </c>
       <c r="M79" t="n">
         <v>3319369204.37</v>
       </c>
       <c r="N79" t="n">
-        <v>6861486697.52717</v>
+        <v>6861486685.686895</v>
       </c>
       <c r="O79" t="n">
         <v>2</v>
@@ -7290,13 +7320,13 @@
         <v>45322.29359953704</v>
       </c>
       <c r="Q79" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R79" t="b">
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0002131641791277433</v>
+        <v>0.0002230494007313711</v>
       </c>
       <c r="T79" t="inlineStr"/>
       <c r="U79" t="inlineStr"/>
@@ -7310,278 +7340,248 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>kucoin-shares</t>
+          <t>algorand</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>kcs</t>
+          <t>algo</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>KuCoin</t>
+          <t>Algorand</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>7.25</v>
+        <v>0.108044</v>
       </c>
       <c r="F80" t="n">
-        <v>994089775</v>
+        <v>978437246</v>
       </c>
       <c r="G80" t="n">
         <v>79</v>
       </c>
       <c r="H80" t="n">
-        <v>29298412</v>
+        <v>48005860</v>
       </c>
       <c r="I80" t="n">
-        <v>7.48</v>
+        <v>0.109247</v>
       </c>
       <c r="J80" t="n">
-        <v>7.18</v>
+        <v>0.103017</v>
       </c>
       <c r="K80" t="n">
-        <v>-0.1272167778339623</v>
+        <v>-0.0006422515543882961</v>
       </c>
       <c r="L80" t="n">
-        <v>-1.72493</v>
+        <v>-0.21947</v>
       </c>
       <c r="M80" t="n">
-        <v>137155021.2773955</v>
+        <v>9055912745.559528</v>
       </c>
       <c r="N80" t="n">
-        <v>142155021.2773955</v>
+        <v>9055945838.232386</v>
       </c>
       <c r="O80" t="n">
-        <v>28.83</v>
+        <v>3.56</v>
       </c>
       <c r="P80" s="1" t="n">
-        <v>44531.29832175926</v>
+        <v>43636.28563657407</v>
       </c>
       <c r="Q80" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R80" t="b">
         <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>0.0002123458665366828</v>
+        <v>0.0002230290492142448</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>Token de exchange</t>
+          <t>Plataforma de contratos inteligentes</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>Utilidad</t>
+          <t>Layer 1</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>N/A (token de exchange)</t>
+          <t>Pure Proof of Stake</t>
         </is>
       </c>
       <c r="W80" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>kucoin.com</t>
+          <t>algorand.com</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>Beneficios en el exchange KuCoin</t>
+          <t>Contratos inteligentes de alta eficiencia</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>Token ERC-20 sobre Ethereum</t>
+          <t>Blockchain propia (Layer 1)</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>Otorga descuentos en comisiones dentro del exchange KuCoin.</t>
+          <t>Fundada por Silvio Micali, ganador del Premio Turing.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>algorand</t>
+          <t>pi-network</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>algo</t>
+          <t>pi</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Algorand</t>
+          <t>Pi Network</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.108912</v>
+        <v>0.086727</v>
       </c>
       <c r="F81" t="n">
-        <v>983516897</v>
+        <v>975075397</v>
       </c>
       <c r="G81" t="n">
         <v>80</v>
       </c>
       <c r="H81" t="n">
-        <v>54321051</v>
+        <v>8830526</v>
       </c>
       <c r="I81" t="n">
-        <v>0.114624</v>
+        <v>0.09050800000000001</v>
       </c>
       <c r="J81" t="n">
-        <v>0.108881</v>
+        <v>0.08605400000000001</v>
       </c>
       <c r="K81" t="n">
-        <v>-0.001904373624831854</v>
+        <v>-0.003643346247182114</v>
       </c>
       <c r="L81" t="n">
-        <v>-1.7185</v>
+        <v>-4.01879</v>
       </c>
       <c r="M81" t="n">
-        <v>9042752944.706263</v>
+        <v>11243022455.381</v>
       </c>
       <c r="N81" t="n">
-        <v>9055738958.909975</v>
+        <v>17296957623.66307</v>
       </c>
       <c r="O81" t="n">
-        <v>3.56</v>
+        <v>2.99</v>
       </c>
       <c r="P81" s="1" t="n">
-        <v>43636.28563657407</v>
+        <v>45714.36184027778</v>
       </c>
       <c r="Q81" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R81" t="b">
         <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0.000206199444210478</v>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Plataforma de contratos inteligentes</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Layer 1</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>Pure Proof of Stake</t>
-        </is>
-      </c>
-      <c r="W81" t="n">
-        <v>2019</v>
-      </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>algorand.com</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>Contratos inteligentes de alta eficiencia</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Layer 1)</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>Fundada por Silvio Micali, ganador del Premio Turing.</t>
-        </is>
-      </c>
+        <v>0.0002210355546336756</v>
+      </c>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>blockchain-capital</t>
+          <t>akedo</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>bcap</t>
+          <t>ake</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Blockchain Capital</t>
+          <t>Akedo</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>107.53</v>
+        <v>0.04244612</v>
       </c>
       <c r="F82" t="n">
-        <v>977656523</v>
+        <v>967612409</v>
       </c>
       <c r="G82" t="n">
         <v>81</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>41153473</v>
       </c>
       <c r="I82" t="n">
-        <v>107.53</v>
+        <v>0.050508</v>
       </c>
       <c r="J82" t="n">
-        <v>107.53</v>
+        <v>0.03827888</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>-0.008421905872240711</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>-16.15818</v>
       </c>
       <c r="M82" t="n">
-        <v>9091942</v>
+        <v>22796250000</v>
       </c>
       <c r="N82" t="n">
-        <v>9091942</v>
+        <v>100000000000</v>
       </c>
       <c r="O82" t="n">
-        <v>107.53</v>
+        <v>0.146656</v>
       </c>
       <c r="P82" s="1" t="n">
-        <v>46287.17361111111</v>
+        <v>46285.43993055556</v>
       </c>
       <c r="Q82" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S82" t="n">
-        <v>0.0002027925824654064</v>
+        <v>0.000216610184507637</v>
       </c>
       <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr"/>
@@ -7595,248 +7595,248 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>cosmos</t>
+          <t>render-token</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>atom</t>
+          <t>render</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Cosmos Hub</t>
+          <t>Render</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="F83" t="n">
-        <v>957085224</v>
+        <v>954643779</v>
       </c>
       <c r="G83" t="n">
         <v>82</v>
       </c>
       <c r="H83" t="n">
-        <v>63768684</v>
+        <v>79009784</v>
       </c>
       <c r="I83" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="J83" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="K83" t="n">
-        <v>0.03481011</v>
+        <v>0.07177500000000001</v>
       </c>
       <c r="L83" t="n">
-        <v>1.97262</v>
+        <v>4.09602</v>
       </c>
       <c r="M83" t="n">
-        <v>532132124.756035</v>
+        <v>518776241.2826915</v>
       </c>
       <c r="N83" t="n">
-        <v>532137677.998407</v>
+        <v>533536414.5626915</v>
       </c>
       <c r="O83" t="n">
-        <v>43.84</v>
+        <v>13.53</v>
       </c>
       <c r="P83" s="1" t="n">
-        <v>44458.66666666666</v>
+        <v>45368.35444444444</v>
       </c>
       <c r="Q83" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R83" t="b">
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.0001908336918537269</v>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>Interoperabilidad</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>Layer 0</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>Proof of Stake (Tendermint)</t>
-        </is>
-      </c>
-      <c r="W83" t="n">
-        <v>2019</v>
-      </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>cosmos.network</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>Interoperabilidad entre blockchains soberanas</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>Blockchain propia (hub, Layer 0)</t>
-        </is>
-      </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>Se autodefine como el "Internet de las blockchains", enfocada en interoperabilidad.</t>
-        </is>
-      </c>
+        <v>0.0002089201027632141</v>
+      </c>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr"/>
+      <c r="X83" t="inlineStr"/>
+      <c r="Y83" t="inlineStr"/>
+      <c r="Z83" t="inlineStr"/>
+      <c r="AA83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>just</t>
+          <t>cosmos</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>jst</t>
+          <t>atom</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>JUST</t>
+          <t>Cosmos Hub</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.112383</v>
+        <v>1.73</v>
       </c>
       <c r="F84" t="n">
-        <v>920300064</v>
+        <v>920031912</v>
       </c>
       <c r="G84" t="n">
         <v>83</v>
       </c>
       <c r="H84" t="n">
-        <v>25632519</v>
+        <v>60625718</v>
       </c>
       <c r="I84" t="n">
-        <v>0.115786</v>
+        <v>1.81</v>
       </c>
       <c r="J84" t="n">
-        <v>0.111845</v>
+        <v>1.67</v>
       </c>
       <c r="K84" t="n">
-        <v>-0.003271375287102293</v>
+        <v>-0.06933092253144868</v>
       </c>
       <c r="L84" t="n">
-        <v>-2.82858</v>
+        <v>-3.8122</v>
       </c>
       <c r="M84" t="n">
-        <v>8188743036.341737</v>
+        <v>532318351.197361</v>
       </c>
       <c r="N84" t="n">
-        <v>8188743036.341737</v>
+        <v>532326799.985017</v>
       </c>
       <c r="O84" t="n">
-        <v>0.193254</v>
+        <v>43.84</v>
       </c>
       <c r="P84" s="1" t="n">
-        <v>44290.85721064815</v>
+        <v>44458.66666666666</v>
       </c>
       <c r="Q84" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R84" t="b">
         <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0.0001694490576323718</v>
-      </c>
-      <c r="T84" t="inlineStr"/>
-      <c r="U84" t="inlineStr"/>
-      <c r="V84" t="inlineStr"/>
-      <c r="W84" t="inlineStr"/>
-      <c r="X84" t="inlineStr"/>
-      <c r="Y84" t="inlineStr"/>
-      <c r="Z84" t="inlineStr"/>
-      <c r="AA84" t="inlineStr"/>
+        <v>0.0001883961085898052</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Layer 0</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Proof of Stake (Tendermint)</t>
+        </is>
+      </c>
+      <c r="W84" t="n">
+        <v>2019</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>cosmos.network</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>Interoperabilidad entre blockchains soberanas</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>Blockchain propia (hub, Layer 0)</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>Se autodefine como el "Internet de las blockchains", enfocada en interoperabilidad.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>render-token</t>
+          <t>just</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>render</t>
+          <t>jst</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Render</t>
+          <t>JUST</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1.77</v>
+        <v>0.111553</v>
       </c>
       <c r="F85" t="n">
-        <v>919142956</v>
+        <v>913475177</v>
       </c>
       <c r="G85" t="n">
         <v>84</v>
       </c>
       <c r="H85" t="n">
-        <v>69728211</v>
+        <v>30017033</v>
       </c>
       <c r="I85" t="n">
-        <v>1.88</v>
+        <v>0.112971</v>
       </c>
       <c r="J85" t="n">
-        <v>1.77</v>
+        <v>0.109697</v>
       </c>
       <c r="K85" t="n">
-        <v>-0.07681907152692014</v>
+        <v>-0.0007749615324724179</v>
       </c>
       <c r="L85" t="n">
-        <v>-4.15402</v>
+        <v>-0.85677</v>
       </c>
       <c r="M85" t="n">
-        <v>518776241.2826915</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="N85" t="n">
-        <v>533536414.5626915</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="O85" t="n">
-        <v>13.53</v>
+        <v>0.193254</v>
       </c>
       <c r="P85" s="1" t="n">
-        <v>45368.35444444444</v>
+        <v>44290.85721064815</v>
       </c>
       <c r="Q85" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R85" t="b">
         <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>0.0001687763860622439</v>
+        <v>0.0001845081244213526</v>
       </c>
       <c r="T85" t="inlineStr"/>
       <c r="U85" t="inlineStr"/>
@@ -7850,7 +7850,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7869,28 +7869,28 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.869165</v>
+        <v>0.865667</v>
       </c>
       <c r="F86" t="n">
-        <v>869403190</v>
+        <v>865666733</v>
       </c>
       <c r="G86" t="n">
         <v>85</v>
       </c>
       <c r="H86" t="n">
-        <v>5535412</v>
+        <v>3721102</v>
       </c>
       <c r="I86" t="n">
-        <v>0.89935</v>
+        <v>0.8732529999999999</v>
       </c>
       <c r="J86" t="n">
-        <v>0.871714</v>
+        <v>0.849772</v>
       </c>
       <c r="K86" t="n">
-        <v>-0.01375341783522532</v>
+        <v>-0.007410946386864792</v>
       </c>
       <c r="L86" t="n">
-        <v>-1.55772</v>
+        <v>-0.87037</v>
       </c>
       <c r="M86" t="n">
         <v>1000000000</v>
@@ -7905,13 +7905,13 @@
         <v>44328.27623842593</v>
       </c>
       <c r="Q86" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R86" t="b">
         <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0.0001398607390413856</v>
+        <v>0.0001561588814840749</v>
       </c>
       <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr"/>
@@ -7925,82 +7925,82 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>filecoin</t>
+          <t>pancakeswap-token</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>fil</t>
+          <t>cake</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Filecoin</t>
+          <t>PancakeSwap</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1.016</v>
+        <v>2.66</v>
       </c>
       <c r="F87" t="n">
-        <v>844421380</v>
+        <v>847334747</v>
       </c>
       <c r="G87" t="n">
         <v>86</v>
       </c>
       <c r="H87" t="n">
-        <v>195620051</v>
+        <v>103069091</v>
       </c>
       <c r="I87" t="n">
-        <v>1.064</v>
+        <v>2.69</v>
       </c>
       <c r="J87" t="n">
-        <v>0.9855390000000001</v>
+        <v>2.52</v>
       </c>
       <c r="K87" t="n">
-        <v>-0.001571817332436831</v>
+        <v>0.058714</v>
       </c>
       <c r="L87" t="n">
-        <v>-0.15447</v>
+        <v>2.31326</v>
       </c>
       <c r="M87" t="n">
-        <v>830787126</v>
+        <v>318999079.8696931</v>
       </c>
       <c r="N87" t="n">
-        <v>1957033216</v>
+        <v>330627631.6087389</v>
       </c>
       <c r="O87" t="n">
-        <v>236.84</v>
+        <v>43.96</v>
       </c>
       <c r="P87" s="1" t="n">
-        <v>44287.22894675926</v>
+        <v>44316.08914351852</v>
       </c>
       <c r="Q87" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R87" t="b">
         <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>0.0001253378480430213</v>
+        <v>0.0001452884602539513</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>Almacenamiento descentralizado</t>
+          <t>DeFi</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>Infraestructura Web3</t>
+          <t>Exchange descentralizado</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>Proof-of-Replication/Spacetime</t>
+          <t>N/A (token BEP-20)</t>
         </is>
       </c>
       <c r="W87" t="n">
@@ -8008,389 +8008,389 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>filecoin.io</t>
+          <t>pancakeswap.finance</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>Almacenamiento descentralizado de archivos</t>
+          <t>Intercambio descentralizado en BNB Chain</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>Blockchain propia (Layer 1)</t>
+          <t>Token BEP-20 sobre BNB Chain</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>Recompensa a quienes ofrecen espacio de almacenamiento descentralizado.</t>
+          <t>Principal exchange descentralizado (DEX) del ecosistema BNB Chain.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>pancakeswap-token</t>
+          <t>injective-protocol</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>cake</t>
+          <t>inj</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>PancakeSwap</t>
+          <t>Injective</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2.6</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="F88" t="n">
-        <v>828522048</v>
+        <v>812515994</v>
       </c>
       <c r="G88" t="n">
         <v>87</v>
       </c>
       <c r="H88" t="n">
-        <v>117790690</v>
+        <v>204137418</v>
       </c>
       <c r="I88" t="n">
-        <v>2.72</v>
+        <v>8.15</v>
       </c>
       <c r="J88" t="n">
-        <v>2.5</v>
+        <v>7.53</v>
       </c>
       <c r="K88" t="n">
-        <v>0.06571100000000001</v>
+        <v>0.055087</v>
       </c>
       <c r="L88" t="n">
-        <v>2.59574</v>
+        <v>0.74266</v>
       </c>
       <c r="M88" t="n">
-        <v>318995668.0660263</v>
+        <v>100000000</v>
       </c>
       <c r="N88" t="n">
-        <v>330627631.6090779</v>
+        <v>100000000</v>
       </c>
       <c r="O88" t="n">
-        <v>43.96</v>
+        <v>52.62</v>
       </c>
       <c r="P88" s="1" t="n">
-        <v>44316.08914351852</v>
+        <v>45365.29608796296</v>
       </c>
       <c r="Q88" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R88" t="b">
         <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>0.0001160949522887583</v>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>DeFi</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>Exchange descentralizado</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>N/A (token BEP-20)</t>
-        </is>
-      </c>
-      <c r="W88" t="n">
-        <v>2020</v>
-      </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>pancakeswap.finance</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>Intercambio descentralizado en BNB Chain</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>Token BEP-20 sobre BNB Chain</t>
-        </is>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>Principal exchange descentralizado (DEX) del ecosistema BNB Chain.</t>
-        </is>
-      </c>
+        <v>0.0001246417877211647</v>
+      </c>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="inlineStr"/>
+      <c r="X88" t="inlineStr"/>
+      <c r="Y88" t="inlineStr"/>
+      <c r="Z88" t="inlineStr"/>
+      <c r="AA88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>filecoin</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>fil</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Dash</t>
+          <t>Filecoin</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>64.44</v>
+        <v>0.972024</v>
       </c>
       <c r="F89" t="n">
-        <v>828395976</v>
+        <v>807602487</v>
       </c>
       <c r="G89" t="n">
         <v>88</v>
       </c>
       <c r="H89" t="n">
-        <v>243663635</v>
+        <v>195192833</v>
       </c>
       <c r="I89" t="n">
-        <v>65.53</v>
+        <v>1.02</v>
       </c>
       <c r="J89" t="n">
-        <v>58.18</v>
+        <v>0.91861</v>
       </c>
       <c r="K89" t="n">
-        <v>4.86</v>
+        <v>-0.04375422227097114</v>
       </c>
       <c r="L89" t="n">
-        <v>8.148160000000001</v>
+        <v>-4.20773</v>
       </c>
       <c r="M89" t="n">
-        <v>12841073.33258205</v>
+        <v>830845988</v>
       </c>
       <c r="N89" t="n">
-        <v>12841268.89159301</v>
+        <v>1957031550</v>
       </c>
       <c r="O89" t="n">
-        <v>1493.59</v>
+        <v>236.84</v>
       </c>
       <c r="P89" s="1" t="n">
-        <v>43088.66666666666</v>
+        <v>44287.22894675926</v>
       </c>
       <c r="Q89" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>0.0001160216617660161</v>
-      </c>
-      <c r="T89" t="inlineStr"/>
-      <c r="U89" t="inlineStr"/>
-      <c r="V89" t="inlineStr"/>
-      <c r="W89" t="inlineStr"/>
-      <c r="X89" t="inlineStr"/>
-      <c r="Y89" t="inlineStr"/>
-      <c r="Z89" t="inlineStr"/>
-      <c r="AA89" t="inlineStr"/>
+        <v>0.0001217281977365792</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Almacenamiento descentralizado</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Infraestructura Web3</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Proof-of-Replication/Spacetime</t>
+        </is>
+      </c>
+      <c r="W89" t="n">
+        <v>2020</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>filecoin.io</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>Almacenamiento descentralizado de archivos</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Layer 1)</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>Recompensa a quienes ofrecen espacio de almacenamiento descentralizado.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>vechain</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>vet</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VeChain</t>
+          <t>Dash</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.00945007</v>
+        <v>61.69</v>
       </c>
       <c r="F90" t="n">
-        <v>812856826</v>
+        <v>792220247</v>
       </c>
       <c r="G90" t="n">
         <v>89</v>
       </c>
       <c r="H90" t="n">
-        <v>23445125</v>
+        <v>206679904</v>
       </c>
       <c r="I90" t="n">
-        <v>0.00988909</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="J90" t="n">
-        <v>0.008951300000000001</v>
+        <v>57.06</v>
       </c>
       <c r="K90" t="n">
-        <v>0.00027041</v>
+        <v>-2.915408481257757</v>
       </c>
       <c r="L90" t="n">
-        <v>2.94573</v>
+        <v>-4.34033</v>
       </c>
       <c r="M90" t="n">
-        <v>85985041177</v>
+        <v>12842253.62878004</v>
       </c>
       <c r="N90" t="n">
-        <v>85985041177</v>
+        <v>12842428.78110528</v>
       </c>
       <c r="O90" t="n">
-        <v>0.280991</v>
+        <v>1493.59</v>
       </c>
       <c r="P90" s="1" t="n">
-        <v>44304.71413194444</v>
+        <v>43088.66666666666</v>
       </c>
       <c r="Q90" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R90" t="b">
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>0.000106988153719272</v>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>Cadena de suministro</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>Trazabilidad</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>Proof of Authority</t>
-        </is>
-      </c>
-      <c r="W90" t="n">
-        <v>2015</v>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>vechain.org</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>Trazabilidad de productos y logística</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Layer 1)</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>Enfocada en trazabilidad de cadenas de suministro para empresas.</t>
-        </is>
-      </c>
+        <v>0.0001126069040446216</v>
+      </c>
+      <c r="T90" t="inlineStr"/>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr"/>
+      <c r="W90" t="inlineStr"/>
+      <c r="X90" t="inlineStr"/>
+      <c r="Y90" t="inlineStr"/>
+      <c r="Z90" t="inlineStr"/>
+      <c r="AA90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>injective-protocol</t>
+          <t>vechain</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>inj</t>
+          <t>vet</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Injective</t>
+          <t>VeChain</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>8.08</v>
+        <v>0.009202760000000001</v>
       </c>
       <c r="F91" t="n">
-        <v>808076123</v>
+        <v>791300059</v>
       </c>
       <c r="G91" t="n">
         <v>90</v>
       </c>
       <c r="H91" t="n">
-        <v>199910565</v>
+        <v>15098082</v>
       </c>
       <c r="I91" t="n">
-        <v>8.279999999999999</v>
+        <v>0.009460730000000001</v>
       </c>
       <c r="J91" t="n">
-        <v>7.59</v>
+        <v>0.008687230000000001</v>
       </c>
       <c r="K91" t="n">
-        <v>0.271737</v>
+        <v>-0.000247786137227807</v>
       </c>
       <c r="L91" t="n">
-        <v>3.47926</v>
+        <v>-2.56094</v>
       </c>
       <c r="M91" t="n">
-        <v>100000000</v>
+        <v>85985041177</v>
       </c>
       <c r="N91" t="n">
-        <v>100000000</v>
+        <v>85985041177</v>
       </c>
       <c r="O91" t="n">
-        <v>52.62</v>
+        <v>0.280991</v>
       </c>
       <c r="P91" s="1" t="n">
-        <v>45365.29608796296</v>
+        <v>44304.71413194444</v>
       </c>
       <c r="Q91" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R91" t="b">
         <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>0.0001042089464254629</v>
-      </c>
-      <c r="T91" t="inlineStr"/>
-      <c r="U91" t="inlineStr"/>
-      <c r="V91" t="inlineStr"/>
-      <c r="W91" t="inlineStr"/>
-      <c r="X91" t="inlineStr"/>
-      <c r="Y91" t="inlineStr"/>
-      <c r="Z91" t="inlineStr"/>
-      <c r="AA91" t="inlineStr"/>
+        <v>0.0001120612549714167</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Cadena de suministro</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Trazabilidad</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Proof of Authority</t>
+        </is>
+      </c>
+      <c r="W91" t="n">
+        <v>2015</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>vechain.org</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>Trazabilidad de productos y logística</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Layer 1)</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>Enfocada en trazabilidad de cadenas de suministro para empresas.</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8409,10 +8409,10 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="F92" t="n">
-        <v>767684870</v>
+        <v>757929367</v>
       </c>
       <c r="G92" t="n">
         <v>91</v>
@@ -8424,19 +8424,19 @@
         <v>1.21</v>
       </c>
       <c r="J92" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="K92" t="n">
-        <v>-0.005142105392973884</v>
+        <v>-0.004682058472634365</v>
       </c>
       <c r="L92" t="n">
-        <v>-0.42371</v>
+        <v>-0.38744</v>
       </c>
       <c r="M92" t="n">
-        <v>635257311.01475</v>
+        <v>629624067.49395</v>
       </c>
       <c r="N92" t="n">
-        <v>635257311.01475</v>
+        <v>629624067.49395</v>
       </c>
       <c r="O92" t="n">
         <v>1.26</v>
@@ -8445,13 +8445,13 @@
         <v>46049.54175925926</v>
       </c>
       <c r="Q92" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R92" t="b">
         <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>8.072795106898724e-05</v>
+        <v>9.227324734470811e-05</v>
       </c>
       <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr"/>
@@ -8465,7 +8465,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8487,7 +8487,7 @@
         <v>11.22</v>
       </c>
       <c r="F93" t="n">
-        <v>736700070</v>
+        <v>738906515</v>
       </c>
       <c r="G93" t="n">
         <v>92</v>
@@ -8502,31 +8502,31 @@
         <v>11.22</v>
       </c>
       <c r="K93" t="n">
-        <v>0.001098</v>
+        <v>0.001101</v>
       </c>
       <c r="L93" t="n">
-        <v>0.00979</v>
+        <v>0.009809999999999999</v>
       </c>
       <c r="M93" t="n">
-        <v>65652959.922754</v>
+        <v>65843132.622857</v>
       </c>
       <c r="N93" t="n">
-        <v>65653772.677143</v>
+        <v>65843132.622857</v>
       </c>
       <c r="O93" t="n">
         <v>11.22</v>
       </c>
       <c r="P93" s="1" t="n">
-        <v>46288.55590277778</v>
+        <v>46289.55208333334</v>
       </c>
       <c r="Q93" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R93" t="b">
         <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>6.27152901366481e-05</v>
+        <v>8.099315940233796e-05</v>
       </c>
       <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr"/>
@@ -8540,173 +8540,143 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>aptos</t>
+          <t>stable-2</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>apt</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Aptos</t>
+          <t>​​Stable</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.8195210000000001</v>
+        <v>0.0264549</v>
       </c>
       <c r="F94" t="n">
-        <v>713656348</v>
+        <v>703950747</v>
       </c>
       <c r="G94" t="n">
         <v>93</v>
       </c>
       <c r="H94" t="n">
-        <v>175330693</v>
+        <v>12196843</v>
       </c>
       <c r="I94" t="n">
-        <v>0.857235</v>
+        <v>0.0272989</v>
       </c>
       <c r="J94" t="n">
-        <v>0.7566310000000001</v>
+        <v>0.02452288</v>
       </c>
       <c r="K94" t="n">
-        <v>0.050185</v>
+        <v>0.00105555</v>
       </c>
       <c r="L94" t="n">
-        <v>6.52315</v>
+        <v>4.17665</v>
       </c>
       <c r="M94" t="n">
-        <v>870678378.6642992</v>
+        <v>26609465706</v>
       </c>
       <c r="N94" t="n">
-        <v>1209118421.186413</v>
+        <v>100000000000</v>
       </c>
       <c r="O94" t="n">
-        <v>19.92</v>
+        <v>0.04323745</v>
       </c>
       <c r="P94" s="1" t="n">
-        <v>44952.26755787037</v>
+        <v>46156.97986111111</v>
       </c>
       <c r="Q94" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>4.931908454535548e-05</v>
-      </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>Plataforma de contratos inteligentes</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>Layer 1</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>Proof of Stake (BFT)</t>
-        </is>
-      </c>
-      <c r="W94" t="n">
-        <v>2022</v>
-      </c>
-      <c r="X94" t="inlineStr">
-        <is>
-          <t>aptosfoundation.org</t>
-        </is>
-      </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>Contratos inteligentes de alto rendimiento</t>
-        </is>
-      </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Layer 1)</t>
-        </is>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>Desarrollada por exingenieros del proyecto Diem (Meta/Facebook).</t>
-        </is>
-      </c>
+        <v>6.026524031149454e-05</v>
+      </c>
+      <c r="T94" t="inlineStr"/>
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr"/>
+      <c r="W94" t="inlineStr"/>
+      <c r="X94" t="inlineStr"/>
+      <c r="Y94" t="inlineStr"/>
+      <c r="Z94" t="inlineStr"/>
+      <c r="AA94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>aerodrome-finance</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>aero</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Aerodrome Finance</t>
+          <t>GHO</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.713074</v>
+        <v>0.998915</v>
       </c>
       <c r="F95" t="n">
-        <v>707608773</v>
+        <v>698241826</v>
       </c>
       <c r="G95" t="n">
         <v>94</v>
       </c>
       <c r="H95" t="n">
-        <v>71562123</v>
+        <v>6097158</v>
       </c>
       <c r="I95" t="n">
-        <v>0.7368209999999999</v>
+        <v>0.999329</v>
       </c>
       <c r="J95" t="n">
-        <v>0.673687</v>
+        <v>0.998743</v>
       </c>
       <c r="K95" t="n">
-        <v>0.01988293</v>
+        <v>-4.182532340247e-06</v>
       </c>
       <c r="L95" t="n">
-        <v>2.86832</v>
+        <v>-0.00078</v>
       </c>
       <c r="M95" t="n">
-        <v>992612383.1289241</v>
+        <v>699000000</v>
       </c>
       <c r="N95" t="n">
-        <v>1983240735.576791</v>
+        <v>699000000</v>
       </c>
       <c r="O95" t="n">
-        <v>2.32</v>
+        <v>1.03</v>
       </c>
       <c r="P95" s="1" t="n">
-        <v>45633.25043981482</v>
+        <v>45350.38608796296</v>
       </c>
       <c r="Q95" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R95" t="b">
         <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>4.580339562892256e-05</v>
+        <v>5.687998919688544e-05</v>
       </c>
       <c r="T95" t="inlineStr"/>
       <c r="U95" t="inlineStr"/>
@@ -8720,68 +8690,68 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>aerodrome-finance</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>aero</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>GHO</t>
+          <t>Aerodrome Finance</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.998898</v>
+        <v>0.697692</v>
       </c>
       <c r="F96" t="n">
-        <v>698246801</v>
+        <v>695345128</v>
       </c>
       <c r="G96" t="n">
         <v>95</v>
       </c>
       <c r="H96" t="n">
-        <v>6795088</v>
+        <v>68096401</v>
       </c>
       <c r="I96" t="n">
-        <v>0.999282</v>
+        <v>0.7153389999999999</v>
       </c>
       <c r="J96" t="n">
-        <v>0.998801</v>
+        <v>0.651207</v>
       </c>
       <c r="K96" t="n">
-        <v>-0.000139018097914612</v>
+        <v>-0.0154599686984972</v>
       </c>
       <c r="L96" t="n">
-        <v>-0.01392</v>
+        <v>-2.05333</v>
       </c>
       <c r="M96" t="n">
-        <v>699000000</v>
+        <v>996635960.3533072</v>
       </c>
       <c r="N96" t="n">
-        <v>699000000</v>
+        <v>1988034890.229641</v>
       </c>
       <c r="O96" t="n">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="P96" s="1" t="n">
-        <v>45350.38608796296</v>
+        <v>45633.25043981482</v>
       </c>
       <c r="Q96" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R96" t="b">
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>4.036091972802752e-05</v>
+        <v>5.51623178307576e-05</v>
       </c>
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
@@ -8795,143 +8765,173 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>janus-henderson-anemoy-aaa-clo-fund</t>
+          <t>aptos</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>jaaa</t>
+          <t>apt</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy AAA CLO Fund</t>
+          <t>Aptos</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1.05</v>
+        <v>0.791697</v>
       </c>
       <c r="F97" t="n">
-        <v>677692166</v>
+        <v>689351600</v>
       </c>
       <c r="G97" t="n">
         <v>96</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>90235638</v>
       </c>
       <c r="I97" t="n">
-        <v>1.05</v>
+        <v>0.822106</v>
       </c>
       <c r="J97" t="n">
-        <v>1.05</v>
+        <v>0.743902</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>-0.02512260180989745</v>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>-3.36128</v>
       </c>
       <c r="M97" t="n">
-        <v>645128652.594015</v>
+        <v>870726490.2274346</v>
       </c>
       <c r="N97" t="n">
-        <v>645128652.594015</v>
+        <v>1209166859.596561</v>
       </c>
       <c r="O97" t="n">
-        <v>1.05</v>
+        <v>19.92</v>
       </c>
       <c r="P97" s="1" t="n">
-        <v>46287.38530092593</v>
+        <v>44952.26755787037</v>
       </c>
       <c r="Q97" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R97" t="b">
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>2.841171654314362e-05</v>
-      </c>
-      <c r="T97" t="inlineStr"/>
-      <c r="U97" t="inlineStr"/>
-      <c r="V97" t="inlineStr"/>
-      <c r="W97" t="inlineStr"/>
-      <c r="X97" t="inlineStr"/>
-      <c r="Y97" t="inlineStr"/>
-      <c r="Z97" t="inlineStr"/>
-      <c r="AA97" t="inlineStr"/>
+        <v>5.160830169663334e-05</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Plataforma de contratos inteligentes</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Layer 1</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Proof of Stake (BFT)</t>
+        </is>
+      </c>
+      <c r="W97" t="n">
+        <v>2022</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>aptosfoundation.org</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>Contratos inteligentes de alto rendimiento</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Layer 1)</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>Desarrollada por exingenieros del proyecto Diem (Meta/Facebook).</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>stable-2</t>
+          <t>ether-fi</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>ethfi</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>​​Stable</t>
+          <t>Ether.fi</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.02542602</v>
+        <v>0.661406</v>
       </c>
       <c r="F98" t="n">
-        <v>676294745</v>
+        <v>638488563</v>
       </c>
       <c r="G98" t="n">
         <v>97</v>
       </c>
       <c r="H98" t="n">
-        <v>8812550</v>
+        <v>47754404</v>
       </c>
       <c r="I98" t="n">
-        <v>0.02547868</v>
+        <v>0.693611</v>
       </c>
       <c r="J98" t="n">
-        <v>0.02415728</v>
+        <v>0.636795</v>
       </c>
       <c r="K98" t="n">
-        <v>0.00102938</v>
+        <v>-0.03011208614870931</v>
       </c>
       <c r="L98" t="n">
-        <v>4.21934</v>
+        <v>-4.37637</v>
       </c>
       <c r="M98" t="n">
-        <v>26579350137</v>
+        <v>965350000</v>
       </c>
       <c r="N98" t="n">
-        <v>100000000000</v>
+        <v>965350000</v>
       </c>
       <c r="O98" t="n">
-        <v>0.04323745</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="P98" s="1" t="n">
-        <v>46156.97986111111</v>
+        <v>45378.63525462963</v>
       </c>
       <c r="Q98" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R98" t="b">
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>2.759934174476732e-05</v>
+        <v>2.144775950369468e-05</v>
       </c>
       <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr"/>
@@ -8945,68 +8945,68 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ether-fi</t>
+          <t>pudgy-penguins</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ethfi</t>
+          <t>pengu</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Ether.fi</t>
+          <t>Pudgy Penguins</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.691782</v>
+        <v>0.009929500000000001</v>
       </c>
       <c r="F99" t="n">
-        <v>666968076</v>
+        <v>624172251</v>
       </c>
       <c r="G99" t="n">
         <v>98</v>
       </c>
       <c r="H99" t="n">
-        <v>54243778</v>
+        <v>330460231</v>
       </c>
       <c r="I99" t="n">
-        <v>0.727727</v>
+        <v>0.01038513</v>
       </c>
       <c r="J99" t="n">
-        <v>0.679153</v>
+        <v>0.00947753</v>
       </c>
       <c r="K99" t="n">
-        <v>-0.01626979708185095</v>
+        <v>-0.000391774588025516</v>
       </c>
       <c r="L99" t="n">
-        <v>-2.29783</v>
+        <v>-3.71032</v>
       </c>
       <c r="M99" t="n">
-        <v>965350000</v>
+        <v>62860396090</v>
       </c>
       <c r="N99" t="n">
-        <v>965350000</v>
+        <v>76722808329.65067</v>
       </c>
       <c r="O99" t="n">
-        <v>8.529999999999999</v>
+        <v>0.06844699999999999</v>
       </c>
       <c r="P99" s="1" t="n">
-        <v>45378.63525462963</v>
+        <v>45643.21206018519</v>
       </c>
       <c r="Q99" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R99" t="b">
         <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>2.217738884124177e-05</v>
+        <v>1.295853515550497e-05</v>
       </c>
       <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr"/>
@@ -9020,68 +9020,68 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>pudgy-penguins</t>
+          <t>flare-networks</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>pengu</t>
+          <t>flr</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Pudgy Penguins</t>
+          <t>Flare</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.01031779</v>
+        <v>0.00712598</v>
       </c>
       <c r="F100" t="n">
-        <v>648368859</v>
+        <v>619178957</v>
       </c>
       <c r="G100" t="n">
         <v>99</v>
       </c>
       <c r="H100" t="n">
-        <v>531306847</v>
+        <v>3353076</v>
       </c>
       <c r="I100" t="n">
-        <v>0.01111058</v>
+        <v>0.00725757</v>
       </c>
       <c r="J100" t="n">
-        <v>0.008808359999999999</v>
+        <v>0.00694767</v>
       </c>
       <c r="K100" t="n">
-        <v>0.00119626</v>
+        <v>-0.000113533696021038</v>
       </c>
       <c r="L100" t="n">
-        <v>13.1147</v>
+        <v>-1.57288</v>
       </c>
       <c r="M100" t="n">
-        <v>62860396090</v>
+        <v>86890312184.51483</v>
       </c>
       <c r="N100" t="n">
-        <v>76722811726.78036</v>
+        <v>106616106401.7717</v>
       </c>
       <c r="O100" t="n">
-        <v>0.06844699999999999</v>
+        <v>0.150073</v>
       </c>
       <c r="P100" s="1" t="n">
-        <v>45643.21206018519</v>
+        <v>44935.80144675926</v>
       </c>
       <c r="Q100" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>1.136494566174738e-05</v>
+        <v>9.997633423098637e-06</v>
       </c>
       <c r="T100" t="inlineStr"/>
       <c r="U100" t="inlineStr"/>
@@ -9095,62 +9095,62 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>flare-networks</t>
+          <t>beldex</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>flr</t>
+          <t>bdx</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Flare</t>
+          <t>Beldex</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.00723778</v>
+        <v>0.076526</v>
       </c>
       <c r="F101" t="n">
-        <v>628819245</v>
+        <v>602318849</v>
       </c>
       <c r="G101" t="n">
         <v>100</v>
       </c>
       <c r="H101" t="n">
-        <v>6889701</v>
+        <v>3397765</v>
       </c>
       <c r="I101" t="n">
-        <v>0.00760419</v>
+        <v>0.07681499999999999</v>
       </c>
       <c r="J101" t="n">
-        <v>0.00692082</v>
+        <v>0.07506</v>
       </c>
       <c r="K101" t="n">
-        <v>0.00027627</v>
+        <v>0.00037111</v>
       </c>
       <c r="L101" t="n">
-        <v>3.96854</v>
+        <v>0.43853</v>
       </c>
       <c r="M101" t="n">
-        <v>86880791700.73494</v>
+        <v>7870799519.638308</v>
       </c>
       <c r="N101" t="n">
-        <v>106608975509.8958</v>
+        <v>9939718245.379999</v>
       </c>
       <c r="O101" t="n">
-        <v>0.150073</v>
+        <v>0.450785</v>
       </c>
       <c r="P101" s="1" t="n">
-        <v>44935.80144675926</v>
+        <v>43450.66666666666</v>
       </c>
       <c r="Q101" s="1" t="n">
-        <v>46288.57835648148</v>
+        <v>46289.57523148148</v>
       </c>
       <c r="R101" t="b">
         <v>0</v>

--- a/src/xlsx/enriched_data.xlsx
+++ b/src/xlsx/enriched_data.xlsx
@@ -560,7 +560,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -579,34 +579,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>83978</v>
+        <v>83598</v>
       </c>
       <c r="F2" t="n">
-        <v>1687012220721</v>
+        <v>1679162755062</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>44006821718</v>
+        <v>38514548082</v>
       </c>
       <c r="I2" t="n">
-        <v>85876</v>
+        <v>85208</v>
       </c>
       <c r="J2" t="n">
-        <v>82941</v>
+        <v>83513</v>
       </c>
       <c r="K2" t="n">
-        <v>-1701.113919286392</v>
+        <v>-604.7274447487289</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.97836</v>
+        <v>-0.77851</v>
       </c>
       <c r="M2" t="n">
-        <v>20088671</v>
+        <v>20089181</v>
       </c>
       <c r="N2" t="n">
-        <v>20088728</v>
+        <v>20089196</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -615,7 +615,7 @@
         <v>45936.45673611111</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
@@ -665,7 +665,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -684,34 +684,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2664.09</v>
+        <v>2688.92</v>
       </c>
       <c r="F3" t="n">
-        <v>325222379231</v>
+        <v>328251353932</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>16572408474</v>
+        <v>15862968693</v>
       </c>
       <c r="I3" t="n">
-        <v>2720.31</v>
+        <v>2739.52</v>
       </c>
       <c r="J3" t="n">
-        <v>2634.74</v>
+        <v>2653.81</v>
       </c>
       <c r="K3" t="n">
-        <v>-49.80841626912115</v>
+        <v>21.97</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.81017</v>
+        <v>0.79044</v>
       </c>
       <c r="M3" t="n">
-        <v>122076229.2680794</v>
+        <v>122078905.3531288</v>
       </c>
       <c r="N3" t="n">
-        <v>122076229.2680793</v>
+        <v>122078905.3531288</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -720,13 +720,13 @@
         <v>45893.47295138889</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1924917898202895</v>
+        <v>0.1951907754594442</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -789,34 +789,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999744</v>
+        <v>0.99973</v>
       </c>
       <c r="F4" t="n">
-        <v>183495697334</v>
+        <v>183727460118</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>77473994732</v>
+        <v>72786037039</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999937</v>
+        <v>0.9998899999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999652</v>
+        <v>0.999287</v>
       </c>
       <c r="K4" t="n">
-        <v>-8.90247621177e-07</v>
+        <v>6.05e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.00043</v>
+        <v>0.00347</v>
       </c>
       <c r="M4" t="n">
-        <v>183542716766.929</v>
+        <v>183779015975.4778</v>
       </c>
       <c r="N4" t="n">
-        <v>189009662872.4462</v>
+        <v>189245961986.9062</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -825,13 +825,13 @@
         <v>43304.66666666666</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1084513191496202</v>
+        <v>0.1090902637525081</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -894,34 +894,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>775.11</v>
+        <v>772.7</v>
       </c>
       <c r="F5" t="n">
-        <v>103213855578</v>
+        <v>102856673958</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1197659217</v>
+        <v>1165366190</v>
       </c>
       <c r="I5" t="n">
-        <v>781.95</v>
+        <v>785.3099999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>758.22</v>
+        <v>770.72</v>
       </c>
       <c r="K5" t="n">
-        <v>-5.754073065851458</v>
+        <v>-4.873413513556216</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.70514</v>
+        <v>-0.62303</v>
       </c>
       <c r="M5" t="n">
-        <v>133159906.26</v>
+        <v>133159842.41</v>
       </c>
       <c r="N5" t="n">
-        <v>133159906.26</v>
+        <v>133159833.97</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -930,13 +930,13 @@
         <v>45943.02875</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0608461422190987</v>
+        <v>0.06091126797012559</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -999,28 +999,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="F6" t="n">
-        <v>94214439065</v>
+        <v>99229873529</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>4658671923</v>
+        <v>6282193834</v>
       </c>
       <c r="I6" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="J6" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.07669192306231665</v>
+        <v>0.07800700000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>-4.8361</v>
+        <v>5.11372</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -1035,13 +1035,13 @@
         <v>45855.82005787037</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05550970740392702</v>
+        <v>0.05875059152725504</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1104,34 +1104,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.99982</v>
+        <v>0.999853</v>
       </c>
       <c r="F7" t="n">
-        <v>75208946184</v>
+        <v>75342386451</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>21520943946</v>
+        <v>20818639756</v>
       </c>
       <c r="I7" t="n">
-        <v>1.002</v>
+        <v>1.001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999305</v>
+        <v>0.99942</v>
       </c>
       <c r="K7" t="n">
-        <v>5.7299e-07</v>
+        <v>3.113e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00027</v>
+        <v>0.00606</v>
       </c>
       <c r="M7" t="n">
-        <v>75222489862.57661</v>
+        <v>75354142543.02426</v>
       </c>
       <c r="N7" t="n">
-        <v>75208587556.4671</v>
+        <v>75302398987.78542</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -1140,13 +1140,13 @@
         <v>43418.66666666666</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04423991299634975</v>
+        <v>0.04451955466178284</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1209,34 +1209,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>114.78</v>
+        <v>119.58</v>
       </c>
       <c r="F8" t="n">
-        <v>67442627183</v>
+        <v>70220425043</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>4787195372</v>
+        <v>5871439186</v>
       </c>
       <c r="I8" t="n">
-        <v>116.94</v>
+        <v>122.01</v>
       </c>
       <c r="J8" t="n">
-        <v>112.72</v>
+        <v>114.46</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.945020311639823</v>
+        <v>4.61</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.62052</v>
+        <v>4.02766</v>
       </c>
       <c r="M8" t="n">
-        <v>587577149.9029876</v>
+        <v>587647593.3659807</v>
       </c>
       <c r="N8" t="n">
-        <v>634608286.6592437</v>
+        <v>634686100.9544628</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -1245,13 +1245,13 @@
         <v>45676.13572916666</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R8" t="b">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03963467497421824</v>
+        <v>0.04146813190715139</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1314,34 +1314,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.339884</v>
+        <v>0.337211</v>
       </c>
       <c r="F9" t="n">
-        <v>32277074717</v>
+        <v>32018650054</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>508747370</v>
+        <v>461988718</v>
       </c>
       <c r="I9" t="n">
-        <v>0.343877</v>
+        <v>0.341481</v>
       </c>
       <c r="J9" t="n">
-        <v>0.338585</v>
+        <v>0.336802</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.001792421662365318</v>
+        <v>-0.002870799508586985</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.53525</v>
+        <v>-0.8316</v>
       </c>
       <c r="M9" t="n">
         <v>94964948406.9399</v>
       </c>
       <c r="N9" t="n">
-        <v>94965004918.81999</v>
+        <v>94966809744.41438</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1350,13 +1350,13 @@
         <v>45629.67407407407</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01878235880425004</v>
+        <v>0.01870931820608082</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1419,34 +1419,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1514.5</v>
+        <v>1593.72</v>
       </c>
       <c r="F10" t="n">
-        <v>25670307558</v>
+        <v>27023589668</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>1530755188</v>
+        <v>1279929296</v>
       </c>
       <c r="I10" t="n">
-        <v>1638.23</v>
+        <v>1622.95</v>
       </c>
       <c r="J10" t="n">
-        <v>1461.52</v>
+        <v>1491.28</v>
       </c>
       <c r="K10" t="n">
-        <v>-120.5149810899129</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>-7.53144</v>
+        <v>5.35021</v>
       </c>
       <c r="M10" t="n">
-        <v>16949703.2905448</v>
+        <v>16951193.9155448</v>
       </c>
       <c r="N10" t="n">
-        <v>16949931.4155448</v>
+        <v>16951806.4155448</v>
       </c>
       <c r="O10" t="n">
         <v>3191.93</v>
@@ -1455,13 +1455,13 @@
         <v>42671.66666666666</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01486470678402283</v>
+        <v>0.01573349708825826</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1524,34 +1524,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.037</v>
+        <v>1.027</v>
       </c>
       <c r="F11" t="n">
-        <v>23885874146</v>
+        <v>23712065535</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>30426403</v>
+        <v>585257867</v>
       </c>
       <c r="I11" t="n">
-        <v>1.037</v>
+        <v>1.047</v>
       </c>
       <c r="J11" t="n">
-        <v>1.022</v>
+        <v>1.012</v>
       </c>
       <c r="K11" t="n">
-        <v>0.00575091</v>
+        <v>-0.009244703155131262</v>
       </c>
       <c r="L11" t="n">
-        <v>0.55813</v>
+        <v>-0.89492</v>
       </c>
       <c r="M11" t="n">
-        <v>23042572971.368</v>
+        <v>23089131934.788</v>
       </c>
       <c r="N11" t="n">
-        <v>23042572971.368</v>
+        <v>23089131934.788</v>
       </c>
       <c r="O11" t="n">
         <v>1.061</v>
@@ -1560,13 +1560,13 @@
         <v>46237.59675925926</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R11" t="b">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01380658122983865</v>
+        <v>0.01376064737561408</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
@@ -1580,7 +1580,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1599,28 +1599,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>92.52</v>
+        <v>92.18000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>20581429395</v>
+        <v>20488667956</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1338426068</v>
+        <v>1155605568</v>
       </c>
       <c r="I12" t="n">
-        <v>95.77</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>89.91</v>
+        <v>91</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.957293932139351</v>
+        <v>-0.1386147680552199</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.12298</v>
+        <v>-0.12922</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1635,13 +1635,13 @@
         <v>46288.22002314815</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R12" t="b">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01184712597086994</v>
+        <v>0.01184029930262358</v>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
@@ -1655,7 +1655,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1674,34 +1674,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.093919</v>
+        <v>0.097402</v>
       </c>
       <c r="F13" t="n">
-        <v>14655932118</v>
+        <v>15194781531</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>1578915177</v>
+        <v>1266625089</v>
       </c>
       <c r="I13" t="n">
-        <v>0.099772</v>
+        <v>0.098981</v>
       </c>
       <c r="J13" t="n">
-        <v>0.091664</v>
+        <v>0.094092</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.005505030732556204</v>
+        <v>0.00300281</v>
       </c>
       <c r="L13" t="n">
-        <v>-5.47073</v>
+        <v>3.13939</v>
       </c>
       <c r="M13" t="n">
-        <v>156048806383.7053</v>
+        <v>156060896383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>156048456383.7052</v>
+        <v>171774773126.5791</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1710,13 +1710,13 @@
         <v>44323.88082175926</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.008333450398624783</v>
+        <v>0.008686451740935837</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1760,248 +1760,278 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>monero</t>
+          <t>chainlink</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>xmr</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Monero</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>549.51</v>
+        <v>13.87</v>
       </c>
       <c r="F14" t="n">
-        <v>10335646084</v>
+        <v>10373383774</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>131877115</v>
+        <v>1063141253</v>
       </c>
       <c r="I14" t="n">
-        <v>566.0700000000001</v>
+        <v>14.19</v>
       </c>
       <c r="J14" t="n">
-        <v>542.46</v>
+        <v>12.46</v>
       </c>
       <c r="K14" t="n">
-        <v>-13.80552932081468</v>
+        <v>1.34</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.47342</v>
+        <v>10.71284</v>
       </c>
       <c r="M14" t="n">
-        <v>18808857.69615291</v>
+        <v>748099970.424884</v>
       </c>
       <c r="N14" t="n">
-        <v>18808888.29599696</v>
+        <v>1000000000</v>
       </c>
       <c r="O14" t="n">
-        <v>797.73</v>
+        <v>52.7</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>46036.48202546296</v>
+        <v>44325.67635416667</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.005771625999228014</v>
+        <v>0.005814090617351435</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>Privacidad</t>
+          <t>Oráculo</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Pagos privados</t>
+          <t>Infraestructura Web3</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Proof of Work (RandomX)</t>
+          <t>N/A (token ERC-20, red de oráculos)</t>
         </is>
       </c>
       <c r="W14" t="n">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>getmonero.org</t>
+          <t>chain.link</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Transacciones privadas</t>
+          <t>Conexión de datos externos a contratos inteligentes</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>Blockchain propia (Layer 1)</t>
+          <t>Token ERC-20 sobre Ethereum</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Prioriza la privacidad total de remitente, destinatario y monto de cada transacción.</t>
+          <t>Provee datos del mundo real (oráculos) a contratos inteligentes.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>whitebit</t>
+          <t>monero</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>wbt</t>
+          <t>xmr</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>WhiteBIT Coin</t>
+          <t>Monero</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>83.98999999999999</v>
+        <v>549.15</v>
       </c>
       <c r="F15" t="n">
-        <v>9982633074</v>
+        <v>10313844161</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>140612680</v>
+        <v>144904867</v>
       </c>
       <c r="I15" t="n">
-        <v>86.09999999999999</v>
+        <v>577.46</v>
       </c>
       <c r="J15" t="n">
-        <v>82.98</v>
+        <v>545.25</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.943211609221805</v>
+        <v>-1.992583697525561</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.22567</v>
+        <v>-0.38245</v>
       </c>
       <c r="M15" t="n">
-        <v>118852171</v>
+        <v>18809274.09052855</v>
       </c>
       <c r="N15" t="n">
-        <v>293421670</v>
+        <v>18809314.29046824</v>
       </c>
       <c r="O15" t="n">
-        <v>87.91</v>
+        <v>797.73</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>46286.85358796296</v>
+        <v>46036.48202546296</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.005562297881782702</v>
-      </c>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
+        <v>0.005778619727307948</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Privacidad</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Pagos privados</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Proof of Work (RandomX)</t>
+        </is>
+      </c>
+      <c r="W15" t="n">
+        <v>2014</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>getmonero.org</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Transacciones privadas</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Layer 1)</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Prioriza la privacidad total de remitente, destinatario y monto de cada transacción.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>whitebit</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>wbt</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>USDS</t>
+          <t>WhiteBIT Coin</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.999883</v>
+        <v>83.58</v>
       </c>
       <c r="F16" t="n">
-        <v>9686691626</v>
+        <v>9932139589</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>141654011</v>
+        <v>128664165</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>85.16</v>
       </c>
       <c r="J16" t="n">
-        <v>0.999647</v>
+        <v>83.58</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.8205541120485e-05</v>
+        <v>-0.5541301889751509</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.009090000000000001</v>
+        <v>-0.86936</v>
       </c>
       <c r="M16" t="n">
-        <v>9687827058.865</v>
+        <v>118852171</v>
       </c>
       <c r="N16" t="n">
-        <v>9697547815.27993</v>
+        <v>293421670</v>
       </c>
       <c r="O16" t="n">
-        <v>1.057</v>
+        <v>87.91</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>45593.90336805556</v>
+        <v>46286.85358796296</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R16" t="b">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.00538681181064929</v>
+        <v>0.005551218166896258</v>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
@@ -2015,112 +2045,82 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>USDS</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>12.46</v>
+        <v>0.99963</v>
       </c>
       <c r="F17" t="n">
-        <v>9317677595</v>
+        <v>9719421143</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>522257174</v>
+        <v>125292033</v>
       </c>
       <c r="I17" t="n">
-        <v>12.75</v>
+        <v>0.99998</v>
       </c>
       <c r="J17" t="n">
-        <v>12.1</v>
+        <v>0.9994</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2108202456293533</v>
+        <v>-0.000183372176973173</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.59865</v>
+        <v>-0.01564</v>
       </c>
       <c r="M17" t="n">
-        <v>748099970.424884</v>
+        <v>9723114647.376017</v>
       </c>
       <c r="N17" t="n">
-        <v>1000000000</v>
+        <v>9723685294.041584</v>
       </c>
       <c r="O17" t="n">
-        <v>52.7</v>
+        <v>1.057</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>44325.67635416667</v>
+        <v>45593.90336805556</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.005167995477449173</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Oráculo</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Infraestructura Web3</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>N/A (token ERC-20, red de oráculos)</t>
-        </is>
-      </c>
-      <c r="W17" t="n">
-        <v>2017</v>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>chain.link</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Conexión de datos externos a contratos inteligentes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Token ERC-20 sobre Ethereum</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Provee datos del mundo real (oráculos) a contratos inteligentes.</t>
-        </is>
-      </c>
+        <v>0.005424490561053617</v>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2139,28 +2139,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.240627</v>
+        <v>0.253462</v>
       </c>
       <c r="F18" t="n">
-        <v>9030496797</v>
+        <v>9508956148</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>592604878</v>
+        <v>716129718</v>
       </c>
       <c r="I18" t="n">
-        <v>0.249431</v>
+        <v>0.258045</v>
       </c>
       <c r="J18" t="n">
-        <v>0.233288</v>
+        <v>0.244758</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.007681261816755242</v>
+        <v>0.0097284</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.03354</v>
+        <v>3.92179</v>
       </c>
       <c r="M18" t="n">
         <v>37529061988.53558</v>
@@ -2175,13 +2175,13 @@
         <v>44440.91678240741</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R18" t="b">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.004997704258403783</v>
+        <v>0.005299105454911796</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.01204162</v>
+        <v>0.01183191</v>
       </c>
       <c r="F19" t="n">
-        <v>8540399072</v>
+        <v>8393353185</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>19988680</v>
+        <v>21898288</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01271105</v>
+        <v>0.01211884</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01195719</v>
+        <v>0.01183761</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0006301626399832819</v>
+        <v>-0.000213334567861646</v>
       </c>
       <c r="L19" t="n">
-        <v>-5.2628</v>
+        <v>-1.88845</v>
       </c>
       <c r="M19" t="n">
-        <v>709240298301.3969</v>
+        <v>709240425836.8521</v>
       </c>
       <c r="N19" t="n">
         <v>1142408526965.963</v>
@@ -2280,13 +2280,13 @@
         <v>46259.82847222222</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.004707088243604554</v>
+        <v>0.004634481886855332</v>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
@@ -2300,7 +2300,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2319,28 +2319,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8.9</v>
+        <v>8.83</v>
       </c>
       <c r="F20" t="n">
-        <v>8187966753</v>
+        <v>8118726601</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>399230</v>
+        <v>418695</v>
       </c>
       <c r="I20" t="n">
-        <v>9.029999999999999</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>8.880000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.08439936080502441</v>
+        <v>-0.07010463306942505</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.93935</v>
+        <v>-0.78849</v>
       </c>
       <c r="M20" t="n">
         <v>919857851.9</v>
@@ -2355,13 +2355,13 @@
         <v>46146.39930555555</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.004498104461779753</v>
+        <v>0.004470872335612828</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2424,31 +2424,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.20324</v>
+        <v>0.216625</v>
       </c>
       <c r="F21" t="n">
-        <v>7100935549</v>
+        <v>7572724921</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>321290636</v>
+        <v>576611230</v>
       </c>
       <c r="I21" t="n">
-        <v>0.213122</v>
+        <v>0.226335</v>
       </c>
       <c r="J21" t="n">
-        <v>0.197178</v>
+        <v>0.20527</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.009336099321796909</v>
+        <v>0.01193091</v>
       </c>
       <c r="L21" t="n">
-        <v>-4.38715</v>
+        <v>5.72779</v>
       </c>
       <c r="M21" t="n">
-        <v>34938629825.38779</v>
+        <v>34944206739.02777</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70147</v>
@@ -2460,13 +2460,13 @@
         <v>43102.66666666666</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R21" t="b">
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.003853521431999544</v>
+        <v>0.00414559031614725</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2529,34 +2529,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>335.52</v>
+        <v>331.29</v>
       </c>
       <c r="F22" t="n">
-        <v>6741819960</v>
+        <v>6653818690</v>
       </c>
       <c r="G22" t="n">
         <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>755674102</v>
+        <v>390668344</v>
       </c>
       <c r="I22" t="n">
-        <v>354.07</v>
+        <v>343.35</v>
       </c>
       <c r="J22" t="n">
-        <v>325.6</v>
+        <v>330.67</v>
       </c>
       <c r="K22" t="n">
-        <v>-19.23857209004734</v>
+        <v>-7.907244704522952</v>
       </c>
       <c r="L22" t="n">
-        <v>-5.41248</v>
+        <v>-2.39817</v>
       </c>
       <c r="M22" t="n">
-        <v>20093784.27165077</v>
+        <v>20094209.27165077</v>
       </c>
       <c r="N22" t="n">
-        <v>20093796.77165077</v>
+        <v>20094490.52165077</v>
       </c>
       <c r="O22" t="n">
         <v>3785.82</v>
@@ -2565,13 +2565,13 @@
         <v>43088.66666666666</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.003640574633832999</v>
+        <v>0.003598149373256409</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2634,34 +2634,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4.5</v>
+        <v>5.05</v>
       </c>
       <c r="F23" t="n">
-        <v>5881404513</v>
+        <v>6593983088</v>
       </c>
       <c r="G23" t="n">
         <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>1941085414</v>
+        <v>1918124956</v>
       </c>
       <c r="I23" t="n">
-        <v>4.76</v>
+        <v>5.17</v>
       </c>
       <c r="J23" t="n">
-        <v>4.09</v>
+        <v>4.45</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.2306575718520847</v>
+        <v>0.556465</v>
       </c>
       <c r="L23" t="n">
-        <v>-4.60616</v>
+        <v>12.66149</v>
       </c>
       <c r="M23" t="n">
-        <v>1307188691</v>
+        <v>1307268578</v>
       </c>
       <c r="N23" t="n">
-        <v>1307188713</v>
+        <v>1307268537</v>
       </c>
       <c r="O23" t="n">
         <v>20.44</v>
@@ -2670,13 +2670,13 @@
         <v>44577.59010416667</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>0.003130369228821503</v>
+        <v>0.003562502146942931</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2739,34 +2739,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>9.19</v>
+        <v>9.6</v>
       </c>
       <c r="F24" t="n">
-        <v>5703573466</v>
+        <v>5950098459</v>
       </c>
       <c r="G24" t="n">
         <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>1293846620</v>
+        <v>1045974012</v>
       </c>
       <c r="I24" t="n">
-        <v>9.58</v>
+        <v>9.91</v>
       </c>
       <c r="J24" t="n">
-        <v>8.81</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.3608256045277365</v>
+        <v>0.419204</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.73341</v>
+        <v>4.53077</v>
       </c>
       <c r="M24" t="n">
-        <v>620592422.6104751</v>
+        <v>620576422.6104751</v>
       </c>
       <c r="N24" t="n">
-        <v>887840418.9163101</v>
+        <v>887824418.9163101</v>
       </c>
       <c r="O24" t="n">
         <v>44.92</v>
@@ -2775,13 +2775,13 @@
         <v>44318.89240740741</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R24" t="b">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.003024919748951515</v>
+        <v>0.003178906088366766</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2844,34 +2844,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>69.09999999999999</v>
+        <v>69.62</v>
       </c>
       <c r="F25" t="n">
-        <v>5364962731</v>
+        <v>5403606227</v>
       </c>
       <c r="G25" t="n">
         <v>24</v>
       </c>
       <c r="H25" t="n">
-        <v>1161909033</v>
+        <v>1096861662</v>
       </c>
       <c r="I25" t="n">
-        <v>69.45</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>59.11</v>
+        <v>69.27</v>
       </c>
       <c r="K25" t="n">
-        <v>6.56</v>
+        <v>-2.348240170860535</v>
       </c>
       <c r="L25" t="n">
-        <v>10.72198</v>
+        <v>-3.35693</v>
       </c>
       <c r="M25" t="n">
-        <v>77644854.4984657</v>
+        <v>77645954.50023881</v>
       </c>
       <c r="N25" t="n">
-        <v>77642716.99309745</v>
+        <v>77648985.75854112</v>
       </c>
       <c r="O25" t="n">
         <v>410.26</v>
@@ -2880,13 +2880,13 @@
         <v>44325.80077546297</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.002824131829819799</v>
+        <v>0.002853331821182805</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2949,34 +2949,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.999875</v>
+        <v>0.999688</v>
       </c>
       <c r="F26" t="n">
-        <v>4896232481</v>
+        <v>4902375830</v>
       </c>
       <c r="G26" t="n">
         <v>25</v>
       </c>
       <c r="H26" t="n">
-        <v>75530601</v>
+        <v>52483485</v>
       </c>
       <c r="I26" t="n">
-        <v>1.001</v>
+        <v>0.999965</v>
       </c>
       <c r="J26" t="n">
-        <v>0.999507</v>
+        <v>0.999373</v>
       </c>
       <c r="K26" t="n">
-        <v>0.00017841</v>
+        <v>-0.000256870725562353</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01751</v>
+        <v>-0.02227</v>
       </c>
       <c r="M26" t="n">
-        <v>4896842976.860238</v>
+        <v>4903958331.263182</v>
       </c>
       <c r="N26" t="n">
-        <v>4898170210.675478</v>
+        <v>4904836849.481181</v>
       </c>
       <c r="O26" t="n">
         <v>1.034</v>
@@ -2985,13 +2985,13 @@
         <v>46000.38208333333</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R26" t="b">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.002546186207299625</v>
+        <v>0.002554722418087756</v>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
@@ -3005,353 +3005,353 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>dai</t>
+          <t>canton-network</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>dai</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Dai</t>
+          <t>Canton</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.99993</v>
+        <v>0.121604</v>
       </c>
       <c r="F27" t="n">
-        <v>4600156531</v>
+        <v>4825964443</v>
       </c>
       <c r="G27" t="n">
         <v>26</v>
       </c>
       <c r="H27" t="n">
-        <v>237007676</v>
+        <v>33356400</v>
       </c>
       <c r="I27" t="n">
+        <v>0.125062</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.108829</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.0120833</v>
+      </c>
+      <c r="L27" t="n">
+        <v>11.14264</v>
+      </c>
+      <c r="M27" t="n">
+        <v>39682485824.63093</v>
+      </c>
+      <c r="N27" t="n">
+        <v>39682485824.63093</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.194152</v>
+      </c>
+      <c r="P27" s="1" t="n">
+        <v>46056.00148148148</v>
+      </c>
+      <c r="Q27" s="1" t="n">
+        <v>46290.59189814814</v>
+      </c>
+      <c r="R27" t="b">
         <v>1</v>
       </c>
-      <c r="J27" t="n">
-        <v>0.999552</v>
-      </c>
-      <c r="K27" t="n">
-        <v>-3.1086359221111e-05</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0.0058</v>
-      </c>
-      <c r="M27" t="n">
-        <v>4600480382.490121</v>
-      </c>
-      <c r="N27" t="n">
-        <v>4600480382.490121</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P27" s="1" t="n">
-        <v>43902.79363425926</v>
-      </c>
-      <c r="Q27" s="1" t="n">
-        <v>46289.57523148148</v>
-      </c>
-      <c r="R27" t="b">
-        <v>0</v>
-      </c>
       <c r="S27" t="n">
-        <v>0.002370620379755953</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Stablecoin</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Colateralizada por cripto</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>N/A (token, colateral cripto)</t>
-        </is>
-      </c>
-      <c r="W27" t="n">
-        <v>2017</v>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>makerdao.com</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>Estabilidad de valor descentralizada</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>Token ERC-20 sobre Ethereum</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>Stablecoin descentralizada, generada mediante colateral cripto sobrecolateralizado.</t>
-        </is>
-      </c>
+        <v>0.002509200121757961</v>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>avalanche-2</t>
+          <t>dai</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>avax</t>
+          <t>dai</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Dai</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>10.24</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>4534909728</v>
+        <v>4587353880</v>
       </c>
       <c r="G28" t="n">
         <v>27</v>
       </c>
       <c r="H28" t="n">
-        <v>543789681</v>
+        <v>223033455</v>
       </c>
       <c r="I28" t="n">
-        <v>10.81</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>9.98</v>
+        <v>0.999431</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.4021845510378839</v>
+        <v>0.00018724</v>
       </c>
       <c r="L28" t="n">
-        <v>-3.71833</v>
+        <v>0.01194</v>
       </c>
       <c r="M28" t="n">
-        <v>443057691.2148384</v>
+        <v>4588238149.248935</v>
       </c>
       <c r="N28" t="n">
-        <v>469726458.1779858</v>
+        <v>4586572939.160765</v>
       </c>
       <c r="O28" t="n">
-        <v>144.96</v>
+        <v>1.22</v>
       </c>
       <c r="P28" s="1" t="n">
-        <v>44521.26314814815</v>
+        <v>43902.79363425926</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R28" t="b">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.002331930614635639</v>
+        <v>0.002367047215198299</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>Plataforma de contratos inteligentes</t>
+          <t>Stablecoin</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>Layer 1</t>
+          <t>Colateralizada por cripto</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Proof of Stake (Avalanche consensus)</t>
+          <t>N/A (token, colateral cripto)</t>
         </is>
       </c>
       <c r="W28" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>avax.network</t>
+          <t>makerdao.com</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>Subredes personalizadas para empresas</t>
+          <t>Estabilidad de valor descentralizada</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>Blockchain propia (Layer 1)</t>
+          <t>Token ERC-20 sobre Ethereum</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Permite crear subredes (subnets) personalizadas para casos de uso específicos.</t>
+          <t>Stablecoin descentralizada, generada mediante colateral cripto sobrecolateralizado.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>usd1-wlfi</t>
+          <t>avalanche-2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>usd1</t>
+          <t>avax</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>USD1</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.999229</v>
+        <v>10.31</v>
       </c>
       <c r="F29" t="n">
-        <v>4405106258</v>
+        <v>4564180526</v>
       </c>
       <c r="G29" t="n">
         <v>28</v>
       </c>
       <c r="H29" t="n">
-        <v>1238503775</v>
+        <v>683104943</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9995810000000001</v>
+        <v>10.73</v>
       </c>
       <c r="J29" t="n">
-        <v>0.999151</v>
+        <v>10.08</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.1375902725284e-05</v>
+        <v>0.03427721</v>
       </c>
       <c r="L29" t="n">
-        <v>0.00131</v>
+        <v>0.1843</v>
       </c>
       <c r="M29" t="n">
-        <v>4408506663.047887</v>
+        <v>443058607.71027</v>
       </c>
       <c r="N29" t="n">
-        <v>4408506663.047887</v>
+        <v>469727409.7648715</v>
       </c>
       <c r="O29" t="n">
-        <v>1.048</v>
+        <v>144.96</v>
       </c>
       <c r="P29" s="1" t="n">
-        <v>46212.42696759259</v>
+        <v>44521.26314814815</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R29" t="b">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.002254960318235035</v>
-      </c>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
+        <v>0.002353241625100278</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Plataforma de contratos inteligentes</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Layer 1</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Proof of Stake (Avalanche consensus)</t>
+        </is>
+      </c>
+      <c r="W29" t="n">
+        <v>2020</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>avax.network</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Subredes personalizadas para empresas</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Layer 1)</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>Permite crear subredes (subnets) personalizadas para casos de uso específicos.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>canton-network</t>
+          <t>sui</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>sui</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Canton</t>
+          <t>Sui</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.109057</v>
+        <v>1.11</v>
       </c>
       <c r="F30" t="n">
-        <v>4326760553</v>
+        <v>4551577017</v>
       </c>
       <c r="G30" t="n">
         <v>29</v>
       </c>
       <c r="H30" t="n">
-        <v>18129687</v>
+        <v>1472217052</v>
       </c>
       <c r="I30" t="n">
-        <v>0.111695</v>
+        <v>1.16</v>
       </c>
       <c r="J30" t="n">
-        <v>0.106336</v>
+        <v>0.986696</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.002755490892089763</v>
+        <v>0.109909</v>
       </c>
       <c r="L30" t="n">
-        <v>-2.56513</v>
+        <v>10.95681</v>
       </c>
       <c r="M30" t="n">
-        <v>39674466050.23323</v>
+        <v>4096537146.540959</v>
       </c>
       <c r="N30" t="n">
-        <v>39674466050.23323</v>
+        <v>10000000000</v>
       </c>
       <c r="O30" t="n">
-        <v>0.194152</v>
+        <v>5.35</v>
       </c>
       <c r="P30" s="1" t="n">
-        <v>46056.00148148148</v>
+        <v>45661.62243055556</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>0.002208503223247018</v>
+        <v>0.002345733049559132</v>
       </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
@@ -3365,187 +3365,187 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>hedera-hashgraph</t>
+          <t>usd1-wlfi</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>hbar</t>
+          <t>usd1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Hedera</t>
+          <t>USD1</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.091989</v>
+        <v>0.999381</v>
       </c>
       <c r="F31" t="n">
-        <v>4032020194</v>
+        <v>4405717013</v>
       </c>
       <c r="G31" t="n">
         <v>30</v>
       </c>
       <c r="H31" t="n">
-        <v>141640161</v>
+        <v>1069576000</v>
       </c>
       <c r="I31" t="n">
-        <v>0.09438000000000001</v>
+        <v>0.9995039999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>0.08828999999999999</v>
+        <v>0.998911</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.002055540979405135</v>
+        <v>0.00014682</v>
       </c>
       <c r="L31" t="n">
-        <v>-2.06873</v>
+        <v>0.01939</v>
       </c>
       <c r="M31" t="n">
-        <v>43831706399.39579</v>
+        <v>4408506662.536045</v>
       </c>
       <c r="N31" t="n">
-        <v>50000000000</v>
+        <v>4408506662.535317</v>
       </c>
       <c r="O31" t="n">
-        <v>0.569229</v>
+        <v>1.048</v>
       </c>
       <c r="P31" s="1" t="n">
-        <v>44454.11143518519</v>
+        <v>46212.42696759259</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R31" t="b">
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0.002033729368638585</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Infraestructura empresarial</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>DLT</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Hashgraph (aBFT)</t>
-        </is>
-      </c>
-      <c r="W31" t="n">
-        <v>2019</v>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>hedera.com</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>Aplicaciones empresariales y tokenización</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>Red propia (hashgraph, no blockchain tradicional)</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>Gobernada por un consejo de grandes empresas globales.</t>
-        </is>
-      </c>
+        <v>0.002258836546492736</v>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>sui</t>
+          <t>hedera-hashgraph</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>sui</t>
+          <t>hbar</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sui</t>
+          <t>Hedera</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.983869</v>
+        <v>0.093875</v>
       </c>
       <c r="F32" t="n">
-        <v>4030455436</v>
+        <v>4113889605</v>
       </c>
       <c r="G32" t="n">
         <v>31</v>
       </c>
       <c r="H32" t="n">
-        <v>871339503</v>
+        <v>159277487</v>
       </c>
       <c r="I32" t="n">
-        <v>1.011</v>
+        <v>0.096666</v>
       </c>
       <c r="J32" t="n">
-        <v>0.936868</v>
+        <v>0.09114899999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.0218399751267605</v>
+        <v>0.00050433</v>
       </c>
       <c r="L32" t="n">
-        <v>-2.13748</v>
+        <v>0.6450399999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>4096537146.540959</v>
+        <v>43831706398.99841</v>
       </c>
       <c r="N32" t="n">
-        <v>10000000000</v>
+        <v>50000000000</v>
       </c>
       <c r="O32" t="n">
-        <v>5.35</v>
+        <v>0.569229</v>
       </c>
       <c r="P32" s="1" t="n">
-        <v>45661.62243055556</v>
+        <v>44454.11143518519</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R32" t="b">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.002032801505253614</v>
-      </c>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
+        <v>0.002084979556511231</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Infraestructura empresarial</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>DLT</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Hashgraph (aBFT)</t>
+        </is>
+      </c>
+      <c r="W32" t="n">
+        <v>2019</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>hedera.com</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>Aplicaciones empresariales y tokenización</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>Red propia (hashgraph, no blockchain tradicional)</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>Gobernada por un consejo de grandes empresas globales.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3567,31 +3567,31 @@
         <v>1.41</v>
       </c>
       <c r="F33" t="n">
-        <v>3956280213</v>
+        <v>3975394185</v>
       </c>
       <c r="G33" t="n">
         <v>32</v>
       </c>
       <c r="H33" t="n">
-        <v>59204372</v>
+        <v>62915494</v>
       </c>
       <c r="I33" t="n">
         <v>1.44</v>
       </c>
       <c r="J33" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.03317149284147103</v>
+        <v>0.00058374</v>
       </c>
       <c r="L33" t="n">
-        <v>-2.33833</v>
+        <v>-0.00125</v>
       </c>
       <c r="M33" t="n">
-        <v>2812142972.624207</v>
+        <v>2813281722.98769</v>
       </c>
       <c r="N33" t="n">
-        <v>5254679247.355583</v>
+        <v>5255255878.351041</v>
       </c>
       <c r="O33" t="n">
         <v>8.25</v>
@@ -3600,13 +3600,13 @@
         <v>45457.69225694444</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R33" t="b">
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.001988817404521246</v>
+        <v>0.002002470524846102</v>
       </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
@@ -3620,7 +3620,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3639,34 +3639,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5.69e-06</v>
+        <v>5.82e-06</v>
       </c>
       <c r="F34" t="n">
-        <v>3351592860</v>
+        <v>3427851999</v>
       </c>
       <c r="G34" t="n">
         <v>33</v>
       </c>
       <c r="H34" t="n">
-        <v>144176003</v>
+        <v>111035612</v>
       </c>
       <c r="I34" t="n">
-        <v>5.98e-06</v>
+        <v>5.97e-06</v>
       </c>
       <c r="J34" t="n">
-        <v>5.56e-06</v>
+        <v>5.72e-06</v>
       </c>
       <c r="K34" t="n">
-        <v>-2.77763758295e-07</v>
+        <v>9.7936e-08</v>
       </c>
       <c r="L34" t="n">
-        <v>-4.60362</v>
+        <v>1.73752</v>
       </c>
       <c r="M34" t="n">
-        <v>589238967875888.2</v>
+        <v>589238965647120.2</v>
       </c>
       <c r="N34" t="n">
-        <v>589496069650408</v>
+        <v>589496067422631</v>
       </c>
       <c r="O34" t="n">
         <v>8.616e-05</v>
@@ -3675,13 +3675,13 @@
         <v>44496.82980324074</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R34" t="b">
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0.001630252531100634</v>
+        <v>0.001676270744646382</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3744,28 +3744,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>288.23</v>
+        <v>300.65</v>
       </c>
       <c r="F35" t="n">
-        <v>3268453797</v>
+        <v>3409201890</v>
       </c>
       <c r="G35" t="n">
         <v>34</v>
       </c>
       <c r="H35" t="n">
-        <v>348005096</v>
+        <v>384273924</v>
       </c>
       <c r="I35" t="n">
-        <v>311.88</v>
+        <v>311.57</v>
       </c>
       <c r="J35" t="n">
-        <v>278.69</v>
+        <v>285.31</v>
       </c>
       <c r="K35" t="n">
-        <v>-21.06650862142038</v>
+        <v>11.87</v>
       </c>
       <c r="L35" t="n">
-        <v>-6.79133</v>
+        <v>4.08622</v>
       </c>
       <c r="M35" t="n">
         <v>11339645.9251</v>
@@ -3780,13 +3780,13 @@
         <v>45358.44833333333</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.001580953091558853</v>
+        <v>0.001665159890337705</v>
       </c>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
@@ -3800,187 +3800,187 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>global-dollar</t>
+          <t>crypto-com-chain</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>usdg</t>
+          <t>cro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Global Dollar</t>
+          <t>Cronos</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.999923</v>
+        <v>0.065552</v>
       </c>
       <c r="F36" t="n">
-        <v>3254497247</v>
+        <v>3260323161</v>
       </c>
       <c r="G36" t="n">
         <v>35</v>
       </c>
       <c r="H36" t="n">
-        <v>945084427</v>
+        <v>18833597</v>
       </c>
       <c r="I36" t="n">
+        <v>0.06647599999999999</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.061944</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.00373544</v>
+      </c>
+      <c r="L36" t="n">
+        <v>5.9134</v>
+      </c>
+      <c r="M36" t="n">
+        <v>49743066210.47476</v>
+      </c>
+      <c r="N36" t="n">
+        <v>98943108426.03091</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.891544</v>
+      </c>
+      <c r="P36" s="1" t="n">
+        <v>44523.66666666666</v>
+      </c>
+      <c r="Q36" s="1" t="n">
+        <v>46290.59189814814</v>
+      </c>
+      <c r="R36" t="b">
         <v>1</v>
       </c>
-      <c r="J36" t="n">
-        <v>0.999736</v>
-      </c>
-      <c r="K36" t="n">
-        <v>-4.532150067571e-05</v>
-      </c>
-      <c r="L36" t="n">
-        <v>-0.00792</v>
-      </c>
-      <c r="M36" t="n">
-        <v>3254747890.046411</v>
-      </c>
-      <c r="N36" t="n">
-        <v>3254747890.046411</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="P36" s="1" t="n">
-        <v>45686.67436342593</v>
-      </c>
-      <c r="Q36" s="1" t="n">
-        <v>46289.57523148148</v>
-      </c>
-      <c r="R36" t="b">
-        <v>0</v>
-      </c>
       <c r="S36" t="n">
-        <v>0.00157267719731481</v>
-      </c>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
+        <v>0.001576464973456518</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Token de exchange</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Layer 1 (Cronos)</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Proof of Stake</t>
+        </is>
+      </c>
+      <c r="W36" t="n">
+        <v>2018</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>cronos.org</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Pagos y DeFi en el ecosistema Crypto.com</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Cronos, EVM-compatible)</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>Token nativo del ecosistema Crypto.com y su red Cronos.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>crypto-com-chain</t>
+          <t>global-dollar</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>cro</t>
+          <t>usdg</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Cronos</t>
+          <t>Global Dollar</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.061385</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>3053335366</v>
+        <v>3258135197</v>
       </c>
       <c r="G37" t="n">
         <v>36</v>
       </c>
       <c r="H37" t="n">
-        <v>13823496</v>
+        <v>903819770</v>
       </c>
       <c r="I37" t="n">
-        <v>0.06524199999999999</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>0.060291</v>
+        <v>0.999507</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.003689313612499391</v>
+        <v>0.00020004</v>
       </c>
       <c r="L37" t="n">
-        <v>-5.73558</v>
+        <v>0.01107</v>
       </c>
       <c r="M37" t="n">
-        <v>49741083117.23193</v>
+        <v>3258247890.046372</v>
       </c>
       <c r="N37" t="n">
-        <v>98941038276.2905</v>
+        <v>3258247890.046372</v>
       </c>
       <c r="O37" t="n">
-        <v>0.891544</v>
+        <v>1.65</v>
       </c>
       <c r="P37" s="1" t="n">
-        <v>44523.66666666666</v>
+        <v>45686.67436342593</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.001453393101095557</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Token de exchange</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Layer 1 (Cronos)</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Proof of Stake</t>
-        </is>
-      </c>
-      <c r="W37" t="n">
-        <v>2018</v>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>cronos.org</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>Pagos y DeFi en el ecosistema Crypto.com</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Cronos, EVM-compatible)</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>Token nativo del ecosistema Crypto.com y su red Cronos.</t>
-        </is>
-      </c>
+        <v>0.001575161487818089</v>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3999,28 +3999,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1.048</v>
+        <v>1.18</v>
       </c>
       <c r="F38" t="n">
-        <v>2838641352</v>
+        <v>3192057316</v>
       </c>
       <c r="G38" t="n">
         <v>37</v>
       </c>
       <c r="H38" t="n">
-        <v>23569633</v>
+        <v>53787879</v>
       </c>
       <c r="I38" t="n">
-        <v>1.094</v>
+        <v>1.19</v>
       </c>
       <c r="J38" t="n">
-        <v>0.935707</v>
+        <v>0.890482</v>
       </c>
       <c r="K38" t="n">
-        <v>0.087975</v>
+        <v>0.129389</v>
       </c>
       <c r="L38" t="n">
-        <v>9.20782</v>
+        <v>12.39428</v>
       </c>
       <c r="M38" t="n">
         <v>2708142280.000001</v>
@@ -4029,19 +4029,19 @@
         <v>10000000000</v>
       </c>
       <c r="O38" t="n">
-        <v>1.094</v>
+        <v>1.19</v>
       </c>
       <c r="P38" s="1" t="n">
-        <v>46289.21423611111</v>
+        <v>46290.58877314815</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R38" t="b">
         <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>0.001326084779576762</v>
+        <v>0.001535795406428585</v>
       </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
@@ -4055,68 +4055,68 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>memecore</t>
+          <t>paypal-usd</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>pyusd</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>MemeCore</t>
+          <t>PayPal USD</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1.22</v>
+        <v>0.99984</v>
       </c>
       <c r="F39" t="n">
-        <v>2768666425</v>
+        <v>2697623562</v>
       </c>
       <c r="G39" t="n">
         <v>38</v>
       </c>
       <c r="H39" t="n">
-        <v>1077781</v>
+        <v>67238143</v>
       </c>
       <c r="I39" t="n">
-        <v>1.27</v>
+        <v>0.999999</v>
       </c>
       <c r="J39" t="n">
-        <v>1.19</v>
+        <v>0.99947</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.04265830950945704</v>
+        <v>-7.6949450457109e-05</v>
       </c>
       <c r="L39" t="n">
-        <v>-3.33534</v>
+        <v>-0.00537</v>
       </c>
       <c r="M39" t="n">
-        <v>2278209780.488189</v>
+        <v>2698087718.884173</v>
       </c>
       <c r="N39" t="n">
-        <v>5417784107.057606</v>
+        <v>2687552417.224173</v>
       </c>
       <c r="O39" t="n">
-        <v>5.64</v>
+        <v>1.021</v>
       </c>
       <c r="P39" s="1" t="n">
-        <v>46205.17638888889</v>
+        <v>45222.61454861111</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001284591352075937</v>
+        <v>0.001241235122304427</v>
       </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
@@ -4130,68 +4130,68 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>paypal-usd</t>
+          <t>memecore</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>pyusd</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>PayPal USD</t>
+          <t>MemeCore</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.999952</v>
+        <v>1.18</v>
       </c>
       <c r="F40" t="n">
-        <v>2681333732</v>
+        <v>2688174131</v>
       </c>
       <c r="G40" t="n">
         <v>39</v>
       </c>
       <c r="H40" t="n">
-        <v>59767782</v>
+        <v>890043</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="J40" t="n">
-        <v>0.999715</v>
+        <v>1.18</v>
       </c>
       <c r="K40" t="n">
-        <v>4.323e-05</v>
+        <v>-0.0425971033575745</v>
       </c>
       <c r="L40" t="n">
-        <v>0.00223</v>
+        <v>-3.42038</v>
       </c>
       <c r="M40" t="n">
-        <v>2681462176.707304</v>
+        <v>2278580063.729613</v>
       </c>
       <c r="N40" t="n">
-        <v>2681462176.707304</v>
+        <v>5418169810.236838</v>
       </c>
       <c r="O40" t="n">
-        <v>1.021</v>
+        <v>5.64</v>
       </c>
       <c r="P40" s="1" t="n">
-        <v>45222.61454861111</v>
+        <v>46205.17638888889</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R40" t="b">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.001232805192078266</v>
+        <v>0.001235605597504283</v>
       </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
@@ -4205,7 +4205,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4224,28 +4224,28 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4271.37</v>
+        <v>4264.36</v>
       </c>
       <c r="F41" t="n">
-        <v>2660311611</v>
+        <v>2655860296</v>
       </c>
       <c r="G41" t="n">
         <v>40</v>
       </c>
       <c r="H41" t="n">
-        <v>217328082</v>
+        <v>223474158</v>
       </c>
       <c r="I41" t="n">
-        <v>4301.85</v>
+        <v>4309.24</v>
       </c>
       <c r="J41" t="n">
-        <v>4248.02</v>
+        <v>4248.16</v>
       </c>
       <c r="K41" t="n">
-        <v>-18.37164533468513</v>
+        <v>-5.299238695430176</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.43368</v>
+        <v>-0.14254</v>
       </c>
       <c r="M41" t="n">
         <v>622823.6595320001</v>
@@ -4260,13 +4260,13 @@
         <v>46050.66666666666</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R41" t="b">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.001220339586310258</v>
+        <v>0.001216354540427906</v>
       </c>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
@@ -4280,248 +4280,248 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>okb</t>
+          <t>ondo-finance</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>okb</t>
+          <t>ondo</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>OKB</t>
+          <t>Ondo</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>119.04</v>
+        <v>0.542535</v>
       </c>
       <c r="F42" t="n">
-        <v>2499814238</v>
+        <v>2639188514</v>
       </c>
       <c r="G42" t="n">
         <v>41</v>
       </c>
       <c r="H42" t="n">
-        <v>39652791</v>
+        <v>1064033883</v>
       </c>
       <c r="I42" t="n">
-        <v>121.52</v>
+        <v>0.578933</v>
       </c>
       <c r="J42" t="n">
-        <v>117.52</v>
+        <v>0.49461</v>
       </c>
       <c r="K42" t="n">
-        <v>-2.843280796039352</v>
+        <v>0.03441119</v>
       </c>
       <c r="L42" t="n">
-        <v>-2.29673</v>
+        <v>7.86321</v>
       </c>
       <c r="M42" t="n">
-        <v>21000000</v>
+        <v>4869330647</v>
       </c>
       <c r="N42" t="n">
-        <v>21000000</v>
+        <v>10000000000</v>
       </c>
       <c r="O42" t="n">
-        <v>228.74</v>
+        <v>2.14</v>
       </c>
       <c r="P42" s="1" t="n">
-        <v>45934.66666666666</v>
+        <v>45641.69166666667</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42" t="n">
-        <v>0.001125168552967867</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Token de exchange</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Utilidad</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>N/A (token de exchange)</t>
-        </is>
-      </c>
-      <c r="W42" t="n">
-        <v>2019</v>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>okx.com</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>Beneficios dentro del exchange OKX</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>Token ERC-20 sobre Ethereum</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>Token nativo del exchange OKX, usado para descuentos y beneficios.</t>
-        </is>
-      </c>
+        <v>0.00120642227993184</v>
+      </c>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>hashnote-usyc</t>
+          <t>okb</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>usyc</t>
+          <t>okb</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Circle USYC</t>
+          <t>OKB</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1.14</v>
+        <v>119.99</v>
       </c>
       <c r="F43" t="n">
-        <v>2432956202</v>
+        <v>2519828086</v>
       </c>
       <c r="G43" t="n">
         <v>42</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>27685004</v>
       </c>
       <c r="I43" t="n">
-        <v>1.14</v>
+        <v>121.16</v>
       </c>
       <c r="J43" t="n">
-        <v>1.14</v>
+        <v>118.89</v>
       </c>
       <c r="K43" t="n">
-        <v>0.00010526</v>
+        <v>0.970076</v>
       </c>
       <c r="L43" t="n">
-        <v>0.00925</v>
+        <v>0.83939</v>
       </c>
       <c r="M43" t="n">
-        <v>2137408897.697903</v>
+        <v>21000000</v>
       </c>
       <c r="N43" t="n">
-        <v>2137408897.697903</v>
+        <v>21000000</v>
       </c>
       <c r="O43" t="n">
-        <v>1.14</v>
+        <v>228.74</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>46289.54166666666</v>
+        <v>45934.66666666666</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R43" t="b">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.00108552336591946</v>
-      </c>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr"/>
+        <v>0.001135312972971254</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Token de exchange</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Utilidad</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>N/A (token de exchange)</t>
+        </is>
+      </c>
+      <c r="W43" t="n">
+        <v>2019</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>okx.com</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>Beneficios dentro del exchange OKX</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>Token ERC-20 sobre Ethereum</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>Token nativo del exchange OKX, usado para descuentos y beneficios.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ripple-usd</t>
+          <t>ethena</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>rlusd</t>
+          <t>ena</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ripple USD</t>
+          <t>Ethena</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>0.246882</v>
       </c>
       <c r="F44" t="n">
-        <v>2373693267</v>
+        <v>2492927210</v>
       </c>
       <c r="G44" t="n">
         <v>43</v>
       </c>
       <c r="H44" t="n">
-        <v>326252990</v>
+        <v>802615669</v>
       </c>
       <c r="I44" t="n">
+        <v>0.249038</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.213698</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.02900795</v>
+      </c>
+      <c r="L44" t="n">
+        <v>13.22522</v>
+      </c>
+      <c r="M44" t="n">
+        <v>10095312500</v>
+      </c>
+      <c r="N44" t="n">
+        <v>15000000000</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P44" s="1" t="n">
+        <v>45393.21892361111</v>
+      </c>
+      <c r="Q44" s="1" t="n">
+        <v>46290.59189814814</v>
+      </c>
+      <c r="R44" t="b">
         <v>1</v>
       </c>
-      <c r="J44" t="n">
-        <v>0.999799</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0.00010926</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0.01618</v>
-      </c>
-      <c r="M44" t="n">
-        <v>2373469066.207216</v>
-      </c>
-      <c r="N44" t="n">
-        <v>2373469066.207212</v>
-      </c>
-      <c r="O44" t="n">
-        <v>1.073</v>
-      </c>
-      <c r="P44" s="1" t="n">
-        <v>45652.11518518518</v>
-      </c>
-      <c r="Q44" s="1" t="n">
-        <v>46289.57523148148</v>
-      </c>
-      <c r="R44" t="b">
-        <v>0</v>
-      </c>
       <c r="S44" t="n">
-        <v>0.001050381888788535</v>
+        <v>0.0011192867012743</v>
       </c>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
@@ -4535,68 +4535,68 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ondo-finance</t>
+          <t>hashnote-usyc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ondo</t>
+          <t>usyc</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Ondo</t>
+          <t>Circle USYC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.484279</v>
+        <v>1.14</v>
       </c>
       <c r="F45" t="n">
-        <v>2358114181</v>
+        <v>2433710271</v>
       </c>
       <c r="G45" t="n">
         <v>44</v>
       </c>
       <c r="H45" t="n">
-        <v>593027601</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0.470252</v>
+        <v>1.14</v>
       </c>
       <c r="J45" t="n">
-        <v>0.406139</v>
+        <v>1.14</v>
       </c>
       <c r="K45" t="n">
-        <v>0.054809</v>
+        <v>0.00034072</v>
       </c>
       <c r="L45" t="n">
-        <v>12.54924</v>
+        <v>0.02993</v>
       </c>
       <c r="M45" t="n">
-        <v>4869330647</v>
+        <v>2137431562.141903</v>
       </c>
       <c r="N45" t="n">
-        <v>10000000000</v>
+        <v>2137431562.141903</v>
       </c>
       <c r="O45" t="n">
-        <v>2.14</v>
+        <v>1.14</v>
       </c>
       <c r="P45" s="1" t="n">
-        <v>45641.69166666667</v>
+        <v>46290.53483796296</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.00104114387021268</v>
+        <v>0.001084008045163773</v>
       </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
@@ -4610,68 +4610,68 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>blackrock-usd-institutional-digital-liquidity-fund</t>
+          <t>ripple-usd</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>buidl</t>
+          <t>rlusd</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>BlackRock USD Institutional Digital Liquidity Fund</t>
+          <t>Ripple USD</t>
         </is>
       </c>
       <c r="E46" t="n">
         <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>2290219820</v>
+        <v>2412736667</v>
       </c>
       <c r="G46" t="n">
         <v>45</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>330311005</v>
       </c>
       <c r="I46" t="n">
         <v>1</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0.999578</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>7.264e-05</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>-0.00149</v>
       </c>
       <c r="M46" t="n">
-        <v>2290219819.817649</v>
+        <v>2412372908.017206</v>
       </c>
       <c r="N46" t="n">
-        <v>2290219819.817649</v>
+        <v>2412372908.017201</v>
       </c>
       <c r="O46" t="n">
-        <v>1</v>
+        <v>1.073</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>45699.87511574074</v>
+        <v>45652.11518518518</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R46" t="b">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.001000884167678537</v>
+        <v>0.001071512962246461</v>
       </c>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
@@ -4685,68 +4685,68 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ondo-us-dollar-yield</t>
+          <t>blackrock-usd-institutional-digital-liquidity-fund</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>usdy</t>
+          <t>buidl</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Ondo US Dollar Yield</t>
+          <t>BlackRock USD Institutional Digital Liquidity Fund</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>2268846569</v>
+        <v>2289899848</v>
       </c>
       <c r="G47" t="n">
         <v>46</v>
       </c>
       <c r="H47" t="n">
-        <v>5646269</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.000774468384536986</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0.03233</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>1980718587.224123</v>
+        <v>2289899848.277649</v>
       </c>
       <c r="N47" t="n">
-        <v>1980723621.969325</v>
+        <v>2289899848.277649</v>
       </c>
       <c r="O47" t="n">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>45377.89175925926</v>
+        <v>45699.87511574074</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R47" t="b">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0.0009882103503721547</v>
+        <v>0.0009983325856786683</v>
       </c>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
@@ -4760,68 +4760,68 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>mantle</t>
+          <t>ondo-us-dollar-yield</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>mnt</t>
+          <t>usdy</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Mantle</t>
+          <t>Ondo US Dollar Yield</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.684297</v>
+        <v>1.15</v>
       </c>
       <c r="F48" t="n">
-        <v>2259748669</v>
+        <v>2274418100</v>
       </c>
       <c r="G48" t="n">
         <v>47</v>
       </c>
       <c r="H48" t="n">
-        <v>65324506</v>
+        <v>2925391</v>
       </c>
       <c r="I48" t="n">
-        <v>0.697646</v>
+        <v>1.15</v>
       </c>
       <c r="J48" t="n">
-        <v>0.644684</v>
+        <v>1.14</v>
       </c>
       <c r="K48" t="n">
-        <v>0.01729176</v>
+        <v>0.00066</v>
       </c>
       <c r="L48" t="n">
-        <v>2.50488</v>
+        <v>0.06019</v>
       </c>
       <c r="M48" t="n">
-        <v>3302294382.53684</v>
+        <v>1984440201.171045</v>
       </c>
       <c r="N48" t="n">
-        <v>6219316794.889999</v>
+        <v>1984440201.171045</v>
       </c>
       <c r="O48" t="n">
-        <v>2.86</v>
+        <v>1.26</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>45938.71164351852</v>
+        <v>45377.89175925926</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R48" t="b">
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0.0009828155172477162</v>
+        <v>0.0009891092912479678</v>
       </c>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
@@ -4835,428 +4835,428 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ethena</t>
+          <t>aave</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ena</t>
+          <t>aave</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Ethena</t>
+          <t>Aave</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.21651</v>
+        <v>146.95</v>
       </c>
       <c r="F49" t="n">
-        <v>2185736780</v>
+        <v>2266346209</v>
       </c>
       <c r="G49" t="n">
         <v>48</v>
       </c>
       <c r="H49" t="n">
-        <v>457659961</v>
+        <v>314980178</v>
       </c>
       <c r="I49" t="n">
-        <v>0.214238</v>
+        <v>149.93</v>
       </c>
       <c r="J49" t="n">
-        <v>0.199436</v>
+        <v>141.56</v>
       </c>
       <c r="K49" t="n">
-        <v>0.00608209</v>
+        <v>4.68</v>
       </c>
       <c r="L49" t="n">
-        <v>3.21791</v>
+        <v>3.04679</v>
       </c>
       <c r="M49" t="n">
-        <v>10095312500</v>
+        <v>15429094.79157746</v>
       </c>
       <c r="N49" t="n">
-        <v>15000000000</v>
+        <v>16000000</v>
       </c>
       <c r="O49" t="n">
-        <v>1.52</v>
+        <v>661.6900000000001</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>45393.21892361111</v>
+        <v>44334.55554398148</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R49" t="b">
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>0.0009389282695994172</v>
-      </c>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr"/>
-      <c r="Y49" t="inlineStr"/>
-      <c r="Z49" t="inlineStr"/>
-      <c r="AA49" t="inlineStr"/>
+        <v>0.0009843004397342031</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>DeFi</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Préstamos</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>N/A (token de gobernanza)</t>
+        </is>
+      </c>
+      <c r="W49" t="n">
+        <v>2017</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>aave.com</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>Préstamos y créditos descentralizados</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>Token ERC-20 sobre Ethereum</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>Pionero en préstamos y créditos flash (flash loans) dentro de DeFi.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>mantle</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>mnt</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Aave</t>
+          <t>Mantle</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>140.97</v>
+        <v>0.665276</v>
       </c>
       <c r="F50" t="n">
-        <v>2174986020</v>
+        <v>2196711123</v>
       </c>
       <c r="G50" t="n">
         <v>49</v>
       </c>
       <c r="H50" t="n">
-        <v>326267479</v>
+        <v>44356784</v>
       </c>
       <c r="I50" t="n">
-        <v>146.9</v>
+        <v>0.688055</v>
       </c>
       <c r="J50" t="n">
-        <v>135.12</v>
+        <v>0.668225</v>
       </c>
       <c r="K50" t="n">
-        <v>-4.943278722712705</v>
+        <v>-0.01741475955394411</v>
       </c>
       <c r="L50" t="n">
-        <v>-3.28341</v>
+        <v>-2.56216</v>
       </c>
       <c r="M50" t="n">
-        <v>15429020.74517355</v>
+        <v>3302294382.53684</v>
       </c>
       <c r="N50" t="n">
-        <v>16000000</v>
+        <v>6219316794.889999</v>
       </c>
       <c r="O50" t="n">
-        <v>661.6900000000001</v>
+        <v>2.86</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>44334.55554398148</v>
+        <v>45938.71164351852</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R50" t="b">
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0.000932553330749695</v>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>DeFi</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Préstamos</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>N/A (token de gobernanza)</t>
-        </is>
-      </c>
-      <c r="W50" t="n">
-        <v>2017</v>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>aave.com</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>Préstamos y créditos descentralizados</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>Token ERC-20 sobre Ethereum</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>Pionero en préstamos y créditos flash (flash loans) dentro de DeFi.</t>
-        </is>
-      </c>
+        <v>0.000942815143572222</v>
+      </c>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>polkadot</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>dot</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Morpho</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2.91</v>
+        <v>1.17</v>
       </c>
       <c r="F51" t="n">
-        <v>2037269448</v>
+        <v>2001539135</v>
       </c>
       <c r="G51" t="n">
         <v>50</v>
       </c>
       <c r="H51" t="n">
-        <v>64550994</v>
+        <v>207694357</v>
       </c>
       <c r="I51" t="n">
-        <v>2.75</v>
+        <v>1.2</v>
       </c>
       <c r="J51" t="n">
-        <v>2.49</v>
+        <v>1.13</v>
       </c>
       <c r="K51" t="n">
-        <v>0.313299</v>
+        <v>0.01144919</v>
       </c>
       <c r="L51" t="n">
-        <v>11.89216</v>
+        <v>1.02324</v>
       </c>
       <c r="M51" t="n">
-        <v>699408032.7999195</v>
+        <v>1704409844.618002</v>
       </c>
       <c r="N51" t="n">
-        <v>1000000000</v>
+        <v>1704422818.276369</v>
       </c>
       <c r="O51" t="n">
-        <v>4.17</v>
+        <v>54.98</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>45674.19883101852</v>
+        <v>44504.25704861111</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0.000850890757583392</v>
-      </c>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
-      <c r="AA51" t="inlineStr"/>
+        <v>0.0008265408888854018</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Layer 0</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Proof of Stake (NPoS)</t>
+        </is>
+      </c>
+      <c r="W51" t="n">
+        <v>2020</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>polkadot.network</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>Interoperabilidad entre blockchains</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Layer 0, relay chain)</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>Permite que blockchains distintas (parachains) se comuniquen entre sí.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>polkadot</t>
+          <t>aster-2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>dot</t>
+          <t>aster</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1.14</v>
+        <v>0.724982</v>
       </c>
       <c r="F52" t="n">
-        <v>1948735881</v>
+        <v>1963838525</v>
       </c>
       <c r="G52" t="n">
         <v>51</v>
       </c>
       <c r="H52" t="n">
-        <v>192569027</v>
+        <v>127074378</v>
       </c>
       <c r="I52" t="n">
-        <v>1.15</v>
+        <v>0.743329</v>
       </c>
       <c r="J52" t="n">
-        <v>1.083</v>
+        <v>0.703643</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.005984068202869786</v>
+        <v>0.01759298</v>
       </c>
       <c r="L52" t="n">
-        <v>-0.45445</v>
+        <v>2.49101</v>
       </c>
       <c r="M52" t="n">
-        <v>1704257813.2567</v>
+        <v>2710487455.649731</v>
       </c>
       <c r="N52" t="n">
-        <v>1704264406.430411</v>
+        <v>7795741639.279309</v>
       </c>
       <c r="O52" t="n">
-        <v>54.98</v>
+        <v>2.41</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>44504.25704861111</v>
+        <v>45924.13766203704</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R52" t="b">
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0.0007983925085505067</v>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>Interoperabilidad</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Layer 0</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Proof of Stake (NPoS)</t>
-        </is>
-      </c>
-      <c r="W52" t="n">
-        <v>2020</v>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>polkadot.network</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>Interoperabilidad entre blockchains</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Layer 0, relay chain)</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>Permite que blockchains distintas (parachains) se comuniquen entre sí.</t>
-        </is>
-      </c>
+        <v>0.0008040806456204283</v>
+      </c>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>aster-2</t>
+          <t>pump-fun</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>aster</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Pump.fun</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.70549</v>
+        <v>0.00412297</v>
       </c>
       <c r="F53" t="n">
-        <v>1912221350</v>
+        <v>1924394724</v>
       </c>
       <c r="G53" t="n">
         <v>52</v>
       </c>
       <c r="H53" t="n">
-        <v>146322990</v>
+        <v>207586639</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7152579999999999</v>
+        <v>0.0042438</v>
       </c>
       <c r="J53" t="n">
-        <v>0.6801</v>
+        <v>0.00380779</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.006181647943094393</v>
+        <v>0.000275</v>
       </c>
       <c r="L53" t="n">
-        <v>-0.88759</v>
+        <v>6.99921</v>
       </c>
       <c r="M53" t="n">
-        <v>2710487455.649731</v>
+        <v>466505755824.3136</v>
       </c>
       <c r="N53" t="n">
-        <v>7795741639.279309</v>
+        <v>831988424975.1174</v>
       </c>
       <c r="O53" t="n">
-        <v>2.41</v>
+        <v>0.00881908</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>45924.13766203704</v>
+        <v>45914.36296296296</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S53" t="n">
-        <v>0.0007767402809636864</v>
+        <v>0.0007805818914688324</v>
       </c>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
@@ -5270,68 +5270,68 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>pax-gold</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>paxg</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>PAX Gold</t>
+          <t>Morpho</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4267.7</v>
+        <v>2.75</v>
       </c>
       <c r="F54" t="n">
-        <v>1856037392</v>
+        <v>1924184577</v>
       </c>
       <c r="G54" t="n">
         <v>53</v>
       </c>
       <c r="H54" t="n">
-        <v>227214239</v>
+        <v>53348378</v>
       </c>
       <c r="I54" t="n">
-        <v>4300.04</v>
+        <v>2.97</v>
       </c>
       <c r="J54" t="n">
-        <v>4242.49</v>
+        <v>2.74</v>
       </c>
       <c r="K54" t="n">
-        <v>-21.90785163517194</v>
+        <v>-0.146431129138374</v>
       </c>
       <c r="L54" t="n">
-        <v>-0.50476</v>
+        <v>-5.53542</v>
       </c>
       <c r="M54" t="n">
-        <v>434903.623539</v>
+        <v>699457605.9572027</v>
       </c>
       <c r="N54" t="n">
-        <v>434903.623539</v>
+        <v>1000000000</v>
       </c>
       <c r="O54" t="n">
-        <v>5619.09</v>
+        <v>4.17</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>46050.93814814815</v>
+        <v>45674.19883101852</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S54" t="n">
-        <v>0.0007434245622065604</v>
+        <v>0.0007804566958090962</v>
       </c>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
@@ -5345,7 +5345,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5364,28 +5364,28 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4.37e-06</v>
+        <v>4.47e-06</v>
       </c>
       <c r="F55" t="n">
-        <v>1840327966</v>
+        <v>1878183996</v>
       </c>
       <c r="G55" t="n">
         <v>54</v>
       </c>
       <c r="H55" t="n">
-        <v>496628766</v>
+        <v>441797072</v>
       </c>
       <c r="I55" t="n">
-        <v>4.73e-06</v>
+        <v>4.61e-06</v>
       </c>
       <c r="J55" t="n">
-        <v>4.22e-06</v>
+        <v>4.36e-06</v>
       </c>
       <c r="K55" t="n">
-        <v>-3.52898805786e-07</v>
+        <v>7.5968e-08</v>
       </c>
       <c r="L55" t="n">
-        <v>-7.4038</v>
+        <v>1.70869</v>
       </c>
       <c r="M55" t="n">
         <v>420690000000000</v>
@@ -5400,13 +5400,13 @@
         <v>45635.35457175926</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0007341092551850813</v>
+        <v>0.0007530517217359946</v>
       </c>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
@@ -5420,68 +5420,68 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>pump-fun</t>
+          <t>pax-gold</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>paxg</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Pump.fun</t>
+          <t>PAX Gold</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.00385277</v>
+        <v>4260.66</v>
       </c>
       <c r="F56" t="n">
-        <v>1798093331</v>
+        <v>1852824419</v>
       </c>
       <c r="G56" t="n">
         <v>55</v>
       </c>
       <c r="H56" t="n">
-        <v>148366653</v>
+        <v>167047949</v>
       </c>
       <c r="I56" t="n">
-        <v>0.00420914</v>
+        <v>4307.53</v>
       </c>
       <c r="J56" t="n">
-        <v>0.0037575</v>
+        <v>4243.51</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.000346574342933239</v>
+        <v>-5.064864292039601</v>
       </c>
       <c r="L56" t="n">
-        <v>-8.292</v>
+        <v>-0.13787</v>
       </c>
       <c r="M56" t="n">
-        <v>466700999693.5743</v>
+        <v>434898.623539</v>
       </c>
       <c r="N56" t="n">
-        <v>832207673323.2832</v>
+        <v>434898.623539</v>
       </c>
       <c r="O56" t="n">
-        <v>0.00881908</v>
+        <v>5619.09</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>45914.36296296296</v>
+        <v>46050.93814814815</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0.0007090651452370091</v>
+        <v>0.0007379436832051372</v>
       </c>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
@@ -5495,7 +5495,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5514,31 +5514,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.054942</v>
+        <v>0.056899</v>
       </c>
       <c r="F57" t="n">
-        <v>1745921284</v>
+        <v>1807955457</v>
       </c>
       <c r="G57" t="n">
         <v>56</v>
       </c>
       <c r="H57" t="n">
-        <v>53692296</v>
+        <v>50840539</v>
       </c>
       <c r="I57" t="n">
-        <v>0.057932</v>
+        <v>0.057528</v>
       </c>
       <c r="J57" t="n">
-        <v>0.053389</v>
+        <v>0.055143</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.002857573217483492</v>
+        <v>0.00178045</v>
       </c>
       <c r="L57" t="n">
-        <v>-4.96231</v>
+        <v>3.24573</v>
       </c>
       <c r="M57" t="n">
-        <v>31777818012</v>
+        <v>31777821956</v>
       </c>
       <c r="N57" t="n">
         <v>100000000000</v>
@@ -5550,13 +5550,13 @@
         <v>45901.18065972222</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0.0006781283919944633</v>
+        <v>0.0007112128742986806</v>
       </c>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
@@ -5570,7 +5570,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5589,34 +5589,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3.05</v>
+        <v>3.13</v>
       </c>
       <c r="F58" t="n">
-        <v>1698964503</v>
+        <v>1744603286</v>
       </c>
       <c r="G58" t="n">
         <v>57</v>
       </c>
       <c r="H58" t="n">
-        <v>104738488</v>
+        <v>113204362</v>
       </c>
       <c r="I58" t="n">
-        <v>3.14</v>
+        <v>3.27</v>
       </c>
       <c r="J58" t="n">
-        <v>2.84</v>
+        <v>3.04</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.04820574080413698</v>
+        <v>-0.01197071337857913</v>
       </c>
       <c r="L58" t="n">
-        <v>-1.54971</v>
+        <v>-0.17087</v>
       </c>
       <c r="M58" t="n">
-        <v>556899104.8894781</v>
+        <v>556900774.9526535</v>
       </c>
       <c r="N58" t="n">
-        <v>556899104.8894781</v>
+        <v>556902306.1412389</v>
       </c>
       <c r="O58" t="n">
         <v>700.65</v>
@@ -5625,13 +5625,13 @@
         <v>44326.33741898148</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R58" t="b">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0006502841644742882</v>
+        <v>0.0006734706422227487</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5694,31 +5694,31 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.07137499999999999</v>
+        <v>0.07366300000000001</v>
       </c>
       <c r="F59" t="n">
-        <v>1671792596</v>
+        <v>1724572631</v>
       </c>
       <c r="G59" t="n">
         <v>58</v>
       </c>
       <c r="H59" t="n">
-        <v>37387940</v>
+        <v>22850133</v>
       </c>
       <c r="I59" t="n">
-        <v>0.07593</v>
+        <v>0.077512</v>
       </c>
       <c r="J59" t="n">
-        <v>0.068749</v>
+        <v>0.071574</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.002659009276291313</v>
+        <v>0.00203783</v>
       </c>
       <c r="L59" t="n">
-        <v>-3.91437</v>
+        <v>2.75947</v>
       </c>
       <c r="M59" t="n">
-        <v>23422655415.78843</v>
+        <v>23420903969.25927</v>
       </c>
       <c r="N59" t="n">
         <v>23459804203.60596</v>
@@ -5730,13 +5730,13 @@
         <v>45630.09302083333</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R59" t="b">
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>0.0006341718853837553</v>
+        <v>0.0006615373237948306</v>
       </c>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
@@ -5750,7 +5750,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5769,31 +5769,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.423671</v>
+        <v>0.449526</v>
       </c>
       <c r="F60" t="n">
-        <v>1546541856</v>
+        <v>1640645152</v>
       </c>
       <c r="G60" t="n">
         <v>59</v>
       </c>
       <c r="H60" t="n">
-        <v>442319003</v>
+        <v>398546805</v>
       </c>
       <c r="I60" t="n">
-        <v>0.448592</v>
+        <v>0.461122</v>
       </c>
       <c r="J60" t="n">
-        <v>0.400932</v>
+        <v>0.428815</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.02246015873684787</v>
+        <v>0.01440768</v>
       </c>
       <c r="L60" t="n">
-        <v>-4.94776</v>
+        <v>3.33176</v>
       </c>
       <c r="M60" t="n">
-        <v>3650340456.196745</v>
+        <v>3651776215.902232</v>
       </c>
       <c r="N60" t="n">
         <v>10000000000</v>
@@ -5805,13 +5805,13 @@
         <v>45360.67409722223</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0.000559901246993311</v>
+        <v>0.0006115372947513761</v>
       </c>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
@@ -5825,68 +5825,68 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>htx-dao</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>htx</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>HTX DAO</t>
+          <t>USDD</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1.71e-06</v>
+        <v>0.998864</v>
       </c>
       <c r="F61" t="n">
-        <v>1537643253</v>
+        <v>1546477735</v>
       </c>
       <c r="G61" t="n">
         <v>60</v>
       </c>
       <c r="H61" t="n">
-        <v>11872337</v>
+        <v>2614071</v>
       </c>
       <c r="I61" t="n">
-        <v>1.73e-06</v>
+        <v>0.999709</v>
       </c>
       <c r="J61" t="n">
-        <v>1.7e-06</v>
+        <v>0.997564</v>
       </c>
       <c r="K61" t="n">
-        <v>-1.6416876349e-08</v>
+        <v>-0.000447157638903684</v>
       </c>
       <c r="L61" t="n">
-        <v>-1.00637</v>
+        <v>-0.04217</v>
       </c>
       <c r="M61" t="n">
-        <v>898232728634017.2</v>
+        <v>1548251336</v>
       </c>
       <c r="N61" t="n">
-        <v>898232728634017.2</v>
+        <v>1548101485</v>
       </c>
       <c r="O61" t="n">
-        <v>3.75e-06</v>
+        <v>1.24</v>
       </c>
       <c r="P61" s="1" t="n">
-        <v>45629.67800925926</v>
+        <v>46212.39942129629</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R61" t="b">
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>0.0005546245921360772</v>
+        <v>0.0005554367941638737</v>
       </c>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
@@ -5900,68 +5900,68 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>htx-dao</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>htx</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>USDD</t>
+          <t>HTX DAO</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.999234</v>
+        <v>1.71e-06</v>
       </c>
       <c r="F62" t="n">
-        <v>1521430844</v>
+        <v>1540537375</v>
       </c>
       <c r="G62" t="n">
         <v>61</v>
       </c>
       <c r="H62" t="n">
-        <v>1396580</v>
+        <v>7980562</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9995309999999999</v>
+        <v>1.73e-06</v>
       </c>
       <c r="J62" t="n">
-        <v>0.997431</v>
+        <v>1.71e-06</v>
       </c>
       <c r="K62" t="n">
-        <v>0.00040721</v>
+        <v>1.983e-09</v>
       </c>
       <c r="L62" t="n">
-        <v>0.04515</v>
+        <v>0.12334</v>
       </c>
       <c r="M62" t="n">
-        <v>1522596897</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="N62" t="n">
-        <v>1530643977</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="O62" t="n">
-        <v>1.24</v>
+        <v>3.75e-06</v>
       </c>
       <c r="P62" s="1" t="n">
-        <v>46212.39942129629</v>
+        <v>45629.67800925926</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R62" t="b">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0.0005450110284455394</v>
+        <v>0.0005518978081718297</v>
       </c>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
@@ -5975,187 +5975,187 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ethereum-classic</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>arb</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Ethereum Classic</t>
+          <t>Arbitrum</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>9.51</v>
+        <v>0.220585</v>
       </c>
       <c r="F63" t="n">
-        <v>1504422259</v>
+        <v>1496742401</v>
       </c>
       <c r="G63" t="n">
         <v>62</v>
       </c>
       <c r="H63" t="n">
-        <v>163869086</v>
+        <v>377134691</v>
       </c>
       <c r="I63" t="n">
-        <v>9.699999999999999</v>
+        <v>0.227066</v>
       </c>
       <c r="J63" t="n">
-        <v>8.65</v>
+        <v>0.21335</v>
       </c>
       <c r="K63" t="n">
-        <v>0.09289</v>
+        <v>0.00293443</v>
       </c>
       <c r="L63" t="n">
-        <v>0.9805199999999999</v>
+        <v>1.34031</v>
       </c>
       <c r="M63" t="n">
-        <v>158269190.6970681</v>
+        <v>6785574605</v>
       </c>
       <c r="N63" t="n">
-        <v>158269579.3562681</v>
+        <v>10000000000</v>
       </c>
       <c r="O63" t="n">
-        <v>167.09</v>
+        <v>2.39</v>
       </c>
       <c r="P63" s="1" t="n">
-        <v>44322.44053240741</v>
+        <v>45303.18748842592</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R63" t="b">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0.0005349253517775363</v>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Plataforma de contratos inteligentes</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Layer 1</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Proof of Work</t>
-        </is>
-      </c>
-      <c r="W63" t="n">
-        <v>2016</v>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>ethereumclassic.org</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>Contratos inteligentes (cadena original)</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>Blockchain propia (fork de Ethereum)</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>Mantiene la cadena original de Ethereum tras la bifurcación de 2016.</t>
-        </is>
-      </c>
+        <v>0.0005258068306034777</v>
+      </c>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum-classic</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>arb</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Arbitrum</t>
+          <t>Ethereum Classic</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.218005</v>
+        <v>9.41</v>
       </c>
       <c r="F64" t="n">
-        <v>1479287884</v>
+        <v>1488173326</v>
       </c>
       <c r="G64" t="n">
         <v>63</v>
       </c>
       <c r="H64" t="n">
-        <v>325788139</v>
+        <v>170646721</v>
       </c>
       <c r="I64" t="n">
-        <v>0.229675</v>
+        <v>10.21</v>
       </c>
       <c r="J64" t="n">
-        <v>0.210805</v>
+        <v>9.35</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.01116477426095458</v>
+        <v>-0.507011005980349</v>
       </c>
       <c r="L64" t="n">
-        <v>-4.93658</v>
+        <v>-5.19538</v>
       </c>
       <c r="M64" t="n">
-        <v>6785574605</v>
+        <v>158279214.6654091</v>
       </c>
       <c r="N64" t="n">
-        <v>10000000000</v>
+        <v>158279620.2718091</v>
       </c>
       <c r="O64" t="n">
-        <v>2.39</v>
+        <v>167.09</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>45303.18748842592</v>
+        <v>44322.44053240741</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R64" t="b">
         <v>1</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0005200212795397609</v>
-      </c>
-      <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr"/>
-      <c r="X64" t="inlineStr"/>
-      <c r="Y64" t="inlineStr"/>
-      <c r="Z64" t="inlineStr"/>
-      <c r="AA64" t="inlineStr"/>
+        <v>0.000520701780338885</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Plataforma de contratos inteligentes</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Layer 1</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Proof of Work</t>
+        </is>
+      </c>
+      <c r="W64" t="n">
+        <v>2016</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>ethereumclassic.org</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>Contratos inteligentes (cadena original)</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>Blockchain propia (fork de Ethereum)</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>Mantiene la cadena original de Ethereum tras la bifurcación de 2016.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6174,34 +6174,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.999204</v>
+        <v>0.999408</v>
       </c>
       <c r="F65" t="n">
-        <v>1465742252</v>
+        <v>1481980463</v>
       </c>
       <c r="G65" t="n">
         <v>64</v>
       </c>
       <c r="H65" t="n">
-        <v>192240310</v>
+        <v>145534813</v>
       </c>
       <c r="I65" t="n">
-        <v>0.999577</v>
+        <v>0.999688</v>
       </c>
       <c r="J65" t="n">
-        <v>0.998874</v>
+        <v>0.998783</v>
       </c>
       <c r="K65" t="n">
-        <v>-7.0129395513e-07</v>
+        <v>0.00015674</v>
       </c>
       <c r="L65" t="n">
-        <v>-0.00393</v>
+        <v>0.02043</v>
       </c>
       <c r="M65" t="n">
-        <v>1466909391.63</v>
+        <v>1482857391.63</v>
       </c>
       <c r="N65" t="n">
-        <v>1466909391.63</v>
+        <v>1482857391.63</v>
       </c>
       <c r="O65" t="n">
         <v>1.008</v>
@@ -6210,13 +6210,13 @@
         <v>46058.54591435185</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R65" t="b">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0.000511989049661981</v>
+        <v>0.0005170123649822992</v>
       </c>
       <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr"/>
@@ -6230,7 +6230,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6249,10 +6249,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="F66" t="n">
-        <v>1455025954</v>
+        <v>1473901965</v>
       </c>
       <c r="G66" t="n">
         <v>65</v>
@@ -6267,16 +6267,16 @@
         <v>1.15</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.003791863830702846</v>
+        <v>0.00221151</v>
       </c>
       <c r="L66" t="n">
-        <v>-0.32807</v>
+        <v>0.19183</v>
       </c>
       <c r="M66" t="n">
-        <v>1263010543.63882</v>
+        <v>1276009571.67166</v>
       </c>
       <c r="N66" t="n">
-        <v>1263010543.63882</v>
+        <v>1276009571.67166</v>
       </c>
       <c r="O66" t="n">
         <v>1.18</v>
@@ -6285,13 +6285,13 @@
         <v>46255.48263888889</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R66" t="b">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0.0005056345459389512</v>
+        <v>0.0005121995773299085</v>
       </c>
       <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr"/>
@@ -6305,7 +6305,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6324,34 +6324,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>29.75</v>
+        <v>30.62</v>
       </c>
       <c r="F67" t="n">
-        <v>1431958745</v>
+        <v>1473626212</v>
       </c>
       <c r="G67" t="n">
         <v>66</v>
       </c>
       <c r="H67" t="n">
-        <v>68957545</v>
+        <v>56626864</v>
       </c>
       <c r="I67" t="n">
-        <v>31.78</v>
+        <v>32.49</v>
       </c>
       <c r="J67" t="n">
-        <v>28.51</v>
+        <v>29.21</v>
       </c>
       <c r="K67" t="n">
-        <v>-2.290645359558955</v>
+        <v>1.079</v>
       </c>
       <c r="L67" t="n">
-        <v>-7.17827</v>
+        <v>3.68225</v>
       </c>
       <c r="M67" t="n">
-        <v>48134255.57614676</v>
+        <v>48143958.52816238</v>
       </c>
       <c r="N67" t="n">
-        <v>81038958.6290253</v>
+        <v>81045681.33699232</v>
       </c>
       <c r="O67" t="n">
         <v>34.53</v>
@@ -6360,13 +6360,13 @@
         <v>46286.34548611111</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.0004919562527942097</v>
+        <v>0.000512035296713201</v>
       </c>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
@@ -6380,68 +6380,68 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>bitget-token</t>
+          <t>usdgo</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>bgb</t>
+          <t>usdgo</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Bitget Token</t>
+          <t>USDGO</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2.04</v>
+        <v>0.9999</v>
       </c>
       <c r="F68" t="n">
-        <v>1431359067</v>
+        <v>1407608854</v>
       </c>
       <c r="G68" t="n">
         <v>67</v>
       </c>
       <c r="H68" t="n">
-        <v>14513852</v>
+        <v>122655681</v>
       </c>
       <c r="I68" t="n">
-        <v>2.08</v>
+        <v>1.001</v>
       </c>
       <c r="J68" t="n">
-        <v>2</v>
+        <v>0.998739</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.03152185663063145</v>
+        <v>-4.820527743532e-06</v>
       </c>
       <c r="L68" t="n">
-        <v>-1.51287</v>
+        <v>-0.04393</v>
       </c>
       <c r="M68" t="n">
-        <v>699992029.6481038</v>
+        <v>1407780807.97</v>
       </c>
       <c r="N68" t="n">
-        <v>910920874.6481038</v>
+        <v>1407780807.97</v>
       </c>
       <c r="O68" t="n">
-        <v>8.449999999999999</v>
+        <v>1.002</v>
       </c>
       <c r="P68" s="1" t="n">
-        <v>45653.15375</v>
+        <v>46092.00303240741</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R68" t="b">
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0.0004916006583451174</v>
+        <v>0.0004727052720692803</v>
       </c>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
@@ -6455,68 +6455,68 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>usdgo</t>
+          <t>bitget-token</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>usdgo</t>
+          <t>bgb</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>USDGO</t>
+          <t>Bitget Token</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>1.98</v>
       </c>
       <c r="F69" t="n">
-        <v>1418449056</v>
+        <v>1384882523</v>
       </c>
       <c r="G69" t="n">
         <v>68</v>
       </c>
       <c r="H69" t="n">
-        <v>20026880</v>
+        <v>59720930</v>
       </c>
       <c r="I69" t="n">
-        <v>1.001</v>
+        <v>2.07</v>
       </c>
       <c r="J69" t="n">
-        <v>0.999789</v>
+        <v>1.89</v>
       </c>
       <c r="K69" t="n">
-        <v>7.656999999999999e-05</v>
+        <v>-0.06647040326293796</v>
       </c>
       <c r="L69" t="n">
-        <v>0.01655</v>
+        <v>-3.32458</v>
       </c>
       <c r="M69" t="n">
-        <v>1417780805.97</v>
+        <v>699992029.6481038</v>
       </c>
       <c r="N69" t="n">
-        <v>1417780805.97</v>
+        <v>910920874.6481038</v>
       </c>
       <c r="O69" t="n">
-        <v>1.002</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="P69" s="1" t="n">
-        <v>46092.00303240741</v>
+        <v>45653.15375</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R69" t="b">
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>0.0004839453362400531</v>
+        <v>0.0004591659971668237</v>
       </c>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
@@ -6530,7 +6530,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6549,34 +6549,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.995592</v>
+        <v>0.995744</v>
       </c>
       <c r="F70" t="n">
-        <v>1371327861</v>
+        <v>1371537564</v>
       </c>
       <c r="G70" t="n">
         <v>69</v>
       </c>
       <c r="H70" t="n">
-        <v>412081</v>
+        <v>492606</v>
       </c>
       <c r="I70" t="n">
-        <v>0.996672</v>
+        <v>0.997607</v>
       </c>
       <c r="J70" t="n">
-        <v>0.993875</v>
+        <v>0.9951140000000001</v>
       </c>
       <c r="K70" t="n">
-        <v>-0.000222884782159927</v>
+        <v>0.00021313</v>
       </c>
       <c r="L70" t="n">
-        <v>-0.02264</v>
+        <v>0.02418</v>
       </c>
       <c r="M70" t="n">
-        <v>1377398957.226253</v>
+        <v>1377413080.69863</v>
       </c>
       <c r="N70" t="n">
-        <v>1377398957.226253</v>
+        <v>1377413080.69863</v>
       </c>
       <c r="O70" t="n">
         <v>1.075</v>
@@ -6585,13 +6585,13 @@
         <v>45785.55951388889</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R70" t="b">
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>0.0004560036152221125</v>
+        <v>0.0004512157007259677</v>
       </c>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
@@ -6605,143 +6605,173 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>bfusd</t>
+          <t>quant-network</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>bfusd</t>
+          <t>qnt</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>BFUSD</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.999628</v>
+        <v>93.06999999999999</v>
       </c>
       <c r="F71" t="n">
-        <v>1319508692</v>
+        <v>1354412807</v>
       </c>
       <c r="G71" t="n">
         <v>70</v>
       </c>
       <c r="H71" t="n">
-        <v>4065721</v>
+        <v>95089796</v>
       </c>
       <c r="I71" t="n">
-        <v>0.9999209999999999</v>
+        <v>104.14</v>
       </c>
       <c r="J71" t="n">
-        <v>0.999528</v>
+        <v>80.03</v>
       </c>
       <c r="K71" t="n">
-        <v>-0.000132570629598927</v>
+        <v>13.59</v>
       </c>
       <c r="L71" t="n">
-        <v>-0.00352</v>
+        <v>17.0986</v>
       </c>
       <c r="M71" t="n">
-        <v>1320000000</v>
+        <v>14544176.16408117</v>
       </c>
       <c r="N71" t="n">
-        <v>1320000000</v>
+        <v>14612493</v>
       </c>
       <c r="O71" t="n">
-        <v>1.007</v>
+        <v>427.42</v>
       </c>
       <c r="P71" s="1" t="n">
-        <v>45940.56990740741</v>
+        <v>44450.05208333334</v>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S71" t="n">
-        <v>0.0004252761100393701</v>
-      </c>
-      <c r="T71" t="inlineStr"/>
-      <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr"/>
-      <c r="W71" t="inlineStr"/>
-      <c r="X71" t="inlineStr"/>
-      <c r="Y71" t="inlineStr"/>
-      <c r="Z71" t="inlineStr"/>
-      <c r="AA71" t="inlineStr"/>
+        <v>0.0004410135791137828</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Infraestructura empresarial</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>N/A (token ERC-20)</t>
+        </is>
+      </c>
+      <c r="W71" t="n">
+        <v>2018</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>quant.network</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>Interoperabilidad entre redes empresariales</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>Token ERC-20 sobre Ethereum</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>Su tecnología Overledger busca conectar múltiples blockchains y redes existentes.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>lighter</t>
+          <t>bfusd</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>lit</t>
+          <t>bfusd</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Lighter</t>
+          <t>BFUSD</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5.21</v>
+        <v>0.999516</v>
       </c>
       <c r="F72" t="n">
-        <v>1302813360</v>
+        <v>1319348505</v>
       </c>
       <c r="G72" t="n">
         <v>71</v>
       </c>
       <c r="H72" t="n">
-        <v>149894014</v>
+        <v>6768478</v>
       </c>
       <c r="I72" t="n">
-        <v>5.54</v>
+        <v>0.999864</v>
       </c>
       <c r="J72" t="n">
-        <v>4.92</v>
+        <v>0.998769</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.114789701572211</v>
+        <v>-9.2806474289331e-05</v>
       </c>
       <c r="L72" t="n">
-        <v>-2.44837</v>
+        <v>-0.0065</v>
       </c>
       <c r="M72" t="n">
-        <v>250000000</v>
+        <v>1320000000</v>
       </c>
       <c r="N72" t="n">
-        <v>1000000000</v>
+        <v>1320000000</v>
       </c>
       <c r="O72" t="n">
-        <v>7.86</v>
+        <v>1.007</v>
       </c>
       <c r="P72" s="1" t="n">
-        <v>46021.04538194444</v>
+        <v>45940.56990740741</v>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R72" t="b">
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>0.0004153761847712207</v>
+        <v>0.0004201239236722264</v>
       </c>
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
@@ -6755,173 +6785,143 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>quant-network</t>
+          <t>lighter</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>qnt</t>
+          <t>lit</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Lighter</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>77.31</v>
+        <v>4.85</v>
       </c>
       <c r="F73" t="n">
-        <v>1124461003</v>
+        <v>1212495922</v>
       </c>
       <c r="G73" t="n">
         <v>72</v>
       </c>
       <c r="H73" t="n">
-        <v>14349702</v>
+        <v>125800863</v>
       </c>
       <c r="I73" t="n">
-        <v>75.26000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="J73" t="n">
-        <v>69.78</v>
+        <v>4.81</v>
       </c>
       <c r="K73" t="n">
-        <v>3.41</v>
+        <v>-0.3229688832451751</v>
       </c>
       <c r="L73" t="n">
-        <v>4.85594</v>
+        <v>-6.27448</v>
       </c>
       <c r="M73" t="n">
-        <v>14544176.16408117</v>
+        <v>250000000</v>
       </c>
       <c r="N73" t="n">
-        <v>14612493</v>
+        <v>1000000000</v>
       </c>
       <c r="O73" t="n">
-        <v>427.42</v>
+        <v>7.86</v>
       </c>
       <c r="P73" s="1" t="n">
-        <v>44450.05208333334</v>
+        <v>46021.04538194444</v>
       </c>
       <c r="Q73" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S73" t="n">
-        <v>0.0003096175807675203</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Interoperabilidad</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Infraestructura empresarial</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>N/A (token ERC-20)</t>
-        </is>
-      </c>
-      <c r="W73" t="n">
-        <v>2018</v>
-      </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>quant.network</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>Interoperabilidad entre redes empresariales</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>Token ERC-20 sobre Ethereum</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>Su tecnología Overledger busca conectar múltiples blockchains y redes existentes.</t>
-        </is>
-      </c>
+        <v>0.0003564662001587139</v>
+      </c>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr"/>
+      <c r="X73" t="inlineStr"/>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>gatechain-token</t>
+          <t>polygon-ecosystem-token</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>gt</t>
+          <t>pol</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>POL (ex-MATIC)</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>10.56</v>
+        <v>0.113301</v>
       </c>
       <c r="F74" t="n">
-        <v>1125588745</v>
+        <v>1202787277</v>
       </c>
       <c r="G74" t="n">
         <v>73</v>
       </c>
       <c r="H74" t="n">
-        <v>3793329</v>
+        <v>120632746</v>
       </c>
       <c r="I74" t="n">
-        <v>10.9</v>
+        <v>0.113885</v>
       </c>
       <c r="J74" t="n">
-        <v>10.38</v>
+        <v>0.10441</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.2992864443187386</v>
+        <v>0.00882021</v>
       </c>
       <c r="L74" t="n">
-        <v>-2.71405</v>
+        <v>8.481</v>
       </c>
       <c r="M74" t="n">
-        <v>106639170.2071135</v>
+        <v>10620499850.30005</v>
       </c>
       <c r="N74" t="n">
-        <v>118890463.1038794</v>
+        <v>10620499850.30005</v>
       </c>
       <c r="O74" t="n">
-        <v>25.38</v>
+        <v>1.29</v>
       </c>
       <c r="P74" s="1" t="n">
-        <v>45682.66666666666</v>
+        <v>45364.45493055556</v>
       </c>
       <c r="Q74" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S74" t="n">
-        <v>0.0003102863043078341</v>
+        <v>0.000350682247897112</v>
       </c>
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
@@ -6935,68 +6935,68 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>polygon-ecosystem-token</t>
+          <t>kaspa</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>pol</t>
+          <t>kas</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>POL (ex-MATIC)</t>
+          <t>Kaspa</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.104148</v>
+        <v>0.0414891</v>
       </c>
       <c r="F75" t="n">
-        <v>1106038183</v>
+        <v>1149882008</v>
       </c>
       <c r="G75" t="n">
         <v>74</v>
       </c>
       <c r="H75" t="n">
-        <v>93832289</v>
+        <v>19397785</v>
       </c>
       <c r="I75" t="n">
-        <v>0.107051</v>
+        <v>0.04231564</v>
       </c>
       <c r="J75" t="n">
-        <v>0.100043</v>
+        <v>0.03920464</v>
       </c>
       <c r="K75" t="n">
-        <v>-0.002443803701124916</v>
+        <v>0.00224125</v>
       </c>
       <c r="L75" t="n">
-        <v>-2.15828</v>
+        <v>5.6164</v>
       </c>
       <c r="M75" t="n">
-        <v>10619918238.50136</v>
+        <v>27719200688.33876</v>
       </c>
       <c r="N75" t="n">
-        <v>10619918238.50136</v>
+        <v>27720665879.75146</v>
       </c>
       <c r="O75" t="n">
-        <v>1.29</v>
+        <v>0.207411</v>
       </c>
       <c r="P75" s="1" t="n">
-        <v>45364.45493055556</v>
+        <v>45504.69498842592</v>
       </c>
       <c r="Q75" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R75" t="b">
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>0.000298693297187621</v>
+        <v>0.0003191637867438613</v>
       </c>
       <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr"/>
@@ -7010,68 +7010,68 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>kaspa</t>
+          <t>gatechain-token</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>kas</t>
+          <t>gt</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Kaspa</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.03898802</v>
+        <v>10.75</v>
       </c>
       <c r="F76" t="n">
-        <v>1080689406</v>
+        <v>1145582393</v>
       </c>
       <c r="G76" t="n">
         <v>75</v>
       </c>
       <c r="H76" t="n">
-        <v>18606938</v>
+        <v>1236749</v>
       </c>
       <c r="I76" t="n">
-        <v>0.04100133</v>
+        <v>10.98</v>
       </c>
       <c r="J76" t="n">
-        <v>0.03807561</v>
+        <v>10.6</v>
       </c>
       <c r="K76" t="n">
-        <v>-0.001977854268385787</v>
+        <v>0.133134</v>
       </c>
       <c r="L76" t="n">
-        <v>-4.83024</v>
+        <v>1.10001</v>
       </c>
       <c r="M76" t="n">
-        <v>27718500422.43598</v>
+        <v>106640355.6187321</v>
       </c>
       <c r="N76" t="n">
-        <v>27718779366.30129</v>
+        <v>118891623.1107255</v>
       </c>
       <c r="O76" t="n">
-        <v>0.207411</v>
+        <v>25.38</v>
       </c>
       <c r="P76" s="1" t="n">
-        <v>45504.69498842592</v>
+        <v>45682.66666666666</v>
       </c>
       <c r="Q76" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0002836620897855169</v>
+        <v>0.0003166022791490046</v>
       </c>
       <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr"/>
@@ -7085,428 +7085,428 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>kucoin-shares</t>
+          <t>jupiter-exchange-solana</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>kcs</t>
+          <t>jup</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>KuCoin</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>7.22</v>
+        <v>0.319361</v>
       </c>
       <c r="F77" t="n">
-        <v>990443671</v>
+        <v>1059995753</v>
       </c>
       <c r="G77" t="n">
         <v>76</v>
       </c>
       <c r="H77" t="n">
-        <v>9745795</v>
+        <v>113892448</v>
       </c>
       <c r="I77" t="n">
-        <v>7.28</v>
+        <v>0.331898</v>
       </c>
       <c r="J77" t="n">
-        <v>7.1</v>
+        <v>0.296086</v>
       </c>
       <c r="K77" t="n">
-        <v>-0.03072494057700936</v>
+        <v>0.02561843</v>
       </c>
       <c r="L77" t="n">
-        <v>-0.30756</v>
+        <v>8.68707</v>
       </c>
       <c r="M77" t="n">
-        <v>137155021.2773955</v>
+        <v>3319369204.37</v>
       </c>
       <c r="N77" t="n">
-        <v>142155021.2773955</v>
+        <v>6861486668.371618</v>
       </c>
       <c r="O77" t="n">
-        <v>28.83</v>
+        <v>2</v>
       </c>
       <c r="P77" s="1" t="n">
-        <v>44531.29832175926</v>
+        <v>45322.29359953704</v>
       </c>
       <c r="Q77" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0002301485668277694</v>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Token de exchange</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>Utilidad</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>N/A (token de exchange)</t>
-        </is>
-      </c>
-      <c r="W77" t="n">
-        <v>2017</v>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>kucoin.com</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>Beneficios en el exchange KuCoin</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>Token ERC-20 sobre Ethereum</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>Otorga descuentos en comisiones dentro del exchange KuCoin.</t>
-        </is>
-      </c>
+        <v>0.0002656138003251419</v>
+      </c>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr"/>
+      <c r="X77" t="inlineStr"/>
+      <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr"/>
+      <c r="AA77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>blockchain-capital</t>
+          <t>algorand</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>bcap</t>
+          <t>algo</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Blockchain Capital</t>
+          <t>Algorand</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>107.53</v>
+        <v>0.115416</v>
       </c>
       <c r="F78" t="n">
-        <v>979825296</v>
+        <v>1045007842</v>
       </c>
       <c r="G78" t="n">
         <v>77</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>71211178</v>
       </c>
       <c r="I78" t="n">
-        <v>107.53</v>
+        <v>0.118425</v>
       </c>
       <c r="J78" t="n">
-        <v>107.53</v>
+        <v>0.110361</v>
       </c>
       <c r="K78" t="n">
-        <v>1.4211e-14</v>
+        <v>0.00568445</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>5.08492</v>
       </c>
       <c r="M78" t="n">
-        <v>9112111</v>
+        <v>9057076849.535131</v>
       </c>
       <c r="N78" t="n">
-        <v>9112111</v>
+        <v>9057147759.259453</v>
       </c>
       <c r="O78" t="n">
-        <v>107.53</v>
+        <v>3.56</v>
       </c>
       <c r="P78" s="1" t="n">
-        <v>46287.17361111111</v>
+        <v>43636.28563657407</v>
       </c>
       <c r="Q78" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R78" t="b">
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>0.0002238521290588657</v>
-      </c>
-      <c r="T78" t="inlineStr"/>
-      <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr"/>
-      <c r="W78" t="inlineStr"/>
-      <c r="X78" t="inlineStr"/>
-      <c r="Y78" t="inlineStr"/>
-      <c r="Z78" t="inlineStr"/>
-      <c r="AA78" t="inlineStr"/>
+        <v>0.0002566847106607102</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Plataforma de contratos inteligentes</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Layer 1</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Pure Proof of Stake</t>
+        </is>
+      </c>
+      <c r="W78" t="n">
+        <v>2019</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>algorand.com</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>Contratos inteligentes de alta eficiencia</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Layer 1)</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>Fundada por Silvio Micali, ganador del Premio Turing.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>jupiter-exchange-solana</t>
+          <t>kucoin-shares</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>jup</t>
+          <t>kcs</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>KuCoin</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.294776</v>
+        <v>7.36</v>
       </c>
       <c r="F79" t="n">
-        <v>978471567</v>
+        <v>1009611380</v>
       </c>
       <c r="G79" t="n">
         <v>78</v>
       </c>
       <c r="H79" t="n">
-        <v>101687450</v>
+        <v>3380693</v>
       </c>
       <c r="I79" t="n">
-        <v>0.300785</v>
+        <v>7.41</v>
       </c>
       <c r="J79" t="n">
-        <v>0.276615</v>
+        <v>7.18</v>
       </c>
       <c r="K79" t="n">
-        <v>-0.005983646650502994</v>
+        <v>0.151384</v>
       </c>
       <c r="L79" t="n">
-        <v>-1.95707</v>
+        <v>2.12723</v>
       </c>
       <c r="M79" t="n">
-        <v>3319369204.37</v>
+        <v>137155021.2773955</v>
       </c>
       <c r="N79" t="n">
-        <v>6861486685.686895</v>
+        <v>142155021.2773955</v>
       </c>
       <c r="O79" t="n">
-        <v>2</v>
+        <v>28.83</v>
       </c>
       <c r="P79" s="1" t="n">
-        <v>45322.29359953704</v>
+        <v>44531.29832175926</v>
       </c>
       <c r="Q79" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R79" t="b">
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0002230494007313711</v>
-      </c>
-      <c r="T79" t="inlineStr"/>
-      <c r="U79" t="inlineStr"/>
-      <c r="V79" t="inlineStr"/>
-      <c r="W79" t="inlineStr"/>
-      <c r="X79" t="inlineStr"/>
-      <c r="Y79" t="inlineStr"/>
-      <c r="Z79" t="inlineStr"/>
-      <c r="AA79" t="inlineStr"/>
+        <v>0.0002355971699753104</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Token de exchange</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Utilidad</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>N/A (token de exchange)</t>
+        </is>
+      </c>
+      <c r="W79" t="n">
+        <v>2017</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>kucoin.com</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>Beneficios en el exchange KuCoin</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>Token ERC-20 sobre Ethereum</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>Otorga descuentos en comisiones dentro del exchange KuCoin.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>algorand</t>
+          <t>pi-network</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>algo</t>
+          <t>pi</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Algorand</t>
+          <t>Pi Network</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.108044</v>
+        <v>0.089106</v>
       </c>
       <c r="F80" t="n">
-        <v>978437246</v>
+        <v>1001481315</v>
       </c>
       <c r="G80" t="n">
         <v>79</v>
       </c>
       <c r="H80" t="n">
-        <v>48005860</v>
+        <v>11009834</v>
       </c>
       <c r="I80" t="n">
-        <v>0.109247</v>
+        <v>0.09019000000000001</v>
       </c>
       <c r="J80" t="n">
-        <v>0.103017</v>
+        <v>0.085051</v>
       </c>
       <c r="K80" t="n">
-        <v>-0.0006422515543882961</v>
+        <v>0.00222097</v>
       </c>
       <c r="L80" t="n">
-        <v>-0.21947</v>
+        <v>2.52261</v>
       </c>
       <c r="M80" t="n">
-        <v>9055912745.559528</v>
+        <v>11243022455.381</v>
       </c>
       <c r="N80" t="n">
-        <v>9055945838.232386</v>
+        <v>17296957623.66307</v>
       </c>
       <c r="O80" t="n">
-        <v>3.56</v>
+        <v>2.99</v>
       </c>
       <c r="P80" s="1" t="n">
-        <v>43636.28563657407</v>
+        <v>45714.36184027778</v>
       </c>
       <c r="Q80" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R80" t="b">
         <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>0.0002230290492142448</v>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>Plataforma de contratos inteligentes</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>Layer 1</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>Pure Proof of Stake</t>
-        </is>
-      </c>
-      <c r="W80" t="n">
-        <v>2019</v>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>algorand.com</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>Contratos inteligentes de alta eficiencia</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Layer 1)</t>
-        </is>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>Fundada por Silvio Micali, ganador del Premio Turing.</t>
-        </is>
-      </c>
+        <v>0.0002307536611392452</v>
+      </c>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>pi-network</t>
+          <t>render-token</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>pi</t>
+          <t>render</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Pi Network</t>
+          <t>Render</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.086727</v>
+        <v>1.92</v>
       </c>
       <c r="F81" t="n">
-        <v>975075397</v>
+        <v>995521344</v>
       </c>
       <c r="G81" t="n">
         <v>80</v>
       </c>
       <c r="H81" t="n">
-        <v>8830526</v>
+        <v>112423046</v>
       </c>
       <c r="I81" t="n">
-        <v>0.09050800000000001</v>
+        <v>1.97</v>
       </c>
       <c r="J81" t="n">
-        <v>0.08605400000000001</v>
+        <v>1.82</v>
       </c>
       <c r="K81" t="n">
-        <v>-0.003643346247182114</v>
+        <v>0.08316900000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>-4.01879</v>
+        <v>4.34985</v>
       </c>
       <c r="M81" t="n">
-        <v>11243022455.381</v>
+        <v>518776241.2826915</v>
       </c>
       <c r="N81" t="n">
-        <v>17296957623.66307</v>
+        <v>533536414.5626915</v>
       </c>
       <c r="O81" t="n">
-        <v>2.99</v>
+        <v>13.53</v>
       </c>
       <c r="P81" s="1" t="n">
-        <v>45714.36184027778</v>
+        <v>45368.35444444444</v>
       </c>
       <c r="Q81" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R81" t="b">
         <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0.0002210355546336756</v>
+        <v>0.0002272029918394067</v>
       </c>
       <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr"/>
@@ -7520,68 +7520,68 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>akedo</t>
+          <t>blockchain-capital</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ake</t>
+          <t>bcap</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Akedo</t>
+          <t>Blockchain Capital</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.04244612</v>
+        <v>107.53</v>
       </c>
       <c r="F82" t="n">
-        <v>967612409</v>
+        <v>978427406</v>
       </c>
       <c r="G82" t="n">
         <v>81</v>
       </c>
       <c r="H82" t="n">
-        <v>41153473</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>0.050508</v>
+        <v>107.53</v>
       </c>
       <c r="J82" t="n">
-        <v>0.03827888</v>
+        <v>107.53</v>
       </c>
       <c r="K82" t="n">
-        <v>-0.008421905872240711</v>
+        <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>-16.15818</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>22796250000</v>
+        <v>9099111</v>
       </c>
       <c r="N82" t="n">
-        <v>100000000000</v>
+        <v>9099111</v>
       </c>
       <c r="O82" t="n">
-        <v>0.146656</v>
+        <v>107.53</v>
       </c>
       <c r="P82" s="1" t="n">
-        <v>46285.43993055556</v>
+        <v>46287.17361111111</v>
       </c>
       <c r="Q82" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0.000216610184507637</v>
+        <v>0.0002170192307321892</v>
       </c>
       <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr"/>
@@ -7595,68 +7595,68 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>render-token</t>
+          <t>just</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>render</t>
+          <t>jst</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Render</t>
+          <t>JUST</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1.84</v>
+        <v>0.117651</v>
       </c>
       <c r="F83" t="n">
-        <v>954643779</v>
+        <v>963523665</v>
       </c>
       <c r="G83" t="n">
         <v>82</v>
       </c>
       <c r="H83" t="n">
-        <v>79009784</v>
+        <v>32137657</v>
       </c>
       <c r="I83" t="n">
-        <v>1.82</v>
+        <v>0.118548</v>
       </c>
       <c r="J83" t="n">
-        <v>1.7</v>
+        <v>0.111445</v>
       </c>
       <c r="K83" t="n">
-        <v>0.07177500000000001</v>
+        <v>0.00652213</v>
       </c>
       <c r="L83" t="n">
-        <v>4.09602</v>
+        <v>5.85401</v>
       </c>
       <c r="M83" t="n">
-        <v>518776241.2826915</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="N83" t="n">
-        <v>533536414.5626915</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="O83" t="n">
-        <v>13.53</v>
+        <v>0.193254</v>
       </c>
       <c r="P83" s="1" t="n">
-        <v>45368.35444444444</v>
+        <v>44290.85721064815</v>
       </c>
       <c r="Q83" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R83" t="b">
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.0002089201027632141</v>
+        <v>0.0002081402855793612</v>
       </c>
       <c r="T83" t="inlineStr"/>
       <c r="U83" t="inlineStr"/>
@@ -7670,7 +7670,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7689,34 +7689,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="F84" t="n">
-        <v>920031912</v>
+        <v>948940173</v>
       </c>
       <c r="G84" t="n">
         <v>83</v>
       </c>
       <c r="H84" t="n">
-        <v>60625718</v>
+        <v>59826778</v>
       </c>
       <c r="I84" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="J84" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="K84" t="n">
-        <v>-0.06933092253144868</v>
+        <v>0.03534209</v>
       </c>
       <c r="L84" t="n">
-        <v>-3.8122</v>
+        <v>1.92624</v>
       </c>
       <c r="M84" t="n">
-        <v>532318351.197361</v>
+        <v>532499193.619167</v>
       </c>
       <c r="N84" t="n">
-        <v>532326799.985017</v>
+        <v>532508903.268164</v>
       </c>
       <c r="O84" t="n">
         <v>43.84</v>
@@ -7725,13 +7725,13 @@
         <v>44458.66666666666</v>
       </c>
       <c r="Q84" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R84" t="b">
         <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0.0001883961085898052</v>
+        <v>0.0001994521296589983</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -7775,82 +7775,112 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>just</t>
+          <t>pancakeswap-token</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>jst</t>
+          <t>cake</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>JUST</t>
+          <t>PancakeSwap</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.111553</v>
+        <v>2.75</v>
       </c>
       <c r="F85" t="n">
-        <v>913475177</v>
+        <v>875979147</v>
       </c>
       <c r="G85" t="n">
         <v>84</v>
       </c>
       <c r="H85" t="n">
-        <v>30017033</v>
+        <v>145535123</v>
       </c>
       <c r="I85" t="n">
-        <v>0.112971</v>
+        <v>2.84</v>
       </c>
       <c r="J85" t="n">
-        <v>0.109697</v>
+        <v>2.68</v>
       </c>
       <c r="K85" t="n">
-        <v>-0.0007749615324724179</v>
+        <v>0.073916</v>
       </c>
       <c r="L85" t="n">
-        <v>-0.85677</v>
+        <v>2.82672</v>
       </c>
       <c r="M85" t="n">
-        <v>8188743036.341737</v>
+        <v>319002175.3752098</v>
       </c>
       <c r="N85" t="n">
-        <v>8188743036.341737</v>
+        <v>330627631.3973402</v>
       </c>
       <c r="O85" t="n">
-        <v>0.193254</v>
+        <v>43.96</v>
       </c>
       <c r="P85" s="1" t="n">
-        <v>44290.85721064815</v>
+        <v>44316.08914351852</v>
       </c>
       <c r="Q85" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R85" t="b">
         <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>0.0001845081244213526</v>
-      </c>
-      <c r="T85" t="inlineStr"/>
-      <c r="U85" t="inlineStr"/>
-      <c r="V85" t="inlineStr"/>
-      <c r="W85" t="inlineStr"/>
-      <c r="X85" t="inlineStr"/>
-      <c r="Y85" t="inlineStr"/>
-      <c r="Z85" t="inlineStr"/>
-      <c r="AA85" t="inlineStr"/>
+        <v>0.0001559853954915126</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>DeFi</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Exchange descentralizado</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>N/A (token BEP-20)</t>
+        </is>
+      </c>
+      <c r="W85" t="n">
+        <v>2020</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>pancakeswap.finance</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>Intercambio descentralizado en BNB Chain</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>Token BEP-20 sobre BNB Chain</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>Principal exchange descentralizado (DEX) del ecosistema BNB Chain.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7869,28 +7899,28 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.865667</v>
+        <v>0.869078</v>
       </c>
       <c r="F86" t="n">
-        <v>865666733</v>
+        <v>869044877</v>
       </c>
       <c r="G86" t="n">
         <v>85</v>
       </c>
       <c r="H86" t="n">
-        <v>3721102</v>
+        <v>7827337</v>
       </c>
       <c r="I86" t="n">
-        <v>0.8732529999999999</v>
+        <v>0.886178</v>
       </c>
       <c r="J86" t="n">
-        <v>0.849772</v>
+        <v>0.857514</v>
       </c>
       <c r="K86" t="n">
-        <v>-0.007410946386864792</v>
+        <v>-5.9932278523078e-05</v>
       </c>
       <c r="L86" t="n">
-        <v>-0.87037</v>
+        <v>0.01997</v>
       </c>
       <c r="M86" t="n">
         <v>1000000000</v>
@@ -7905,13 +7935,13 @@
         <v>44328.27623842593</v>
       </c>
       <c r="Q86" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R86" t="b">
         <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0.0001561588814840749</v>
+        <v>0.0001518542848525864</v>
       </c>
       <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr"/>
@@ -7925,82 +7955,82 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>pancakeswap-token</t>
+          <t>filecoin</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>cake</t>
+          <t>fil</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>PancakeSwap</t>
+          <t>Filecoin</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2.66</v>
+        <v>1.009</v>
       </c>
       <c r="F87" t="n">
-        <v>847334747</v>
+        <v>838317629</v>
       </c>
       <c r="G87" t="n">
         <v>86</v>
       </c>
       <c r="H87" t="n">
-        <v>103069091</v>
+        <v>159594715</v>
       </c>
       <c r="I87" t="n">
-        <v>2.69</v>
+        <v>1.038</v>
       </c>
       <c r="J87" t="n">
-        <v>2.52</v>
+        <v>0.972841</v>
       </c>
       <c r="K87" t="n">
-        <v>0.058714</v>
+        <v>0.01481956</v>
       </c>
       <c r="L87" t="n">
-        <v>2.31326</v>
+        <v>1.41486</v>
       </c>
       <c r="M87" t="n">
-        <v>318999079.8696931</v>
+        <v>831061204</v>
       </c>
       <c r="N87" t="n">
-        <v>330627631.6087389</v>
+        <v>1957029463</v>
       </c>
       <c r="O87" t="n">
-        <v>43.96</v>
+        <v>236.84</v>
       </c>
       <c r="P87" s="1" t="n">
-        <v>44316.08914351852</v>
+        <v>44287.22894675926</v>
       </c>
       <c r="Q87" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R87" t="b">
         <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>0.0001452884602539513</v>
+        <v>0.0001335484413942665</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>DeFi</t>
+          <t>Almacenamiento descentralizado</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>Exchange descentralizado</t>
+          <t>Infraestructura Web3</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>N/A (token BEP-20)</t>
+          <t>Proof-of-Replication/Spacetime</t>
         </is>
       </c>
       <c r="W87" t="n">
@@ -8008,90 +8038,90 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>pancakeswap.finance</t>
+          <t>filecoin.io</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>Intercambio descentralizado en BNB Chain</t>
+          <t>Almacenamiento descentralizado de archivos</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>Token BEP-20 sobre BNB Chain</t>
+          <t>Blockchain propia (Layer 1)</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>Principal exchange descentralizado (DEX) del ecosistema BNB Chain.</t>
+          <t>Recompensa a quienes ofrecen espacio de almacenamiento descentralizado.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>injective-protocol</t>
+          <t>akedo</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>inj</t>
+          <t>ake</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Injective</t>
+          <t>Akedo</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>8.130000000000001</v>
+        <v>0.03640452</v>
       </c>
       <c r="F88" t="n">
-        <v>812515994</v>
+        <v>828564766</v>
       </c>
       <c r="G88" t="n">
         <v>87</v>
       </c>
       <c r="H88" t="n">
-        <v>204137418</v>
+        <v>38920263</v>
       </c>
       <c r="I88" t="n">
-        <v>8.15</v>
+        <v>0.04574245</v>
       </c>
       <c r="J88" t="n">
-        <v>7.53</v>
+        <v>0.0346635</v>
       </c>
       <c r="K88" t="n">
-        <v>0.055087</v>
+        <v>-0.007543193430547573</v>
       </c>
       <c r="L88" t="n">
-        <v>0.74266</v>
+        <v>-17.12125</v>
       </c>
       <c r="M88" t="n">
-        <v>100000000</v>
+        <v>22796250000</v>
       </c>
       <c r="N88" t="n">
-        <v>100000000</v>
+        <v>100000000000</v>
       </c>
       <c r="O88" t="n">
-        <v>52.62</v>
+        <v>0.146656</v>
       </c>
       <c r="P88" s="1" t="n">
-        <v>45365.29608796296</v>
+        <v>46285.43993055556</v>
       </c>
       <c r="Q88" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S88" t="n">
-        <v>0.0001246417877211647</v>
+        <v>0.0001277381461361803</v>
       </c>
       <c r="T88" t="inlineStr"/>
       <c r="U88" t="inlineStr"/>
@@ -8105,112 +8135,82 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>filecoin</t>
+          <t>injective-protocol</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>fil</t>
+          <t>inj</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Filecoin</t>
+          <t>Injective</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.972024</v>
+        <v>8.15</v>
       </c>
       <c r="F89" t="n">
-        <v>807602487</v>
+        <v>815036849</v>
       </c>
       <c r="G89" t="n">
         <v>88</v>
       </c>
       <c r="H89" t="n">
-        <v>195192833</v>
+        <v>197208993</v>
       </c>
       <c r="I89" t="n">
-        <v>1.02</v>
+        <v>8.66</v>
       </c>
       <c r="J89" t="n">
-        <v>0.91861</v>
+        <v>7.81</v>
       </c>
       <c r="K89" t="n">
-        <v>-0.04375422227097114</v>
+        <v>0.111556</v>
       </c>
       <c r="L89" t="n">
-        <v>-4.20773</v>
+        <v>1.58886</v>
       </c>
       <c r="M89" t="n">
-        <v>830845988</v>
+        <v>100000000</v>
       </c>
       <c r="N89" t="n">
-        <v>1957031550</v>
+        <v>100000000</v>
       </c>
       <c r="O89" t="n">
-        <v>236.84</v>
+        <v>52.62</v>
       </c>
       <c r="P89" s="1" t="n">
-        <v>44287.22894675926</v>
+        <v>45365.29608796296</v>
       </c>
       <c r="Q89" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R89" t="b">
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>0.0001217281977365792</v>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>Almacenamiento descentralizado</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>Infraestructura Web3</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>Proof-of-Replication/Spacetime</t>
-        </is>
-      </c>
-      <c r="W89" t="n">
-        <v>2020</v>
-      </c>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>filecoin.io</t>
-        </is>
-      </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>Almacenamiento descentralizado de archivos</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Layer 1)</t>
-        </is>
-      </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>Recompensa a quienes ofrecen espacio de almacenamiento descentralizado.</t>
-        </is>
-      </c>
+        <v>0.0001196788519579596</v>
+      </c>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr"/>
+      <c r="W89" t="inlineStr"/>
+      <c r="X89" t="inlineStr"/>
+      <c r="Y89" t="inlineStr"/>
+      <c r="Z89" t="inlineStr"/>
+      <c r="AA89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8229,34 +8229,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>61.69</v>
+        <v>63.43</v>
       </c>
       <c r="F90" t="n">
-        <v>792220247</v>
+        <v>814699071</v>
       </c>
       <c r="G90" t="n">
         <v>89</v>
       </c>
       <c r="H90" t="n">
-        <v>206679904</v>
+        <v>170596830</v>
       </c>
       <c r="I90" t="n">
-        <v>64.76000000000001</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="J90" t="n">
-        <v>57.06</v>
+        <v>61.89</v>
       </c>
       <c r="K90" t="n">
-        <v>-2.915408481257757</v>
+        <v>0.13786</v>
       </c>
       <c r="L90" t="n">
-        <v>-4.34033</v>
+        <v>0.25428</v>
       </c>
       <c r="M90" t="n">
-        <v>12842253.62878004</v>
+        <v>12843030.2492792</v>
       </c>
       <c r="N90" t="n">
-        <v>12842428.78110528</v>
+        <v>12843282.71574738</v>
       </c>
       <c r="O90" t="n">
         <v>1493.59</v>
@@ -8265,13 +8265,13 @@
         <v>43088.66666666666</v>
       </c>
       <c r="Q90" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R90" t="b">
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>0.0001126069040446216</v>
+        <v>0.0001194776197749907</v>
       </c>
       <c r="T90" t="inlineStr"/>
       <c r="U90" t="inlineStr"/>
@@ -8285,7 +8285,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8304,28 +8304,28 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.009202760000000001</v>
+        <v>0.009269289999999999</v>
       </c>
       <c r="F91" t="n">
-        <v>791300059</v>
+        <v>796885287</v>
       </c>
       <c r="G91" t="n">
         <v>90</v>
       </c>
       <c r="H91" t="n">
-        <v>15098082</v>
+        <v>16263493</v>
       </c>
       <c r="I91" t="n">
-        <v>0.009460730000000001</v>
+        <v>0.009602390000000001</v>
       </c>
       <c r="J91" t="n">
-        <v>0.008687230000000001</v>
+        <v>0.009108389999999999</v>
       </c>
       <c r="K91" t="n">
-        <v>-0.000247786137227807</v>
+        <v>-7.7648113541154e-05</v>
       </c>
       <c r="L91" t="n">
-        <v>-2.56094</v>
+        <v>-0.64808</v>
       </c>
       <c r="M91" t="n">
         <v>85985041177</v>
@@ -8340,13 +8340,13 @@
         <v>44304.71413194444</v>
       </c>
       <c r="Q91" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R91" t="b">
         <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>0.0001120612549714167</v>
+        <v>0.000108865008411151</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -8390,68 +8390,68 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>eutbl</t>
+          <t>aerodrome-finance</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>eutbl</t>
+          <t>aero</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Spiko EU T-Bills Money Market Fund</t>
+          <t>Aerodrome Finance</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1.2</v>
+        <v>0.787972</v>
       </c>
       <c r="F92" t="n">
-        <v>757929367</v>
+        <v>785722199</v>
       </c>
       <c r="G92" t="n">
         <v>91</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>81946992</v>
       </c>
       <c r="I92" t="n">
-        <v>1.21</v>
+        <v>0.7992629999999999</v>
       </c>
       <c r="J92" t="n">
-        <v>1.2</v>
+        <v>0.683981</v>
       </c>
       <c r="K92" t="n">
-        <v>-0.004682058472634365</v>
+        <v>0.081188</v>
       </c>
       <c r="L92" t="n">
-        <v>-0.38744</v>
+        <v>11.31651</v>
       </c>
       <c r="M92" t="n">
-        <v>629624067.49395</v>
+        <v>996570413.9183272</v>
       </c>
       <c r="N92" t="n">
-        <v>629624067.49395</v>
+        <v>1988034890.229641</v>
       </c>
       <c r="O92" t="n">
-        <v>1.26</v>
+        <v>2.32</v>
       </c>
       <c r="P92" s="1" t="n">
-        <v>46049.54175925926</v>
+        <v>45633.25043981482</v>
       </c>
       <c r="Q92" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S92" t="n">
-        <v>9.227324734470811e-05</v>
+        <v>0.0001022145676870272</v>
       </c>
       <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr"/>
@@ -8465,29 +8465,29 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>superstate-short-duration-us-government-securities-fund-ustb</t>
+          <t>eutbl</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ustb</t>
+          <t>eutbl</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Invesco Short Duration US Government Securities Fund</t>
+          <t>Spiko EU T-Bills Money Market Fund</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>11.22</v>
+        <v>1.21</v>
       </c>
       <c r="F93" t="n">
-        <v>738906515</v>
+        <v>751325184</v>
       </c>
       <c r="G93" t="n">
         <v>92</v>
@@ -8496,37 +8496,37 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>11.22</v>
+        <v>1.21</v>
       </c>
       <c r="J93" t="n">
-        <v>11.22</v>
+        <v>1.2</v>
       </c>
       <c r="K93" t="n">
-        <v>0.001101</v>
+        <v>0.00228199</v>
       </c>
       <c r="L93" t="n">
-        <v>0.009809999999999999</v>
+        <v>0.18932</v>
       </c>
       <c r="M93" t="n">
-        <v>65843132.622857</v>
+        <v>622138754.14688</v>
       </c>
       <c r="N93" t="n">
-        <v>65843132.622857</v>
+        <v>622138754.14688</v>
       </c>
       <c r="O93" t="n">
-        <v>11.22</v>
+        <v>1.26</v>
       </c>
       <c r="P93" s="1" t="n">
-        <v>46289.55208333334</v>
+        <v>46049.54175925926</v>
       </c>
       <c r="Q93" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R93" t="b">
         <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>8.099315940233796e-05</v>
+        <v>8.172245033165977e-05</v>
       </c>
       <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr"/>
@@ -8540,68 +8540,68 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>stable-2</t>
+          <t>superstate-short-duration-us-government-securities-fund-ustb</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>ustb</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>​​Stable</t>
+          <t>Invesco Short Duration US Government Securities Fund</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.0264549</v>
+        <v>11.22</v>
       </c>
       <c r="F94" t="n">
-        <v>703950747</v>
+        <v>743434067</v>
       </c>
       <c r="G94" t="n">
         <v>93</v>
       </c>
       <c r="H94" t="n">
-        <v>12196843</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>0.0272989</v>
+        <v>11.22</v>
       </c>
       <c r="J94" t="n">
-        <v>0.02452288</v>
+        <v>11.22</v>
       </c>
       <c r="K94" t="n">
-        <v>0.00105555</v>
+        <v>0.001127</v>
       </c>
       <c r="L94" t="n">
-        <v>4.17665</v>
+        <v>0.01004</v>
       </c>
       <c r="M94" t="n">
-        <v>26609465706</v>
+        <v>66239925.553293</v>
       </c>
       <c r="N94" t="n">
-        <v>100000000000</v>
+        <v>65432278.887564</v>
       </c>
       <c r="O94" t="n">
-        <v>0.04323745</v>
+        <v>11.22</v>
       </c>
       <c r="P94" s="1" t="n">
-        <v>46156.97986111111</v>
+        <v>46290.55567129629</v>
       </c>
       <c r="Q94" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R94" t="b">
         <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>6.026524031149454e-05</v>
+        <v>7.702129543118554e-05</v>
       </c>
       <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
@@ -8615,143 +8615,173 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>aptos</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>apt</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>GHO</t>
+          <t>Aptos</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.998915</v>
+        <v>0.8325709999999999</v>
       </c>
       <c r="F95" t="n">
-        <v>698241826</v>
+        <v>724751497</v>
       </c>
       <c r="G95" t="n">
         <v>94</v>
       </c>
       <c r="H95" t="n">
-        <v>6097158</v>
+        <v>101637914</v>
       </c>
       <c r="I95" t="n">
-        <v>0.999329</v>
+        <v>0.85581</v>
       </c>
       <c r="J95" t="n">
-        <v>0.998743</v>
+        <v>0.789766</v>
       </c>
       <c r="K95" t="n">
-        <v>-4.182532340247e-06</v>
+        <v>0.02921252</v>
       </c>
       <c r="L95" t="n">
-        <v>-0.00078</v>
+        <v>3.11922</v>
       </c>
       <c r="M95" t="n">
-        <v>699000000</v>
+        <v>870774816.4093153</v>
       </c>
       <c r="N95" t="n">
-        <v>699000000</v>
+        <v>1209214727.55166</v>
       </c>
       <c r="O95" t="n">
-        <v>1.03</v>
+        <v>19.92</v>
       </c>
       <c r="P95" s="1" t="n">
-        <v>45350.38608796296</v>
+        <v>44952.26755787037</v>
       </c>
       <c r="Q95" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R95" t="b">
         <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>5.687998919688544e-05</v>
-      </c>
-      <c r="T95" t="inlineStr"/>
-      <c r="U95" t="inlineStr"/>
-      <c r="V95" t="inlineStr"/>
-      <c r="W95" t="inlineStr"/>
-      <c r="X95" t="inlineStr"/>
-      <c r="Y95" t="inlineStr"/>
-      <c r="Z95" t="inlineStr"/>
-      <c r="AA95" t="inlineStr"/>
+        <v>6.589110239147358e-05</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Plataforma de contratos inteligentes</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Layer 1</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Proof of Stake (BFT)</t>
+        </is>
+      </c>
+      <c r="W95" t="n">
+        <v>2022</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>aptosfoundation.org</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>Contratos inteligentes de alto rendimiento</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Layer 1)</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>Desarrollada por exingenieros del proyecto Diem (Meta/Facebook).</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>aerodrome-finance</t>
+          <t>stable-2</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>aero</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Aerodrome Finance</t>
+          <t>​​Stable</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.697692</v>
+        <v>0.02631056</v>
       </c>
       <c r="F96" t="n">
-        <v>695345128</v>
+        <v>700639422</v>
       </c>
       <c r="G96" t="n">
         <v>95</v>
       </c>
       <c r="H96" t="n">
-        <v>68096401</v>
+        <v>9115526</v>
       </c>
       <c r="I96" t="n">
-        <v>0.7153389999999999</v>
+        <v>0.02737397</v>
       </c>
       <c r="J96" t="n">
-        <v>0.651207</v>
+        <v>0.02615656</v>
       </c>
       <c r="K96" t="n">
-        <v>-0.0154599686984972</v>
+        <v>-0.000168753897356013</v>
       </c>
       <c r="L96" t="n">
-        <v>-2.05333</v>
+        <v>-0.61511</v>
       </c>
       <c r="M96" t="n">
-        <v>996635960.3533072</v>
+        <v>26639136488</v>
       </c>
       <c r="N96" t="n">
-        <v>1988034890.229641</v>
+        <v>100000000000</v>
       </c>
       <c r="O96" t="n">
-        <v>2.32</v>
+        <v>0.04323745</v>
       </c>
       <c r="P96" s="1" t="n">
-        <v>45633.25043981482</v>
+        <v>46156.97986111111</v>
       </c>
       <c r="Q96" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R96" t="b">
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>5.51623178307576e-05</v>
+        <v>5.152626664681893e-05</v>
       </c>
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
@@ -8765,112 +8795,82 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>aptos</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>apt</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Aptos</t>
+          <t>GHO</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.791697</v>
+        <v>0.998972</v>
       </c>
       <c r="F97" t="n">
-        <v>689351600</v>
+        <v>698274572</v>
       </c>
       <c r="G97" t="n">
         <v>96</v>
       </c>
       <c r="H97" t="n">
-        <v>90235638</v>
+        <v>13503661</v>
       </c>
       <c r="I97" t="n">
-        <v>0.822106</v>
+        <v>0.999205</v>
       </c>
       <c r="J97" t="n">
-        <v>0.743902</v>
+        <v>0.998501</v>
       </c>
       <c r="K97" t="n">
-        <v>-0.02512260180989745</v>
+        <v>9.83e-05</v>
       </c>
       <c r="L97" t="n">
-        <v>-3.36128</v>
+        <v>0.01256</v>
       </c>
       <c r="M97" t="n">
-        <v>870726490.2274346</v>
+        <v>699000000</v>
       </c>
       <c r="N97" t="n">
-        <v>1209166859.596561</v>
+        <v>699000000</v>
       </c>
       <c r="O97" t="n">
-        <v>19.92</v>
+        <v>1.03</v>
       </c>
       <c r="P97" s="1" t="n">
-        <v>44952.26755787037</v>
+        <v>45350.38608796296</v>
       </c>
       <c r="Q97" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R97" t="b">
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>5.160830169663334e-05</v>
-      </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>Plataforma de contratos inteligentes</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>Layer 1</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>Proof of Stake (BFT)</t>
-        </is>
-      </c>
-      <c r="W97" t="n">
-        <v>2022</v>
-      </c>
-      <c r="X97" t="inlineStr">
-        <is>
-          <t>aptosfoundation.org</t>
-        </is>
-      </c>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>Contratos inteligentes de alto rendimiento</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Layer 1)</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>Desarrollada por exingenieros del proyecto Diem (Meta/Facebook).</t>
-        </is>
-      </c>
+        <v>5.011740068191353e-05</v>
+      </c>
+      <c r="T97" t="inlineStr"/>
+      <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr"/>
+      <c r="W97" t="inlineStr"/>
+      <c r="X97" t="inlineStr"/>
+      <c r="Y97" t="inlineStr"/>
+      <c r="Z97" t="inlineStr"/>
+      <c r="AA97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8889,28 +8889,28 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.661406</v>
+        <v>0.702283</v>
       </c>
       <c r="F98" t="n">
-        <v>638488563</v>
+        <v>677749555</v>
       </c>
       <c r="G98" t="n">
         <v>97</v>
       </c>
       <c r="H98" t="n">
-        <v>47754404</v>
+        <v>40195319</v>
       </c>
       <c r="I98" t="n">
-        <v>0.693611</v>
+        <v>0.720453</v>
       </c>
       <c r="J98" t="n">
-        <v>0.636795</v>
+        <v>0.662928</v>
       </c>
       <c r="K98" t="n">
-        <v>-0.03011208614870931</v>
+        <v>0.03319348</v>
       </c>
       <c r="L98" t="n">
-        <v>-4.37637</v>
+        <v>5.01347</v>
       </c>
       <c r="M98" t="n">
         <v>965350000</v>
@@ -8925,13 +8925,13 @@
         <v>45378.63525462963</v>
       </c>
       <c r="Q98" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R98" t="b">
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>2.144775950369468e-05</v>
+        <v>3.788956471751625e-05</v>
       </c>
       <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr"/>
@@ -8945,68 +8945,68 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>pudgy-penguins</t>
+          <t>flare-networks</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>pengu</t>
+          <t>flr</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Pudgy Penguins</t>
+          <t>Flare</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.009929500000000001</v>
+        <v>0.00723579</v>
       </c>
       <c r="F99" t="n">
-        <v>624172251</v>
+        <v>628745882</v>
       </c>
       <c r="G99" t="n">
         <v>98</v>
       </c>
       <c r="H99" t="n">
-        <v>330460231</v>
+        <v>5236400</v>
       </c>
       <c r="I99" t="n">
-        <v>0.01038513</v>
+        <v>0.00735749</v>
       </c>
       <c r="J99" t="n">
-        <v>0.00947753</v>
+        <v>0.00701469</v>
       </c>
       <c r="K99" t="n">
-        <v>-0.000391774588025516</v>
+        <v>9.613e-05</v>
       </c>
       <c r="L99" t="n">
-        <v>-3.71032</v>
+        <v>1.34649</v>
       </c>
       <c r="M99" t="n">
-        <v>62860396090</v>
+        <v>86909124669.39235</v>
       </c>
       <c r="N99" t="n">
-        <v>76722808329.65067</v>
+        <v>106621854713.5677</v>
       </c>
       <c r="O99" t="n">
-        <v>0.06844699999999999</v>
+        <v>0.150073</v>
       </c>
       <c r="P99" s="1" t="n">
-        <v>45643.21206018519</v>
+        <v>44935.80144675926</v>
       </c>
       <c r="Q99" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R99" t="b">
         <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>1.295853515550497e-05</v>
+        <v>8.695490232853771e-06</v>
       </c>
       <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr"/>
@@ -9020,68 +9020,68 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>flare-networks</t>
+          <t>beldex</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>flr</t>
+          <t>bdx</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Flare</t>
+          <t>Beldex</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.00712598</v>
+        <v>0.078194</v>
       </c>
       <c r="F100" t="n">
-        <v>619178957</v>
+        <v>615482724</v>
       </c>
       <c r="G100" t="n">
         <v>99</v>
       </c>
       <c r="H100" t="n">
-        <v>3353076</v>
+        <v>2909104</v>
       </c>
       <c r="I100" t="n">
-        <v>0.00725757</v>
+        <v>0.078414</v>
       </c>
       <c r="J100" t="n">
-        <v>0.00694767</v>
+        <v>0.076556</v>
       </c>
       <c r="K100" t="n">
-        <v>-0.000113533696021038</v>
+        <v>0.0017067</v>
       </c>
       <c r="L100" t="n">
-        <v>-1.57288</v>
+        <v>2.23001</v>
       </c>
       <c r="M100" t="n">
-        <v>86890312184.51483</v>
+        <v>7870839322.119331</v>
       </c>
       <c r="N100" t="n">
-        <v>106616106401.7717</v>
+        <v>9939718245.379999</v>
       </c>
       <c r="O100" t="n">
-        <v>0.150073</v>
+        <v>0.450785</v>
       </c>
       <c r="P100" s="1" t="n">
-        <v>44935.80144675926</v>
+        <v>43450.66666666666</v>
       </c>
       <c r="Q100" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R100" t="b">
         <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>9.997633423098637e-06</v>
+        <v>7.939269652626453e-07</v>
       </c>
       <c r="T100" t="inlineStr"/>
       <c r="U100" t="inlineStr"/>
@@ -9095,62 +9095,62 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>beldex</t>
+          <t>pudgy-penguins</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>bdx</t>
+          <t>pengu</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Beldex</t>
+          <t>Pudgy Penguins</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.076526</v>
+        <v>0.00976846</v>
       </c>
       <c r="F101" t="n">
-        <v>602318849</v>
+        <v>614150079</v>
       </c>
       <c r="G101" t="n">
         <v>100</v>
       </c>
       <c r="H101" t="n">
-        <v>3397765</v>
+        <v>295384177</v>
       </c>
       <c r="I101" t="n">
-        <v>0.07681499999999999</v>
+        <v>0.01012583</v>
       </c>
       <c r="J101" t="n">
-        <v>0.07506</v>
+        <v>0.009481379999999999</v>
       </c>
       <c r="K101" t="n">
-        <v>0.00037111</v>
+        <v>-0.000222560486343474</v>
       </c>
       <c r="L101" t="n">
-        <v>0.43853</v>
+        <v>-2.2942</v>
       </c>
       <c r="M101" t="n">
-        <v>7870799519.638308</v>
+        <v>62860396090</v>
       </c>
       <c r="N101" t="n">
-        <v>9939718245.379999</v>
+        <v>76722804262.29102</v>
       </c>
       <c r="O101" t="n">
-        <v>0.450785</v>
+        <v>0.06844699999999999</v>
       </c>
       <c r="P101" s="1" t="n">
-        <v>43450.66666666666</v>
+        <v>45643.21206018519</v>
       </c>
       <c r="Q101" s="1" t="n">
-        <v>46289.57523148148</v>
+        <v>46290.59189814814</v>
       </c>
       <c r="R101" t="b">
         <v>0</v>

--- a/src/xlsx/enriched_data.xlsx
+++ b/src/xlsx/enriched_data.xlsx
@@ -560,7 +560,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -579,34 +579,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>83598</v>
+        <v>83960</v>
       </c>
       <c r="F2" t="n">
-        <v>1679162755062</v>
+        <v>1686713805167</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>38514548082</v>
+        <v>25094148124</v>
       </c>
       <c r="I2" t="n">
-        <v>85208</v>
+        <v>84296</v>
       </c>
       <c r="J2" t="n">
-        <v>83513</v>
+        <v>83230</v>
       </c>
       <c r="K2" t="n">
-        <v>-604.7274447487289</v>
+        <v>-256.859398715038</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.77851</v>
+        <v>-0.32156</v>
       </c>
       <c r="M2" t="n">
-        <v>20089181</v>
+        <v>20089568</v>
       </c>
       <c r="N2" t="n">
-        <v>20089196</v>
+        <v>20089609</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -615,7 +615,7 @@
         <v>45936.45673611111</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
@@ -665,7 +665,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -684,34 +684,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2688.92</v>
+        <v>2685.41</v>
       </c>
       <c r="F3" t="n">
-        <v>328251353932</v>
+        <v>327852902474</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>15862968693</v>
+        <v>9448881653</v>
       </c>
       <c r="I3" t="n">
-        <v>2739.52</v>
+        <v>2697.72</v>
       </c>
       <c r="J3" t="n">
-        <v>2653.81</v>
+        <v>2669.73</v>
       </c>
       <c r="K3" t="n">
-        <v>21.97</v>
+        <v>-20.30064927189733</v>
       </c>
       <c r="L3" t="n">
-        <v>0.79044</v>
+        <v>-0.78586</v>
       </c>
       <c r="M3" t="n">
-        <v>122078905.3531288</v>
+        <v>122081755.2385784</v>
       </c>
       <c r="N3" t="n">
-        <v>122078905.3531288</v>
+        <v>122081755.2385784</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -720,13 +720,13 @@
         <v>45893.47295138889</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1951907754594442</v>
+        <v>0.1940729385010486</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -789,34 +789,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.99973</v>
+        <v>0.999844</v>
       </c>
       <c r="F4" t="n">
-        <v>183727460118</v>
+        <v>183789394509</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>72786037039</v>
+        <v>49145434159</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9998899999999999</v>
+        <v>0.999887</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999287</v>
+        <v>0.999719</v>
       </c>
       <c r="K4" t="n">
-        <v>6.05e-06</v>
+        <v>8.093e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00347</v>
+        <v>0.00231</v>
       </c>
       <c r="M4" t="n">
-        <v>183779015975.4778</v>
+        <v>183818815971.0418</v>
       </c>
       <c r="N4" t="n">
-        <v>189245961986.9062</v>
+        <v>189285761986.9062</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -825,13 +825,13 @@
         <v>43304.66666666666</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1090902637525081</v>
+        <v>0.1086302861932471</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -894,34 +894,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>772.7</v>
+        <v>772.3099999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>102856673958</v>
+        <v>102840641561</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1165366190</v>
+        <v>743839388</v>
       </c>
       <c r="I5" t="n">
-        <v>785.3099999999999</v>
+        <v>777.74</v>
       </c>
       <c r="J5" t="n">
-        <v>770.72</v>
+        <v>769.51</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.873413513556216</v>
+        <v>-3.343418307023285</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.62303</v>
+        <v>-0.44597</v>
       </c>
       <c r="M5" t="n">
-        <v>133159842.41</v>
+        <v>133159792.88</v>
       </c>
       <c r="N5" t="n">
-        <v>133159833.97</v>
+        <v>133159791.14</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -930,13 +930,13 @@
         <v>45943.02875</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06091126797012559</v>
+        <v>0.06062037549076425</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -999,28 +999,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="F6" t="n">
-        <v>99229873529</v>
+        <v>96751811786</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>6282193834</v>
+        <v>3887008543</v>
       </c>
       <c r="I6" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="J6" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="K6" t="n">
-        <v>0.07800700000000001</v>
+        <v>-0.05239949727053506</v>
       </c>
       <c r="L6" t="n">
-        <v>5.11372</v>
+        <v>-3.32178</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -1035,13 +1035,13 @@
         <v>45855.82005787037</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R6" t="b">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05875059152725504</v>
+        <v>0.05700915032503313</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1104,34 +1104,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999853</v>
+        <v>0.9998899999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>75342386451</v>
+        <v>75325511675</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>20818639756</v>
+        <v>13529945029</v>
       </c>
       <c r="I7" t="n">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.99942</v>
+        <v>0.999804</v>
       </c>
       <c r="K7" t="n">
-        <v>3.113e-05</v>
+        <v>-3.190448686907e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00606</v>
+        <v>-0.00778</v>
       </c>
       <c r="M7" t="n">
-        <v>75354142543.02426</v>
+        <v>75333929675.06418</v>
       </c>
       <c r="N7" t="n">
-        <v>75302398987.78542</v>
+        <v>75334626227.45894</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -1140,13 +1140,13 @@
         <v>43418.66666666666</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04451955466178284</v>
+        <v>0.04430142207041121</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1209,34 +1209,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>119.58</v>
+        <v>120.65</v>
       </c>
       <c r="F8" t="n">
-        <v>70220425043</v>
+        <v>70914599486</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>5871439186</v>
+        <v>4716262120</v>
       </c>
       <c r="I8" t="n">
-        <v>122.01</v>
+        <v>122.75</v>
       </c>
       <c r="J8" t="n">
-        <v>114.46</v>
+        <v>118.59</v>
       </c>
       <c r="K8" t="n">
-        <v>4.61</v>
+        <v>0.7919079999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>4.02766</v>
+        <v>0.60627</v>
       </c>
       <c r="M8" t="n">
-        <v>587647593.3659807</v>
+        <v>587712762.0220828</v>
       </c>
       <c r="N8" t="n">
-        <v>634686100.9544628</v>
+        <v>634763960.9711117</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -1245,13 +1245,13 @@
         <v>45676.13572916666</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R8" t="b">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.04146813190715139</v>
+        <v>0.04168535335288052</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1314,34 +1314,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.337211</v>
+        <v>0.336607</v>
       </c>
       <c r="F9" t="n">
-        <v>32018650054</v>
+        <v>31961192093</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>461988718</v>
+        <v>267042689</v>
       </c>
       <c r="I9" t="n">
-        <v>0.341481</v>
+        <v>0.338229</v>
       </c>
       <c r="J9" t="n">
-        <v>0.336802</v>
+        <v>0.33599</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.002870799508586985</v>
+        <v>-0.000351358735391327</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.8316</v>
+        <v>-0.13818</v>
       </c>
       <c r="M9" t="n">
-        <v>94964948406.9399</v>
+        <v>94967057481.15408</v>
       </c>
       <c r="N9" t="n">
-        <v>94966809744.41438</v>
+        <v>94968826620.64949</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1350,13 +1350,13 @@
         <v>45629.67407407407</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01870931820608082</v>
+        <v>0.01858246983228179</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1419,34 +1419,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1593.72</v>
+        <v>1539.58</v>
       </c>
       <c r="F10" t="n">
-        <v>27023589668</v>
+        <v>26102989564</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>1279929296</v>
+        <v>778167418</v>
       </c>
       <c r="I10" t="n">
-        <v>1622.95</v>
+        <v>1596.86</v>
       </c>
       <c r="J10" t="n">
-        <v>1491.28</v>
+        <v>1517.49</v>
       </c>
       <c r="K10" t="n">
-        <v>80.68000000000001</v>
+        <v>-76.6470678720184</v>
       </c>
       <c r="L10" t="n">
-        <v>5.35021</v>
+        <v>-4.78454</v>
       </c>
       <c r="M10" t="n">
-        <v>16951193.9155448</v>
+        <v>16952175.1655448</v>
       </c>
       <c r="N10" t="n">
-        <v>16951806.4155448</v>
+        <v>16953504.8530448</v>
       </c>
       <c r="O10" t="n">
         <v>3191.93</v>
@@ -1455,13 +1455,13 @@
         <v>42671.66666666666</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01573349708825826</v>
+        <v>0.01510802742209395</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1524,34 +1524,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.027</v>
+        <v>1.026</v>
       </c>
       <c r="F11" t="n">
-        <v>23712065535</v>
+        <v>23747335901</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>585257867</v>
+        <v>22346272</v>
       </c>
       <c r="I11" t="n">
-        <v>1.047</v>
+        <v>1.032</v>
       </c>
       <c r="J11" t="n">
-        <v>1.012</v>
+        <v>1.023</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.009244703155131262</v>
+        <v>-0.001108940741380682</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.89492</v>
+        <v>-0.10223</v>
       </c>
       <c r="M11" t="n">
-        <v>23089131934.788</v>
+        <v>23149018497.978</v>
       </c>
       <c r="N11" t="n">
-        <v>23089131934.788</v>
+        <v>23149018497.978</v>
       </c>
       <c r="O11" t="n">
         <v>1.061</v>
@@ -1560,13 +1560,13 @@
         <v>46237.59675925926</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R11" t="b">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01376064737561408</v>
+        <v>0.01371091235993534</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
@@ -1580,7 +1580,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1599,28 +1599,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>92.18000000000001</v>
+        <v>91.83</v>
       </c>
       <c r="F12" t="n">
-        <v>20488667956</v>
+        <v>20428508325</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1155605568</v>
+        <v>693710930</v>
       </c>
       <c r="I12" t="n">
-        <v>94.73999999999999</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>91</v>
+        <v>90.41</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1386147680552199</v>
+        <v>-1.224155095273204</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.12922</v>
+        <v>-1.3402</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1635,13 +1635,13 @@
         <v>46288.22002314815</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R12" t="b">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01184029930262358</v>
+        <v>0.01174254830541985</v>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
@@ -1655,7 +1655,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1674,34 +1674,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.097402</v>
+        <v>0.097069</v>
       </c>
       <c r="F13" t="n">
-        <v>15194781531</v>
+        <v>15151071047</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>1266625089</v>
+        <v>996069177</v>
       </c>
       <c r="I13" t="n">
-        <v>0.098981</v>
+        <v>0.099703</v>
       </c>
       <c r="J13" t="n">
-        <v>0.094092</v>
+        <v>0.09641</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00300281</v>
+        <v>-0.000756068771230411</v>
       </c>
       <c r="L13" t="n">
-        <v>3.13939</v>
+        <v>-0.76364</v>
       </c>
       <c r="M13" t="n">
-        <v>156060896383.7052</v>
+        <v>156075366383.7053</v>
       </c>
       <c r="N13" t="n">
-        <v>171774773126.5791</v>
+        <v>171787443126.579</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1710,13 +1710,13 @@
         <v>44323.88082175926</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R13" t="b">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.008686451740935837</v>
+        <v>0.008612552064248677</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1779,28 +1779,28 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>13.87</v>
+        <v>14.22</v>
       </c>
       <c r="F14" t="n">
-        <v>10373383774</v>
+        <v>10640884885</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>1063141253</v>
+        <v>707084096</v>
       </c>
       <c r="I14" t="n">
-        <v>14.19</v>
+        <v>14.35</v>
       </c>
       <c r="J14" t="n">
-        <v>12.46</v>
+        <v>13.69</v>
       </c>
       <c r="K14" t="n">
-        <v>1.34</v>
+        <v>0.198978</v>
       </c>
       <c r="L14" t="n">
-        <v>10.71284</v>
+        <v>1.36679</v>
       </c>
       <c r="M14" t="n">
         <v>748099970.424884</v>
@@ -1815,13 +1815,13 @@
         <v>44325.67635416667</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.005814090617351435</v>
+        <v>0.00593760492790068</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1884,34 +1884,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>549.15</v>
+        <v>549.3</v>
       </c>
       <c r="F15" t="n">
-        <v>10313844161</v>
+        <v>10336344317</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>144904867</v>
+        <v>92067811</v>
       </c>
       <c r="I15" t="n">
-        <v>577.46</v>
+        <v>561.22</v>
       </c>
       <c r="J15" t="n">
-        <v>545.25</v>
+        <v>546.01</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.992583697525561</v>
+        <v>-7.378489186112347</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.38245</v>
+        <v>-1.39045</v>
       </c>
       <c r="M15" t="n">
-        <v>18809274.09052855</v>
+        <v>18809710.28932691</v>
       </c>
       <c r="N15" t="n">
-        <v>18809314.29046824</v>
+        <v>18809742.0893211</v>
       </c>
       <c r="O15" t="n">
         <v>797.73</v>
@@ -1920,13 +1920,13 @@
         <v>46036.48202546296</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.005778619727307948</v>
+        <v>0.005756984906683606</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1989,28 +1989,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>83.58</v>
+        <v>83.8</v>
       </c>
       <c r="F16" t="n">
-        <v>9932139589</v>
+        <v>9959623112</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>128664165</v>
+        <v>77723889</v>
       </c>
       <c r="I16" t="n">
-        <v>85.16</v>
+        <v>84.13</v>
       </c>
       <c r="J16" t="n">
-        <v>83.58</v>
+        <v>83.17</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5541301889751509</v>
+        <v>-0.346154198101928</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.86936</v>
+        <v>-0.44687</v>
       </c>
       <c r="M16" t="n">
         <v>118852171</v>
@@ -2025,13 +2025,13 @@
         <v>46286.85358796296</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R16" t="b">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.005551218166896258</v>
+        <v>0.005533555258256532</v>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
@@ -2045,7 +2045,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2064,34 +2064,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.99963</v>
+        <v>0.999721</v>
       </c>
       <c r="F17" t="n">
-        <v>9719421143</v>
+        <v>9746623829</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>125292033</v>
+        <v>172309969</v>
       </c>
       <c r="I17" t="n">
-        <v>0.99998</v>
+        <v>0.999868</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9994</v>
+        <v>0.999566</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.000183372176973173</v>
+        <v>5.916e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.01564</v>
+        <v>4e-05</v>
       </c>
       <c r="M17" t="n">
-        <v>9723114647.376017</v>
+        <v>9748883836.049854</v>
       </c>
       <c r="N17" t="n">
-        <v>9723685294.041584</v>
+        <v>9749012892.848028</v>
       </c>
       <c r="O17" t="n">
         <v>1.057</v>
@@ -2100,13 +2100,13 @@
         <v>45593.90336805556</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.005424490561053617</v>
+        <v>0.005407227474515479</v>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
@@ -2120,7 +2120,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2139,28 +2139,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.253462</v>
+        <v>0.254453</v>
       </c>
       <c r="F18" t="n">
-        <v>9508956148</v>
+        <v>9549016320</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>716129718</v>
+        <v>640158278</v>
       </c>
       <c r="I18" t="n">
-        <v>0.258045</v>
+        <v>0.26468</v>
       </c>
       <c r="J18" t="n">
-        <v>0.244758</v>
+        <v>0.251137</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0097284</v>
+        <v>-0.00139232354027119</v>
       </c>
       <c r="L18" t="n">
-        <v>3.92179</v>
+        <v>-0.55041</v>
       </c>
       <c r="M18" t="n">
         <v>37529061988.53558</v>
@@ -2175,13 +2175,13 @@
         <v>44440.91678240741</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R18" t="b">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.005299105454911796</v>
+        <v>0.005290028400833337</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.01183191</v>
+        <v>0.0123665</v>
       </c>
       <c r="F19" t="n">
-        <v>8393353185</v>
+        <v>8770640199</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>21898288</v>
+        <v>21274799</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01211884</v>
+        <v>0.01245443</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01183761</v>
+        <v>0.01041574</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.000213334567861646</v>
+        <v>0.00048121</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.88845</v>
+        <v>4.06067</v>
       </c>
       <c r="M19" t="n">
-        <v>709240425836.8521</v>
+        <v>709240980011.2261</v>
       </c>
       <c r="N19" t="n">
         <v>1142408526965.963</v>
@@ -2280,13 +2280,13 @@
         <v>46259.82847222222</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R19" t="b">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.004634481886855332</v>
+        <v>0.004828381164758426</v>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
@@ -2300,7 +2300,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2319,28 +2319,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8.83</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>8118726601</v>
+        <v>8240992585</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>418695</v>
+        <v>256366</v>
       </c>
       <c r="I20" t="n">
-        <v>8.970000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="J20" t="n">
-        <v>8.77</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.07010463306942505</v>
+        <v>0.123426</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.78849</v>
+        <v>1.39349</v>
       </c>
       <c r="M20" t="n">
         <v>919857851.9</v>
@@ -2355,13 +2355,13 @@
         <v>46146.39930555555</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.004470872335612828</v>
+        <v>0.004514252364426471</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2424,34 +2424,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.216625</v>
+        <v>0.217446</v>
       </c>
       <c r="F21" t="n">
-        <v>7572724921</v>
+        <v>7604775177</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>576611230</v>
+        <v>309237779</v>
       </c>
       <c r="I21" t="n">
-        <v>0.226335</v>
+        <v>0.222301</v>
       </c>
       <c r="J21" t="n">
-        <v>0.20527</v>
+        <v>0.214962</v>
       </c>
       <c r="K21" t="n">
-        <v>0.01193091</v>
+        <v>-0.004574860917676671</v>
       </c>
       <c r="L21" t="n">
-        <v>5.72779</v>
+        <v>-2.08151</v>
       </c>
       <c r="M21" t="n">
-        <v>34944206739.02777</v>
+        <v>34970186880.78098</v>
       </c>
       <c r="N21" t="n">
-        <v>50001786839.70147</v>
+        <v>50001786839.70047</v>
       </c>
       <c r="O21" t="n">
         <v>0.875563</v>
@@ -2460,13 +2460,13 @@
         <v>43102.66666666666</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R21" t="b">
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.00414559031614725</v>
+        <v>0.004136918065464922</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2529,34 +2529,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>331.29</v>
+        <v>334.23</v>
       </c>
       <c r="F22" t="n">
-        <v>6653818690</v>
+        <v>6716090248</v>
       </c>
       <c r="G22" t="n">
         <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>390668344</v>
+        <v>269285553</v>
       </c>
       <c r="I22" t="n">
-        <v>343.35</v>
+        <v>346.7</v>
       </c>
       <c r="J22" t="n">
-        <v>330.67</v>
+        <v>328.62</v>
       </c>
       <c r="K22" t="n">
-        <v>-7.907244704522952</v>
+        <v>-2.183653193960083</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.39817</v>
+        <v>-0.6936099999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>20094209.27165077</v>
+        <v>20094721.77165077</v>
       </c>
       <c r="N22" t="n">
-        <v>20094490.52165077</v>
+        <v>20094740.52165077</v>
       </c>
       <c r="O22" t="n">
         <v>3785.82</v>
@@ -2565,13 +2565,13 @@
         <v>43088.66666666666</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R22" t="b">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.003598149373256409</v>
+        <v>0.003609847758262784</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2634,34 +2634,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5.05</v>
+        <v>4.81</v>
       </c>
       <c r="F23" t="n">
-        <v>6593983088</v>
+        <v>6296456192</v>
       </c>
       <c r="G23" t="n">
         <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>1918124956</v>
+        <v>1146375776</v>
       </c>
       <c r="I23" t="n">
-        <v>5.17</v>
+        <v>5.19</v>
       </c>
       <c r="J23" t="n">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="K23" t="n">
-        <v>0.556465</v>
+        <v>-0.2873737443377689</v>
       </c>
       <c r="L23" t="n">
-        <v>12.66149</v>
+        <v>-5.73872</v>
       </c>
       <c r="M23" t="n">
-        <v>1307268578</v>
+        <v>1307347222</v>
       </c>
       <c r="N23" t="n">
-        <v>1307268537</v>
+        <v>1307347213</v>
       </c>
       <c r="O23" t="n">
         <v>20.44</v>
@@ -2670,13 +2670,13 @@
         <v>44577.59010416667</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R23" t="b">
         <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>0.003562502146942931</v>
+        <v>0.003360966919181514</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2739,34 +2739,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>9.6</v>
+        <v>9.58</v>
       </c>
       <c r="F24" t="n">
-        <v>5950098459</v>
+        <v>5946668939</v>
       </c>
       <c r="G24" t="n">
         <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>1045974012</v>
+        <v>800674531</v>
       </c>
       <c r="I24" t="n">
-        <v>9.91</v>
+        <v>9.82</v>
       </c>
       <c r="J24" t="n">
-        <v>9.050000000000001</v>
+        <v>9.41</v>
       </c>
       <c r="K24" t="n">
-        <v>0.419204</v>
+        <v>-0.1653949180304011</v>
       </c>
       <c r="L24" t="n">
-        <v>4.53077</v>
+        <v>-1.72443</v>
       </c>
       <c r="M24" t="n">
-        <v>620576422.6104751</v>
+        <v>620534422.6104751</v>
       </c>
       <c r="N24" t="n">
-        <v>887824418.9163101</v>
+        <v>887782418.9163101</v>
       </c>
       <c r="O24" t="n">
         <v>44.92</v>
@@ -2775,13 +2775,13 @@
         <v>44318.89240740741</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R24" t="b">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.003178906088366766</v>
+        <v>0.003153511533276008</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2844,34 +2844,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>69.62</v>
+        <v>72.2</v>
       </c>
       <c r="F25" t="n">
-        <v>5403606227</v>
+        <v>5609463118</v>
       </c>
       <c r="G25" t="n">
         <v>24</v>
       </c>
       <c r="H25" t="n">
-        <v>1096861662</v>
+        <v>715362160</v>
       </c>
       <c r="I25" t="n">
-        <v>74.65000000000001</v>
+        <v>74.94</v>
       </c>
       <c r="J25" t="n">
-        <v>69.27</v>
+        <v>69.12</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.348240170860535</v>
+        <v>2.02</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.35693</v>
+        <v>2.92147</v>
       </c>
       <c r="M25" t="n">
-        <v>77645954.50023881</v>
+        <v>77649504.50722787</v>
       </c>
       <c r="N25" t="n">
-        <v>77648985.75854112</v>
+        <v>77652329.51466258</v>
       </c>
       <c r="O25" t="n">
         <v>410.26</v>
@@ -2880,13 +2880,13 @@
         <v>44325.80077546297</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.002853331821182805</v>
+        <v>0.00295351807117824</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2930,68 +2930,68 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ethena-usde</t>
+          <t>canton-network</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>usde</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ethena USDe</t>
+          <t>Canton</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.999688</v>
+        <v>0.138686</v>
       </c>
       <c r="F26" t="n">
-        <v>4902375830</v>
+        <v>5501910688</v>
       </c>
       <c r="G26" t="n">
         <v>25</v>
       </c>
       <c r="H26" t="n">
-        <v>52483485</v>
+        <v>49591999</v>
       </c>
       <c r="I26" t="n">
-        <v>0.999965</v>
+        <v>0.139192</v>
       </c>
       <c r="J26" t="n">
-        <v>0.999373</v>
+        <v>0.121498</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.000256870725562353</v>
+        <v>0.01639462</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.02227</v>
+        <v>13.26358</v>
       </c>
       <c r="M26" t="n">
-        <v>4903958331.263182</v>
+        <v>39689579709.8557</v>
       </c>
       <c r="N26" t="n">
-        <v>4904836849.481181</v>
+        <v>39690487676.93661</v>
       </c>
       <c r="O26" t="n">
-        <v>1.034</v>
+        <v>0.194152</v>
       </c>
       <c r="P26" s="1" t="n">
-        <v>46000.38208333333</v>
+        <v>46056.00148148148</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>0.002554722418087756</v>
+        <v>0.00288972978078355</v>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
@@ -3005,68 +3005,68 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>canton-network</t>
+          <t>ethena-usde</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>usde</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Canton</t>
+          <t>Ethena USDe</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.121604</v>
+        <v>0.999536</v>
       </c>
       <c r="F27" t="n">
-        <v>4825964443</v>
+        <v>4935885909</v>
       </c>
       <c r="G27" t="n">
         <v>26</v>
       </c>
       <c r="H27" t="n">
-        <v>33356400</v>
+        <v>76175068</v>
       </c>
       <c r="I27" t="n">
-        <v>0.125062</v>
+        <v>0.999904</v>
       </c>
       <c r="J27" t="n">
-        <v>0.108829</v>
+        <v>0.99938</v>
       </c>
       <c r="K27" t="n">
-        <v>0.0120833</v>
+        <v>-0.00022803499806956</v>
       </c>
       <c r="L27" t="n">
-        <v>11.14264</v>
+        <v>-0.03194</v>
       </c>
       <c r="M27" t="n">
-        <v>39682485824.63093</v>
+        <v>4938195973.919382</v>
       </c>
       <c r="N27" t="n">
-        <v>39682485824.63093</v>
+        <v>4938195973.919382</v>
       </c>
       <c r="O27" t="n">
-        <v>0.194152</v>
+        <v>1.034</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>46056.00148148148</v>
+        <v>46000.38208333333</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.002509200121757961</v>
+        <v>0.002554026041003406</v>
       </c>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
@@ -3080,292 +3080,292 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>dai</t>
+          <t>avalanche-2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>dai</t>
+          <t>avax</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Dai</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>10.75</v>
       </c>
       <c r="F28" t="n">
-        <v>4587353880</v>
+        <v>4761827953</v>
       </c>
       <c r="G28" t="n">
         <v>27</v>
       </c>
       <c r="H28" t="n">
-        <v>223033455</v>
+        <v>559088789</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>10.98</v>
       </c>
       <c r="J28" t="n">
-        <v>0.999431</v>
+        <v>10.21</v>
       </c>
       <c r="K28" t="n">
-        <v>0.00018724</v>
+        <v>0.258827</v>
       </c>
       <c r="L28" t="n">
-        <v>0.01194</v>
+        <v>2.41792</v>
       </c>
       <c r="M28" t="n">
-        <v>4588238149.248935</v>
+        <v>443072344.6634147</v>
       </c>
       <c r="N28" t="n">
-        <v>4586572939.160765</v>
+        <v>469741151.0943739</v>
       </c>
       <c r="O28" t="n">
-        <v>1.22</v>
+        <v>144.96</v>
       </c>
       <c r="P28" s="1" t="n">
-        <v>43902.79363425926</v>
+        <v>44521.26314814815</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R28" t="b">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.002367047215198299</v>
+        <v>0.002450793976020456</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>Stablecoin</t>
+          <t>Plataforma de contratos inteligentes</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>Colateralizada por cripto</t>
+          <t>Layer 1</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>N/A (token, colateral cripto)</t>
+          <t>Proof of Stake (Avalanche consensus)</t>
         </is>
       </c>
       <c r="W28" t="n">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>makerdao.com</t>
+          <t>avax.network</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>Estabilidad de valor descentralizada</t>
+          <t>Subredes personalizadas para empresas</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>Token ERC-20 sobre Ethereum</t>
+          <t>Blockchain propia (Layer 1)</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Stablecoin descentralizada, generada mediante colateral cripto sobrecolateralizado.</t>
+          <t>Permite crear subredes (subnets) personalizadas para casos de uso específicos.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>avalanche-2</t>
+          <t>sui</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>avax</t>
+          <t>sui</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Sui</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>10.31</v>
+        <v>1.16</v>
       </c>
       <c r="F29" t="n">
-        <v>4564180526</v>
+        <v>4753799821</v>
       </c>
       <c r="G29" t="n">
         <v>28</v>
       </c>
       <c r="H29" t="n">
-        <v>683104943</v>
+        <v>1339722489</v>
       </c>
       <c r="I29" t="n">
-        <v>10.73</v>
+        <v>1.21</v>
       </c>
       <c r="J29" t="n">
-        <v>10.08</v>
+        <v>1.092</v>
       </c>
       <c r="K29" t="n">
-        <v>0.03427721</v>
+        <v>0.02996564</v>
       </c>
       <c r="L29" t="n">
-        <v>0.1843</v>
+        <v>2.58125</v>
       </c>
       <c r="M29" t="n">
-        <v>443058607.71027</v>
+        <v>4096537146.540959</v>
       </c>
       <c r="N29" t="n">
-        <v>469727409.7648715</v>
+        <v>10000000000</v>
       </c>
       <c r="O29" t="n">
-        <v>144.96</v>
+        <v>5.35</v>
       </c>
       <c r="P29" s="1" t="n">
-        <v>44521.26314814815</v>
+        <v>45661.62243055556</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R29" t="b">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.002353241625100278</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Plataforma de contratos inteligentes</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Layer 1</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Proof of Stake (Avalanche consensus)</t>
-        </is>
-      </c>
-      <c r="W29" t="n">
-        <v>2020</v>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>avax.network</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>Subredes personalizadas para empresas</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Layer 1)</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>Permite crear subredes (subnets) personalizadas para casos de uso específicos.</t>
-        </is>
-      </c>
+        <v>0.002446032569743137</v>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>sui</t>
+          <t>dai</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sui</t>
+          <t>dai</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sui</t>
+          <t>Dai</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1.11</v>
+        <v>0.999823</v>
       </c>
       <c r="F30" t="n">
-        <v>4551577017</v>
+        <v>4589357607</v>
       </c>
       <c r="G30" t="n">
         <v>29</v>
       </c>
       <c r="H30" t="n">
-        <v>1472217052</v>
+        <v>140221645</v>
       </c>
       <c r="I30" t="n">
-        <v>1.16</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>0.986696</v>
+        <v>0.999596</v>
       </c>
       <c r="K30" t="n">
-        <v>0.109909</v>
+        <v>-2.0855752196347e-05</v>
       </c>
       <c r="L30" t="n">
-        <v>10.95681</v>
+        <v>0.01123</v>
       </c>
       <c r="M30" t="n">
-        <v>4096537146.540959</v>
+        <v>4589747532.385433</v>
       </c>
       <c r="N30" t="n">
-        <v>10000000000</v>
+        <v>4591667218.493917</v>
       </c>
       <c r="O30" t="n">
-        <v>5.35</v>
+        <v>1.22</v>
       </c>
       <c r="P30" s="1" t="n">
-        <v>45661.62243055556</v>
+        <v>43902.79363425926</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.002345733049559132</v>
-      </c>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
+        <v>0.002348503506942996</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stablecoin</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Colateralizada por cripto</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>N/A (token, colateral cripto)</t>
+        </is>
+      </c>
+      <c r="W30" t="n">
+        <v>2017</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>makerdao.com</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Estabilidad de valor descentralizada</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>Token ERC-20 sobre Ethereum</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>Stablecoin descentralizada, generada mediante colateral cripto sobrecolateralizado.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3384,34 +3384,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.999381</v>
+        <v>0.99944</v>
       </c>
       <c r="F31" t="n">
-        <v>4405717013</v>
+        <v>4416045793</v>
       </c>
       <c r="G31" t="n">
         <v>30</v>
       </c>
       <c r="H31" t="n">
-        <v>1069576000</v>
+        <v>719181505</v>
       </c>
       <c r="I31" t="n">
-        <v>0.9995039999999999</v>
+        <v>0.999638</v>
       </c>
       <c r="J31" t="n">
-        <v>0.998911</v>
+        <v>0.999288</v>
       </c>
       <c r="K31" t="n">
-        <v>0.00014682</v>
+        <v>5.47e-05</v>
       </c>
       <c r="L31" t="n">
-        <v>0.01939</v>
+        <v>-6e-05</v>
       </c>
       <c r="M31" t="n">
-        <v>4408506662.536045</v>
+        <v>4418506659.422955</v>
       </c>
       <c r="N31" t="n">
-        <v>4408506662.535317</v>
+        <v>4418506659.422955</v>
       </c>
       <c r="O31" t="n">
         <v>1.048</v>
@@ -3420,13 +3420,13 @@
         <v>46212.42696759259</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R31" t="b">
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0.002258836546492736</v>
+        <v>0.002245713971455397</v>
       </c>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
@@ -3440,608 +3440,608 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>hedera-hashgraph</t>
+          <t>the-open-network</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>hbar</t>
+          <t>gram</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Hedera</t>
+          <t>Gram (prev. Toncoin)</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.093875</v>
+        <v>1.47</v>
       </c>
       <c r="F32" t="n">
-        <v>4113889605</v>
+        <v>4135698799</v>
       </c>
       <c r="G32" t="n">
         <v>31</v>
       </c>
       <c r="H32" t="n">
-        <v>159277487</v>
+        <v>53047848</v>
       </c>
       <c r="I32" t="n">
-        <v>0.096666</v>
+        <v>1.47</v>
       </c>
       <c r="J32" t="n">
-        <v>0.09114899999999999</v>
+        <v>1.41</v>
       </c>
       <c r="K32" t="n">
-        <v>0.00050433</v>
+        <v>0.04290891</v>
       </c>
       <c r="L32" t="n">
-        <v>0.6450399999999999</v>
+        <v>3.02347</v>
       </c>
       <c r="M32" t="n">
-        <v>43831706398.99841</v>
+        <v>2813828939.846996</v>
       </c>
       <c r="N32" t="n">
-        <v>50000000000</v>
+        <v>5255812914.165484</v>
       </c>
       <c r="O32" t="n">
-        <v>0.569229</v>
+        <v>8.25</v>
       </c>
       <c r="P32" s="1" t="n">
-        <v>44454.11143518519</v>
+        <v>45457.69225694444</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R32" t="b">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.002084979556511231</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Infraestructura empresarial</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>DLT</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Hashgraph (aBFT)</t>
-        </is>
-      </c>
-      <c r="W32" t="n">
-        <v>2019</v>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>hedera.com</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>Aplicaciones empresariales y tokenización</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>Red propia (hashgraph, no blockchain tradicional)</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>Gobernada por un consejo de grandes empresas globales.</t>
-        </is>
-      </c>
+        <v>0.002079442921470283</v>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>the-open-network</t>
+          <t>hedera-hashgraph</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>gram</t>
+          <t>hbar</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Gram (prev. Toncoin)</t>
+          <t>Hedera</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1.41</v>
+        <v>0.093301</v>
       </c>
       <c r="F33" t="n">
-        <v>3975394185</v>
+        <v>4090022875</v>
       </c>
       <c r="G33" t="n">
         <v>32</v>
       </c>
       <c r="H33" t="n">
-        <v>62915494</v>
+        <v>109322812</v>
       </c>
       <c r="I33" t="n">
-        <v>1.44</v>
+        <v>0.09580900000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>1.4</v>
+        <v>0.092637</v>
       </c>
       <c r="K33" t="n">
-        <v>0.00058374</v>
+        <v>-0.00144075792829608</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.00125</v>
+        <v>-1.52119</v>
       </c>
       <c r="M33" t="n">
-        <v>2813281722.98769</v>
+        <v>43831706398.51672</v>
       </c>
       <c r="N33" t="n">
-        <v>5255255878.351041</v>
+        <v>50000000000</v>
       </c>
       <c r="O33" t="n">
-        <v>8.25</v>
+        <v>0.569229</v>
       </c>
       <c r="P33" s="1" t="n">
-        <v>45457.69225694444</v>
+        <v>44454.11143518519</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R33" t="b">
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.002002470524846102</v>
-      </c>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
+        <v>0.002052352979344775</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Infraestructura empresarial</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>DLT</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Hashgraph (aBFT)</t>
+        </is>
+      </c>
+      <c r="W33" t="n">
+        <v>2019</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>hedera.com</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Aplicaciones empresariales y tokenización</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>Red propia (hashgraph, no blockchain tradicional)</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>Gobernada por un consejo de grandes empresas globales.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>shiba-inu</t>
+          <t>bittensor</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>shib</t>
+          <t>tao</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Shiba Inu</t>
+          <t>Bittensor</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5.82e-06</v>
+        <v>327</v>
       </c>
       <c r="F34" t="n">
-        <v>3427851999</v>
+        <v>3707907231</v>
       </c>
       <c r="G34" t="n">
         <v>33</v>
       </c>
       <c r="H34" t="n">
-        <v>111035612</v>
+        <v>382394337</v>
       </c>
       <c r="I34" t="n">
-        <v>5.97e-06</v>
+        <v>337.55</v>
       </c>
       <c r="J34" t="n">
-        <v>5.72e-06</v>
+        <v>297.69</v>
       </c>
       <c r="K34" t="n">
-        <v>9.7936e-08</v>
+        <v>23.23</v>
       </c>
       <c r="L34" t="n">
-        <v>1.73752</v>
+        <v>7.55059</v>
       </c>
       <c r="M34" t="n">
-        <v>589238965647120.2</v>
+        <v>11339645.9251</v>
       </c>
       <c r="N34" t="n">
-        <v>589496067422631</v>
+        <v>21000000</v>
       </c>
       <c r="O34" t="n">
-        <v>8.616e-05</v>
+        <v>757.6</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>44496.82980324074</v>
+        <v>45358.44833333333</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
-        <v>0.001676270744646382</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Meme coin</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Ecosistema DeFi</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>N/A (token ERC-20)</t>
-        </is>
-      </c>
-      <c r="W34" t="n">
-        <v>2020</v>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>shibatoken.com</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>Ecosistema meme y DeFi comunitario</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>Token ERC-20 sobre Ethereum</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>Token meme inspirado en Dogecoin, con ecosistema DeFi propio (ShibaSwap).</t>
-        </is>
-      </c>
+        <v>0.001825723942103813</v>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>bittensor</t>
+          <t>shiba-inu</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>tao</t>
+          <t>shib</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Bittensor</t>
+          <t>Shiba Inu</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>300.65</v>
+        <v>5.88e-06</v>
       </c>
       <c r="F35" t="n">
-        <v>3409201890</v>
+        <v>3463211758</v>
       </c>
       <c r="G35" t="n">
         <v>34</v>
       </c>
       <c r="H35" t="n">
-        <v>384273924</v>
+        <v>95935944</v>
       </c>
       <c r="I35" t="n">
-        <v>311.57</v>
+        <v>6.02e-06</v>
       </c>
       <c r="J35" t="n">
-        <v>285.31</v>
+        <v>5.76e-06</v>
       </c>
       <c r="K35" t="n">
-        <v>11.87</v>
+        <v>9.411000000000001e-09</v>
       </c>
       <c r="L35" t="n">
-        <v>4.08622</v>
+        <v>0.1525</v>
       </c>
       <c r="M35" t="n">
-        <v>11339645.9251</v>
+        <v>589238954375651.4</v>
       </c>
       <c r="N35" t="n">
-        <v>21000000</v>
+        <v>589496066158401.1</v>
       </c>
       <c r="O35" t="n">
-        <v>757.6</v>
+        <v>8.616e-05</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>45358.44833333333</v>
+        <v>44496.82980324074</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R35" t="b">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.001665159890337705</v>
-      </c>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr"/>
+        <v>0.001680597459234109</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Meme coin</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ecosistema DeFi</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>N/A (token ERC-20)</t>
+        </is>
+      </c>
+      <c r="W35" t="n">
+        <v>2020</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>shibatoken.com</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>Ecosistema meme y DeFi comunitario</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>Token ERC-20 sobre Ethereum</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>Token meme inspirado en Dogecoin, con ecosistema DeFi propio (ShibaSwap).</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>crypto-com-chain</t>
+          <t>global-dollar</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>cro</t>
+          <t>usdg</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cronos</t>
+          <t>Global Dollar</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.065552</v>
+        <v>0.999976</v>
       </c>
       <c r="F36" t="n">
-        <v>3260323161</v>
+        <v>3245194299</v>
       </c>
       <c r="G36" t="n">
         <v>35</v>
       </c>
       <c r="H36" t="n">
-        <v>18833597</v>
+        <v>633298325</v>
       </c>
       <c r="I36" t="n">
-        <v>0.06647599999999999</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>0.061944</v>
+        <v>0.99988</v>
       </c>
       <c r="K36" t="n">
-        <v>0.00373544</v>
+        <v>-1.0853928892107e-05</v>
       </c>
       <c r="L36" t="n">
-        <v>5.9134</v>
+        <v>-0.00629</v>
       </c>
       <c r="M36" t="n">
-        <v>49743066210.47476</v>
+        <v>3245247840.059057</v>
       </c>
       <c r="N36" t="n">
-        <v>98943108426.03091</v>
+        <v>3245247890.04586</v>
       </c>
       <c r="O36" t="n">
-        <v>0.891544</v>
+        <v>1.65</v>
       </c>
       <c r="P36" s="1" t="n">
-        <v>44523.66666666666</v>
+        <v>45686.67436342593</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.001576464973456518</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Token de exchange</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Layer 1 (Cronos)</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Proof of Stake</t>
-        </is>
-      </c>
-      <c r="W36" t="n">
-        <v>2018</v>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>cronos.org</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>Pagos y DeFi en el ecosistema Crypto.com</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Cronos, EVM-compatible)</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>Token nativo del ecosistema Crypto.com y su red Cronos.</t>
-        </is>
-      </c>
+        <v>0.001551293444570708</v>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>global-dollar</t>
+          <t>crypto-com-chain</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>usdg</t>
+          <t>cro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Global Dollar</t>
+          <t>Cronos</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>0.065125</v>
       </c>
       <c r="F37" t="n">
-        <v>3258135197</v>
+        <v>3240132067</v>
       </c>
       <c r="G37" t="n">
         <v>36</v>
       </c>
       <c r="H37" t="n">
-        <v>903819770</v>
+        <v>9453924</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0.06684</v>
       </c>
       <c r="J37" t="n">
-        <v>0.999507</v>
+        <v>0.064841</v>
       </c>
       <c r="K37" t="n">
-        <v>0.00020004</v>
+        <v>-0.000783069008371232</v>
       </c>
       <c r="L37" t="n">
-        <v>0.01107</v>
+        <v>-1.16763</v>
       </c>
       <c r="M37" t="n">
-        <v>3258247890.046372</v>
+        <v>49744967558.72809</v>
       </c>
       <c r="N37" t="n">
-        <v>3258247890.046372</v>
+        <v>98944988794.0228</v>
       </c>
       <c r="O37" t="n">
-        <v>1.65</v>
+        <v>0.891544</v>
       </c>
       <c r="P37" s="1" t="n">
-        <v>45686.67436342593</v>
+        <v>44523.66666666666</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R37" t="b">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.001575161487818089</v>
-      </c>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr"/>
+        <v>0.001548291084467256</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Token de exchange</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Layer 1 (Cronos)</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Proof of Stake</t>
+        </is>
+      </c>
+      <c r="W37" t="n">
+        <v>2018</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>cronos.org</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>Pagos y DeFi en el ecosistema Crypto.com</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Cronos, EVM-compatible)</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>Token nativo del ecosistema Crypto.com y su red Cronos.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>bitway</t>
+          <t>ethena</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>btw</t>
+          <t>ena</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Bitway</t>
+          <t>Ethena</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1.18</v>
+        <v>0.27802</v>
       </c>
       <c r="F38" t="n">
-        <v>3192057316</v>
+        <v>2808076310</v>
       </c>
       <c r="G38" t="n">
         <v>37</v>
       </c>
       <c r="H38" t="n">
-        <v>53787879</v>
+        <v>1005453744</v>
       </c>
       <c r="I38" t="n">
-        <v>1.19</v>
+        <v>0.285151</v>
       </c>
       <c r="J38" t="n">
-        <v>0.890482</v>
+        <v>0.241291</v>
       </c>
       <c r="K38" t="n">
-        <v>0.129389</v>
+        <v>0.0326462</v>
       </c>
       <c r="L38" t="n">
-        <v>12.39428</v>
+        <v>13.30858</v>
       </c>
       <c r="M38" t="n">
-        <v>2708142280.000001</v>
+        <v>10095312500</v>
       </c>
       <c r="N38" t="n">
-        <v>10000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="O38" t="n">
-        <v>1.19</v>
+        <v>1.52</v>
       </c>
       <c r="P38" s="1" t="n">
-        <v>46290.58877314815</v>
+        <v>45393.21892361111</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R38" t="b">
         <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>0.001535795406428585</v>
+        <v>0.001292043056466274</v>
       </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
@@ -4055,7 +4055,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4074,34 +4074,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.99984</v>
+        <v>0.999876</v>
       </c>
       <c r="F39" t="n">
-        <v>2697623562</v>
+        <v>2781139028</v>
       </c>
       <c r="G39" t="n">
         <v>38</v>
       </c>
       <c r="H39" t="n">
-        <v>67238143</v>
+        <v>131160440</v>
       </c>
       <c r="I39" t="n">
-        <v>0.999999</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>0.99947</v>
+        <v>0.999783</v>
       </c>
       <c r="K39" t="n">
-        <v>-7.6949450457109e-05</v>
+        <v>-2.1815366736511e-05</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.00537</v>
+        <v>-0.0077</v>
       </c>
       <c r="M39" t="n">
-        <v>2698087718.884173</v>
+        <v>2781433279.25909</v>
       </c>
       <c r="N39" t="n">
-        <v>2687552417.224173</v>
+        <v>2781433279.25909</v>
       </c>
       <c r="O39" t="n">
         <v>1.021</v>
@@ -4110,13 +4110,13 @@
         <v>45222.61454861111</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001241235122304427</v>
+        <v>0.001276066818954396</v>
       </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
@@ -4130,7 +4130,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4149,34 +4149,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="F40" t="n">
-        <v>2688174131</v>
+        <v>2770339731</v>
       </c>
       <c r="G40" t="n">
         <v>39</v>
       </c>
       <c r="H40" t="n">
-        <v>890043</v>
+        <v>733691</v>
       </c>
       <c r="I40" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="J40" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.0425971033575745</v>
+        <v>0.0229915</v>
       </c>
       <c r="L40" t="n">
-        <v>-3.42038</v>
+        <v>1.87105</v>
       </c>
       <c r="M40" t="n">
-        <v>2278580063.729613</v>
+        <v>2278934927.291677</v>
       </c>
       <c r="N40" t="n">
-        <v>5418169810.236838</v>
+        <v>5418524673.845001</v>
       </c>
       <c r="O40" t="n">
         <v>5.64</v>
@@ -4185,13 +4185,13 @@
         <v>46205.17638888889</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R40" t="b">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.001235605597504283</v>
+        <v>0.001269661861920004</v>
       </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
@@ -4205,7 +4205,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4224,28 +4224,28 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4264.36</v>
+        <v>4280.2</v>
       </c>
       <c r="F41" t="n">
-        <v>2655860296</v>
+        <v>2665795127</v>
       </c>
       <c r="G41" t="n">
         <v>40</v>
       </c>
       <c r="H41" t="n">
-        <v>223474158</v>
+        <v>158821903</v>
       </c>
       <c r="I41" t="n">
-        <v>4309.24</v>
+        <v>4294.81</v>
       </c>
       <c r="J41" t="n">
-        <v>4248.16</v>
+        <v>4258.21</v>
       </c>
       <c r="K41" t="n">
-        <v>-5.299238695430176</v>
+        <v>-2.179440761827209</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.14254</v>
+        <v>-0.06114</v>
       </c>
       <c r="M41" t="n">
         <v>622823.6595320001</v>
@@ -4260,13 +4260,13 @@
         <v>46050.66666666666</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R41" t="b">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.001216354540427906</v>
+        <v>0.001207657483598195</v>
       </c>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
@@ -4280,7 +4280,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4299,28 +4299,28 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.542535</v>
+        <v>0.544212</v>
       </c>
       <c r="F42" t="n">
-        <v>2639188514</v>
+        <v>2650847943</v>
       </c>
       <c r="G42" t="n">
         <v>41</v>
       </c>
       <c r="H42" t="n">
-        <v>1064033883</v>
+        <v>298694066</v>
       </c>
       <c r="I42" t="n">
-        <v>0.578933</v>
+        <v>0.561067</v>
       </c>
       <c r="J42" t="n">
-        <v>0.49461</v>
+        <v>0.529581</v>
       </c>
       <c r="K42" t="n">
-        <v>0.03441119</v>
+        <v>-0.005807456750666073</v>
       </c>
       <c r="L42" t="n">
-        <v>7.86321</v>
+        <v>-1.03503</v>
       </c>
       <c r="M42" t="n">
         <v>4869330647</v>
@@ -4335,13 +4335,13 @@
         <v>45641.69166666667</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.00120642227993184</v>
+        <v>0.001198792455503759</v>
       </c>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
@@ -4355,7 +4355,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4374,28 +4374,28 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>119.99</v>
+        <v>121.01</v>
       </c>
       <c r="F43" t="n">
-        <v>2519828086</v>
+        <v>2541041221</v>
       </c>
       <c r="G43" t="n">
         <v>42</v>
       </c>
       <c r="H43" t="n">
-        <v>27685004</v>
+        <v>20506755</v>
       </c>
       <c r="I43" t="n">
-        <v>121.16</v>
+        <v>122.05</v>
       </c>
       <c r="J43" t="n">
-        <v>118.89</v>
+        <v>119.33</v>
       </c>
       <c r="K43" t="n">
-        <v>0.970076</v>
+        <v>0.409047</v>
       </c>
       <c r="L43" t="n">
-        <v>0.83939</v>
+        <v>0.31462</v>
       </c>
       <c r="M43" t="n">
         <v>21000000</v>
@@ -4410,13 +4410,13 @@
         <v>45934.66666666666</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R43" t="b">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.001135312972971254</v>
+        <v>0.001133667166654172</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4460,68 +4460,68 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ethena</t>
+          <t>bitway</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ena</t>
+          <t>btw</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ethena</t>
+          <t>Bitway</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.246882</v>
+        <v>0.92262</v>
       </c>
       <c r="F44" t="n">
-        <v>2492927210</v>
+        <v>2501644736</v>
       </c>
       <c r="G44" t="n">
         <v>43</v>
       </c>
       <c r="H44" t="n">
-        <v>802615669</v>
+        <v>35332630</v>
       </c>
       <c r="I44" t="n">
-        <v>0.249038</v>
+        <v>1.37</v>
       </c>
       <c r="J44" t="n">
-        <v>0.213698</v>
+        <v>0.763491</v>
       </c>
       <c r="K44" t="n">
-        <v>0.02900795</v>
+        <v>-0.2469231384713139</v>
       </c>
       <c r="L44" t="n">
-        <v>13.22522</v>
+        <v>-20.93606</v>
       </c>
       <c r="M44" t="n">
-        <v>10095312500</v>
+        <v>2708142280.000001</v>
       </c>
       <c r="N44" t="n">
-        <v>15000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="O44" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>45393.21892361111</v>
+        <v>46291.06377314815</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R44" t="b">
         <v>1</v>
       </c>
       <c r="S44" t="n">
-        <v>0.0011192867012743</v>
+        <v>0.001110301498154538</v>
       </c>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
@@ -4535,68 +4535,68 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>hashnote-usyc</t>
+          <t>ripple-usd</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>usyc</t>
+          <t>rlusd</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Circle USYC</t>
+          <t>Ripple USD</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1.14</v>
+        <v>0.999962</v>
       </c>
       <c r="F45" t="n">
-        <v>2433710271</v>
+        <v>2491193156</v>
       </c>
       <c r="G45" t="n">
         <v>44</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>303948811</v>
       </c>
       <c r="I45" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>1.14</v>
+        <v>0.99984</v>
       </c>
       <c r="K45" t="n">
-        <v>0.00034072</v>
+        <v>-1.5146618305151e-05</v>
       </c>
       <c r="L45" t="n">
-        <v>0.02993</v>
+        <v>-0.01141</v>
       </c>
       <c r="M45" t="n">
-        <v>2137431562.141903</v>
+        <v>2491272908.017196</v>
       </c>
       <c r="N45" t="n">
-        <v>2137431562.141903</v>
+        <v>2491272908.0172</v>
       </c>
       <c r="O45" t="n">
-        <v>1.14</v>
+        <v>1.073</v>
       </c>
       <c r="P45" s="1" t="n">
-        <v>46290.53483796296</v>
+        <v>45652.11518518518</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R45" t="b">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.001084008045163773</v>
+        <v>0.00110410276865932</v>
       </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
@@ -4610,68 +4610,68 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ripple-usd</t>
+          <t>hashnote-usyc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>rlusd</t>
+          <t>usyc</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Ripple USD</t>
+          <t>Circle USYC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="F46" t="n">
-        <v>2412736667</v>
+        <v>2405269933</v>
       </c>
       <c r="G46" t="n">
         <v>45</v>
       </c>
       <c r="H46" t="n">
-        <v>330311005</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="J46" t="n">
-        <v>0.999578</v>
+        <v>1.14</v>
       </c>
       <c r="K46" t="n">
-        <v>7.264e-05</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.00149</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>2412372908.017206</v>
+        <v>2112453536.871665</v>
       </c>
       <c r="N46" t="n">
-        <v>2412372908.017201</v>
+        <v>2112453536.871665</v>
       </c>
       <c r="O46" t="n">
-        <v>1.073</v>
+        <v>1.14</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>45652.11518518518</v>
+        <v>46290.53483796296</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R46" t="b">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.001071512962246461</v>
+        <v>0.001053142548603189</v>
       </c>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
@@ -4685,143 +4685,173 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>blackrock-usd-institutional-digital-liquidity-fund</t>
+          <t>aave</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>buidl</t>
+          <t>aave</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>BlackRock USD Institutional Digital Liquidity Fund</t>
+          <t>Aave</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>154.59</v>
       </c>
       <c r="F47" t="n">
-        <v>2289899848</v>
+        <v>2384979455</v>
       </c>
       <c r="G47" t="n">
         <v>46</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>366713824</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>156.56</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>145.2</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>3.13157</v>
       </c>
       <c r="M47" t="n">
-        <v>2289899848.277649</v>
+        <v>15429292.82562298</v>
       </c>
       <c r="N47" t="n">
-        <v>2289899848.277649</v>
+        <v>16000000</v>
       </c>
       <c r="O47" t="n">
-        <v>1</v>
+        <v>661.6900000000001</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>45699.87511574074</v>
+        <v>44334.55554398148</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R47" t="b">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0.0009983325856786683</v>
-      </c>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr"/>
-      <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr"/>
-      <c r="AA47" t="inlineStr"/>
+        <v>0.001041108465292276</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>DeFi</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Préstamos</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>N/A (token de gobernanza)</t>
+        </is>
+      </c>
+      <c r="W47" t="n">
+        <v>2017</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>aave.com</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>Préstamos y créditos descentralizados</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>Token ERC-20 sobre Ethereum</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>Pionero en préstamos y créditos flash (flash loans) dentro de DeFi.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ondo-us-dollar-yield</t>
+          <t>mantle</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>usdy</t>
+          <t>mnt</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Ondo US Dollar Yield</t>
+          <t>Mantle</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1.15</v>
+        <v>0.7011039999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>2274418100</v>
+        <v>2315344740</v>
       </c>
       <c r="G48" t="n">
         <v>47</v>
       </c>
       <c r="H48" t="n">
-        <v>2925391</v>
+        <v>45747180</v>
       </c>
       <c r="I48" t="n">
-        <v>1.15</v>
+        <v>0.714831</v>
       </c>
       <c r="J48" t="n">
-        <v>1.14</v>
+        <v>0.658871</v>
       </c>
       <c r="K48" t="n">
-        <v>0.00066</v>
+        <v>0.02610291</v>
       </c>
       <c r="L48" t="n">
-        <v>0.06019</v>
+        <v>3.89981</v>
       </c>
       <c r="M48" t="n">
-        <v>1984440201.171045</v>
+        <v>3302294382.53684</v>
       </c>
       <c r="N48" t="n">
-        <v>1984440201.171045</v>
+        <v>6219316794.889999</v>
       </c>
       <c r="O48" t="n">
-        <v>1.26</v>
+        <v>2.86</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>45377.89175925926</v>
+        <v>45938.71164351852</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R48" t="b">
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0.0009891092912479678</v>
+        <v>0.0009998087994272514</v>
       </c>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
@@ -4835,173 +4865,143 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>blackrock-usd-institutional-digital-liquidity-fund</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>buidl</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Aave</t>
+          <t>BlackRock USD Institutional Digital Liquidity Fund</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>146.95</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>2266346209</v>
+        <v>2290130495</v>
       </c>
       <c r="G49" t="n">
         <v>48</v>
       </c>
       <c r="H49" t="n">
-        <v>314980178</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>149.93</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
-        <v>141.56</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>3.04679</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>15429094.79157746</v>
+        <v>2290130494.717649</v>
       </c>
       <c r="N49" t="n">
-        <v>16000000</v>
+        <v>2290130494.717649</v>
       </c>
       <c r="O49" t="n">
-        <v>661.6900000000001</v>
+        <v>1</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>44334.55554398148</v>
+        <v>45699.87511574074</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R49" t="b">
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>0.0009843004397342031</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>DeFi</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Préstamos</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>N/A (token de gobernanza)</t>
-        </is>
-      </c>
-      <c r="W49" t="n">
-        <v>2017</v>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>aave.com</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>Préstamos y créditos descentralizados</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>Token ERC-20 sobre Ethereum</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>Pionero en préstamos y créditos flash (flash loans) dentro de DeFi.</t>
-        </is>
-      </c>
+        <v>0.0009848544782450814</v>
+      </c>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>mantle</t>
+          <t>ondo-us-dollar-yield</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>mnt</t>
+          <t>usdy</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Mantle</t>
+          <t>Ondo US Dollar Yield</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.665276</v>
+        <v>1.15</v>
       </c>
       <c r="F50" t="n">
-        <v>2196711123</v>
+        <v>2276483255</v>
       </c>
       <c r="G50" t="n">
         <v>49</v>
       </c>
       <c r="H50" t="n">
-        <v>44356784</v>
+        <v>799036</v>
       </c>
       <c r="I50" t="n">
-        <v>0.688055</v>
+        <v>1.15</v>
       </c>
       <c r="J50" t="n">
-        <v>0.668225</v>
+        <v>1.14</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.01741475955394411</v>
+        <v>0.00341799</v>
       </c>
       <c r="L50" t="n">
-        <v>-2.56216</v>
+        <v>0.29273</v>
       </c>
       <c r="M50" t="n">
-        <v>3302294382.53684</v>
+        <v>1985130003.146069</v>
       </c>
       <c r="N50" t="n">
-        <v>6219316794.889999</v>
+        <v>1985178145.937342</v>
       </c>
       <c r="O50" t="n">
-        <v>2.86</v>
+        <v>1.26</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>45938.71164351852</v>
+        <v>45377.89175925926</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R50" t="b">
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0.000942815143572222</v>
+        <v>0.0009767604341755422</v>
       </c>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
@@ -5015,7 +5015,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5034,34 +5034,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="F51" t="n">
-        <v>2001539135</v>
+        <v>2079194205</v>
       </c>
       <c r="G51" t="n">
         <v>50</v>
       </c>
       <c r="H51" t="n">
-        <v>207694357</v>
+        <v>211092465</v>
       </c>
       <c r="I51" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="J51" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="K51" t="n">
-        <v>0.01144919</v>
+        <v>0.03290304</v>
       </c>
       <c r="L51" t="n">
-        <v>1.02324</v>
+        <v>2.79315</v>
       </c>
       <c r="M51" t="n">
-        <v>1704409844.618002</v>
+        <v>1704554979.517097</v>
       </c>
       <c r="N51" t="n">
-        <v>1704422818.276369</v>
+        <v>1704565831.886456</v>
       </c>
       <c r="O51" t="n">
         <v>54.98</v>
@@ -5070,13 +5070,13 @@
         <v>44504.25704861111</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R51" t="b">
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0.0008265408888854018</v>
+        <v>0.0008597502354000008</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5120,68 +5120,68 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>aster-2</t>
+          <t>pump-fun</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>aster</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Pump.fun</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.724982</v>
+        <v>0.00438534</v>
       </c>
       <c r="F52" t="n">
-        <v>1963838525</v>
+        <v>2045009163</v>
       </c>
       <c r="G52" t="n">
         <v>51</v>
       </c>
       <c r="H52" t="n">
-        <v>127074378</v>
+        <v>242824041</v>
       </c>
       <c r="I52" t="n">
-        <v>0.743329</v>
+        <v>0.0046177</v>
       </c>
       <c r="J52" t="n">
-        <v>0.703643</v>
+        <v>0.00402625</v>
       </c>
       <c r="K52" t="n">
-        <v>0.01759298</v>
+        <v>0.00021342</v>
       </c>
       <c r="L52" t="n">
-        <v>2.49101</v>
+        <v>5.08412</v>
       </c>
       <c r="M52" t="n">
-        <v>2710487455.649731</v>
+        <v>466206167126.4446</v>
       </c>
       <c r="N52" t="n">
-        <v>7795741639.279309</v>
+        <v>831708723495.5499</v>
       </c>
       <c r="O52" t="n">
-        <v>2.41</v>
+        <v>0.00881908</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>45924.13766203704</v>
+        <v>45914.36296296296</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R52" t="b">
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0.0008040806456204283</v>
+        <v>0.00083947542258312</v>
       </c>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
@@ -5195,68 +5195,68 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>pump-fun</t>
+          <t>aster-2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>aster</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Pump.fun</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.00412297</v>
+        <v>0.7262960000000001</v>
       </c>
       <c r="F53" t="n">
-        <v>1924394724</v>
+        <v>1968338876</v>
       </c>
       <c r="G53" t="n">
         <v>52</v>
       </c>
       <c r="H53" t="n">
-        <v>207586639</v>
+        <v>89676145</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0042438</v>
+        <v>0.742024</v>
       </c>
       <c r="J53" t="n">
-        <v>0.00380779</v>
+        <v>0.719024</v>
       </c>
       <c r="K53" t="n">
-        <v>0.000275</v>
+        <v>-0.007135555905350199</v>
       </c>
       <c r="L53" t="n">
-        <v>6.99921</v>
+        <v>-1.06051</v>
       </c>
       <c r="M53" t="n">
-        <v>466505755824.3136</v>
+        <v>2710487455.649731</v>
       </c>
       <c r="N53" t="n">
-        <v>831988424975.1174</v>
+        <v>7795741639.279309</v>
       </c>
       <c r="O53" t="n">
-        <v>0.00881908</v>
+        <v>2.41</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>45914.36296296296</v>
+        <v>45924.13766203704</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0.0007805818914688324</v>
+        <v>0.0007940030280328506</v>
       </c>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
@@ -5270,7 +5270,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5292,28 +5292,28 @@
         <v>2.75</v>
       </c>
       <c r="F54" t="n">
-        <v>1924184577</v>
+        <v>1927060250</v>
       </c>
       <c r="G54" t="n">
         <v>53</v>
       </c>
       <c r="H54" t="n">
-        <v>53348378</v>
+        <v>34153385</v>
       </c>
       <c r="I54" t="n">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="J54" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.146431129138374</v>
+        <v>-0.05197841826801719</v>
       </c>
       <c r="L54" t="n">
-        <v>-5.53542</v>
+        <v>-1.84535</v>
       </c>
       <c r="M54" t="n">
-        <v>699457605.9572027</v>
+        <v>699504178.637211</v>
       </c>
       <c r="N54" t="n">
         <v>1000000000</v>
@@ -5325,13 +5325,13 @@
         <v>45674.19883101852</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>0.0007804566958090962</v>
+        <v>0.0007695210801830271</v>
       </c>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
@@ -5345,68 +5345,68 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>world-liberty-financial</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>wlfi</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Pepe</t>
+          <t>World Liberty Financial</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4.47e-06</v>
+        <v>0.058929</v>
       </c>
       <c r="F55" t="n">
-        <v>1878183996</v>
+        <v>1872782612</v>
       </c>
       <c r="G55" t="n">
         <v>54</v>
       </c>
       <c r="H55" t="n">
-        <v>441797072</v>
+        <v>37901605</v>
       </c>
       <c r="I55" t="n">
-        <v>4.61e-06</v>
+        <v>0.059528</v>
       </c>
       <c r="J55" t="n">
-        <v>4.36e-06</v>
+        <v>0.056538</v>
       </c>
       <c r="K55" t="n">
-        <v>7.5968e-08</v>
+        <v>0.00152381</v>
       </c>
       <c r="L55" t="n">
-        <v>1.70869</v>
+        <v>2.6126</v>
       </c>
       <c r="M55" t="n">
-        <v>420690000000000</v>
+        <v>31777915436</v>
       </c>
       <c r="N55" t="n">
-        <v>420690000000000</v>
+        <v>100000000000</v>
       </c>
       <c r="O55" t="n">
-        <v>2.803e-05</v>
+        <v>0.331336</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>45635.35457175926</v>
+        <v>45901.18065972222</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R55" t="b">
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0007530517217359946</v>
+        <v>0.0007373295459268335</v>
       </c>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
@@ -5420,7 +5420,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5439,28 +5439,28 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4260.66</v>
+        <v>4278.8</v>
       </c>
       <c r="F56" t="n">
-        <v>1852824419</v>
+        <v>1860862541</v>
       </c>
       <c r="G56" t="n">
         <v>55</v>
       </c>
       <c r="H56" t="n">
-        <v>167047949</v>
+        <v>89054883</v>
       </c>
       <c r="I56" t="n">
-        <v>4307.53</v>
+        <v>4290.58</v>
       </c>
       <c r="J56" t="n">
-        <v>4243.51</v>
+        <v>4254.67</v>
       </c>
       <c r="K56" t="n">
-        <v>-5.064864292039601</v>
+        <v>-1.201781688529081</v>
       </c>
       <c r="L56" t="n">
-        <v>-0.13787</v>
+        <v>-0.03731</v>
       </c>
       <c r="M56" t="n">
         <v>434898.623539</v>
@@ -5475,13 +5475,13 @@
         <v>46050.93814814815</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R56" t="b">
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0.0007379436832051372</v>
+        <v>0.0007302598688356388</v>
       </c>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
@@ -5495,68 +5495,68 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>world-liberty-financial</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>wlfi</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>World Liberty Financial</t>
+          <t>Pepe</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.056899</v>
+        <v>4.36e-06</v>
       </c>
       <c r="F57" t="n">
-        <v>1807955457</v>
+        <v>1834875262</v>
       </c>
       <c r="G57" t="n">
         <v>56</v>
       </c>
       <c r="H57" t="n">
-        <v>50840539</v>
+        <v>267690605</v>
       </c>
       <c r="I57" t="n">
-        <v>0.057528</v>
+        <v>4.53e-06</v>
       </c>
       <c r="J57" t="n">
-        <v>0.055143</v>
+        <v>4.37e-06</v>
       </c>
       <c r="K57" t="n">
-        <v>0.00178045</v>
+        <v>-1.18407185435e-07</v>
       </c>
       <c r="L57" t="n">
-        <v>3.24573</v>
+        <v>-2.82471</v>
       </c>
       <c r="M57" t="n">
-        <v>31777821956</v>
+        <v>420690000000000</v>
       </c>
       <c r="N57" t="n">
-        <v>100000000000</v>
+        <v>420690000000000</v>
       </c>
       <c r="O57" t="n">
-        <v>0.331336</v>
+        <v>2.803e-05</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>45901.18065972222</v>
+        <v>45635.35457175926</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R57" t="b">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0.0007112128742986806</v>
+        <v>0.0007148470687769156</v>
       </c>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
@@ -5570,173 +5570,143 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>internet-computer</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>icp</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Internet Computer</t>
+          <t>Sky</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3.13</v>
+        <v>0.07786800000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>1744603286</v>
+        <v>1823715076</v>
       </c>
       <c r="G58" t="n">
         <v>57</v>
       </c>
       <c r="H58" t="n">
-        <v>113204362</v>
+        <v>22188256</v>
       </c>
       <c r="I58" t="n">
-        <v>3.27</v>
+        <v>0.079861</v>
       </c>
       <c r="J58" t="n">
-        <v>3.04</v>
+        <v>0.073389</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.01197071337857913</v>
+        <v>0.00329694</v>
       </c>
       <c r="L58" t="n">
-        <v>-0.17087</v>
+        <v>4.39628</v>
       </c>
       <c r="M58" t="n">
-        <v>556900774.9526535</v>
+        <v>23419583386.47268</v>
       </c>
       <c r="N58" t="n">
-        <v>556902306.1412389</v>
+        <v>23459804203.60596</v>
       </c>
       <c r="O58" t="n">
-        <v>700.65</v>
+        <v>0.100535</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>44326.33741898148</v>
+        <v>45630.09302083333</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R58" t="b">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0006734706422227487</v>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Infraestructura descentralizada</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Hosting</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Proof of Stake (Chain Key)</t>
-        </is>
-      </c>
-      <c r="W58" t="n">
-        <v>2021</v>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>internetcomputer.org</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>Hosting descentralizado de aplicaciones</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Layer 1)</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>Busca reemplazar servidores tradicionales con "canisters" en cadena.</t>
-        </is>
-      </c>
+        <v>0.0007082280720194573</v>
+      </c>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>worldcoin-wld</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>wld</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sky</t>
+          <t>Worldcoin</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.07366300000000001</v>
+        <v>0.485774</v>
       </c>
       <c r="F59" t="n">
-        <v>1724572631</v>
+        <v>1804553072</v>
       </c>
       <c r="G59" t="n">
         <v>58</v>
       </c>
       <c r="H59" t="n">
-        <v>22850133</v>
+        <v>438376989</v>
       </c>
       <c r="I59" t="n">
-        <v>0.077512</v>
+        <v>0.511413</v>
       </c>
       <c r="J59" t="n">
-        <v>0.071574</v>
+        <v>0.445403</v>
       </c>
       <c r="K59" t="n">
-        <v>0.00203783</v>
+        <v>0.03244423</v>
       </c>
       <c r="L59" t="n">
-        <v>2.75947</v>
+        <v>7.0463</v>
       </c>
       <c r="M59" t="n">
-        <v>23420903969.25927</v>
+        <v>3715164012.295929</v>
       </c>
       <c r="N59" t="n">
-        <v>23459804203.60596</v>
+        <v>10000000000</v>
       </c>
       <c r="O59" t="n">
-        <v>0.100535</v>
+        <v>11.74</v>
       </c>
       <c r="P59" s="1" t="n">
-        <v>45630.09302083333</v>
+        <v>45360.67409722223</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S59" t="n">
-        <v>0.0006615373237948306</v>
+        <v>0.0006968632755597566</v>
       </c>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
@@ -5750,143 +5720,173 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>worldcoin-wld</t>
+          <t>internet-computer</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>wld</t>
+          <t>icp</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Worldcoin</t>
+          <t>Internet Computer</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.449526</v>
+        <v>3.19</v>
       </c>
       <c r="F60" t="n">
-        <v>1640645152</v>
+        <v>1776740656</v>
       </c>
       <c r="G60" t="n">
         <v>59</v>
       </c>
       <c r="H60" t="n">
-        <v>398546805</v>
+        <v>65739470</v>
       </c>
       <c r="I60" t="n">
-        <v>0.461122</v>
+        <v>3.24</v>
       </c>
       <c r="J60" t="n">
-        <v>0.428815</v>
+        <v>3.1</v>
       </c>
       <c r="K60" t="n">
-        <v>0.01440768</v>
+        <v>0.00480555</v>
       </c>
       <c r="L60" t="n">
-        <v>3.33176</v>
+        <v>0.06728000000000001</v>
       </c>
       <c r="M60" t="n">
-        <v>3651776215.902232</v>
+        <v>556904472.5478657</v>
       </c>
       <c r="N60" t="n">
-        <v>10000000000</v>
+        <v>556914950.9844009</v>
       </c>
       <c r="O60" t="n">
-        <v>11.74</v>
+        <v>700.65</v>
       </c>
       <c r="P60" s="1" t="n">
-        <v>45360.67409722223</v>
+        <v>44326.33741898148</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R60" t="b">
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0.0006115372947513761</v>
-      </c>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
-      <c r="X60" t="inlineStr"/>
-      <c r="Y60" t="inlineStr"/>
-      <c r="Z60" t="inlineStr"/>
-      <c r="AA60" t="inlineStr"/>
+        <v>0.0006803680046636372</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Infraestructura descentralizada</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Hosting</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Proof of Stake (Chain Key)</t>
+        </is>
+      </c>
+      <c r="W60" t="n">
+        <v>2021</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>internetcomputer.org</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>Hosting descentralizado de aplicaciones</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Layer 1)</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>Busca reemplazar servidores tradicionales con "canisters" en cadena.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>htx-dao</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>htx</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>USDD</t>
+          <t>HTX DAO</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.998864</v>
+        <v>1.72e-06</v>
       </c>
       <c r="F61" t="n">
-        <v>1546477735</v>
+        <v>1546169711</v>
       </c>
       <c r="G61" t="n">
         <v>60</v>
       </c>
       <c r="H61" t="n">
-        <v>2614071</v>
+        <v>23653359</v>
       </c>
       <c r="I61" t="n">
-        <v>0.999709</v>
+        <v>1.73e-06</v>
       </c>
       <c r="J61" t="n">
-        <v>0.997564</v>
+        <v>1.71e-06</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.000447157638903684</v>
+        <v>3.848e-09</v>
       </c>
       <c r="L61" t="n">
-        <v>-0.04217</v>
+        <v>0.16571</v>
       </c>
       <c r="M61" t="n">
-        <v>1548251336</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="N61" t="n">
-        <v>1548101485</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="O61" t="n">
-        <v>1.24</v>
+        <v>3.75e-06</v>
       </c>
       <c r="P61" s="1" t="n">
-        <v>46212.39942129629</v>
+        <v>45629.67800925926</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R61" t="b">
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>0.0005554367941638737</v>
+        <v>0.0005436186406907534</v>
       </c>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
@@ -5900,68 +5900,68 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>htx-dao</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>htx</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>HTX DAO</t>
+          <t>USDD</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1.71e-06</v>
+        <v>0.998621</v>
       </c>
       <c r="F62" t="n">
-        <v>1540537375</v>
+        <v>1545202266</v>
       </c>
       <c r="G62" t="n">
         <v>61</v>
       </c>
       <c r="H62" t="n">
-        <v>7980562</v>
+        <v>2539973</v>
       </c>
       <c r="I62" t="n">
-        <v>1.73e-06</v>
+        <v>0.999776</v>
       </c>
       <c r="J62" t="n">
-        <v>1.71e-06</v>
+        <v>0.996449</v>
       </c>
       <c r="K62" t="n">
-        <v>1.983e-09</v>
+        <v>-0.000251913610240129</v>
       </c>
       <c r="L62" t="n">
-        <v>0.12334</v>
+        <v>0.0061</v>
       </c>
       <c r="M62" t="n">
-        <v>898232728634017.2</v>
+        <v>1547266660</v>
       </c>
       <c r="N62" t="n">
-        <v>898232728634017.2</v>
+        <v>1547454437</v>
       </c>
       <c r="O62" t="n">
-        <v>3.75e-06</v>
+        <v>1.24</v>
       </c>
       <c r="P62" s="1" t="n">
-        <v>45629.67800925926</v>
+        <v>46212.39942129629</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R62" t="b">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0.0005518978081718297</v>
+        <v>0.000543044858558626</v>
       </c>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
@@ -5975,262 +5975,292 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>quant-network</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>arb</t>
+          <t>qnt</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Arbitrum</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.220585</v>
+        <v>104.32</v>
       </c>
       <c r="F63" t="n">
-        <v>1496742401</v>
+        <v>1517436637</v>
       </c>
       <c r="G63" t="n">
         <v>62</v>
       </c>
       <c r="H63" t="n">
-        <v>377134691</v>
+        <v>57913062</v>
       </c>
       <c r="I63" t="n">
-        <v>0.227066</v>
+        <v>109.85</v>
       </c>
       <c r="J63" t="n">
-        <v>0.21335</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>0.00293443</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>1.34031</v>
+        <v>9.33052</v>
       </c>
       <c r="M63" t="n">
-        <v>6785574605</v>
+        <v>14544176.16408117</v>
       </c>
       <c r="N63" t="n">
-        <v>10000000000</v>
+        <v>14612493</v>
       </c>
       <c r="O63" t="n">
-        <v>2.39</v>
+        <v>427.42</v>
       </c>
       <c r="P63" s="1" t="n">
-        <v>45303.18748842592</v>
+        <v>44450.05208333334</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S63" t="n">
-        <v>0.0005258068306034777</v>
-      </c>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
-      <c r="X63" t="inlineStr"/>
-      <c r="Y63" t="inlineStr"/>
-      <c r="Z63" t="inlineStr"/>
-      <c r="AA63" t="inlineStr"/>
+        <v>0.0005265773365729003</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Infraestructura empresarial</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>N/A (token ERC-20)</t>
+        </is>
+      </c>
+      <c r="W63" t="n">
+        <v>2018</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>quant.network</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>Interoperabilidad entre redes empresariales</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>Token ERC-20 sobre Ethereum</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>Su tecnología Overledger busca conectar múltiples blockchains y redes existentes.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ethereum-classic</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>arb</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Ethereum Classic</t>
+          <t>Arbitrum</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>9.41</v>
+        <v>0.221969</v>
       </c>
       <c r="F64" t="n">
-        <v>1488173326</v>
+        <v>1506183242</v>
       </c>
       <c r="G64" t="n">
         <v>63</v>
       </c>
       <c r="H64" t="n">
-        <v>170646721</v>
+        <v>288056013</v>
       </c>
       <c r="I64" t="n">
-        <v>10.21</v>
+        <v>0.230716</v>
       </c>
       <c r="J64" t="n">
-        <v>9.35</v>
+        <v>0.217349</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.507011005980349</v>
+        <v>-0.002383285914097838</v>
       </c>
       <c r="L64" t="n">
-        <v>-5.19538</v>
+        <v>-1.09454</v>
       </c>
       <c r="M64" t="n">
-        <v>158279214.6654091</v>
+        <v>6785574605</v>
       </c>
       <c r="N64" t="n">
-        <v>158279620.2718091</v>
+        <v>10000000000</v>
       </c>
       <c r="O64" t="n">
-        <v>167.09</v>
+        <v>2.39</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>44322.44053240741</v>
+        <v>45303.18748842592</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0.000520701780338885</v>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>Plataforma de contratos inteligentes</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Layer 1</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Proof of Work</t>
-        </is>
-      </c>
-      <c r="W64" t="n">
-        <v>2016</v>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>ethereumclassic.org</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>Contratos inteligentes (cadena original)</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>Blockchain propia (fork de Ethereum)</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>Mantiene la cadena original de Ethereum tras la bifurcación de 2016.</t>
-        </is>
-      </c>
+        <v>0.0005199030584725715</v>
+      </c>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="inlineStr"/>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>united-stables</t>
+          <t>ethereum-classic</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>United Stables</t>
+          <t>Ethereum Classic</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.999408</v>
+        <v>9.41</v>
       </c>
       <c r="F65" t="n">
-        <v>1481980463</v>
+        <v>1489108155</v>
       </c>
       <c r="G65" t="n">
         <v>64</v>
       </c>
       <c r="H65" t="n">
-        <v>145534813</v>
+        <v>100188156</v>
       </c>
       <c r="I65" t="n">
-        <v>0.999688</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="J65" t="n">
-        <v>0.998783</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>0.00015674</v>
+        <v>-0.1362743174851957</v>
       </c>
       <c r="L65" t="n">
-        <v>0.02043</v>
+        <v>-1.50089</v>
       </c>
       <c r="M65" t="n">
-        <v>1482857391.63</v>
+        <v>158289223.9571552</v>
       </c>
       <c r="N65" t="n">
-        <v>1482857391.63</v>
+        <v>158290115.2467552</v>
       </c>
       <c r="O65" t="n">
-        <v>1.008</v>
+        <v>167.09</v>
       </c>
       <c r="P65" s="1" t="n">
-        <v>46058.54591435185</v>
+        <v>44322.44053240741</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R65" t="b">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0.0005170123649822992</v>
-      </c>
-      <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr"/>
-      <c r="X65" t="inlineStr"/>
-      <c r="Y65" t="inlineStr"/>
-      <c r="Z65" t="inlineStr"/>
-      <c r="AA65" t="inlineStr"/>
+        <v>0.0005097759919983821</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Plataforma de contratos inteligentes</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Layer 1</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Proof of Work</t>
+        </is>
+      </c>
+      <c r="W65" t="n">
+        <v>2016</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>ethereumclassic.org</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>Contratos inteligentes (cadena original)</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>Blockchain propia (fork de Ethereum)</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>Mantiene la cadena original de Ethereum tras la bifurcación de 2016.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6249,10 +6279,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="F66" t="n">
-        <v>1473901965</v>
+        <v>1488884774</v>
       </c>
       <c r="G66" t="n">
         <v>65</v>
@@ -6267,16 +6297,16 @@
         <v>1.15</v>
       </c>
       <c r="K66" t="n">
-        <v>0.00221151</v>
+        <v>-0.001114153641704085</v>
       </c>
       <c r="L66" t="n">
-        <v>0.19183</v>
+        <v>-0.10063</v>
       </c>
       <c r="M66" t="n">
-        <v>1276009571.67166</v>
+        <v>1289618689.24777</v>
       </c>
       <c r="N66" t="n">
-        <v>1276009571.67166</v>
+        <v>1289618689.24777</v>
       </c>
       <c r="O66" t="n">
         <v>1.18</v>
@@ -6285,13 +6315,13 @@
         <v>46255.48263888889</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R66" t="b">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0.0005121995773299085</v>
+        <v>0.0005096435069202053</v>
       </c>
       <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr"/>
@@ -6305,68 +6335,68 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>venice-token</t>
+          <t>united-stables</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>vvv</t>
+          <t>u</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Venice Token</t>
+          <t>United Stables</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>30.62</v>
+        <v>0.999503</v>
       </c>
       <c r="F67" t="n">
-        <v>1473626212</v>
+        <v>1482134028</v>
       </c>
       <c r="G67" t="n">
         <v>66</v>
       </c>
       <c r="H67" t="n">
-        <v>56626864</v>
+        <v>106423415</v>
       </c>
       <c r="I67" t="n">
-        <v>32.49</v>
+        <v>0.999776</v>
       </c>
       <c r="J67" t="n">
-        <v>29.21</v>
+        <v>0.999155</v>
       </c>
       <c r="K67" t="n">
-        <v>1.079</v>
+        <v>0.00011111</v>
       </c>
       <c r="L67" t="n">
-        <v>3.68225</v>
+        <v>0.0083</v>
       </c>
       <c r="M67" t="n">
-        <v>48143958.52816238</v>
+        <v>1482857391.63</v>
       </c>
       <c r="N67" t="n">
-        <v>81045681.33699232</v>
+        <v>1482857391.63</v>
       </c>
       <c r="O67" t="n">
-        <v>34.53</v>
+        <v>1.008</v>
       </c>
       <c r="P67" s="1" t="n">
-        <v>46286.34548611111</v>
+        <v>46058.54591435185</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R67" t="b">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.000512035296713201</v>
+        <v>0.0005056397057394342</v>
       </c>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
@@ -6380,68 +6410,68 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>usdgo</t>
+          <t>venice-token</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>usdgo</t>
+          <t>vvv</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>USDGO</t>
+          <t>Venice Token</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.9999</v>
+        <v>29.61</v>
       </c>
       <c r="F68" t="n">
-        <v>1407608854</v>
+        <v>1426184735</v>
       </c>
       <c r="G68" t="n">
         <v>67</v>
       </c>
       <c r="H68" t="n">
-        <v>122655681</v>
+        <v>32239771</v>
       </c>
       <c r="I68" t="n">
-        <v>1.001</v>
+        <v>30.81</v>
       </c>
       <c r="J68" t="n">
-        <v>0.998739</v>
+        <v>29.43</v>
       </c>
       <c r="K68" t="n">
-        <v>-4.820527743532e-06</v>
+        <v>-1.582409286039994</v>
       </c>
       <c r="L68" t="n">
-        <v>-0.04393</v>
+        <v>-5.04948</v>
       </c>
       <c r="M68" t="n">
-        <v>1407780807.97</v>
+        <v>48162092.89562348</v>
       </c>
       <c r="N68" t="n">
-        <v>1407780807.97</v>
+        <v>81051713.11454831</v>
       </c>
       <c r="O68" t="n">
-        <v>1.002</v>
+        <v>34.53</v>
       </c>
       <c r="P68" s="1" t="n">
-        <v>46092.00303240741</v>
+        <v>46286.34548611111</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S68" t="n">
-        <v>0.0004727052720692803</v>
+        <v>0.0004724567293133173</v>
       </c>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
@@ -6455,7 +6485,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6474,28 +6504,28 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="F69" t="n">
-        <v>1384882523</v>
+        <v>1425004849</v>
       </c>
       <c r="G69" t="n">
         <v>68</v>
       </c>
       <c r="H69" t="n">
-        <v>59720930</v>
+        <v>25742695</v>
       </c>
       <c r="I69" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="J69" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.06647040326293796</v>
+        <v>0.04829227</v>
       </c>
       <c r="L69" t="n">
-        <v>-3.32458</v>
+        <v>2.25009</v>
       </c>
       <c r="M69" t="n">
         <v>699992029.6481038</v>
@@ -6510,13 +6540,13 @@
         <v>45653.15375</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R69" t="b">
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>0.0004591659971668237</v>
+        <v>0.0004717569505096154</v>
       </c>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
@@ -6530,68 +6560,68 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>falcon-finance</t>
+          <t>usdgo</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>usdf</t>
+          <t>usdgo</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Falcon USD</t>
+          <t>USDGO</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.995744</v>
+        <v>0.99978</v>
       </c>
       <c r="F70" t="n">
-        <v>1371537564</v>
+        <v>1407468740</v>
       </c>
       <c r="G70" t="n">
         <v>69</v>
       </c>
       <c r="H70" t="n">
-        <v>492606</v>
+        <v>17760947</v>
       </c>
       <c r="I70" t="n">
-        <v>0.997607</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
-        <v>0.9951140000000001</v>
+        <v>0.999597</v>
       </c>
       <c r="K70" t="n">
-        <v>0.00021313</v>
+        <v>-0.000191808189512366</v>
       </c>
       <c r="L70" t="n">
-        <v>0.02418</v>
+        <v>-0.01941</v>
       </c>
       <c r="M70" t="n">
-        <v>1377413080.69863</v>
+        <v>1407780804.97</v>
       </c>
       <c r="N70" t="n">
-        <v>1377413080.69863</v>
+        <v>1407780804.97</v>
       </c>
       <c r="O70" t="n">
-        <v>1.075</v>
+        <v>1.002</v>
       </c>
       <c r="P70" s="1" t="n">
-        <v>45785.55951388889</v>
+        <v>46092.00303240741</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R70" t="b">
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>0.0004512157007259677</v>
+        <v>0.0004613564564130624</v>
       </c>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
@@ -6605,112 +6635,82 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>quant-network</t>
+          <t>falcon-finance</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>qnt</t>
+          <t>usdf</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Falcon USD</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>93.06999999999999</v>
+        <v>0.996037</v>
       </c>
       <c r="F71" t="n">
-        <v>1354412807</v>
+        <v>1371951063</v>
       </c>
       <c r="G71" t="n">
         <v>70</v>
       </c>
       <c r="H71" t="n">
-        <v>95089796</v>
+        <v>343325</v>
       </c>
       <c r="I71" t="n">
-        <v>104.14</v>
+        <v>0.996958</v>
       </c>
       <c r="J71" t="n">
-        <v>80.03</v>
+        <v>0.995733</v>
       </c>
       <c r="K71" t="n">
-        <v>13.59</v>
+        <v>0.00052593</v>
       </c>
       <c r="L71" t="n">
-        <v>17.0986</v>
+        <v>0.0473</v>
       </c>
       <c r="M71" t="n">
-        <v>14544176.16408117</v>
+        <v>1377413080.69863</v>
       </c>
       <c r="N71" t="n">
-        <v>14612493</v>
+        <v>1377413080.69863</v>
       </c>
       <c r="O71" t="n">
-        <v>427.42</v>
+        <v>1.075</v>
       </c>
       <c r="P71" s="1" t="n">
-        <v>44450.05208333334</v>
+        <v>45785.55951388889</v>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>0.0004410135791137828</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Interoperabilidad</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Infraestructura empresarial</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>N/A (token ERC-20)</t>
-        </is>
-      </c>
-      <c r="W71" t="n">
-        <v>2018</v>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>quant.network</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>Interoperabilidad entre redes empresariales</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>Token ERC-20 sobre Ethereum</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>Su tecnología Overledger busca conectar múltiples blockchains y redes existentes.</t>
-        </is>
-      </c>
+        <v>0.0004402912708601111</v>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr"/>
+      <c r="X71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6729,28 +6729,28 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.999516</v>
+        <v>0.9997239999999999</v>
       </c>
       <c r="F72" t="n">
-        <v>1319348505</v>
+        <v>1319632232</v>
       </c>
       <c r="G72" t="n">
         <v>71</v>
       </c>
       <c r="H72" t="n">
-        <v>6768478</v>
+        <v>968552</v>
       </c>
       <c r="I72" t="n">
-        <v>0.999864</v>
+        <v>0.999837</v>
       </c>
       <c r="J72" t="n">
-        <v>0.998769</v>
+        <v>0.999417</v>
       </c>
       <c r="K72" t="n">
-        <v>-9.2806474289331e-05</v>
+        <v>0.00046168</v>
       </c>
       <c r="L72" t="n">
-        <v>-0.0065</v>
+        <v>0.04044</v>
       </c>
       <c r="M72" t="n">
         <v>1320000000</v>
@@ -6765,13 +6765,13 @@
         <v>45940.56990740741</v>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R72" t="b">
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>0.0004201239236722264</v>
+        <v>0.0004092614858060801</v>
       </c>
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
@@ -6785,68 +6785,68 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>lighter</t>
+          <t>polygon-ecosystem-token</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>lit</t>
+          <t>pol</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Lighter</t>
+          <t>POL (ex-MATIC)</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4.85</v>
+        <v>0.118846</v>
       </c>
       <c r="F73" t="n">
-        <v>1212495922</v>
+        <v>1262197947</v>
       </c>
       <c r="G73" t="n">
         <v>72</v>
       </c>
       <c r="H73" t="n">
-        <v>125800863</v>
+        <v>128937182</v>
       </c>
       <c r="I73" t="n">
-        <v>5.5</v>
+        <v>0.120365</v>
       </c>
       <c r="J73" t="n">
-        <v>4.81</v>
+        <v>0.11172</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.3229688832451751</v>
+        <v>0.00581829</v>
       </c>
       <c r="L73" t="n">
-        <v>-6.27448</v>
+        <v>5.11378</v>
       </c>
       <c r="M73" t="n">
-        <v>250000000</v>
+        <v>10621081493.65423</v>
       </c>
       <c r="N73" t="n">
-        <v>1000000000</v>
+        <v>10621081493.65423</v>
       </c>
       <c r="O73" t="n">
-        <v>7.86</v>
+        <v>1.29</v>
       </c>
       <c r="P73" s="1" t="n">
-        <v>46021.04538194444</v>
+        <v>45364.45493055556</v>
       </c>
       <c r="Q73" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0.0003564662001587139</v>
+        <v>0.0003751977752028758</v>
       </c>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
@@ -6860,68 +6860,68 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>polygon-ecosystem-token</t>
+          <t>kaspa</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>pol</t>
+          <t>kas</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>POL (ex-MATIC)</t>
+          <t>Kaspa</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.113301</v>
+        <v>0.04542232</v>
       </c>
       <c r="F74" t="n">
-        <v>1202787277</v>
+        <v>1259118653</v>
       </c>
       <c r="G74" t="n">
         <v>73</v>
       </c>
       <c r="H74" t="n">
-        <v>120632746</v>
+        <v>23423308</v>
       </c>
       <c r="I74" t="n">
-        <v>0.113885</v>
+        <v>0.04566325</v>
       </c>
       <c r="J74" t="n">
-        <v>0.10441</v>
+        <v>0.04102786</v>
       </c>
       <c r="K74" t="n">
-        <v>0.00882021</v>
+        <v>0.00334235</v>
       </c>
       <c r="L74" t="n">
-        <v>8.481</v>
+        <v>7.91683</v>
       </c>
       <c r="M74" t="n">
-        <v>10620499850.30005</v>
+        <v>27720927947.15285</v>
       </c>
       <c r="N74" t="n">
-        <v>10620499850.30005</v>
+        <v>27722506351.82228</v>
       </c>
       <c r="O74" t="n">
-        <v>1.29</v>
+        <v>0.207411</v>
       </c>
       <c r="P74" s="1" t="n">
-        <v>45364.45493055556</v>
+        <v>45504.69498842592</v>
       </c>
       <c r="Q74" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R74" t="b">
         <v>1</v>
       </c>
       <c r="S74" t="n">
-        <v>0.000350682247897112</v>
+        <v>0.0003733714761607935</v>
       </c>
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
@@ -6935,68 +6935,68 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>kaspa</t>
+          <t>lighter</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>kas</t>
+          <t>lit</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Kaspa</t>
+          <t>Lighter</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.0414891</v>
+        <v>4.79</v>
       </c>
       <c r="F75" t="n">
-        <v>1149882008</v>
+        <v>1196387939</v>
       </c>
       <c r="G75" t="n">
         <v>74</v>
       </c>
       <c r="H75" t="n">
-        <v>19397785</v>
+        <v>90622785</v>
       </c>
       <c r="I75" t="n">
-        <v>0.04231564</v>
+        <v>4.93</v>
       </c>
       <c r="J75" t="n">
-        <v>0.03920464</v>
+        <v>4.69</v>
       </c>
       <c r="K75" t="n">
-        <v>0.00224125</v>
+        <v>-0.1230667607995493</v>
       </c>
       <c r="L75" t="n">
-        <v>5.6164</v>
+        <v>-2.44909</v>
       </c>
       <c r="M75" t="n">
-        <v>27719200688.33876</v>
+        <v>250000000</v>
       </c>
       <c r="N75" t="n">
-        <v>27720665879.75146</v>
+        <v>1000000000</v>
       </c>
       <c r="O75" t="n">
-        <v>0.207411</v>
+        <v>7.86</v>
       </c>
       <c r="P75" s="1" t="n">
-        <v>45504.69498842592</v>
+        <v>46021.04538194444</v>
       </c>
       <c r="Q75" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R75" t="b">
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>0.0003191637867438613</v>
+        <v>0.0003361665055125409</v>
       </c>
       <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr"/>
@@ -7010,7 +7010,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7029,34 +7029,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>10.75</v>
+        <v>10.85</v>
       </c>
       <c r="F76" t="n">
-        <v>1145582393</v>
+        <v>1157017948</v>
       </c>
       <c r="G76" t="n">
         <v>75</v>
       </c>
       <c r="H76" t="n">
-        <v>1236749</v>
+        <v>2307769</v>
       </c>
       <c r="I76" t="n">
-        <v>10.98</v>
+        <v>10.94</v>
       </c>
       <c r="J76" t="n">
-        <v>10.6</v>
+        <v>10.66</v>
       </c>
       <c r="K76" t="n">
-        <v>0.133134</v>
+        <v>0.02972548</v>
       </c>
       <c r="L76" t="n">
-        <v>1.10001</v>
+        <v>0.1931</v>
       </c>
       <c r="M76" t="n">
-        <v>106640355.6187321</v>
+        <v>106641451.5494122</v>
       </c>
       <c r="N76" t="n">
-        <v>118891623.1107255</v>
+        <v>118892748.0467987</v>
       </c>
       <c r="O76" t="n">
         <v>25.38</v>
@@ -7065,13 +7065,13 @@
         <v>45682.66666666666</v>
       </c>
       <c r="Q76" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R76" t="b">
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0003166022791490046</v>
+        <v>0.0003128165503442166</v>
       </c>
       <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr"/>
@@ -7085,7 +7085,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7104,34 +7104,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.319361</v>
+        <v>0.348185</v>
       </c>
       <c r="F77" t="n">
-        <v>1059995753</v>
+        <v>1155689790</v>
       </c>
       <c r="G77" t="n">
         <v>76</v>
       </c>
       <c r="H77" t="n">
-        <v>113892448</v>
+        <v>125061347</v>
       </c>
       <c r="I77" t="n">
-        <v>0.331898</v>
+        <v>0.353561</v>
       </c>
       <c r="J77" t="n">
-        <v>0.296086</v>
+        <v>0.316158</v>
       </c>
       <c r="K77" t="n">
-        <v>0.02561843</v>
+        <v>0.02654711</v>
       </c>
       <c r="L77" t="n">
-        <v>8.68707</v>
+        <v>8.200060000000001</v>
       </c>
       <c r="M77" t="n">
         <v>3319369204.37</v>
       </c>
       <c r="N77" t="n">
-        <v>6861486668.371618</v>
+        <v>6861486658.154251</v>
       </c>
       <c r="O77" t="n">
         <v>2</v>
@@ -7140,13 +7140,13 @@
         <v>45322.29359953704</v>
       </c>
       <c r="Q77" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R77" t="b">
         <v>1</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0002656138003251419</v>
+        <v>0.0003120288328728956</v>
       </c>
       <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr"/>
@@ -7160,7 +7160,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7179,34 +7179,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.115416</v>
+        <v>0.116944</v>
       </c>
       <c r="F78" t="n">
-        <v>1045007842</v>
+        <v>1059206801</v>
       </c>
       <c r="G78" t="n">
         <v>77</v>
       </c>
       <c r="H78" t="n">
-        <v>71211178</v>
+        <v>60144257</v>
       </c>
       <c r="I78" t="n">
-        <v>0.118425</v>
+        <v>0.118949</v>
       </c>
       <c r="J78" t="n">
-        <v>0.110361</v>
+        <v>0.112661</v>
       </c>
       <c r="K78" t="n">
-        <v>0.00568445</v>
+        <v>0.00046668</v>
       </c>
       <c r="L78" t="n">
-        <v>5.08492</v>
+        <v>0.41247</v>
       </c>
       <c r="M78" t="n">
-        <v>9057076849.535131</v>
+        <v>9057191179.647024</v>
       </c>
       <c r="N78" t="n">
-        <v>9057147759.259453</v>
+        <v>9057345611.155615</v>
       </c>
       <c r="O78" t="n">
         <v>3.56</v>
@@ -7215,13 +7215,13 @@
         <v>43636.28563657407</v>
       </c>
       <c r="Q78" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R78" t="b">
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>0.0002566847106607102</v>
+        <v>0.0002548057192670042</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -7265,173 +7265,143 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>kucoin-shares</t>
+          <t>pi-network</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>kcs</t>
+          <t>pi</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>KuCoin</t>
+          <t>Pi Network</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>7.36</v>
+        <v>0.091715</v>
       </c>
       <c r="F79" t="n">
-        <v>1009611380</v>
+        <v>1031168252</v>
       </c>
       <c r="G79" t="n">
         <v>78</v>
       </c>
       <c r="H79" t="n">
-        <v>3380693</v>
+        <v>8549644</v>
       </c>
       <c r="I79" t="n">
-        <v>7.41</v>
+        <v>0.09243899999999999</v>
       </c>
       <c r="J79" t="n">
-        <v>7.18</v>
+        <v>0.088589</v>
       </c>
       <c r="K79" t="n">
-        <v>0.151384</v>
+        <v>0.0019178</v>
       </c>
       <c r="L79" t="n">
-        <v>2.12723</v>
+        <v>2.1716</v>
       </c>
       <c r="M79" t="n">
-        <v>137155021.2773955</v>
+        <v>11243022455.381</v>
       </c>
       <c r="N79" t="n">
-        <v>142155021.2773955</v>
+        <v>17296957623.66307</v>
       </c>
       <c r="O79" t="n">
-        <v>28.83</v>
+        <v>2.99</v>
       </c>
       <c r="P79" s="1" t="n">
-        <v>44531.29832175926</v>
+        <v>45714.36184027778</v>
       </c>
       <c r="Q79" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R79" t="b">
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0002355971699753104</v>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>Token de exchange</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>Utilidad</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>N/A (token de exchange)</t>
-        </is>
-      </c>
-      <c r="W79" t="n">
-        <v>2017</v>
-      </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>kucoin.com</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>Beneficios en el exchange KuCoin</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>Token ERC-20 sobre Ethereum</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>Otorga descuentos en comisiones dentro del exchange KuCoin.</t>
-        </is>
-      </c>
+        <v>0.0002381763311085243</v>
+      </c>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr"/>
+      <c r="X79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>pi-network</t>
+          <t>render-token</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>pi</t>
+          <t>render</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Pi Network</t>
+          <t>Render</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.089106</v>
+        <v>1.97</v>
       </c>
       <c r="F80" t="n">
-        <v>1001481315</v>
+        <v>1022531450</v>
       </c>
       <c r="G80" t="n">
         <v>79</v>
       </c>
       <c r="H80" t="n">
-        <v>11009834</v>
+        <v>86881391</v>
       </c>
       <c r="I80" t="n">
-        <v>0.09019000000000001</v>
+        <v>2.03</v>
       </c>
       <c r="J80" t="n">
-        <v>0.085051</v>
+        <v>1.9</v>
       </c>
       <c r="K80" t="n">
-        <v>0.00222097</v>
+        <v>0.03418244</v>
       </c>
       <c r="L80" t="n">
-        <v>2.52261</v>
+        <v>1.78692</v>
       </c>
       <c r="M80" t="n">
-        <v>11243022455.381</v>
+        <v>518776241.2826915</v>
       </c>
       <c r="N80" t="n">
-        <v>17296957623.66307</v>
+        <v>533536414.5626915</v>
       </c>
       <c r="O80" t="n">
-        <v>2.99</v>
+        <v>13.53</v>
       </c>
       <c r="P80" s="1" t="n">
-        <v>45714.36184027778</v>
+        <v>45368.35444444444</v>
       </c>
       <c r="Q80" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R80" t="b">
         <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>0.0002307536611392452</v>
+        <v>0.0002330539286294967</v>
       </c>
       <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr"/>
@@ -7445,68 +7415,68 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>render-token</t>
+          <t>just</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>render</t>
+          <t>jst</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Render</t>
+          <t>JUST</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1.92</v>
+        <v>0.123629</v>
       </c>
       <c r="F81" t="n">
-        <v>995521344</v>
+        <v>1012500582</v>
       </c>
       <c r="G81" t="n">
         <v>80</v>
       </c>
       <c r="H81" t="n">
-        <v>112423046</v>
+        <v>36482428</v>
       </c>
       <c r="I81" t="n">
-        <v>1.97</v>
+        <v>0.123932</v>
       </c>
       <c r="J81" t="n">
-        <v>1.82</v>
+        <v>0.11751</v>
       </c>
       <c r="K81" t="n">
-        <v>0.08316900000000001</v>
+        <v>0.00542943</v>
       </c>
       <c r="L81" t="n">
-        <v>4.34985</v>
+        <v>4.64102</v>
       </c>
       <c r="M81" t="n">
-        <v>518776241.2826915</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="N81" t="n">
-        <v>533536414.5626915</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="O81" t="n">
-        <v>13.53</v>
+        <v>0.193254</v>
       </c>
       <c r="P81" s="1" t="n">
-        <v>45368.35444444444</v>
+        <v>44290.85721064815</v>
       </c>
       <c r="Q81" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R81" t="b">
         <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0.0002272029918394067</v>
+        <v>0.0002271047192913646</v>
       </c>
       <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr"/>
@@ -7520,143 +7490,173 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>blockchain-capital</t>
+          <t>kucoin-shares</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>bcap</t>
+          <t>kcs</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Blockchain Capital</t>
+          <t>KuCoin</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>107.53</v>
+        <v>7.34</v>
       </c>
       <c r="F82" t="n">
-        <v>978427406</v>
+        <v>1006756504</v>
       </c>
       <c r="G82" t="n">
         <v>81</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>2930807</v>
       </c>
       <c r="I82" t="n">
-        <v>107.53</v>
+        <v>7.41</v>
       </c>
       <c r="J82" t="n">
-        <v>107.53</v>
+        <v>7.3</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>-0.05190538893039687</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>-0.79274</v>
       </c>
       <c r="M82" t="n">
-        <v>9099111</v>
+        <v>137155021.2773955</v>
       </c>
       <c r="N82" t="n">
-        <v>9099111</v>
+        <v>142155021.2773955</v>
       </c>
       <c r="O82" t="n">
-        <v>107.53</v>
+        <v>28.83</v>
       </c>
       <c r="P82" s="1" t="n">
-        <v>46287.17361111111</v>
+        <v>44531.29832175926</v>
       </c>
       <c r="Q82" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R82" t="b">
         <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0.0002170192307321892</v>
-      </c>
-      <c r="T82" t="inlineStr"/>
-      <c r="U82" t="inlineStr"/>
-      <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
-      <c r="X82" t="inlineStr"/>
-      <c r="Y82" t="inlineStr"/>
-      <c r="Z82" t="inlineStr"/>
-      <c r="AA82" t="inlineStr"/>
+        <v>0.0002236979630189703</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Token de exchange</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Utilidad</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>N/A (token de exchange)</t>
+        </is>
+      </c>
+      <c r="W82" t="n">
+        <v>2017</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>kucoin.com</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>Beneficios en el exchange KuCoin</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>Token ERC-20 sobre Ethereum</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>Otorga descuentos en comisiones dentro del exchange KuCoin.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>just</t>
+          <t>blockchain-capital</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>jst</t>
+          <t>bcap</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>JUST</t>
+          <t>Blockchain Capital</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.117651</v>
+        <v>107.53</v>
       </c>
       <c r="F83" t="n">
-        <v>963523665</v>
+        <v>979825296</v>
       </c>
       <c r="G83" t="n">
         <v>82</v>
       </c>
       <c r="H83" t="n">
-        <v>32137657</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>0.118548</v>
+        <v>107.53</v>
       </c>
       <c r="J83" t="n">
-        <v>0.111445</v>
+        <v>107.53</v>
       </c>
       <c r="K83" t="n">
-        <v>0.00652213</v>
+        <v>1.4211e-14</v>
       </c>
       <c r="L83" t="n">
-        <v>5.85401</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>8188743036.341737</v>
+        <v>9112111</v>
       </c>
       <c r="N83" t="n">
-        <v>8188743036.341737</v>
+        <v>9112111</v>
       </c>
       <c r="O83" t="n">
-        <v>0.193254</v>
+        <v>107.53</v>
       </c>
       <c r="P83" s="1" t="n">
-        <v>44290.85721064815</v>
+        <v>46287.17361111111</v>
       </c>
       <c r="Q83" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R83" t="b">
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.0002081402855793612</v>
+        <v>0.0002077253279368638</v>
       </c>
       <c r="T83" t="inlineStr"/>
       <c r="U83" t="inlineStr"/>
@@ -7670,7 +7670,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7689,34 +7689,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="F84" t="n">
-        <v>948940173</v>
+        <v>971545414</v>
       </c>
       <c r="G84" t="n">
         <v>83</v>
       </c>
       <c r="H84" t="n">
-        <v>59826778</v>
+        <v>70338630</v>
       </c>
       <c r="I84" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="J84" t="n">
         <v>1.75</v>
       </c>
       <c r="K84" t="n">
-        <v>0.03534209</v>
+        <v>0.01496126</v>
       </c>
       <c r="L84" t="n">
-        <v>1.92624</v>
+        <v>0.83594</v>
       </c>
       <c r="M84" t="n">
-        <v>532499193.619167</v>
+        <v>532679589.941325</v>
       </c>
       <c r="N84" t="n">
-        <v>532508903.268164</v>
+        <v>532693432.459343</v>
       </c>
       <c r="O84" t="n">
         <v>43.84</v>
@@ -7725,13 +7725,13 @@
         <v>44458.66666666666</v>
       </c>
       <c r="Q84" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R84" t="b">
         <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0.0001994521296589983</v>
+        <v>0.0002028146112059655</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -7775,173 +7775,143 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>pancakeswap-token</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>cake</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>PancakeSwap</t>
+          <t>Dash</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2.75</v>
+        <v>69.95</v>
       </c>
       <c r="F85" t="n">
-        <v>875979147</v>
+        <v>898822093</v>
       </c>
       <c r="G85" t="n">
         <v>84</v>
       </c>
       <c r="H85" t="n">
-        <v>145535123</v>
+        <v>203716422</v>
       </c>
       <c r="I85" t="n">
-        <v>2.84</v>
+        <v>69.89</v>
       </c>
       <c r="J85" t="n">
-        <v>2.68</v>
+        <v>61.31</v>
       </c>
       <c r="K85" t="n">
-        <v>0.073916</v>
+        <v>5.96</v>
       </c>
       <c r="L85" t="n">
-        <v>2.82672</v>
+        <v>9.46149</v>
       </c>
       <c r="M85" t="n">
-        <v>319002175.3752098</v>
+        <v>12843583.773267</v>
       </c>
       <c r="N85" t="n">
-        <v>330627631.3973402</v>
+        <v>12844558.462616</v>
       </c>
       <c r="O85" t="n">
-        <v>43.96</v>
+        <v>1493.59</v>
       </c>
       <c r="P85" s="1" t="n">
-        <v>44316.08914351852</v>
+        <v>43088.66666666666</v>
       </c>
       <c r="Q85" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S85" t="n">
-        <v>0.0001559853954915126</v>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>DeFi</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>Exchange descentralizado</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>N/A (token BEP-20)</t>
-        </is>
-      </c>
-      <c r="W85" t="n">
-        <v>2020</v>
-      </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>pancakeswap.finance</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>Intercambio descentralizado en BNB Chain</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>Token BEP-20 sobre BNB Chain</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>Principal exchange descentralizado (DEX) del ecosistema BNB Chain.</t>
-        </is>
-      </c>
+        <v>0.0001596831234430739</v>
+      </c>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
+      <c r="W85" t="inlineStr"/>
+      <c r="X85" t="inlineStr"/>
+      <c r="Y85" t="inlineStr"/>
+      <c r="Z85" t="inlineStr"/>
+      <c r="AA85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>nexo</t>
+          <t>aerodrome-finance</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>nexo</t>
+          <t>aero</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NEXO</t>
+          <t>Aerodrome Finance</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.869078</v>
+        <v>0.902818</v>
       </c>
       <c r="F86" t="n">
-        <v>869044877</v>
+        <v>899670268</v>
       </c>
       <c r="G86" t="n">
         <v>85</v>
       </c>
       <c r="H86" t="n">
-        <v>7827337</v>
+        <v>194318021</v>
       </c>
       <c r="I86" t="n">
-        <v>0.886178</v>
+        <v>0.928633</v>
       </c>
       <c r="J86" t="n">
-        <v>0.857514</v>
+        <v>0.778429</v>
       </c>
       <c r="K86" t="n">
-        <v>-5.9932278523078e-05</v>
+        <v>0.117348</v>
       </c>
       <c r="L86" t="n">
-        <v>0.01997</v>
+        <v>14.85755</v>
       </c>
       <c r="M86" t="n">
-        <v>1000000000</v>
+        <v>996440490.4616158</v>
       </c>
       <c r="N86" t="n">
-        <v>1000000000</v>
+        <v>1988034890.229641</v>
       </c>
       <c r="O86" t="n">
-        <v>4.07</v>
+        <v>2.32</v>
       </c>
       <c r="P86" s="1" t="n">
-        <v>44328.27623842593</v>
+        <v>45633.25043981482</v>
       </c>
       <c r="Q86" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S86" t="n">
-        <v>0.0001518542848525864</v>
+        <v>0.0001601861677090707</v>
       </c>
       <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr"/>
@@ -7955,7 +7925,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7974,34 +7944,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1.009</v>
+        <v>1.077</v>
       </c>
       <c r="F87" t="n">
-        <v>838317629</v>
+        <v>894854410</v>
       </c>
       <c r="G87" t="n">
         <v>86</v>
       </c>
       <c r="H87" t="n">
-        <v>159594715</v>
+        <v>156645519</v>
       </c>
       <c r="I87" t="n">
-        <v>1.038</v>
+        <v>1.1</v>
       </c>
       <c r="J87" t="n">
-        <v>0.972841</v>
+        <v>0.996161</v>
       </c>
       <c r="K87" t="n">
-        <v>0.01481956</v>
+        <v>0.054072</v>
       </c>
       <c r="L87" t="n">
-        <v>1.41486</v>
+        <v>5.26212</v>
       </c>
       <c r="M87" t="n">
-        <v>831061204</v>
+        <v>831111902</v>
       </c>
       <c r="N87" t="n">
-        <v>1957029463</v>
+        <v>1957027561</v>
       </c>
       <c r="O87" t="n">
         <v>236.84</v>
@@ -8010,13 +7980,13 @@
         <v>44287.22894675926</v>
       </c>
       <c r="Q87" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R87" t="b">
         <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>0.0001335484413942665</v>
+        <v>0.0001573299296063742</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -8060,143 +8030,173 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>akedo</t>
+          <t>pancakeswap-token</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ake</t>
+          <t>cake</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Akedo</t>
+          <t>PancakeSwap</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.03640452</v>
+        <v>2.77</v>
       </c>
       <c r="F88" t="n">
-        <v>828564766</v>
+        <v>885011773</v>
       </c>
       <c r="G88" t="n">
         <v>87</v>
       </c>
       <c r="H88" t="n">
-        <v>38920263</v>
+        <v>92529235</v>
       </c>
       <c r="I88" t="n">
-        <v>0.04574245</v>
+        <v>2.83</v>
       </c>
       <c r="J88" t="n">
-        <v>0.0346635</v>
+        <v>2.74</v>
       </c>
       <c r="K88" t="n">
-        <v>-0.007543193430547573</v>
+        <v>0.00491875</v>
       </c>
       <c r="L88" t="n">
-        <v>-17.12125</v>
+        <v>0.19917</v>
       </c>
       <c r="M88" t="n">
-        <v>22796250000</v>
+        <v>319003107.6029418</v>
       </c>
       <c r="N88" t="n">
-        <v>100000000000</v>
+        <v>330627631.389633</v>
       </c>
       <c r="O88" t="n">
-        <v>0.146656</v>
+        <v>43.96</v>
       </c>
       <c r="P88" s="1" t="n">
-        <v>46285.43993055556</v>
+        <v>44316.08914351852</v>
       </c>
       <c r="Q88" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>0.0001277381461361803</v>
-      </c>
-      <c r="T88" t="inlineStr"/>
-      <c r="U88" t="inlineStr"/>
-      <c r="V88" t="inlineStr"/>
-      <c r="W88" t="inlineStr"/>
-      <c r="X88" t="inlineStr"/>
-      <c r="Y88" t="inlineStr"/>
-      <c r="Z88" t="inlineStr"/>
-      <c r="AA88" t="inlineStr"/>
+        <v>0.0001514923582264852</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>DeFi</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Exchange descentralizado</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>N/A (token BEP-20)</t>
+        </is>
+      </c>
+      <c r="W88" t="n">
+        <v>2020</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>pancakeswap.finance</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>Intercambio descentralizado en BNB Chain</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>Token BEP-20 sobre BNB Chain</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>Principal exchange descentralizado (DEX) del ecosistema BNB Chain.</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>injective-protocol</t>
+          <t>nexo</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>inj</t>
+          <t>nexo</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Injective</t>
+          <t>NEXO</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>8.15</v>
+        <v>0.861675</v>
       </c>
       <c r="F89" t="n">
-        <v>815036849</v>
+        <v>861531313</v>
       </c>
       <c r="G89" t="n">
         <v>88</v>
       </c>
       <c r="H89" t="n">
-        <v>197208993</v>
+        <v>4126065</v>
       </c>
       <c r="I89" t="n">
-        <v>8.66</v>
+        <v>0.878094</v>
       </c>
       <c r="J89" t="n">
-        <v>7.81</v>
+        <v>0.860256</v>
       </c>
       <c r="K89" t="n">
-        <v>0.111556</v>
+        <v>-0.01030049736247129</v>
       </c>
       <c r="L89" t="n">
-        <v>1.58886</v>
+        <v>-1.39503</v>
       </c>
       <c r="M89" t="n">
-        <v>100000000</v>
+        <v>1000000000</v>
       </c>
       <c r="N89" t="n">
-        <v>100000000</v>
+        <v>1000000000</v>
       </c>
       <c r="O89" t="n">
-        <v>52.62</v>
+        <v>4.07</v>
       </c>
       <c r="P89" s="1" t="n">
-        <v>45365.29608796296</v>
+        <v>44328.27623842593</v>
       </c>
       <c r="Q89" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R89" t="b">
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>0.0001196788519579596</v>
+        <v>0.0001375663279073106</v>
       </c>
       <c r="T89" t="inlineStr"/>
       <c r="U89" t="inlineStr"/>
@@ -8210,248 +8210,248 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>vechain</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>vet</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Dash</t>
+          <t>VeChain</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>63.43</v>
+        <v>0.009570739999999999</v>
       </c>
       <c r="F90" t="n">
-        <v>814699071</v>
+        <v>822603089</v>
       </c>
       <c r="G90" t="n">
         <v>89</v>
       </c>
       <c r="H90" t="n">
-        <v>170596830</v>
+        <v>16882621</v>
       </c>
       <c r="I90" t="n">
-        <v>65.15000000000001</v>
+        <v>0.00982453</v>
       </c>
       <c r="J90" t="n">
-        <v>61.89</v>
+        <v>0.00921142</v>
       </c>
       <c r="K90" t="n">
-        <v>0.13786</v>
+        <v>0.00015465</v>
       </c>
       <c r="L90" t="n">
-        <v>0.25428</v>
+        <v>1.51333</v>
       </c>
       <c r="M90" t="n">
-        <v>12843030.2492792</v>
+        <v>85985041177</v>
       </c>
       <c r="N90" t="n">
-        <v>12843282.71574738</v>
+        <v>85985041177</v>
       </c>
       <c r="O90" t="n">
-        <v>1493.59</v>
+        <v>0.280991</v>
       </c>
       <c r="P90" s="1" t="n">
-        <v>43088.66666666666</v>
+        <v>44304.71413194444</v>
       </c>
       <c r="Q90" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R90" t="b">
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>0.0001194776197749907</v>
-      </c>
-      <c r="T90" t="inlineStr"/>
-      <c r="U90" t="inlineStr"/>
-      <c r="V90" t="inlineStr"/>
-      <c r="W90" t="inlineStr"/>
-      <c r="X90" t="inlineStr"/>
-      <c r="Y90" t="inlineStr"/>
-      <c r="Z90" t="inlineStr"/>
-      <c r="AA90" t="inlineStr"/>
+        <v>0.0001144783804098757</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Cadena de suministro</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Trazabilidad</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Proof of Authority</t>
+        </is>
+      </c>
+      <c r="W90" t="n">
+        <v>2015</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>vechain.org</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>Trazabilidad de productos y logística</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Layer 1)</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>Enfocada en trazabilidad de cadenas de suministro para empresas.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>vechain</t>
+          <t>injective-protocol</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>vet</t>
+          <t>inj</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VeChain</t>
+          <t>Injective</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.009269289999999999</v>
+        <v>7.72</v>
       </c>
       <c r="F91" t="n">
-        <v>796885287</v>
+        <v>771644501</v>
       </c>
       <c r="G91" t="n">
         <v>90</v>
       </c>
       <c r="H91" t="n">
-        <v>16263493</v>
+        <v>135312541</v>
       </c>
       <c r="I91" t="n">
-        <v>0.009602390000000001</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="J91" t="n">
-        <v>0.009108389999999999</v>
+        <v>7.72</v>
       </c>
       <c r="K91" t="n">
-        <v>-7.7648113541154e-05</v>
+        <v>-0.5346314063898721</v>
       </c>
       <c r="L91" t="n">
-        <v>-0.64808</v>
+        <v>-6.36509</v>
       </c>
       <c r="M91" t="n">
-        <v>85985041177</v>
+        <v>100000000</v>
       </c>
       <c r="N91" t="n">
-        <v>85985041177</v>
+        <v>100000000</v>
       </c>
       <c r="O91" t="n">
-        <v>0.280991</v>
+        <v>52.62</v>
       </c>
       <c r="P91" s="1" t="n">
-        <v>44304.71413194444</v>
+        <v>45365.29608796296</v>
       </c>
       <c r="Q91" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S91" t="n">
-        <v>0.000108865008411151</v>
-      </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>Cadena de suministro</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>Trazabilidad</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>Proof of Authority</t>
-        </is>
-      </c>
-      <c r="W91" t="n">
-        <v>2015</v>
-      </c>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>vechain.org</t>
-        </is>
-      </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>Trazabilidad de productos y logística</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Layer 1)</t>
-        </is>
-      </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>Enfocada en trazabilidad de cadenas de suministro para empresas.</t>
-        </is>
-      </c>
+        <v>8.42553421256885e-05</v>
+      </c>
+      <c r="T91" t="inlineStr"/>
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" t="inlineStr"/>
+      <c r="W91" t="inlineStr"/>
+      <c r="X91" t="inlineStr"/>
+      <c r="Y91" t="inlineStr"/>
+      <c r="Z91" t="inlineStr"/>
+      <c r="AA91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>aerodrome-finance</t>
+          <t>akedo</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>aero</t>
+          <t>ake</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Aerodrome Finance</t>
+          <t>Akedo</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.787972</v>
+        <v>0.03331356</v>
       </c>
       <c r="F92" t="n">
-        <v>785722199</v>
+        <v>759306553</v>
       </c>
       <c r="G92" t="n">
         <v>91</v>
       </c>
       <c r="H92" t="n">
-        <v>81946992</v>
+        <v>27698737</v>
       </c>
       <c r="I92" t="n">
-        <v>0.7992629999999999</v>
+        <v>0.03884774</v>
       </c>
       <c r="J92" t="n">
-        <v>0.683981</v>
+        <v>0.03173795</v>
       </c>
       <c r="K92" t="n">
-        <v>0.081188</v>
+        <v>-0.002265419230698736</v>
       </c>
       <c r="L92" t="n">
-        <v>11.31651</v>
+        <v>-6.40924</v>
       </c>
       <c r="M92" t="n">
-        <v>996570413.9183272</v>
+        <v>22796250000</v>
       </c>
       <c r="N92" t="n">
-        <v>1988034890.229641</v>
+        <v>100000000000</v>
       </c>
       <c r="O92" t="n">
-        <v>2.32</v>
+        <v>0.146656</v>
       </c>
       <c r="P92" s="1" t="n">
-        <v>45633.25043981482</v>
+        <v>46285.43993055556</v>
       </c>
       <c r="Q92" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R92" t="b">
         <v>1</v>
       </c>
       <c r="S92" t="n">
-        <v>0.0001022145676870272</v>
+        <v>7.693782628807716e-05</v>
       </c>
       <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr"/>
@@ -8465,7 +8465,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8487,7 +8487,7 @@
         <v>1.21</v>
       </c>
       <c r="F93" t="n">
-        <v>751325184</v>
+        <v>750951665</v>
       </c>
       <c r="G93" t="n">
         <v>92</v>
@@ -8499,13 +8499,13 @@
         <v>1.21</v>
       </c>
       <c r="J93" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="K93" t="n">
-        <v>0.00228199</v>
+        <v>-0.001218802952861919</v>
       </c>
       <c r="L93" t="n">
-        <v>0.18932</v>
+        <v>-0.10087</v>
       </c>
       <c r="M93" t="n">
         <v>622138754.14688</v>
@@ -8520,13 +8520,13 @@
         <v>46049.54175925926</v>
       </c>
       <c r="Q93" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R93" t="b">
         <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>8.172245033165977e-05</v>
+        <v>7.198262423491006e-05</v>
       </c>
       <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr"/>
@@ -8540,7 +8540,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8562,7 +8562,7 @@
         <v>11.22</v>
       </c>
       <c r="F94" t="n">
-        <v>743434067</v>
+        <v>750639257</v>
       </c>
       <c r="G94" t="n">
         <v>93</v>
@@ -8577,31 +8577,31 @@
         <v>11.22</v>
       </c>
       <c r="K94" t="n">
-        <v>0.001127</v>
+        <v>-1.776e-15</v>
       </c>
       <c r="L94" t="n">
-        <v>0.01004</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>66239925.553293</v>
+        <v>66881907.490516</v>
       </c>
       <c r="N94" t="n">
-        <v>65432278.887564</v>
+        <v>67220432.10558</v>
       </c>
       <c r="O94" t="n">
         <v>11.22</v>
       </c>
       <c r="P94" s="1" t="n">
-        <v>46290.55567129629</v>
+        <v>46290.60069444445</v>
       </c>
       <c r="Q94" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R94" t="b">
         <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>7.702129543118554e-05</v>
+        <v>7.179733811700808e-05</v>
       </c>
       <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
@@ -8615,7 +8615,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8634,34 +8634,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.8325709999999999</v>
+        <v>0.851433</v>
       </c>
       <c r="F95" t="n">
-        <v>724751497</v>
+        <v>741492801</v>
       </c>
       <c r="G95" t="n">
         <v>94</v>
       </c>
       <c r="H95" t="n">
-        <v>101637914</v>
+        <v>75433484</v>
       </c>
       <c r="I95" t="n">
-        <v>0.85581</v>
+        <v>0.884076</v>
       </c>
       <c r="J95" t="n">
-        <v>0.789766</v>
+        <v>0.821013</v>
       </c>
       <c r="K95" t="n">
-        <v>0.02921252</v>
+        <v>0.00793612</v>
       </c>
       <c r="L95" t="n">
-        <v>3.11922</v>
+        <v>0.9504899999999999</v>
       </c>
       <c r="M95" t="n">
-        <v>870774816.4093153</v>
+        <v>870824126.8087161</v>
       </c>
       <c r="N95" t="n">
-        <v>1209214727.55166</v>
+        <v>1209264224.764171</v>
       </c>
       <c r="O95" t="n">
         <v>19.92</v>
@@ -8670,13 +8670,13 @@
         <v>44952.26755787037</v>
       </c>
       <c r="Q95" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R95" t="b">
         <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>6.589110239147358e-05</v>
+        <v>6.637266485383536e-05</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8739,31 +8739,31 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.02631056</v>
+        <v>0.02629561</v>
       </c>
       <c r="F96" t="n">
-        <v>700639422</v>
+        <v>700826412</v>
       </c>
       <c r="G96" t="n">
         <v>95</v>
       </c>
       <c r="H96" t="n">
-        <v>9115526</v>
+        <v>7435307</v>
       </c>
       <c r="I96" t="n">
-        <v>0.02737397</v>
+        <v>0.02648915</v>
       </c>
       <c r="J96" t="n">
-        <v>0.02615656</v>
+        <v>0.0261506</v>
       </c>
       <c r="K96" t="n">
-        <v>-0.000168753897356013</v>
+        <v>-1.4782660178021e-05</v>
       </c>
       <c r="L96" t="n">
-        <v>-0.61511</v>
+        <v>-0.0921</v>
       </c>
       <c r="M96" t="n">
-        <v>26639136488</v>
+        <v>26667653978</v>
       </c>
       <c r="N96" t="n">
         <v>100000000000</v>
@@ -8775,13 +8775,13 @@
         <v>46156.97986111111</v>
       </c>
       <c r="Q96" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R96" t="b">
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>5.152626664681893e-05</v>
+        <v>4.225382875840334e-05</v>
       </c>
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
@@ -8795,7 +8795,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8814,28 +8814,28 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.998972</v>
+        <v>0.999358</v>
       </c>
       <c r="F97" t="n">
-        <v>698274572</v>
+        <v>698549235</v>
       </c>
       <c r="G97" t="n">
         <v>96</v>
       </c>
       <c r="H97" t="n">
-        <v>13503661</v>
+        <v>8380549</v>
       </c>
       <c r="I97" t="n">
-        <v>0.999205</v>
+        <v>0.999463</v>
       </c>
       <c r="J97" t="n">
-        <v>0.998501</v>
+        <v>0.998962</v>
       </c>
       <c r="K97" t="n">
-        <v>9.83e-05</v>
+        <v>0.00032863</v>
       </c>
       <c r="L97" t="n">
-        <v>0.01256</v>
+        <v>0.02713</v>
       </c>
       <c r="M97" t="n">
         <v>699000000</v>
@@ -8850,13 +8850,13 @@
         <v>45350.38608796296</v>
       </c>
       <c r="Q97" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R97" t="b">
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>5.011740068191353e-05</v>
+        <v>4.090325743466747e-05</v>
       </c>
       <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr"/>
@@ -8870,7 +8870,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8889,28 +8889,28 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.702283</v>
+        <v>0.722031</v>
       </c>
       <c r="F98" t="n">
-        <v>677749555</v>
+        <v>696754452</v>
       </c>
       <c r="G98" t="n">
         <v>97</v>
       </c>
       <c r="H98" t="n">
-        <v>40195319</v>
+        <v>48061733</v>
       </c>
       <c r="I98" t="n">
-        <v>0.720453</v>
+        <v>0.733568</v>
       </c>
       <c r="J98" t="n">
-        <v>0.662928</v>
+        <v>0.693392</v>
       </c>
       <c r="K98" t="n">
-        <v>0.03319348</v>
+        <v>0.01214067</v>
       </c>
       <c r="L98" t="n">
-        <v>5.01347</v>
+        <v>1.65693</v>
       </c>
       <c r="M98" t="n">
         <v>965350000</v>
@@ -8925,13 +8925,13 @@
         <v>45378.63525462963</v>
       </c>
       <c r="Q98" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R98" t="b">
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>3.788956471751625e-05</v>
+        <v>3.983878925668718e-05</v>
       </c>
       <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr"/>
@@ -8945,68 +8945,68 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>flare-networks</t>
+          <t>blockstack</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>flr</t>
+          <t>stx</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Flare</t>
+          <t>Stacks</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.00723579</v>
+        <v>0.34205</v>
       </c>
       <c r="F99" t="n">
-        <v>628745882</v>
+        <v>640435847</v>
       </c>
       <c r="G99" t="n">
         <v>98</v>
       </c>
       <c r="H99" t="n">
-        <v>5236400</v>
+        <v>45309726</v>
       </c>
       <c r="I99" t="n">
-        <v>0.00735749</v>
+        <v>0.354392</v>
       </c>
       <c r="J99" t="n">
-        <v>0.00701469</v>
+        <v>0.317674</v>
       </c>
       <c r="K99" t="n">
-        <v>9.613e-05</v>
+        <v>0.0143636</v>
       </c>
       <c r="L99" t="n">
-        <v>1.34649</v>
+        <v>4.63936</v>
       </c>
       <c r="M99" t="n">
-        <v>86909124669.39235</v>
+        <v>1869484493.906829</v>
       </c>
       <c r="N99" t="n">
-        <v>106621854713.5677</v>
+        <v>1869484493.906829</v>
       </c>
       <c r="O99" t="n">
-        <v>0.150073</v>
+        <v>3.86</v>
       </c>
       <c r="P99" s="1" t="n">
-        <v>44935.80144675926</v>
+        <v>45383.19094907407</v>
       </c>
       <c r="Q99" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R99" t="b">
         <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>8.695490232853771e-06</v>
+        <v>6.436777508892736e-06</v>
       </c>
       <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr"/>
@@ -9020,68 +9020,68 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>beldex</t>
+          <t>pudgy-penguins</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>bdx</t>
+          <t>pengu</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Beldex</t>
+          <t>Pudgy Penguins</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.078194</v>
+        <v>0.01004023</v>
       </c>
       <c r="F100" t="n">
-        <v>615482724</v>
+        <v>631292348</v>
       </c>
       <c r="G100" t="n">
         <v>99</v>
       </c>
       <c r="H100" t="n">
-        <v>2909104</v>
+        <v>231573455</v>
       </c>
       <c r="I100" t="n">
-        <v>0.078414</v>
+        <v>0.01045105</v>
       </c>
       <c r="J100" t="n">
-        <v>0.076556</v>
+        <v>0.009655270000000001</v>
       </c>
       <c r="K100" t="n">
-        <v>0.0017067</v>
+        <v>8.313999999999999e-05</v>
       </c>
       <c r="L100" t="n">
-        <v>2.23001</v>
+        <v>0.90963</v>
       </c>
       <c r="M100" t="n">
-        <v>7870839322.119331</v>
+        <v>62860396090</v>
       </c>
       <c r="N100" t="n">
-        <v>9939718245.379999</v>
+        <v>76722802826.57365</v>
       </c>
       <c r="O100" t="n">
-        <v>0.450785</v>
+        <v>0.06844699999999999</v>
       </c>
       <c r="P100" s="1" t="n">
-        <v>43450.66666666666</v>
+        <v>45643.21206018519</v>
       </c>
       <c r="Q100" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R100" t="b">
         <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>7.939269652626453e-07</v>
+        <v>1.013858013391262e-06</v>
       </c>
       <c r="T100" t="inlineStr"/>
       <c r="U100" t="inlineStr"/>
@@ -9095,62 +9095,62 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>pudgy-penguins</t>
+          <t>flare-networks</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>pengu</t>
+          <t>flr</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Pudgy Penguins</t>
+          <t>Flare</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.00976846</v>
+        <v>0.00724299</v>
       </c>
       <c r="F101" t="n">
-        <v>614150079</v>
+        <v>629582898</v>
       </c>
       <c r="G101" t="n">
         <v>100</v>
       </c>
       <c r="H101" t="n">
-        <v>295384177</v>
+        <v>3598829</v>
       </c>
       <c r="I101" t="n">
-        <v>0.01012583</v>
+        <v>0.00736006</v>
       </c>
       <c r="J101" t="n">
-        <v>0.009481379999999999</v>
+        <v>0.00721363</v>
       </c>
       <c r="K101" t="n">
-        <v>-0.000222560486343474</v>
+        <v>-6.687276971504101e-05</v>
       </c>
       <c r="L101" t="n">
-        <v>-2.2942</v>
+        <v>-0.91779</v>
       </c>
       <c r="M101" t="n">
-        <v>62860396090</v>
+        <v>86930131704.80014</v>
       </c>
       <c r="N101" t="n">
-        <v>76722804262.29102</v>
+        <v>106628765964.3372</v>
       </c>
       <c r="O101" t="n">
-        <v>0.06844699999999999</v>
+        <v>0.150073</v>
       </c>
       <c r="P101" s="1" t="n">
-        <v>45643.21206018519</v>
+        <v>44935.80144675926</v>
       </c>
       <c r="Q101" s="1" t="n">
-        <v>46290.59189814814</v>
+        <v>46291.55798611111</v>
       </c>
       <c r="R101" t="b">
         <v>0</v>

--- a/src/xlsx/enriched_data.xlsx
+++ b/src/xlsx/enriched_data.xlsx
@@ -560,7 +560,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -579,34 +579,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>83960</v>
+        <v>84945</v>
       </c>
       <c r="F2" t="n">
-        <v>1686713805167</v>
+        <v>1706532619602</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>25094148124</v>
+        <v>21184097131</v>
       </c>
       <c r="I2" t="n">
-        <v>84296</v>
+        <v>85089</v>
       </c>
       <c r="J2" t="n">
-        <v>83230</v>
+        <v>83835</v>
       </c>
       <c r="K2" t="n">
-        <v>-256.859398715038</v>
+        <v>994.61</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.32156</v>
+        <v>1.14458</v>
       </c>
       <c r="M2" t="n">
-        <v>20089568</v>
+        <v>20089965</v>
       </c>
       <c r="N2" t="n">
-        <v>20089609</v>
+        <v>20090134</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -615,7 +615,7 @@
         <v>45936.45673611111</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
@@ -665,7 +665,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -684,34 +684,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2685.41</v>
+        <v>2704.75</v>
       </c>
       <c r="F3" t="n">
-        <v>327852902474</v>
+        <v>330207990871</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>9448881653</v>
+        <v>7613539121</v>
       </c>
       <c r="I3" t="n">
-        <v>2697.72</v>
+        <v>2720.75</v>
       </c>
       <c r="J3" t="n">
-        <v>2669.73</v>
+        <v>2666.72</v>
       </c>
       <c r="K3" t="n">
-        <v>-20.30064927189733</v>
+        <v>17.76</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.78586</v>
+        <v>0.58869</v>
       </c>
       <c r="M3" t="n">
-        <v>122081755.2385784</v>
+        <v>122084677.7313143</v>
       </c>
       <c r="N3" t="n">
-        <v>122081755.2385784</v>
+        <v>122084677.7313143</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -720,13 +720,13 @@
         <v>45893.47295138889</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1940729385010486</v>
+        <v>0.1931924377023068</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -789,31 +789,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999844</v>
+        <v>0.999839</v>
       </c>
       <c r="F4" t="n">
-        <v>183789394509</v>
+        <v>183789253110</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>49145434159</v>
+        <v>41514989094</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999887</v>
+        <v>0.999873</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999719</v>
+        <v>0.999715</v>
       </c>
       <c r="K4" t="n">
-        <v>8.093e-05</v>
+        <v>1.089e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00231</v>
+        <v>-0.001</v>
       </c>
       <c r="M4" t="n">
-        <v>183818815971.0418</v>
+        <v>183818815967.1891</v>
       </c>
       <c r="N4" t="n">
         <v>189285761986.9062</v>
@@ -825,13 +825,13 @@
         <v>43304.66666666666</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1086302861932471</v>
+        <v>0.1073611284155017</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -894,34 +894,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>772.3099999999999</v>
+        <v>779.8099999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>102840641561</v>
+        <v>103839803578</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>743839388</v>
+        <v>709749417</v>
       </c>
       <c r="I5" t="n">
-        <v>777.74</v>
+        <v>782.71</v>
       </c>
       <c r="J5" t="n">
-        <v>769.51</v>
+        <v>766.86</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.343418307023285</v>
+        <v>7.32</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.44597</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>133159792.88</v>
+        <v>133159695.65</v>
       </c>
       <c r="N5" t="n">
-        <v>133159791.14</v>
+        <v>133159692.37</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -930,13 +930,13 @@
         <v>45943.02875</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06062037549076425</v>
+        <v>0.06049440879323557</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -999,28 +999,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="F6" t="n">
-        <v>96751811786</v>
+        <v>96195766748</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>3887008543</v>
+        <v>2780906745</v>
       </c>
       <c r="I6" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="J6" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.05239949727053506</v>
+        <v>-0.01407680591755334</v>
       </c>
       <c r="L6" t="n">
-        <v>-3.32178</v>
+        <v>-1.07668</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -1035,13 +1035,13 @@
         <v>45855.82005787037</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R6" t="b">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05700915032503313</v>
+        <v>0.05601344071914651</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1104,34 +1104,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9998899999999999</v>
+        <v>0.99999</v>
       </c>
       <c r="F7" t="n">
-        <v>75325511675</v>
+        <v>75195810814</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>13529945029</v>
+        <v>9492352280</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999804</v>
+        <v>0.999451</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.190448686907e-06</v>
+        <v>0.00010164</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.00778</v>
+        <v>0.0074</v>
       </c>
       <c r="M7" t="n">
-        <v>75333929675.06418</v>
+        <v>75196575861.07713</v>
       </c>
       <c r="N7" t="n">
-        <v>75334626227.45894</v>
+        <v>75209861269.7758</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -1140,13 +1140,13 @@
         <v>43418.66666666666</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04430142207041121</v>
+        <v>0.04370317401187176</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1209,34 +1209,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>120.65</v>
+        <v>122.88</v>
       </c>
       <c r="F8" t="n">
-        <v>70914599486</v>
+        <v>72226558654</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>4716262120</v>
+        <v>3632253379</v>
       </c>
       <c r="I8" t="n">
-        <v>122.75</v>
+        <v>124.77</v>
       </c>
       <c r="J8" t="n">
-        <v>118.59</v>
+        <v>120.11</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7919079999999999</v>
+        <v>1.94</v>
       </c>
       <c r="L8" t="n">
-        <v>0.60627</v>
+        <v>1.39633</v>
       </c>
       <c r="M8" t="n">
-        <v>587712762.0220828</v>
+        <v>587783255.1105938</v>
       </c>
       <c r="N8" t="n">
-        <v>634763960.9711117</v>
+        <v>634841718.6764878</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -1245,13 +1245,13 @@
         <v>45676.13572916666</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R8" t="b">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.04168535335288052</v>
+        <v>0.04196258531132255</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1314,34 +1314,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.336607</v>
+        <v>0.333493</v>
       </c>
       <c r="F9" t="n">
-        <v>31961192093</v>
+        <v>31670810269</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>267042689</v>
+        <v>346156219</v>
       </c>
       <c r="I9" t="n">
-        <v>0.338229</v>
+        <v>0.336714</v>
       </c>
       <c r="J9" t="n">
-        <v>0.33599</v>
+        <v>0.33245</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.000351358735391327</v>
+        <v>-0.002821045035316549</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.13818</v>
+        <v>-0.84712</v>
       </c>
       <c r="M9" t="n">
         <v>94967057481.15408</v>
       </c>
       <c r="N9" t="n">
-        <v>94968826620.64949</v>
+        <v>94971253492.20189</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1350,13 +1350,13 @@
         <v>45629.67407407407</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01858246983228179</v>
+        <v>0.01818862689438308</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1419,34 +1419,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1539.58</v>
+        <v>1643.08</v>
       </c>
       <c r="F10" t="n">
-        <v>26102989564</v>
+        <v>27858352423</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>778167418</v>
+        <v>1413804468</v>
       </c>
       <c r="I10" t="n">
-        <v>1596.86</v>
+        <v>1687.78</v>
       </c>
       <c r="J10" t="n">
-        <v>1517.49</v>
+        <v>1546.39</v>
       </c>
       <c r="K10" t="n">
-        <v>-76.6470678720184</v>
+        <v>101.84</v>
       </c>
       <c r="L10" t="n">
-        <v>-4.78454</v>
+        <v>6.20596</v>
       </c>
       <c r="M10" t="n">
-        <v>16952175.1655448</v>
+        <v>16954918.9155448</v>
       </c>
       <c r="N10" t="n">
-        <v>16953504.8530448</v>
+        <v>16955384.5405448</v>
       </c>
       <c r="O10" t="n">
         <v>3191.93</v>
@@ -1455,13 +1455,13 @@
         <v>42671.66666666666</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01510802742209395</v>
+        <v>0.01595374730501611</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1524,49 +1524,49 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.026</v>
+        <v>1.058</v>
       </c>
       <c r="F11" t="n">
-        <v>23747335901</v>
+        <v>24516003984</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>22346272</v>
+        <v>401487</v>
       </c>
       <c r="I11" t="n">
-        <v>1.032</v>
+        <v>1.062</v>
       </c>
       <c r="J11" t="n">
-        <v>1.023</v>
+        <v>1.016</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.001108940741380682</v>
+        <v>0.0316886</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.10223</v>
+        <v>3.09073</v>
       </c>
       <c r="M11" t="n">
-        <v>23149018497.978</v>
+        <v>23181959779.848</v>
       </c>
       <c r="N11" t="n">
-        <v>23149018497.978</v>
+        <v>23193525454.108</v>
       </c>
       <c r="O11" t="n">
-        <v>1.061</v>
+        <v>1.062</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>46237.59675925926</v>
+        <v>46292.546875</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.54976851852</v>
       </c>
       <c r="R11" t="b">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01371091235993534</v>
+        <v>0.01399444792162468</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
@@ -1580,7 +1580,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1599,28 +1599,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>91.83</v>
+        <v>92.06999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>20428508325</v>
+        <v>20480194044</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>693710930</v>
+        <v>607402270</v>
       </c>
       <c r="I12" t="n">
-        <v>92.81999999999999</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>90.41</v>
+        <v>91.06</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.224155095273204</v>
+        <v>-0.1449201937953575</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3402</v>
+        <v>-0.28565</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1635,13 +1635,13 @@
         <v>46288.22002314815</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R12" t="b">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01174254830541985</v>
+        <v>0.01162863835052777</v>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
@@ -1655,7 +1655,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1674,34 +1674,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.097069</v>
+        <v>0.09762</v>
       </c>
       <c r="F13" t="n">
-        <v>15151071047</v>
+        <v>15237393273</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>996069177</v>
+        <v>773469735</v>
       </c>
       <c r="I13" t="n">
-        <v>0.099703</v>
+        <v>0.098832</v>
       </c>
       <c r="J13" t="n">
-        <v>0.09641</v>
+        <v>0.095327</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.000756068771230411</v>
+        <v>0.00030094</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.76364</v>
+        <v>0.11394</v>
       </c>
       <c r="M13" t="n">
-        <v>156075366383.7053</v>
+        <v>156089086383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171787443126.579</v>
+        <v>171801603126.579</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1710,13 +1710,13 @@
         <v>44323.88082175926</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R13" t="b">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.008612552064248677</v>
+        <v>0.008555285435552284</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1779,28 +1779,28 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>14.22</v>
+        <v>14.11</v>
       </c>
       <c r="F14" t="n">
-        <v>10640884885</v>
+        <v>10552392004</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>707084096</v>
+        <v>450403576</v>
       </c>
       <c r="I14" t="n">
-        <v>14.35</v>
+        <v>14.47</v>
       </c>
       <c r="J14" t="n">
-        <v>13.69</v>
+        <v>13.91</v>
       </c>
       <c r="K14" t="n">
-        <v>0.198978</v>
+        <v>-0.2941581756086027</v>
       </c>
       <c r="L14" t="n">
-        <v>1.36679</v>
+        <v>-2.07594</v>
       </c>
       <c r="M14" t="n">
         <v>748099970.424884</v>
@@ -1815,13 +1815,13 @@
         <v>44325.67635416667</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R14" t="b">
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.00593760492790068</v>
+        <v>0.005808917046657994</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1884,34 +1884,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>549.3</v>
+        <v>547.5599999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>10336344317</v>
+        <v>10299613386</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>92067811</v>
+        <v>98485371</v>
       </c>
       <c r="I15" t="n">
-        <v>561.22</v>
+        <v>562.88</v>
       </c>
       <c r="J15" t="n">
-        <v>546.01</v>
+        <v>546.5</v>
       </c>
       <c r="K15" t="n">
-        <v>-7.378489186112347</v>
+        <v>-2.077478602360884</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.39045</v>
+        <v>-0.5147</v>
       </c>
       <c r="M15" t="n">
-        <v>18809710.28932691</v>
+        <v>18810142.88639648</v>
       </c>
       <c r="N15" t="n">
-        <v>18809742.0893211</v>
+        <v>18810186.68579455</v>
       </c>
       <c r="O15" t="n">
         <v>797.73</v>
@@ -1920,13 +1920,13 @@
         <v>46036.48202546296</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.005756984906683606</v>
+        <v>0.005660737106887825</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1989,28 +1989,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>83.8</v>
+        <v>84.7</v>
       </c>
       <c r="F16" t="n">
-        <v>9959623112</v>
+        <v>10066394234</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>77723889</v>
+        <v>38669946</v>
       </c>
       <c r="I16" t="n">
-        <v>84.13</v>
+        <v>84.88</v>
       </c>
       <c r="J16" t="n">
-        <v>83.17</v>
+        <v>83.59</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.346154198101928</v>
+        <v>0.922706</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.44687</v>
+        <v>1.03738</v>
       </c>
       <c r="M16" t="n">
         <v>118852171</v>
@@ -2025,13 +2025,13 @@
         <v>46286.85358796296</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R16" t="b">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.005533555258256532</v>
+        <v>0.005524023012277932</v>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
@@ -2045,7 +2045,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2064,34 +2064,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.999721</v>
+        <v>0.999722</v>
       </c>
       <c r="F17" t="n">
-        <v>9746623829</v>
+        <v>9770898995</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>172309969</v>
+        <v>50701799</v>
       </c>
       <c r="I17" t="n">
-        <v>0.999868</v>
+        <v>0.999846</v>
       </c>
       <c r="J17" t="n">
-        <v>0.999566</v>
+        <v>0.999595</v>
       </c>
       <c r="K17" t="n">
-        <v>5.916e-05</v>
+        <v>1.442e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>4e-05</v>
+        <v>-0.00079</v>
       </c>
       <c r="M17" t="n">
-        <v>9748883836.049854</v>
+        <v>9773614544.067293</v>
       </c>
       <c r="N17" t="n">
-        <v>9749012892.848028</v>
+        <v>9773387427.242182</v>
       </c>
       <c r="O17" t="n">
         <v>1.057</v>
@@ -2100,13 +2100,13 @@
         <v>45593.90336805556</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.005407227474515479</v>
+        <v>0.005350802401041773</v>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
@@ -2120,7 +2120,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2139,31 +2139,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.254453</v>
+        <v>0.255618</v>
       </c>
       <c r="F18" t="n">
-        <v>9549016320</v>
+        <v>9594683963</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>640158278</v>
+        <v>441302587</v>
       </c>
       <c r="I18" t="n">
-        <v>0.26468</v>
+        <v>0.260642</v>
       </c>
       <c r="J18" t="n">
-        <v>0.251137</v>
+        <v>0.248192</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.00139232354027119</v>
+        <v>-2.0971475922005e-05</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.55041</v>
+        <v>-0.18042</v>
       </c>
       <c r="M18" t="n">
-        <v>37529061988.53558</v>
+        <v>37535193928.91081</v>
       </c>
       <c r="N18" t="n">
         <v>45000000000</v>
@@ -2175,13 +2175,13 @@
         <v>44440.91678240741</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R18" t="b">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.005290028400833337</v>
+        <v>0.005247504372771207</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.0123665</v>
+        <v>0.01263123</v>
       </c>
       <c r="F19" t="n">
-        <v>8770640199</v>
+        <v>8958633558</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>21274799</v>
+        <v>16784296</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01245443</v>
+        <v>0.01335759</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01041574</v>
+        <v>0.0125299</v>
       </c>
       <c r="K19" t="n">
-        <v>0.00048121</v>
+        <v>-6.0112472093053e-05</v>
       </c>
       <c r="L19" t="n">
-        <v>4.06067</v>
+        <v>-0.66867</v>
       </c>
       <c r="M19" t="n">
-        <v>709240980011.2261</v>
+        <v>709244646514.1578</v>
       </c>
       <c r="N19" t="n">
         <v>1142408526965.963</v>
@@ -2280,13 +2280,13 @@
         <v>46259.82847222222</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R19" t="b">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.004828381164758426</v>
+        <v>0.004874648822529645</v>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
@@ -2300,7 +2300,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2319,28 +2319,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8.960000000000001</v>
+        <v>9.02</v>
       </c>
       <c r="F20" t="n">
-        <v>8240992585</v>
+        <v>8297568479</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>256366</v>
+        <v>457739</v>
       </c>
       <c r="I20" t="n">
-        <v>8.99</v>
+        <v>9.09</v>
       </c>
       <c r="J20" t="n">
-        <v>8.789999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.123426</v>
+        <v>0.060879</v>
       </c>
       <c r="L20" t="n">
-        <v>1.39349</v>
+        <v>0.67213</v>
       </c>
       <c r="M20" t="n">
         <v>919857851.9</v>
@@ -2355,13 +2355,13 @@
         <v>46146.39930555555</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.004514252364426471</v>
+        <v>0.004487129560159194</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2424,31 +2424,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.217446</v>
+        <v>0.216352</v>
       </c>
       <c r="F21" t="n">
-        <v>7604775177</v>
+        <v>7565866358</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>309237779</v>
+        <v>183063798</v>
       </c>
       <c r="I21" t="n">
-        <v>0.222301</v>
+        <v>0.22079</v>
       </c>
       <c r="J21" t="n">
-        <v>0.214962</v>
+        <v>0.213075</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.004574860917676671</v>
+        <v>-0.001367816087023216</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.08151</v>
+        <v>-0.78912</v>
       </c>
       <c r="M21" t="n">
-        <v>34970186880.78098</v>
+        <v>34970178928.73618</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70047</v>
@@ -2460,13 +2460,13 @@
         <v>43102.66666666666</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R21" t="b">
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.004136918065464922</v>
+        <v>0.004058202552497949</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2510,217 +2510,217 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>bitcoin-cash</t>
+          <t>near</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>bch</t>
+          <t>near</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Bitcoin Cash</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>334.23</v>
+        <v>5.22</v>
       </c>
       <c r="F22" t="n">
-        <v>6716090248</v>
+        <v>6827716511</v>
       </c>
       <c r="G22" t="n">
         <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>269285553</v>
+        <v>1198271957</v>
       </c>
       <c r="I22" t="n">
-        <v>346.7</v>
+        <v>5.48</v>
       </c>
       <c r="J22" t="n">
-        <v>328.62</v>
+        <v>4.75</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.183653193960083</v>
+        <v>0.40177</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6936099999999999</v>
+        <v>8.261290000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>20094721.77165077</v>
+        <v>1307451804</v>
       </c>
       <c r="N22" t="n">
-        <v>20094740.52165077</v>
+        <v>1307451811</v>
       </c>
       <c r="O22" t="n">
-        <v>3785.82</v>
+        <v>20.44</v>
       </c>
       <c r="P22" s="1" t="n">
-        <v>43088.66666666666</v>
+        <v>44577.59010416667</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0.003609847758262784</v>
+        <v>0.003625495859442845</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Plataforma de contratos inteligentes</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Fork de Bitcoin</t>
+          <t>Layer 1</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Proof of Work</t>
+          <t>Proof of Stake (sharding)</t>
         </is>
       </c>
       <c r="W22" t="n">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>bitcoincash.org</t>
+          <t>near.org</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>Pagos cotidianos de bajo costo</t>
+          <t>dApps escalables mediante sharding</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>Blockchain propia (fork de Bitcoin)</t>
+          <t>Blockchain propia (Layer 1)</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Surgió de una bifurcación de Bitcoin en 2017 para aumentar el tamaño de bloque.</t>
+          <t>Usa sharding para escalar el procesamiento de transacciones.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>bitcoin-cash</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>bch</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NEAR Protocol</t>
+          <t>Bitcoin Cash</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4.81</v>
+        <v>335.51</v>
       </c>
       <c r="F23" t="n">
-        <v>6296456192</v>
+        <v>6742198101</v>
       </c>
       <c r="G23" t="n">
         <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>1146375776</v>
+        <v>247963129</v>
       </c>
       <c r="I23" t="n">
-        <v>5.19</v>
+        <v>346.97</v>
       </c>
       <c r="J23" t="n">
-        <v>4.8</v>
+        <v>330.66</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.2873737443377689</v>
+        <v>2.58</v>
       </c>
       <c r="L23" t="n">
-        <v>-5.73872</v>
+        <v>0.58889</v>
       </c>
       <c r="M23" t="n">
-        <v>1307347222</v>
+        <v>20095159.27165077</v>
       </c>
       <c r="N23" t="n">
-        <v>1307347213</v>
+        <v>20095440.52165077</v>
       </c>
       <c r="O23" t="n">
-        <v>20.44</v>
+        <v>3785.82</v>
       </c>
       <c r="P23" s="1" t="n">
-        <v>44577.59010416667</v>
+        <v>43088.66666666666</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.003360966919181514</v>
+        <v>0.003575364590653961</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>Plataforma de contratos inteligentes</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>Layer 1</t>
+          <t>Fork de Bitcoin</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Proof of Stake (sharding)</t>
+          <t>Proof of Work</t>
         </is>
       </c>
       <c r="W23" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>near.org</t>
+          <t>bitcoincash.org</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>dApps escalables mediante sharding</t>
+          <t>Pagos cotidianos de bajo costo</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>Blockchain propia (Layer 1)</t>
+          <t>Blockchain propia (fork de Bitcoin)</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Usa sharding para escalar el procesamiento de transacciones.</t>
+          <t>Surgió de una bifurcación de Bitcoin en 2017 para aumentar el tamaño de bloque.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2739,34 +2739,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>9.58</v>
+        <v>9.84</v>
       </c>
       <c r="F24" t="n">
-        <v>5946668939</v>
+        <v>6104724987</v>
       </c>
       <c r="G24" t="n">
         <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>800674531</v>
+        <v>660893823</v>
       </c>
       <c r="I24" t="n">
-        <v>9.82</v>
+        <v>10.18</v>
       </c>
       <c r="J24" t="n">
-        <v>9.41</v>
+        <v>9.42</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.1653949180304011</v>
+        <v>0.238426</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.72443</v>
+        <v>2.18965</v>
       </c>
       <c r="M24" t="n">
-        <v>620534422.6104751</v>
+        <v>620466422.6104751</v>
       </c>
       <c r="N24" t="n">
-        <v>887782418.9163101</v>
+        <v>887714418.9163101</v>
       </c>
       <c r="O24" t="n">
         <v>44.92</v>
@@ -2775,13 +2775,13 @@
         <v>44318.89240740741</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R24" t="b">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.003153511533276008</v>
+        <v>0.003201675042127265</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2844,34 +2844,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>72.2</v>
+        <v>71.11</v>
       </c>
       <c r="F25" t="n">
-        <v>5609463118</v>
+        <v>5521697779</v>
       </c>
       <c r="G25" t="n">
         <v>24</v>
       </c>
       <c r="H25" t="n">
-        <v>715362160</v>
+        <v>382049880</v>
       </c>
       <c r="I25" t="n">
-        <v>74.94</v>
+        <v>73.34</v>
       </c>
       <c r="J25" t="n">
-        <v>69.12</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>2.02</v>
+        <v>-1.248465999589328</v>
       </c>
       <c r="L25" t="n">
-        <v>2.92147</v>
+        <v>-1.8904</v>
       </c>
       <c r="M25" t="n">
-        <v>77649504.50722787</v>
+        <v>77653329.51737037</v>
       </c>
       <c r="N25" t="n">
-        <v>77652329.51466258</v>
+        <v>77656204.52533114</v>
       </c>
       <c r="O25" t="n">
         <v>410.26</v>
@@ -2880,13 +2880,13 @@
         <v>44325.80077546297</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.00295351807117824</v>
+        <v>0.002859901923620027</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2949,34 +2949,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.138686</v>
+        <v>0.134479</v>
       </c>
       <c r="F26" t="n">
-        <v>5501910688</v>
+        <v>5338537105</v>
       </c>
       <c r="G26" t="n">
         <v>25</v>
       </c>
       <c r="H26" t="n">
-        <v>49591999</v>
+        <v>25873598</v>
       </c>
       <c r="I26" t="n">
-        <v>0.139192</v>
+        <v>0.140118</v>
       </c>
       <c r="J26" t="n">
-        <v>0.121498</v>
+        <v>0.132386</v>
       </c>
       <c r="K26" t="n">
-        <v>0.01639462</v>
+        <v>-0.003221599252645951</v>
       </c>
       <c r="L26" t="n">
-        <v>13.26358</v>
+        <v>-2.49593</v>
       </c>
       <c r="M26" t="n">
-        <v>39689579709.8557</v>
+        <v>39697885231.8137</v>
       </c>
       <c r="N26" t="n">
-        <v>39690487676.93661</v>
+        <v>39697885231.8137</v>
       </c>
       <c r="O26" t="n">
         <v>0.194152</v>
@@ -2985,13 +2985,13 @@
         <v>46056.00148148148</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.00288972978078355</v>
+        <v>0.002752532329402278</v>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
@@ -3005,68 +3005,68 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ethena-usde</t>
+          <t>sui</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>usde</t>
+          <t>sui</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Ethena USDe</t>
+          <t>Sui</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.999536</v>
+        <v>1.25</v>
       </c>
       <c r="F27" t="n">
-        <v>4935885909</v>
+        <v>5105248088</v>
       </c>
       <c r="G27" t="n">
         <v>26</v>
       </c>
       <c r="H27" t="n">
-        <v>76175068</v>
+        <v>1048651897</v>
       </c>
       <c r="I27" t="n">
-        <v>0.999904</v>
+        <v>1.29</v>
       </c>
       <c r="J27" t="n">
-        <v>0.99938</v>
+        <v>1.13</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.00022803499806956</v>
+        <v>0.06920900000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.03194</v>
+        <v>5.55749</v>
       </c>
       <c r="M27" t="n">
-        <v>4938195973.919382</v>
+        <v>4096537146.540959</v>
       </c>
       <c r="N27" t="n">
-        <v>4938195973.919382</v>
+        <v>10000000000</v>
       </c>
       <c r="O27" t="n">
-        <v>1.034</v>
+        <v>5.35</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>46000.38208333333</v>
+        <v>45661.62243055556</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R27" t="b">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.002554026041003406</v>
+        <v>0.002615777279621517</v>
       </c>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
@@ -3080,187 +3080,187 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>avalanche-2</t>
+          <t>ethena-usde</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>avax</t>
+          <t>usde</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Ethena USDe</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>10.75</v>
+        <v>0.999802</v>
       </c>
       <c r="F28" t="n">
-        <v>4761827953</v>
+        <v>4944958342</v>
       </c>
       <c r="G28" t="n">
         <v>27</v>
       </c>
       <c r="H28" t="n">
-        <v>559088789</v>
+        <v>20888227</v>
       </c>
       <c r="I28" t="n">
-        <v>10.98</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>10.21</v>
+        <v>0.999522</v>
       </c>
       <c r="K28" t="n">
-        <v>0.258827</v>
+        <v>0.00028489</v>
       </c>
       <c r="L28" t="n">
-        <v>2.41792</v>
+        <v>0.02869</v>
       </c>
       <c r="M28" t="n">
-        <v>443072344.6634147</v>
+        <v>4945939106.979231</v>
       </c>
       <c r="N28" t="n">
-        <v>469741151.0943739</v>
+        <v>4950082292.661032</v>
       </c>
       <c r="O28" t="n">
-        <v>144.96</v>
+        <v>1.034</v>
       </c>
       <c r="P28" s="1" t="n">
-        <v>44521.26314814815</v>
+        <v>46000.38208333333</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R28" t="b">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.002450793976020456</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Plataforma de contratos inteligentes</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Layer 1</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Proof of Stake (Avalanche consensus)</t>
-        </is>
-      </c>
-      <c r="W28" t="n">
-        <v>2020</v>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>avax.network</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>Subredes personalizadas para empresas</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Layer 1)</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>Permite crear subredes (subnets) personalizadas para casos de uso específicos.</t>
-        </is>
-      </c>
+        <v>0.002521814724180789</v>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>sui</t>
+          <t>avalanche-2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>sui</t>
+          <t>avax</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sui</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1.16</v>
+        <v>10.98</v>
       </c>
       <c r="F29" t="n">
-        <v>4753799821</v>
+        <v>4864646128</v>
       </c>
       <c r="G29" t="n">
         <v>28</v>
       </c>
       <c r="H29" t="n">
-        <v>1339722489</v>
+        <v>590874472</v>
       </c>
       <c r="I29" t="n">
-        <v>1.21</v>
+        <v>11.26</v>
       </c>
       <c r="J29" t="n">
-        <v>1.092</v>
+        <v>10.55</v>
       </c>
       <c r="K29" t="n">
-        <v>0.02996564</v>
+        <v>0.119876</v>
       </c>
       <c r="L29" t="n">
-        <v>2.58125</v>
+        <v>0.93719</v>
       </c>
       <c r="M29" t="n">
-        <v>4096537146.540959</v>
+        <v>443075362.6635053</v>
       </c>
       <c r="N29" t="n">
-        <v>10000000000</v>
+        <v>469744144.6508019</v>
       </c>
       <c r="O29" t="n">
-        <v>5.35</v>
+        <v>144.96</v>
       </c>
       <c r="P29" s="1" t="n">
-        <v>45661.62243055556</v>
+        <v>44521.26314814815</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R29" t="b">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.002446032569743137</v>
-      </c>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
+        <v>0.002474735350428817</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Plataforma de contratos inteligentes</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Layer 1</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Proof of Stake (Avalanche consensus)</t>
+        </is>
+      </c>
+      <c r="W29" t="n">
+        <v>2020</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>avax.network</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Subredes personalizadas para empresas</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Layer 1)</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>Permite crear subredes (subnets) personalizadas para casos de uso específicos.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3279,34 +3279,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.999823</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>4589357607</v>
+        <v>4599126620</v>
       </c>
       <c r="G30" t="n">
         <v>29</v>
       </c>
       <c r="H30" t="n">
-        <v>140221645</v>
+        <v>109783985</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>0.999596</v>
+        <v>0.999735</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.0855752196347e-05</v>
+        <v>2.744e-05</v>
       </c>
       <c r="L30" t="n">
-        <v>0.01123</v>
+        <v>-0.00236</v>
       </c>
       <c r="M30" t="n">
-        <v>4589747532.385433</v>
+        <v>4599037814.56804</v>
       </c>
       <c r="N30" t="n">
-        <v>4591667218.493917</v>
+        <v>4600951017.574961</v>
       </c>
       <c r="O30" t="n">
         <v>1.22</v>
@@ -3315,13 +3315,13 @@
         <v>43902.79363425926</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R30" t="b">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.002348503506942996</v>
+        <v>0.002319086644796425</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3365,68 +3365,68 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>usd1-wlfi</t>
+          <t>the-open-network</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>usd1</t>
+          <t>gram</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>USD1</t>
+          <t>Gram (prev. Toncoin)</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.99944</v>
+        <v>1.59</v>
       </c>
       <c r="F31" t="n">
-        <v>4416045793</v>
+        <v>4483348301</v>
       </c>
       <c r="G31" t="n">
         <v>30</v>
       </c>
       <c r="H31" t="n">
-        <v>719181505</v>
+        <v>165132672</v>
       </c>
       <c r="I31" t="n">
-        <v>0.999638</v>
+        <v>1.65</v>
       </c>
       <c r="J31" t="n">
-        <v>0.999288</v>
+        <v>1.47</v>
       </c>
       <c r="K31" t="n">
-        <v>5.47e-05</v>
+        <v>0.119041</v>
       </c>
       <c r="L31" t="n">
-        <v>-6e-05</v>
+        <v>7.84259</v>
       </c>
       <c r="M31" t="n">
-        <v>4418506659.422955</v>
+        <v>2814574919.172927</v>
       </c>
       <c r="N31" t="n">
-        <v>4418506659.422955</v>
+        <v>5256420917.725853</v>
       </c>
       <c r="O31" t="n">
-        <v>1.048</v>
+        <v>8.25</v>
       </c>
       <c r="P31" s="1" t="n">
-        <v>46212.42696759259</v>
+        <v>45457.69225694444</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>0.002245713971455397</v>
+        <v>0.00225121688400791</v>
       </c>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
@@ -3440,68 +3440,68 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>the-open-network</t>
+          <t>usd1-wlfi</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>gram</t>
+          <t>usd1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Gram (prev. Toncoin)</t>
+          <t>USD1</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1.47</v>
+        <v>0.999517</v>
       </c>
       <c r="F32" t="n">
-        <v>4135698799</v>
+        <v>4416372376</v>
       </c>
       <c r="G32" t="n">
         <v>31</v>
       </c>
       <c r="H32" t="n">
-        <v>53047848</v>
+        <v>580406931</v>
       </c>
       <c r="I32" t="n">
-        <v>1.47</v>
+        <v>0.999779</v>
       </c>
       <c r="J32" t="n">
-        <v>1.41</v>
+        <v>0.999336</v>
       </c>
       <c r="K32" t="n">
-        <v>0.04290891</v>
+        <v>-2.4808525936781e-05</v>
       </c>
       <c r="L32" t="n">
-        <v>3.02347</v>
+        <v>-0.00141</v>
       </c>
       <c r="M32" t="n">
-        <v>2813828939.846996</v>
+        <v>4418506659.421694</v>
       </c>
       <c r="N32" t="n">
-        <v>5255812914.165484</v>
+        <v>4418506659.421694</v>
       </c>
       <c r="O32" t="n">
-        <v>8.25</v>
+        <v>1.048</v>
       </c>
       <c r="P32" s="1" t="n">
-        <v>45457.69225694444</v>
+        <v>46212.42696759259</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R32" t="b">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.002079442921470283</v>
+        <v>0.002211955301635656</v>
       </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
@@ -3515,7 +3515,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3534,31 +3534,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.093301</v>
+        <v>0.093954</v>
       </c>
       <c r="F33" t="n">
-        <v>4090022875</v>
+        <v>4118142843</v>
       </c>
       <c r="G33" t="n">
         <v>32</v>
       </c>
       <c r="H33" t="n">
-        <v>109322812</v>
+        <v>94801236</v>
       </c>
       <c r="I33" t="n">
-        <v>0.09580900000000001</v>
+        <v>0.09583800000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>0.092637</v>
+        <v>0.091875</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.00144075792829608</v>
+        <v>0.00052865</v>
       </c>
       <c r="L33" t="n">
-        <v>-1.52119</v>
+        <v>0.41416</v>
       </c>
       <c r="M33" t="n">
-        <v>43831706398.51672</v>
+        <v>43831706398.13715</v>
       </c>
       <c r="N33" t="n">
         <v>50000000000</v>
@@ -3570,13 +3570,13 @@
         <v>44454.11143518519</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R33" t="b">
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.002052352979344775</v>
+        <v>0.00203713183520771</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3639,28 +3639,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>327</v>
+        <v>327.02</v>
       </c>
       <c r="F34" t="n">
-        <v>3707907231</v>
+        <v>3708300309</v>
       </c>
       <c r="G34" t="n">
         <v>33</v>
       </c>
       <c r="H34" t="n">
-        <v>382394337</v>
+        <v>323099760</v>
       </c>
       <c r="I34" t="n">
-        <v>337.55</v>
+        <v>340.69</v>
       </c>
       <c r="J34" t="n">
-        <v>297.69</v>
+        <v>311.96</v>
       </c>
       <c r="K34" t="n">
-        <v>23.23</v>
+        <v>1.8</v>
       </c>
       <c r="L34" t="n">
-        <v>7.55059</v>
+        <v>0.37067</v>
       </c>
       <c r="M34" t="n">
         <v>11339645.9251</v>
@@ -3675,13 +3675,13 @@
         <v>45358.44833333333</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0.001825723942103813</v>
+        <v>0.00179688033575781</v>
       </c>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
@@ -3695,7 +3695,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3714,31 +3714,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5.88e-06</v>
+        <v>5.95e-06</v>
       </c>
       <c r="F35" t="n">
-        <v>3463211758</v>
+        <v>3503571968</v>
       </c>
       <c r="G35" t="n">
         <v>34</v>
       </c>
       <c r="H35" t="n">
-        <v>95935944</v>
+        <v>91103023</v>
       </c>
       <c r="I35" t="n">
-        <v>6.02e-06</v>
+        <v>6.06e-06</v>
       </c>
       <c r="J35" t="n">
-        <v>5.76e-06</v>
+        <v>5.82e-06</v>
       </c>
       <c r="K35" t="n">
-        <v>9.411000000000001e-09</v>
+        <v>2.0646e-08</v>
       </c>
       <c r="L35" t="n">
-        <v>0.1525</v>
+        <v>0.15974</v>
       </c>
       <c r="M35" t="n">
-        <v>589238954375651.4</v>
+        <v>589238950487743.1</v>
       </c>
       <c r="N35" t="n">
         <v>589496066158401.1</v>
@@ -3750,13 +3750,13 @@
         <v>44496.82980324074</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R35" t="b">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.001680597459234109</v>
+        <v>0.001676867680104211</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3800,248 +3800,248 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>global-dollar</t>
+          <t>crypto-com-chain</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>usdg</t>
+          <t>cro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Global Dollar</t>
+          <t>Cronos</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.999976</v>
+        <v>0.067637</v>
       </c>
       <c r="F36" t="n">
-        <v>3245194299</v>
+        <v>3364743367</v>
       </c>
       <c r="G36" t="n">
         <v>35</v>
       </c>
       <c r="H36" t="n">
-        <v>633298325</v>
+        <v>14644812</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0.069409</v>
       </c>
       <c r="J36" t="n">
-        <v>0.99988</v>
+        <v>0.064829</v>
       </c>
       <c r="K36" t="n">
-        <v>-1.0853928892107e-05</v>
+        <v>0.00239858</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.00629</v>
+        <v>3.62235</v>
       </c>
       <c r="M36" t="n">
-        <v>3245247840.059057</v>
+        <v>49747076136.16346</v>
       </c>
       <c r="N36" t="n">
-        <v>3245247890.04586</v>
+        <v>98947092789.99742</v>
       </c>
       <c r="O36" t="n">
-        <v>1.65</v>
+        <v>0.891544</v>
       </c>
       <c r="P36" s="1" t="n">
-        <v>45686.67436342593</v>
+        <v>44523.66666666666</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R36" t="b">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.001551293444570708</v>
-      </c>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
+        <v>0.00159548574243353</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Token de exchange</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Layer 1 (Cronos)</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Proof of Stake</t>
+        </is>
+      </c>
+      <c r="W36" t="n">
+        <v>2018</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>cronos.org</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Pagos y DeFi en el ecosistema Crypto.com</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Cronos, EVM-compatible)</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>Token nativo del ecosistema Crypto.com y su red Cronos.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>crypto-com-chain</t>
+          <t>global-dollar</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>cro</t>
+          <t>usdg</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Cronos</t>
+          <t>Global Dollar</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.065125</v>
+        <v>0.999914</v>
       </c>
       <c r="F37" t="n">
-        <v>3240132067</v>
+        <v>3257336904</v>
       </c>
       <c r="G37" t="n">
         <v>36</v>
       </c>
       <c r="H37" t="n">
-        <v>9453924</v>
+        <v>356072551</v>
       </c>
       <c r="I37" t="n">
-        <v>0.06684</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>0.064841</v>
+        <v>0.999776</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.000783069008371232</v>
+        <v>-5.2135512535911e-05</v>
       </c>
       <c r="L37" t="n">
-        <v>-1.16763</v>
+        <v>-0.01242</v>
       </c>
       <c r="M37" t="n">
-        <v>49744967558.72809</v>
+        <v>3257616338.025859</v>
       </c>
       <c r="N37" t="n">
-        <v>98944988794.0228</v>
+        <v>3251901649.165859</v>
       </c>
       <c r="O37" t="n">
-        <v>0.891544</v>
+        <v>1.65</v>
       </c>
       <c r="P37" s="1" t="n">
-        <v>44523.66666666666</v>
+        <v>45686.67436342593</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R37" t="b">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.001548291084467256</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Token de exchange</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Layer 1 (Cronos)</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Proof of Stake</t>
-        </is>
-      </c>
-      <c r="W37" t="n">
-        <v>2018</v>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>cronos.org</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>Pagos y DeFi en el ecosistema Crypto.com</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Cronos, EVM-compatible)</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>Token nativo del ecosistema Crypto.com y su red Cronos.</t>
-        </is>
-      </c>
+        <v>0.001532523600523779</v>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ethena</t>
+          <t>bitway</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ena</t>
+          <t>btw</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ethena</t>
+          <t>Bitway</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.27802</v>
+        <v>1.15</v>
       </c>
       <c r="F38" t="n">
-        <v>2808076310</v>
+        <v>3119414355</v>
       </c>
       <c r="G38" t="n">
         <v>37</v>
       </c>
       <c r="H38" t="n">
-        <v>1005453744</v>
+        <v>29009108</v>
       </c>
       <c r="I38" t="n">
-        <v>0.285151</v>
+        <v>1.17</v>
       </c>
       <c r="J38" t="n">
-        <v>0.241291</v>
+        <v>0.980191</v>
       </c>
       <c r="K38" t="n">
-        <v>0.0326462</v>
+        <v>0.247137</v>
       </c>
       <c r="L38" t="n">
-        <v>13.30858</v>
+        <v>30.27369</v>
       </c>
       <c r="M38" t="n">
-        <v>10095312500</v>
+        <v>2708142280.000001</v>
       </c>
       <c r="N38" t="n">
-        <v>15000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="O38" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="P38" s="1" t="n">
-        <v>45393.21892361111</v>
+        <v>46291.06377314815</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R38" t="b">
         <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>0.001292043056466274</v>
+        <v>0.001451672794528122</v>
       </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
@@ -4055,7 +4055,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4074,34 +4074,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.999876</v>
+        <v>0.999938</v>
       </c>
       <c r="F39" t="n">
-        <v>2781139028</v>
+        <v>2779131582</v>
       </c>
       <c r="G39" t="n">
         <v>38</v>
       </c>
       <c r="H39" t="n">
-        <v>131160440</v>
+        <v>25936708</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0.9999670000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>0.999783</v>
+        <v>0.999771</v>
       </c>
       <c r="K39" t="n">
-        <v>-2.1815366736511e-05</v>
+        <v>8.165000000000001e-05</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.0077</v>
+        <v>0.0064</v>
       </c>
       <c r="M39" t="n">
-        <v>2781433279.25909</v>
+        <v>2779304258.944445</v>
       </c>
       <c r="N39" t="n">
-        <v>2781433279.25909</v>
+        <v>2779106296.067445</v>
       </c>
       <c r="O39" t="n">
         <v>1.021</v>
@@ -4110,13 +4110,13 @@
         <v>45222.61454861111</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001276066818954396</v>
+        <v>0.001252197533499652</v>
       </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
@@ -4130,7 +4130,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4149,34 +4149,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="F40" t="n">
-        <v>2770339731</v>
+        <v>2737839732</v>
       </c>
       <c r="G40" t="n">
         <v>39</v>
       </c>
       <c r="H40" t="n">
-        <v>733691</v>
+        <v>888350</v>
       </c>
       <c r="I40" t="n">
         <v>1.25</v>
       </c>
       <c r="J40" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="K40" t="n">
-        <v>0.0229915</v>
+        <v>-0.01496321878625895</v>
       </c>
       <c r="L40" t="n">
-        <v>1.87105</v>
+        <v>-1.24104</v>
       </c>
       <c r="M40" t="n">
-        <v>2278934927.291677</v>
+        <v>2279320630.284911</v>
       </c>
       <c r="N40" t="n">
-        <v>5418524673.845001</v>
+        <v>5418910376.770718</v>
       </c>
       <c r="O40" t="n">
         <v>5.64</v>
@@ -4185,13 +4185,13 @@
         <v>46205.17638888889</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R40" t="b">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.001269661861920004</v>
+        <v>0.001227992069072281</v>
       </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
@@ -4205,68 +4205,68 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>tether-gold</t>
+          <t>ethena</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>xaut</t>
+          <t>ena</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tether Gold</t>
+          <t>Ethena</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4280.2</v>
+        <v>0.270724</v>
       </c>
       <c r="F41" t="n">
-        <v>2665795127</v>
+        <v>2733047422</v>
       </c>
       <c r="G41" t="n">
         <v>40</v>
       </c>
       <c r="H41" t="n">
-        <v>158821903</v>
+        <v>396426394</v>
       </c>
       <c r="I41" t="n">
-        <v>4294.81</v>
+        <v>0.278982</v>
       </c>
       <c r="J41" t="n">
-        <v>4258.21</v>
+        <v>0.264816</v>
       </c>
       <c r="K41" t="n">
-        <v>-2.179440761827209</v>
+        <v>-0.006224754725193959</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.06114</v>
+        <v>-2.34562</v>
       </c>
       <c r="M41" t="n">
-        <v>622823.6595320001</v>
+        <v>10095312500</v>
       </c>
       <c r="N41" t="n">
-        <v>707747.089</v>
+        <v>15000000000</v>
       </c>
       <c r="O41" t="n">
-        <v>5504.62</v>
+        <v>1.52</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>46050.66666666666</v>
+        <v>45393.21892361111</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R41" t="b">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.001207657483598195</v>
+        <v>0.001225182795832406</v>
       </c>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
@@ -4280,68 +4280,68 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ondo-finance</t>
+          <t>tether-gold</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ondo</t>
+          <t>xaut</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Ondo</t>
+          <t>Tether Gold</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.544212</v>
+        <v>4278.67</v>
       </c>
       <c r="F42" t="n">
-        <v>2650847943</v>
+        <v>2664855583</v>
       </c>
       <c r="G42" t="n">
         <v>41</v>
       </c>
       <c r="H42" t="n">
-        <v>298694066</v>
+        <v>54750536</v>
       </c>
       <c r="I42" t="n">
-        <v>0.561067</v>
+        <v>4281.16</v>
       </c>
       <c r="J42" t="n">
-        <v>0.529581</v>
+        <v>4275.97</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.005807456750666073</v>
+        <v>-1.303744959958749</v>
       </c>
       <c r="L42" t="n">
-        <v>-1.03503</v>
+        <v>-0.03263</v>
       </c>
       <c r="M42" t="n">
-        <v>4869330647</v>
+        <v>622823.6595320001</v>
       </c>
       <c r="N42" t="n">
-        <v>10000000000</v>
+        <v>707747.089</v>
       </c>
       <c r="O42" t="n">
-        <v>2.14</v>
+        <v>5504.62</v>
       </c>
       <c r="P42" s="1" t="n">
-        <v>45641.69166666667</v>
+        <v>46050.66666666666</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R42" t="b">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.001198792455503759</v>
+        <v>0.001185208439315286</v>
       </c>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
@@ -4355,187 +4355,187 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>okb</t>
+          <t>ondo-finance</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>okb</t>
+          <t>ondo</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>OKB</t>
+          <t>Ondo</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>121.01</v>
+        <v>0.544944</v>
       </c>
       <c r="F43" t="n">
-        <v>2541041221</v>
+        <v>2653513899</v>
       </c>
       <c r="G43" t="n">
         <v>42</v>
       </c>
       <c r="H43" t="n">
-        <v>20506755</v>
+        <v>238823362</v>
       </c>
       <c r="I43" t="n">
-        <v>122.05</v>
+        <v>0.55672</v>
       </c>
       <c r="J43" t="n">
-        <v>119.33</v>
+        <v>0.528791</v>
       </c>
       <c r="K43" t="n">
-        <v>0.409047</v>
+        <v>-0.003066278902767117</v>
       </c>
       <c r="L43" t="n">
-        <v>0.31462</v>
+        <v>-0.67402</v>
       </c>
       <c r="M43" t="n">
-        <v>21000000</v>
+        <v>4869330647</v>
       </c>
       <c r="N43" t="n">
-        <v>21000000</v>
+        <v>10000000000</v>
       </c>
       <c r="O43" t="n">
-        <v>228.74</v>
+        <v>2.14</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>45934.66666666666</v>
+        <v>45641.69166666667</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R43" t="b">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.001133667166654172</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Token de exchange</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Utilidad</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>N/A (token de exchange)</t>
-        </is>
-      </c>
-      <c r="W43" t="n">
-        <v>2019</v>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>okx.com</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>Beneficios dentro del exchange OKX</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>Token ERC-20 sobre Ethereum</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>Token nativo del exchange OKX, usado para descuentos y beneficios.</t>
-        </is>
-      </c>
+        <v>0.001178559894176028</v>
+      </c>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>bitway</t>
+          <t>okb</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>btw</t>
+          <t>okb</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Bitway</t>
+          <t>OKB</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.92262</v>
+        <v>121.84</v>
       </c>
       <c r="F44" t="n">
-        <v>2501644736</v>
+        <v>2558597443</v>
       </c>
       <c r="G44" t="n">
         <v>43</v>
       </c>
       <c r="H44" t="n">
-        <v>35332630</v>
+        <v>19655996</v>
       </c>
       <c r="I44" t="n">
-        <v>1.37</v>
+        <v>122.43</v>
       </c>
       <c r="J44" t="n">
-        <v>0.763491</v>
+        <v>120.04</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.2469231384713139</v>
+        <v>0.758443</v>
       </c>
       <c r="L44" t="n">
-        <v>-20.93606</v>
+        <v>0.54911</v>
       </c>
       <c r="M44" t="n">
-        <v>2708142280.000001</v>
+        <v>21000000</v>
       </c>
       <c r="N44" t="n">
-        <v>10000000000</v>
+        <v>21000000</v>
       </c>
       <c r="O44" t="n">
-        <v>1.37</v>
+        <v>228.74</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>46291.06377314815</v>
+        <v>45934.66666666666</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.001110301498154538</v>
-      </c>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr"/>
+        <v>0.001122919449408354</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Token de exchange</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Utilidad</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>N/A (token de exchange)</t>
+        </is>
+      </c>
+      <c r="W44" t="n">
+        <v>2019</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>okx.com</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>Beneficios dentro del exchange OKX</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>Token ERC-20 sobre Ethereum</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>Token nativo del exchange OKX, usado para descuentos y beneficios.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4554,34 +4554,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.999962</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>2491193156</v>
+        <v>2491318521</v>
       </c>
       <c r="G45" t="n">
         <v>44</v>
       </c>
       <c r="H45" t="n">
-        <v>303948811</v>
+        <v>105209885</v>
       </c>
       <c r="I45" t="n">
         <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>0.99984</v>
+        <v>0.999878</v>
       </c>
       <c r="K45" t="n">
-        <v>-1.5146618305151e-05</v>
+        <v>3.171e-05</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.01141</v>
+        <v>-0.00186</v>
       </c>
       <c r="M45" t="n">
-        <v>2491272908.017196</v>
+        <v>2491272908.017204</v>
       </c>
       <c r="N45" t="n">
-        <v>2491272908.0172</v>
+        <v>2491272908.017204</v>
       </c>
       <c r="O45" t="n">
         <v>1.073</v>
@@ -4590,13 +4590,13 @@
         <v>45652.11518518518</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R45" t="b">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.00110410276865932</v>
+        <v>0.001083480248859509</v>
       </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
@@ -4610,7 +4610,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4665,13 +4665,13 @@
         <v>46290.53483796296</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R46" t="b">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.001053142548603189</v>
+        <v>0.001033038187390733</v>
       </c>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
@@ -4685,7 +4685,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4704,31 +4704,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>154.59</v>
+        <v>154.56</v>
       </c>
       <c r="F47" t="n">
-        <v>2384979455</v>
+        <v>2384820190</v>
       </c>
       <c r="G47" t="n">
         <v>46</v>
       </c>
       <c r="H47" t="n">
-        <v>366713824</v>
+        <v>268585001</v>
       </c>
       <c r="I47" t="n">
-        <v>156.56</v>
+        <v>157.25</v>
       </c>
       <c r="J47" t="n">
-        <v>145.2</v>
+        <v>152.7</v>
       </c>
       <c r="K47" t="n">
-        <v>4.81</v>
+        <v>-0.2979510974178083</v>
       </c>
       <c r="L47" t="n">
-        <v>3.13157</v>
+        <v>-0.38129</v>
       </c>
       <c r="M47" t="n">
-        <v>15429292.82562298</v>
+        <v>15429382.51379187</v>
       </c>
       <c r="N47" t="n">
         <v>16000000</v>
@@ -4740,13 +4740,13 @@
         <v>44334.55554398148</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R47" t="b">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0.001041108465292276</v>
+        <v>0.001021050457929947</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -4790,82 +4790,112 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>mantle</t>
+          <t>quant-network</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>mnt</t>
+          <t>qnt</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Mantle</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.7011039999999999</v>
+        <v>163.55</v>
       </c>
       <c r="F48" t="n">
-        <v>2315344740</v>
+        <v>2378700069</v>
       </c>
       <c r="G48" t="n">
         <v>47</v>
       </c>
       <c r="H48" t="n">
-        <v>45747180</v>
+        <v>587701192</v>
       </c>
       <c r="I48" t="n">
-        <v>0.714831</v>
+        <v>193.67</v>
       </c>
       <c r="J48" t="n">
-        <v>0.658871</v>
+        <v>109.62</v>
       </c>
       <c r="K48" t="n">
-        <v>0.02610291</v>
+        <v>57.02</v>
       </c>
       <c r="L48" t="n">
-        <v>3.89981</v>
+        <v>53.08112</v>
       </c>
       <c r="M48" t="n">
-        <v>3302294382.53684</v>
+        <v>14544176.16408117</v>
       </c>
       <c r="N48" t="n">
-        <v>6219316794.889999</v>
+        <v>14612493</v>
       </c>
       <c r="O48" t="n">
-        <v>2.86</v>
+        <v>427.42</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>45938.71164351852</v>
+        <v>44450.05208333334</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S48" t="n">
-        <v>0.0009998087994272514</v>
-      </c>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr"/>
-      <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr"/>
-      <c r="AA48" t="inlineStr"/>
+        <v>0.001017462816030717</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Infraestructura empresarial</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>N/A (token ERC-20)</t>
+        </is>
+      </c>
+      <c r="W48" t="n">
+        <v>2018</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>quant.network</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>Interoperabilidad entre redes empresariales</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>Token ERC-20 sobre Ethereum</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>Su tecnología Overledger busca conectar múltiples blockchains y redes existentes.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4920,13 +4950,13 @@
         <v>45699.87511574074</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R49" t="b">
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>0.0009848544782450814</v>
+        <v>0.0009655429414597221</v>
       </c>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
@@ -4940,7 +4970,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4959,16 +4989,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="F50" t="n">
-        <v>2276483255</v>
+        <v>2270709990</v>
       </c>
       <c r="G50" t="n">
         <v>49</v>
       </c>
       <c r="H50" t="n">
-        <v>799036</v>
+        <v>3224800</v>
       </c>
       <c r="I50" t="n">
         <v>1.15</v>
@@ -4977,16 +5007,16 @@
         <v>1.14</v>
       </c>
       <c r="K50" t="n">
-        <v>0.00341799</v>
+        <v>-0.002379409004520161</v>
       </c>
       <c r="L50" t="n">
-        <v>0.29273</v>
+        <v>-0.19936</v>
       </c>
       <c r="M50" t="n">
-        <v>1985130003.146069</v>
+        <v>1984602261.82023</v>
       </c>
       <c r="N50" t="n">
-        <v>1985178145.937342</v>
+        <v>1984602261.82023</v>
       </c>
       <c r="O50" t="n">
         <v>1.26</v>
@@ -4995,13 +5025,13 @@
         <v>45377.89175925926</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R50" t="b">
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0.0009767604341755422</v>
+        <v>0.0009541585558499936</v>
       </c>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
@@ -5015,112 +5045,82 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>polkadot</t>
+          <t>mantle</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>dot</t>
+          <t>mnt</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Mantle</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1.22</v>
+        <v>0.679908</v>
       </c>
       <c r="F51" t="n">
-        <v>2079194205</v>
+        <v>2245256772</v>
       </c>
       <c r="G51" t="n">
         <v>50</v>
       </c>
       <c r="H51" t="n">
-        <v>211092465</v>
+        <v>34224894</v>
       </c>
       <c r="I51" t="n">
-        <v>1.25</v>
+        <v>0.701793</v>
       </c>
       <c r="J51" t="n">
-        <v>1.16</v>
+        <v>0.673049</v>
       </c>
       <c r="K51" t="n">
-        <v>0.03290304</v>
+        <v>-0.02121843084676744</v>
       </c>
       <c r="L51" t="n">
-        <v>2.79315</v>
+        <v>-3.1601</v>
       </c>
       <c r="M51" t="n">
-        <v>1704554979.517097</v>
+        <v>3302294382.53684</v>
       </c>
       <c r="N51" t="n">
-        <v>1704565831.886456</v>
+        <v>6219316794.889999</v>
       </c>
       <c r="O51" t="n">
-        <v>54.98</v>
+        <v>2.86</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>44504.25704861111</v>
+        <v>45938.71164351852</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R51" t="b">
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0.0008597502354000008</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Interoperabilidad</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Layer 0</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Proof of Stake (NPoS)</t>
-        </is>
-      </c>
-      <c r="W51" t="n">
-        <v>2020</v>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>polkadot.network</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>Interoperabilidad entre blockchains</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Layer 0, relay chain)</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>Permite que blockchains distintas (parachains) se comuniquen entre sí.</t>
-        </is>
-      </c>
+        <v>0.0009392377672958091</v>
+      </c>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5139,34 +5139,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.00438534</v>
+        <v>0.0047743</v>
       </c>
       <c r="F52" t="n">
-        <v>2045009163</v>
+        <v>2224546738</v>
       </c>
       <c r="G52" t="n">
         <v>51</v>
       </c>
       <c r="H52" t="n">
-        <v>242824041</v>
+        <v>152156872</v>
       </c>
       <c r="I52" t="n">
-        <v>0.0046177</v>
+        <v>0.00465735</v>
       </c>
       <c r="J52" t="n">
-        <v>0.00402625</v>
+        <v>0.00430512</v>
       </c>
       <c r="K52" t="n">
-        <v>0.00021342</v>
+        <v>0.00036175</v>
       </c>
       <c r="L52" t="n">
-        <v>5.08412</v>
+        <v>7.8613</v>
       </c>
       <c r="M52" t="n">
-        <v>466206167126.4446</v>
+        <v>465942213332.9943</v>
       </c>
       <c r="N52" t="n">
-        <v>831708723495.5499</v>
+        <v>831454033588.2654</v>
       </c>
       <c r="O52" t="n">
         <v>0.00881908</v>
@@ -5175,13 +5175,13 @@
         <v>45914.36296296296</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S52" t="n">
-        <v>0.00083947542258312</v>
+        <v>0.0009270974541038201</v>
       </c>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
@@ -5195,68 +5195,68 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>aster-2</t>
+          <t>worldcoin-wld</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>aster</t>
+          <t>wld</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Worldcoin</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.7262960000000001</v>
+        <v>0.569147</v>
       </c>
       <c r="F53" t="n">
-        <v>1968338876</v>
+        <v>2115298987</v>
       </c>
       <c r="G53" t="n">
         <v>52</v>
       </c>
       <c r="H53" t="n">
-        <v>89676145</v>
+        <v>901731266</v>
       </c>
       <c r="I53" t="n">
-        <v>0.742024</v>
+        <v>0.586331</v>
       </c>
       <c r="J53" t="n">
-        <v>0.719024</v>
+        <v>0.510792</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.007135555905350199</v>
+        <v>0.074793</v>
       </c>
       <c r="L53" t="n">
-        <v>-1.06051</v>
+        <v>14.87998</v>
       </c>
       <c r="M53" t="n">
-        <v>2710487455.649731</v>
+        <v>3716610114.975046</v>
       </c>
       <c r="N53" t="n">
-        <v>7795741639.279309</v>
+        <v>10000000000</v>
       </c>
       <c r="O53" t="n">
-        <v>2.41</v>
+        <v>11.74</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>45924.13766203704</v>
+        <v>45360.67409722223</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S53" t="n">
-        <v>0.0007940030280328506</v>
+        <v>0.0008630559410546174</v>
       </c>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
@@ -5270,143 +5270,173 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>polkadot</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>dot</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Morpho</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2.75</v>
+        <v>1.24</v>
       </c>
       <c r="F54" t="n">
-        <v>1927060250</v>
+        <v>2110569559</v>
       </c>
       <c r="G54" t="n">
         <v>53</v>
       </c>
       <c r="H54" t="n">
-        <v>34153385</v>
+        <v>235174355</v>
       </c>
       <c r="I54" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J54" t="n">
-        <v>2.69</v>
+        <v>1.22</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.05197841826801719</v>
+        <v>0.01278622</v>
       </c>
       <c r="L54" t="n">
-        <v>-1.84535</v>
+        <v>0.8834</v>
       </c>
       <c r="M54" t="n">
-        <v>699504178.637211</v>
+        <v>1704715523.71559</v>
       </c>
       <c r="N54" t="n">
-        <v>1000000000</v>
+        <v>1704725434.729766</v>
       </c>
       <c r="O54" t="n">
-        <v>4.17</v>
+        <v>54.98</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>45674.19883101852</v>
+        <v>44504.25704861111</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R54" t="b">
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>0.0007695210801830271</v>
-      </c>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr"/>
-      <c r="AA54" t="inlineStr"/>
+        <v>0.0008602835295202394</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Layer 0</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Proof of Stake (NPoS)</t>
+        </is>
+      </c>
+      <c r="W54" t="n">
+        <v>2020</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>polkadot.network</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>Interoperabilidad entre blockchains</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Layer 0, relay chain)</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>Permite que blockchains distintas (parachains) se comuniquen entre sí.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>world-liberty-financial</t>
+          <t>aster-2</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>wlfi</t>
+          <t>aster</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>World Liberty Financial</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.058929</v>
+        <v>0.7336</v>
       </c>
       <c r="F55" t="n">
-        <v>1872782612</v>
+        <v>1988412632</v>
       </c>
       <c r="G55" t="n">
         <v>54</v>
       </c>
       <c r="H55" t="n">
-        <v>37901605</v>
+        <v>104763058</v>
       </c>
       <c r="I55" t="n">
-        <v>0.059528</v>
+        <v>0.748192</v>
       </c>
       <c r="J55" t="n">
-        <v>0.056538</v>
+        <v>0.725587</v>
       </c>
       <c r="K55" t="n">
-        <v>0.00152381</v>
+        <v>0.00587709</v>
       </c>
       <c r="L55" t="n">
-        <v>2.6126</v>
+        <v>0.63976</v>
       </c>
       <c r="M55" t="n">
-        <v>31777915436</v>
+        <v>2710487455.649731</v>
       </c>
       <c r="N55" t="n">
-        <v>100000000000</v>
+        <v>7795741639.235296</v>
       </c>
       <c r="O55" t="n">
-        <v>0.331336</v>
+        <v>2.41</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>45901.18065972222</v>
+        <v>45924.13766203704</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R55" t="b">
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0007373295459268335</v>
+        <v>0.0007886746006140415</v>
       </c>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
@@ -5420,68 +5450,68 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>pax-gold</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>paxg</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>PAX Gold</t>
+          <t>Morpho</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4278.8</v>
+        <v>2.7</v>
       </c>
       <c r="F56" t="n">
-        <v>1860862541</v>
+        <v>1887686340</v>
       </c>
       <c r="G56" t="n">
         <v>55</v>
       </c>
       <c r="H56" t="n">
-        <v>89054883</v>
+        <v>25300729</v>
       </c>
       <c r="I56" t="n">
-        <v>4290.58</v>
+        <v>2.79</v>
       </c>
       <c r="J56" t="n">
-        <v>4254.67</v>
+        <v>2.66</v>
       </c>
       <c r="K56" t="n">
-        <v>-1.201781688529081</v>
+        <v>-0.04959945040026925</v>
       </c>
       <c r="L56" t="n">
-        <v>-0.03731</v>
+        <v>-1.8954</v>
       </c>
       <c r="M56" t="n">
-        <v>434898.623539</v>
+        <v>699556652.9224828</v>
       </c>
       <c r="N56" t="n">
-        <v>434898.623539</v>
+        <v>1000000000</v>
       </c>
       <c r="O56" t="n">
-        <v>5619.09</v>
+        <v>4.17</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>46050.93814814815</v>
+        <v>45674.19883101852</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R56" t="b">
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0.0007302598688356388</v>
+        <v>0.0007296284043814454</v>
       </c>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
@@ -5495,68 +5525,68 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>pax-gold</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>paxg</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Pepe</t>
+          <t>PAX Gold</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4.36e-06</v>
+        <v>4277.06</v>
       </c>
       <c r="F57" t="n">
-        <v>1834875262</v>
+        <v>1860087960</v>
       </c>
       <c r="G57" t="n">
         <v>56</v>
       </c>
       <c r="H57" t="n">
-        <v>267690605</v>
+        <v>45264204</v>
       </c>
       <c r="I57" t="n">
-        <v>4.53e-06</v>
+        <v>4280.33</v>
       </c>
       <c r="J57" t="n">
-        <v>4.37e-06</v>
+        <v>4275.7</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.18407185435e-07</v>
+        <v>-1.179323987517819</v>
       </c>
       <c r="L57" t="n">
-        <v>-2.82471</v>
+        <v>-0.02825</v>
       </c>
       <c r="M57" t="n">
-        <v>420690000000000</v>
+        <v>434898.623539</v>
       </c>
       <c r="N57" t="n">
-        <v>420690000000000</v>
+        <v>434898.623539</v>
       </c>
       <c r="O57" t="n">
-        <v>2.803e-05</v>
+        <v>5619.09</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>45635.35457175926</v>
+        <v>46050.93814814815</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R57" t="b">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0.0007148470687769156</v>
+        <v>0.0007134501124099534</v>
       </c>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
@@ -5570,68 +5600,68 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Sky</t>
+          <t>Pepe</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.07786800000000001</v>
+        <v>4.4e-06</v>
       </c>
       <c r="F58" t="n">
-        <v>1823715076</v>
+        <v>1850216165</v>
       </c>
       <c r="G58" t="n">
         <v>57</v>
       </c>
       <c r="H58" t="n">
-        <v>22188256</v>
+        <v>221340576</v>
       </c>
       <c r="I58" t="n">
-        <v>0.079861</v>
+        <v>4.46e-06</v>
       </c>
       <c r="J58" t="n">
-        <v>0.073389</v>
+        <v>4.26e-06</v>
       </c>
       <c r="K58" t="n">
-        <v>0.00329694</v>
+        <v>1.2419e-08</v>
       </c>
       <c r="L58" t="n">
-        <v>4.39628</v>
+        <v>0.03035</v>
       </c>
       <c r="M58" t="n">
-        <v>23419583386.47268</v>
+        <v>420690000000000</v>
       </c>
       <c r="N58" t="n">
-        <v>23459804203.60596</v>
+        <v>420690000000000</v>
       </c>
       <c r="O58" t="n">
-        <v>0.100535</v>
+        <v>2.803e-05</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>45630.09302083333</v>
+        <v>45635.35457175926</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R58" t="b">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0007082280720194573</v>
+        <v>0.0007076632226797332</v>
       </c>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
@@ -5645,68 +5675,68 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>worldcoin-wld</t>
+          <t>world-liberty-financial</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>wld</t>
+          <t>wlfi</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Worldcoin</t>
+          <t>World Liberty Financial</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.485774</v>
+        <v>0.057871</v>
       </c>
       <c r="F59" t="n">
-        <v>1804553072</v>
+        <v>1839035952</v>
       </c>
       <c r="G59" t="n">
         <v>58</v>
       </c>
       <c r="H59" t="n">
-        <v>438376989</v>
+        <v>30663601</v>
       </c>
       <c r="I59" t="n">
-        <v>0.511413</v>
+        <v>0.059744</v>
       </c>
       <c r="J59" t="n">
-        <v>0.445403</v>
+        <v>0.057715</v>
       </c>
       <c r="K59" t="n">
-        <v>0.03244423</v>
+        <v>-0.000902270316658009</v>
       </c>
       <c r="L59" t="n">
-        <v>7.0463</v>
+        <v>-1.63875</v>
       </c>
       <c r="M59" t="n">
-        <v>3715164012.295929</v>
+        <v>31778313765</v>
       </c>
       <c r="N59" t="n">
-        <v>10000000000</v>
+        <v>100000000000</v>
       </c>
       <c r="O59" t="n">
-        <v>11.74</v>
+        <v>0.331336</v>
       </c>
       <c r="P59" s="1" t="n">
-        <v>45360.67409722223</v>
+        <v>45901.18065972222</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>0.0006968632755597566</v>
+        <v>0.000701109332552216</v>
       </c>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
@@ -5720,7 +5750,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5742,31 +5772,31 @@
         <v>3.19</v>
       </c>
       <c r="F60" t="n">
-        <v>1776740656</v>
+        <v>1778798653</v>
       </c>
       <c r="G60" t="n">
         <v>59</v>
       </c>
       <c r="H60" t="n">
-        <v>65739470</v>
+        <v>78606572</v>
       </c>
       <c r="I60" t="n">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="J60" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="K60" t="n">
-        <v>0.00480555</v>
+        <v>-0.03047850031257626</v>
       </c>
       <c r="L60" t="n">
-        <v>0.06728000000000001</v>
+        <v>-1.17424</v>
       </c>
       <c r="M60" t="n">
-        <v>556904472.5478657</v>
+        <v>556917030.5505874</v>
       </c>
       <c r="N60" t="n">
-        <v>556914950.9844009</v>
+        <v>556917120.3081846</v>
       </c>
       <c r="O60" t="n">
         <v>700.65</v>
@@ -5775,13 +5805,13 @@
         <v>44326.33741898148</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R60" t="b">
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0.0006803680046636372</v>
+        <v>0.000665797962435707</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -5825,68 +5855,68 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>htx-dao</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>htx</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>HTX DAO</t>
+          <t>Sky</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1.72e-06</v>
+        <v>0.07538599999999999</v>
       </c>
       <c r="F61" t="n">
-        <v>1546169711</v>
+        <v>1766226743</v>
       </c>
       <c r="G61" t="n">
         <v>60</v>
       </c>
       <c r="H61" t="n">
-        <v>23653359</v>
+        <v>13841969</v>
       </c>
       <c r="I61" t="n">
-        <v>1.73e-06</v>
+        <v>0.07837</v>
       </c>
       <c r="J61" t="n">
-        <v>1.71e-06</v>
+        <v>0.074742</v>
       </c>
       <c r="K61" t="n">
-        <v>3.848e-09</v>
+        <v>-0.002002319107970107</v>
       </c>
       <c r="L61" t="n">
-        <v>0.16571</v>
+        <v>-2.66222</v>
       </c>
       <c r="M61" t="n">
-        <v>898232728634017.2</v>
+        <v>23429167587.39992</v>
       </c>
       <c r="N61" t="n">
-        <v>898232728634017.2</v>
+        <v>23459804203.60596</v>
       </c>
       <c r="O61" t="n">
-        <v>3.75e-06</v>
+        <v>0.100535</v>
       </c>
       <c r="P61" s="1" t="n">
-        <v>45629.67800925926</v>
+        <v>45630.09302083333</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R61" t="b">
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>0.0005436186406907534</v>
+        <v>0.0006584282533941139</v>
       </c>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
@@ -5900,7 +5930,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5919,34 +5949,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.998621</v>
+        <v>0.999459</v>
       </c>
       <c r="F62" t="n">
-        <v>1545202266</v>
+        <v>1551884400</v>
       </c>
       <c r="G62" t="n">
         <v>61</v>
       </c>
       <c r="H62" t="n">
-        <v>2539973</v>
+        <v>1407159</v>
       </c>
       <c r="I62" t="n">
-        <v>0.999776</v>
+        <v>0.999821</v>
       </c>
       <c r="J62" t="n">
-        <v>0.996449</v>
+        <v>0.9963109999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.000251913610240129</v>
+        <v>0.00187557</v>
       </c>
       <c r="L62" t="n">
-        <v>0.0061</v>
+        <v>0.19288</v>
       </c>
       <c r="M62" t="n">
-        <v>1547266660</v>
+        <v>1552724047</v>
       </c>
       <c r="N62" t="n">
-        <v>1547454437</v>
+        <v>1561034969</v>
       </c>
       <c r="O62" t="n">
         <v>1.24</v>
@@ -5955,13 +5985,13 @@
         <v>46212.39942129629</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R62" t="b">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0.000543044858558626</v>
+        <v>0.0005327798274028898</v>
       </c>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
@@ -5975,112 +6005,82 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>quant-network</t>
+          <t>htx-dao</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>qnt</t>
+          <t>htx</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>HTX DAO</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>104.32</v>
+        <v>1.71e-06</v>
       </c>
       <c r="F63" t="n">
-        <v>1517436637</v>
+        <v>1532950340</v>
       </c>
       <c r="G63" t="n">
         <v>62</v>
       </c>
       <c r="H63" t="n">
-        <v>57913062</v>
+        <v>62256208</v>
       </c>
       <c r="I63" t="n">
-        <v>109.85</v>
+        <v>1.72e-06</v>
       </c>
       <c r="J63" t="n">
-        <v>92.81999999999999</v>
+        <v>1.7e-06</v>
       </c>
       <c r="K63" t="n">
-        <v>9.050000000000001</v>
+        <v>-1.4842378741e-08</v>
       </c>
       <c r="L63" t="n">
-        <v>9.33052</v>
+        <v>-0.9144</v>
       </c>
       <c r="M63" t="n">
-        <v>14544176.16408117</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="N63" t="n">
-        <v>14612493</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="O63" t="n">
-        <v>427.42</v>
+        <v>3.75e-06</v>
       </c>
       <c r="P63" s="1" t="n">
-        <v>44450.05208333334</v>
+        <v>45629.67800925926</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0.0005265773365729003</v>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Interoperabilidad</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Infraestructura empresarial</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>N/A (token ERC-20)</t>
-        </is>
-      </c>
-      <c r="W63" t="n">
-        <v>2018</v>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>quant.network</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>Interoperabilidad entre redes empresariales</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>Token ERC-20 sobre Ethereum</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>Su tecnología Overledger busca conectar múltiples blockchains y redes existentes.</t>
-        </is>
-      </c>
+        <v>0.0005216805979957382</v>
+      </c>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6099,28 +6099,28 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.221969</v>
+        <v>0.222546</v>
       </c>
       <c r="F64" t="n">
-        <v>1506183242</v>
+        <v>1510102474</v>
       </c>
       <c r="G64" t="n">
         <v>63</v>
       </c>
       <c r="H64" t="n">
-        <v>288056013</v>
+        <v>331283079</v>
       </c>
       <c r="I64" t="n">
-        <v>0.230716</v>
+        <v>0.236179</v>
       </c>
       <c r="J64" t="n">
-        <v>0.217349</v>
+        <v>0.218077</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.002383285914097838</v>
+        <v>-0.000257700923587345</v>
       </c>
       <c r="L64" t="n">
-        <v>-1.09454</v>
+        <v>-0.38116</v>
       </c>
       <c r="M64" t="n">
         <v>6785574605</v>
@@ -6135,13 +6135,13 @@
         <v>45303.18748842592</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R64" t="b">
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0005199030584725715</v>
+        <v>0.0005082870782647422</v>
       </c>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
@@ -6155,7 +6155,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6174,34 +6174,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>9.41</v>
+        <v>9.48</v>
       </c>
       <c r="F65" t="n">
-        <v>1489108155</v>
+        <v>1500778097</v>
       </c>
       <c r="G65" t="n">
         <v>64</v>
       </c>
       <c r="H65" t="n">
-        <v>100188156</v>
+        <v>66682110</v>
       </c>
       <c r="I65" t="n">
-        <v>9.640000000000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="J65" t="n">
         <v>9.279999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.1362743174851957</v>
+        <v>0.02589166</v>
       </c>
       <c r="L65" t="n">
-        <v>-1.50089</v>
+        <v>0.08377999999999999</v>
       </c>
       <c r="M65" t="n">
-        <v>158289223.9571552</v>
+        <v>158300159.3516731</v>
       </c>
       <c r="N65" t="n">
-        <v>158290115.2467552</v>
+        <v>158300993.7583609</v>
       </c>
       <c r="O65" t="n">
         <v>167.09</v>
@@ -6210,13 +6210,13 @@
         <v>44322.44053240741</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R65" t="b">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0.0005097759919983821</v>
+        <v>0.0005028210873783835</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="F66" t="n">
-        <v>1488884774</v>
+        <v>1493327917</v>
       </c>
       <c r="G66" t="n">
         <v>65</v>
@@ -6297,10 +6297,10 @@
         <v>1.15</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.001114153641704085</v>
+        <v>0.00344531</v>
       </c>
       <c r="L66" t="n">
-        <v>-0.10063</v>
+        <v>0.29842</v>
       </c>
       <c r="M66" t="n">
         <v>1289618689.24777</v>
@@ -6315,13 +6315,13 @@
         <v>46255.48263888889</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R66" t="b">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0.0005096435069202053</v>
+        <v>0.0004984537590322932</v>
       </c>
       <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr"/>
@@ -6335,7 +6335,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6354,28 +6354,28 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.999503</v>
+        <v>0.999939</v>
       </c>
       <c r="F67" t="n">
-        <v>1482134028</v>
+        <v>1482767260</v>
       </c>
       <c r="G67" t="n">
         <v>66</v>
       </c>
       <c r="H67" t="n">
-        <v>106423415</v>
+        <v>73034322</v>
       </c>
       <c r="I67" t="n">
-        <v>0.999776</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
-        <v>0.999155</v>
+        <v>0.999428</v>
       </c>
       <c r="K67" t="n">
-        <v>0.00011111</v>
+        <v>0.00046141</v>
       </c>
       <c r="L67" t="n">
-        <v>0.0083</v>
+        <v>0.04588</v>
       </c>
       <c r="M67" t="n">
         <v>1482857391.63</v>
@@ -6390,13 +6390,13 @@
         <v>46058.54591435185</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R67" t="b">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.0005056397057394342</v>
+        <v>0.000492263055362122</v>
       </c>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
@@ -6410,7 +6410,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6429,34 +6429,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>29.61</v>
+        <v>30.39</v>
       </c>
       <c r="F68" t="n">
-        <v>1426184735</v>
+        <v>1464276446</v>
       </c>
       <c r="G68" t="n">
         <v>67</v>
       </c>
       <c r="H68" t="n">
-        <v>32239771</v>
+        <v>45333775</v>
       </c>
       <c r="I68" t="n">
-        <v>30.81</v>
+        <v>31.66</v>
       </c>
       <c r="J68" t="n">
-        <v>29.43</v>
+        <v>29.1</v>
       </c>
       <c r="K68" t="n">
-        <v>-1.582409286039994</v>
+        <v>0.64928</v>
       </c>
       <c r="L68" t="n">
-        <v>-5.04948</v>
+        <v>2.07967</v>
       </c>
       <c r="M68" t="n">
-        <v>48162092.89562348</v>
+        <v>48180888.23223712</v>
       </c>
       <c r="N68" t="n">
-        <v>81051713.11454831</v>
+        <v>81058245.79412135</v>
       </c>
       <c r="O68" t="n">
         <v>34.53</v>
@@ -6465,13 +6465,13 @@
         <v>46286.34548611111</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0.0004724567293133173</v>
+        <v>0.0004814236587133856</v>
       </c>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
@@ -6485,7 +6485,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6504,28 +6504,28 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="F69" t="n">
-        <v>1425004849</v>
+        <v>1440844743</v>
       </c>
       <c r="G69" t="n">
         <v>68</v>
       </c>
       <c r="H69" t="n">
-        <v>25742695</v>
+        <v>18336426</v>
       </c>
       <c r="I69" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="J69" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="K69" t="n">
-        <v>0.04829227</v>
+        <v>0.02820162</v>
       </c>
       <c r="L69" t="n">
-        <v>2.25009</v>
+        <v>1.33113</v>
       </c>
       <c r="M69" t="n">
         <v>699992029.6481038</v>
@@ -6540,13 +6540,13 @@
         <v>45653.15375</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R69" t="b">
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>0.0004717569505096154</v>
+        <v>0.0004676878911602436</v>
       </c>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
@@ -6560,7 +6560,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6579,28 +6579,28 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.99978</v>
+        <v>0.999829</v>
       </c>
       <c r="F70" t="n">
-        <v>1407468740</v>
+        <v>1407539791</v>
       </c>
       <c r="G70" t="n">
         <v>69</v>
       </c>
       <c r="H70" t="n">
-        <v>17760947</v>
+        <v>12037464</v>
       </c>
       <c r="I70" t="n">
         <v>1</v>
       </c>
       <c r="J70" t="n">
-        <v>0.999597</v>
+        <v>0.999684</v>
       </c>
       <c r="K70" t="n">
-        <v>-0.000191808189512366</v>
+        <v>-4.8164414465091e-05</v>
       </c>
       <c r="L70" t="n">
-        <v>-0.01941</v>
+        <v>0.00213</v>
       </c>
       <c r="M70" t="n">
         <v>1407780804.97</v>
@@ -6615,13 +6615,13 @@
         <v>46092.00303240741</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R70" t="b">
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>0.0004613564564130624</v>
+        <v>0.0004481643815356741</v>
       </c>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
@@ -6635,7 +6635,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6654,34 +6654,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.996037</v>
+        <v>0.996287</v>
       </c>
       <c r="F71" t="n">
-        <v>1371951063</v>
+        <v>1372311161</v>
       </c>
       <c r="G71" t="n">
         <v>70</v>
       </c>
       <c r="H71" t="n">
-        <v>343325</v>
+        <v>243744</v>
       </c>
       <c r="I71" t="n">
-        <v>0.996958</v>
+        <v>0.997027</v>
       </c>
       <c r="J71" t="n">
-        <v>0.995733</v>
+        <v>0.995825</v>
       </c>
       <c r="K71" t="n">
-        <v>0.00052593</v>
+        <v>0.00014679</v>
       </c>
       <c r="L71" t="n">
-        <v>0.0473</v>
+        <v>0.01261</v>
       </c>
       <c r="M71" t="n">
-        <v>1377413080.69863</v>
+        <v>1377425695.547727</v>
       </c>
       <c r="N71" t="n">
-        <v>1377413080.69863</v>
+        <v>1377425695.547727</v>
       </c>
       <c r="O71" t="n">
         <v>1.075</v>
@@ -6690,13 +6690,13 @@
         <v>45785.55951388889</v>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R71" t="b">
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>0.0004402912708601111</v>
+        <v>0.0004275132033905924</v>
       </c>
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
@@ -6710,7 +6710,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6729,28 +6729,28 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9997239999999999</v>
+        <v>0.999823</v>
       </c>
       <c r="F72" t="n">
-        <v>1319632232</v>
+        <v>1319766748</v>
       </c>
       <c r="G72" t="n">
         <v>71</v>
       </c>
       <c r="H72" t="n">
-        <v>968552</v>
+        <v>2994702</v>
       </c>
       <c r="I72" t="n">
-        <v>0.999837</v>
+        <v>0.999844</v>
       </c>
       <c r="J72" t="n">
-        <v>0.999417</v>
+        <v>0.9995849999999999</v>
       </c>
       <c r="K72" t="n">
-        <v>0.00046168</v>
+        <v>0.00012028</v>
       </c>
       <c r="L72" t="n">
-        <v>0.04044</v>
+        <v>-8.000000000000001e-05</v>
       </c>
       <c r="M72" t="n">
         <v>1320000000</v>
@@ -6765,13 +6765,13 @@
         <v>45940.56990740741</v>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R72" t="b">
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>0.0004092614858060801</v>
+        <v>0.000396711436946886</v>
       </c>
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
@@ -6785,68 +6785,68 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>polygon-ecosystem-token</t>
+          <t>kaspa</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>pol</t>
+          <t>kas</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>POL (ex-MATIC)</t>
+          <t>Kaspa</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.118846</v>
+        <v>0.04719838</v>
       </c>
       <c r="F73" t="n">
-        <v>1262197947</v>
+        <v>1308528302</v>
       </c>
       <c r="G73" t="n">
         <v>72</v>
       </c>
       <c r="H73" t="n">
-        <v>128937182</v>
+        <v>47407083</v>
       </c>
       <c r="I73" t="n">
-        <v>0.120365</v>
+        <v>0.05004</v>
       </c>
       <c r="J73" t="n">
-        <v>0.11172</v>
+        <v>0.04630187</v>
       </c>
       <c r="K73" t="n">
-        <v>0.00581829</v>
+        <v>0.00095407</v>
       </c>
       <c r="L73" t="n">
-        <v>5.11378</v>
+        <v>0.56796</v>
       </c>
       <c r="M73" t="n">
-        <v>10621081493.65423</v>
+        <v>27724007642.5208</v>
       </c>
       <c r="N73" t="n">
-        <v>10621081493.65423</v>
+        <v>27724481654.36061</v>
       </c>
       <c r="O73" t="n">
-        <v>1.29</v>
+        <v>0.207411</v>
       </c>
       <c r="P73" s="1" t="n">
-        <v>45364.45493055556</v>
+        <v>45504.69498842592</v>
       </c>
       <c r="Q73" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R73" t="b">
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0.0003751977752028758</v>
+        <v>0.0003901234103781581</v>
       </c>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
@@ -6860,68 +6860,68 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>kaspa</t>
+          <t>polygon-ecosystem-token</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>kas</t>
+          <t>pol</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Kaspa</t>
+          <t>POL (ex-MATIC)</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.04542232</v>
+        <v>0.120243</v>
       </c>
       <c r="F74" t="n">
-        <v>1259118653</v>
+        <v>1277184843</v>
       </c>
       <c r="G74" t="n">
         <v>73</v>
       </c>
       <c r="H74" t="n">
-        <v>23423308</v>
+        <v>95872465</v>
       </c>
       <c r="I74" t="n">
-        <v>0.04566325</v>
+        <v>0.121327</v>
       </c>
       <c r="J74" t="n">
-        <v>0.04102786</v>
+        <v>0.116262</v>
       </c>
       <c r="K74" t="n">
-        <v>0.00334235</v>
+        <v>0.00340135</v>
       </c>
       <c r="L74" t="n">
-        <v>7.91683</v>
+        <v>2.56314</v>
       </c>
       <c r="M74" t="n">
-        <v>27720927947.15285</v>
+        <v>10621663168.56562</v>
       </c>
       <c r="N74" t="n">
-        <v>27722506351.82228</v>
+        <v>10621663168.56562</v>
       </c>
       <c r="O74" t="n">
-        <v>0.207411</v>
+        <v>1.29</v>
       </c>
       <c r="P74" s="1" t="n">
-        <v>45504.69498842592</v>
+        <v>45364.45493055556</v>
       </c>
       <c r="Q74" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>0.0003733714761607935</v>
+        <v>0.0003717497365937372</v>
       </c>
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
@@ -6935,68 +6935,68 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>lighter</t>
+          <t>gatechain-token</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>lit</t>
+          <t>gt</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Lighter</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4.79</v>
+        <v>11.32</v>
       </c>
       <c r="F75" t="n">
-        <v>1196387939</v>
+        <v>1207191445</v>
       </c>
       <c r="G75" t="n">
         <v>74</v>
       </c>
       <c r="H75" t="n">
-        <v>90622785</v>
+        <v>3245938</v>
       </c>
       <c r="I75" t="n">
-        <v>4.93</v>
+        <v>11.52</v>
       </c>
       <c r="J75" t="n">
-        <v>4.69</v>
+        <v>10.91</v>
       </c>
       <c r="K75" t="n">
-        <v>-0.1230667607995493</v>
+        <v>0.410629</v>
       </c>
       <c r="L75" t="n">
-        <v>-2.44909</v>
+        <v>3.58984</v>
       </c>
       <c r="M75" t="n">
-        <v>250000000</v>
+        <v>106642631.3647594</v>
       </c>
       <c r="N75" t="n">
-        <v>1000000000</v>
+        <v>118893925.8661137</v>
       </c>
       <c r="O75" t="n">
-        <v>7.86</v>
+        <v>25.38</v>
       </c>
       <c r="P75" s="1" t="n">
-        <v>46021.04538194444</v>
+        <v>45682.66666666666</v>
       </c>
       <c r="Q75" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R75" t="b">
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>0.0003361665055125409</v>
+        <v>0.0003307192982520359</v>
       </c>
       <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr"/>
@@ -7010,68 +7010,68 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>gatechain-token</t>
+          <t>lighter</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>gt</t>
+          <t>lit</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Lighter</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>10.85</v>
+        <v>4.72</v>
       </c>
       <c r="F76" t="n">
-        <v>1157017948</v>
+        <v>1180731234</v>
       </c>
       <c r="G76" t="n">
         <v>75</v>
       </c>
       <c r="H76" t="n">
-        <v>2307769</v>
+        <v>58496380</v>
       </c>
       <c r="I76" t="n">
-        <v>10.94</v>
+        <v>4.89</v>
       </c>
       <c r="J76" t="n">
-        <v>10.66</v>
+        <v>4.69</v>
       </c>
       <c r="K76" t="n">
-        <v>0.02972548</v>
+        <v>-0.08699979852313344</v>
       </c>
       <c r="L76" t="n">
-        <v>0.1931</v>
+        <v>-1.87926</v>
       </c>
       <c r="M76" t="n">
-        <v>106641451.5494122</v>
+        <v>250000000</v>
       </c>
       <c r="N76" t="n">
-        <v>118892748.0467987</v>
+        <v>1000000000</v>
       </c>
       <c r="O76" t="n">
-        <v>25.38</v>
+        <v>7.86</v>
       </c>
       <c r="P76" s="1" t="n">
-        <v>45682.66666666666</v>
+        <v>46021.04538194444</v>
       </c>
       <c r="Q76" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R76" t="b">
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0003128165503442166</v>
+        <v>0.0003152082059638188</v>
       </c>
       <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr"/>
@@ -7085,7 +7085,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7104,34 +7104,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.348185</v>
+        <v>0.337782</v>
       </c>
       <c r="F77" t="n">
-        <v>1155689790</v>
+        <v>1121221656</v>
       </c>
       <c r="G77" t="n">
         <v>76</v>
       </c>
       <c r="H77" t="n">
-        <v>125061347</v>
+        <v>71175471</v>
       </c>
       <c r="I77" t="n">
-        <v>0.353561</v>
+        <v>0.349064</v>
       </c>
       <c r="J77" t="n">
-        <v>0.316158</v>
+        <v>0.333481</v>
       </c>
       <c r="K77" t="n">
-        <v>0.02654711</v>
+        <v>-0.00995213786966459</v>
       </c>
       <c r="L77" t="n">
-        <v>8.200060000000001</v>
+        <v>-3.12964</v>
       </c>
       <c r="M77" t="n">
         <v>3319369204.37</v>
       </c>
       <c r="N77" t="n">
-        <v>6861486658.154251</v>
+        <v>6861486605.78232</v>
       </c>
       <c r="O77" t="n">
         <v>2</v>
@@ -7140,13 +7140,13 @@
         <v>45322.29359953704</v>
       </c>
       <c r="Q77" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0003120288328728956</v>
+        <v>0.0002803234291042975</v>
       </c>
       <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr"/>
@@ -7160,7 +7160,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7179,34 +7179,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.116944</v>
+        <v>0.116621</v>
       </c>
       <c r="F78" t="n">
-        <v>1059206801</v>
+        <v>1056297663</v>
       </c>
       <c r="G78" t="n">
         <v>77</v>
       </c>
       <c r="H78" t="n">
-        <v>60144257</v>
+        <v>54255734</v>
       </c>
       <c r="I78" t="n">
-        <v>0.118949</v>
+        <v>0.122291</v>
       </c>
       <c r="J78" t="n">
-        <v>0.112661</v>
+        <v>0.114367</v>
       </c>
       <c r="K78" t="n">
-        <v>0.00046668</v>
+        <v>-0.00112436041593722</v>
       </c>
       <c r="L78" t="n">
-        <v>0.41247</v>
+        <v>-1.18246</v>
       </c>
       <c r="M78" t="n">
-        <v>9057191179.647024</v>
+        <v>9057509901.325378</v>
       </c>
       <c r="N78" t="n">
-        <v>9057345611.155615</v>
+        <v>9057560465.347652</v>
       </c>
       <c r="O78" t="n">
         <v>3.56</v>
@@ -7215,13 +7215,13 @@
         <v>43636.28563657407</v>
       </c>
       <c r="Q78" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R78" t="b">
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>0.0002548057192670042</v>
+        <v>0.0002422646983125228</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -7265,68 +7265,68 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>pi-network</t>
+          <t>render-token</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>pi</t>
+          <t>render</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Pi Network</t>
+          <t>Render</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.091715</v>
+        <v>2.04</v>
       </c>
       <c r="F79" t="n">
-        <v>1031168252</v>
+        <v>1056012807</v>
       </c>
       <c r="G79" t="n">
         <v>78</v>
       </c>
       <c r="H79" t="n">
-        <v>8549644</v>
+        <v>91707565</v>
       </c>
       <c r="I79" t="n">
-        <v>0.09243899999999999</v>
+        <v>2.09</v>
       </c>
       <c r="J79" t="n">
-        <v>0.088589</v>
+        <v>1.94</v>
       </c>
       <c r="K79" t="n">
-        <v>0.0019178</v>
+        <v>0.055344</v>
       </c>
       <c r="L79" t="n">
-        <v>2.1716</v>
+        <v>2.54596</v>
       </c>
       <c r="M79" t="n">
-        <v>11243022455.381</v>
+        <v>518776241.2826915</v>
       </c>
       <c r="N79" t="n">
-        <v>17296957623.66307</v>
+        <v>533536414.5626915</v>
       </c>
       <c r="O79" t="n">
-        <v>2.99</v>
+        <v>13.53</v>
       </c>
       <c r="P79" s="1" t="n">
-        <v>45714.36184027778</v>
+        <v>45368.35444444444</v>
       </c>
       <c r="Q79" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R79" t="b">
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0002381763311085243</v>
+        <v>0.0002420977144700714</v>
       </c>
       <c r="T79" t="inlineStr"/>
       <c r="U79" t="inlineStr"/>
@@ -7340,68 +7340,68 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>render-token</t>
+          <t>pi-network</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>render</t>
+          <t>pi</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Render</t>
+          <t>Pi Network</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1.97</v>
+        <v>0.091359</v>
       </c>
       <c r="F80" t="n">
-        <v>1022531450</v>
+        <v>1027154222</v>
       </c>
       <c r="G80" t="n">
         <v>79</v>
       </c>
       <c r="H80" t="n">
-        <v>86881391</v>
+        <v>5617919</v>
       </c>
       <c r="I80" t="n">
-        <v>2.03</v>
+        <v>0.092292</v>
       </c>
       <c r="J80" t="n">
-        <v>1.9</v>
+        <v>0.09067600000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>0.03418244</v>
+        <v>0.00039385</v>
       </c>
       <c r="L80" t="n">
-        <v>1.78692</v>
+        <v>0.38458</v>
       </c>
       <c r="M80" t="n">
-        <v>518776241.2826915</v>
+        <v>11243022455.381</v>
       </c>
       <c r="N80" t="n">
-        <v>533536414.5626915</v>
+        <v>17296957623.66307</v>
       </c>
       <c r="O80" t="n">
-        <v>13.53</v>
+        <v>2.99</v>
       </c>
       <c r="P80" s="1" t="n">
-        <v>45368.35444444444</v>
+        <v>45714.36184027778</v>
       </c>
       <c r="Q80" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R80" t="b">
         <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>0.0002330539286294967</v>
+        <v>0.0002251806847743386</v>
       </c>
       <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr"/>
@@ -7415,7 +7415,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7434,28 +7434,28 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.123629</v>
+        <v>0.125321</v>
       </c>
       <c r="F81" t="n">
-        <v>1012500582</v>
+        <v>1026222647</v>
       </c>
       <c r="G81" t="n">
         <v>80</v>
       </c>
       <c r="H81" t="n">
-        <v>36482428</v>
+        <v>26999028</v>
       </c>
       <c r="I81" t="n">
-        <v>0.123932</v>
+        <v>0.126484</v>
       </c>
       <c r="J81" t="n">
-        <v>0.11751</v>
+        <v>0.121647</v>
       </c>
       <c r="K81" t="n">
-        <v>0.00542943</v>
+        <v>0.0023243</v>
       </c>
       <c r="L81" t="n">
-        <v>4.64102</v>
+        <v>1.86023</v>
       </c>
       <c r="M81" t="n">
         <v>8188743036.341737</v>
@@ -7470,13 +7470,13 @@
         <v>44290.85721064815</v>
       </c>
       <c r="Q81" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R81" t="b">
         <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0.0002271047192913646</v>
+        <v>0.0002246345914042443</v>
       </c>
       <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr"/>
@@ -7490,7 +7490,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7509,28 +7509,28 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>7.34</v>
+        <v>7.35</v>
       </c>
       <c r="F82" t="n">
-        <v>1006756504</v>
+        <v>1007460396</v>
       </c>
       <c r="G82" t="n">
         <v>81</v>
       </c>
       <c r="H82" t="n">
-        <v>2930807</v>
+        <v>3147466</v>
       </c>
       <c r="I82" t="n">
-        <v>7.41</v>
+        <v>7.43</v>
       </c>
       <c r="J82" t="n">
         <v>7.3</v>
       </c>
       <c r="K82" t="n">
-        <v>-0.05190538893039687</v>
+        <v>-0.01908651121025873</v>
       </c>
       <c r="L82" t="n">
-        <v>-0.79274</v>
+        <v>-0.36652</v>
       </c>
       <c r="M82" t="n">
         <v>137155021.2773955</v>
@@ -7545,13 +7545,13 @@
         <v>44531.29832175926</v>
       </c>
       <c r="Q82" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R82" t="b">
         <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0.0002236979630189703</v>
+        <v>0.0002136360771899891</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -7595,608 +7595,608 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>blockchain-capital</t>
+          <t>cosmos</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>bcap</t>
+          <t>atom</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Blockchain Capital</t>
+          <t>Cosmos Hub</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>107.53</v>
+        <v>1.86</v>
       </c>
       <c r="F83" t="n">
-        <v>979825296</v>
+        <v>991343118</v>
       </c>
       <c r="G83" t="n">
         <v>82</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>79646205</v>
       </c>
       <c r="I83" t="n">
-        <v>107.53</v>
+        <v>1.92</v>
       </c>
       <c r="J83" t="n">
-        <v>107.53</v>
+        <v>1.82</v>
       </c>
       <c r="K83" t="n">
-        <v>1.4211e-14</v>
+        <v>0.02838852</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.35332</v>
       </c>
       <c r="M83" t="n">
-        <v>9112111</v>
+        <v>532857541.963055</v>
       </c>
       <c r="N83" t="n">
-        <v>9112111</v>
+        <v>532884992.164956</v>
       </c>
       <c r="O83" t="n">
-        <v>107.53</v>
+        <v>43.84</v>
       </c>
       <c r="P83" s="1" t="n">
-        <v>46287.17361111111</v>
+        <v>44458.66666666666</v>
       </c>
       <c r="Q83" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R83" t="b">
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.0002077253279368638</v>
-      </c>
-      <c r="T83" t="inlineStr"/>
-      <c r="U83" t="inlineStr"/>
-      <c r="V83" t="inlineStr"/>
-      <c r="W83" t="inlineStr"/>
-      <c r="X83" t="inlineStr"/>
-      <c r="Y83" t="inlineStr"/>
-      <c r="Z83" t="inlineStr"/>
-      <c r="AA83" t="inlineStr"/>
+        <v>0.000204188057803717</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Layer 0</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Proof of Stake (Tendermint)</t>
+        </is>
+      </c>
+      <c r="W83" t="n">
+        <v>2019</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>cosmos.network</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>Interoperabilidad entre blockchains soberanas</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>Blockchain propia (hub, Layer 0)</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>Se autodefine como el "Internet de las blockchains", enfocada en interoperabilidad.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>cosmos</t>
+          <t>blockchain-capital</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>atom</t>
+          <t>bcap</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Cosmos Hub</t>
+          <t>Blockchain Capital</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1.82</v>
+        <v>107.53</v>
       </c>
       <c r="F84" t="n">
-        <v>971545414</v>
+        <v>979825296</v>
       </c>
       <c r="G84" t="n">
         <v>83</v>
       </c>
       <c r="H84" t="n">
-        <v>70338630</v>
+        <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>1.84</v>
+        <v>107.53</v>
       </c>
       <c r="J84" t="n">
-        <v>1.75</v>
+        <v>107.53</v>
       </c>
       <c r="K84" t="n">
-        <v>0.01496126</v>
+        <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>0.83594</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>532679589.941325</v>
+        <v>9112111</v>
       </c>
       <c r="N84" t="n">
-        <v>532693432.459343</v>
+        <v>9112111</v>
       </c>
       <c r="O84" t="n">
-        <v>43.84</v>
+        <v>107.53</v>
       </c>
       <c r="P84" s="1" t="n">
-        <v>44458.66666666666</v>
+        <v>46287.17361111111</v>
       </c>
       <c r="Q84" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R84" t="b">
         <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0.0002028146112059655</v>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>Interoperabilidad</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>Layer 0</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>Proof of Stake (Tendermint)</t>
-        </is>
-      </c>
-      <c r="W84" t="n">
-        <v>2019</v>
-      </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>cosmos.network</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>Interoperabilidad entre blockchains soberanas</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>Blockchain propia (hub, Layer 0)</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>Se autodefine como el "Internet de las blockchains", enfocada en interoperabilidad.</t>
-        </is>
-      </c>
+        <v>0.0001974362597926862</v>
+      </c>
+      <c r="T84" t="inlineStr"/>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
+      <c r="W84" t="inlineStr"/>
+      <c r="X84" t="inlineStr"/>
+      <c r="Y84" t="inlineStr"/>
+      <c r="Z84" t="inlineStr"/>
+      <c r="AA84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>filecoin</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>fil</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Dash</t>
+          <t>Filecoin</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>69.95</v>
+        <v>1.13</v>
       </c>
       <c r="F85" t="n">
-        <v>898822093</v>
+        <v>941293895</v>
       </c>
       <c r="G85" t="n">
         <v>84</v>
       </c>
       <c r="H85" t="n">
-        <v>203716422</v>
+        <v>269952848</v>
       </c>
       <c r="I85" t="n">
-        <v>69.89</v>
+        <v>1.23</v>
       </c>
       <c r="J85" t="n">
-        <v>61.31</v>
+        <v>1.11</v>
       </c>
       <c r="K85" t="n">
-        <v>5.96</v>
+        <v>0.03173026</v>
       </c>
       <c r="L85" t="n">
-        <v>9.46149</v>
+        <v>2.72604</v>
       </c>
       <c r="M85" t="n">
-        <v>12843583.773267</v>
+        <v>831179167</v>
       </c>
       <c r="N85" t="n">
-        <v>12844558.462616</v>
+        <v>1957025314</v>
       </c>
       <c r="O85" t="n">
-        <v>1493.59</v>
+        <v>236.84</v>
       </c>
       <c r="P85" s="1" t="n">
-        <v>43088.66666666666</v>
+        <v>44287.22894675926</v>
       </c>
       <c r="Q85" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>0.0001596831234430739</v>
-      </c>
-      <c r="T85" t="inlineStr"/>
-      <c r="U85" t="inlineStr"/>
-      <c r="V85" t="inlineStr"/>
-      <c r="W85" t="inlineStr"/>
-      <c r="X85" t="inlineStr"/>
-      <c r="Y85" t="inlineStr"/>
-      <c r="Z85" t="inlineStr"/>
-      <c r="AA85" t="inlineStr"/>
+        <v>0.0001748489827333574</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Almacenamiento descentralizado</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Infraestructura Web3</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Proof-of-Replication/Spacetime</t>
+        </is>
+      </c>
+      <c r="W85" t="n">
+        <v>2020</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>filecoin.io</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>Almacenamiento descentralizado de archivos</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Layer 1)</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>Recompensa a quienes ofrecen espacio de almacenamiento descentralizado.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>aerodrome-finance</t>
+          <t>pancakeswap-token</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>aero</t>
+          <t>cake</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Aerodrome Finance</t>
+          <t>PancakeSwap</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.902818</v>
+        <v>2.85</v>
       </c>
       <c r="F86" t="n">
-        <v>899670268</v>
+        <v>908529695</v>
       </c>
       <c r="G86" t="n">
         <v>85</v>
       </c>
       <c r="H86" t="n">
-        <v>194318021</v>
+        <v>77912488</v>
       </c>
       <c r="I86" t="n">
-        <v>0.928633</v>
+        <v>2.85</v>
       </c>
       <c r="J86" t="n">
-        <v>0.778429</v>
+        <v>2.73</v>
       </c>
       <c r="K86" t="n">
-        <v>0.117348</v>
+        <v>0.076643</v>
       </c>
       <c r="L86" t="n">
-        <v>14.85755</v>
+        <v>2.67349</v>
       </c>
       <c r="M86" t="n">
-        <v>996440490.4616158</v>
+        <v>319007063.5169999</v>
       </c>
       <c r="N86" t="n">
-        <v>1988034890.229641</v>
+        <v>330627631.389633</v>
       </c>
       <c r="O86" t="n">
-        <v>2.32</v>
+        <v>43.96</v>
       </c>
       <c r="P86" s="1" t="n">
-        <v>45633.25043981482</v>
+        <v>44316.08914351852</v>
       </c>
       <c r="Q86" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0.0001601861677090707</v>
-      </c>
-      <c r="T86" t="inlineStr"/>
-      <c r="U86" t="inlineStr"/>
-      <c r="V86" t="inlineStr"/>
-      <c r="W86" t="inlineStr"/>
-      <c r="X86" t="inlineStr"/>
-      <c r="Y86" t="inlineStr"/>
-      <c r="Z86" t="inlineStr"/>
-      <c r="AA86" t="inlineStr"/>
+        <v>0.0001556424643140749</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>DeFi</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Exchange descentralizado</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>N/A (token BEP-20)</t>
+        </is>
+      </c>
+      <c r="W86" t="n">
+        <v>2020</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>pancakeswap.finance</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>Intercambio descentralizado en BNB Chain</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>Token BEP-20 sobre BNB Chain</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>Principal exchange descentralizado (DEX) del ecosistema BNB Chain.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>filecoin</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>fil</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Filecoin</t>
+          <t>Dash</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1.077</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="F87" t="n">
-        <v>894854410</v>
+        <v>873971493</v>
       </c>
       <c r="G87" t="n">
         <v>86</v>
       </c>
       <c r="H87" t="n">
-        <v>156645519</v>
+        <v>247801178</v>
       </c>
       <c r="I87" t="n">
-        <v>1.1</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="J87" t="n">
-        <v>0.996161</v>
+        <v>67.39</v>
       </c>
       <c r="K87" t="n">
-        <v>0.054072</v>
+        <v>-3.421776370279872</v>
       </c>
       <c r="L87" t="n">
-        <v>5.26212</v>
+        <v>-5.54929</v>
       </c>
       <c r="M87" t="n">
-        <v>831111902</v>
+        <v>12844541.1311104</v>
       </c>
       <c r="N87" t="n">
-        <v>1957027561</v>
+        <v>12845072.79742164</v>
       </c>
       <c r="O87" t="n">
-        <v>236.84</v>
+        <v>1493.59</v>
       </c>
       <c r="P87" s="1" t="n">
-        <v>44287.22894675926</v>
+        <v>43088.66666666666</v>
       </c>
       <c r="Q87" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S87" t="n">
-        <v>0.0001573299296063742</v>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>Almacenamiento descentralizado</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>Infraestructura Web3</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>Proof-of-Replication/Spacetime</t>
-        </is>
-      </c>
-      <c r="W87" t="n">
-        <v>2020</v>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>filecoin.io</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>Almacenamiento descentralizado de archivos</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Layer 1)</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>Recompensa a quienes ofrecen espacio de almacenamiento descentralizado.</t>
-        </is>
-      </c>
+        <v>0.0001353842940169126</v>
+      </c>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="inlineStr"/>
+      <c r="X87" t="inlineStr"/>
+      <c r="Y87" t="inlineStr"/>
+      <c r="Z87" t="inlineStr"/>
+      <c r="AA87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>pancakeswap-token</t>
+          <t>nexo</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>cake</t>
+          <t>nexo</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>PancakeSwap</t>
+          <t>NEXO</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2.77</v>
+        <v>0.8730869999999999</v>
       </c>
       <c r="F88" t="n">
-        <v>885011773</v>
+        <v>873086578</v>
       </c>
       <c r="G88" t="n">
         <v>87</v>
       </c>
       <c r="H88" t="n">
-        <v>92529235</v>
+        <v>2294259</v>
       </c>
       <c r="I88" t="n">
-        <v>2.83</v>
+        <v>0.877911</v>
       </c>
       <c r="J88" t="n">
-        <v>2.74</v>
+        <v>0.860154</v>
       </c>
       <c r="K88" t="n">
-        <v>0.00491875</v>
+        <v>0.01323611</v>
       </c>
       <c r="L88" t="n">
-        <v>0.19917</v>
+        <v>1.53336</v>
       </c>
       <c r="M88" t="n">
-        <v>319003107.6029418</v>
+        <v>1000000000</v>
       </c>
       <c r="N88" t="n">
-        <v>330627631.389633</v>
+        <v>1000000000</v>
       </c>
       <c r="O88" t="n">
-        <v>43.96</v>
+        <v>4.07</v>
       </c>
       <c r="P88" s="1" t="n">
-        <v>44316.08914351852</v>
+        <v>44328.27623842593</v>
       </c>
       <c r="Q88" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R88" t="b">
         <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>0.0001514923582264852</v>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>DeFi</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>Exchange descentralizado</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>N/A (token BEP-20)</t>
-        </is>
-      </c>
-      <c r="W88" t="n">
-        <v>2020</v>
-      </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>pancakeswap.finance</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>Intercambio descentralizado en BNB Chain</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>Token BEP-20 sobre BNB Chain</t>
-        </is>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>Principal exchange descentralizado (DEX) del ecosistema BNB Chain.</t>
-        </is>
-      </c>
+        <v>0.0001348655529444311</v>
+      </c>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="inlineStr"/>
+      <c r="X88" t="inlineStr"/>
+      <c r="Y88" t="inlineStr"/>
+      <c r="Z88" t="inlineStr"/>
+      <c r="AA88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>nexo</t>
+          <t>aerodrome-finance</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>nexo</t>
+          <t>aero</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NEXO</t>
+          <t>Aerodrome Finance</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.861675</v>
+        <v>0.838323</v>
       </c>
       <c r="F89" t="n">
-        <v>861531313</v>
+        <v>834868741</v>
       </c>
       <c r="G89" t="n">
         <v>88</v>
       </c>
       <c r="H89" t="n">
-        <v>4126065</v>
+        <v>58811903</v>
       </c>
       <c r="I89" t="n">
-        <v>0.878094</v>
+        <v>0.906338</v>
       </c>
       <c r="J89" t="n">
-        <v>0.860256</v>
+        <v>0.835148</v>
       </c>
       <c r="K89" t="n">
-        <v>-0.01030049736247129</v>
+        <v>-0.05729116391142453</v>
       </c>
       <c r="L89" t="n">
-        <v>-1.39503</v>
+        <v>-6.73881</v>
       </c>
       <c r="M89" t="n">
-        <v>1000000000</v>
+        <v>995878990.7676159</v>
       </c>
       <c r="N89" t="n">
-        <v>1000000000</v>
+        <v>1988034890.229641</v>
       </c>
       <c r="O89" t="n">
-        <v>4.07</v>
+        <v>2.32</v>
       </c>
       <c r="P89" s="1" t="n">
-        <v>44328.27623842593</v>
+        <v>45633.25043981482</v>
       </c>
       <c r="Q89" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S89" t="n">
-        <v>0.0001375663279073106</v>
+        <v>0.0001124620884836588</v>
       </c>
       <c r="T89" t="inlineStr"/>
       <c r="U89" t="inlineStr"/>
@@ -8210,7 +8210,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8229,28 +8229,28 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.009570739999999999</v>
+        <v>0.009290690000000001</v>
       </c>
       <c r="F90" t="n">
-        <v>822603089</v>
+        <v>798860722</v>
       </c>
       <c r="G90" t="n">
         <v>89</v>
       </c>
       <c r="H90" t="n">
-        <v>16882621</v>
+        <v>12727870</v>
       </c>
       <c r="I90" t="n">
-        <v>0.00982453</v>
+        <v>0.009642649999999999</v>
       </c>
       <c r="J90" t="n">
-        <v>0.00921142</v>
+        <v>0.0090861</v>
       </c>
       <c r="K90" t="n">
-        <v>0.00015465</v>
+        <v>-0.000247057142484391</v>
       </c>
       <c r="L90" t="n">
-        <v>1.51333</v>
+        <v>-2.59179</v>
       </c>
       <c r="M90" t="n">
         <v>85985041177</v>
@@ -8265,13 +8265,13 @@
         <v>44304.71413194444</v>
       </c>
       <c r="Q90" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R90" t="b">
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>0.0001144783804098757</v>
+        <v>9.135402907230818e-05</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8334,28 +8334,28 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>7.72</v>
+        <v>7.8</v>
       </c>
       <c r="F91" t="n">
-        <v>771644501</v>
+        <v>779556411</v>
       </c>
       <c r="G91" t="n">
         <v>90</v>
       </c>
       <c r="H91" t="n">
-        <v>135312541</v>
+        <v>75993346</v>
       </c>
       <c r="I91" t="n">
-        <v>8.289999999999999</v>
+        <v>7.91</v>
       </c>
       <c r="J91" t="n">
-        <v>7.72</v>
+        <v>7.53</v>
       </c>
       <c r="K91" t="n">
-        <v>-0.5346314063898721</v>
+        <v>0.02302876</v>
       </c>
       <c r="L91" t="n">
-        <v>-6.36509</v>
+        <v>0.11708</v>
       </c>
       <c r="M91" t="n">
         <v>100000000</v>
@@ -8370,13 +8370,13 @@
         <v>45365.29608796296</v>
       </c>
       <c r="Q91" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>8.42553421256885e-05</v>
+        <v>8.00377568974021e-05</v>
       </c>
       <c r="T91" t="inlineStr"/>
       <c r="U91" t="inlineStr"/>
@@ -8390,68 +8390,68 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>akedo</t>
+          <t>superstate-short-duration-us-government-securities-fund-ustb</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ake</t>
+          <t>ustb</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Akedo</t>
+          <t>Invesco Short Duration US Government Securities Fund</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.03331356</v>
+        <v>11.22</v>
       </c>
       <c r="F92" t="n">
-        <v>759306553</v>
+        <v>755835754</v>
       </c>
       <c r="G92" t="n">
         <v>91</v>
       </c>
       <c r="H92" t="n">
-        <v>27698737</v>
+        <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>0.03884774</v>
+        <v>11.22</v>
       </c>
       <c r="J92" t="n">
-        <v>0.03173795</v>
+        <v>11.22</v>
       </c>
       <c r="K92" t="n">
-        <v>-0.002265419230698736</v>
+        <v>-1.776e-15</v>
       </c>
       <c r="L92" t="n">
-        <v>-6.40924</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>22796250000</v>
+        <v>67344915.025351</v>
       </c>
       <c r="N92" t="n">
-        <v>100000000000</v>
+        <v>67362730.289611</v>
       </c>
       <c r="O92" t="n">
-        <v>0.146656</v>
+        <v>11.22</v>
       </c>
       <c r="P92" s="1" t="n">
-        <v>46285.43993055556</v>
+        <v>46290.60069444445</v>
       </c>
       <c r="Q92" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>7.693782628807716e-05</v>
+        <v>6.613260323615043e-05</v>
       </c>
       <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr"/>
@@ -8465,7 +8465,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8487,7 +8487,7 @@
         <v>1.21</v>
       </c>
       <c r="F93" t="n">
-        <v>750951665</v>
+        <v>753192661</v>
       </c>
       <c r="G93" t="n">
         <v>92</v>
@@ -8502,10 +8502,10 @@
         <v>1.21</v>
       </c>
       <c r="K93" t="n">
-        <v>-0.001218802952861919</v>
+        <v>0.00360208</v>
       </c>
       <c r="L93" t="n">
-        <v>-0.10087</v>
+        <v>0.29842</v>
       </c>
       <c r="M93" t="n">
         <v>622138754.14688</v>
@@ -8520,13 +8520,13 @@
         <v>46049.54175925926</v>
       </c>
       <c r="Q93" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R93" t="b">
         <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>7.198262423491006e-05</v>
+        <v>6.458321047245174e-05</v>
       </c>
       <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr"/>
@@ -8540,68 +8540,68 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>superstate-short-duration-us-government-securities-fund-ustb</t>
+          <t>akedo</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ustb</t>
+          <t>ake</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Invesco Short Duration US Government Securities Fund</t>
+          <t>Akedo</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>11.22</v>
+        <v>0.03295427</v>
       </c>
       <c r="F94" t="n">
-        <v>750639257</v>
+        <v>751233720</v>
       </c>
       <c r="G94" t="n">
         <v>93</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>10660053</v>
       </c>
       <c r="I94" t="n">
-        <v>11.22</v>
+        <v>0.03490335</v>
       </c>
       <c r="J94" t="n">
-        <v>11.22</v>
+        <v>0.03231072</v>
       </c>
       <c r="K94" t="n">
-        <v>-1.776e-15</v>
+        <v>-0.0005019983910915169</v>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>-1.63124</v>
       </c>
       <c r="M94" t="n">
-        <v>66881907.490516</v>
+        <v>22796250000</v>
       </c>
       <c r="N94" t="n">
-        <v>67220432.10558</v>
+        <v>100000000000</v>
       </c>
       <c r="O94" t="n">
-        <v>11.22</v>
+        <v>0.146656</v>
       </c>
       <c r="P94" s="1" t="n">
-        <v>46290.60069444445</v>
+        <v>46285.43993055556</v>
       </c>
       <c r="Q94" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R94" t="b">
         <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>7.179733811700808e-05</v>
+        <v>6.343487062594893e-05</v>
       </c>
       <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
@@ -8615,7 +8615,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8634,34 +8634,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.851433</v>
+        <v>0.844279</v>
       </c>
       <c r="F95" t="n">
-        <v>741492801</v>
+        <v>735259936</v>
       </c>
       <c r="G95" t="n">
         <v>94</v>
       </c>
       <c r="H95" t="n">
-        <v>75433484</v>
+        <v>73602536</v>
       </c>
       <c r="I95" t="n">
-        <v>0.884076</v>
+        <v>0.8880710000000001</v>
       </c>
       <c r="J95" t="n">
-        <v>0.821013</v>
+        <v>0.823677</v>
       </c>
       <c r="K95" t="n">
-        <v>0.00793612</v>
+        <v>-0.01321669499369493</v>
       </c>
       <c r="L95" t="n">
-        <v>0.9504899999999999</v>
+        <v>-1.68815</v>
       </c>
       <c r="M95" t="n">
-        <v>870824126.8087161</v>
+        <v>870873636.8145826</v>
       </c>
       <c r="N95" t="n">
-        <v>1209264224.764171</v>
+        <v>1209313832.95197</v>
       </c>
       <c r="O95" t="n">
         <v>19.92</v>
@@ -8670,13 +8670,13 @@
         <v>44952.26755787037</v>
       </c>
       <c r="Q95" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R95" t="b">
         <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>6.637266485383536e-05</v>
+        <v>5.407096805479993e-05</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8739,31 +8739,31 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.02629561</v>
+        <v>0.0273212</v>
       </c>
       <c r="F96" t="n">
-        <v>700826412</v>
+        <v>729438612</v>
       </c>
       <c r="G96" t="n">
         <v>95</v>
       </c>
       <c r="H96" t="n">
-        <v>7435307</v>
+        <v>8924569</v>
       </c>
       <c r="I96" t="n">
-        <v>0.02648915</v>
+        <v>0.02784859</v>
       </c>
       <c r="J96" t="n">
-        <v>0.0261506</v>
+        <v>0.02632666</v>
       </c>
       <c r="K96" t="n">
-        <v>-1.4782660178021e-05</v>
+        <v>0.00100423</v>
       </c>
       <c r="L96" t="n">
-        <v>-0.0921</v>
+        <v>3.83836</v>
       </c>
       <c r="M96" t="n">
-        <v>26667653978</v>
+        <v>26698629629</v>
       </c>
       <c r="N96" t="n">
         <v>100000000000</v>
@@ -8775,13 +8775,13 @@
         <v>46156.97986111111</v>
       </c>
       <c r="Q96" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R96" t="b">
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>4.225382875840334e-05</v>
+        <v>5.065848227365432e-05</v>
       </c>
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
@@ -8795,68 +8795,68 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>ether-fi</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>ethfi</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>GHO</t>
+          <t>Ether.fi</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.999358</v>
+        <v>0.726699</v>
       </c>
       <c r="F97" t="n">
-        <v>698549235</v>
+        <v>701519313</v>
       </c>
       <c r="G97" t="n">
         <v>96</v>
       </c>
       <c r="H97" t="n">
-        <v>8380549</v>
+        <v>48866275</v>
       </c>
       <c r="I97" t="n">
-        <v>0.999463</v>
+        <v>0.77495</v>
       </c>
       <c r="J97" t="n">
-        <v>0.998962</v>
+        <v>0.715746</v>
       </c>
       <c r="K97" t="n">
-        <v>0.00032863</v>
+        <v>-0.01192318502549083</v>
       </c>
       <c r="L97" t="n">
-        <v>0.02713</v>
+        <v>-1.7926</v>
       </c>
       <c r="M97" t="n">
-        <v>699000000</v>
+        <v>965350000</v>
       </c>
       <c r="N97" t="n">
-        <v>699000000</v>
+        <v>965350000</v>
       </c>
       <c r="O97" t="n">
-        <v>1.03</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="P97" s="1" t="n">
-        <v>45350.38608796296</v>
+        <v>45378.63525462963</v>
       </c>
       <c r="Q97" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R97" t="b">
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>4.090325743466747e-05</v>
+        <v>3.42920661701952e-05</v>
       </c>
       <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr"/>
@@ -8870,68 +8870,68 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ether-fi</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ethfi</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Ether.fi</t>
+          <t>GHO</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.722031</v>
+        <v>0.999126</v>
       </c>
       <c r="F98" t="n">
-        <v>696754452</v>
+        <v>698389404</v>
       </c>
       <c r="G98" t="n">
         <v>97</v>
       </c>
       <c r="H98" t="n">
-        <v>48061733</v>
+        <v>5829779</v>
       </c>
       <c r="I98" t="n">
-        <v>0.733568</v>
+        <v>0.99955</v>
       </c>
       <c r="J98" t="n">
-        <v>0.693392</v>
+        <v>0.999075</v>
       </c>
       <c r="K98" t="n">
-        <v>0.01214067</v>
+        <v>-0.000268288243765125</v>
       </c>
       <c r="L98" t="n">
-        <v>1.65693</v>
+        <v>-0.02899</v>
       </c>
       <c r="M98" t="n">
-        <v>965350000</v>
+        <v>699000000</v>
       </c>
       <c r="N98" t="n">
-        <v>965350000</v>
+        <v>699000000</v>
       </c>
       <c r="O98" t="n">
-        <v>8.529999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="P98" s="1" t="n">
-        <v>45378.63525462963</v>
+        <v>45350.38608796296</v>
       </c>
       <c r="Q98" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R98" t="b">
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>3.983878925668718e-05</v>
+        <v>3.245729972208482e-05</v>
       </c>
       <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr"/>
@@ -8945,68 +8945,68 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>blockstack</t>
+          <t>pyth-network</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>stx</t>
+          <t>pyth</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Stacks</t>
+          <t>Pyth Network</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.34205</v>
+        <v>0.084497</v>
       </c>
       <c r="F99" t="n">
-        <v>640435847</v>
+        <v>665409755</v>
       </c>
       <c r="G99" t="n">
         <v>98</v>
       </c>
       <c r="H99" t="n">
-        <v>45309726</v>
+        <v>76338725</v>
       </c>
       <c r="I99" t="n">
-        <v>0.354392</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="J99" t="n">
-        <v>0.317674</v>
+        <v>0.07602100000000001</v>
       </c>
       <c r="K99" t="n">
-        <v>0.0143636</v>
+        <v>0.0068687</v>
       </c>
       <c r="L99" t="n">
-        <v>4.63936</v>
+        <v>8.45149</v>
       </c>
       <c r="M99" t="n">
-        <v>1869484493.906829</v>
+        <v>7874959366.564093</v>
       </c>
       <c r="N99" t="n">
-        <v>1869484493.906829</v>
+        <v>10000000000</v>
       </c>
       <c r="O99" t="n">
-        <v>3.86</v>
+        <v>1.2</v>
       </c>
       <c r="P99" s="1" t="n">
-        <v>45383.19094907407</v>
+        <v>45366.95920138889</v>
       </c>
       <c r="Q99" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S99" t="n">
-        <v>6.436777508892736e-06</v>
+        <v>1.31244841496011e-05</v>
       </c>
       <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr"/>
@@ -9020,7 +9020,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9039,34 +9039,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.01004023</v>
+        <v>0.01028858</v>
       </c>
       <c r="F100" t="n">
-        <v>631292348</v>
+        <v>646744381</v>
       </c>
       <c r="G100" t="n">
         <v>99</v>
       </c>
       <c r="H100" t="n">
-        <v>231573455</v>
+        <v>226596574</v>
       </c>
       <c r="I100" t="n">
-        <v>0.01045105</v>
+        <v>0.01089866</v>
       </c>
       <c r="J100" t="n">
-        <v>0.009655270000000001</v>
+        <v>0.00968985</v>
       </c>
       <c r="K100" t="n">
-        <v>8.313999999999999e-05</v>
+        <v>0.00019913</v>
       </c>
       <c r="L100" t="n">
-        <v>0.90963</v>
+        <v>1.84229</v>
       </c>
       <c r="M100" t="n">
         <v>62860396090</v>
       </c>
       <c r="N100" t="n">
-        <v>76722802826.57365</v>
+        <v>76722802065.26431</v>
       </c>
       <c r="O100" t="n">
         <v>0.06844699999999999</v>
@@ -9075,13 +9075,13 @@
         <v>45643.21206018519</v>
       </c>
       <c r="Q100" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R100" t="b">
         <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>1.013858013391262e-06</v>
+        <v>2.182759659645712e-06</v>
       </c>
       <c r="T100" t="inlineStr"/>
       <c r="U100" t="inlineStr"/>
@@ -9095,62 +9095,62 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>flare-networks</t>
+          <t>blockstack</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>flr</t>
+          <t>stx</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Flare</t>
+          <t>Stacks</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.00724299</v>
+        <v>0.343903</v>
       </c>
       <c r="F101" t="n">
-        <v>629582898</v>
+        <v>643020834</v>
       </c>
       <c r="G101" t="n">
         <v>100</v>
       </c>
       <c r="H101" t="n">
-        <v>3598829</v>
+        <v>39789264</v>
       </c>
       <c r="I101" t="n">
-        <v>0.00736006</v>
+        <v>0.359663</v>
       </c>
       <c r="J101" t="n">
-        <v>0.00721363</v>
+        <v>0.33177</v>
       </c>
       <c r="K101" t="n">
-        <v>-6.687276971504101e-05</v>
+        <v>0.00180173</v>
       </c>
       <c r="L101" t="n">
-        <v>-0.91779</v>
+        <v>0.39596</v>
       </c>
       <c r="M101" t="n">
-        <v>86930131704.80014</v>
+        <v>1869771711.979279</v>
       </c>
       <c r="N101" t="n">
-        <v>106628765964.3372</v>
+        <v>1869771711.979279</v>
       </c>
       <c r="O101" t="n">
-        <v>0.150073</v>
+        <v>3.86</v>
       </c>
       <c r="P101" s="1" t="n">
-        <v>44935.80144675926</v>
+        <v>45383.19094907407</v>
       </c>
       <c r="Q101" s="1" t="n">
-        <v>46291.55798611111</v>
+        <v>46292.596875</v>
       </c>
       <c r="R101" t="b">
         <v>0</v>

--- a/src/xlsx/enriched_data.xlsx
+++ b/src/xlsx/enriched_data.xlsx
@@ -560,7 +560,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -579,34 +579,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>84945</v>
+        <v>83628</v>
       </c>
       <c r="F2" t="n">
-        <v>1706532619602</v>
+        <v>1680129050993</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>21184097131</v>
+        <v>40095045364</v>
       </c>
       <c r="I2" t="n">
-        <v>85089</v>
+        <v>84945</v>
       </c>
       <c r="J2" t="n">
-        <v>83835</v>
+        <v>82581</v>
       </c>
       <c r="K2" t="n">
-        <v>994.61</v>
+        <v>-800.5256324028014</v>
       </c>
       <c r="L2" t="n">
-        <v>1.14458</v>
+        <v>-0.9496</v>
       </c>
       <c r="M2" t="n">
-        <v>20089965</v>
+        <v>20090481</v>
       </c>
       <c r="N2" t="n">
-        <v>20090134</v>
+        <v>20090481</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -615,7 +615,7 @@
         <v>45936.45673611111</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
@@ -665,7 +665,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -684,34 +684,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2704.75</v>
+        <v>2684.27</v>
       </c>
       <c r="F3" t="n">
-        <v>330207990871</v>
+        <v>327704876617</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>7613539121</v>
+        <v>15847058740</v>
       </c>
       <c r="I3" t="n">
-        <v>2720.75</v>
+        <v>2698.21</v>
       </c>
       <c r="J3" t="n">
-        <v>2666.72</v>
+        <v>2636.99</v>
       </c>
       <c r="K3" t="n">
-        <v>17.76</v>
+        <v>-4.079040065399113</v>
       </c>
       <c r="L3" t="n">
-        <v>0.58869</v>
+        <v>-0.1606</v>
       </c>
       <c r="M3" t="n">
-        <v>122084677.7313143</v>
+        <v>122087473.8258867</v>
       </c>
       <c r="N3" t="n">
-        <v>122084677.7313143</v>
+        <v>122087473.8258867</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -720,13 +720,13 @@
         <v>45893.47295138889</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1931924377023068</v>
+        <v>0.1947520924015897</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -789,31 +789,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999839</v>
+        <v>0.999806</v>
       </c>
       <c r="F4" t="n">
-        <v>183789253110</v>
+        <v>183775189298</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>41514989094</v>
+        <v>71523929844</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999873</v>
+        <v>0.999854</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999715</v>
+        <v>0.999602</v>
       </c>
       <c r="K4" t="n">
-        <v>1.089e-05</v>
+        <v>6.45e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.001</v>
+        <v>0.00226</v>
       </c>
       <c r="M4" t="n">
-        <v>183818815967.1891</v>
+        <v>183818815964.5838</v>
       </c>
       <c r="N4" t="n">
         <v>189285761986.9062</v>
@@ -825,13 +825,13 @@
         <v>43304.66666666666</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1073611284155017</v>
+        <v>0.1090548076659088</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -894,34 +894,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>779.8099999999999</v>
+        <v>766.03</v>
       </c>
       <c r="F5" t="n">
-        <v>103839803578</v>
+        <v>102003832094</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>709749417</v>
+        <v>1032103584</v>
       </c>
       <c r="I5" t="n">
-        <v>782.71</v>
+        <v>783.74</v>
       </c>
       <c r="J5" t="n">
-        <v>766.86</v>
+        <v>757.15</v>
       </c>
       <c r="K5" t="n">
-        <v>7.32</v>
+        <v>-9.840246612364126</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8614000000000001</v>
+        <v>-1.27744</v>
       </c>
       <c r="M5" t="n">
-        <v>133159695.65</v>
+        <v>133159627.49</v>
       </c>
       <c r="N5" t="n">
-        <v>133159692.37</v>
+        <v>133159623.53</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -930,13 +930,13 @@
         <v>45943.02875</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06049440879323557</v>
+        <v>0.06036726160042665</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -999,28 +999,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="F6" t="n">
-        <v>96195766748</v>
+        <v>93930368802</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2780906745</v>
+        <v>4038950114</v>
       </c>
       <c r="I6" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.01407680591755334</v>
+        <v>-0.02702585931666324</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.07668</v>
+        <v>-1.80241</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -1035,13 +1035,13 @@
         <v>45855.82005787037</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R6" t="b">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05601344071914651</v>
+        <v>0.0555602346734234</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1104,34 +1104,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.99999</v>
+        <v>0.999896</v>
       </c>
       <c r="F7" t="n">
-        <v>75195810814</v>
+        <v>74840870406</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>9492352280</v>
+        <v>24447087511</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0.9999400000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999451</v>
+        <v>0.99954</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00010164</v>
+        <v>2.851e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0074</v>
+        <v>-0.00016</v>
       </c>
       <c r="M7" t="n">
-        <v>75196575861.07713</v>
+        <v>74852146130.23332</v>
       </c>
       <c r="N7" t="n">
-        <v>75209861269.7758</v>
+        <v>74843470364.92506</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -1140,13 +1140,13 @@
         <v>43418.66666666666</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04370317401187176</v>
+        <v>0.04419414189593023</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1209,34 +1209,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>122.88</v>
+        <v>118.84</v>
       </c>
       <c r="F8" t="n">
-        <v>72226558654</v>
+        <v>69846507958</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>3632253379</v>
+        <v>4138249881</v>
       </c>
       <c r="I8" t="n">
-        <v>124.77</v>
+        <v>123.36</v>
       </c>
       <c r="J8" t="n">
-        <v>120.11</v>
+        <v>117.57</v>
       </c>
       <c r="K8" t="n">
-        <v>1.94</v>
+        <v>-3.085955386790999</v>
       </c>
       <c r="L8" t="n">
-        <v>1.39633</v>
+        <v>-2.55265</v>
       </c>
       <c r="M8" t="n">
-        <v>587783255.1105938</v>
+        <v>587781862.721426</v>
       </c>
       <c r="N8" t="n">
-        <v>634841718.6764878</v>
+        <v>634840553.4996796</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -1245,13 +1245,13 @@
         <v>45676.13572916666</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R8" t="b">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.04196258531132255</v>
+        <v>0.0412204447473299</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1314,34 +1314,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.333493</v>
+        <v>0.33473</v>
       </c>
       <c r="F9" t="n">
-        <v>31670810269</v>
+        <v>31789740830</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>346156219</v>
+        <v>374027967</v>
       </c>
       <c r="I9" t="n">
-        <v>0.336714</v>
+        <v>0.335666</v>
       </c>
       <c r="J9" t="n">
-        <v>0.33245</v>
+        <v>0.332966</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.002821045035316549</v>
+        <v>0.00079635</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.84712</v>
+        <v>0.22394</v>
       </c>
       <c r="M9" t="n">
-        <v>94967057481.15408</v>
+        <v>94972937401.45468</v>
       </c>
       <c r="N9" t="n">
-        <v>94971253492.20189</v>
+        <v>94972951495.66699</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1350,13 +1350,13 @@
         <v>45629.67407407407</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01818862689438308</v>
+        <v>0.01856103604966932</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1419,34 +1419,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1643.08</v>
+        <v>1520.86</v>
       </c>
       <c r="F10" t="n">
-        <v>27858352423</v>
+        <v>25781910827</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>1413804468</v>
+        <v>1007938825</v>
       </c>
       <c r="I10" t="n">
-        <v>1687.78</v>
+        <v>1612.88</v>
       </c>
       <c r="J10" t="n">
-        <v>1546.39</v>
+        <v>1510.24</v>
       </c>
       <c r="K10" t="n">
-        <v>101.84</v>
+        <v>-60.80843903747132</v>
       </c>
       <c r="L10" t="n">
-        <v>6.20596</v>
+        <v>-3.87843</v>
       </c>
       <c r="M10" t="n">
         <v>16954918.9155448</v>
       </c>
       <c r="N10" t="n">
-        <v>16955384.5405448</v>
+        <v>16957395.4780448</v>
       </c>
       <c r="O10" t="n">
         <v>3191.93</v>
@@ -1455,13 +1455,13 @@
         <v>42671.66666666666</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01595374730501611</v>
+        <v>0.01498390941234429</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1524,34 +1524,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.058</v>
+        <v>1.059</v>
       </c>
       <c r="F11" t="n">
-        <v>24516003984</v>
+        <v>24577771416</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>401487</v>
+        <v>24871973</v>
       </c>
       <c r="I11" t="n">
-        <v>1.062</v>
+        <v>1.061</v>
       </c>
       <c r="J11" t="n">
-        <v>1.016</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0316886</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>3.09073</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>23181959779.848</v>
+        <v>23202972251.118</v>
       </c>
       <c r="N11" t="n">
-        <v>23193525454.108</v>
+        <v>23202972251.118</v>
       </c>
       <c r="O11" t="n">
         <v>1.062</v>
@@ -1560,13 +1560,13 @@
         <v>46292.546875</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>46292.54976851852</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R11" t="b">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01399444792162468</v>
+        <v>0.01426695184863325</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
@@ -1580,7 +1580,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1599,28 +1599,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>92.06999999999999</v>
+        <v>88.73</v>
       </c>
       <c r="F12" t="n">
-        <v>20480194044</v>
+        <v>19730034003</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>607402270</v>
+        <v>946302648</v>
       </c>
       <c r="I12" t="n">
-        <v>93.84999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>91.06</v>
+        <v>86.95</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1449201937953575</v>
+        <v>-2.541052861800551</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.28565</v>
+        <v>-2.84228</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1635,13 +1635,13 @@
         <v>46288.22002314815</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R12" t="b">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01162863835052777</v>
+        <v>0.01138055682378397</v>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
@@ -1655,7 +1655,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1674,34 +1674,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.09762</v>
+        <v>0.094098</v>
       </c>
       <c r="F13" t="n">
-        <v>15237393273</v>
+        <v>14688879088</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>773469735</v>
+        <v>1186766570</v>
       </c>
       <c r="I13" t="n">
-        <v>0.098832</v>
+        <v>0.09775</v>
       </c>
       <c r="J13" t="n">
-        <v>0.095327</v>
+        <v>0.09178600000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00030094</v>
+        <v>-0.002719752810769568</v>
       </c>
       <c r="L13" t="n">
-        <v>0.11394</v>
+        <v>-2.81425</v>
       </c>
       <c r="M13" t="n">
-        <v>156089086383.7052</v>
+        <v>156104906383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171801603126.579</v>
+        <v>156104946383.7052</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1710,13 +1710,13 @@
         <v>44323.88082175926</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R13" t="b">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.008555285435552284</v>
+        <v>0.008378998936772549</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1779,28 +1779,28 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>14.11</v>
+        <v>15.24</v>
       </c>
       <c r="F14" t="n">
-        <v>10552392004</v>
+        <v>11408877171</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>450403576</v>
+        <v>1101883443</v>
       </c>
       <c r="I14" t="n">
-        <v>14.47</v>
+        <v>15.26</v>
       </c>
       <c r="J14" t="n">
-        <v>13.91</v>
+        <v>13.54</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2941581756086027</v>
+        <v>1.13</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.07594</v>
+        <v>8.05315</v>
       </c>
       <c r="M14" t="n">
         <v>748099970.424884</v>
@@ -1815,13 +1815,13 @@
         <v>44325.67635416667</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.005808917046657994</v>
+        <v>0.006426050497499297</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1884,34 +1884,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>547.5599999999999</v>
+        <v>538.36</v>
       </c>
       <c r="F15" t="n">
-        <v>10299613386</v>
+        <v>10125842981</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>98485371</v>
+        <v>120623998</v>
       </c>
       <c r="I15" t="n">
-        <v>562.88</v>
+        <v>552.95</v>
       </c>
       <c r="J15" t="n">
-        <v>546.5</v>
+        <v>526.49</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.077478602360884</v>
+        <v>-6.988445927827684</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5147</v>
+        <v>-1.28901</v>
       </c>
       <c r="M15" t="n">
-        <v>18810142.88639648</v>
+        <v>18810613.88120856</v>
       </c>
       <c r="N15" t="n">
-        <v>18810186.68579455</v>
+        <v>18810665.48043185</v>
       </c>
       <c r="O15" t="n">
         <v>797.73</v>
@@ -1920,13 +1920,13 @@
         <v>46036.48202546296</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.005660737106887825</v>
+        <v>0.005662118133341864</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1989,28 +1989,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>84.7</v>
+        <v>83.58</v>
       </c>
       <c r="F16" t="n">
-        <v>10066394234</v>
+        <v>9934621135</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>38669946</v>
+        <v>129548567</v>
       </c>
       <c r="I16" t="n">
-        <v>84.88</v>
+        <v>84.67</v>
       </c>
       <c r="J16" t="n">
-        <v>83.59</v>
+        <v>82.44</v>
       </c>
       <c r="K16" t="n">
-        <v>0.922706</v>
+        <v>-0.6630199170941751</v>
       </c>
       <c r="L16" t="n">
-        <v>1.03738</v>
+        <v>-0.7719</v>
       </c>
       <c r="M16" t="n">
         <v>118852171</v>
@@ -2025,13 +2025,13 @@
         <v>46286.85358796296</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R16" t="b">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.005524023012277932</v>
+        <v>0.005548262588390776</v>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
@@ -2045,7 +2045,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2064,34 +2064,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.999722</v>
+        <v>0.999699</v>
       </c>
       <c r="F17" t="n">
-        <v>9770898995</v>
+        <v>9780317209</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>50701799</v>
+        <v>123079087</v>
       </c>
       <c r="I17" t="n">
-        <v>0.999846</v>
+        <v>0.999839</v>
       </c>
       <c r="J17" t="n">
-        <v>0.999595</v>
+        <v>0.999263</v>
       </c>
       <c r="K17" t="n">
-        <v>1.442e-05</v>
+        <v>-2.0502185588134e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.00079</v>
+        <v>-0.00617</v>
       </c>
       <c r="M17" t="n">
-        <v>9773614544.067293</v>
+        <v>9783695712.381886</v>
       </c>
       <c r="N17" t="n">
-        <v>9773387427.242182</v>
+        <v>9782223070.353539</v>
       </c>
       <c r="O17" t="n">
         <v>1.057</v>
@@ -2100,13 +2100,13 @@
         <v>45593.90336805556</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.005350802401041773</v>
+        <v>0.005456388370301581</v>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
@@ -2120,7 +2120,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2139,28 +2139,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.255618</v>
+        <v>0.245232</v>
       </c>
       <c r="F18" t="n">
-        <v>9594683963</v>
+        <v>9204678078</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>441302587</v>
+        <v>647377627</v>
       </c>
       <c r="I18" t="n">
-        <v>0.260642</v>
+        <v>0.257648</v>
       </c>
       <c r="J18" t="n">
-        <v>0.248192</v>
+        <v>0.239932</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.0971475922005e-05</v>
+        <v>-0.009054533622238931</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.18042</v>
+        <v>-3.58698</v>
       </c>
       <c r="M18" t="n">
         <v>37535193928.91081</v>
@@ -2175,13 +2175,13 @@
         <v>44440.91678240741</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R18" t="b">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.005247504372771207</v>
+        <v>0.005113646636937204</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.01263123</v>
+        <v>0.01254237</v>
       </c>
       <c r="F19" t="n">
-        <v>8958633558</v>
+        <v>8901184461</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>16784296</v>
+        <v>23847322</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01335759</v>
+        <v>0.01276074</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0125299</v>
+        <v>0.01249052</v>
       </c>
       <c r="K19" t="n">
-        <v>-6.0112472093053e-05</v>
+        <v>-3.131499559115e-05</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.66867</v>
+        <v>-0.22871</v>
       </c>
       <c r="M19" t="n">
-        <v>709244646514.1578</v>
+        <v>709245362584.6495</v>
       </c>
       <c r="N19" t="n">
         <v>1142408526965.963</v>
@@ -2280,13 +2280,13 @@
         <v>46259.82847222222</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R19" t="b">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.004874648822529645</v>
+        <v>0.004932943271314889</v>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
@@ -2300,7 +2300,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2319,28 +2319,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9.02</v>
+        <v>9.06</v>
       </c>
       <c r="F20" t="n">
-        <v>8297568479</v>
+        <v>8334089166</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>457739</v>
+        <v>442380</v>
       </c>
       <c r="I20" t="n">
         <v>9.09</v>
       </c>
       <c r="J20" t="n">
-        <v>8.960000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="K20" t="n">
-        <v>0.060879</v>
+        <v>0.04916048</v>
       </c>
       <c r="L20" t="n">
-        <v>0.67213</v>
+        <v>0.54394</v>
       </c>
       <c r="M20" t="n">
         <v>919857851.9</v>
@@ -2355,13 +2355,13 @@
         <v>46146.39930555555</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.004487129560159194</v>
+        <v>0.004595288629849796</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2424,34 +2424,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.216352</v>
+        <v>0.224252</v>
       </c>
       <c r="F21" t="n">
-        <v>7565866358</v>
+        <v>7854903242</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>183063798</v>
+        <v>619426342</v>
       </c>
       <c r="I21" t="n">
-        <v>0.22079</v>
+        <v>0.230315</v>
       </c>
       <c r="J21" t="n">
-        <v>0.213075</v>
+        <v>0.207092</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.001367816087023216</v>
+        <v>0.00840275</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.78912</v>
+        <v>4.06931</v>
       </c>
       <c r="M21" t="n">
-        <v>34970178928.73618</v>
+        <v>34970168660.84914</v>
       </c>
       <c r="N21" t="n">
-        <v>50001786839.70047</v>
+        <v>50001786839.69947</v>
       </c>
       <c r="O21" t="n">
         <v>0.875563</v>
@@ -2460,13 +2460,13 @@
         <v>43102.66666666666</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R21" t="b">
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.004058202552497949</v>
+        <v>0.00430997617391884</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2529,34 +2529,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5.22</v>
+        <v>4.94</v>
       </c>
       <c r="F22" t="n">
-        <v>6827716511</v>
+        <v>6465087552</v>
       </c>
       <c r="G22" t="n">
         <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>1198271957</v>
+        <v>1429170480</v>
       </c>
       <c r="I22" t="n">
-        <v>5.48</v>
+        <v>5.57</v>
       </c>
       <c r="J22" t="n">
-        <v>4.75</v>
+        <v>4.84</v>
       </c>
       <c r="K22" t="n">
-        <v>0.40177</v>
+        <v>-0.2435762471134959</v>
       </c>
       <c r="L22" t="n">
-        <v>8.261290000000001</v>
+        <v>-4.529</v>
       </c>
       <c r="M22" t="n">
-        <v>1307451804</v>
+        <v>1307529703</v>
       </c>
       <c r="N22" t="n">
-        <v>1307451811</v>
+        <v>1307556131</v>
       </c>
       <c r="O22" t="n">
         <v>20.44</v>
@@ -2565,13 +2565,13 @@
         <v>44577.59010416667</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.003625495859442845</v>
+        <v>0.003482464955527386</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2634,34 +2634,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>335.51</v>
+        <v>309.33</v>
       </c>
       <c r="F23" t="n">
-        <v>6742198101</v>
+        <v>6217118545</v>
       </c>
       <c r="G23" t="n">
         <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>247963129</v>
+        <v>311030789</v>
       </c>
       <c r="I23" t="n">
-        <v>346.97</v>
+        <v>337.08</v>
       </c>
       <c r="J23" t="n">
-        <v>330.66</v>
+        <v>305.68</v>
       </c>
       <c r="K23" t="n">
-        <v>2.58</v>
+        <v>-24.90571333688507</v>
       </c>
       <c r="L23" t="n">
-        <v>0.58889</v>
+        <v>-7.47269</v>
       </c>
       <c r="M23" t="n">
-        <v>20095159.27165077</v>
+        <v>20095599.89665077</v>
       </c>
       <c r="N23" t="n">
-        <v>20095440.52165077</v>
+        <v>20095881.14665077</v>
       </c>
       <c r="O23" t="n">
         <v>3785.82</v>
@@ -2670,13 +2670,13 @@
         <v>43088.66666666666</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>0.003575364590653961</v>
+        <v>0.003334821540229715</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2720,353 +2720,383 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>uniswap</t>
+          <t>hedera-hashgraph</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>uni</t>
+          <t>hbar</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Uniswap</t>
+          <t>Hedera</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>9.84</v>
+        <v>0.125007</v>
       </c>
       <c r="F24" t="n">
-        <v>6104724987</v>
+        <v>5478359322</v>
       </c>
       <c r="G24" t="n">
         <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>660893823</v>
+        <v>1224885680</v>
       </c>
       <c r="I24" t="n">
-        <v>10.18</v>
+        <v>0.128218</v>
       </c>
       <c r="J24" t="n">
-        <v>9.42</v>
+        <v>0.09357</v>
       </c>
       <c r="K24" t="n">
-        <v>0.238426</v>
+        <v>0.03147097</v>
       </c>
       <c r="L24" t="n">
-        <v>2.18965</v>
+        <v>33.68015</v>
       </c>
       <c r="M24" t="n">
-        <v>620466422.6104751</v>
+        <v>43831706397.79829</v>
       </c>
       <c r="N24" t="n">
-        <v>887714418.9163101</v>
+        <v>50000000000</v>
       </c>
       <c r="O24" t="n">
-        <v>44.92</v>
+        <v>0.569229</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>44318.89240740741</v>
+        <v>44454.11143518519</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>0.003201675042127265</v>
+        <v>0.002894956348664167</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>DeFi</t>
+          <t>Infraestructura empresarial</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>Exchange descentralizado</t>
+          <t>DLT</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>N/A (token ERC-20)</t>
+          <t>Hashgraph (aBFT)</t>
         </is>
       </c>
       <c r="W24" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>uniswap.org</t>
+          <t>hedera.com</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>Intercambio descentralizado de tokens</t>
+          <t>Aplicaciones empresariales y tokenización</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>Token ERC-20 sobre Ethereum</t>
+          <t>Red propia (hashgraph, no blockchain tradicional)</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Uno de los mayores exchanges descentralizados (DEX) del ecosistema Ethereum.</t>
+          <t>Gobernada por un consejo de grandes empresas globales.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>litecoin</t>
+          <t>uniswap</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ltc</t>
+          <t>uni</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Litecoin</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>71.11</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>5521697779</v>
+        <v>5496586683</v>
       </c>
       <c r="G25" t="n">
         <v>24</v>
       </c>
       <c r="H25" t="n">
-        <v>382049880</v>
+        <v>1026550959</v>
       </c>
       <c r="I25" t="n">
-        <v>73.34</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>70.68000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.248465999589328</v>
+        <v>-0.8321021447589825</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.8904</v>
+        <v>-8.594530000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>77653329.51737037</v>
+        <v>620420422.6104751</v>
       </c>
       <c r="N25" t="n">
-        <v>77656204.52533114</v>
+        <v>887668418.9163101</v>
       </c>
       <c r="O25" t="n">
-        <v>410.26</v>
+        <v>44.92</v>
       </c>
       <c r="P25" s="1" t="n">
-        <v>44325.80077546297</v>
+        <v>44318.89240740741</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>0.002859901923620027</v>
+        <v>0.00290580911555815</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>DeFi</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>Store of value ligero</t>
+          <t>Exchange descentralizado</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Proof of Work</t>
+          <t>N/A (token ERC-20)</t>
         </is>
       </c>
       <c r="W25" t="n">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>litecoin.org</t>
+          <t>uniswap.org</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>Pagos rápidos de bajo costo</t>
+          <t>Intercambio descentralizado de tokens</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>Blockchain propia (Layer 1)</t>
+          <t>Token ERC-20 sobre Ethereum</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Fue diseñada como complemento más rápido y liviano de Bitcoin.</t>
+          <t>Uno de los mayores exchanges descentralizados (DEX) del ecosistema Ethereum.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>canton-network</t>
+          <t>litecoin</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>ltc</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Canton</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.134479</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>5338537105</v>
+        <v>5355747288</v>
       </c>
       <c r="G26" t="n">
         <v>25</v>
       </c>
       <c r="H26" t="n">
-        <v>25873598</v>
+        <v>576510489</v>
       </c>
       <c r="I26" t="n">
-        <v>0.140118</v>
+        <v>72.37</v>
       </c>
       <c r="J26" t="n">
-        <v>0.132386</v>
+        <v>68.88</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.003221599252645951</v>
+        <v>-2.254265189007285</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.49593</v>
+        <v>-3.11095</v>
       </c>
       <c r="M26" t="n">
-        <v>39697885231.8137</v>
+        <v>77657260.78055078</v>
       </c>
       <c r="N26" t="n">
-        <v>39697885231.8137</v>
+        <v>77657485.78143089</v>
       </c>
       <c r="O26" t="n">
-        <v>0.194152</v>
+        <v>410.26</v>
       </c>
       <c r="P26" s="1" t="n">
-        <v>46056.00148148148</v>
+        <v>44325.80077546297</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R26" t="b">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.002752532329402278</v>
-      </c>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr"/>
+        <v>0.002821951824125525</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Pagos</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Store of value ligero</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Proof of Work</t>
+        </is>
+      </c>
+      <c r="W26" t="n">
+        <v>2011</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>litecoin.org</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Pagos rápidos de bajo costo</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Layer 1)</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Fue diseñada como complemento más rápido y liviano de Bitcoin.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>sui</t>
+          <t>canton-network</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sui</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sui</t>
+          <t>Canton</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1.25</v>
+        <v>0.129887</v>
       </c>
       <c r="F27" t="n">
-        <v>5105248088</v>
+        <v>5157498978</v>
       </c>
       <c r="G27" t="n">
         <v>26</v>
       </c>
       <c r="H27" t="n">
-        <v>1048651897</v>
+        <v>47163157</v>
       </c>
       <c r="I27" t="n">
-        <v>1.29</v>
+        <v>0.146469</v>
       </c>
       <c r="J27" t="n">
-        <v>1.13</v>
+        <v>0.126784</v>
       </c>
       <c r="K27" t="n">
-        <v>0.06920900000000001</v>
+        <v>-0.004338971851093582</v>
       </c>
       <c r="L27" t="n">
-        <v>5.55749</v>
+        <v>-3.21821</v>
       </c>
       <c r="M27" t="n">
-        <v>4096537146.540959</v>
+        <v>39706020978.0548</v>
       </c>
       <c r="N27" t="n">
-        <v>10000000000</v>
+        <v>39706741614.41362</v>
       </c>
       <c r="O27" t="n">
-        <v>5.35</v>
+        <v>0.194152</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>45661.62243055556</v>
+        <v>46056.00148148148</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R27" t="b">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.002615777279621517</v>
+        <v>0.002703912646893221</v>
       </c>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
@@ -3080,292 +3110,262 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ethena-usde</t>
+          <t>avalanche-2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>usde</t>
+          <t>avax</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ethena USDe</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.999802</v>
+        <v>10.41</v>
       </c>
       <c r="F28" t="n">
-        <v>4944958342</v>
+        <v>4894866629</v>
       </c>
       <c r="G28" t="n">
         <v>27</v>
       </c>
       <c r="H28" t="n">
-        <v>20888227</v>
+        <v>625276181</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>11.08</v>
       </c>
       <c r="J28" t="n">
-        <v>0.999522</v>
+        <v>10.15</v>
       </c>
       <c r="K28" t="n">
-        <v>0.00028489</v>
+        <v>-0.5173540689691229</v>
       </c>
       <c r="L28" t="n">
-        <v>0.02869</v>
+        <v>-4.6792</v>
       </c>
       <c r="M28" t="n">
-        <v>4945939106.979231</v>
+        <v>469753866.6488752</v>
       </c>
       <c r="N28" t="n">
-        <v>4950082292.661032</v>
+        <v>469754193.1768665</v>
       </c>
       <c r="O28" t="n">
-        <v>1.034</v>
+        <v>144.96</v>
       </c>
       <c r="P28" s="1" t="n">
-        <v>46000.38208333333</v>
+        <v>44521.26314814815</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R28" t="b">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.002521814724180789</v>
-      </c>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
+        <v>0.002547538519968521</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Plataforma de contratos inteligentes</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Layer 1</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Proof of Stake (Avalanche consensus)</t>
+        </is>
+      </c>
+      <c r="W28" t="n">
+        <v>2020</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>avax.network</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Subredes personalizadas para empresas</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Layer 1)</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>Permite crear subredes (subnets) personalizadas para casos de uso específicos.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>avalanche-2</t>
+          <t>ethena-usde</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>avax</t>
+          <t>usde</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Ethena USDe</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>10.98</v>
+        <v>0.999864</v>
       </c>
       <c r="F29" t="n">
-        <v>4864646128</v>
+        <v>4903829117</v>
       </c>
       <c r="G29" t="n">
         <v>28</v>
       </c>
       <c r="H29" t="n">
-        <v>590874472</v>
+        <v>36827169</v>
       </c>
       <c r="I29" t="n">
-        <v>11.26</v>
+        <v>0.999934</v>
       </c>
       <c r="J29" t="n">
-        <v>10.55</v>
+        <v>0.9996</v>
       </c>
       <c r="K29" t="n">
-        <v>0.119876</v>
+        <v>8.536e-05</v>
       </c>
       <c r="L29" t="n">
-        <v>0.93719</v>
+        <v>0.0046</v>
       </c>
       <c r="M29" t="n">
-        <v>443075362.6635053</v>
+        <v>4904696488.396321</v>
       </c>
       <c r="N29" t="n">
-        <v>469744144.6508019</v>
+        <v>4904696584.801255</v>
       </c>
       <c r="O29" t="n">
-        <v>144.96</v>
+        <v>1.034</v>
       </c>
       <c r="P29" s="1" t="n">
-        <v>44521.26314814815</v>
+        <v>46000.38208333333</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R29" t="b">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.002474735350428817</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Plataforma de contratos inteligentes</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Layer 1</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Proof of Stake (Avalanche consensus)</t>
-        </is>
-      </c>
-      <c r="W29" t="n">
-        <v>2020</v>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>avax.network</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>Subredes personalizadas para empresas</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Layer 1)</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>Permite crear subredes (subnets) personalizadas para casos de uso específicos.</t>
-        </is>
-      </c>
+        <v>0.002552874881773948</v>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>dai</t>
+          <t>sui</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>dai</t>
+          <t>sui</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Dai</t>
+          <t>Sui</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="F30" t="n">
-        <v>4599126620</v>
+        <v>4741714688</v>
       </c>
       <c r="G30" t="n">
         <v>29</v>
       </c>
       <c r="H30" t="n">
-        <v>109783985</v>
+        <v>1609363322</v>
       </c>
       <c r="I30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-0.09112931843792849</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-7.29204</v>
+      </c>
+      <c r="M30" t="n">
+        <v>4096537146.540959</v>
+      </c>
+      <c r="N30" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="O30" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="P30" s="1" t="n">
+        <v>45661.62243055556</v>
+      </c>
+      <c r="Q30" s="1" t="n">
+        <v>46293.71134259259</v>
+      </c>
+      <c r="R30" t="b">
         <v>1</v>
       </c>
-      <c r="J30" t="n">
-        <v>0.999735</v>
-      </c>
-      <c r="K30" t="n">
-        <v>2.744e-05</v>
-      </c>
-      <c r="L30" t="n">
-        <v>-0.00236</v>
-      </c>
-      <c r="M30" t="n">
-        <v>4599037814.56804</v>
-      </c>
-      <c r="N30" t="n">
-        <v>4600951017.574961</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P30" s="1" t="n">
-        <v>43902.79363425926</v>
-      </c>
-      <c r="Q30" s="1" t="n">
-        <v>46292.596875</v>
-      </c>
-      <c r="R30" t="b">
-        <v>0</v>
-      </c>
       <c r="S30" t="n">
-        <v>0.002319086644796425</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Stablecoin</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Colateralizada por cripto</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>N/A (token, colateral cripto)</t>
-        </is>
-      </c>
-      <c r="W30" t="n">
-        <v>2017</v>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>makerdao.com</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>Estabilidad de valor descentralizada</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>Token ERC-20 sobre Ethereum</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>Stablecoin descentralizada, generada mediante colateral cripto sobrecolateralizado.</t>
-        </is>
-      </c>
+        <v>0.002456350206145466</v>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3384,34 +3384,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="F31" t="n">
-        <v>4483348301</v>
+        <v>4660277648</v>
       </c>
       <c r="G31" t="n">
         <v>30</v>
       </c>
       <c r="H31" t="n">
-        <v>165132672</v>
+        <v>151551042</v>
       </c>
       <c r="I31" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="J31" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="K31" t="n">
-        <v>0.119041</v>
+        <v>-0.03378944504757952</v>
       </c>
       <c r="L31" t="n">
-        <v>7.84259</v>
+        <v>-1.94732</v>
       </c>
       <c r="M31" t="n">
-        <v>2814574919.172927</v>
+        <v>2815210027.833801</v>
       </c>
       <c r="N31" t="n">
-        <v>5256420917.725853</v>
+        <v>5257062331.929954</v>
       </c>
       <c r="O31" t="n">
         <v>8.25</v>
@@ -3420,13 +3420,13 @@
         <v>45457.69225694444</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0.00225121688400791</v>
+        <v>0.002407861716141015</v>
       </c>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
@@ -3440,367 +3440,367 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>usd1-wlfi</t>
+          <t>dai</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>usd1</t>
+          <t>dai</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>USD1</t>
+          <t>Dai</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.999517</v>
+        <v>0.999949</v>
       </c>
       <c r="F32" t="n">
-        <v>4416372376</v>
+        <v>4587404099</v>
       </c>
       <c r="G32" t="n">
         <v>31</v>
       </c>
       <c r="H32" t="n">
-        <v>580406931</v>
+        <v>193253226</v>
       </c>
       <c r="I32" t="n">
-        <v>0.999779</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>0.999336</v>
+        <v>0.999637</v>
       </c>
       <c r="K32" t="n">
-        <v>-2.4808525936781e-05</v>
+        <v>2.63e-05</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.00141</v>
+        <v>0.008160000000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>4418506659.421694</v>
+        <v>4587020648.060517</v>
       </c>
       <c r="N32" t="n">
-        <v>4418506659.421694</v>
+        <v>4593374140.490763</v>
       </c>
       <c r="O32" t="n">
-        <v>1.048</v>
+        <v>1.22</v>
       </c>
       <c r="P32" s="1" t="n">
-        <v>46212.42696759259</v>
+        <v>43902.79363425926</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R32" t="b">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.002211955301635656</v>
-      </c>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
+        <v>0.002364472020834367</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Stablecoin</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Colateralizada por cripto</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>N/A (token, colateral cripto)</t>
+        </is>
+      </c>
+      <c r="W32" t="n">
+        <v>2017</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>makerdao.com</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>Estabilidad de valor descentralizada</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>Token ERC-20 sobre Ethereum</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>Stablecoin descentralizada, generada mediante colateral cripto sobrecolateralizado.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>hedera-hashgraph</t>
+          <t>usd1-wlfi</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>hbar</t>
+          <t>usd1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Hedera</t>
+          <t>USD1</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.093954</v>
+        <v>0.999368</v>
       </c>
       <c r="F33" t="n">
-        <v>4118142843</v>
+        <v>4415532827</v>
       </c>
       <c r="G33" t="n">
         <v>32</v>
       </c>
       <c r="H33" t="n">
-        <v>94801236</v>
+        <v>995762212</v>
       </c>
       <c r="I33" t="n">
-        <v>0.09583800000000001</v>
+        <v>0.999614</v>
       </c>
       <c r="J33" t="n">
-        <v>0.091875</v>
+        <v>0.9992760000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>0.00052865</v>
+        <v>4.46e-06</v>
       </c>
       <c r="L33" t="n">
-        <v>0.41416</v>
+        <v>-0.00552</v>
       </c>
       <c r="M33" t="n">
-        <v>43831706398.13715</v>
+        <v>4418501462.580373</v>
       </c>
       <c r="N33" t="n">
-        <v>50000000000</v>
+        <v>4418501462.580373</v>
       </c>
       <c r="O33" t="n">
-        <v>0.569229</v>
+        <v>1.048</v>
       </c>
       <c r="P33" s="1" t="n">
-        <v>44454.11143518519</v>
+        <v>46212.42696759259</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R33" t="b">
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.00203713183520771</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Infraestructura empresarial</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>DLT</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Hashgraph (aBFT)</t>
-        </is>
-      </c>
-      <c r="W33" t="n">
-        <v>2019</v>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>hedera.com</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>Aplicaciones empresariales y tokenización</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>Red propia (hashgraph, no blockchain tradicional)</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>Gobernada por un consejo de grandes empresas globales.</t>
-        </is>
-      </c>
+        <v>0.00226213801588497</v>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>bittensor</t>
+          <t>quant-network</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>tao</t>
+          <t>qnt</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Bittensor</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>327.02</v>
+        <v>244.32</v>
       </c>
       <c r="F34" t="n">
-        <v>3708300309</v>
+        <v>3529967203</v>
       </c>
       <c r="G34" t="n">
         <v>33</v>
       </c>
       <c r="H34" t="n">
-        <v>323099760</v>
+        <v>1554158496</v>
       </c>
       <c r="I34" t="n">
-        <v>340.69</v>
+        <v>358.2</v>
       </c>
       <c r="J34" t="n">
-        <v>311.96</v>
+        <v>181.33</v>
       </c>
       <c r="K34" t="n">
-        <v>1.8</v>
+        <v>59.51</v>
       </c>
       <c r="L34" t="n">
-        <v>0.37067</v>
+        <v>31.00905</v>
       </c>
       <c r="M34" t="n">
-        <v>11339645.9251</v>
+        <v>14544176.16408117</v>
       </c>
       <c r="N34" t="n">
-        <v>21000000</v>
+        <v>14612493</v>
       </c>
       <c r="O34" t="n">
-        <v>757.6</v>
+        <v>427.42</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>45358.44833333333</v>
+        <v>44450.05208333334</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
-        <v>0.00179688033575781</v>
-      </c>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr"/>
+        <v>0.001734862713300187</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Infraestructura empresarial</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>N/A (token ERC-20)</t>
+        </is>
+      </c>
+      <c r="W34" t="n">
+        <v>2018</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>quant.network</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>Interoperabilidad entre redes empresariales</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>Token ERC-20 sobre Ethereum</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>Su tecnología Overledger busca conectar múltiples blockchains y redes existentes.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>shiba-inu</t>
+          <t>bittensor</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>shib</t>
+          <t>tao</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Shiba Inu</t>
+          <t>Bittensor</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5.95e-06</v>
+        <v>301.09</v>
       </c>
       <c r="F35" t="n">
-        <v>3503571968</v>
+        <v>3414990064</v>
       </c>
       <c r="G35" t="n">
         <v>34</v>
       </c>
       <c r="H35" t="n">
-        <v>91103023</v>
+        <v>336490928</v>
       </c>
       <c r="I35" t="n">
-        <v>6.06e-06</v>
+        <v>329.59</v>
       </c>
       <c r="J35" t="n">
-        <v>5.82e-06</v>
+        <v>294.98</v>
       </c>
       <c r="K35" t="n">
-        <v>2.0646e-08</v>
+        <v>-22.94888112986712</v>
       </c>
       <c r="L35" t="n">
-        <v>0.15974</v>
+        <v>-7.07539</v>
       </c>
       <c r="M35" t="n">
-        <v>589238950487743.1</v>
+        <v>11339645.9251</v>
       </c>
       <c r="N35" t="n">
-        <v>589496066158401.1</v>
+        <v>21000000</v>
       </c>
       <c r="O35" t="n">
-        <v>8.616e-05</v>
+        <v>757.6</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>44496.82980324074</v>
+        <v>45358.44833333333</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
-        <v>0.001676867680104211</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Meme coin</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Ecosistema DeFi</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>N/A (token ERC-20)</t>
-        </is>
-      </c>
-      <c r="W35" t="n">
-        <v>2020</v>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>shibatoken.com</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>Ecosistema meme y DeFi comunitario</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>Token ERC-20 sobre Ethereum</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>Token meme inspirado en Dogecoin, con ecosistema DeFi propio (ShibaSwap).</t>
-        </is>
-      </c>
+        <v>0.001666404087407819</v>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3819,34 +3819,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.067637</v>
+        <v>0.068595</v>
       </c>
       <c r="F36" t="n">
-        <v>3364743367</v>
+        <v>3412255351</v>
       </c>
       <c r="G36" t="n">
         <v>35</v>
       </c>
       <c r="H36" t="n">
-        <v>14644812</v>
+        <v>24280237</v>
       </c>
       <c r="I36" t="n">
-        <v>0.069409</v>
+        <v>0.069992</v>
       </c>
       <c r="J36" t="n">
-        <v>0.064829</v>
+        <v>0.063356</v>
       </c>
       <c r="K36" t="n">
-        <v>0.00239858</v>
+        <v>0.00139798</v>
       </c>
       <c r="L36" t="n">
-        <v>3.62235</v>
+        <v>2.05436</v>
       </c>
       <c r="M36" t="n">
-        <v>49747076136.16346</v>
+        <v>49749274711.3246</v>
       </c>
       <c r="N36" t="n">
-        <v>98947092789.99742</v>
+        <v>98949285642.86087</v>
       </c>
       <c r="O36" t="n">
         <v>0.891544</v>
@@ -3855,13 +3855,13 @@
         <v>44523.66666666666</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R36" t="b">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.00159548574243353</v>
+        <v>0.001664775809857879</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3905,143 +3905,173 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>global-dollar</t>
+          <t>shiba-inu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>usdg</t>
+          <t>shib</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Global Dollar</t>
+          <t>Shiba Inu</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.999914</v>
+        <v>5.66e-06</v>
       </c>
       <c r="F37" t="n">
-        <v>3257336904</v>
+        <v>3334571030</v>
       </c>
       <c r="G37" t="n">
         <v>36</v>
       </c>
       <c r="H37" t="n">
-        <v>356072551</v>
+        <v>106187506</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>5.97e-06</v>
       </c>
       <c r="J37" t="n">
-        <v>0.999776</v>
+        <v>5.57e-06</v>
       </c>
       <c r="K37" t="n">
-        <v>-5.2135512535911e-05</v>
+        <v>-2.46623257087e-07</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.01242</v>
+        <v>-4.17712</v>
       </c>
       <c r="M37" t="n">
-        <v>3257616338.025859</v>
+        <v>589238950149691.8</v>
       </c>
       <c r="N37" t="n">
-        <v>3251901649.165859</v>
+        <v>589496065820349.8</v>
       </c>
       <c r="O37" t="n">
-        <v>1.65</v>
+        <v>8.616e-05</v>
       </c>
       <c r="P37" s="1" t="n">
-        <v>45686.67436342593</v>
+        <v>44496.82980324074</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R37" t="b">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.001532523600523779</v>
-      </c>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr"/>
+        <v>0.001618521729131087</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Meme coin</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ecosistema DeFi</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>N/A (token ERC-20)</t>
+        </is>
+      </c>
+      <c r="W37" t="n">
+        <v>2020</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>shibatoken.com</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>Ecosistema meme y DeFi comunitario</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>Token ERC-20 sobre Ethereum</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>Token meme inspirado en Dogecoin, con ecosistema DeFi propio (ShibaSwap).</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>bitway</t>
+          <t>global-dollar</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>btw</t>
+          <t>usdg</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Bitway</t>
+          <t>Global Dollar</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>3119414355</v>
+        <v>3249435947</v>
       </c>
       <c r="G38" t="n">
         <v>37</v>
       </c>
       <c r="H38" t="n">
-        <v>29009108</v>
+        <v>870343715</v>
       </c>
       <c r="I38" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>0.980191</v>
+        <v>0.999722</v>
       </c>
       <c r="K38" t="n">
-        <v>0.247137</v>
+        <v>0.00032742</v>
       </c>
       <c r="L38" t="n">
-        <v>30.27369</v>
+        <v>0.02515</v>
       </c>
       <c r="M38" t="n">
-        <v>2708142280.000001</v>
+        <v>3249196081.805783</v>
       </c>
       <c r="N38" t="n">
-        <v>10000000000</v>
+        <v>3249196081.805783</v>
       </c>
       <c r="O38" t="n">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="P38" s="1" t="n">
-        <v>46291.06377314815</v>
+        <v>45686.67436342593</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0.001451672794528122</v>
+        <v>0.001567831384527776</v>
       </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
@@ -4055,68 +4085,68 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>paypal-usd</t>
+          <t>tether-gold</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>pyusd</t>
+          <t>xaut</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>PayPal USD</t>
+          <t>Tether Gold</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.999938</v>
+        <v>4132.8</v>
       </c>
       <c r="F39" t="n">
-        <v>2779131582</v>
+        <v>2848646256</v>
       </c>
       <c r="G39" t="n">
         <v>38</v>
       </c>
       <c r="H39" t="n">
-        <v>25936708</v>
+        <v>355101151</v>
       </c>
       <c r="I39" t="n">
-        <v>0.9999670000000001</v>
+        <v>4280.38</v>
       </c>
       <c r="J39" t="n">
-        <v>0.999771</v>
+        <v>4117.91</v>
       </c>
       <c r="K39" t="n">
-        <v>8.165000000000001e-05</v>
+        <v>-146.5443765912078</v>
       </c>
       <c r="L39" t="n">
-        <v>0.0064</v>
+        <v>-3.43151</v>
       </c>
       <c r="M39" t="n">
-        <v>2779304258.944445</v>
+        <v>689324.089</v>
       </c>
       <c r="N39" t="n">
-        <v>2779106296.067445</v>
+        <v>707747.089</v>
       </c>
       <c r="O39" t="n">
-        <v>1.021</v>
+        <v>5504.62</v>
       </c>
       <c r="P39" s="1" t="n">
-        <v>45222.61454861111</v>
+        <v>46050.66666666666</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001252197533499652</v>
+        <v>0.001329196889389687</v>
       </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
@@ -4130,68 +4160,68 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>memecore</t>
+          <t>paypal-usd</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>pyusd</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>MemeCore</t>
+          <t>PayPal USD</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1.2</v>
+        <v>0.999898</v>
       </c>
       <c r="F40" t="n">
-        <v>2737839732</v>
+        <v>2727482123</v>
       </c>
       <c r="G40" t="n">
         <v>39</v>
       </c>
       <c r="H40" t="n">
-        <v>888350</v>
+        <v>64835723</v>
       </c>
       <c r="I40" t="n">
-        <v>1.25</v>
+        <v>0.999984</v>
       </c>
       <c r="J40" t="n">
-        <v>1.19</v>
+        <v>0.999622</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.01496321878625895</v>
+        <v>3.343e-05</v>
       </c>
       <c r="L40" t="n">
-        <v>-1.24104</v>
+        <v>-0.00056</v>
       </c>
       <c r="M40" t="n">
-        <v>2279320630.284911</v>
+        <v>2727880777.060247</v>
       </c>
       <c r="N40" t="n">
-        <v>5418910376.770718</v>
+        <v>2727880777.060247</v>
       </c>
       <c r="O40" t="n">
-        <v>5.64</v>
+        <v>1.021</v>
       </c>
       <c r="P40" s="1" t="n">
-        <v>46205.17638888889</v>
+        <v>45222.61454861111</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R40" t="b">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.001227992069072281</v>
+        <v>0.001257054460688099</v>
       </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
@@ -4205,68 +4235,68 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ethena</t>
+          <t>memecore</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ena</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Ethena</t>
+          <t>MemeCore</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.270724</v>
+        <v>1.15</v>
       </c>
       <c r="F41" t="n">
-        <v>2733047422</v>
+        <v>2627985656</v>
       </c>
       <c r="G41" t="n">
         <v>40</v>
       </c>
       <c r="H41" t="n">
-        <v>396426394</v>
+        <v>1879104</v>
       </c>
       <c r="I41" t="n">
-        <v>0.278982</v>
+        <v>1.21</v>
       </c>
       <c r="J41" t="n">
-        <v>0.264816</v>
+        <v>1.14</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.006224754725193959</v>
+        <v>-0.02519123899448772</v>
       </c>
       <c r="L41" t="n">
-        <v>-2.34562</v>
+        <v>-2.32052</v>
       </c>
       <c r="M41" t="n">
-        <v>10095312500</v>
+        <v>2279737202.761663</v>
       </c>
       <c r="N41" t="n">
-        <v>15000000000</v>
+        <v>5419326949.268888</v>
       </c>
       <c r="O41" t="n">
-        <v>1.52</v>
+        <v>5.64</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>45393.21892361111</v>
+        <v>46205.17638888889</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R41" t="b">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.001225182795832406</v>
+        <v>0.001197813193500494</v>
       </c>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
@@ -4280,68 +4310,68 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>tether-gold</t>
+          <t>ethena</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>xaut</t>
+          <t>ena</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tether Gold</t>
+          <t>Ethena</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4278.67</v>
+        <v>0.258992</v>
       </c>
       <c r="F42" t="n">
-        <v>2664855583</v>
+        <v>2614910012</v>
       </c>
       <c r="G42" t="n">
         <v>41</v>
       </c>
       <c r="H42" t="n">
-        <v>54750536</v>
+        <v>681564422</v>
       </c>
       <c r="I42" t="n">
-        <v>4281.16</v>
+        <v>0.294013</v>
       </c>
       <c r="J42" t="n">
-        <v>4275.97</v>
+        <v>0.256098</v>
       </c>
       <c r="K42" t="n">
-        <v>-1.303744959958749</v>
+        <v>-0.01683506024812859</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.03263</v>
+        <v>-6.11802</v>
       </c>
       <c r="M42" t="n">
-        <v>622823.6595320001</v>
+        <v>10095312500</v>
       </c>
       <c r="N42" t="n">
-        <v>707747.089</v>
+        <v>15000000000</v>
       </c>
       <c r="O42" t="n">
-        <v>5504.62</v>
+        <v>1.52</v>
       </c>
       <c r="P42" s="1" t="n">
-        <v>46050.66666666666</v>
+        <v>45393.21892361111</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42" t="n">
-        <v>0.001185208439315286</v>
+        <v>0.00119002781434875</v>
       </c>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
@@ -4355,68 +4385,68 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ondo-finance</t>
+          <t>bitway</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ondo</t>
+          <t>btw</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Ondo</t>
+          <t>Bitway</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.544944</v>
+        <v>0.93493</v>
       </c>
       <c r="F43" t="n">
-        <v>2653513899</v>
+        <v>2537403368</v>
       </c>
       <c r="G43" t="n">
         <v>42</v>
       </c>
       <c r="H43" t="n">
-        <v>238823362</v>
+        <v>34318069</v>
       </c>
       <c r="I43" t="n">
-        <v>0.55672</v>
+        <v>1.43</v>
       </c>
       <c r="J43" t="n">
-        <v>0.528791</v>
+        <v>0.937479</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.003066278902767117</v>
+        <v>-0.2436023418964792</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.67402</v>
+        <v>-20.42315</v>
       </c>
       <c r="M43" t="n">
-        <v>4869330647</v>
+        <v>2708142280.000001</v>
       </c>
       <c r="N43" t="n">
         <v>10000000000</v>
       </c>
       <c r="O43" t="n">
-        <v>2.14</v>
+        <v>1.43</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>45641.69166666667</v>
+        <v>46293.32349537037</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43" t="n">
-        <v>0.001178559894176028</v>
+        <v>0.001143879524419837</v>
       </c>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
@@ -4430,112 +4460,82 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>okb</t>
+          <t>ondo-finance</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>okb</t>
+          <t>ondo</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>OKB</t>
+          <t>Ondo</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>121.84</v>
+        <v>0.514319</v>
       </c>
       <c r="F44" t="n">
-        <v>2558597443</v>
+        <v>2503804853</v>
       </c>
       <c r="G44" t="n">
         <v>43</v>
       </c>
       <c r="H44" t="n">
-        <v>19655996</v>
+        <v>736048329</v>
       </c>
       <c r="I44" t="n">
-        <v>122.43</v>
+        <v>0.606332</v>
       </c>
       <c r="J44" t="n">
-        <v>120.04</v>
+        <v>0.507278</v>
       </c>
       <c r="K44" t="n">
-        <v>0.758443</v>
+        <v>-0.03149847428975283</v>
       </c>
       <c r="L44" t="n">
-        <v>0.54911</v>
+        <v>-5.75793</v>
       </c>
       <c r="M44" t="n">
-        <v>21000000</v>
+        <v>4869330647</v>
       </c>
       <c r="N44" t="n">
-        <v>21000000</v>
+        <v>10000000000</v>
       </c>
       <c r="O44" t="n">
-        <v>228.74</v>
+        <v>2.14</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>45934.66666666666</v>
+        <v>45641.69166666667</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S44" t="n">
-        <v>0.001122919449408354</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Token de exchange</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Utilidad</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>N/A (token de exchange)</t>
-        </is>
-      </c>
-      <c r="W44" t="n">
-        <v>2019</v>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>okx.com</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>Beneficios dentro del exchange OKX</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>Token ERC-20 sobre Ethereum</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>Token nativo del exchange OKX, usado para descuentos y beneficios.</t>
-        </is>
-      </c>
+        <v>0.001123874607016872</v>
+      </c>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4557,31 +4557,31 @@
         <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>2491318521</v>
+        <v>2493492656</v>
       </c>
       <c r="G45" t="n">
         <v>44</v>
       </c>
       <c r="H45" t="n">
-        <v>105209885</v>
+        <v>237412002</v>
       </c>
       <c r="I45" t="n">
         <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>0.999878</v>
+        <v>0.9998359999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>3.171e-05</v>
+        <v>0.00015506</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.00186</v>
+        <v>0.00961</v>
       </c>
       <c r="M45" t="n">
-        <v>2491272908.017204</v>
+        <v>2493192589.017205</v>
       </c>
       <c r="N45" t="n">
-        <v>2491272908.017204</v>
+        <v>2493192589.017197</v>
       </c>
       <c r="O45" t="n">
         <v>1.073</v>
@@ -4590,13 +4590,13 @@
         <v>45652.11518518518</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R45" t="b">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.001083480248859509</v>
+        <v>0.00111773461394789</v>
       </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
@@ -4610,292 +4610,262 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>hashnote-usyc</t>
+          <t>okb</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>usyc</t>
+          <t>okb</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Circle USYC</t>
+          <t>OKB</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1.14</v>
+        <v>117.98</v>
       </c>
       <c r="F46" t="n">
-        <v>2405269933</v>
+        <v>2477847045</v>
       </c>
       <c r="G46" t="n">
         <v>45</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>26770356</v>
       </c>
       <c r="I46" t="n">
-        <v>1.14</v>
+        <v>121.64</v>
       </c>
       <c r="J46" t="n">
-        <v>1.14</v>
+        <v>116.19</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>-3.238687743650871</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>-2.64985</v>
       </c>
       <c r="M46" t="n">
-        <v>2112453536.871665</v>
+        <v>21000000</v>
       </c>
       <c r="N46" t="n">
-        <v>2112453536.871665</v>
+        <v>21000000</v>
       </c>
       <c r="O46" t="n">
-        <v>1.14</v>
+        <v>228.74</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>46290.53483796296</v>
+        <v>45934.66666666666</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R46" t="b">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.001033038187390733</v>
-      </c>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
-      <c r="AA46" t="inlineStr"/>
+        <v>0.001108419048787528</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Token de exchange</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Utilidad</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>N/A (token de exchange)</t>
+        </is>
+      </c>
+      <c r="W46" t="n">
+        <v>2019</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>okx.com</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>Beneficios dentro del exchange OKX</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>Token ERC-20 sobre Ethereum</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>Token nativo del exchange OKX, usado para descuentos y beneficios.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>pump-fun</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Aave</t>
+          <t>Pump.fun</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>154.56</v>
+        <v>0.00529086</v>
       </c>
       <c r="F47" t="n">
-        <v>2384820190</v>
+        <v>2460168381</v>
       </c>
       <c r="G47" t="n">
         <v>46</v>
       </c>
       <c r="H47" t="n">
-        <v>268585001</v>
+        <v>572952538</v>
       </c>
       <c r="I47" t="n">
-        <v>157.25</v>
+        <v>0.00553383</v>
       </c>
       <c r="J47" t="n">
-        <v>152.7</v>
+        <v>0.00475129</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.2979510974178083</v>
+        <v>0.00042116</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.38129</v>
+        <v>8.642609999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>15429382.51379187</v>
+        <v>465673351301.2534</v>
       </c>
       <c r="N47" t="n">
-        <v>16000000</v>
+        <v>831175023761.6196</v>
       </c>
       <c r="O47" t="n">
-        <v>661.6900000000001</v>
+        <v>0.00881908</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>44334.55554398148</v>
+        <v>45914.36296296296</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S47" t="n">
-        <v>0.001021050457929947</v>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>DeFi</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Préstamos</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>N/A (token de gobernanza)</t>
-        </is>
-      </c>
-      <c r="W47" t="n">
-        <v>2017</v>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>aave.com</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>Préstamos y créditos descentralizados</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>Token ERC-20 sobre Ethereum</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>Pionero en préstamos y créditos flash (flash loans) dentro de DeFi.</t>
-        </is>
-      </c>
+        <v>0.001097892981992173</v>
+      </c>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>quant-network</t>
+          <t>hashnote-usyc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>qnt</t>
+          <t>usyc</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Circle USYC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>163.55</v>
+        <v>1.14</v>
       </c>
       <c r="F48" t="n">
-        <v>2378700069</v>
+        <v>2405472293</v>
       </c>
       <c r="G48" t="n">
         <v>47</v>
       </c>
       <c r="H48" t="n">
-        <v>587701192</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>193.67</v>
+        <v>1.14</v>
       </c>
       <c r="J48" t="n">
-        <v>109.62</v>
+        <v>1.14</v>
       </c>
       <c r="K48" t="n">
-        <v>57.02</v>
+        <v>8.394999999999999e-05</v>
       </c>
       <c r="L48" t="n">
-        <v>53.08112</v>
+        <v>0.00737</v>
       </c>
       <c r="M48" t="n">
-        <v>14544176.16408117</v>
+        <v>2112475511.779951</v>
       </c>
       <c r="N48" t="n">
-        <v>14612493</v>
+        <v>2112475511.779951</v>
       </c>
       <c r="O48" t="n">
-        <v>427.42</v>
+        <v>1.14</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>44450.05208333334</v>
+        <v>46293.53819444445</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0.001017462816030717</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Interoperabilidad</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Infraestructura empresarial</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>N/A (token ERC-20)</t>
-        </is>
-      </c>
-      <c r="W48" t="n">
-        <v>2018</v>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>quant.network</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>Interoperabilidad entre redes empresariales</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>Token ERC-20 sobre Ethereum</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>Su tecnología Overledger busca conectar múltiples blockchains y redes existentes.</t>
-        </is>
-      </c>
+        <v>0.001065326342582507</v>
+      </c>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4938,10 +4908,10 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>2290130494.717649</v>
+        <v>2290130494.717648</v>
       </c>
       <c r="N49" t="n">
-        <v>2290130494.717649</v>
+        <v>2290824910.967649</v>
       </c>
       <c r="O49" t="n">
         <v>1</v>
@@ -4950,13 +4920,13 @@
         <v>45699.87511574074</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R49" t="b">
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>0.0009655429414597221</v>
+        <v>0.0009966505947972438</v>
       </c>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
@@ -4970,7 +4940,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4989,16 +4959,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="F50" t="n">
-        <v>2270709990</v>
+        <v>2277857846</v>
       </c>
       <c r="G50" t="n">
         <v>49</v>
       </c>
       <c r="H50" t="n">
-        <v>3224800</v>
+        <v>6730334</v>
       </c>
       <c r="I50" t="n">
         <v>1.15</v>
@@ -5007,16 +4977,16 @@
         <v>1.14</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.002379409004520161</v>
+        <v>-0.000936034336752822</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.19936</v>
+        <v>0.07034</v>
       </c>
       <c r="M50" t="n">
-        <v>1984602261.82023</v>
+        <v>1984709596.999284</v>
       </c>
       <c r="N50" t="n">
-        <v>1984602261.82023</v>
+        <v>1984709435.346785</v>
       </c>
       <c r="O50" t="n">
         <v>1.26</v>
@@ -5025,13 +4995,13 @@
         <v>45377.89175925926</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R50" t="b">
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0.0009541585558499936</v>
+        <v>0.0009893433275099672</v>
       </c>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
@@ -5045,143 +5015,173 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>mantle</t>
+          <t>aave</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>mnt</t>
+          <t>aave</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Mantle</t>
+          <t>Aave</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.679908</v>
+        <v>147.2</v>
       </c>
       <c r="F51" t="n">
-        <v>2245256772</v>
+        <v>2271547914</v>
       </c>
       <c r="G51" t="n">
         <v>50</v>
       </c>
       <c r="H51" t="n">
-        <v>34224894</v>
+        <v>293261212</v>
       </c>
       <c r="I51" t="n">
-        <v>0.701793</v>
+        <v>156.09</v>
       </c>
       <c r="J51" t="n">
-        <v>0.673049</v>
+        <v>144.24</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.02121843084676744</v>
+        <v>-7.21563997944952</v>
       </c>
       <c r="L51" t="n">
-        <v>-3.1601</v>
+        <v>-4.67855</v>
       </c>
       <c r="M51" t="n">
-        <v>3302294382.53684</v>
+        <v>15429843.6986945</v>
       </c>
       <c r="N51" t="n">
-        <v>6219316794.889999</v>
+        <v>16000000</v>
       </c>
       <c r="O51" t="n">
-        <v>2.86</v>
+        <v>661.6900000000001</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>45938.71164351852</v>
+        <v>44334.55554398148</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R51" t="b">
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0.0009392377672958091</v>
-      </c>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
-      <c r="AA51" t="inlineStr"/>
+        <v>0.0009855863260925439</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>DeFi</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Préstamos</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>N/A (token de gobernanza)</t>
+        </is>
+      </c>
+      <c r="W51" t="n">
+        <v>2017</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>aave.com</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>Préstamos y créditos descentralizados</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>Token ERC-20 sobre Ethereum</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>Pionero en préstamos y créditos flash (flash loans) dentro de DeFi.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>pump-fun</t>
+          <t>mantle</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>mnt</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Pump.fun</t>
+          <t>Mantle</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.0047743</v>
+        <v>0.6638230000000001</v>
       </c>
       <c r="F52" t="n">
-        <v>2224546738</v>
+        <v>2191878963</v>
       </c>
       <c r="G52" t="n">
         <v>51</v>
       </c>
       <c r="H52" t="n">
-        <v>152156872</v>
+        <v>50044353</v>
       </c>
       <c r="I52" t="n">
-        <v>0.00465735</v>
+        <v>0.68062</v>
       </c>
       <c r="J52" t="n">
-        <v>0.00430512</v>
+        <v>0.645253</v>
       </c>
       <c r="K52" t="n">
-        <v>0.00036175</v>
+        <v>-0.01230162116184752</v>
       </c>
       <c r="L52" t="n">
-        <v>7.8613</v>
+        <v>-1.84702</v>
       </c>
       <c r="M52" t="n">
-        <v>465942213332.9943</v>
+        <v>3302294382.53684</v>
       </c>
       <c r="N52" t="n">
-        <v>831454033588.2654</v>
+        <v>6219316794.889999</v>
       </c>
       <c r="O52" t="n">
-        <v>0.00881908</v>
+        <v>2.86</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>45914.36296296296</v>
+        <v>45938.71164351852</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0.0009270974541038201</v>
+        <v>0.0009381505753060643</v>
       </c>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
@@ -5195,248 +5195,248 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>worldcoin-wld</t>
+          <t>polkadot</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>wld</t>
+          <t>dot</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Worldcoin</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.569147</v>
+        <v>1.18</v>
       </c>
       <c r="F53" t="n">
-        <v>2115298987</v>
+        <v>2007319649</v>
       </c>
       <c r="G53" t="n">
         <v>52</v>
       </c>
       <c r="H53" t="n">
-        <v>901731266</v>
+        <v>244497952</v>
       </c>
       <c r="I53" t="n">
-        <v>0.586331</v>
+        <v>1.28</v>
       </c>
       <c r="J53" t="n">
-        <v>0.510792</v>
+        <v>1.15</v>
       </c>
       <c r="K53" t="n">
-        <v>0.074793</v>
+        <v>-0.06470265556528054</v>
       </c>
       <c r="L53" t="n">
-        <v>14.87998</v>
+        <v>-5.18136</v>
       </c>
       <c r="M53" t="n">
-        <v>3716610114.975046</v>
+        <v>1704886483.786375</v>
       </c>
       <c r="N53" t="n">
-        <v>10000000000</v>
+        <v>1704899329.838796</v>
       </c>
       <c r="O53" t="n">
-        <v>11.74</v>
+        <v>54.98</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>45360.67409722223</v>
+        <v>44504.25704861111</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R53" t="b">
         <v>1</v>
       </c>
       <c r="S53" t="n">
-        <v>0.0008630559410546174</v>
-      </c>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
-      <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr"/>
-      <c r="AA53" t="inlineStr"/>
+        <v>0.0008282619736069203</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Layer 0</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Proof of Stake (NPoS)</t>
+        </is>
+      </c>
+      <c r="W53" t="n">
+        <v>2020</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>polkadot.network</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>Interoperabilidad entre blockchains</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Layer 0, relay chain)</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>Permite que blockchains distintas (parachains) se comuniquen entre sí.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>polkadot</t>
+          <t>aster-2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>dot</t>
+          <t>aster</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1.24</v>
+        <v>0.705728</v>
       </c>
       <c r="F54" t="n">
-        <v>2110569559</v>
+        <v>1913698382</v>
       </c>
       <c r="G54" t="n">
         <v>53</v>
       </c>
       <c r="H54" t="n">
-        <v>235174355</v>
+        <v>157013298</v>
       </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>0.731046</v>
       </c>
       <c r="J54" t="n">
-        <v>1.22</v>
+        <v>0.691268</v>
       </c>
       <c r="K54" t="n">
-        <v>0.01278622</v>
+        <v>-0.0225634663327704</v>
       </c>
       <c r="L54" t="n">
-        <v>0.8834</v>
+        <v>-3.03764</v>
       </c>
       <c r="M54" t="n">
-        <v>1704715523.71559</v>
+        <v>2710487455.649731</v>
       </c>
       <c r="N54" t="n">
-        <v>1704725434.729766</v>
+        <v>7795741639.235296</v>
       </c>
       <c r="O54" t="n">
-        <v>54.98</v>
+        <v>2.41</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>44504.25704861111</v>
+        <v>45924.13766203704</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R54" t="b">
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>0.0008602835295202394</v>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Interoperabilidad</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Layer 0</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Proof of Stake (NPoS)</t>
-        </is>
-      </c>
-      <c r="W54" t="n">
-        <v>2020</v>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>polkadot.network</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>Interoperabilidad entre blockchains</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Layer 0, relay chain)</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>Permite que blockchains distintas (parachains) se comuniquen entre sí.</t>
-        </is>
-      </c>
+        <v>0.0007725188637255505</v>
+      </c>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>aster-2</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>aster</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Sky</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.7336</v>
+        <v>0.078918</v>
       </c>
       <c r="F55" t="n">
-        <v>1988412632</v>
+        <v>1848788378</v>
       </c>
       <c r="G55" t="n">
         <v>54</v>
       </c>
       <c r="H55" t="n">
-        <v>104763058</v>
+        <v>54904330</v>
       </c>
       <c r="I55" t="n">
-        <v>0.748192</v>
+        <v>0.086122</v>
       </c>
       <c r="J55" t="n">
-        <v>0.725587</v>
+        <v>0.075368</v>
       </c>
       <c r="K55" t="n">
-        <v>0.00587709</v>
+        <v>0.0035739</v>
       </c>
       <c r="L55" t="n">
-        <v>0.63976</v>
+        <v>4.72112</v>
       </c>
       <c r="M55" t="n">
-        <v>2710487455.649731</v>
+        <v>23427763031.73964</v>
       </c>
       <c r="N55" t="n">
-        <v>7795741639.235296</v>
+        <v>23459804203.60596</v>
       </c>
       <c r="O55" t="n">
-        <v>2.41</v>
+        <v>0.100535</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>45924.13766203704</v>
+        <v>45630.09302083333</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R55" t="b">
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0007886746006140415</v>
+        <v>0.0007338707488119577</v>
       </c>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
@@ -5450,68 +5450,68 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>worldcoin-wld</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>wld</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Morpho</t>
+          <t>Worldcoin</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2.7</v>
+        <v>0.494779</v>
       </c>
       <c r="F56" t="n">
-        <v>1887686340</v>
+        <v>1839776123</v>
       </c>
       <c r="G56" t="n">
         <v>55</v>
       </c>
       <c r="H56" t="n">
-        <v>25300729</v>
+        <v>582507152</v>
       </c>
       <c r="I56" t="n">
-        <v>2.79</v>
+        <v>0.570169</v>
       </c>
       <c r="J56" t="n">
-        <v>2.66</v>
+        <v>0.479532</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.04959945040026925</v>
+        <v>-0.06908515140453114</v>
       </c>
       <c r="L56" t="n">
-        <v>-1.8954</v>
+        <v>-12.17096</v>
       </c>
       <c r="M56" t="n">
-        <v>699556652.9224828</v>
+        <v>3718065690.775289</v>
       </c>
       <c r="N56" t="n">
-        <v>1000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="O56" t="n">
-        <v>4.17</v>
+        <v>11.74</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>45674.19883101852</v>
+        <v>45360.67409722223</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S56" t="n">
-        <v>0.0007296284043814454</v>
+        <v>0.0007285047551991612</v>
       </c>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
@@ -5525,68 +5525,68 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>pax-gold</t>
+          <t>world-liberty-financial</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>paxg</t>
+          <t>wlfi</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>PAX Gold</t>
+          <t>World Liberty Financial</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4277.06</v>
+        <v>0.056742</v>
       </c>
       <c r="F57" t="n">
-        <v>1860087960</v>
+        <v>1803133010</v>
       </c>
       <c r="G57" t="n">
         <v>56</v>
       </c>
       <c r="H57" t="n">
-        <v>45264204</v>
+        <v>49316785</v>
       </c>
       <c r="I57" t="n">
-        <v>4280.33</v>
+        <v>0.059219</v>
       </c>
       <c r="J57" t="n">
-        <v>4275.7</v>
+        <v>0.055922</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.179323987517819</v>
+        <v>-0.001156049151996331</v>
       </c>
       <c r="L57" t="n">
-        <v>-0.02825</v>
+        <v>-2.0139</v>
       </c>
       <c r="M57" t="n">
-        <v>434898.623539</v>
+        <v>31778337976</v>
       </c>
       <c r="N57" t="n">
-        <v>434898.623539</v>
+        <v>100000000000</v>
       </c>
       <c r="O57" t="n">
-        <v>5619.09</v>
+        <v>0.331336</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>46050.93814814815</v>
+        <v>45901.18065972222</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R57" t="b">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0.0007134501124099534</v>
+        <v>0.0007066870513824157</v>
       </c>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
@@ -5600,68 +5600,68 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>pax-gold</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>paxg</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Pepe</t>
+          <t>PAX Gold</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4.4e-06</v>
+        <v>4137.84</v>
       </c>
       <c r="F58" t="n">
-        <v>1850216165</v>
+        <v>1799327494</v>
       </c>
       <c r="G58" t="n">
         <v>57</v>
       </c>
       <c r="H58" t="n">
-        <v>221340576</v>
+        <v>216736087</v>
       </c>
       <c r="I58" t="n">
-        <v>4.46e-06</v>
+        <v>4277.43</v>
       </c>
       <c r="J58" t="n">
-        <v>4.26e-06</v>
+        <v>4123.5</v>
       </c>
       <c r="K58" t="n">
-        <v>1.2419e-08</v>
+        <v>-137.5311100150984</v>
       </c>
       <c r="L58" t="n">
-        <v>0.03035</v>
+        <v>-3.22734</v>
       </c>
       <c r="M58" t="n">
-        <v>420690000000000</v>
+        <v>434898.623539</v>
       </c>
       <c r="N58" t="n">
-        <v>420690000000000</v>
+        <v>434898.623539</v>
       </c>
       <c r="O58" t="n">
-        <v>2.803e-05</v>
+        <v>5619.09</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>45635.35457175926</v>
+        <v>46050.93814814815</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R58" t="b">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0007076632226797332</v>
+        <v>0.0007044212062027803</v>
       </c>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
@@ -5675,68 +5675,68 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>world-liberty-financial</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>wlfi</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>World Liberty Financial</t>
+          <t>Morpho</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.057871</v>
+        <v>2.56</v>
       </c>
       <c r="F59" t="n">
-        <v>1839035952</v>
+        <v>1792931419</v>
       </c>
       <c r="G59" t="n">
         <v>58</v>
       </c>
       <c r="H59" t="n">
-        <v>30663601</v>
+        <v>37143462</v>
       </c>
       <c r="I59" t="n">
-        <v>0.059744</v>
+        <v>2.74</v>
       </c>
       <c r="J59" t="n">
-        <v>0.057715</v>
+        <v>2.48</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.000902270316658009</v>
+        <v>-0.1192164771803483</v>
       </c>
       <c r="L59" t="n">
-        <v>-1.63875</v>
+        <v>-4.47209</v>
       </c>
       <c r="M59" t="n">
-        <v>31778313765</v>
+        <v>699612259.0237948</v>
       </c>
       <c r="N59" t="n">
-        <v>100000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="O59" t="n">
-        <v>0.331336</v>
+        <v>4.17</v>
       </c>
       <c r="P59" s="1" t="n">
-        <v>45901.18065972222</v>
+        <v>45674.19883101852</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R59" t="b">
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>0.000701109332552216</v>
+        <v>0.0007006129143161251</v>
       </c>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
@@ -5750,248 +5750,248 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>internet-computer</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>icp</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Internet Computer</t>
+          <t>Pepe</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3.19</v>
+        <v>4.2e-06</v>
       </c>
       <c r="F60" t="n">
-        <v>1778798653</v>
+        <v>1767019114</v>
       </c>
       <c r="G60" t="n">
         <v>59</v>
       </c>
       <c r="H60" t="n">
-        <v>78606572</v>
+        <v>328614208</v>
       </c>
       <c r="I60" t="n">
-        <v>3.35</v>
+        <v>4.42e-06</v>
       </c>
       <c r="J60" t="n">
-        <v>3.12</v>
+        <v>4.13e-06</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.03047850031257626</v>
+        <v>-1.73908170515e-07</v>
       </c>
       <c r="L60" t="n">
-        <v>-1.17424</v>
+        <v>-3.98642</v>
       </c>
       <c r="M60" t="n">
-        <v>556917030.5505874</v>
+        <v>420690000000000</v>
       </c>
       <c r="N60" t="n">
-        <v>556917120.3081846</v>
+        <v>420690000000000</v>
       </c>
       <c r="O60" t="n">
-        <v>700.65</v>
+        <v>2.803e-05</v>
       </c>
       <c r="P60" s="1" t="n">
-        <v>44326.33741898148</v>
+        <v>45635.35457175926</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R60" t="b">
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0.000665797962435707</v>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>Infraestructura descentralizada</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Hosting</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Proof of Stake (Chain Key)</t>
-        </is>
-      </c>
-      <c r="W60" t="n">
-        <v>2021</v>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>internetcomputer.org</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>Hosting descentralizado de aplicaciones</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Layer 1)</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>Busca reemplazar servidores tradicionales con "canisters" en cadena.</t>
-        </is>
-      </c>
+        <v>0.0006851844490626633</v>
+      </c>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>internet-computer</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>icp</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Sky</t>
+          <t>Internet Computer</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.07538599999999999</v>
+        <v>3</v>
       </c>
       <c r="F61" t="n">
-        <v>1766226743</v>
+        <v>1671242413</v>
       </c>
       <c r="G61" t="n">
         <v>60</v>
       </c>
       <c r="H61" t="n">
-        <v>13841969</v>
+        <v>85782383</v>
       </c>
       <c r="I61" t="n">
-        <v>0.07837</v>
+        <v>3.2</v>
       </c>
       <c r="J61" t="n">
-        <v>0.074742</v>
+        <v>2.91</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.002002319107970107</v>
+        <v>-0.1799278695271669</v>
       </c>
       <c r="L61" t="n">
-        <v>-2.66222</v>
+        <v>-5.62245</v>
       </c>
       <c r="M61" t="n">
-        <v>23429167587.39992</v>
+        <v>556920108.2163103</v>
       </c>
       <c r="N61" t="n">
-        <v>23459804203.60596</v>
+        <v>556920196.8271762</v>
       </c>
       <c r="O61" t="n">
-        <v>0.100535</v>
+        <v>700.65</v>
       </c>
       <c r="P61" s="1" t="n">
-        <v>45630.09302083333</v>
+        <v>44326.33741898148</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S61" t="n">
-        <v>0.0006584282533941139</v>
-      </c>
-      <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
-      <c r="X61" t="inlineStr"/>
-      <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr"/>
-      <c r="AA61" t="inlineStr"/>
+        <v>0.0006281579705818915</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Infraestructura descentralizada</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Hosting</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Proof of Stake (Chain Key)</t>
+        </is>
+      </c>
+      <c r="W61" t="n">
+        <v>2021</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>internetcomputer.org</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>Hosting descentralizado de aplicaciones</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Layer 1)</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>Busca reemplazar servidores tradicionales con "canisters" en cadena.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>htx-dao</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>htx</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>USDD</t>
+          <t>HTX DAO</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.999459</v>
+        <v>1.71e-06</v>
       </c>
       <c r="F62" t="n">
-        <v>1551884400</v>
+        <v>1540082967</v>
       </c>
       <c r="G62" t="n">
         <v>61</v>
       </c>
       <c r="H62" t="n">
-        <v>1407159</v>
+        <v>76593027</v>
       </c>
       <c r="I62" t="n">
-        <v>0.999821</v>
+        <v>1.72e-06</v>
       </c>
       <c r="J62" t="n">
-        <v>0.9963109999999999</v>
+        <v>1.69e-06</v>
       </c>
       <c r="K62" t="n">
-        <v>0.00187557</v>
+        <v>1.448e-08</v>
       </c>
       <c r="L62" t="n">
-        <v>0.19288</v>
+        <v>1.04611</v>
       </c>
       <c r="M62" t="n">
-        <v>1552724047</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="N62" t="n">
-        <v>1561034969</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="O62" t="n">
-        <v>1.24</v>
+        <v>3.75e-06</v>
       </c>
       <c r="P62" s="1" t="n">
-        <v>46212.39942129629</v>
+        <v>45629.67800925926</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R62" t="b">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0.0005327798274028898</v>
+        <v>0.0005500642249550824</v>
       </c>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
@@ -6005,68 +6005,68 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>htx-dao</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>htx</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>HTX DAO</t>
+          <t>USDD</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1.71e-06</v>
+        <v>0.998519</v>
       </c>
       <c r="F63" t="n">
-        <v>1532950340</v>
+        <v>1537334861</v>
       </c>
       <c r="G63" t="n">
         <v>62</v>
       </c>
       <c r="H63" t="n">
-        <v>62256208</v>
+        <v>2247162</v>
       </c>
       <c r="I63" t="n">
-        <v>1.72e-06</v>
+        <v>0.999598</v>
       </c>
       <c r="J63" t="n">
-        <v>1.7e-06</v>
+        <v>0.997117</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.4842378741e-08</v>
+        <v>0.00140294</v>
       </c>
       <c r="L63" t="n">
-        <v>-0.9144</v>
+        <v>0.13648</v>
       </c>
       <c r="M63" t="n">
-        <v>898232728634017.2</v>
+        <v>1539682561</v>
       </c>
       <c r="N63" t="n">
-        <v>898232728634017.2</v>
+        <v>1539527810</v>
       </c>
       <c r="O63" t="n">
-        <v>3.75e-06</v>
+        <v>1.24</v>
       </c>
       <c r="P63" s="1" t="n">
-        <v>45629.67800925926</v>
+        <v>46212.39942129629</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R63" t="b">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0.0005216805979957382</v>
+        <v>0.0005484279730688132</v>
       </c>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
@@ -6080,68 +6080,68 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>united-stables</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>arb</t>
+          <t>u</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Arbitrum</t>
+          <t>United Stables</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.222546</v>
+        <v>0.999685</v>
       </c>
       <c r="F64" t="n">
-        <v>1510102474</v>
+        <v>1521359338</v>
       </c>
       <c r="G64" t="n">
         <v>63</v>
       </c>
       <c r="H64" t="n">
-        <v>331283079</v>
+        <v>143067957</v>
       </c>
       <c r="I64" t="n">
-        <v>0.236179</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
-        <v>0.218077</v>
+        <v>0.999323</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.000257700923587345</v>
+        <v>-0.0001200862768026</v>
       </c>
       <c r="L64" t="n">
-        <v>-0.38116</v>
+        <v>-0.01824</v>
       </c>
       <c r="M64" t="n">
-        <v>6785574605</v>
+        <v>1521842391.63</v>
       </c>
       <c r="N64" t="n">
-        <v>10000000000</v>
+        <v>1541830391.63</v>
       </c>
       <c r="O64" t="n">
-        <v>2.39</v>
+        <v>1.008</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>45303.18748842592</v>
+        <v>46058.54591435185</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R64" t="b">
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0005082870782647422</v>
+        <v>0.0005389159747532879</v>
       </c>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
@@ -6155,248 +6155,248 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ethereum-classic</t>
+          <t>spiko-amundi-overnight-swap-fund-eur</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>eursafo</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Ethereum Classic</t>
+          <t>Spiko Amundi Overnight Swap Fund (EUR)</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>9.48</v>
+        <v>1.15</v>
       </c>
       <c r="F65" t="n">
-        <v>1500778097</v>
+        <v>1486924506</v>
       </c>
       <c r="G65" t="n">
         <v>64</v>
       </c>
       <c r="H65" t="n">
-        <v>66682110</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>9.609999999999999</v>
+        <v>1.16</v>
       </c>
       <c r="J65" t="n">
-        <v>9.279999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="K65" t="n">
-        <v>0.02589166</v>
+        <v>-0.00496535212476612</v>
       </c>
       <c r="L65" t="n">
-        <v>0.08377999999999999</v>
+        <v>-0.4288</v>
       </c>
       <c r="M65" t="n">
-        <v>158300159.3516731</v>
+        <v>1289618689.24777</v>
       </c>
       <c r="N65" t="n">
-        <v>158300993.7583609</v>
+        <v>1290400520.88146</v>
       </c>
       <c r="O65" t="n">
-        <v>167.09</v>
+        <v>1.18</v>
       </c>
       <c r="P65" s="1" t="n">
-        <v>44322.44053240741</v>
+        <v>46255.48263888889</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R65" t="b">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0.0005028210873783835</v>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Plataforma de contratos inteligentes</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Layer 1</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Proof of Work</t>
-        </is>
-      </c>
-      <c r="W65" t="n">
-        <v>2016</v>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>ethereumclassic.org</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>Contratos inteligentes (cadena original)</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>Blockchain propia (fork de Ethereum)</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>Mantiene la cadena original de Ethereum tras la bifurcación de 2016.</t>
-        </is>
-      </c>
+        <v>0.00051841310520846</v>
+      </c>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr"/>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>spiko-amundi-overnight-swap-fund-eur</t>
+          <t>ethereum-classic</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>eursafo</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Spiko Amundi Overnight Swap Fund (EUR)</t>
+          <t>Ethereum Classic</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1.16</v>
+        <v>9.16</v>
       </c>
       <c r="F66" t="n">
-        <v>1493327917</v>
+        <v>1450440617</v>
       </c>
       <c r="G66" t="n">
         <v>65</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>101110639</v>
       </c>
       <c r="I66" t="n">
-        <v>1.16</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="J66" t="n">
-        <v>1.15</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="K66" t="n">
-        <v>0.00344531</v>
+        <v>-0.3224684997324374</v>
       </c>
       <c r="L66" t="n">
-        <v>0.29842</v>
+        <v>-3.38828</v>
       </c>
       <c r="M66" t="n">
-        <v>1289618689.24777</v>
+        <v>158311851.2298701</v>
       </c>
       <c r="N66" t="n">
-        <v>1289618689.24777</v>
+        <v>158312284.7914701</v>
       </c>
       <c r="O66" t="n">
-        <v>1.18</v>
+        <v>167.09</v>
       </c>
       <c r="P66" s="1" t="n">
-        <v>46255.48263888889</v>
+        <v>44322.44053240741</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R66" t="b">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0.0004984537590322932</v>
-      </c>
-      <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr"/>
-      <c r="X66" t="inlineStr"/>
-      <c r="Y66" t="inlineStr"/>
-      <c r="Z66" t="inlineStr"/>
-      <c r="AA66" t="inlineStr"/>
+        <v>0.0004966902050748109</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Plataforma de contratos inteligentes</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Layer 1</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Proof of Work</t>
+        </is>
+      </c>
+      <c r="W66" t="n">
+        <v>2016</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>ethereumclassic.org</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>Contratos inteligentes (cadena original)</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>Blockchain propia (fork de Ethereum)</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>Mantiene la cadena original de Ethereum tras la bifurcación de 2016.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>united-stables</t>
+          <t>usdgo</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>usdgo</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>United Stables</t>
+          <t>USDGO</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.999939</v>
+        <v>0.999961</v>
       </c>
       <c r="F67" t="n">
-        <v>1482767260</v>
+        <v>1405685505</v>
       </c>
       <c r="G67" t="n">
         <v>66</v>
       </c>
       <c r="H67" t="n">
-        <v>73034322</v>
+        <v>21425849</v>
       </c>
       <c r="I67" t="n">
         <v>1</v>
       </c>
       <c r="J67" t="n">
-        <v>0.999428</v>
+        <v>0.999569</v>
       </c>
       <c r="K67" t="n">
-        <v>0.00046141</v>
+        <v>0.0001201</v>
       </c>
       <c r="L67" t="n">
-        <v>0.04588</v>
+        <v>0.0092</v>
       </c>
       <c r="M67" t="n">
-        <v>1482857391.63</v>
+        <v>1405780804.97</v>
       </c>
       <c r="N67" t="n">
-        <v>1482857391.63</v>
+        <v>1405780804.97</v>
       </c>
       <c r="O67" t="n">
-        <v>1.008</v>
+        <v>1.002</v>
       </c>
       <c r="P67" s="1" t="n">
-        <v>46058.54591435185</v>
+        <v>46092.00303240741</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R67" t="b">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.000492263055362122</v>
+        <v>0.0004700425297558152</v>
       </c>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
@@ -6410,68 +6410,68 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>venice-token</t>
+          <t>bitget-token</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>vvv</t>
+          <t>bgb</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Venice Token</t>
+          <t>Bitget Token</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>30.39</v>
+        <v>2</v>
       </c>
       <c r="F68" t="n">
-        <v>1464276446</v>
+        <v>1401020986</v>
       </c>
       <c r="G68" t="n">
         <v>67</v>
       </c>
       <c r="H68" t="n">
-        <v>45333775</v>
+        <v>24694339</v>
       </c>
       <c r="I68" t="n">
-        <v>31.66</v>
+        <v>2.04</v>
       </c>
       <c r="J68" t="n">
-        <v>29.1</v>
+        <v>1.96</v>
       </c>
       <c r="K68" t="n">
-        <v>0.64928</v>
+        <v>-0.04226071514682195</v>
       </c>
       <c r="L68" t="n">
-        <v>2.07967</v>
+        <v>-2.07292</v>
       </c>
       <c r="M68" t="n">
-        <v>48180888.23223712</v>
+        <v>699992029.6481038</v>
       </c>
       <c r="N68" t="n">
-        <v>81058245.79412135</v>
+        <v>910920874.6481038</v>
       </c>
       <c r="O68" t="n">
-        <v>34.53</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="P68" s="1" t="n">
-        <v>46286.34548611111</v>
+        <v>45653.15375</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R68" t="b">
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0.0004814236587133856</v>
+        <v>0.0004672652249457795</v>
       </c>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
@@ -6485,68 +6485,68 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>bitget-token</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>bgb</t>
+          <t>arb</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Bitget Token</t>
+          <t>Arbitrum</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2.06</v>
+        <v>0.20396</v>
       </c>
       <c r="F69" t="n">
-        <v>1440844743</v>
+        <v>1384569299</v>
       </c>
       <c r="G69" t="n">
         <v>68</v>
       </c>
       <c r="H69" t="n">
-        <v>18336426</v>
+        <v>353688143</v>
       </c>
       <c r="I69" t="n">
-        <v>2.08</v>
+        <v>0.233802</v>
       </c>
       <c r="J69" t="n">
-        <v>2</v>
+        <v>0.200698</v>
       </c>
       <c r="K69" t="n">
-        <v>0.02820162</v>
+        <v>-0.01751778309882746</v>
       </c>
       <c r="L69" t="n">
-        <v>1.33113</v>
+        <v>-7.84335</v>
       </c>
       <c r="M69" t="n">
-        <v>699992029.6481038</v>
+        <v>6785574605</v>
       </c>
       <c r="N69" t="n">
-        <v>910920874.6481038</v>
+        <v>10000000000</v>
       </c>
       <c r="O69" t="n">
-        <v>8.449999999999999</v>
+        <v>2.39</v>
       </c>
       <c r="P69" s="1" t="n">
-        <v>45653.15375</v>
+        <v>45303.18748842592</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S69" t="n">
-        <v>0.0004676878911602436</v>
+        <v>0.0004574697134603933</v>
       </c>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
@@ -6560,68 +6560,68 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>usdgo</t>
+          <t>falcon-finance</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>usdgo</t>
+          <t>usdf</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>USDGO</t>
+          <t>Falcon USD</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.999829</v>
+        <v>0.9958900000000001</v>
       </c>
       <c r="F70" t="n">
-        <v>1407539791</v>
+        <v>1371720403</v>
       </c>
       <c r="G70" t="n">
         <v>69</v>
       </c>
       <c r="H70" t="n">
-        <v>12037464</v>
+        <v>424718</v>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0.996785</v>
       </c>
       <c r="J70" t="n">
-        <v>0.999684</v>
+        <v>0.995811</v>
       </c>
       <c r="K70" t="n">
-        <v>-4.8164414465091e-05</v>
+        <v>-0.000212570827806124</v>
       </c>
       <c r="L70" t="n">
-        <v>0.00213</v>
+        <v>-0.02529</v>
       </c>
       <c r="M70" t="n">
-        <v>1407780804.97</v>
+        <v>1377438577.534634</v>
       </c>
       <c r="N70" t="n">
-        <v>1407780804.97</v>
+        <v>1377438577.534634</v>
       </c>
       <c r="O70" t="n">
-        <v>1.002</v>
+        <v>1.075</v>
       </c>
       <c r="P70" s="1" t="n">
-        <v>46092.00303240741</v>
+        <v>45785.55951388889</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R70" t="b">
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>0.0004481643815356741</v>
+        <v>0.0004498193425080082</v>
       </c>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
@@ -6635,68 +6635,68 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>falcon-finance</t>
+          <t>bfusd</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>usdf</t>
+          <t>bfusd</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Falcon USD</t>
+          <t>BFUSD</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.996287</v>
+        <v>0.999285</v>
       </c>
       <c r="F71" t="n">
-        <v>1372311161</v>
+        <v>1318998182</v>
       </c>
       <c r="G71" t="n">
         <v>70</v>
       </c>
       <c r="H71" t="n">
-        <v>243744</v>
+        <v>2418026</v>
       </c>
       <c r="I71" t="n">
-        <v>0.997027</v>
+        <v>0.999842</v>
       </c>
       <c r="J71" t="n">
-        <v>0.995825</v>
+        <v>0.998856</v>
       </c>
       <c r="K71" t="n">
-        <v>0.00014679</v>
+        <v>-0.000435796602689664</v>
       </c>
       <c r="L71" t="n">
-        <v>0.01261</v>
+        <v>-0.04781</v>
       </c>
       <c r="M71" t="n">
-        <v>1377425695.547727</v>
+        <v>1320000000</v>
       </c>
       <c r="N71" t="n">
-        <v>1377425695.547727</v>
+        <v>1320000000</v>
       </c>
       <c r="O71" t="n">
-        <v>1.075</v>
+        <v>1.007</v>
       </c>
       <c r="P71" s="1" t="n">
-        <v>45785.55951388889</v>
+        <v>45940.56990740741</v>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R71" t="b">
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>0.0004275132033905924</v>
+        <v>0.0004184279647520026</v>
       </c>
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
@@ -6710,68 +6710,68 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>bfusd</t>
+          <t>venice-token</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>bfusd</t>
+          <t>vvv</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>BFUSD</t>
+          <t>Venice Token</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.999823</v>
+        <v>27.11</v>
       </c>
       <c r="F72" t="n">
-        <v>1319766748</v>
+        <v>1306844943</v>
       </c>
       <c r="G72" t="n">
         <v>71</v>
       </c>
       <c r="H72" t="n">
-        <v>2994702</v>
+        <v>42868049</v>
       </c>
       <c r="I72" t="n">
-        <v>0.999844</v>
+        <v>30.41</v>
       </c>
       <c r="J72" t="n">
-        <v>0.9995849999999999</v>
+        <v>26.62</v>
       </c>
       <c r="K72" t="n">
-        <v>0.00012028</v>
+        <v>-2.770333202562018</v>
       </c>
       <c r="L72" t="n">
-        <v>-8.000000000000001e-05</v>
+        <v>-9.330870000000001</v>
       </c>
       <c r="M72" t="n">
-        <v>1320000000</v>
+        <v>48210709.26338548</v>
       </c>
       <c r="N72" t="n">
-        <v>1320000000</v>
+        <v>81065296.20457117</v>
       </c>
       <c r="O72" t="n">
-        <v>1.007</v>
+        <v>34.53</v>
       </c>
       <c r="P72" s="1" t="n">
-        <v>45940.56990740741</v>
+        <v>46286.34548611111</v>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S72" t="n">
-        <v>0.000396711436946886</v>
+        <v>0.0004111917954637623</v>
       </c>
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
@@ -6785,7 +6785,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6804,34 +6804,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.04719838</v>
+        <v>0.04609591</v>
       </c>
       <c r="F73" t="n">
-        <v>1308528302</v>
+        <v>1278277820</v>
       </c>
       <c r="G73" t="n">
         <v>72</v>
       </c>
       <c r="H73" t="n">
-        <v>47407083</v>
+        <v>29621657</v>
       </c>
       <c r="I73" t="n">
-        <v>0.05004</v>
+        <v>0.0489498</v>
       </c>
       <c r="J73" t="n">
-        <v>0.04630187</v>
+        <v>0.045136</v>
       </c>
       <c r="K73" t="n">
-        <v>0.00095407</v>
+        <v>-0.001751469046742338</v>
       </c>
       <c r="L73" t="n">
-        <v>0.56796</v>
+        <v>-3.62464</v>
       </c>
       <c r="M73" t="n">
-        <v>27724007642.5208</v>
+        <v>27726432137.69469</v>
       </c>
       <c r="N73" t="n">
-        <v>27724481654.36061</v>
+        <v>27726512265.92985</v>
       </c>
       <c r="O73" t="n">
         <v>0.207411</v>
@@ -6840,13 +6840,13 @@
         <v>45504.69498842592</v>
       </c>
       <c r="Q73" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R73" t="b">
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0.0003901234103781581</v>
+        <v>0.0003941826230031546</v>
       </c>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
@@ -6860,7 +6860,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6879,34 +6879,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.120243</v>
+        <v>0.11572</v>
       </c>
       <c r="F74" t="n">
-        <v>1277184843</v>
+        <v>1229343996</v>
       </c>
       <c r="G74" t="n">
         <v>73</v>
       </c>
       <c r="H74" t="n">
-        <v>95872465</v>
+        <v>160169997</v>
       </c>
       <c r="I74" t="n">
-        <v>0.121327</v>
+        <v>0.124807</v>
       </c>
       <c r="J74" t="n">
-        <v>0.116262</v>
+        <v>0.112007</v>
       </c>
       <c r="K74" t="n">
-        <v>0.00340135</v>
+        <v>-0.00483219239587962</v>
       </c>
       <c r="L74" t="n">
-        <v>2.56314</v>
+        <v>-4.00707</v>
       </c>
       <c r="M74" t="n">
-        <v>10621663168.56562</v>
+        <v>10622244875.03591</v>
       </c>
       <c r="N74" t="n">
-        <v>10621663168.56562</v>
+        <v>10622244875.03591</v>
       </c>
       <c r="O74" t="n">
         <v>1.29</v>
@@ -6915,13 +6915,13 @@
         <v>45364.45493055556</v>
       </c>
       <c r="Q74" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R74" t="b">
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>0.0003717497365937372</v>
+        <v>0.0003650468975899575</v>
       </c>
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
@@ -6935,143 +6935,173 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>gatechain-token</t>
+          <t>algorand</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>gt</t>
+          <t>algo</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Algorand</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>11.32</v>
+        <v>0.132643</v>
       </c>
       <c r="F75" t="n">
-        <v>1207191445</v>
+        <v>1199789437</v>
       </c>
       <c r="G75" t="n">
         <v>74</v>
       </c>
       <c r="H75" t="n">
-        <v>3245938</v>
+        <v>202471569</v>
       </c>
       <c r="I75" t="n">
-        <v>11.52</v>
+        <v>0.137178</v>
       </c>
       <c r="J75" t="n">
-        <v>10.91</v>
+        <v>0.115069</v>
       </c>
       <c r="K75" t="n">
-        <v>0.410629</v>
+        <v>0.01542584</v>
       </c>
       <c r="L75" t="n">
-        <v>3.58984</v>
+        <v>13.0003</v>
       </c>
       <c r="M75" t="n">
-        <v>106642631.3647594</v>
+        <v>9057776356.697313</v>
       </c>
       <c r="N75" t="n">
-        <v>118893925.8661137</v>
+        <v>9057797996.419762</v>
       </c>
       <c r="O75" t="n">
-        <v>25.38</v>
+        <v>3.56</v>
       </c>
       <c r="P75" s="1" t="n">
-        <v>45682.66666666666</v>
+        <v>43636.28563657407</v>
       </c>
       <c r="Q75" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S75" t="n">
-        <v>0.0003307192982520359</v>
-      </c>
-      <c r="T75" t="inlineStr"/>
-      <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr"/>
-      <c r="W75" t="inlineStr"/>
-      <c r="X75" t="inlineStr"/>
-      <c r="Y75" t="inlineStr"/>
-      <c r="Z75" t="inlineStr"/>
-      <c r="AA75" t="inlineStr"/>
+        <v>0.0003474497951086118</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Plataforma de contratos inteligentes</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Layer 1</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Pure Proof of Stake</t>
+        </is>
+      </c>
+      <c r="W75" t="n">
+        <v>2019</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>algorand.com</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>Contratos inteligentes de alta eficiencia</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Layer 1)</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>Fundada por Silvio Micali, ganador del Premio Turing.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>lighter</t>
+          <t>gatechain-token</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>lit</t>
+          <t>gt</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Lighter</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4.72</v>
+        <v>10.88</v>
       </c>
       <c r="F76" t="n">
-        <v>1180731234</v>
+        <v>1160531563</v>
       </c>
       <c r="G76" t="n">
         <v>75</v>
       </c>
       <c r="H76" t="n">
-        <v>58496380</v>
+        <v>4608829</v>
       </c>
       <c r="I76" t="n">
-        <v>4.89</v>
+        <v>11.36</v>
       </c>
       <c r="J76" t="n">
-        <v>4.69</v>
+        <v>10.78</v>
       </c>
       <c r="K76" t="n">
-        <v>-0.08699979852313344</v>
+        <v>-0.3825807371700041</v>
       </c>
       <c r="L76" t="n">
-        <v>-1.87926</v>
+        <v>-3.44934</v>
       </c>
       <c r="M76" t="n">
-        <v>250000000</v>
+        <v>106643867.5587171</v>
       </c>
       <c r="N76" t="n">
-        <v>1000000000</v>
+        <v>118895217.5817878</v>
       </c>
       <c r="O76" t="n">
-        <v>7.86</v>
+        <v>25.38</v>
       </c>
       <c r="P76" s="1" t="n">
-        <v>46021.04538194444</v>
+        <v>45682.66666666666</v>
       </c>
       <c r="Q76" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R76" t="b">
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0003152082059638188</v>
+        <v>0.0003240752344535956</v>
       </c>
       <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr"/>
@@ -7085,68 +7115,68 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>jupiter-exchange-solana</t>
+          <t>lighter</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>jup</t>
+          <t>lit</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Lighter</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.337782</v>
+        <v>4.37</v>
       </c>
       <c r="F77" t="n">
-        <v>1121221656</v>
+        <v>1090939386</v>
       </c>
       <c r="G77" t="n">
         <v>76</v>
       </c>
       <c r="H77" t="n">
-        <v>71175471</v>
+        <v>97238180</v>
       </c>
       <c r="I77" t="n">
-        <v>0.349064</v>
+        <v>4.74</v>
       </c>
       <c r="J77" t="n">
-        <v>0.333481</v>
+        <v>4.32</v>
       </c>
       <c r="K77" t="n">
-        <v>-0.00995213786966459</v>
+        <v>-0.3215552809411752</v>
       </c>
       <c r="L77" t="n">
-        <v>-3.12964</v>
+        <v>-6.89839</v>
       </c>
       <c r="M77" t="n">
-        <v>3319369204.37</v>
+        <v>250000000</v>
       </c>
       <c r="N77" t="n">
-        <v>6861486605.78232</v>
+        <v>1000000000</v>
       </c>
       <c r="O77" t="n">
-        <v>2</v>
+        <v>7.86</v>
       </c>
       <c r="P77" s="1" t="n">
-        <v>45322.29359953704</v>
+        <v>46021.04538194444</v>
       </c>
       <c r="Q77" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0002803234291042975</v>
+        <v>0.0002826393033483828</v>
       </c>
       <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr"/>
@@ -7160,173 +7190,143 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>algorand</t>
+          <t>jupiter-exchange-solana</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>algo</t>
+          <t>jup</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Algorand</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.116621</v>
+        <v>0.328163</v>
       </c>
       <c r="F78" t="n">
-        <v>1056297663</v>
+        <v>1089550785</v>
       </c>
       <c r="G78" t="n">
         <v>77</v>
       </c>
       <c r="H78" t="n">
-        <v>54255734</v>
+        <v>154089728</v>
       </c>
       <c r="I78" t="n">
-        <v>0.122291</v>
+        <v>0.373954</v>
       </c>
       <c r="J78" t="n">
-        <v>0.114367</v>
+        <v>0.321335</v>
       </c>
       <c r="K78" t="n">
-        <v>-0.00112436041593722</v>
+        <v>-0.0104877932576023</v>
       </c>
       <c r="L78" t="n">
-        <v>-1.18246</v>
+        <v>-3.09456</v>
       </c>
       <c r="M78" t="n">
-        <v>9057509901.325378</v>
+        <v>3319369204.37</v>
       </c>
       <c r="N78" t="n">
-        <v>9057560465.347652</v>
+        <v>6861486562.065324</v>
       </c>
       <c r="O78" t="n">
-        <v>3.56</v>
+        <v>2</v>
       </c>
       <c r="P78" s="1" t="n">
-        <v>43636.28563657407</v>
+        <v>45322.29359953704</v>
       </c>
       <c r="Q78" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R78" t="b">
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>0.0002422646983125228</v>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>Plataforma de contratos inteligentes</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>Layer 1</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>Pure Proof of Stake</t>
-        </is>
-      </c>
-      <c r="W78" t="n">
-        <v>2019</v>
-      </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>algorand.com</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>Contratos inteligentes de alta eficiencia</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Layer 1)</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>Fundada por Silvio Micali, ganador del Premio Turing.</t>
-        </is>
-      </c>
+        <v>0.0002818125153694893</v>
+      </c>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr"/>
+      <c r="X78" t="inlineStr"/>
+      <c r="Y78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr"/>
+      <c r="AA78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>render-token</t>
+          <t>just</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>render</t>
+          <t>jst</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Render</t>
+          <t>JUST</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2.04</v>
+        <v>0.130378</v>
       </c>
       <c r="F79" t="n">
-        <v>1056012807</v>
+        <v>1067564318</v>
       </c>
       <c r="G79" t="n">
         <v>78</v>
       </c>
       <c r="H79" t="n">
-        <v>91707565</v>
+        <v>31352283</v>
       </c>
       <c r="I79" t="n">
-        <v>2.09</v>
+        <v>0.131925</v>
       </c>
       <c r="J79" t="n">
-        <v>1.94</v>
+        <v>0.125117</v>
       </c>
       <c r="K79" t="n">
-        <v>0.055344</v>
+        <v>0.00524757</v>
       </c>
       <c r="L79" t="n">
-        <v>2.54596</v>
+        <v>4.19324</v>
       </c>
       <c r="M79" t="n">
-        <v>518776241.2826915</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="N79" t="n">
-        <v>533536414.5626915</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="O79" t="n">
-        <v>13.53</v>
+        <v>0.193254</v>
       </c>
       <c r="P79" s="1" t="n">
-        <v>45368.35444444444</v>
+        <v>44290.85721064815</v>
       </c>
       <c r="Q79" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R79" t="b">
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0002420977144700714</v>
+        <v>0.0002687215363093137</v>
       </c>
       <c r="T79" t="inlineStr"/>
       <c r="U79" t="inlineStr"/>
@@ -7340,143 +7340,173 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>pi-network</t>
+          <t>kucoin-shares</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>pi</t>
+          <t>kcs</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Pi Network</t>
+          <t>KuCoin</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.091359</v>
+        <v>7.41</v>
       </c>
       <c r="F80" t="n">
-        <v>1027154222</v>
+        <v>1016411424</v>
       </c>
       <c r="G80" t="n">
         <v>79</v>
       </c>
       <c r="H80" t="n">
-        <v>5617919</v>
+        <v>3091540</v>
       </c>
       <c r="I80" t="n">
-        <v>0.092292</v>
+        <v>7.43</v>
       </c>
       <c r="J80" t="n">
-        <v>0.09067600000000001</v>
+        <v>7.26</v>
       </c>
       <c r="K80" t="n">
-        <v>0.00039385</v>
+        <v>0.110963</v>
       </c>
       <c r="L80" t="n">
-        <v>0.38458</v>
+        <v>1.51707</v>
       </c>
       <c r="M80" t="n">
-        <v>11243022455.381</v>
+        <v>137155021.2773955</v>
       </c>
       <c r="N80" t="n">
-        <v>17296957623.66307</v>
+        <v>142155021.2773955</v>
       </c>
       <c r="O80" t="n">
-        <v>2.99</v>
+        <v>28.83</v>
       </c>
       <c r="P80" s="1" t="n">
-        <v>45714.36184027778</v>
+        <v>44531.29832175926</v>
       </c>
       <c r="Q80" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R80" t="b">
         <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>0.0002251806847743386</v>
-      </c>
-      <c r="T80" t="inlineStr"/>
-      <c r="U80" t="inlineStr"/>
-      <c r="V80" t="inlineStr"/>
-      <c r="W80" t="inlineStr"/>
-      <c r="X80" t="inlineStr"/>
-      <c r="Y80" t="inlineStr"/>
-      <c r="Z80" t="inlineStr"/>
-      <c r="AA80" t="inlineStr"/>
+        <v>0.0002382645527374928</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Token de exchange</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Utilidad</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>N/A (token de exchange)</t>
+        </is>
+      </c>
+      <c r="W80" t="n">
+        <v>2017</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>kucoin.com</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>Beneficios en el exchange KuCoin</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>Token ERC-20 sobre Ethereum</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>Otorga descuentos en comisiones dentro del exchange KuCoin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>just</t>
+          <t>pi-network</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>jst</t>
+          <t>pi</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>JUST</t>
+          <t>Pi Network</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.125321</v>
+        <v>0.089464</v>
       </c>
       <c r="F81" t="n">
-        <v>1026222647</v>
+        <v>1006057012</v>
       </c>
       <c r="G81" t="n">
         <v>80</v>
       </c>
       <c r="H81" t="n">
-        <v>26999028</v>
+        <v>8386959</v>
       </c>
       <c r="I81" t="n">
-        <v>0.126484</v>
+        <v>0.091534</v>
       </c>
       <c r="J81" t="n">
-        <v>0.121647</v>
+        <v>0.088142</v>
       </c>
       <c r="K81" t="n">
-        <v>0.0023243</v>
+        <v>-0.001120415701620109</v>
       </c>
       <c r="L81" t="n">
-        <v>1.86023</v>
+        <v>-1.19691</v>
       </c>
       <c r="M81" t="n">
-        <v>8188743036.341737</v>
+        <v>11243022455.381</v>
       </c>
       <c r="N81" t="n">
-        <v>8188743036.341737</v>
+        <v>17296957623.66307</v>
       </c>
       <c r="O81" t="n">
-        <v>0.193254</v>
+        <v>2.99</v>
       </c>
       <c r="P81" s="1" t="n">
-        <v>44290.85721064815</v>
+        <v>45714.36184027778</v>
       </c>
       <c r="Q81" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R81" t="b">
         <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0.0002246345914042443</v>
+        <v>0.000232099424403212</v>
       </c>
       <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr"/>
@@ -7490,292 +7520,262 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>kucoin-shares</t>
+          <t>render-token</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>kcs</t>
+          <t>render</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>KuCoin</t>
+          <t>Render</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>7.35</v>
+        <v>1.92</v>
       </c>
       <c r="F82" t="n">
-        <v>1007460396</v>
+        <v>998052162</v>
       </c>
       <c r="G82" t="n">
         <v>81</v>
       </c>
       <c r="H82" t="n">
-        <v>3147466</v>
+        <v>101424166</v>
       </c>
       <c r="I82" t="n">
-        <v>7.43</v>
+        <v>2.09</v>
       </c>
       <c r="J82" t="n">
-        <v>7.3</v>
+        <v>1.9</v>
       </c>
       <c r="K82" t="n">
-        <v>-0.01908651121025873</v>
+        <v>-0.08383911960281076</v>
       </c>
       <c r="L82" t="n">
-        <v>-0.36652</v>
+        <v>-4.18526</v>
       </c>
       <c r="M82" t="n">
-        <v>137155021.2773955</v>
+        <v>518776241.2826915</v>
       </c>
       <c r="N82" t="n">
-        <v>142155021.2773955</v>
+        <v>533536414.5626915</v>
       </c>
       <c r="O82" t="n">
-        <v>28.83</v>
+        <v>13.53</v>
       </c>
       <c r="P82" s="1" t="n">
-        <v>44531.29832175926</v>
+        <v>45368.35444444444</v>
       </c>
       <c r="Q82" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R82" t="b">
         <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0.0002136360771899891</v>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>Token de exchange</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>Utilidad</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>N/A (token de exchange)</t>
-        </is>
-      </c>
-      <c r="W82" t="n">
-        <v>2017</v>
-      </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>kucoin.com</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>Beneficios en el exchange KuCoin</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>Token ERC-20 sobre Ethereum</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>Otorga descuentos en comisiones dentro del exchange KuCoin.</t>
-        </is>
-      </c>
+        <v>0.0002273332505686506</v>
+      </c>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="inlineStr"/>
+      <c r="Y82" t="inlineStr"/>
+      <c r="Z82" t="inlineStr"/>
+      <c r="AA82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>cosmos</t>
+          <t>blockchain-capital</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>atom</t>
+          <t>bcap</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Cosmos Hub</t>
+          <t>Blockchain Capital</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1.86</v>
+        <v>107.53</v>
       </c>
       <c r="F83" t="n">
-        <v>991343118</v>
+        <v>979825296</v>
       </c>
       <c r="G83" t="n">
         <v>82</v>
       </c>
       <c r="H83" t="n">
-        <v>79646205</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>1.92</v>
+        <v>107.53</v>
       </c>
       <c r="J83" t="n">
-        <v>1.82</v>
+        <v>107.53</v>
       </c>
       <c r="K83" t="n">
-        <v>0.02838852</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>1.35332</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>532857541.963055</v>
+        <v>9112111</v>
       </c>
       <c r="N83" t="n">
-        <v>532884992.164956</v>
+        <v>9112111</v>
       </c>
       <c r="O83" t="n">
-        <v>43.84</v>
+        <v>107.53</v>
       </c>
       <c r="P83" s="1" t="n">
-        <v>44458.66666666666</v>
+        <v>46287.17361111111</v>
       </c>
       <c r="Q83" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R83" t="b">
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.000204188057803717</v>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>Interoperabilidad</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>Layer 0</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>Proof of Stake (Tendermint)</t>
-        </is>
-      </c>
-      <c r="W83" t="n">
-        <v>2019</v>
-      </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>cosmos.network</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>Interoperabilidad entre blockchains soberanas</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>Blockchain propia (hub, Layer 0)</t>
-        </is>
-      </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>Se autodefine como el "Internet de las blockchains", enfocada en interoperabilidad.</t>
-        </is>
-      </c>
+        <v>0.000216480778402994</v>
+      </c>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr"/>
+      <c r="X83" t="inlineStr"/>
+      <c r="Y83" t="inlineStr"/>
+      <c r="Z83" t="inlineStr"/>
+      <c r="AA83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>blockchain-capital</t>
+          <t>cosmos</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>bcap</t>
+          <t>atom</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Blockchain Capital</t>
+          <t>Cosmos Hub</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>107.53</v>
+        <v>1.72</v>
       </c>
       <c r="F84" t="n">
-        <v>979825296</v>
+        <v>914644255</v>
       </c>
       <c r="G84" t="n">
         <v>83</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>71054341</v>
       </c>
       <c r="I84" t="n">
-        <v>107.53</v>
+        <v>1.89</v>
       </c>
       <c r="J84" t="n">
-        <v>107.53</v>
+        <v>1.69</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>-0.152939379036215</v>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>-8.151149999999999</v>
       </c>
       <c r="M84" t="n">
-        <v>9112111</v>
+        <v>533071893.64372</v>
       </c>
       <c r="N84" t="n">
-        <v>9112111</v>
+        <v>533095087.665018</v>
       </c>
       <c r="O84" t="n">
-        <v>107.53</v>
+        <v>43.84</v>
       </c>
       <c r="P84" s="1" t="n">
-        <v>46287.17361111111</v>
+        <v>44458.66666666666</v>
       </c>
       <c r="Q84" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S84" t="n">
-        <v>0.0001974362597926862</v>
-      </c>
-      <c r="T84" t="inlineStr"/>
-      <c r="U84" t="inlineStr"/>
-      <c r="V84" t="inlineStr"/>
-      <c r="W84" t="inlineStr"/>
-      <c r="X84" t="inlineStr"/>
-      <c r="Y84" t="inlineStr"/>
-      <c r="Z84" t="inlineStr"/>
-      <c r="AA84" t="inlineStr"/>
+        <v>0.0001776712851428242</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Layer 0</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Proof of Stake (Tendermint)</t>
+        </is>
+      </c>
+      <c r="W84" t="n">
+        <v>2019</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>cosmos.network</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>Interoperabilidad entre blockchains soberanas</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>Blockchain propia (hub, Layer 0)</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>Se autodefine como el "Internet de las blockchains", enfocada en interoperabilidad.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7794,34 +7794,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1.13</v>
+        <v>1.052</v>
       </c>
       <c r="F85" t="n">
-        <v>941293895</v>
+        <v>875114564</v>
       </c>
       <c r="G85" t="n">
         <v>84</v>
       </c>
       <c r="H85" t="n">
-        <v>269952848</v>
+        <v>179237600</v>
       </c>
       <c r="I85" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="J85" t="n">
-        <v>1.11</v>
+        <v>1.021</v>
       </c>
       <c r="K85" t="n">
-        <v>0.03173026</v>
+        <v>-0.09836054262543192</v>
       </c>
       <c r="L85" t="n">
-        <v>2.72604</v>
+        <v>-8.578329999999999</v>
       </c>
       <c r="M85" t="n">
-        <v>831179167</v>
+        <v>831242083</v>
       </c>
       <c r="N85" t="n">
-        <v>1957025314</v>
+        <v>1957023439</v>
       </c>
       <c r="O85" t="n">
         <v>236.84</v>
@@ -7830,13 +7830,13 @@
         <v>44287.22894675926</v>
       </c>
       <c r="Q85" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S85" t="n">
-        <v>0.0001748489827333574</v>
+        <v>0.0001541348817208368</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -7880,112 +7880,82 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>pancakeswap-token</t>
+          <t>nexo</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>cake</t>
+          <t>nexo</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>PancakeSwap</t>
+          <t>NEXO</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2.85</v>
+        <v>0.859483</v>
       </c>
       <c r="F86" t="n">
-        <v>908529695</v>
+        <v>859354234</v>
       </c>
       <c r="G86" t="n">
         <v>85</v>
       </c>
       <c r="H86" t="n">
-        <v>77912488</v>
+        <v>7206984</v>
       </c>
       <c r="I86" t="n">
-        <v>2.85</v>
+        <v>0.889543</v>
       </c>
       <c r="J86" t="n">
-        <v>2.73</v>
+        <v>0.849503</v>
       </c>
       <c r="K86" t="n">
-        <v>0.076643</v>
+        <v>-0.01097855995793973</v>
       </c>
       <c r="L86" t="n">
-        <v>2.67349</v>
+        <v>-1.27462</v>
       </c>
       <c r="M86" t="n">
-        <v>319007063.5169999</v>
+        <v>1000000000</v>
       </c>
       <c r="N86" t="n">
-        <v>330627631.389633</v>
+        <v>1000000000</v>
       </c>
       <c r="O86" t="n">
-        <v>43.96</v>
+        <v>4.07</v>
       </c>
       <c r="P86" s="1" t="n">
-        <v>44316.08914351852</v>
+        <v>44328.27623842593</v>
       </c>
       <c r="Q86" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R86" t="b">
         <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0.0001556424643140749</v>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>DeFi</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>Exchange descentralizado</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>N/A (token BEP-20)</t>
-        </is>
-      </c>
-      <c r="W86" t="n">
-        <v>2020</v>
-      </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>pancakeswap.finance</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>Intercambio descentralizado en BNB Chain</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>Token BEP-20 sobre BNB Chain</t>
-        </is>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>Principal exchange descentralizado (DEX) del ecosistema BNB Chain.</t>
-        </is>
-      </c>
+        <v>0.0001447510116333208</v>
+      </c>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="inlineStr"/>
+      <c r="X86" t="inlineStr"/>
+      <c r="Y86" t="inlineStr"/>
+      <c r="Z86" t="inlineStr"/>
+      <c r="AA86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8004,34 +7974,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>68.04000000000001</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="F87" t="n">
-        <v>873971493</v>
+        <v>830684935</v>
       </c>
       <c r="G87" t="n">
         <v>86</v>
       </c>
       <c r="H87" t="n">
-        <v>247801178</v>
+        <v>157304922</v>
       </c>
       <c r="I87" t="n">
-        <v>73.54000000000001</v>
+        <v>69.68000000000001</v>
       </c>
       <c r="J87" t="n">
-        <v>67.39</v>
+        <v>63.18</v>
       </c>
       <c r="K87" t="n">
-        <v>-3.421776370279872</v>
+        <v>-3.579599346798872</v>
       </c>
       <c r="L87" t="n">
-        <v>-5.54929</v>
+        <v>-5.24642</v>
       </c>
       <c r="M87" t="n">
-        <v>12844541.1311104</v>
+        <v>12846155.1088331</v>
       </c>
       <c r="N87" t="n">
-        <v>12845072.79742164</v>
+        <v>12846476.4636538</v>
       </c>
       <c r="O87" t="n">
         <v>1493.59</v>
@@ -8040,13 +8010,13 @@
         <v>43088.66666666666</v>
       </c>
       <c r="Q87" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R87" t="b">
         <v>1</v>
       </c>
       <c r="S87" t="n">
-        <v>0.0001353842940169126</v>
+        <v>0.0001276810024827413</v>
       </c>
       <c r="T87" t="inlineStr"/>
       <c r="U87" t="inlineStr"/>
@@ -8060,82 +8030,112 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>nexo</t>
+          <t>pancakeswap-token</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>nexo</t>
+          <t>cake</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NEXO</t>
+          <t>PancakeSwap</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.8730869999999999</v>
+        <v>2.61</v>
       </c>
       <c r="F88" t="n">
-        <v>873086578</v>
+        <v>831942989</v>
       </c>
       <c r="G88" t="n">
         <v>87</v>
       </c>
       <c r="H88" t="n">
-        <v>2294259</v>
+        <v>108660441</v>
       </c>
       <c r="I88" t="n">
-        <v>0.877911</v>
+        <v>2.84</v>
       </c>
       <c r="J88" t="n">
-        <v>0.860154</v>
+        <v>2.59</v>
       </c>
       <c r="K88" t="n">
-        <v>0.01323611</v>
+        <v>-0.1668992740823865</v>
       </c>
       <c r="L88" t="n">
-        <v>1.53336</v>
+        <v>-6.0504</v>
       </c>
       <c r="M88" t="n">
-        <v>1000000000</v>
+        <v>318686521.7818068</v>
       </c>
       <c r="N88" t="n">
-        <v>1000000000</v>
+        <v>330299406.389633</v>
       </c>
       <c r="O88" t="n">
-        <v>4.07</v>
+        <v>43.96</v>
       </c>
       <c r="P88" s="1" t="n">
-        <v>44328.27623842593</v>
+        <v>44316.08914351852</v>
       </c>
       <c r="Q88" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S88" t="n">
-        <v>0.0001348655529444311</v>
-      </c>
-      <c r="T88" t="inlineStr"/>
-      <c r="U88" t="inlineStr"/>
-      <c r="V88" t="inlineStr"/>
-      <c r="W88" t="inlineStr"/>
-      <c r="X88" t="inlineStr"/>
-      <c r="Y88" t="inlineStr"/>
-      <c r="Z88" t="inlineStr"/>
-      <c r="AA88" t="inlineStr"/>
+        <v>0.0001284300613729473</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>DeFi</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Exchange descentralizado</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>N/A (token BEP-20)</t>
+        </is>
+      </c>
+      <c r="W88" t="n">
+        <v>2020</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>pancakeswap.finance</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>Intercambio descentralizado en BNB Chain</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>Token BEP-20 sobre BNB Chain</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>Principal exchange descentralizado (DEX) del ecosistema BNB Chain.</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8154,31 +8154,31 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.838323</v>
+        <v>0.810537</v>
       </c>
       <c r="F89" t="n">
-        <v>834868741</v>
+        <v>806751236</v>
       </c>
       <c r="G89" t="n">
         <v>88</v>
       </c>
       <c r="H89" t="n">
-        <v>58811903</v>
+        <v>84274522</v>
       </c>
       <c r="I89" t="n">
-        <v>0.906338</v>
+        <v>0.860877</v>
       </c>
       <c r="J89" t="n">
-        <v>0.835148</v>
+        <v>0.766646</v>
       </c>
       <c r="K89" t="n">
-        <v>-0.05729116391142453</v>
+        <v>-0.01572964013575917</v>
       </c>
       <c r="L89" t="n">
-        <v>-6.73881</v>
+        <v>-2.06426</v>
       </c>
       <c r="M89" t="n">
-        <v>995878990.7676159</v>
+        <v>995776144.5308471</v>
       </c>
       <c r="N89" t="n">
         <v>1988034890.229641</v>
@@ -8190,13 +8190,13 @@
         <v>45633.25043981482</v>
       </c>
       <c r="Q89" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>0.0001124620884836588</v>
+        <v>0.000113430620534539</v>
       </c>
       <c r="T89" t="inlineStr"/>
       <c r="U89" t="inlineStr"/>
@@ -8210,7 +8210,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8229,28 +8229,28 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.009290690000000001</v>
+        <v>0.0088728</v>
       </c>
       <c r="F90" t="n">
-        <v>798860722</v>
+        <v>762872738</v>
       </c>
       <c r="G90" t="n">
         <v>89</v>
       </c>
       <c r="H90" t="n">
-        <v>12727870</v>
+        <v>14145069</v>
       </c>
       <c r="I90" t="n">
-        <v>0.009642649999999999</v>
+        <v>0.00942057</v>
       </c>
       <c r="J90" t="n">
-        <v>0.0090861</v>
+        <v>0.008678440000000001</v>
       </c>
       <c r="K90" t="n">
-        <v>-0.000247057142484391</v>
+        <v>-0.000378466448109313</v>
       </c>
       <c r="L90" t="n">
-        <v>-2.59179</v>
+        <v>-4.09952</v>
       </c>
       <c r="M90" t="n">
         <v>85985041177</v>
@@ -8265,13 +8265,13 @@
         <v>44304.71413194444</v>
       </c>
       <c r="Q90" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R90" t="b">
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>9.135402907230818e-05</v>
+        <v>8.730489062486519e-05</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -8315,68 +8315,68 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>injective-protocol</t>
+          <t>superstate-short-duration-us-government-securities-fund-ustb</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>inj</t>
+          <t>ustb</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Injective</t>
+          <t>Invesco Short Duration US Government Securities Fund</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>7.8</v>
+        <v>11.22</v>
       </c>
       <c r="F91" t="n">
-        <v>779556411</v>
+        <v>744133773</v>
       </c>
       <c r="G91" t="n">
         <v>90</v>
       </c>
       <c r="H91" t="n">
-        <v>75993346</v>
+        <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>7.91</v>
+        <v>11.22</v>
       </c>
       <c r="J91" t="n">
-        <v>7.53</v>
+        <v>11.22</v>
       </c>
       <c r="K91" t="n">
-        <v>0.02302876</v>
+        <v>0.001092</v>
       </c>
       <c r="L91" t="n">
-        <v>0.11708</v>
+        <v>0.009730000000000001</v>
       </c>
       <c r="M91" t="n">
-        <v>100000000</v>
+        <v>66295818.90593</v>
       </c>
       <c r="N91" t="n">
-        <v>100000000</v>
+        <v>66313632.296237</v>
       </c>
       <c r="O91" t="n">
-        <v>52.62</v>
+        <v>11.22</v>
       </c>
       <c r="P91" s="1" t="n">
-        <v>45365.29608796296</v>
+        <v>46293.65983796296</v>
       </c>
       <c r="Q91" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R91" t="b">
         <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>8.00377568974021e-05</v>
+        <v>7.614750920363168e-05</v>
       </c>
       <c r="T91" t="inlineStr"/>
       <c r="U91" t="inlineStr"/>
@@ -8390,68 +8390,68 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>superstate-short-duration-us-government-securities-fund-ustb</t>
+          <t>akedo</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ustb</t>
+          <t>ake</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Invesco Short Duration US Government Securities Fund</t>
+          <t>Akedo</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>11.22</v>
+        <v>0.03223242</v>
       </c>
       <c r="F92" t="n">
-        <v>755835754</v>
+        <v>733590336</v>
       </c>
       <c r="G92" t="n">
         <v>91</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>12704955</v>
       </c>
       <c r="I92" t="n">
-        <v>11.22</v>
+        <v>0.03303273</v>
       </c>
       <c r="J92" t="n">
-        <v>11.22</v>
+        <v>0.02846185</v>
       </c>
       <c r="K92" t="n">
-        <v>-1.776e-15</v>
+        <v>-0.0006220277736381789</v>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>-1.8565</v>
       </c>
       <c r="M92" t="n">
-        <v>67344915.025351</v>
+        <v>22796250000</v>
       </c>
       <c r="N92" t="n">
-        <v>67362730.289611</v>
+        <v>100000000000</v>
       </c>
       <c r="O92" t="n">
-        <v>11.22</v>
+        <v>0.146656</v>
       </c>
       <c r="P92" s="1" t="n">
-        <v>46290.60069444445</v>
+        <v>46285.43993055556</v>
       </c>
       <c r="Q92" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R92" t="b">
         <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>6.613260323615043e-05</v>
+        <v>6.986983335014959e-05</v>
       </c>
       <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr"/>
@@ -8465,68 +8465,68 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>eutbl</t>
+          <t>injective-protocol</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>eutbl</t>
+          <t>inj</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Spiko EU T-Bills Money Market Fund</t>
+          <t>Injective</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1.21</v>
+        <v>7.32</v>
       </c>
       <c r="F93" t="n">
-        <v>753192661</v>
+        <v>732514377</v>
       </c>
       <c r="G93" t="n">
         <v>92</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>127694507</v>
       </c>
       <c r="I93" t="n">
-        <v>1.21</v>
+        <v>7.9</v>
       </c>
       <c r="J93" t="n">
-        <v>1.21</v>
+        <v>7.24</v>
       </c>
       <c r="K93" t="n">
-        <v>0.00360208</v>
+        <v>-0.4318888678095671</v>
       </c>
       <c r="L93" t="n">
-        <v>0.29842</v>
+        <v>-5.52713</v>
       </c>
       <c r="M93" t="n">
-        <v>622138754.14688</v>
+        <v>100000000</v>
       </c>
       <c r="N93" t="n">
-        <v>622138754.14688</v>
+        <v>100000000</v>
       </c>
       <c r="O93" t="n">
-        <v>1.26</v>
+        <v>52.62</v>
       </c>
       <c r="P93" s="1" t="n">
-        <v>46049.54175925926</v>
+        <v>45365.29608796296</v>
       </c>
       <c r="Q93" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S93" t="n">
-        <v>6.458321047245174e-05</v>
+        <v>6.922919578256735e-05</v>
       </c>
       <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr"/>
@@ -8540,68 +8540,68 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>akedo</t>
+          <t>eutbl</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ake</t>
+          <t>eutbl</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Akedo</t>
+          <t>Spiko EU T-Bills Money Market Fund</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.03295427</v>
+        <v>1.21</v>
       </c>
       <c r="F94" t="n">
-        <v>751233720</v>
+        <v>730880634</v>
       </c>
       <c r="G94" t="n">
         <v>93</v>
       </c>
       <c r="H94" t="n">
-        <v>10660053</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>0.03490335</v>
+        <v>1.21</v>
       </c>
       <c r="J94" t="n">
-        <v>0.03231072</v>
+        <v>1.2</v>
       </c>
       <c r="K94" t="n">
-        <v>-0.0005019983910915169</v>
+        <v>-0.005213524096191691</v>
       </c>
       <c r="L94" t="n">
-        <v>-1.63124</v>
+        <v>-0.43064</v>
       </c>
       <c r="M94" t="n">
-        <v>22796250000</v>
+        <v>606320017.89252</v>
       </c>
       <c r="N94" t="n">
-        <v>100000000000</v>
+        <v>606320017.89252</v>
       </c>
       <c r="O94" t="n">
-        <v>0.146656</v>
+        <v>1.26</v>
       </c>
       <c r="P94" s="1" t="n">
-        <v>46285.43993055556</v>
+        <v>46049.54175925926</v>
       </c>
       <c r="Q94" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R94" t="b">
         <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>6.343487062594893e-05</v>
+        <v>6.825644761876693e-05</v>
       </c>
       <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
@@ -8615,248 +8615,248 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>aptos</t>
+          <t>stable-2</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>apt</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Aptos</t>
+          <t>​​Stable</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.844279</v>
+        <v>0.02696925</v>
       </c>
       <c r="F95" t="n">
-        <v>735259936</v>
+        <v>720871261</v>
       </c>
       <c r="G95" t="n">
         <v>94</v>
       </c>
       <c r="H95" t="n">
-        <v>73602536</v>
+        <v>9558237</v>
       </c>
       <c r="I95" t="n">
-        <v>0.8880710000000001</v>
+        <v>0.02887433</v>
       </c>
       <c r="J95" t="n">
-        <v>0.823677</v>
+        <v>0.02667611</v>
       </c>
       <c r="K95" t="n">
-        <v>-0.01321669499369493</v>
+        <v>-0.000392140960818538</v>
       </c>
       <c r="L95" t="n">
-        <v>-1.68815</v>
+        <v>-1.49528</v>
       </c>
       <c r="M95" t="n">
-        <v>870873636.8145826</v>
+        <v>26731478395</v>
       </c>
       <c r="N95" t="n">
-        <v>1209313832.95197</v>
+        <v>100000000000</v>
       </c>
       <c r="O95" t="n">
-        <v>19.92</v>
+        <v>0.04323745</v>
       </c>
       <c r="P95" s="1" t="n">
-        <v>44952.26755787037</v>
+        <v>46156.97986111111</v>
       </c>
       <c r="Q95" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R95" t="b">
         <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>5.407096805479993e-05</v>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>Plataforma de contratos inteligentes</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>Layer 1</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>Proof of Stake (BFT)</t>
-        </is>
-      </c>
-      <c r="W95" t="n">
-        <v>2022</v>
-      </c>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>aptosfoundation.org</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>Contratos inteligentes de alto rendimiento</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Layer 1)</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>Desarrollada por exingenieros del proyecto Diem (Meta/Facebook).</t>
-        </is>
-      </c>
+        <v>6.229675921823914e-05</v>
+      </c>
+      <c r="T95" t="inlineStr"/>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr"/>
+      <c r="W95" t="inlineStr"/>
+      <c r="X95" t="inlineStr"/>
+      <c r="Y95" t="inlineStr"/>
+      <c r="Z95" t="inlineStr"/>
+      <c r="AA95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>stable-2</t>
+          <t>aptos</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>apt</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>​​Stable</t>
+          <t>Aptos</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.0273212</v>
+        <v>0.8152160000000001</v>
       </c>
       <c r="F96" t="n">
-        <v>729438612</v>
+        <v>710071940</v>
       </c>
       <c r="G96" t="n">
         <v>95</v>
       </c>
       <c r="H96" t="n">
-        <v>8924569</v>
+        <v>101428331</v>
       </c>
       <c r="I96" t="n">
-        <v>0.02784859</v>
+        <v>0.8736660000000001</v>
       </c>
       <c r="J96" t="n">
-        <v>0.02632666</v>
+        <v>0.796221</v>
       </c>
       <c r="K96" t="n">
-        <v>0.00100423</v>
+        <v>-0.02857829351369168</v>
       </c>
       <c r="L96" t="n">
-        <v>3.83836</v>
+        <v>-3.4414</v>
       </c>
       <c r="M96" t="n">
-        <v>26698629629</v>
+        <v>870930831.2042739</v>
       </c>
       <c r="N96" t="n">
-        <v>100000000000</v>
+        <v>1209370935.873864</v>
       </c>
       <c r="O96" t="n">
-        <v>0.04323745</v>
+        <v>19.92</v>
       </c>
       <c r="P96" s="1" t="n">
-        <v>46156.97986111111</v>
+        <v>44952.26755787037</v>
       </c>
       <c r="Q96" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R96" t="b">
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>5.065848227365432e-05</v>
-      </c>
-      <c r="T96" t="inlineStr"/>
-      <c r="U96" t="inlineStr"/>
-      <c r="V96" t="inlineStr"/>
-      <c r="W96" t="inlineStr"/>
-      <c r="X96" t="inlineStr"/>
-      <c r="Y96" t="inlineStr"/>
-      <c r="Z96" t="inlineStr"/>
-      <c r="AA96" t="inlineStr"/>
+        <v>5.586672727744962e-05</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Plataforma de contratos inteligentes</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Layer 1</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Proof of Stake (BFT)</t>
+        </is>
+      </c>
+      <c r="W96" t="n">
+        <v>2022</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>aptosfoundation.org</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>Contratos inteligentes de alto rendimiento</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Layer 1)</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>Desarrollada por exingenieros del proyecto Diem (Meta/Facebook).</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ether-fi</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ethfi</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Ether.fi</t>
+          <t>GHO</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.726699</v>
+        <v>0.999342</v>
       </c>
       <c r="F97" t="n">
-        <v>701519313</v>
+        <v>698509109</v>
       </c>
       <c r="G97" t="n">
         <v>96</v>
       </c>
       <c r="H97" t="n">
-        <v>48866275</v>
+        <v>6414414</v>
       </c>
       <c r="I97" t="n">
-        <v>0.77495</v>
+        <v>0.999571</v>
       </c>
       <c r="J97" t="n">
-        <v>0.715746</v>
+        <v>0.998854</v>
       </c>
       <c r="K97" t="n">
-        <v>-0.01192318502549083</v>
+        <v>0.00032362</v>
       </c>
       <c r="L97" t="n">
-        <v>-1.7926</v>
+        <v>0.02817</v>
       </c>
       <c r="M97" t="n">
-        <v>965350000</v>
+        <v>699000000</v>
       </c>
       <c r="N97" t="n">
-        <v>965350000</v>
+        <v>699000000</v>
       </c>
       <c r="O97" t="n">
-        <v>8.529999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="P97" s="1" t="n">
-        <v>45378.63525462963</v>
+        <v>45350.38608796296</v>
       </c>
       <c r="Q97" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R97" t="b">
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>3.42920661701952e-05</v>
+        <v>4.898209326611213e-05</v>
       </c>
       <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr"/>
@@ -8870,68 +8870,68 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>xdce-crowd-sale</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>xdc</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>GHO</t>
+          <t>XDC Network</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.999126</v>
+        <v>0.0345497</v>
       </c>
       <c r="F98" t="n">
-        <v>698389404</v>
+        <v>689160440</v>
       </c>
       <c r="G98" t="n">
         <v>97</v>
       </c>
       <c r="H98" t="n">
-        <v>5829779</v>
+        <v>37492134</v>
       </c>
       <c r="I98" t="n">
-        <v>0.99955</v>
+        <v>0.03561706</v>
       </c>
       <c r="J98" t="n">
-        <v>0.999075</v>
+        <v>0.03188839</v>
       </c>
       <c r="K98" t="n">
-        <v>-0.000268288243765125</v>
+        <v>0.00191179</v>
       </c>
       <c r="L98" t="n">
-        <v>-0.02899</v>
+        <v>5.9083</v>
       </c>
       <c r="M98" t="n">
-        <v>699000000</v>
+        <v>19946688440</v>
       </c>
       <c r="N98" t="n">
-        <v>699000000</v>
+        <v>38065686425.1</v>
       </c>
       <c r="O98" t="n">
-        <v>1.03</v>
+        <v>0.192754</v>
       </c>
       <c r="P98" s="1" t="n">
-        <v>45350.38608796296</v>
+        <v>44428.86097222222</v>
       </c>
       <c r="Q98" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R98" t="b">
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>3.245729972208482e-05</v>
+        <v>4.341579513738081e-05</v>
       </c>
       <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr"/>
@@ -8945,68 +8945,68 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>pyth-network</t>
+          <t>ether-fi</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>pyth</t>
+          <t>ethfi</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Pyth Network</t>
+          <t>Ether.fi</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.084497</v>
+        <v>0.695922</v>
       </c>
       <c r="F99" t="n">
-        <v>665409755</v>
+        <v>672035613</v>
       </c>
       <c r="G99" t="n">
         <v>98</v>
       </c>
       <c r="H99" t="n">
-        <v>76338725</v>
+        <v>56806951</v>
       </c>
       <c r="I99" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.7287400000000001</v>
       </c>
       <c r="J99" t="n">
-        <v>0.07602100000000001</v>
+        <v>0.66335</v>
       </c>
       <c r="K99" t="n">
-        <v>0.0068687</v>
+        <v>-0.00323059170023321</v>
       </c>
       <c r="L99" t="n">
-        <v>8.45149</v>
+        <v>-0.39936</v>
       </c>
       <c r="M99" t="n">
-        <v>7874959366.564093</v>
+        <v>965350000</v>
       </c>
       <c r="N99" t="n">
-        <v>10000000000</v>
+        <v>965350000</v>
       </c>
       <c r="O99" t="n">
-        <v>1.2</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="P99" s="1" t="n">
-        <v>45366.95920138889</v>
+        <v>45378.63525462963</v>
       </c>
       <c r="Q99" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>1.31244841496011e-05</v>
+        <v>3.321948885196762e-05</v>
       </c>
       <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr"/>
@@ -9020,68 +9020,68 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>pudgy-penguins</t>
+          <t>pyth-network</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>pengu</t>
+          <t>pyth</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Pudgy Penguins</t>
+          <t>Pyth Network</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.01028858</v>
+        <v>0.07896</v>
       </c>
       <c r="F100" t="n">
-        <v>646744381</v>
+        <v>621914490</v>
       </c>
       <c r="G100" t="n">
         <v>99</v>
       </c>
       <c r="H100" t="n">
-        <v>226596574</v>
+        <v>54917622</v>
       </c>
       <c r="I100" t="n">
-        <v>0.01089866</v>
+        <v>0.08641</v>
       </c>
       <c r="J100" t="n">
-        <v>0.00968985</v>
+        <v>0.07798099999999999</v>
       </c>
       <c r="K100" t="n">
-        <v>0.00019913</v>
+        <v>-0.006167896403060341</v>
       </c>
       <c r="L100" t="n">
-        <v>1.84229</v>
+        <v>-7.27312</v>
       </c>
       <c r="M100" t="n">
-        <v>62860396090</v>
+        <v>7874959364.858932</v>
       </c>
       <c r="N100" t="n">
-        <v>76722802065.26431</v>
+        <v>10000000000</v>
       </c>
       <c r="O100" t="n">
-        <v>0.06844699999999999</v>
+        <v>1.2</v>
       </c>
       <c r="P100" s="1" t="n">
-        <v>45643.21206018519</v>
+        <v>45366.95920138889</v>
       </c>
       <c r="Q100" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S100" t="n">
-        <v>2.182759659645712e-06</v>
+        <v>3.376832836997776e-06</v>
       </c>
       <c r="T100" t="inlineStr"/>
       <c r="U100" t="inlineStr"/>
@@ -9095,62 +9095,62 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>blockstack</t>
+          <t>flare-networks</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>stx</t>
+          <t>flr</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Stacks</t>
+          <t>Flare</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.343903</v>
+        <v>0.00708898</v>
       </c>
       <c r="F101" t="n">
-        <v>643020834</v>
+        <v>616243056</v>
       </c>
       <c r="G101" t="n">
         <v>100</v>
       </c>
       <c r="H101" t="n">
-        <v>39789264</v>
+        <v>5875819</v>
       </c>
       <c r="I101" t="n">
-        <v>0.359663</v>
+        <v>0.00739575</v>
       </c>
       <c r="J101" t="n">
-        <v>0.33177</v>
+        <v>0.00693629</v>
       </c>
       <c r="K101" t="n">
-        <v>0.00180173</v>
+        <v>-0.000279257244197242</v>
       </c>
       <c r="L101" t="n">
-        <v>0.39596</v>
+        <v>-3.82284</v>
       </c>
       <c r="M101" t="n">
-        <v>1869771711.979279</v>
+        <v>86949015480.60582</v>
       </c>
       <c r="N101" t="n">
-        <v>1869771711.979279</v>
+        <v>106642103160.9111</v>
       </c>
       <c r="O101" t="n">
-        <v>3.86</v>
+        <v>0.150073</v>
       </c>
       <c r="P101" s="1" t="n">
-        <v>45383.19094907407</v>
+        <v>44935.80144675926</v>
       </c>
       <c r="Q101" s="1" t="n">
-        <v>46292.596875</v>
+        <v>46293.71134259259</v>
       </c>
       <c r="R101" t="b">
         <v>0</v>

--- a/src/xlsx/enriched_data.xlsx
+++ b/src/xlsx/enriched_data.xlsx
@@ -560,7 +560,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -579,16 +579,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>83628</v>
+        <v>83568</v>
       </c>
       <c r="F2" t="n">
-        <v>1680129050993</v>
+        <v>1679008903650</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>40095045364</v>
+        <v>41791363643</v>
       </c>
       <c r="I2" t="n">
         <v>84945</v>
@@ -597,16 +597,16 @@
         <v>82581</v>
       </c>
       <c r="K2" t="n">
-        <v>-800.5256324028014</v>
+        <v>-786.8917941942054</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.9496</v>
+        <v>-0.93283</v>
       </c>
       <c r="M2" t="n">
         <v>20090481</v>
       </c>
       <c r="N2" t="n">
-        <v>20090481</v>
+        <v>20090690</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -615,7 +615,7 @@
         <v>45936.45673611111</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
@@ -665,7 +665,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -684,28 +684,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2684.27</v>
+        <v>2690.99</v>
       </c>
       <c r="F3" t="n">
-        <v>327704876617</v>
+        <v>328578897942</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>15847058740</v>
+        <v>17136731362</v>
       </c>
       <c r="I3" t="n">
-        <v>2698.21</v>
+        <v>2717.37</v>
       </c>
       <c r="J3" t="n">
         <v>2636.99</v>
       </c>
       <c r="K3" t="n">
-        <v>-4.079040065399113</v>
+        <v>7.15</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.1606</v>
+        <v>0.26649</v>
       </c>
       <c r="M3" t="n">
         <v>122087473.8258867</v>
@@ -720,13 +720,13 @@
         <v>45893.47295138889</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1947520924015897</v>
+        <v>0.1953999540371524</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -789,31 +789,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999806</v>
+        <v>0.999718</v>
       </c>
       <c r="F4" t="n">
-        <v>183775189298</v>
+        <v>183821621020</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>71523929844</v>
+        <v>76015680441</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999854</v>
+        <v>0.9998359999999999</v>
       </c>
       <c r="J4" t="n">
         <v>0.999602</v>
       </c>
       <c r="K4" t="n">
-        <v>6.45e-05</v>
+        <v>-3.3051755416236e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00226</v>
+        <v>-0.00331</v>
       </c>
       <c r="M4" t="n">
-        <v>183818815964.5838</v>
+        <v>183874242892.1083</v>
       </c>
       <c r="N4" t="n">
         <v>189285761986.9062</v>
@@ -825,13 +825,13 @@
         <v>43304.66666666666</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1090548076659088</v>
+        <v>0.1091520839716213</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -894,16 +894,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>766.03</v>
+        <v>763.86</v>
       </c>
       <c r="F5" t="n">
-        <v>102003832094</v>
+        <v>101716240299</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1032103584</v>
+        <v>1060279716</v>
       </c>
       <c r="I5" t="n">
         <v>783.74</v>
@@ -912,16 +912,16 @@
         <v>757.15</v>
       </c>
       <c r="K5" t="n">
-        <v>-9.840246612364126</v>
+        <v>-13.44815267303102</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.27744</v>
+        <v>-1.73009</v>
       </c>
       <c r="M5" t="n">
-        <v>133159627.49</v>
+        <v>133159615.43</v>
       </c>
       <c r="N5" t="n">
-        <v>133159623.53</v>
+        <v>133159615.43</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -930,13 +930,13 @@
         <v>45943.02875</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06036726160042665</v>
+        <v>0.0602328561533096</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -999,28 +999,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="F6" t="n">
-        <v>93930368802</v>
+        <v>94079399488</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>4038950114</v>
+        <v>4363467206</v>
       </c>
       <c r="I6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="J6" t="n">
         <v>1.47</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.02702585931666324</v>
+        <v>-0.0167705133797087</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.80241</v>
+        <v>-1.10837</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -1035,13 +1035,13 @@
         <v>45855.82005787037</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R6" t="b">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0555602346734234</v>
+        <v>0.05568274808286571</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1104,34 +1104,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999896</v>
+        <v>0.999924</v>
       </c>
       <c r="F7" t="n">
-        <v>74840870406</v>
+        <v>74721963135</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>24447087511</v>
+        <v>20683397359</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9999400000000001</v>
+        <v>0.99999</v>
       </c>
       <c r="J7" t="n">
         <v>0.99954</v>
       </c>
       <c r="K7" t="n">
-        <v>2.851e-05</v>
+        <v>9.628000000000001e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.00016</v>
+        <v>0.00963</v>
       </c>
       <c r="M7" t="n">
-        <v>74852146130.23332</v>
+        <v>74728156839.12137</v>
       </c>
       <c r="N7" t="n">
-        <v>74843470364.92506</v>
+        <v>74784667843.85722</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -1140,13 +1140,13 @@
         <v>43418.66666666666</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04419414189593023</v>
+        <v>0.04414938899463879</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1209,34 +1209,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>118.84</v>
+        <v>118.76</v>
       </c>
       <c r="F8" t="n">
-        <v>69846507958</v>
+        <v>69818192382</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>4138249881</v>
+        <v>4131466796</v>
       </c>
       <c r="I8" t="n">
-        <v>123.36</v>
+        <v>122.78</v>
       </c>
       <c r="J8" t="n">
-        <v>117.57</v>
+        <v>117.29</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.085955386790999</v>
+        <v>-3.09094262113662</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.55265</v>
+        <v>-2.53671</v>
       </c>
       <c r="M8" t="n">
-        <v>587781862.721426</v>
+        <v>587852966.003577</v>
       </c>
       <c r="N8" t="n">
-        <v>634840553.4996796</v>
+        <v>634919033.5810466</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -1245,13 +1245,13 @@
         <v>45676.13572916666</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R8" t="b">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0412204447473299</v>
+        <v>0.04122767209218704</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1314,34 +1314,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.33473</v>
+        <v>0.335415</v>
       </c>
       <c r="F9" t="n">
-        <v>31789740830</v>
+        <v>31859208139</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>374027967</v>
+        <v>370370261</v>
       </c>
       <c r="I9" t="n">
-        <v>0.335666</v>
+        <v>0.336428</v>
       </c>
       <c r="J9" t="n">
         <v>0.332966</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00079635</v>
+        <v>0.00208902</v>
       </c>
       <c r="L9" t="n">
-        <v>0.22394</v>
+        <v>0.6267200000000001</v>
       </c>
       <c r="M9" t="n">
         <v>94972937401.45468</v>
       </c>
       <c r="N9" t="n">
-        <v>94972951495.66699</v>
+        <v>94973450849.00569</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1350,13 +1350,13 @@
         <v>45629.67407407407</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01856103604966932</v>
+        <v>0.0186113200135701</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1419,34 +1419,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1520.86</v>
+        <v>1483.83</v>
       </c>
       <c r="F10" t="n">
-        <v>25781910827</v>
+        <v>25160679961</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>1007938825</v>
+        <v>1246400077</v>
       </c>
       <c r="I10" t="n">
-        <v>1612.88</v>
+        <v>1597.81</v>
       </c>
       <c r="J10" t="n">
-        <v>1510.24</v>
+        <v>1449.25</v>
       </c>
       <c r="K10" t="n">
-        <v>-60.80843903747132</v>
+        <v>-106.6162647415517</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.87843</v>
+        <v>-6.70353</v>
       </c>
       <c r="M10" t="n">
         <v>16954918.9155448</v>
       </c>
       <c r="N10" t="n">
-        <v>16957395.4780448</v>
+        <v>16957822.0405448</v>
       </c>
       <c r="O10" t="n">
         <v>3191.93</v>
@@ -1455,13 +1455,13 @@
         <v>42671.66666666666</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01498390941234429</v>
+        <v>0.0146202682321958</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1524,16 +1524,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.059</v>
+        <v>1.004</v>
       </c>
       <c r="F11" t="n">
-        <v>24577771416</v>
+        <v>23304050621</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>24871973</v>
+        <v>346868158</v>
       </c>
       <c r="I11" t="n">
         <v>1.061</v>
@@ -1560,13 +1560,13 @@
         <v>46292.546875</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R11" t="b">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01426695184863325</v>
+        <v>0.01351406943182422</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
@@ -1580,7 +1580,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1599,28 +1599,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>88.73</v>
+        <v>87.48</v>
       </c>
       <c r="F12" t="n">
-        <v>19730034003</v>
+        <v>19463829972</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>946302648</v>
+        <v>947092964</v>
       </c>
       <c r="I12" t="n">
-        <v>92.09999999999999</v>
+        <v>92.02</v>
       </c>
       <c r="J12" t="n">
-        <v>86.95</v>
+        <v>86.41</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.541052861800551</v>
+        <v>-4.128673681278386</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.84228</v>
+        <v>-4.50706</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1635,13 +1635,13 @@
         <v>46288.22002314815</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R12" t="b">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01138055682378397</v>
+        <v>0.01122602658796506</v>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
@@ -1655,7 +1655,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1674,34 +1674,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.094098</v>
+        <v>0.093836</v>
       </c>
       <c r="F13" t="n">
-        <v>14688879088</v>
+        <v>14648714526</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>1186766570</v>
+        <v>1130717325</v>
       </c>
       <c r="I13" t="n">
-        <v>0.09775</v>
+        <v>0.097729</v>
       </c>
       <c r="J13" t="n">
         <v>0.09178600000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.002719752810769568</v>
+        <v>-0.002506339708048783</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.81425</v>
+        <v>-2.6015</v>
       </c>
       <c r="M13" t="n">
-        <v>156104906383.7052</v>
+        <v>156108476383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>156104946383.7052</v>
+        <v>156108686383.7052</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1710,13 +1710,13 @@
         <v>44323.88082175926</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R13" t="b">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.008378998936772549</v>
+        <v>0.008357131426577676</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1779,28 +1779,28 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>15.24</v>
+        <v>15.43</v>
       </c>
       <c r="F14" t="n">
-        <v>11408877171</v>
+        <v>11540186445</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>1101883443</v>
+        <v>1376547983</v>
       </c>
       <c r="I14" t="n">
-        <v>15.26</v>
+        <v>15.44</v>
       </c>
       <c r="J14" t="n">
         <v>13.54</v>
       </c>
       <c r="K14" t="n">
-        <v>1.13</v>
+        <v>1.43</v>
       </c>
       <c r="L14" t="n">
-        <v>8.05315</v>
+        <v>10.23398</v>
       </c>
       <c r="M14" t="n">
         <v>748099970.424884</v>
@@ -1815,13 +1815,13 @@
         <v>44325.67635416667</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R14" t="b">
         <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.006426050497499297</v>
+        <v>0.006505038518187269</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1884,16 +1884,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>538.36</v>
+        <v>541.1799999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>10125842981</v>
+        <v>10184194565</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>120623998</v>
+        <v>134844428</v>
       </c>
       <c r="I15" t="n">
         <v>552.95</v>
@@ -1902,16 +1902,16 @@
         <v>526.49</v>
       </c>
       <c r="K15" t="n">
-        <v>-6.988445927827684</v>
+        <v>-6.981361077774636</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.28901</v>
+        <v>-1.27359</v>
       </c>
       <c r="M15" t="n">
-        <v>18810613.88120856</v>
+        <v>18810763.27902782</v>
       </c>
       <c r="N15" t="n">
-        <v>18810665.48043185</v>
+        <v>18810782.47899366</v>
       </c>
       <c r="O15" t="n">
         <v>797.73</v>
@@ -1920,13 +1920,13 @@
         <v>46036.48202546296</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.005662118133341864</v>
+        <v>0.005697124650484629</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1989,16 +1989,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>83.58</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>9934621135</v>
+        <v>9937666187</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>129548567</v>
+        <v>143486762</v>
       </c>
       <c r="I16" t="n">
         <v>84.67</v>
@@ -2007,10 +2007,10 @@
         <v>82.44</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6630199170941751</v>
+        <v>-0.6211830702093124</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7719</v>
+        <v>-0.73752</v>
       </c>
       <c r="M16" t="n">
         <v>118852171</v>
@@ -2025,13 +2025,13 @@
         <v>46286.85358796296</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R16" t="b">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.005548262588390776</v>
+        <v>0.005550240514741547</v>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
@@ -2045,7 +2045,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2064,34 +2064,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.999699</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>9780317209</v>
+        <v>9787052779</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>123079087</v>
+        <v>182329149</v>
       </c>
       <c r="I17" t="n">
-        <v>0.999839</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0.999263</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.0502185588134e-05</v>
+        <v>0.00050491</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.00617</v>
+        <v>0.05051</v>
       </c>
       <c r="M17" t="n">
-        <v>9783695712.381886</v>
+        <v>9785581101.437241</v>
       </c>
       <c r="N17" t="n">
-        <v>9782223070.353539</v>
+        <v>9785581101.437241</v>
       </c>
       <c r="O17" t="n">
         <v>1.057</v>
@@ -2100,13 +2100,13 @@
         <v>45593.90336805556</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.005456388370301581</v>
+        <v>0.005460503501725542</v>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
@@ -2120,7 +2120,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2139,16 +2139,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.245232</v>
+        <v>0.246807</v>
       </c>
       <c r="F18" t="n">
-        <v>9204678078</v>
+        <v>9262416295</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>647377627</v>
+        <v>688332747</v>
       </c>
       <c r="I18" t="n">
         <v>0.257648</v>
@@ -2157,10 +2157,10 @@
         <v>0.239932</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.009054533622238931</v>
+        <v>-0.007398015687884063</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.58698</v>
+        <v>-2.91026</v>
       </c>
       <c r="M18" t="n">
         <v>37535193928.91081</v>
@@ -2175,13 +2175,13 @@
         <v>44440.91678240741</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R18" t="b">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.005113646636937204</v>
+        <v>0.00514791970444915</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.01254237</v>
+        <v>0.01249497</v>
       </c>
       <c r="F19" t="n">
-        <v>8901184461</v>
+        <v>8856846797</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>23847322</v>
+        <v>22092708</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01276074</v>
+        <v>0.01272728</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01249052</v>
+        <v>0.01243449</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.131499559115e-05</v>
+        <v>-0.000240401238128117</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.22871</v>
+        <v>-1.88767</v>
       </c>
       <c r="M19" t="n">
-        <v>709245362584.6495</v>
+        <v>709245550890.849</v>
       </c>
       <c r="N19" t="n">
         <v>1142408526965.963</v>
@@ -2280,13 +2280,13 @@
         <v>46259.82847222222</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R19" t="b">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.004932943271314889</v>
+        <v>0.004906277238454887</v>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
@@ -2300,7 +2300,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2319,16 +2319,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9.06</v>
+        <v>9.01</v>
       </c>
       <c r="F20" t="n">
-        <v>8334089166</v>
+        <v>8289654987</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>442380</v>
+        <v>513731</v>
       </c>
       <c r="I20" t="n">
         <v>9.09</v>
@@ -2337,10 +2337,10 @@
         <v>8.99</v>
       </c>
       <c r="K20" t="n">
-        <v>0.04916048</v>
+        <v>-0.03364701529956093</v>
       </c>
       <c r="L20" t="n">
-        <v>0.54394</v>
+        <v>-0.37197</v>
       </c>
       <c r="M20" t="n">
         <v>919857851.9</v>
@@ -2355,13 +2355,13 @@
         <v>46146.39930555555</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.004595288629849796</v>
+        <v>0.004568338541545904</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2424,31 +2424,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.224252</v>
+        <v>0.231162</v>
       </c>
       <c r="F21" t="n">
-        <v>7854903242</v>
+        <v>8084763830</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>619426342</v>
+        <v>804882888</v>
       </c>
       <c r="I21" t="n">
-        <v>0.230315</v>
+        <v>0.234286</v>
       </c>
       <c r="J21" t="n">
         <v>0.207092</v>
       </c>
       <c r="K21" t="n">
-        <v>0.00840275</v>
+        <v>0.0158957</v>
       </c>
       <c r="L21" t="n">
-        <v>4.06931</v>
+        <v>7.3842</v>
       </c>
       <c r="M21" t="n">
-        <v>34970168660.84914</v>
+        <v>35011603519.11985</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.69947</v>
@@ -2460,13 +2460,13 @@
         <v>43102.66666666666</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>0.00430997617391884</v>
+        <v>0.004446262289061311</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2529,34 +2529,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4.94</v>
+        <v>4.81</v>
       </c>
       <c r="F22" t="n">
-        <v>6465087552</v>
+        <v>6298371842</v>
       </c>
       <c r="G22" t="n">
         <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>1429170480</v>
+        <v>1394025532</v>
       </c>
       <c r="I22" t="n">
-        <v>5.57</v>
+        <v>5.41</v>
       </c>
       <c r="J22" t="n">
-        <v>4.84</v>
+        <v>4.68</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2435762471134959</v>
+        <v>-0.5640137186954686</v>
       </c>
       <c r="L22" t="n">
-        <v>-4.529</v>
+        <v>-10.48548</v>
       </c>
       <c r="M22" t="n">
-        <v>1307529703</v>
+        <v>1307555791</v>
       </c>
       <c r="N22" t="n">
-        <v>1307556131</v>
+        <v>1307555814</v>
       </c>
       <c r="O22" t="n">
         <v>20.44</v>
@@ -2565,13 +2565,13 @@
         <v>44577.59010416667</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0.003482464955527386</v>
+        <v>0.003381911623290297</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2634,34 +2634,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>309.33</v>
+        <v>310.23</v>
       </c>
       <c r="F23" t="n">
-        <v>6217118545</v>
+        <v>6233927496</v>
       </c>
       <c r="G23" t="n">
         <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>311030789</v>
+        <v>319655074</v>
       </c>
       <c r="I23" t="n">
-        <v>337.08</v>
+        <v>333.53</v>
       </c>
       <c r="J23" t="n">
         <v>305.68</v>
       </c>
       <c r="K23" t="n">
-        <v>-24.90571333688507</v>
+        <v>-21.90225423208983</v>
       </c>
       <c r="L23" t="n">
-        <v>-7.47269</v>
+        <v>-6.59451</v>
       </c>
       <c r="M23" t="n">
-        <v>20095599.89665077</v>
+        <v>20095728.02165077</v>
       </c>
       <c r="N23" t="n">
-        <v>20095881.14665077</v>
+        <v>20095996.77165077</v>
       </c>
       <c r="O23" t="n">
         <v>3785.82</v>
@@ -2670,13 +2670,13 @@
         <v>43088.66666666666</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R23" t="b">
         <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>0.003334821540229715</v>
+        <v>0.003343515021071391</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2720,322 +2720,322 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>hedera-hashgraph</t>
+          <t>uniswap</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>hbar</t>
+          <t>uni</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Hedera</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.125007</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>5478359322</v>
+        <v>5458427163</v>
       </c>
       <c r="G24" t="n">
         <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>1224885680</v>
+        <v>1054591594</v>
       </c>
       <c r="I24" t="n">
-        <v>0.128218</v>
+        <v>9.75</v>
       </c>
       <c r="J24" t="n">
-        <v>0.09357</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>0.03147097</v>
+        <v>-0.8418264650542291</v>
       </c>
       <c r="L24" t="n">
-        <v>33.68015</v>
+        <v>-8.731439999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>43831706397.79829</v>
+        <v>620402422.6104751</v>
       </c>
       <c r="N24" t="n">
-        <v>50000000000</v>
+        <v>887650418.9163101</v>
       </c>
       <c r="O24" t="n">
-        <v>0.569229</v>
+        <v>44.92</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>44454.11143518519</v>
+        <v>44318.89240740741</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R24" t="b">
         <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>0.002894956348664167</v>
+        <v>0.002881463969970174</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>Infraestructura empresarial</t>
+          <t>DeFi</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>DLT</t>
+          <t>Exchange descentralizado</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Hashgraph (aBFT)</t>
+          <t>N/A (token ERC-20)</t>
         </is>
       </c>
       <c r="W24" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>hedera.com</t>
+          <t>uniswap.org</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>Aplicaciones empresariales y tokenización</t>
+          <t>Intercambio descentralizado de tokens</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>Red propia (hashgraph, no blockchain tradicional)</t>
+          <t>Token ERC-20 sobre Ethereum</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Gobernada por un consejo de grandes empresas globales.</t>
+          <t>Uno de los mayores exchanges descentralizados (DEX) del ecosistema Ethereum.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>uniswap</t>
+          <t>litecoin</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>uni</t>
+          <t>ltc</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Uniswap</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>8.859999999999999</v>
+        <v>69.17</v>
       </c>
       <c r="F25" t="n">
-        <v>5496586683</v>
+        <v>5373060690</v>
       </c>
       <c r="G25" t="n">
         <v>24</v>
       </c>
       <c r="H25" t="n">
-        <v>1026550959</v>
+        <v>623930559</v>
       </c>
       <c r="I25" t="n">
-        <v>9.800000000000001</v>
+        <v>72.37</v>
       </c>
       <c r="J25" t="n">
-        <v>8.69</v>
+        <v>68.67</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.8321021447589825</v>
+        <v>-1.943114471304327</v>
       </c>
       <c r="L25" t="n">
-        <v>-8.594530000000001</v>
+        <v>-2.73237</v>
       </c>
       <c r="M25" t="n">
-        <v>620420422.6104751</v>
+        <v>77658035.78231663</v>
       </c>
       <c r="N25" t="n">
-        <v>887668418.9163101</v>
+        <v>77658392.03312041</v>
       </c>
       <c r="O25" t="n">
-        <v>44.92</v>
+        <v>410.26</v>
       </c>
       <c r="P25" s="1" t="n">
-        <v>44318.89240740741</v>
+        <v>44325.80077546297</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.00290580911555815</v>
+        <v>0.002830601749929769</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>DeFi</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>Exchange descentralizado</t>
+          <t>Store of value ligero</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>N/A (token ERC-20)</t>
+          <t>Proof of Work</t>
         </is>
       </c>
       <c r="W25" t="n">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>uniswap.org</t>
+          <t>litecoin.org</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>Intercambio descentralizado de tokens</t>
+          <t>Pagos rápidos de bajo costo</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>Token ERC-20 sobre Ethereum</t>
+          <t>Blockchain propia (Layer 1)</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Uno de los mayores exchanges descentralizados (DEX) del ecosistema Ethereum.</t>
+          <t>Fue diseñada como complemento más rápido y liviano de Bitcoin.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>litecoin</t>
+          <t>hedera-hashgraph</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ltc</t>
+          <t>hbar</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Litecoin</t>
+          <t>Hedera</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>68.93000000000001</v>
+        <v>0.121547</v>
       </c>
       <c r="F26" t="n">
-        <v>5355747288</v>
+        <v>5327080739</v>
       </c>
       <c r="G26" t="n">
         <v>25</v>
       </c>
       <c r="H26" t="n">
-        <v>576510489</v>
+        <v>1425715601</v>
       </c>
       <c r="I26" t="n">
-        <v>72.37</v>
+        <v>0.13063</v>
       </c>
       <c r="J26" t="n">
-        <v>68.88</v>
+        <v>0.09417200000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.254265189007285</v>
+        <v>0.025786</v>
       </c>
       <c r="L26" t="n">
-        <v>-3.11095</v>
+        <v>26.92754</v>
       </c>
       <c r="M26" t="n">
-        <v>77657260.78055078</v>
+        <v>43831706398.00587</v>
       </c>
       <c r="N26" t="n">
-        <v>77657485.78143089</v>
+        <v>50000000000</v>
       </c>
       <c r="O26" t="n">
-        <v>410.26</v>
+        <v>0.569229</v>
       </c>
       <c r="P26" s="1" t="n">
-        <v>44325.80077546297</v>
+        <v>44454.11143518519</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>0.002821951824125525</v>
+        <v>0.002803206423602897</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Infraestructura empresarial</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>Store of value ligero</t>
+          <t>DLT</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Proof of Work</t>
+          <t>Hashgraph (aBFT)</t>
         </is>
       </c>
       <c r="W26" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>litecoin.org</t>
+          <t>hedera.com</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>Pagos rápidos de bajo costo</t>
+          <t>Aplicaciones empresariales y tokenización</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>Blockchain propia (Layer 1)</t>
+          <t>Red propia (hashgraph, no blockchain tradicional)</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>Fue diseñada como complemento más rápido y liviano de Bitcoin.</t>
+          <t>Gobernada por un consejo de grandes empresas globales.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3054,16 +3054,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.129887</v>
+        <v>0.130293</v>
       </c>
       <c r="F27" t="n">
-        <v>5157498978</v>
+        <v>5175449953</v>
       </c>
       <c r="G27" t="n">
         <v>26</v>
       </c>
       <c r="H27" t="n">
-        <v>47163157</v>
+        <v>44678786</v>
       </c>
       <c r="I27" t="n">
         <v>0.146469</v>
@@ -3072,16 +3072,16 @@
         <v>0.126784</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.004338971851093582</v>
+        <v>-0.005405086768866557</v>
       </c>
       <c r="L27" t="n">
-        <v>-3.21821</v>
+        <v>-3.98318</v>
       </c>
       <c r="M27" t="n">
-        <v>39706020978.0548</v>
+        <v>39715601982.75846</v>
       </c>
       <c r="N27" t="n">
-        <v>39706741614.41362</v>
+        <v>39715601982.75846</v>
       </c>
       <c r="O27" t="n">
         <v>0.194152</v>
@@ -3090,13 +3090,13 @@
         <v>46056.00148148148</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R27" t="b">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.002703912646893221</v>
+        <v>0.002712863246341356</v>
       </c>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
@@ -3110,7 +3110,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3129,34 +3129,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>10.41</v>
+        <v>10.59</v>
       </c>
       <c r="F28" t="n">
-        <v>4894866629</v>
+        <v>4974459949</v>
       </c>
       <c r="G28" t="n">
         <v>27</v>
       </c>
       <c r="H28" t="n">
-        <v>625276181</v>
+        <v>632595575</v>
       </c>
       <c r="I28" t="n">
-        <v>11.08</v>
+        <v>10.97</v>
       </c>
       <c r="J28" t="n">
         <v>10.15</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.5173540689691229</v>
+        <v>-0.2666317242894269</v>
       </c>
       <c r="L28" t="n">
-        <v>-4.6792</v>
+        <v>-2.45624</v>
       </c>
       <c r="M28" t="n">
-        <v>469753866.6488752</v>
+        <v>469757793.2209306</v>
       </c>
       <c r="N28" t="n">
-        <v>469754193.1768665</v>
+        <v>469757977.1927229</v>
       </c>
       <c r="O28" t="n">
         <v>144.96</v>
@@ -3165,13 +3165,13 @@
         <v>44521.26314814815</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R28" t="b">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.002547538519968521</v>
+        <v>0.002593111340820204</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3234,34 +3234,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.999864</v>
+        <v>0.999656</v>
       </c>
       <c r="F29" t="n">
-        <v>4903829117</v>
+        <v>4902930682</v>
       </c>
       <c r="G29" t="n">
         <v>28</v>
       </c>
       <c r="H29" t="n">
-        <v>36827169</v>
+        <v>38369354</v>
       </c>
       <c r="I29" t="n">
         <v>0.999934</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9996</v>
+        <v>0.999574</v>
       </c>
       <c r="K29" t="n">
-        <v>8.536e-05</v>
+        <v>-0.000115381751319976</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0046</v>
+        <v>-0.01154</v>
       </c>
       <c r="M29" t="n">
-        <v>4904696488.396321</v>
+        <v>4904709277.703256</v>
       </c>
       <c r="N29" t="n">
-        <v>4904696584.801255</v>
+        <v>4904709277.703256</v>
       </c>
       <c r="O29" t="n">
         <v>1.034</v>
@@ -3270,13 +3270,13 @@
         <v>46000.38208333333</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R29" t="b">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.002552874881773948</v>
+        <v>0.002550493470014145</v>
       </c>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
@@ -3290,7 +3290,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3312,13 +3312,13 @@
         <v>1.16</v>
       </c>
       <c r="F30" t="n">
-        <v>4741714688</v>
+        <v>4769737147</v>
       </c>
       <c r="G30" t="n">
         <v>29</v>
       </c>
       <c r="H30" t="n">
-        <v>1609363322</v>
+        <v>1566711905</v>
       </c>
       <c r="I30" t="n">
         <v>1.29</v>
@@ -3327,10 +3327,10 @@
         <v>1.14</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.09112931843792849</v>
+        <v>-0.09491413056535136</v>
       </c>
       <c r="L30" t="n">
-        <v>-7.29204</v>
+        <v>-7.53669</v>
       </c>
       <c r="M30" t="n">
         <v>4096537146.540959</v>
@@ -3345,13 +3345,13 @@
         <v>45661.62243055556</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R30" t="b">
         <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>0.002456350206145466</v>
+        <v>0.002471135395971079</v>
       </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
@@ -3365,187 +3365,187 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>the-open-network</t>
+          <t>dai</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>gram</t>
+          <t>dai</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Gram (prev. Toncoin)</t>
+          <t>Dai</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.66</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>4660277648</v>
+        <v>4604389852</v>
       </c>
       <c r="G31" t="n">
         <v>30</v>
       </c>
       <c r="H31" t="n">
-        <v>151551042</v>
+        <v>250973333</v>
       </c>
       <c r="I31" t="n">
-        <v>1.72</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>1.56</v>
+        <v>0.999637</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.03378944504757952</v>
+        <v>0.00024019</v>
       </c>
       <c r="L31" t="n">
-        <v>-1.94732</v>
+        <v>0.02402</v>
       </c>
       <c r="M31" t="n">
-        <v>2815210027.833801</v>
+        <v>4603186689.020486</v>
       </c>
       <c r="N31" t="n">
-        <v>5257062331.929954</v>
+        <v>4603186689.020486</v>
       </c>
       <c r="O31" t="n">
-        <v>8.25</v>
+        <v>1.22</v>
       </c>
       <c r="P31" s="1" t="n">
-        <v>45457.69225694444</v>
+        <v>43902.79363425926</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R31" t="b">
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0.002407861716141015</v>
-      </c>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
+        <v>0.002372619781985529</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Stablecoin</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Colateralizada por cripto</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>N/A (token, colateral cripto)</t>
+        </is>
+      </c>
+      <c r="W31" t="n">
+        <v>2017</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>makerdao.com</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Estabilidad de valor descentralizada</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>Token ERC-20 sobre Ethereum</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Stablecoin descentralizada, generada mediante colateral cripto sobrecolateralizado.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>dai</t>
+          <t>the-open-network</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>dai</t>
+          <t>gram</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Dai</t>
+          <t>Gram (prev. Toncoin)</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.999949</v>
+        <v>1.57</v>
       </c>
       <c r="F32" t="n">
-        <v>4587404099</v>
+        <v>4422703171</v>
       </c>
       <c r="G32" t="n">
         <v>31</v>
       </c>
       <c r="H32" t="n">
-        <v>193253226</v>
+        <v>136193316</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>1.72</v>
       </c>
       <c r="J32" t="n">
-        <v>0.999637</v>
+        <v>1.56</v>
       </c>
       <c r="K32" t="n">
-        <v>2.63e-05</v>
+        <v>-0.05930901304330449</v>
       </c>
       <c r="L32" t="n">
-        <v>0.008160000000000001</v>
+        <v>-3.63858</v>
       </c>
       <c r="M32" t="n">
-        <v>4587020648.060517</v>
+        <v>2815376675.777718</v>
       </c>
       <c r="N32" t="n">
-        <v>4593374140.490763</v>
+        <v>5257210699.824263</v>
       </c>
       <c r="O32" t="n">
-        <v>1.22</v>
+        <v>8.25</v>
       </c>
       <c r="P32" s="1" t="n">
-        <v>43902.79363425926</v>
+        <v>45457.69225694444</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R32" t="b">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.002364472020834367</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Stablecoin</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Colateralizada por cripto</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>N/A (token, colateral cripto)</t>
-        </is>
-      </c>
-      <c r="W32" t="n">
-        <v>2017</v>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>makerdao.com</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>Estabilidad de valor descentralizada</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>Token ERC-20 sobre Ethereum</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>Stablecoin descentralizada, generada mediante colateral cripto sobrecolateralizado.</t>
-        </is>
-      </c>
+        <v>0.002264368994261958</v>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3564,16 +3564,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.999368</v>
+        <v>0.999463</v>
       </c>
       <c r="F33" t="n">
-        <v>4415532827</v>
+        <v>4416147310</v>
       </c>
       <c r="G33" t="n">
         <v>32</v>
       </c>
       <c r="H33" t="n">
-        <v>995762212</v>
+        <v>1101714230</v>
       </c>
       <c r="I33" t="n">
         <v>0.999614</v>
@@ -3582,16 +3582,16 @@
         <v>0.9992760000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>4.46e-06</v>
+        <v>3.417e-05</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.00552</v>
+        <v>0.00342</v>
       </c>
       <c r="M33" t="n">
-        <v>4418501462.580373</v>
+        <v>4418501462.568161</v>
       </c>
       <c r="N33" t="n">
-        <v>4418501462.580373</v>
+        <v>4418501462.568161</v>
       </c>
       <c r="O33" t="n">
         <v>1.048</v>
@@ -3600,13 +3600,13 @@
         <v>46212.42696759259</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R33" t="b">
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.00226213801588497</v>
+        <v>0.002260462945048278</v>
       </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
@@ -3620,262 +3620,262 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>quant-network</t>
+          <t>bittensor</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>qnt</t>
+          <t>tao</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Bittensor</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>244.32</v>
+        <v>306.81</v>
       </c>
       <c r="F34" t="n">
-        <v>3529967203</v>
+        <v>3478509724</v>
       </c>
       <c r="G34" t="n">
         <v>33</v>
       </c>
       <c r="H34" t="n">
-        <v>1554158496</v>
+        <v>357229159</v>
       </c>
       <c r="I34" t="n">
-        <v>358.2</v>
+        <v>322.51</v>
       </c>
       <c r="J34" t="n">
-        <v>181.33</v>
+        <v>294.98</v>
       </c>
       <c r="K34" t="n">
-        <v>59.51</v>
+        <v>-12.62353650183701</v>
       </c>
       <c r="L34" t="n">
-        <v>31.00905</v>
+        <v>-3.95187</v>
       </c>
       <c r="M34" t="n">
-        <v>14544176.16408117</v>
+        <v>11339645.9251</v>
       </c>
       <c r="N34" t="n">
-        <v>14612493</v>
+        <v>21000000</v>
       </c>
       <c r="O34" t="n">
-        <v>427.42</v>
+        <v>757.6</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>44450.05208333334</v>
+        <v>45358.44833333333</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0.001734862713300187</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Interoperabilidad</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Infraestructura empresarial</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>N/A (token ERC-20)</t>
-        </is>
-      </c>
-      <c r="W34" t="n">
-        <v>2018</v>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>quant.network</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>Interoperabilidad entre redes empresariales</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>Token ERC-20 sobre Ethereum</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>Su tecnología Overledger busca conectar múltiples blockchains y redes existentes.</t>
-        </is>
-      </c>
+        <v>0.00170180885590386</v>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>bittensor</t>
+          <t>crypto-com-chain</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>tao</t>
+          <t>cro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Bittensor</t>
+          <t>Cronos</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>301.09</v>
+        <v>0.069746</v>
       </c>
       <c r="F35" t="n">
-        <v>3414990064</v>
+        <v>3471504430</v>
       </c>
       <c r="G35" t="n">
         <v>34</v>
       </c>
       <c r="H35" t="n">
-        <v>336490928</v>
+        <v>27317850</v>
       </c>
       <c r="I35" t="n">
-        <v>329.59</v>
+        <v>0.07027700000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>294.98</v>
+        <v>0.063356</v>
       </c>
       <c r="K35" t="n">
-        <v>-22.94888112986712</v>
+        <v>0.0032569</v>
       </c>
       <c r="L35" t="n">
-        <v>-7.07539</v>
+        <v>4.89839</v>
       </c>
       <c r="M35" t="n">
-        <v>11339645.9251</v>
+        <v>49749850607.73766</v>
       </c>
       <c r="N35" t="n">
-        <v>21000000</v>
+        <v>98949813113.73965</v>
       </c>
       <c r="O35" t="n">
-        <v>757.6</v>
+        <v>0.891544</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>45358.44833333333</v>
+        <v>44523.66666666666</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.001666404087407819</v>
-      </c>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr"/>
+        <v>0.001697635029899877</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Token de exchange</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Layer 1 (Cronos)</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Proof of Stake</t>
+        </is>
+      </c>
+      <c r="W35" t="n">
+        <v>2018</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>cronos.org</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>Pagos y DeFi en el ecosistema Crypto.com</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Cronos, EVM-compatible)</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>Token nativo del ecosistema Crypto.com y su red Cronos.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>crypto-com-chain</t>
+          <t>quant-network</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>cro</t>
+          <t>qnt</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cronos</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.068595</v>
+        <v>233.52</v>
       </c>
       <c r="F36" t="n">
-        <v>3412255351</v>
+        <v>3404008537</v>
       </c>
       <c r="G36" t="n">
         <v>35</v>
       </c>
       <c r="H36" t="n">
-        <v>24280237</v>
+        <v>1187422261</v>
       </c>
       <c r="I36" t="n">
-        <v>0.069992</v>
+        <v>318.36</v>
       </c>
       <c r="J36" t="n">
-        <v>0.063356</v>
+        <v>196.87</v>
       </c>
       <c r="K36" t="n">
-        <v>0.00139798</v>
+        <v>-59.4741723556501</v>
       </c>
       <c r="L36" t="n">
-        <v>2.05436</v>
+        <v>-20.29896</v>
       </c>
       <c r="M36" t="n">
-        <v>49749274711.3246</v>
+        <v>14544176.16408117</v>
       </c>
       <c r="N36" t="n">
-        <v>98949285642.86087</v>
+        <v>14612493</v>
       </c>
       <c r="O36" t="n">
-        <v>0.891544</v>
+        <v>427.42</v>
       </c>
       <c r="P36" s="1" t="n">
-        <v>44523.66666666666</v>
+        <v>44450.05208333334</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
-        <v>0.001664775809857879</v>
+        <v>0.001657420284684977</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>Token de exchange</t>
+          <t>Interoperabilidad</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>Layer 1 (Cronos)</t>
+          <t>Infraestructura empresarial</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>Proof of Stake</t>
+          <t>N/A (token ERC-20)</t>
         </is>
       </c>
       <c r="W36" t="n">
@@ -3883,29 +3883,29 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>cronos.org</t>
+          <t>quant.network</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>Pagos y DeFi en el ecosistema Crypto.com</t>
+          <t>Interoperabilidad entre redes empresariales</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>Blockchain propia (Cronos, EVM-compatible)</t>
+          <t>Token ERC-20 sobre Ethereum</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>Token nativo del ecosistema Crypto.com y su red Cronos.</t>
+          <t>Su tecnología Overledger busca conectar múltiples blockchains y redes existentes.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3924,16 +3924,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5.66e-06</v>
+        <v>5.67e-06</v>
       </c>
       <c r="F37" t="n">
-        <v>3334571030</v>
+        <v>3342061176</v>
       </c>
       <c r="G37" t="n">
         <v>36</v>
       </c>
       <c r="H37" t="n">
-        <v>106187506</v>
+        <v>106938634</v>
       </c>
       <c r="I37" t="n">
         <v>5.97e-06</v>
@@ -3942,16 +3942,16 @@
         <v>5.57e-06</v>
       </c>
       <c r="K37" t="n">
-        <v>-2.46623257087e-07</v>
+        <v>-2.20313350693e-07</v>
       </c>
       <c r="L37" t="n">
-        <v>-4.17712</v>
+        <v>-3.73928</v>
       </c>
       <c r="M37" t="n">
-        <v>589238950149691.8</v>
+        <v>589238950007622.8</v>
       </c>
       <c r="N37" t="n">
-        <v>589496065820349.8</v>
+        <v>589496065678280.8</v>
       </c>
       <c r="O37" t="n">
         <v>8.616e-05</v>
@@ -3960,13 +3960,13 @@
         <v>44496.82980324074</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R37" t="b">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.001618521729131087</v>
+        <v>0.001620511411735471</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4010,68 +4010,68 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>global-dollar</t>
+          <t>tether-gold</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>usdg</t>
+          <t>xaut</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Global Dollar</t>
+          <t>Tether Gold</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>4130.18</v>
       </c>
       <c r="F38" t="n">
-        <v>3249435947</v>
+        <v>3341742939</v>
       </c>
       <c r="G38" t="n">
         <v>37</v>
       </c>
       <c r="H38" t="n">
-        <v>870343715</v>
+        <v>382493388</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>4260.39</v>
       </c>
       <c r="J38" t="n">
-        <v>0.999722</v>
+        <v>4117.57</v>
       </c>
       <c r="K38" t="n">
-        <v>0.00032742</v>
+        <v>-129.6709194783843</v>
       </c>
       <c r="L38" t="n">
-        <v>0.02515</v>
+        <v>-3.04402</v>
       </c>
       <c r="M38" t="n">
-        <v>3249196081.805783</v>
+        <v>808994.63</v>
       </c>
       <c r="N38" t="n">
-        <v>3249196081.805783</v>
+        <v>827417.63</v>
       </c>
       <c r="O38" t="n">
-        <v>1.65</v>
+        <v>5504.62</v>
       </c>
       <c r="P38" s="1" t="n">
-        <v>45686.67436342593</v>
+        <v>46050.66666666666</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R38" t="b">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0.001567831384527776</v>
+        <v>0.001620321802867374</v>
       </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
@@ -4085,68 +4085,68 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>tether-gold</t>
+          <t>global-dollar</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>xaut</t>
+          <t>usdg</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tether Gold</t>
+          <t>Global Dollar</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4132.8</v>
+        <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>2848646256</v>
+        <v>3245641532</v>
       </c>
       <c r="G39" t="n">
         <v>38</v>
       </c>
       <c r="H39" t="n">
-        <v>355101151</v>
+        <v>952102462</v>
       </c>
       <c r="I39" t="n">
-        <v>4280.38</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>4117.91</v>
+        <v>0.999722</v>
       </c>
       <c r="K39" t="n">
-        <v>-146.5443765912078</v>
+        <v>0.00018089</v>
       </c>
       <c r="L39" t="n">
-        <v>-3.43151</v>
+        <v>0.01809</v>
       </c>
       <c r="M39" t="n">
-        <v>689324.089</v>
+        <v>3245296082.805759</v>
       </c>
       <c r="N39" t="n">
-        <v>707747.089</v>
+        <v>3245296082.805759</v>
       </c>
       <c r="O39" t="n">
-        <v>5504.62</v>
+        <v>1.65</v>
       </c>
       <c r="P39" s="1" t="n">
-        <v>46050.66666666666</v>
+        <v>45686.67436342593</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001329196889389687</v>
+        <v>0.001563063599063797</v>
       </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
@@ -4160,68 +4160,68 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>paypal-usd</t>
+          <t>bitway</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>pyusd</t>
+          <t>btw</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>PayPal USD</t>
+          <t>Bitway</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.999898</v>
+        <v>1.12</v>
       </c>
       <c r="F40" t="n">
-        <v>2727482123</v>
+        <v>3032135937</v>
       </c>
       <c r="G40" t="n">
         <v>39</v>
       </c>
       <c r="H40" t="n">
-        <v>64835723</v>
+        <v>48416090</v>
       </c>
       <c r="I40" t="n">
-        <v>0.999984</v>
+        <v>1.43</v>
       </c>
       <c r="J40" t="n">
-        <v>0.999622</v>
+        <v>0.8876540000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>3.343e-05</v>
+        <v>-0.09268075734569159</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.00056</v>
+        <v>-7.63968</v>
       </c>
       <c r="M40" t="n">
-        <v>2727880777.060247</v>
+        <v>2708142280.000001</v>
       </c>
       <c r="N40" t="n">
-        <v>2727880777.060247</v>
+        <v>10000000000</v>
       </c>
       <c r="O40" t="n">
-        <v>1.021</v>
+        <v>1.43</v>
       </c>
       <c r="P40" s="1" t="n">
-        <v>45222.61454861111</v>
+        <v>46293.32349537037</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S40" t="n">
-        <v>0.001257054460688099</v>
+        <v>0.001435854776078364</v>
       </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
@@ -4235,68 +4235,68 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>memecore</t>
+          <t>paypal-usd</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>pyusd</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>MemeCore</t>
+          <t>PayPal USD</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>2627985656</v>
+        <v>2713619511</v>
       </c>
       <c r="G41" t="n">
         <v>40</v>
       </c>
       <c r="H41" t="n">
-        <v>1879104</v>
+        <v>76340355</v>
       </c>
       <c r="I41" t="n">
-        <v>1.21</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>1.14</v>
+        <v>0.999622</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.02519123899448772</v>
+        <v>0.00031337</v>
       </c>
       <c r="L41" t="n">
-        <v>-2.32052</v>
+        <v>0.03134</v>
       </c>
       <c r="M41" t="n">
-        <v>2279737202.761663</v>
+        <v>2713243486.123999</v>
       </c>
       <c r="N41" t="n">
-        <v>5419326949.268888</v>
+        <v>2713243486.123999</v>
       </c>
       <c r="O41" t="n">
-        <v>5.64</v>
+        <v>1.021</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>46205.17638888889</v>
+        <v>45222.61454861111</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R41" t="b">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.001197813193500494</v>
+        <v>0.001246079423104657</v>
       </c>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
@@ -4310,68 +4310,68 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ethena</t>
+          <t>memecore</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ena</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Ethena</t>
+          <t>MemeCore</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.258992</v>
+        <v>1.15</v>
       </c>
       <c r="F42" t="n">
-        <v>2614910012</v>
+        <v>2625571250</v>
       </c>
       <c r="G42" t="n">
         <v>41</v>
       </c>
       <c r="H42" t="n">
-        <v>681564422</v>
+        <v>980609</v>
       </c>
       <c r="I42" t="n">
-        <v>0.294013</v>
+        <v>1.19</v>
       </c>
       <c r="J42" t="n">
-        <v>0.256098</v>
+        <v>1.14</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.01683506024812859</v>
+        <v>-0.00887619437693199</v>
       </c>
       <c r="L42" t="n">
-        <v>-6.11802</v>
+        <v>-0.76502</v>
       </c>
       <c r="M42" t="n">
-        <v>10095312500</v>
+        <v>2279845200.804474</v>
       </c>
       <c r="N42" t="n">
-        <v>15000000000</v>
+        <v>5419434947.311699</v>
       </c>
       <c r="O42" t="n">
-        <v>1.52</v>
+        <v>5.64</v>
       </c>
       <c r="P42" s="1" t="n">
-        <v>45393.21892361111</v>
+        <v>46205.17638888889</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.00119002781434875</v>
+        <v>0.001193619366272309</v>
       </c>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
@@ -4385,68 +4385,68 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>bitway</t>
+          <t>ethena</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>btw</t>
+          <t>ena</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Bitway</t>
+          <t>Ethena</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.93493</v>
+        <v>0.255935</v>
       </c>
       <c r="F43" t="n">
-        <v>2537403368</v>
+        <v>2584980367</v>
       </c>
       <c r="G43" t="n">
         <v>42</v>
       </c>
       <c r="H43" t="n">
-        <v>34318069</v>
+        <v>578101430</v>
       </c>
       <c r="I43" t="n">
-        <v>1.43</v>
+        <v>0.276244</v>
       </c>
       <c r="J43" t="n">
-        <v>0.937479</v>
+        <v>0.252859</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.2436023418964792</v>
+        <v>-0.01390925014699845</v>
       </c>
       <c r="L43" t="n">
-        <v>-20.42315</v>
+        <v>-5.15455</v>
       </c>
       <c r="M43" t="n">
-        <v>2708142280.000001</v>
+        <v>10095312500</v>
       </c>
       <c r="N43" t="n">
-        <v>10000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="O43" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>46293.32349537037</v>
+        <v>45393.21892361111</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R43" t="b">
         <v>1</v>
       </c>
       <c r="S43" t="n">
-        <v>0.001143879524419837</v>
+        <v>0.00116943490192434</v>
       </c>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
@@ -4460,68 +4460,68 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ondo-finance</t>
+          <t>ripple-usd</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ondo</t>
+          <t>rlusd</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ondo</t>
+          <t>Ripple USD</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.514319</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>2503804853</v>
+        <v>2518062817</v>
       </c>
       <c r="G44" t="n">
         <v>43</v>
       </c>
       <c r="H44" t="n">
-        <v>736048329</v>
+        <v>289618947</v>
       </c>
       <c r="I44" t="n">
-        <v>0.606332</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>0.507278</v>
+        <v>0.999804</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.03149847428975283</v>
+        <v>2.755e-05</v>
       </c>
       <c r="L44" t="n">
-        <v>-5.75793</v>
+        <v>0.00276</v>
       </c>
       <c r="M44" t="n">
-        <v>4869330647</v>
+        <v>2517692589.017203</v>
       </c>
       <c r="N44" t="n">
-        <v>10000000000</v>
+        <v>2517692589.017201</v>
       </c>
       <c r="O44" t="n">
-        <v>2.14</v>
+        <v>1.073</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>45641.69166666667</v>
+        <v>45652.11518518518</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.001123874607016872</v>
+        <v>0.001129564739399706</v>
       </c>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
@@ -4535,68 +4535,68 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ripple-usd</t>
+          <t>ondo-finance</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>rlusd</t>
+          <t>ondo</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Ripple USD</t>
+          <t>Ondo</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>0.516524</v>
       </c>
       <c r="F45" t="n">
-        <v>2493492656</v>
+        <v>2513007633</v>
       </c>
       <c r="G45" t="n">
         <v>44</v>
       </c>
       <c r="H45" t="n">
-        <v>237412002</v>
+        <v>735237064</v>
       </c>
       <c r="I45" t="n">
+        <v>0.606332</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.507278</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-0.06008141897191299</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-10.41985</v>
+      </c>
+      <c r="M45" t="n">
+        <v>4869330647</v>
+      </c>
+      <c r="N45" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="P45" s="1" t="n">
+        <v>45641.69166666667</v>
+      </c>
+      <c r="Q45" s="1" t="n">
+        <v>46293.98981481481</v>
+      </c>
+      <c r="R45" t="b">
         <v>1</v>
       </c>
-      <c r="J45" t="n">
-        <v>0.9998359999999999</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0.00015506</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0.00961</v>
-      </c>
-      <c r="M45" t="n">
-        <v>2493192589.017205</v>
-      </c>
-      <c r="N45" t="n">
-        <v>2493192589.017197</v>
-      </c>
-      <c r="O45" t="n">
-        <v>1.073</v>
-      </c>
-      <c r="P45" s="1" t="n">
-        <v>45652.11518518518</v>
-      </c>
-      <c r="Q45" s="1" t="n">
-        <v>46293.71134259259</v>
-      </c>
-      <c r="R45" t="b">
-        <v>0</v>
-      </c>
       <c r="S45" t="n">
-        <v>0.00111773461394789</v>
+        <v>0.001126552808931959</v>
       </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
@@ -4610,7 +4610,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4629,28 +4629,28 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>117.98</v>
+        <v>118.92</v>
       </c>
       <c r="F46" t="n">
-        <v>2477847045</v>
+        <v>2497437538</v>
       </c>
       <c r="G46" t="n">
         <v>45</v>
       </c>
       <c r="H46" t="n">
-        <v>26770356</v>
+        <v>30711223</v>
       </c>
       <c r="I46" t="n">
-        <v>121.64</v>
+        <v>121.52</v>
       </c>
       <c r="J46" t="n">
         <v>116.19</v>
       </c>
       <c r="K46" t="n">
-        <v>-3.238687743650871</v>
+        <v>-2.007908685297622</v>
       </c>
       <c r="L46" t="n">
-        <v>-2.64985</v>
+        <v>-1.66044</v>
       </c>
       <c r="M46" t="n">
         <v>21000000</v>
@@ -4665,13 +4665,13 @@
         <v>45934.66666666666</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R46" t="b">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.001108419048787528</v>
+        <v>0.001117275986660762</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -4715,68 +4715,68 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>pump-fun</t>
+          <t>hashnote-usyc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>usyc</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Pump.fun</t>
+          <t>Circle USYC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.00529086</v>
+        <v>1.14</v>
       </c>
       <c r="F47" t="n">
-        <v>2460168381</v>
+        <v>2405472293</v>
       </c>
       <c r="G47" t="n">
         <v>46</v>
       </c>
       <c r="H47" t="n">
-        <v>572952538</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0.00553383</v>
+        <v>1.14</v>
       </c>
       <c r="J47" t="n">
-        <v>0.00475129</v>
+        <v>1.14</v>
       </c>
       <c r="K47" t="n">
-        <v>0.00042116</v>
+        <v>8.394999999999999e-05</v>
       </c>
       <c r="L47" t="n">
-        <v>8.642609999999999</v>
+        <v>0.00737</v>
       </c>
       <c r="M47" t="n">
-        <v>465673351301.2534</v>
+        <v>2112475511.779951</v>
       </c>
       <c r="N47" t="n">
-        <v>831175023761.6196</v>
+        <v>2112475511.779951</v>
       </c>
       <c r="O47" t="n">
-        <v>0.00881908</v>
+        <v>1.14</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>45914.36296296296</v>
+        <v>46293.53819444445</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0.001097892981992173</v>
+        <v>0.001062482150592827</v>
       </c>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
@@ -4790,143 +4790,173 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>hashnote-usyc</t>
+          <t>aave</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>usyc</t>
+          <t>aave</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Circle USYC</t>
+          <t>Aave</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1.14</v>
+        <v>149.08</v>
       </c>
       <c r="F48" t="n">
-        <v>2405472293</v>
+        <v>2300108110</v>
       </c>
       <c r="G48" t="n">
         <v>47</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>305771857</v>
       </c>
       <c r="I48" t="n">
-        <v>1.14</v>
+        <v>156.09</v>
       </c>
       <c r="J48" t="n">
-        <v>1.14</v>
+        <v>144.24</v>
       </c>
       <c r="K48" t="n">
-        <v>8.394999999999999e-05</v>
+        <v>-5.567608393971454</v>
       </c>
       <c r="L48" t="n">
-        <v>0.00737</v>
+        <v>-3.60016</v>
       </c>
       <c r="M48" t="n">
-        <v>2112475511.779951</v>
+        <v>15429846.8408245</v>
       </c>
       <c r="N48" t="n">
-        <v>2112475511.779951</v>
+        <v>16000000</v>
       </c>
       <c r="O48" t="n">
-        <v>1.14</v>
+        <v>661.6900000000001</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>46293.53819444445</v>
+        <v>44334.55554398148</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R48" t="b">
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0.001065326342582507</v>
-      </c>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr"/>
-      <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr"/>
-      <c r="AA48" t="inlineStr"/>
+        <v>0.000999705089859352</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>DeFi</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Préstamos</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>N/A (token de gobernanza)</t>
+        </is>
+      </c>
+      <c r="W48" t="n">
+        <v>2017</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>aave.com</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>Préstamos y créditos descentralizados</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>Token ERC-20 sobre Ethereum</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>Pionero en préstamos y créditos flash (flash loans) dentro de DeFi.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>blackrock-usd-institutional-digital-liquidity-fund</t>
+          <t>pump-fun</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>buidl</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>BlackRock USD Institutional Digital Liquidity Fund</t>
+          <t>Pump.fun</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0.00491688</v>
       </c>
       <c r="F49" t="n">
-        <v>2290130495</v>
+        <v>2290748183</v>
       </c>
       <c r="G49" t="n">
         <v>48</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>519720465</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0.00553383</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>0.00475129</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>-0.000190855359834726</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>-3.7366</v>
       </c>
       <c r="M49" t="n">
-        <v>2290130494.717648</v>
+        <v>465601390833.6057</v>
       </c>
       <c r="N49" t="n">
-        <v>2290824910.967649</v>
+        <v>831113211088.8768</v>
       </c>
       <c r="O49" t="n">
-        <v>1</v>
+        <v>0.00881908</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>45699.87511574074</v>
+        <v>45914.36296296296</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R49" t="b">
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>0.0009966505947972438</v>
+        <v>0.0009941283493673776</v>
       </c>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
@@ -4940,7 +4970,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4962,13 +4992,13 @@
         <v>1.15</v>
       </c>
       <c r="F50" t="n">
-        <v>2277857846</v>
+        <v>2277727629</v>
       </c>
       <c r="G50" t="n">
         <v>49</v>
       </c>
       <c r="H50" t="n">
-        <v>6730334</v>
+        <v>6606951</v>
       </c>
       <c r="I50" t="n">
         <v>1.15</v>
@@ -4977,16 +5007,16 @@
         <v>1.14</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.000936034336752822</v>
+        <v>-0.001272510992295972</v>
       </c>
       <c r="L50" t="n">
-        <v>0.07034</v>
+        <v>-0.11085</v>
       </c>
       <c r="M50" t="n">
-        <v>1984709596.999284</v>
+        <v>1984710539.255756</v>
       </c>
       <c r="N50" t="n">
-        <v>1984709435.346785</v>
+        <v>1984710539.255756</v>
       </c>
       <c r="O50" t="n">
         <v>1.26</v>
@@ -4995,13 +5025,13 @@
         <v>45377.89175925926</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R50" t="b">
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0.0009893433275099672</v>
+        <v>0.0009863705697693381</v>
       </c>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
@@ -5015,112 +5045,82 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>blackrock-usd-institutional-digital-liquidity-fund</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>buidl</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Aave</t>
+          <t>BlackRock USD Institutional Digital Liquidity Fund</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>147.2</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>2271547914</v>
+        <v>2262528018</v>
       </c>
       <c r="G51" t="n">
         <v>50</v>
       </c>
       <c r="H51" t="n">
-        <v>293261212</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>156.09</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
-        <v>144.24</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
-        <v>-7.21563997944952</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>-4.67855</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>15429843.6986945</v>
+        <v>2262528017.957648</v>
       </c>
       <c r="N51" t="n">
-        <v>16000000</v>
+        <v>2262528017.957649</v>
       </c>
       <c r="O51" t="n">
-        <v>661.6900000000001</v>
+        <v>1</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>44334.55554398148</v>
+        <v>45699.87511574074</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R51" t="b">
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0.0009855863260925439</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>DeFi</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Préstamos</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>N/A (token de gobernanza)</t>
-        </is>
-      </c>
-      <c r="W51" t="n">
-        <v>2017</v>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>aave.com</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>Préstamos y créditos descentralizados</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>Token ERC-20 sobre Ethereum</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>Pionero en préstamos y créditos flash (flash loans) dentro de DeFi.</t>
-        </is>
-      </c>
+        <v>0.000977314485664627</v>
+      </c>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5139,28 +5139,28 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.6638230000000001</v>
+        <v>0.664998</v>
       </c>
       <c r="F52" t="n">
-        <v>2191878963</v>
+        <v>2195882880</v>
       </c>
       <c r="G52" t="n">
         <v>51</v>
       </c>
       <c r="H52" t="n">
-        <v>50044353</v>
+        <v>49538783</v>
       </c>
       <c r="I52" t="n">
-        <v>0.68062</v>
+        <v>0.678633</v>
       </c>
       <c r="J52" t="n">
         <v>0.645253</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.01230162116184752</v>
+        <v>-0.01170561711242624</v>
       </c>
       <c r="L52" t="n">
-        <v>-1.84702</v>
+        <v>-1.7298</v>
       </c>
       <c r="M52" t="n">
         <v>3302294382.53684</v>
@@ -5175,13 +5175,13 @@
         <v>45938.71164351852</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R52" t="b">
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0.0009381505753060643</v>
+        <v>0.0009376066290031576</v>
       </c>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
@@ -5195,7 +5195,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5217,13 +5217,13 @@
         <v>1.18</v>
       </c>
       <c r="F53" t="n">
-        <v>2007319649</v>
+        <v>2010967813</v>
       </c>
       <c r="G53" t="n">
         <v>52</v>
       </c>
       <c r="H53" t="n">
-        <v>244497952</v>
+        <v>238420983</v>
       </c>
       <c r="I53" t="n">
         <v>1.28</v>
@@ -5232,16 +5232,16 @@
         <v>1.15</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.06470265556528054</v>
+        <v>-0.08159105673549938</v>
       </c>
       <c r="L53" t="n">
-        <v>-5.18136</v>
+        <v>-6.46856</v>
       </c>
       <c r="M53" t="n">
-        <v>1704886483.786375</v>
+        <v>1704933188.986922</v>
       </c>
       <c r="N53" t="n">
-        <v>1704899329.838796</v>
+        <v>1704939271.72706</v>
       </c>
       <c r="O53" t="n">
         <v>54.98</v>
@@ -5250,13 +5250,13 @@
         <v>44504.25704861111</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R53" t="b">
         <v>1</v>
       </c>
       <c r="S53" t="n">
-        <v>0.0008282619736069203</v>
+        <v>0.000827432335793922</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5319,28 +5319,28 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.705728</v>
+        <v>0.705874</v>
       </c>
       <c r="F54" t="n">
-        <v>1913698382</v>
+        <v>1913221851</v>
       </c>
       <c r="G54" t="n">
         <v>53</v>
       </c>
       <c r="H54" t="n">
-        <v>157013298</v>
+        <v>148290397</v>
       </c>
       <c r="I54" t="n">
-        <v>0.731046</v>
+        <v>0.728537</v>
       </c>
       <c r="J54" t="n">
         <v>0.691268</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.0225634663327704</v>
+        <v>-0.01531979021963337</v>
       </c>
       <c r="L54" t="n">
-        <v>-3.03764</v>
+        <v>-2.12423</v>
       </c>
       <c r="M54" t="n">
         <v>2710487455.649731</v>
@@ -5355,13 +5355,13 @@
         <v>45924.13766203704</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R54" t="b">
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>0.0007725188637255505</v>
+        <v>0.0007691942892565524</v>
       </c>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
@@ -5375,68 +5375,68 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>worldcoin-wld</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>wld</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sky</t>
+          <t>Worldcoin</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.078918</v>
+        <v>0.489236</v>
       </c>
       <c r="F55" t="n">
-        <v>1848788378</v>
+        <v>1880285323</v>
       </c>
       <c r="G55" t="n">
         <v>54</v>
       </c>
       <c r="H55" t="n">
-        <v>54904330</v>
+        <v>576858965</v>
       </c>
       <c r="I55" t="n">
-        <v>0.086122</v>
+        <v>0.550406</v>
       </c>
       <c r="J55" t="n">
-        <v>0.075368</v>
+        <v>0.479236</v>
       </c>
       <c r="K55" t="n">
-        <v>0.0035739</v>
+        <v>-0.05424942963407592</v>
       </c>
       <c r="L55" t="n">
-        <v>4.72112</v>
+        <v>-9.98176</v>
       </c>
       <c r="M55" t="n">
-        <v>23427763031.73964</v>
+        <v>3842804411.877398</v>
       </c>
       <c r="N55" t="n">
-        <v>23459804203.60596</v>
+        <v>10000000000</v>
       </c>
       <c r="O55" t="n">
-        <v>0.100535</v>
+        <v>11.74</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>45630.09302083333</v>
+        <v>45360.67409722223</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0007338707488119577</v>
+        <v>0.0007495703681124403</v>
       </c>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
@@ -5450,68 +5450,68 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>worldcoin-wld</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>wld</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Worldcoin</t>
+          <t>Sky</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.494779</v>
+        <v>0.07874100000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>1839776123</v>
+        <v>1844658418</v>
       </c>
       <c r="G56" t="n">
         <v>55</v>
       </c>
       <c r="H56" t="n">
-        <v>582507152</v>
+        <v>45824177</v>
       </c>
       <c r="I56" t="n">
-        <v>0.570169</v>
+        <v>0.086122</v>
       </c>
       <c r="J56" t="n">
-        <v>0.479532</v>
+        <v>0.076969</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.06908515140453114</v>
+        <v>-0.002860198225835303</v>
       </c>
       <c r="L56" t="n">
-        <v>-12.17096</v>
+        <v>-3.50511</v>
       </c>
       <c r="M56" t="n">
-        <v>3718065690.775289</v>
+        <v>23427301924.81371</v>
       </c>
       <c r="N56" t="n">
-        <v>10000000000</v>
+        <v>23459804203.60596</v>
       </c>
       <c r="O56" t="n">
-        <v>11.74</v>
+        <v>0.100535</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>45360.67409722223</v>
+        <v>45630.09302083333</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0.0007285047551991612</v>
+        <v>0.0007283434927621067</v>
       </c>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
@@ -5525,7 +5525,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5544,28 +5544,28 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.056742</v>
+        <v>0.05706</v>
       </c>
       <c r="F57" t="n">
-        <v>1803133010</v>
+        <v>1812807338</v>
       </c>
       <c r="G57" t="n">
         <v>56</v>
       </c>
       <c r="H57" t="n">
-        <v>49316785</v>
+        <v>41472649</v>
       </c>
       <c r="I57" t="n">
-        <v>0.059219</v>
+        <v>0.058699</v>
       </c>
       <c r="J57" t="n">
         <v>0.055922</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.001156049151996331</v>
+        <v>-0.001561998729134401</v>
       </c>
       <c r="L57" t="n">
-        <v>-2.0139</v>
+        <v>-2.66453</v>
       </c>
       <c r="M57" t="n">
         <v>31778337976</v>
@@ -5580,13 +5580,13 @@
         <v>45901.18065972222</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R57" t="b">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0.0007066870513824157</v>
+        <v>0.0007093662926675854</v>
       </c>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
@@ -5600,7 +5600,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5619,28 +5619,28 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4137.84</v>
+        <v>4136.85</v>
       </c>
       <c r="F58" t="n">
-        <v>1799327494</v>
+        <v>1799291089</v>
       </c>
       <c r="G58" t="n">
         <v>57</v>
       </c>
       <c r="H58" t="n">
-        <v>216736087</v>
+        <v>226703873</v>
       </c>
       <c r="I58" t="n">
-        <v>4277.43</v>
+        <v>4257.32</v>
       </c>
       <c r="J58" t="n">
-        <v>4123.5</v>
+        <v>4122.98</v>
       </c>
       <c r="K58" t="n">
-        <v>-137.5311100150984</v>
+        <v>-120.5855415487467</v>
       </c>
       <c r="L58" t="n">
-        <v>-3.22734</v>
+        <v>-2.83235</v>
       </c>
       <c r="M58" t="n">
         <v>434898.623539</v>
@@ -5655,13 +5655,13 @@
         <v>46050.93814814815</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R58" t="b">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0007044212062027803</v>
+        <v>0.0007013131729052296</v>
       </c>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
@@ -5675,7 +5675,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5694,16 +5694,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="F59" t="n">
-        <v>1792931419</v>
+        <v>1770954366</v>
       </c>
       <c r="G59" t="n">
         <v>58</v>
       </c>
       <c r="H59" t="n">
-        <v>37143462</v>
+        <v>37287589</v>
       </c>
       <c r="I59" t="n">
         <v>2.74</v>
@@ -5712,13 +5712,13 @@
         <v>2.48</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.1192164771803483</v>
+        <v>-0.1731332388288185</v>
       </c>
       <c r="L59" t="n">
-        <v>-4.47209</v>
+        <v>-6.40201</v>
       </c>
       <c r="M59" t="n">
-        <v>699612259.0237948</v>
+        <v>699626678.4133558</v>
       </c>
       <c r="N59" t="n">
         <v>1000000000</v>
@@ -5730,13 +5730,13 @@
         <v>45674.19883101852</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S59" t="n">
-        <v>0.0007006129143161251</v>
+        <v>0.0006844298627507851</v>
       </c>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
@@ -5750,7 +5750,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5772,25 +5772,25 @@
         <v>4.2e-06</v>
       </c>
       <c r="F60" t="n">
-        <v>1767019114</v>
+        <v>1768776298</v>
       </c>
       <c r="G60" t="n">
         <v>59</v>
       </c>
       <c r="H60" t="n">
-        <v>328614208</v>
+        <v>337465988</v>
       </c>
       <c r="I60" t="n">
-        <v>4.42e-06</v>
+        <v>4.41e-06</v>
       </c>
       <c r="J60" t="n">
-        <v>4.13e-06</v>
+        <v>4.11e-06</v>
       </c>
       <c r="K60" t="n">
-        <v>-1.73908170515e-07</v>
+        <v>-1.35704872059e-07</v>
       </c>
       <c r="L60" t="n">
-        <v>-3.98642</v>
+        <v>-3.12649</v>
       </c>
       <c r="M60" t="n">
         <v>420690000000000</v>
@@ -5805,13 +5805,13 @@
         <v>45635.35457175926</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R60" t="b">
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0.0006851844490626633</v>
+        <v>0.0006831321475004552</v>
       </c>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
@@ -5825,7 +5825,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5844,34 +5844,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="F61" t="n">
-        <v>1671242413</v>
+        <v>1733015070</v>
       </c>
       <c r="G61" t="n">
         <v>60</v>
       </c>
       <c r="H61" t="n">
-        <v>85782383</v>
+        <v>89623916</v>
       </c>
       <c r="I61" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="J61" t="n">
         <v>2.91</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.1799278695271669</v>
+        <v>-0.02113898384443047</v>
       </c>
       <c r="L61" t="n">
-        <v>-5.62245</v>
+        <v>-0.67499</v>
       </c>
       <c r="M61" t="n">
-        <v>556920108.2163103</v>
+        <v>556920633.6324656</v>
       </c>
       <c r="N61" t="n">
-        <v>556920196.8271762</v>
+        <v>556921311.0764827</v>
       </c>
       <c r="O61" t="n">
         <v>700.65</v>
@@ -5880,13 +5880,13 @@
         <v>44326.33741898148</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>0.0006281579705818915</v>
+        <v>0.0006618252411292491</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5949,28 +5949,28 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1.71e-06</v>
+        <v>1.73e-06</v>
       </c>
       <c r="F62" t="n">
-        <v>1540082967</v>
+        <v>1552450723</v>
       </c>
       <c r="G62" t="n">
         <v>61</v>
       </c>
       <c r="H62" t="n">
-        <v>76593027</v>
+        <v>71390824</v>
       </c>
       <c r="I62" t="n">
-        <v>1.72e-06</v>
+        <v>1.73e-06</v>
       </c>
       <c r="J62" t="n">
         <v>1.69e-06</v>
       </c>
       <c r="K62" t="n">
-        <v>1.448e-08</v>
+        <v>3.3866e-08</v>
       </c>
       <c r="L62" t="n">
-        <v>1.04611</v>
+        <v>1.9985</v>
       </c>
       <c r="M62" t="n">
         <v>898232728634017.2</v>
@@ -5985,13 +5985,13 @@
         <v>45629.67800925926</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R62" t="b">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0.0005500642249550824</v>
+        <v>0.0005542431515123321</v>
       </c>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
@@ -6005,68 +6005,68 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>united-stables</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>u</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>USDD</t>
+          <t>United Stables</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.998519</v>
+        <v>0.9996429999999999</v>
       </c>
       <c r="F63" t="n">
-        <v>1537334861</v>
+        <v>1541410445</v>
       </c>
       <c r="G63" t="n">
         <v>62</v>
       </c>
       <c r="H63" t="n">
-        <v>2247162</v>
+        <v>157085622</v>
       </c>
       <c r="I63" t="n">
-        <v>0.999598</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
-        <v>0.997117</v>
+        <v>0.999323</v>
       </c>
       <c r="K63" t="n">
-        <v>0.00140294</v>
+        <v>-0.000191171553905467</v>
       </c>
       <c r="L63" t="n">
-        <v>0.13648</v>
+        <v>-0.01912</v>
       </c>
       <c r="M63" t="n">
-        <v>1539682561</v>
+        <v>1541830391.63</v>
       </c>
       <c r="N63" t="n">
-        <v>1539527810</v>
+        <v>1541830391.63</v>
       </c>
       <c r="O63" t="n">
-        <v>1.24</v>
+        <v>1.008</v>
       </c>
       <c r="P63" s="1" t="n">
-        <v>46212.39942129629</v>
+        <v>46058.54591435185</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R63" t="b">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0.0005484279730688132</v>
+        <v>0.0005476652406626799</v>
       </c>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
@@ -6080,68 +6080,68 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>united-stables</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>United Stables</t>
+          <t>USDD</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.999685</v>
+        <v>0.998424</v>
       </c>
       <c r="F64" t="n">
-        <v>1521359338</v>
+        <v>1539266689</v>
       </c>
       <c r="G64" t="n">
         <v>63</v>
       </c>
       <c r="H64" t="n">
-        <v>143067957</v>
+        <v>2345045</v>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>0.999598</v>
       </c>
       <c r="J64" t="n">
-        <v>0.999323</v>
+        <v>0.997139</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.0001200862768026</v>
+        <v>-0.00059551229409438</v>
       </c>
       <c r="L64" t="n">
-        <v>-0.01824</v>
+        <v>-0.05961</v>
       </c>
       <c r="M64" t="n">
-        <v>1521842391.63</v>
+        <v>1541691414</v>
       </c>
       <c r="N64" t="n">
-        <v>1541830391.63</v>
+        <v>1541685913</v>
       </c>
       <c r="O64" t="n">
-        <v>1.008</v>
+        <v>1.24</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>46058.54591435185</v>
+        <v>46212.39942129629</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R64" t="b">
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0005389159747532879</v>
+        <v>0.0005463879688538172</v>
       </c>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
@@ -6155,7 +6155,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6177,7 +6177,7 @@
         <v>1.15</v>
       </c>
       <c r="F65" t="n">
-        <v>1486924506</v>
+        <v>1487612740</v>
       </c>
       <c r="G65" t="n">
         <v>64</v>
@@ -6186,19 +6186,19 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="J65" t="n">
         <v>1.15</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.00496535212476612</v>
+        <v>-4.6342781097941e-05</v>
       </c>
       <c r="L65" t="n">
-        <v>-0.4288</v>
+        <v>-0.00402</v>
       </c>
       <c r="M65" t="n">
-        <v>1289618689.24777</v>
+        <v>1290400520.88146</v>
       </c>
       <c r="N65" t="n">
         <v>1290400520.88146</v>
@@ -6210,13 +6210,13 @@
         <v>46255.48263888889</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R65" t="b">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0.00051841310520846</v>
+        <v>0.0005156120163321067</v>
       </c>
       <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr"/>
@@ -6230,7 +6230,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6249,16 +6249,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>9.16</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="F66" t="n">
-        <v>1450440617</v>
+        <v>1470078511</v>
       </c>
       <c r="G66" t="n">
         <v>65</v>
       </c>
       <c r="H66" t="n">
-        <v>101110639</v>
+        <v>102249672</v>
       </c>
       <c r="I66" t="n">
         <v>9.630000000000001</v>
@@ -6267,16 +6267,16 @@
         <v>8.970000000000001</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.3224684997324374</v>
+        <v>-0.2738372789181227</v>
       </c>
       <c r="L66" t="n">
-        <v>-3.38828</v>
+        <v>-2.86439</v>
       </c>
       <c r="M66" t="n">
-        <v>158311851.2298701</v>
+        <v>158315119.3216007</v>
       </c>
       <c r="N66" t="n">
-        <v>158312284.7914701</v>
+        <v>158315691.5840007</v>
       </c>
       <c r="O66" t="n">
         <v>167.09</v>
@@ -6285,13 +6285,13 @@
         <v>44322.44053240741</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R66" t="b">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0.0004966902050748109</v>
+        <v>0.0005051649428816568</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6354,16 +6354,16 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.999961</v>
+        <v>1</v>
       </c>
       <c r="F67" t="n">
-        <v>1405685505</v>
+        <v>1405841571</v>
       </c>
       <c r="G67" t="n">
         <v>66</v>
       </c>
       <c r="H67" t="n">
-        <v>21425849</v>
+        <v>21458447</v>
       </c>
       <c r="I67" t="n">
         <v>1</v>
@@ -6372,10 +6372,10 @@
         <v>0.999569</v>
       </c>
       <c r="K67" t="n">
-        <v>0.0001201</v>
+        <v>0.00016125</v>
       </c>
       <c r="L67" t="n">
-        <v>0.0092</v>
+        <v>0.01613</v>
       </c>
       <c r="M67" t="n">
         <v>1405780804.97</v>
@@ -6390,13 +6390,13 @@
         <v>46092.00303240741</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R67" t="b">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.0004700425297558152</v>
+        <v>0.0004668919152844838</v>
       </c>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
@@ -6410,7 +6410,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6432,13 +6432,13 @@
         <v>2</v>
       </c>
       <c r="F68" t="n">
-        <v>1401020986</v>
+        <v>1399137121</v>
       </c>
       <c r="G68" t="n">
         <v>67</v>
       </c>
       <c r="H68" t="n">
-        <v>24694339</v>
+        <v>24662450</v>
       </c>
       <c r="I68" t="n">
         <v>2.04</v>
@@ -6447,10 +6447,10 @@
         <v>1.96</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.04226071514682195</v>
+        <v>-0.0211529442187357</v>
       </c>
       <c r="L68" t="n">
-        <v>-2.07292</v>
+        <v>-1.04721</v>
       </c>
       <c r="M68" t="n">
         <v>699992029.6481038</v>
@@ -6465,13 +6465,13 @@
         <v>45653.15375</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R68" t="b">
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0.0004672652249457795</v>
+        <v>0.000462897335220834</v>
       </c>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
@@ -6485,68 +6485,68 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>falcon-finance</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>arb</t>
+          <t>usdf</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Arbitrum</t>
+          <t>Falcon USD</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.20396</v>
+        <v>0.9956930000000001</v>
       </c>
       <c r="F69" t="n">
-        <v>1384569299</v>
+        <v>1371499587</v>
       </c>
       <c r="G69" t="n">
         <v>68</v>
       </c>
       <c r="H69" t="n">
-        <v>353688143</v>
+        <v>431019</v>
       </c>
       <c r="I69" t="n">
-        <v>0.233802</v>
+        <v>0.996485</v>
       </c>
       <c r="J69" t="n">
-        <v>0.200698</v>
+        <v>0.995563</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.01751778309882746</v>
+        <v>-0.000373019832163979</v>
       </c>
       <c r="L69" t="n">
-        <v>-7.84335</v>
+        <v>-0.03745</v>
       </c>
       <c r="M69" t="n">
-        <v>6785574605</v>
+        <v>1377438577.534634</v>
       </c>
       <c r="N69" t="n">
-        <v>10000000000</v>
+        <v>1377438577.534634</v>
       </c>
       <c r="O69" t="n">
-        <v>2.39</v>
+        <v>1.075</v>
       </c>
       <c r="P69" s="1" t="n">
-        <v>45303.18748842592</v>
+        <v>45785.55951388889</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>0.0004574697134603933</v>
+        <v>0.0004464306090427221</v>
       </c>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
@@ -6560,68 +6560,68 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>falcon-finance</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>usdf</t>
+          <t>arb</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Falcon USD</t>
+          <t>Arbitrum</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9958900000000001</v>
+        <v>0.201268</v>
       </c>
       <c r="F70" t="n">
-        <v>1371720403</v>
+        <v>1365796592</v>
       </c>
       <c r="G70" t="n">
         <v>69</v>
       </c>
       <c r="H70" t="n">
-        <v>424718</v>
+        <v>321921982</v>
       </c>
       <c r="I70" t="n">
-        <v>0.996785</v>
+        <v>0.228493</v>
       </c>
       <c r="J70" t="n">
-        <v>0.995811</v>
+        <v>0.19785</v>
       </c>
       <c r="K70" t="n">
-        <v>-0.000212570827806124</v>
+        <v>-0.02485014670989169</v>
       </c>
       <c r="L70" t="n">
-        <v>-0.02529</v>
+        <v>-10.98992</v>
       </c>
       <c r="M70" t="n">
-        <v>1377438577.534634</v>
+        <v>6785574605</v>
       </c>
       <c r="N70" t="n">
-        <v>1377438577.534634</v>
+        <v>10000000000</v>
       </c>
       <c r="O70" t="n">
-        <v>1.075</v>
+        <v>2.39</v>
       </c>
       <c r="P70" s="1" t="n">
-        <v>45785.55951388889</v>
+        <v>45303.18748842592</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S70" t="n">
-        <v>0.0004498193425080082</v>
+        <v>0.0004430327061379209</v>
       </c>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
@@ -6635,68 +6635,68 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>bfusd</t>
+          <t>venice-token</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>bfusd</t>
+          <t>vvv</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>BFUSD</t>
+          <t>Venice Token</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.999285</v>
+        <v>27.9</v>
       </c>
       <c r="F71" t="n">
-        <v>1318998182</v>
+        <v>1345616698</v>
       </c>
       <c r="G71" t="n">
         <v>70</v>
       </c>
       <c r="H71" t="n">
-        <v>2418026</v>
+        <v>47354685</v>
       </c>
       <c r="I71" t="n">
-        <v>0.999842</v>
+        <v>29.43</v>
       </c>
       <c r="J71" t="n">
-        <v>0.998856</v>
+        <v>26.62</v>
       </c>
       <c r="K71" t="n">
-        <v>-0.000435796602689664</v>
+        <v>-1.357647037195715</v>
       </c>
       <c r="L71" t="n">
-        <v>-0.04781</v>
+        <v>-4.64051</v>
       </c>
       <c r="M71" t="n">
-        <v>1320000000</v>
+        <v>48212581.75746144</v>
       </c>
       <c r="N71" t="n">
-        <v>1320000000</v>
+        <v>81066921.51445468</v>
       </c>
       <c r="O71" t="n">
-        <v>1.007</v>
+        <v>34.53</v>
       </c>
       <c r="P71" s="1" t="n">
-        <v>45940.56990740741</v>
+        <v>46286.34548611111</v>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R71" t="b">
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>0.0004184279647520026</v>
+        <v>0.0004310093183493677</v>
       </c>
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
@@ -6710,68 +6710,68 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>venice-token</t>
+          <t>bfusd</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>vvv</t>
+          <t>bfusd</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Venice Token</t>
+          <t>BFUSD</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>27.11</v>
+        <v>0.999</v>
       </c>
       <c r="F72" t="n">
-        <v>1306844943</v>
+        <v>1318674349</v>
       </c>
       <c r="G72" t="n">
         <v>71</v>
       </c>
       <c r="H72" t="n">
-        <v>42868049</v>
+        <v>2400815</v>
       </c>
       <c r="I72" t="n">
-        <v>30.41</v>
+        <v>0.999831</v>
       </c>
       <c r="J72" t="n">
-        <v>26.62</v>
+        <v>0.998856</v>
       </c>
       <c r="K72" t="n">
-        <v>-2.770333202562018</v>
+        <v>-0.00064779606848675</v>
       </c>
       <c r="L72" t="n">
-        <v>-9.330870000000001</v>
+        <v>-0.0648</v>
       </c>
       <c r="M72" t="n">
-        <v>48210709.26338548</v>
+        <v>1320000000</v>
       </c>
       <c r="N72" t="n">
-        <v>81065296.20457117</v>
+        <v>1320000000</v>
       </c>
       <c r="O72" t="n">
-        <v>34.53</v>
+        <v>1.007</v>
       </c>
       <c r="P72" s="1" t="n">
-        <v>46286.34548611111</v>
+        <v>45940.56990740741</v>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>0.0004111917954637623</v>
+        <v>0.0004149567905233277</v>
       </c>
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
@@ -6785,7 +6785,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6804,34 +6804,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.04609591</v>
+        <v>0.04529207</v>
       </c>
       <c r="F73" t="n">
-        <v>1278277820</v>
+        <v>1255918293</v>
       </c>
       <c r="G73" t="n">
         <v>72</v>
       </c>
       <c r="H73" t="n">
-        <v>29621657</v>
+        <v>30399822</v>
       </c>
       <c r="I73" t="n">
-        <v>0.0489498</v>
+        <v>0.04846213</v>
       </c>
       <c r="J73" t="n">
-        <v>0.045136</v>
+        <v>0.04423726</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.001751469046742338</v>
+        <v>-0.001377032437974476</v>
       </c>
       <c r="L73" t="n">
-        <v>-3.62464</v>
+        <v>-2.95063</v>
       </c>
       <c r="M73" t="n">
         <v>27726432137.69469</v>
       </c>
       <c r="N73" t="n">
-        <v>27726512265.92985</v>
+        <v>27727128832.73649</v>
       </c>
       <c r="O73" t="n">
         <v>0.207411</v>
@@ -6840,13 +6840,13 @@
         <v>45504.69498842592</v>
       </c>
       <c r="Q73" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R73" t="b">
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0.0003941826230031546</v>
+        <v>0.000377566088799713</v>
       </c>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
@@ -6860,7 +6860,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6879,28 +6879,28 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.11572</v>
+        <v>0.117084</v>
       </c>
       <c r="F74" t="n">
-        <v>1229343996</v>
+        <v>1243518815</v>
       </c>
       <c r="G74" t="n">
         <v>73</v>
       </c>
       <c r="H74" t="n">
-        <v>160169997</v>
+        <v>152447718</v>
       </c>
       <c r="I74" t="n">
-        <v>0.124807</v>
+        <v>0.123201</v>
       </c>
       <c r="J74" t="n">
         <v>0.112007</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.00483219239587962</v>
+        <v>-0.004229877617648245</v>
       </c>
       <c r="L74" t="n">
-        <v>-4.00707</v>
+        <v>-3.48671</v>
       </c>
       <c r="M74" t="n">
         <v>10622244875.03591</v>
@@ -6915,13 +6915,13 @@
         <v>45364.45493055556</v>
       </c>
       <c r="Q74" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R74" t="b">
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>0.0003650468975899575</v>
+        <v>0.0003701783526515631</v>
       </c>
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
@@ -6935,7 +6935,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6954,34 +6954,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.132643</v>
+        <v>0.13483</v>
       </c>
       <c r="F75" t="n">
-        <v>1199789437</v>
+        <v>1221251465</v>
       </c>
       <c r="G75" t="n">
         <v>74</v>
       </c>
       <c r="H75" t="n">
-        <v>202471569</v>
+        <v>241054875</v>
       </c>
       <c r="I75" t="n">
-        <v>0.137178</v>
+        <v>0.13905</v>
       </c>
       <c r="J75" t="n">
         <v>0.115069</v>
       </c>
       <c r="K75" t="n">
-        <v>0.01542584</v>
+        <v>0.01603922</v>
       </c>
       <c r="L75" t="n">
-        <v>13.0003</v>
+        <v>13.50211</v>
       </c>
       <c r="M75" t="n">
         <v>9057776356.697313</v>
       </c>
       <c r="N75" t="n">
-        <v>9057797996.419762</v>
+        <v>9057846423.090742</v>
       </c>
       <c r="O75" t="n">
         <v>3.56</v>
@@ -6990,13 +6990,13 @@
         <v>43636.28563657407</v>
       </c>
       <c r="Q75" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R75" t="b">
         <v>1</v>
       </c>
       <c r="S75" t="n">
-        <v>0.0003474497951086118</v>
+        <v>0.0003569112371714996</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7059,34 +7059,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>10.88</v>
+        <v>10.87</v>
       </c>
       <c r="F76" t="n">
-        <v>1160531563</v>
+        <v>1159938519</v>
       </c>
       <c r="G76" t="n">
         <v>75</v>
       </c>
       <c r="H76" t="n">
-        <v>4608829</v>
+        <v>4692820</v>
       </c>
       <c r="I76" t="n">
-        <v>11.36</v>
+        <v>11.3</v>
       </c>
       <c r="J76" t="n">
         <v>10.78</v>
       </c>
       <c r="K76" t="n">
-        <v>-0.3825807371700041</v>
+        <v>-0.3826935637173854</v>
       </c>
       <c r="L76" t="n">
-        <v>-3.44934</v>
+        <v>-3.39955</v>
       </c>
       <c r="M76" t="n">
-        <v>106643867.5587171</v>
+        <v>106644263.3697571</v>
       </c>
       <c r="N76" t="n">
-        <v>118895217.5817878</v>
+        <v>118895495.4768023</v>
       </c>
       <c r="O76" t="n">
         <v>25.38</v>
@@ -7095,13 +7095,13 @@
         <v>45682.66666666666</v>
       </c>
       <c r="Q76" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R76" t="b">
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0003240752344535956</v>
+        <v>0.0003203803551848737</v>
       </c>
       <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr"/>
@@ -7115,7 +7115,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7134,28 +7134,28 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4.37</v>
+        <v>4.44</v>
       </c>
       <c r="F77" t="n">
-        <v>1090939386</v>
+        <v>1110658966</v>
       </c>
       <c r="G77" t="n">
         <v>76</v>
       </c>
       <c r="H77" t="n">
-        <v>97238180</v>
+        <v>103597738</v>
       </c>
       <c r="I77" t="n">
-        <v>4.74</v>
+        <v>4.66</v>
       </c>
       <c r="J77" t="n">
         <v>4.32</v>
       </c>
       <c r="K77" t="n">
-        <v>-0.3215552809411752</v>
+        <v>-0.2009295045816213</v>
       </c>
       <c r="L77" t="n">
-        <v>-6.89839</v>
+        <v>-4.32803</v>
       </c>
       <c r="M77" t="n">
         <v>250000000</v>
@@ -7170,13 +7170,13 @@
         <v>46021.04538194444</v>
       </c>
       <c r="Q77" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0002826393033483828</v>
+        <v>0.0002910190921492224</v>
       </c>
       <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr"/>
@@ -7190,7 +7190,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7209,34 +7209,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.328163</v>
+        <v>0.326262</v>
       </c>
       <c r="F78" t="n">
-        <v>1089550785</v>
+        <v>1083045706</v>
       </c>
       <c r="G78" t="n">
         <v>77</v>
       </c>
       <c r="H78" t="n">
-        <v>154089728</v>
+        <v>142469140</v>
       </c>
       <c r="I78" t="n">
-        <v>0.373954</v>
+        <v>0.372198</v>
       </c>
       <c r="J78" t="n">
-        <v>0.321335</v>
+        <v>0.319689</v>
       </c>
       <c r="K78" t="n">
-        <v>-0.0104877932576023</v>
+        <v>-0.04654824195593921</v>
       </c>
       <c r="L78" t="n">
-        <v>-3.09456</v>
+        <v>-12.48576</v>
       </c>
       <c r="M78" t="n">
         <v>3319369204.37</v>
       </c>
       <c r="N78" t="n">
-        <v>6861486562.065324</v>
+        <v>6861486559.019737</v>
       </c>
       <c r="O78" t="n">
         <v>2</v>
@@ -7245,13 +7245,13 @@
         <v>45322.29359953704</v>
       </c>
       <c r="Q78" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S78" t="n">
-        <v>0.0002818125153694893</v>
+        <v>0.0002745668286692386</v>
       </c>
       <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr"/>
@@ -7265,7 +7265,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7284,28 +7284,28 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.130378</v>
+        <v>0.12986</v>
       </c>
       <c r="F79" t="n">
-        <v>1067564318</v>
+        <v>1063329137</v>
       </c>
       <c r="G79" t="n">
         <v>78</v>
       </c>
       <c r="H79" t="n">
-        <v>31352283</v>
+        <v>37836323</v>
       </c>
       <c r="I79" t="n">
         <v>0.131925</v>
       </c>
       <c r="J79" t="n">
-        <v>0.125117</v>
+        <v>0.126056</v>
       </c>
       <c r="K79" t="n">
-        <v>0.00524757</v>
+        <v>0.00354789</v>
       </c>
       <c r="L79" t="n">
-        <v>4.19324</v>
+        <v>2.80884</v>
       </c>
       <c r="M79" t="n">
         <v>8188743036.341737</v>
@@ -7320,13 +7320,13 @@
         <v>44290.85721064815</v>
       </c>
       <c r="Q79" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R79" t="b">
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0002687215363093137</v>
+        <v>0.0002628194946670498</v>
       </c>
       <c r="T79" t="inlineStr"/>
       <c r="U79" t="inlineStr"/>
@@ -7340,7 +7340,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7359,31 +7359,31 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>7.41</v>
+        <v>7.44</v>
       </c>
       <c r="F80" t="n">
-        <v>1016411424</v>
+        <v>1020951262</v>
       </c>
       <c r="G80" t="n">
         <v>79</v>
       </c>
       <c r="H80" t="n">
-        <v>3091540</v>
+        <v>3048433</v>
       </c>
       <c r="I80" t="n">
-        <v>7.43</v>
+        <v>7.45</v>
       </c>
       <c r="J80" t="n">
         <v>7.26</v>
       </c>
       <c r="K80" t="n">
-        <v>0.110963</v>
+        <v>0.124544</v>
       </c>
       <c r="L80" t="n">
-        <v>1.51707</v>
+        <v>1.70282</v>
       </c>
       <c r="M80" t="n">
-        <v>137155021.2773955</v>
+        <v>137155021.7355672</v>
       </c>
       <c r="N80" t="n">
         <v>142155021.2773955</v>
@@ -7395,13 +7395,13 @@
         <v>44531.29832175926</v>
       </c>
       <c r="Q80" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R80" t="b">
         <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>0.0002382645527374928</v>
+        <v>0.0002375703221600072</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -7445,68 +7445,68 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>pi-network</t>
+          <t>render-token</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>pi</t>
+          <t>render</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Pi Network</t>
+          <t>Render</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.089464</v>
+        <v>1.94</v>
       </c>
       <c r="F81" t="n">
-        <v>1006057012</v>
+        <v>1007878021</v>
       </c>
       <c r="G81" t="n">
         <v>80</v>
       </c>
       <c r="H81" t="n">
-        <v>8386959</v>
+        <v>105811089</v>
       </c>
       <c r="I81" t="n">
-        <v>0.091534</v>
+        <v>2.09</v>
       </c>
       <c r="J81" t="n">
-        <v>0.088142</v>
+        <v>1.88</v>
       </c>
       <c r="K81" t="n">
-        <v>-0.001120415701620109</v>
+        <v>-0.1062081559773733</v>
       </c>
       <c r="L81" t="n">
-        <v>-1.19691</v>
+        <v>-5.18352</v>
       </c>
       <c r="M81" t="n">
-        <v>11243022455.381</v>
+        <v>518776241.2826915</v>
       </c>
       <c r="N81" t="n">
-        <v>17296957623.66307</v>
+        <v>533536414.5626915</v>
       </c>
       <c r="O81" t="n">
-        <v>2.99</v>
+        <v>13.53</v>
       </c>
       <c r="P81" s="1" t="n">
-        <v>45714.36184027778</v>
+        <v>45368.35444444444</v>
       </c>
       <c r="Q81" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S81" t="n">
-        <v>0.000232099424403212</v>
+        <v>0.0002297811511070664</v>
       </c>
       <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr"/>
@@ -7520,68 +7520,68 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>render-token</t>
+          <t>pi-network</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>render</t>
+          <t>pi</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Render</t>
+          <t>Pi Network</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1.92</v>
+        <v>0.089061</v>
       </c>
       <c r="F82" t="n">
-        <v>998052162</v>
+        <v>1000529433</v>
       </c>
       <c r="G82" t="n">
         <v>81</v>
       </c>
       <c r="H82" t="n">
-        <v>101424166</v>
+        <v>8562997</v>
       </c>
       <c r="I82" t="n">
-        <v>2.09</v>
+        <v>0.091534</v>
       </c>
       <c r="J82" t="n">
-        <v>1.9</v>
+        <v>0.088142</v>
       </c>
       <c r="K82" t="n">
-        <v>-0.08383911960281076</v>
+        <v>-0.001592062216003651</v>
       </c>
       <c r="L82" t="n">
-        <v>-4.18526</v>
+        <v>-1.75621</v>
       </c>
       <c r="M82" t="n">
-        <v>518776241.2826915</v>
+        <v>11243022455.381</v>
       </c>
       <c r="N82" t="n">
-        <v>533536414.5626915</v>
+        <v>17296957623.66307</v>
       </c>
       <c r="O82" t="n">
-        <v>13.53</v>
+        <v>2.99</v>
       </c>
       <c r="P82" s="1" t="n">
-        <v>45368.35444444444</v>
+        <v>45714.36184027778</v>
       </c>
       <c r="Q82" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R82" t="b">
         <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0.0002273332505686506</v>
+        <v>0.0002254027870174281</v>
       </c>
       <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr"/>
@@ -7595,7 +7595,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7632,7 +7632,7 @@
         <v>107.53</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>-1.4211e-14</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -7650,13 +7650,13 @@
         <v>46287.17361111111</v>
       </c>
       <c r="Q83" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R83" t="b">
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.000216480778402994</v>
+        <v>0.0002130670498734008</v>
       </c>
       <c r="T83" t="inlineStr"/>
       <c r="U83" t="inlineStr"/>
@@ -7670,7 +7670,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7689,16 +7689,16 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="F84" t="n">
-        <v>914644255</v>
+        <v>922328114</v>
       </c>
       <c r="G84" t="n">
         <v>83</v>
       </c>
       <c r="H84" t="n">
-        <v>71054341</v>
+        <v>72353589</v>
       </c>
       <c r="I84" t="n">
         <v>1.89</v>
@@ -7707,16 +7707,16 @@
         <v>1.69</v>
       </c>
       <c r="K84" t="n">
-        <v>-0.152939379036215</v>
+        <v>-0.1492814572188828</v>
       </c>
       <c r="L84" t="n">
-        <v>-8.151149999999999</v>
+        <v>-7.94375</v>
       </c>
       <c r="M84" t="n">
-        <v>533071893.64372</v>
+        <v>533140304.847045</v>
       </c>
       <c r="N84" t="n">
-        <v>533095087.665018</v>
+        <v>533140304.847045</v>
       </c>
       <c r="O84" t="n">
         <v>43.84</v>
@@ -7725,13 +7725,13 @@
         <v>44458.66666666666</v>
       </c>
       <c r="Q84" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R84" t="b">
         <v>1</v>
       </c>
       <c r="S84" t="n">
-        <v>0.0001776712851428242</v>
+        <v>0.0001788096392083586</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7794,34 +7794,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1.052</v>
+        <v>1.06</v>
       </c>
       <c r="F85" t="n">
-        <v>875114564</v>
+        <v>880685714</v>
       </c>
       <c r="G85" t="n">
         <v>84</v>
       </c>
       <c r="H85" t="n">
-        <v>179237600</v>
+        <v>166877189</v>
       </c>
       <c r="I85" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="J85" t="n">
         <v>1.021</v>
       </c>
       <c r="K85" t="n">
-        <v>-0.09836054262543192</v>
+        <v>-0.07233708610244571</v>
       </c>
       <c r="L85" t="n">
-        <v>-8.578329999999999</v>
+        <v>-6.39048</v>
       </c>
       <c r="M85" t="n">
-        <v>831242083</v>
+        <v>831252997</v>
       </c>
       <c r="N85" t="n">
-        <v>1957023439</v>
+        <v>1957023067</v>
       </c>
       <c r="O85" t="n">
         <v>236.84</v>
@@ -7830,13 +7830,13 @@
         <v>44287.22894675926</v>
       </c>
       <c r="Q85" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R85" t="b">
         <v>1</v>
       </c>
       <c r="S85" t="n">
-        <v>0.0001541348817208368</v>
+        <v>0.000153998670248559</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -7880,68 +7880,68 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>nexo</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>nexo</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NEXO</t>
+          <t>Dash</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.859483</v>
+        <v>65.52</v>
       </c>
       <c r="F86" t="n">
-        <v>859354234</v>
+        <v>841803422</v>
       </c>
       <c r="G86" t="n">
         <v>85</v>
       </c>
       <c r="H86" t="n">
-        <v>7206984</v>
+        <v>154007039</v>
       </c>
       <c r="I86" t="n">
-        <v>0.889543</v>
+        <v>68.88</v>
       </c>
       <c r="J86" t="n">
-        <v>0.849503</v>
+        <v>63.18</v>
       </c>
       <c r="K86" t="n">
-        <v>-0.01097855995793973</v>
+        <v>-2.774559080096893</v>
       </c>
       <c r="L86" t="n">
-        <v>-1.27462</v>
+        <v>-4.06248</v>
       </c>
       <c r="M86" t="n">
-        <v>1000000000</v>
+        <v>12846801.60815124</v>
       </c>
       <c r="N86" t="n">
-        <v>1000000000</v>
+        <v>12846967.2331195</v>
       </c>
       <c r="O86" t="n">
-        <v>4.07</v>
+        <v>1493.59</v>
       </c>
       <c r="P86" s="1" t="n">
-        <v>44328.27623842593</v>
+        <v>43088.66666666666</v>
       </c>
       <c r="Q86" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R86" t="b">
         <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0.0001447510116333208</v>
+        <v>0.0001308322019398672</v>
       </c>
       <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr"/>
@@ -7955,68 +7955,68 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>nexo</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>nexo</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Dash</t>
+          <t>NEXO</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>64.65000000000001</v>
+        <v>0.8269609999999999</v>
       </c>
       <c r="F87" t="n">
-        <v>830684935</v>
+        <v>827073904</v>
       </c>
       <c r="G87" t="n">
         <v>86</v>
       </c>
       <c r="H87" t="n">
-        <v>157304922</v>
+        <v>7876360</v>
       </c>
       <c r="I87" t="n">
-        <v>69.68000000000001</v>
+        <v>0.8834880000000001</v>
       </c>
       <c r="J87" t="n">
-        <v>63.18</v>
+        <v>0.8333390000000001</v>
       </c>
       <c r="K87" t="n">
-        <v>-3.579599346798872</v>
+        <v>-0.04848970496131588</v>
       </c>
       <c r="L87" t="n">
-        <v>-5.24642</v>
+        <v>-5.53883</v>
       </c>
       <c r="M87" t="n">
-        <v>12846155.1088331</v>
+        <v>1000000000</v>
       </c>
       <c r="N87" t="n">
-        <v>12846476.4636538</v>
+        <v>1000000000</v>
       </c>
       <c r="O87" t="n">
-        <v>1493.59</v>
+        <v>4.07</v>
       </c>
       <c r="P87" s="1" t="n">
-        <v>43088.66666666666</v>
+        <v>44328.27623842593</v>
       </c>
       <c r="Q87" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R87" t="b">
         <v>1</v>
       </c>
       <c r="S87" t="n">
-        <v>0.0001276810024827413</v>
+        <v>0.0001220562040653256</v>
       </c>
       <c r="T87" t="inlineStr"/>
       <c r="U87" t="inlineStr"/>
@@ -8030,7 +8030,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8049,31 +8049,31 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="F88" t="n">
-        <v>831942989</v>
+        <v>824919392</v>
       </c>
       <c r="G88" t="n">
         <v>87</v>
       </c>
       <c r="H88" t="n">
-        <v>108660441</v>
+        <v>104584532</v>
       </c>
       <c r="I88" t="n">
         <v>2.84</v>
       </c>
       <c r="J88" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="K88" t="n">
-        <v>-0.1668992740823865</v>
+        <v>-0.2411439652573488</v>
       </c>
       <c r="L88" t="n">
-        <v>-6.0504</v>
+        <v>-8.52224</v>
       </c>
       <c r="M88" t="n">
-        <v>318686521.7818068</v>
+        <v>318687703.0077946</v>
       </c>
       <c r="N88" t="n">
         <v>330299406.389633</v>
@@ -8085,13 +8085,13 @@
         <v>44316.08914351852</v>
       </c>
       <c r="Q88" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R88" t="b">
         <v>1</v>
       </c>
       <c r="S88" t="n">
-        <v>0.0001284300613729473</v>
+        <v>0.0001207725237213609</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8154,31 +8154,31 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.810537</v>
+        <v>0.828161</v>
       </c>
       <c r="F89" t="n">
-        <v>806751236</v>
+        <v>824769272</v>
       </c>
       <c r="G89" t="n">
         <v>88</v>
       </c>
       <c r="H89" t="n">
-        <v>84274522</v>
+        <v>93550416</v>
       </c>
       <c r="I89" t="n">
-        <v>0.860877</v>
+        <v>0.844204</v>
       </c>
       <c r="J89" t="n">
         <v>0.766646</v>
       </c>
       <c r="K89" t="n">
-        <v>-0.01572964013575917</v>
+        <v>-0.01108347407055277</v>
       </c>
       <c r="L89" t="n">
-        <v>-2.06426</v>
+        <v>-1.32065</v>
       </c>
       <c r="M89" t="n">
-        <v>995776144.5308471</v>
+        <v>995760456.212387</v>
       </c>
       <c r="N89" t="n">
         <v>1988034890.229641</v>
@@ -8190,13 +8190,13 @@
         <v>45633.25043981482</v>
       </c>
       <c r="Q89" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R89" t="b">
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>0.000113430620534539</v>
+        <v>0.0001206830806858911</v>
       </c>
       <c r="T89" t="inlineStr"/>
       <c r="U89" t="inlineStr"/>
@@ -8210,173 +8210,143 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>vechain</t>
+          <t>superstate-short-duration-us-government-securities-fund-ustb</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>vet</t>
+          <t>ustb</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VeChain</t>
+          <t>Invesco Short Duration US Government Securities Fund</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.0088728</v>
+        <v>11.22</v>
       </c>
       <c r="F90" t="n">
-        <v>762872738</v>
+        <v>793773358</v>
       </c>
       <c r="G90" t="n">
         <v>89</v>
       </c>
       <c r="H90" t="n">
-        <v>14145069</v>
+        <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>0.00942057</v>
+        <v>11.22</v>
       </c>
       <c r="J90" t="n">
-        <v>0.008678440000000001</v>
+        <v>11.22</v>
       </c>
       <c r="K90" t="n">
-        <v>-0.000378466448109313</v>
+        <v>0.001092</v>
       </c>
       <c r="L90" t="n">
-        <v>-4.09952</v>
+        <v>0.009730000000000001</v>
       </c>
       <c r="M90" t="n">
-        <v>85985041177</v>
+        <v>70718272.30833299</v>
       </c>
       <c r="N90" t="n">
-        <v>85985041177</v>
+        <v>70769366.984749</v>
       </c>
       <c r="O90" t="n">
-        <v>0.280991</v>
+        <v>11.22</v>
       </c>
       <c r="P90" s="1" t="n">
-        <v>44304.71413194444</v>
+        <v>46293.65983796296</v>
       </c>
       <c r="Q90" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R90" t="b">
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>8.730489062486519e-05</v>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>Cadena de suministro</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>Trazabilidad</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>Proof of Authority</t>
-        </is>
-      </c>
-      <c r="W90" t="n">
-        <v>2015</v>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>vechain.org</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>Trazabilidad de productos y logística</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Layer 1)</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>Enfocada en trazabilidad de cadenas de suministro para empresas.</t>
-        </is>
-      </c>
+        <v>0.0001022153972638352</v>
+      </c>
+      <c r="T90" t="inlineStr"/>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr"/>
+      <c r="W90" t="inlineStr"/>
+      <c r="X90" t="inlineStr"/>
+      <c r="Y90" t="inlineStr"/>
+      <c r="Z90" t="inlineStr"/>
+      <c r="AA90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>superstate-short-duration-us-government-securities-fund-ustb</t>
+          <t>stable-2</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ustb</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Invesco Short Duration US Government Securities Fund</t>
+          <t>​​Stable</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>11.22</v>
+        <v>0.02914287</v>
       </c>
       <c r="F91" t="n">
-        <v>744133773</v>
+        <v>779378621</v>
       </c>
       <c r="G91" t="n">
         <v>90</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>11011319</v>
       </c>
       <c r="I91" t="n">
-        <v>11.22</v>
+        <v>0.02892869</v>
       </c>
       <c r="J91" t="n">
-        <v>11.22</v>
+        <v>0.02667611</v>
       </c>
       <c r="K91" t="n">
-        <v>0.001092</v>
+        <v>0.00166779</v>
       </c>
       <c r="L91" t="n">
-        <v>0.009730000000000001</v>
+        <v>6.07018</v>
       </c>
       <c r="M91" t="n">
-        <v>66295818.90593</v>
+        <v>26740211248</v>
       </c>
       <c r="N91" t="n">
-        <v>66313632.296237</v>
+        <v>100000000000</v>
       </c>
       <c r="O91" t="n">
-        <v>11.22</v>
+        <v>0.04323745</v>
       </c>
       <c r="P91" s="1" t="n">
-        <v>46293.65983796296</v>
+        <v>46156.97986111111</v>
       </c>
       <c r="Q91" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S91" t="n">
-        <v>7.614750920363168e-05</v>
+        <v>9.363886534224858e-05</v>
       </c>
       <c r="T91" t="inlineStr"/>
       <c r="U91" t="inlineStr"/>
@@ -8390,82 +8360,112 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>akedo</t>
+          <t>vechain</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ake</t>
+          <t>vet</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Akedo</t>
+          <t>VeChain</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.03223242</v>
+        <v>0.00885798</v>
       </c>
       <c r="F92" t="n">
-        <v>733590336</v>
+        <v>761736772</v>
       </c>
       <c r="G92" t="n">
         <v>91</v>
       </c>
       <c r="H92" t="n">
-        <v>12704955</v>
+        <v>13058453</v>
       </c>
       <c r="I92" t="n">
-        <v>0.03303273</v>
+        <v>0.009248940000000001</v>
       </c>
       <c r="J92" t="n">
-        <v>0.02846185</v>
+        <v>0.00864553</v>
       </c>
       <c r="K92" t="n">
-        <v>-0.0006220277736381789</v>
+        <v>-0.000288199262861687</v>
       </c>
       <c r="L92" t="n">
-        <v>-1.8565</v>
+        <v>-3.15104</v>
       </c>
       <c r="M92" t="n">
-        <v>22796250000</v>
+        <v>85985041177</v>
       </c>
       <c r="N92" t="n">
-        <v>100000000000</v>
+        <v>85985041177</v>
       </c>
       <c r="O92" t="n">
-        <v>0.146656</v>
+        <v>0.280991</v>
       </c>
       <c r="P92" s="1" t="n">
-        <v>46285.43993055556</v>
+        <v>44304.71413194444</v>
       </c>
       <c r="Q92" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R92" t="b">
         <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>6.986983335014959e-05</v>
-      </c>
-      <c r="T92" t="inlineStr"/>
-      <c r="U92" t="inlineStr"/>
-      <c r="V92" t="inlineStr"/>
-      <c r="W92" t="inlineStr"/>
-      <c r="X92" t="inlineStr"/>
-      <c r="Y92" t="inlineStr"/>
-      <c r="Z92" t="inlineStr"/>
-      <c r="AA92" t="inlineStr"/>
+        <v>8.312767079216326e-05</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Cadena de suministro</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Trazabilidad</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Proof of Authority</t>
+        </is>
+      </c>
+      <c r="W92" t="n">
+        <v>2015</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>vechain.org</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>Trazabilidad de productos y logística</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Layer 1)</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>Enfocada en trazabilidad de cadenas de suministro para empresas.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8484,28 +8484,28 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>7.32</v>
+        <v>7.33</v>
       </c>
       <c r="F93" t="n">
-        <v>732514377</v>
+        <v>732881399</v>
       </c>
       <c r="G93" t="n">
         <v>92</v>
       </c>
       <c r="H93" t="n">
-        <v>127694507</v>
+        <v>124056405</v>
       </c>
       <c r="I93" t="n">
-        <v>7.9</v>
+        <v>7.83</v>
       </c>
       <c r="J93" t="n">
-        <v>7.24</v>
+        <v>7.19</v>
       </c>
       <c r="K93" t="n">
-        <v>-0.4318888678095671</v>
+        <v>-0.4105163792450979</v>
       </c>
       <c r="L93" t="n">
-        <v>-5.52713</v>
+        <v>-5.30368</v>
       </c>
       <c r="M93" t="n">
         <v>100000000</v>
@@ -8520,13 +8520,13 @@
         <v>45365.29608796296</v>
       </c>
       <c r="Q93" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R93" t="b">
         <v>1</v>
       </c>
       <c r="S93" t="n">
-        <v>6.922919578256735e-05</v>
+        <v>6.593534364900049e-05</v>
       </c>
       <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr"/>
@@ -8540,7 +8540,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8562,7 +8562,7 @@
         <v>1.21</v>
       </c>
       <c r="F94" t="n">
-        <v>730880634</v>
+        <v>730775894</v>
       </c>
       <c r="G94" t="n">
         <v>93</v>
@@ -8577,10 +8577,10 @@
         <v>1.2</v>
       </c>
       <c r="K94" t="n">
-        <v>-0.005213524096191691</v>
+        <v>-7.068572791646399e-05</v>
       </c>
       <c r="L94" t="n">
-        <v>-0.43064</v>
+        <v>-0.00586</v>
       </c>
       <c r="M94" t="n">
         <v>606320017.89252</v>
@@ -8595,13 +8595,13 @@
         <v>46049.54175925926</v>
       </c>
       <c r="Q94" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R94" t="b">
         <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>6.825644761876693e-05</v>
+        <v>6.468086217819902e-05</v>
       </c>
       <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
@@ -8615,187 +8615,187 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>stable-2</t>
+          <t>aptos</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>apt</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>​​Stable</t>
+          <t>Aptos</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.02696925</v>
+        <v>0.830133</v>
       </c>
       <c r="F95" t="n">
-        <v>720871261</v>
+        <v>722897865</v>
       </c>
       <c r="G95" t="n">
         <v>94</v>
       </c>
       <c r="H95" t="n">
-        <v>9558237</v>
+        <v>97446300</v>
       </c>
       <c r="I95" t="n">
-        <v>0.02887433</v>
+        <v>0.8736660000000001</v>
       </c>
       <c r="J95" t="n">
-        <v>0.02667611</v>
+        <v>0.796221</v>
       </c>
       <c r="K95" t="n">
-        <v>-0.000392140960818538</v>
+        <v>-0.03436538616411289</v>
       </c>
       <c r="L95" t="n">
-        <v>-1.49528</v>
+        <v>-3.97518</v>
       </c>
       <c r="M95" t="n">
-        <v>26731478395</v>
+        <v>870942902.9405427</v>
       </c>
       <c r="N95" t="n">
-        <v>100000000000</v>
+        <v>1209383289.125979</v>
       </c>
       <c r="O95" t="n">
-        <v>0.04323745</v>
+        <v>19.92</v>
       </c>
       <c r="P95" s="1" t="n">
-        <v>46156.97986111111</v>
+        <v>44952.26755787037</v>
       </c>
       <c r="Q95" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R95" t="b">
         <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>6.229675921823914e-05</v>
-      </c>
-      <c r="T95" t="inlineStr"/>
-      <c r="U95" t="inlineStr"/>
-      <c r="V95" t="inlineStr"/>
-      <c r="W95" t="inlineStr"/>
-      <c r="X95" t="inlineStr"/>
-      <c r="Y95" t="inlineStr"/>
-      <c r="Z95" t="inlineStr"/>
-      <c r="AA95" t="inlineStr"/>
+        <v>5.998705171138151e-05</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Plataforma de contratos inteligentes</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Layer 1</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Proof of Stake (BFT)</t>
+        </is>
+      </c>
+      <c r="W95" t="n">
+        <v>2022</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>aptosfoundation.org</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>Contratos inteligentes de alto rendimiento</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Layer 1)</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>Desarrollada por exingenieros del proyecto Diem (Meta/Facebook).</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>aptos</t>
+          <t>akedo</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>apt</t>
+          <t>ake</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Aptos</t>
+          <t>Akedo</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.8152160000000001</v>
+        <v>0.03120101</v>
       </c>
       <c r="F96" t="n">
-        <v>710071940</v>
+        <v>711640350</v>
       </c>
       <c r="G96" t="n">
         <v>95</v>
       </c>
       <c r="H96" t="n">
-        <v>101428331</v>
+        <v>15865482</v>
       </c>
       <c r="I96" t="n">
-        <v>0.8736660000000001</v>
+        <v>0.03294704</v>
       </c>
       <c r="J96" t="n">
-        <v>0.796221</v>
+        <v>0.02846185</v>
       </c>
       <c r="K96" t="n">
-        <v>-0.02857829351369168</v>
+        <v>0.00081761</v>
       </c>
       <c r="L96" t="n">
-        <v>-3.4414</v>
+        <v>2.69098</v>
       </c>
       <c r="M96" t="n">
-        <v>870930831.2042739</v>
+        <v>22796250000</v>
       </c>
       <c r="N96" t="n">
-        <v>1209370935.873864</v>
+        <v>100000000000</v>
       </c>
       <c r="O96" t="n">
-        <v>19.92</v>
+        <v>0.146656</v>
       </c>
       <c r="P96" s="1" t="n">
-        <v>44952.26755787037</v>
+        <v>46285.43993055556</v>
       </c>
       <c r="Q96" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R96" t="b">
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>5.586672727744962e-05</v>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>Plataforma de contratos inteligentes</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>Layer 1</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>Proof of Stake (BFT)</t>
-        </is>
-      </c>
-      <c r="W96" t="n">
-        <v>2022</v>
-      </c>
-      <c r="X96" t="inlineStr">
-        <is>
-          <t>aptosfoundation.org</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>Contratos inteligentes de alto rendimiento</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Layer 1)</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>Desarrollada por exingenieros del proyecto Diem (Meta/Facebook).</t>
-        </is>
-      </c>
+        <v>5.327970882937953e-05</v>
+      </c>
+      <c r="T96" t="inlineStr"/>
+      <c r="U96" t="inlineStr"/>
+      <c r="V96" t="inlineStr"/>
+      <c r="W96" t="inlineStr"/>
+      <c r="X96" t="inlineStr"/>
+      <c r="Y96" t="inlineStr"/>
+      <c r="Z96" t="inlineStr"/>
+      <c r="AA96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8814,16 +8814,16 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.999342</v>
+        <v>0.99948</v>
       </c>
       <c r="F97" t="n">
-        <v>698509109</v>
+        <v>698633598</v>
       </c>
       <c r="G97" t="n">
         <v>96</v>
       </c>
       <c r="H97" t="n">
-        <v>6414414</v>
+        <v>12705371</v>
       </c>
       <c r="I97" t="n">
         <v>0.999571</v>
@@ -8832,10 +8832,10 @@
         <v>0.998854</v>
       </c>
       <c r="K97" t="n">
-        <v>0.00032362</v>
+        <v>0.00024192</v>
       </c>
       <c r="L97" t="n">
-        <v>0.02817</v>
+        <v>0.02421</v>
       </c>
       <c r="M97" t="n">
         <v>699000000</v>
@@ -8850,13 +8850,13 @@
         <v>45350.38608796296</v>
       </c>
       <c r="Q97" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R97" t="b">
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>4.898209326611213e-05</v>
+        <v>4.553015260447865e-05</v>
       </c>
       <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr"/>
@@ -8870,7 +8870,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8889,28 +8889,28 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.0345497</v>
+        <v>0.03446413</v>
       </c>
       <c r="F98" t="n">
-        <v>689160440</v>
+        <v>687460655</v>
       </c>
       <c r="G98" t="n">
         <v>97</v>
       </c>
       <c r="H98" t="n">
-        <v>37492134</v>
+        <v>40281267</v>
       </c>
       <c r="I98" t="n">
-        <v>0.03561706</v>
+        <v>0.03635087</v>
       </c>
       <c r="J98" t="n">
-        <v>0.03188839</v>
+        <v>0.03245616</v>
       </c>
       <c r="K98" t="n">
-        <v>0.00191179</v>
+        <v>0.00032728</v>
       </c>
       <c r="L98" t="n">
-        <v>5.9083</v>
+        <v>0.95873</v>
       </c>
       <c r="M98" t="n">
         <v>19946688440</v>
@@ -8925,13 +8925,13 @@
         <v>44428.86097222222</v>
       </c>
       <c r="Q98" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R98" t="b">
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>4.341579513738081e-05</v>
+        <v>3.887319858735641e-05</v>
       </c>
       <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr"/>
@@ -8945,7 +8945,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8964,16 +8964,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.695922</v>
+        <v>0.705315</v>
       </c>
       <c r="F99" t="n">
-        <v>672035613</v>
+        <v>681103656</v>
       </c>
       <c r="G99" t="n">
         <v>98</v>
       </c>
       <c r="H99" t="n">
-        <v>56806951</v>
+        <v>58090067</v>
       </c>
       <c r="I99" t="n">
         <v>0.7287400000000001</v>
@@ -8982,10 +8982,10 @@
         <v>0.66335</v>
       </c>
       <c r="K99" t="n">
-        <v>-0.00323059170023321</v>
+        <v>-0.01101288620817187</v>
       </c>
       <c r="L99" t="n">
-        <v>-0.39936</v>
+        <v>-1.53741</v>
       </c>
       <c r="M99" t="n">
         <v>965350000</v>
@@ -9000,13 +9000,13 @@
         <v>45378.63525462963</v>
       </c>
       <c r="Q99" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R99" t="b">
         <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>3.321948885196762e-05</v>
+        <v>3.508563339259152e-05</v>
       </c>
       <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr"/>
@@ -9020,7 +9020,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9039,31 +9039,31 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.07896</v>
+        <v>0.080959</v>
       </c>
       <c r="F100" t="n">
-        <v>621914490</v>
+        <v>637475365</v>
       </c>
       <c r="G100" t="n">
         <v>99</v>
       </c>
       <c r="H100" t="n">
-        <v>54917622</v>
+        <v>52852766</v>
       </c>
       <c r="I100" t="n">
-        <v>0.08641</v>
+        <v>0.08483</v>
       </c>
       <c r="J100" t="n">
         <v>0.07798099999999999</v>
       </c>
       <c r="K100" t="n">
-        <v>-0.006167896403060341</v>
+        <v>-0.002308890805568356</v>
       </c>
       <c r="L100" t="n">
-        <v>-7.27312</v>
+        <v>-2.77283</v>
       </c>
       <c r="M100" t="n">
-        <v>7874959364.858932</v>
+        <v>7874959363.63714</v>
       </c>
       <c r="N100" t="n">
         <v>10000000000</v>
@@ -9075,13 +9075,13 @@
         <v>45366.95920138889</v>
       </c>
       <c r="Q100" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>3.376832836997776e-06</v>
+        <v>9.091450209823293e-06</v>
       </c>
       <c r="T100" t="inlineStr"/>
       <c r="U100" t="inlineStr"/>
@@ -9095,7 +9095,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9114,34 +9114,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.00708898</v>
+        <v>0.00715495</v>
       </c>
       <c r="F101" t="n">
-        <v>616243056</v>
+        <v>622216396</v>
       </c>
       <c r="G101" t="n">
         <v>100</v>
       </c>
       <c r="H101" t="n">
-        <v>5875819</v>
+        <v>4627448</v>
       </c>
       <c r="I101" t="n">
-        <v>0.00739575</v>
+        <v>0.00719155</v>
       </c>
       <c r="J101" t="n">
         <v>0.00693629</v>
       </c>
       <c r="K101" t="n">
-        <v>-0.000279257244197242</v>
+        <v>8.72e-06</v>
       </c>
       <c r="L101" t="n">
-        <v>-3.82284</v>
+        <v>0.12203</v>
       </c>
       <c r="M101" t="n">
-        <v>86949015480.60582</v>
+        <v>86964280297.02844</v>
       </c>
       <c r="N101" t="n">
-        <v>106642103160.9111</v>
+        <v>106649366601.2216</v>
       </c>
       <c r="O101" t="n">
         <v>0.150073</v>
@@ -9150,7 +9150,7 @@
         <v>44935.80144675926</v>
       </c>
       <c r="Q101" s="1" t="n">
-        <v>46293.71134259259</v>
+        <v>46293.98981481481</v>
       </c>
       <c r="R101" t="b">
         <v>0</v>

--- a/src/xlsx/enriched_data.xlsx
+++ b/src/xlsx/enriched_data.xlsx
@@ -560,7 +560,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -579,16 +579,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>83568</v>
+        <v>83507</v>
       </c>
       <c r="F2" t="n">
-        <v>1679008903650</v>
+        <v>1677708109294</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>41791363643</v>
+        <v>41723595724</v>
       </c>
       <c r="I2" t="n">
         <v>84945</v>
@@ -597,16 +597,16 @@
         <v>82581</v>
       </c>
       <c r="K2" t="n">
-        <v>-786.8917941942054</v>
+        <v>-943.0202493105753</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.93283</v>
+        <v>-1.09898</v>
       </c>
       <c r="M2" t="n">
         <v>20090481</v>
       </c>
       <c r="N2" t="n">
-        <v>20090690</v>
+        <v>20090790</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -615,7 +615,7 @@
         <v>45936.45673611111</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
@@ -665,7 +665,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -684,16 +684,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2690.99</v>
+        <v>2688.58</v>
       </c>
       <c r="F3" t="n">
-        <v>328578897942</v>
+        <v>328230175563</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>17136731362</v>
+        <v>17124992169</v>
       </c>
       <c r="I3" t="n">
         <v>2717.37</v>
@@ -702,10 +702,10 @@
         <v>2636.99</v>
       </c>
       <c r="K3" t="n">
-        <v>7.15</v>
+        <v>1.57</v>
       </c>
       <c r="L3" t="n">
-        <v>0.26649</v>
+        <v>0.06862</v>
       </c>
       <c r="M3" t="n">
         <v>122087473.8258867</v>
@@ -720,13 +720,13 @@
         <v>45893.47295138889</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1953999540371524</v>
+        <v>0.1953435503201923</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -789,16 +789,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999718</v>
+        <v>0.99966</v>
       </c>
       <c r="F4" t="n">
-        <v>183821621020</v>
+        <v>183812509434</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>76015680441</v>
+        <v>75915231025</v>
       </c>
       <c r="I4" t="n">
         <v>0.9998359999999999</v>
@@ -807,10 +807,10 @@
         <v>0.999602</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.3051755416236e-05</v>
+        <v>-0.000117278820729316</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.00331</v>
+        <v>-0.00747</v>
       </c>
       <c r="M4" t="n">
         <v>183874242892.1083</v>
@@ -825,13 +825,13 @@
         <v>43304.66666666666</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1091520839716213</v>
+        <v>0.1092312815725885</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -894,16 +894,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>763.86</v>
+        <v>763.48</v>
       </c>
       <c r="F5" t="n">
-        <v>101716240299</v>
+        <v>101664628051</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1060279716</v>
+        <v>1057079982</v>
       </c>
       <c r="I5" t="n">
         <v>783.74</v>
@@ -912,10 +912,10 @@
         <v>757.15</v>
       </c>
       <c r="K5" t="n">
-        <v>-13.44815267303102</v>
+        <v>-15.24681102564591</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.73009</v>
+        <v>-1.92599</v>
       </c>
       <c r="M5" t="n">
         <v>133159615.43</v>
@@ -930,13 +930,13 @@
         <v>45943.02875</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0602328561533096</v>
+        <v>0.06024876697925312</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1002,13 +1002,13 @@
         <v>1.5</v>
       </c>
       <c r="F6" t="n">
-        <v>94079399488</v>
+        <v>94017254994</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>4363467206</v>
+        <v>4351788248</v>
       </c>
       <c r="I6" t="n">
         <v>1.53</v>
@@ -1017,10 +1017,10 @@
         <v>1.47</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0167705133797087</v>
+        <v>-0.02329244526184704</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.10837</v>
+        <v>-1.49005</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -1035,13 +1035,13 @@
         <v>45855.82005787037</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R6" t="b">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05568274808286571</v>
+        <v>0.05568884947366665</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1104,16 +1104,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999924</v>
+        <v>0.999868</v>
       </c>
       <c r="F7" t="n">
-        <v>74721963135</v>
+        <v>74718233752</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>20683397359</v>
+        <v>20699802142</v>
       </c>
       <c r="I7" t="n">
         <v>0.99999</v>
@@ -1122,10 +1122,10 @@
         <v>0.99954</v>
       </c>
       <c r="K7" t="n">
-        <v>9.628000000000001e-05</v>
+        <v>1.402e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00963</v>
+        <v>0.00566</v>
       </c>
       <c r="M7" t="n">
         <v>74728156839.12137</v>
@@ -1140,13 +1140,13 @@
         <v>43418.66666666666</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04414938899463879</v>
+        <v>0.04418137571161074</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1209,16 +1209,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>118.76</v>
+        <v>118.72</v>
       </c>
       <c r="F8" t="n">
-        <v>69818192382</v>
+        <v>69795574274</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>4131466796</v>
+        <v>4127386361</v>
       </c>
       <c r="I8" t="n">
         <v>122.78</v>
@@ -1227,10 +1227,10 @@
         <v>117.29</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.09094262113662</v>
+        <v>-3.397568826272234</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.53671</v>
+        <v>-2.76459</v>
       </c>
       <c r="M8" t="n">
         <v>587852966.003577</v>
@@ -1245,13 +1245,13 @@
         <v>45676.13572916666</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R8" t="b">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.04122767209218704</v>
+        <v>0.04124612971792581</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1314,16 +1314,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.335415</v>
+        <v>0.335426</v>
       </c>
       <c r="F9" t="n">
-        <v>31859208139</v>
+        <v>31855177757</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>370370261</v>
+        <v>369670324</v>
       </c>
       <c r="I9" t="n">
         <v>0.336428</v>
@@ -1332,10 +1332,10 @@
         <v>0.332966</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00208902</v>
+        <v>0.0020336</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6267200000000001</v>
+        <v>0.63876</v>
       </c>
       <c r="M9" t="n">
         <v>94972937401.45468</v>
@@ -1350,13 +1350,13 @@
         <v>45629.67407407407</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0186113200135701</v>
+        <v>0.01862331833455798</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1419,16 +1419,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1483.83</v>
+        <v>1482.49</v>
       </c>
       <c r="F10" t="n">
-        <v>25160679961</v>
+        <v>25135097323</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>1246400077</v>
+        <v>1174267473</v>
       </c>
       <c r="I10" t="n">
         <v>1597.81</v>
@@ -1437,10 +1437,10 @@
         <v>1449.25</v>
       </c>
       <c r="K10" t="n">
-        <v>-106.6162647415517</v>
+        <v>-109.1756073353763</v>
       </c>
       <c r="L10" t="n">
-        <v>-6.70353</v>
+        <v>-6.84076</v>
       </c>
       <c r="M10" t="n">
         <v>16954918.9155448</v>
@@ -1455,13 +1455,13 @@
         <v>42671.66666666666</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0146202682321958</v>
+        <v>0.01461631982911739</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1527,13 +1527,13 @@
         <v>1.004</v>
       </c>
       <c r="F11" t="n">
-        <v>23304050621</v>
+        <v>23305129622</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>346868158</v>
+        <v>346887269</v>
       </c>
       <c r="I11" t="n">
         <v>1.061</v>
@@ -1560,13 +1560,13 @@
         <v>46292.546875</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R11" t="b">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01351406943182422</v>
+        <v>0.01352516059152669</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
@@ -1580,7 +1580,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1599,16 +1599,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>87.48</v>
+        <v>87.42</v>
       </c>
       <c r="F12" t="n">
-        <v>19463829972</v>
+        <v>19448324061</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>947092964</v>
+        <v>945834851</v>
       </c>
       <c r="I12" t="n">
         <v>92.02</v>
@@ -1617,10 +1617,10 @@
         <v>86.41</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.128673681278386</v>
+        <v>-4.268039658764607</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.50706</v>
+        <v>-4.60868</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1635,13 +1635,13 @@
         <v>46288.22002314815</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R12" t="b">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01122602658796506</v>
+        <v>0.01122545387365589</v>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
@@ -1655,7 +1655,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1674,16 +1674,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.093836</v>
+        <v>0.09386799999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>14648714526</v>
+        <v>14653287577</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>1130717325</v>
+        <v>1169157074</v>
       </c>
       <c r="I13" t="n">
         <v>0.097729</v>
@@ -1692,10 +1692,10 @@
         <v>0.09178600000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.002506339708048783</v>
+        <v>-0.003065646797607444</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.6015</v>
+        <v>-3.10572</v>
       </c>
       <c r="M13" t="n">
         <v>156108476383.7052</v>
@@ -1710,13 +1710,13 @@
         <v>44323.88082175926</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R13" t="b">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.008357131426577676</v>
+        <v>0.008366305949218835</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1779,16 +1779,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>15.43</v>
+        <v>15.45</v>
       </c>
       <c r="F14" t="n">
-        <v>11540186445</v>
+        <v>11559102076</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>1376547983</v>
+        <v>1380617023</v>
       </c>
       <c r="I14" t="n">
         <v>15.44</v>
@@ -1797,10 +1797,10 @@
         <v>13.54</v>
       </c>
       <c r="K14" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="L14" t="n">
-        <v>10.23398</v>
+        <v>10.05567</v>
       </c>
       <c r="M14" t="n">
         <v>748099970.424884</v>
@@ -1815,13 +1815,13 @@
         <v>44325.67635416667</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R14" t="b">
         <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.006505038518187269</v>
+        <v>0.006521328526726429</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1884,16 +1884,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>541.1799999999999</v>
+        <v>540.59</v>
       </c>
       <c r="F15" t="n">
-        <v>10184194565</v>
+        <v>10167764151</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>134844428</v>
+        <v>134744544</v>
       </c>
       <c r="I15" t="n">
         <v>552.95</v>
@@ -1902,10 +1902,10 @@
         <v>526.49</v>
       </c>
       <c r="K15" t="n">
-        <v>-6.981361077774636</v>
+        <v>-7.731023366242312</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.27359</v>
+        <v>-1.42426</v>
       </c>
       <c r="M15" t="n">
         <v>18810763.27902782</v>
@@ -1920,13 +1920,13 @@
         <v>46036.48202546296</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.005697124650484629</v>
+        <v>0.005691712119483614</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1989,16 +1989,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>83.59999999999999</v>
+        <v>83.55</v>
       </c>
       <c r="F16" t="n">
-        <v>9937666187</v>
+        <v>9929723944</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>143486762</v>
+        <v>140390630</v>
       </c>
       <c r="I16" t="n">
         <v>84.67</v>
@@ -2007,10 +2007,10 @@
         <v>82.44</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6211830702093124</v>
+        <v>-0.7241445535054822</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.73752</v>
+        <v>-0.8309800000000001</v>
       </c>
       <c r="M16" t="n">
         <v>118852171</v>
@@ -2025,13 +2025,13 @@
         <v>46286.85358796296</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R16" t="b">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.005550240514741547</v>
+        <v>0.005549775313361782</v>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
@@ -2045,7 +2045,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2064,16 +2064,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0.9993880000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>9787052779</v>
+        <v>9780099329</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>182329149</v>
+        <v>184157283</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
@@ -2082,10 +2082,10 @@
         <v>0.999263</v>
       </c>
       <c r="K17" t="n">
-        <v>0.00050491</v>
+        <v>-0.000242087193309426</v>
       </c>
       <c r="L17" t="n">
-        <v>0.05051</v>
+        <v>0.04688</v>
       </c>
       <c r="M17" t="n">
         <v>9785581101.437241</v>
@@ -2100,13 +2100,13 @@
         <v>45593.90336805556</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.005460503501725542</v>
+        <v>0.005460558284701121</v>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
@@ -2120,7 +2120,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2139,16 +2139,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.246807</v>
+        <v>0.246928</v>
       </c>
       <c r="F18" t="n">
-        <v>9262416295</v>
+        <v>9267950685</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>688332747</v>
+        <v>688844092</v>
       </c>
       <c r="I18" t="n">
         <v>0.257648</v>
@@ -2157,10 +2157,10 @@
         <v>0.239932</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.007398015687884063</v>
+        <v>-0.008754438216891397</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.91026</v>
+        <v>-3.43806</v>
       </c>
       <c r="M18" t="n">
         <v>37535193928.91081</v>
@@ -2175,13 +2175,13 @@
         <v>44440.91678240741</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R18" t="b">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.00514791970444915</v>
+        <v>0.00515517818230108</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2244,16 +2244,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.01249497</v>
+        <v>0.01246908</v>
       </c>
       <c r="F19" t="n">
-        <v>8856846797</v>
+        <v>8843668256</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>22092708</v>
+        <v>24550183</v>
       </c>
       <c r="I19" t="n">
         <v>0.01272728</v>
@@ -2262,10 +2262,10 @@
         <v>0.01243449</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.000240401238128117</v>
+        <v>-0.000276699067652026</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.88767</v>
+        <v>-2.10203</v>
       </c>
       <c r="M19" t="n">
         <v>709245550890.849</v>
@@ -2280,13 +2280,13 @@
         <v>46259.82847222222</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R19" t="b">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.004906277238454887</v>
+        <v>0.004902190279018537</v>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
@@ -2300,7 +2300,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2322,13 +2322,13 @@
         <v>9.01</v>
       </c>
       <c r="F20" t="n">
-        <v>8289654987</v>
+        <v>8291891423</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>513731</v>
+        <v>514783</v>
       </c>
       <c r="I20" t="n">
         <v>9.09</v>
@@ -2337,10 +2337,10 @@
         <v>8.99</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.03364701529956093</v>
+        <v>-0.02435654173043034</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.37197</v>
+        <v>-0.26776</v>
       </c>
       <c r="M20" t="n">
         <v>919857851.9</v>
@@ -2355,13 +2355,13 @@
         <v>46146.39930555555</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.004568338541545904</v>
+        <v>0.004573180981156352</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2424,16 +2424,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.231162</v>
+        <v>0.231172</v>
       </c>
       <c r="F21" t="n">
-        <v>8084763830</v>
+        <v>8093216704</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>804882888</v>
+        <v>807501121</v>
       </c>
       <c r="I21" t="n">
         <v>0.234286</v>
@@ -2442,10 +2442,10 @@
         <v>0.207092</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0158957</v>
+        <v>0.01511079</v>
       </c>
       <c r="L21" t="n">
-        <v>7.3842</v>
+        <v>7.12082</v>
       </c>
       <c r="M21" t="n">
         <v>35011603519.11985</v>
@@ -2460,13 +2460,13 @@
         <v>43102.66666666666</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R21" t="b">
         <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>0.004446262289061311</v>
+        <v>0.004454716729140253</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2532,13 +2532,13 @@
         <v>4.81</v>
       </c>
       <c r="F22" t="n">
-        <v>6298371842</v>
+        <v>6288156938</v>
       </c>
       <c r="G22" t="n">
         <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>1394025532</v>
+        <v>1391815200</v>
       </c>
       <c r="I22" t="n">
         <v>5.41</v>
@@ -2547,10 +2547,10 @@
         <v>4.68</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5640137186954686</v>
+        <v>-0.5524592487800861</v>
       </c>
       <c r="L22" t="n">
-        <v>-10.48548</v>
+        <v>-10.19063</v>
       </c>
       <c r="M22" t="n">
         <v>1307555791</v>
@@ -2565,13 +2565,13 @@
         <v>44577.59010416667</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R22" t="b">
         <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0.003381911623290297</v>
+        <v>0.003378409405793571</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2634,16 +2634,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>310.23</v>
+        <v>310.25</v>
       </c>
       <c r="F23" t="n">
-        <v>6233927496</v>
+        <v>6234765915</v>
       </c>
       <c r="G23" t="n">
         <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>319655074</v>
+        <v>319374656</v>
       </c>
       <c r="I23" t="n">
         <v>333.53</v>
@@ -2652,10 +2652,10 @@
         <v>305.68</v>
       </c>
       <c r="K23" t="n">
-        <v>-21.90225423208983</v>
+        <v>-22.80743476250382</v>
       </c>
       <c r="L23" t="n">
-        <v>-6.59451</v>
+        <v>-6.83202</v>
       </c>
       <c r="M23" t="n">
         <v>20095728.02165077</v>
@@ -2670,13 +2670,13 @@
         <v>43088.66666666666</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R23" t="b">
         <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>0.003343515021071391</v>
+        <v>0.003346573812236903</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2739,16 +2739,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>8.800000000000001</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>5458427163</v>
+        <v>5453702214</v>
       </c>
       <c r="G24" t="n">
         <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>1054591594</v>
+        <v>1053902012</v>
       </c>
       <c r="I24" t="n">
         <v>9.75</v>
@@ -2757,10 +2757,10 @@
         <v>8.619999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.8418264650542291</v>
+        <v>-0.8819458893726182</v>
       </c>
       <c r="L24" t="n">
-        <v>-8.731439999999999</v>
+        <v>-9.08259</v>
       </c>
       <c r="M24" t="n">
         <v>620402422.6104751</v>
@@ -2775,13 +2775,13 @@
         <v>44318.89240740741</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R24" t="b">
         <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>0.002881463969970174</v>
+        <v>0.002880847082728399</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2844,16 +2844,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>69.17</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>5373060690</v>
+        <v>5375881728</v>
       </c>
       <c r="G25" t="n">
         <v>24</v>
       </c>
       <c r="H25" t="n">
-        <v>623930559</v>
+        <v>624869305</v>
       </c>
       <c r="I25" t="n">
         <v>72.37</v>
@@ -2862,10 +2862,10 @@
         <v>68.67</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.943114471304327</v>
+        <v>-2.091962717714054</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.73237</v>
+        <v>-2.86092</v>
       </c>
       <c r="M25" t="n">
         <v>77658035.78231663</v>
@@ -2880,13 +2880,13 @@
         <v>44325.80077546297</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.002830601749929769</v>
+        <v>0.002834444874576696</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2949,16 +2949,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.121547</v>
+        <v>0.121675</v>
       </c>
       <c r="F26" t="n">
-        <v>5327080739</v>
+        <v>5332618809</v>
       </c>
       <c r="G26" t="n">
         <v>25</v>
       </c>
       <c r="H26" t="n">
-        <v>1425715601</v>
+        <v>1504736922</v>
       </c>
       <c r="I26" t="n">
         <v>0.13063</v>
@@ -2967,10 +2967,10 @@
         <v>0.09417200000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.025786</v>
+        <v>0.02572026</v>
       </c>
       <c r="L26" t="n">
-        <v>26.92754</v>
+        <v>26.78407</v>
       </c>
       <c r="M26" t="n">
         <v>43831706398.00587</v>
@@ -2985,13 +2985,13 @@
         <v>44454.11143518519</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R26" t="b">
         <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>0.002803206423602897</v>
+        <v>0.002808648389924977</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3054,16 +3054,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.130293</v>
+        <v>0.130599</v>
       </c>
       <c r="F27" t="n">
-        <v>5175449953</v>
+        <v>5186854556</v>
       </c>
       <c r="G27" t="n">
         <v>26</v>
       </c>
       <c r="H27" t="n">
-        <v>44678786</v>
+        <v>49511163</v>
       </c>
       <c r="I27" t="n">
         <v>0.146469</v>
@@ -3072,10 +3072,10 @@
         <v>0.126784</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.005405086768866557</v>
+        <v>-0.00562873057806304</v>
       </c>
       <c r="L27" t="n">
-        <v>-3.98318</v>
+        <v>-4.15985</v>
       </c>
       <c r="M27" t="n">
         <v>39715601982.75846</v>
@@ -3090,13 +3090,13 @@
         <v>46056.00148148148</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R27" t="b">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.002712863246341356</v>
+        <v>0.002721733188588614</v>
       </c>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
@@ -3110,7 +3110,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3129,16 +3129,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>10.59</v>
+        <v>10.58</v>
       </c>
       <c r="F28" t="n">
-        <v>4974459949</v>
+        <v>4970915308</v>
       </c>
       <c r="G28" t="n">
         <v>27</v>
       </c>
       <c r="H28" t="n">
-        <v>632595575</v>
+        <v>632241115</v>
       </c>
       <c r="I28" t="n">
         <v>10.97</v>
@@ -3147,10 +3147,10 @@
         <v>10.15</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.2666317242894269</v>
+        <v>-0.3376764675811188</v>
       </c>
       <c r="L28" t="n">
-        <v>-2.45624</v>
+        <v>-2.93974</v>
       </c>
       <c r="M28" t="n">
         <v>469757793.2209306</v>
@@ -3165,13 +3165,13 @@
         <v>44521.26314814815</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R28" t="b">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.002593111340820204</v>
+        <v>0.002592974574387484</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3234,16 +3234,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.999656</v>
+        <v>0.999611</v>
       </c>
       <c r="F29" t="n">
-        <v>4902930682</v>
+        <v>4902804026</v>
       </c>
       <c r="G29" t="n">
         <v>28</v>
       </c>
       <c r="H29" t="n">
-        <v>38369354</v>
+        <v>38262359</v>
       </c>
       <c r="I29" t="n">
         <v>0.999934</v>
@@ -3252,10 +3252,10 @@
         <v>0.999574</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.000115381751319976</v>
+        <v>-0.00018926019552612</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.01154</v>
+        <v>-0.01496</v>
       </c>
       <c r="M29" t="n">
         <v>4904709277.703256</v>
@@ -3270,13 +3270,13 @@
         <v>46000.38208333333</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R29" t="b">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.002550493470014145</v>
+        <v>0.002552361696631318</v>
       </c>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
@@ -3290,7 +3290,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3312,13 +3312,13 @@
         <v>1.16</v>
       </c>
       <c r="F30" t="n">
-        <v>4769737147</v>
+        <v>4772225187</v>
       </c>
       <c r="G30" t="n">
         <v>29</v>
       </c>
       <c r="H30" t="n">
-        <v>1566711905</v>
+        <v>1564352652</v>
       </c>
       <c r="I30" t="n">
         <v>1.29</v>
@@ -3327,10 +3327,10 @@
         <v>1.14</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.09491413056535136</v>
+        <v>-0.1093248864460741</v>
       </c>
       <c r="L30" t="n">
-        <v>-7.53669</v>
+        <v>-8.51948</v>
       </c>
       <c r="M30" t="n">
         <v>4096537146.540959</v>
@@ -3345,13 +3345,13 @@
         <v>45661.62243055556</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R30" t="b">
         <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>0.002471135395971079</v>
+        <v>0.002474501138583841</v>
       </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
@@ -3365,7 +3365,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3387,13 +3387,13 @@
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>4604389852</v>
+        <v>4603721775</v>
       </c>
       <c r="G31" t="n">
         <v>30</v>
       </c>
       <c r="H31" t="n">
-        <v>250973333</v>
+        <v>250957765</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
@@ -3402,16 +3402,16 @@
         <v>0.999637</v>
       </c>
       <c r="K31" t="n">
-        <v>0.00024019</v>
+        <v>0.00023832</v>
       </c>
       <c r="L31" t="n">
-        <v>0.02402</v>
+        <v>0.02834</v>
       </c>
       <c r="M31" t="n">
         <v>4603186689.020486</v>
       </c>
       <c r="N31" t="n">
-        <v>4603186689.020486</v>
+        <v>4662323535.788444</v>
       </c>
       <c r="O31" t="n">
         <v>1.22</v>
@@ -3420,13 +3420,13 @@
         <v>43902.79363425926</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R31" t="b">
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0.002372619781985529</v>
+        <v>0.002374027204279495</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3492,13 +3492,13 @@
         <v>1.57</v>
       </c>
       <c r="F32" t="n">
-        <v>4422703171</v>
+        <v>4421697849</v>
       </c>
       <c r="G32" t="n">
         <v>31</v>
       </c>
       <c r="H32" t="n">
-        <v>136193316</v>
+        <v>135951517</v>
       </c>
       <c r="I32" t="n">
         <v>1.72</v>
@@ -3507,10 +3507,10 @@
         <v>1.56</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.05930901304330449</v>
+        <v>-0.05791636793099908</v>
       </c>
       <c r="L32" t="n">
-        <v>-3.63858</v>
+        <v>-3.51437</v>
       </c>
       <c r="M32" t="n">
         <v>2815376675.777718</v>
@@ -3525,13 +3525,13 @@
         <v>45457.69225694444</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R32" t="b">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.002264368994261958</v>
+        <v>0.0022654913606092</v>
       </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
@@ -3545,7 +3545,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3564,16 +3564,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.999463</v>
+        <v>0.99943</v>
       </c>
       <c r="F33" t="n">
-        <v>4416147310</v>
+        <v>4415979237</v>
       </c>
       <c r="G33" t="n">
         <v>32</v>
       </c>
       <c r="H33" t="n">
-        <v>1101714230</v>
+        <v>1100248355</v>
       </c>
       <c r="I33" t="n">
         <v>0.999614</v>
@@ -3582,10 +3582,10 @@
         <v>0.9992760000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>3.417e-05</v>
+        <v>-2.6369358830269e-05</v>
       </c>
       <c r="L33" t="n">
-        <v>0.00342</v>
+        <v>-0.00066</v>
       </c>
       <c r="M33" t="n">
         <v>4418501462.568161</v>
@@ -3600,13 +3600,13 @@
         <v>46212.42696759259</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R33" t="b">
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.002260462945048278</v>
+        <v>0.002262081510092939</v>
       </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
@@ -3620,7 +3620,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3639,16 +3639,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>306.81</v>
+        <v>307.07</v>
       </c>
       <c r="F34" t="n">
-        <v>3478509724</v>
+        <v>3481552392</v>
       </c>
       <c r="G34" t="n">
         <v>33</v>
       </c>
       <c r="H34" t="n">
-        <v>357229159</v>
+        <v>357267906</v>
       </c>
       <c r="I34" t="n">
         <v>322.51</v>
@@ -3657,10 +3657,10 @@
         <v>294.98</v>
       </c>
       <c r="K34" t="n">
-        <v>-12.62353650183701</v>
+        <v>-12.95459664751877</v>
       </c>
       <c r="L34" t="n">
-        <v>-3.95187</v>
+        <v>-4.00743</v>
       </c>
       <c r="M34" t="n">
         <v>11339645.9251</v>
@@ -3675,13 +3675,13 @@
         <v>45358.44833333333</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R34" t="b">
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0.00170180885590386</v>
+        <v>0.001704908570255092</v>
       </c>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
@@ -3695,7 +3695,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3714,16 +3714,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.069746</v>
+        <v>0.069276</v>
       </c>
       <c r="F35" t="n">
-        <v>3471504430</v>
+        <v>3446526996</v>
       </c>
       <c r="G35" t="n">
         <v>34</v>
       </c>
       <c r="H35" t="n">
-        <v>27317850</v>
+        <v>26946295</v>
       </c>
       <c r="I35" t="n">
         <v>0.07027700000000001</v>
@@ -3732,10 +3732,10 @@
         <v>0.063356</v>
       </c>
       <c r="K35" t="n">
-        <v>0.0032569</v>
+        <v>0.00250399</v>
       </c>
       <c r="L35" t="n">
-        <v>4.89839</v>
+        <v>3.77278</v>
       </c>
       <c r="M35" t="n">
         <v>49749850607.73766</v>
@@ -3750,13 +3750,13 @@
         <v>44523.66666666666</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R35" t="b">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.001697635029899877</v>
+        <v>0.001684023893233313</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3800,77 +3800,77 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>quant-network</t>
+          <t>shiba-inu</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>qnt</t>
+          <t>shib</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Shiba Inu</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>233.52</v>
+        <v>5.67e-06</v>
       </c>
       <c r="F36" t="n">
-        <v>3404008537</v>
+        <v>3342254447</v>
       </c>
       <c r="G36" t="n">
         <v>35</v>
       </c>
       <c r="H36" t="n">
-        <v>1187422261</v>
+        <v>106657770</v>
       </c>
       <c r="I36" t="n">
-        <v>318.36</v>
+        <v>5.97e-06</v>
       </c>
       <c r="J36" t="n">
-        <v>196.87</v>
+        <v>5.57e-06</v>
       </c>
       <c r="K36" t="n">
-        <v>-59.4741723556501</v>
+        <v>-2.50118412735e-07</v>
       </c>
       <c r="L36" t="n">
-        <v>-20.29896</v>
+        <v>-4.21184</v>
       </c>
       <c r="M36" t="n">
-        <v>14544176.16408117</v>
+        <v>589238950007622.8</v>
       </c>
       <c r="N36" t="n">
-        <v>14612493</v>
+        <v>589496065678280.8</v>
       </c>
       <c r="O36" t="n">
-        <v>427.42</v>
+        <v>8.616e-05</v>
       </c>
       <c r="P36" s="1" t="n">
-        <v>44450.05208333334</v>
+        <v>44496.82980324074</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.001657420284684977</v>
+        <v>0.001621849049925258</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>Interoperabilidad</t>
+          <t>Meme coin</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>Infraestructura empresarial</t>
+          <t>Ecosistema DeFi</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3879,16 +3879,16 @@
         </is>
       </c>
       <c r="W36" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>quant.network</t>
+          <t>shibatoken.com</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>Interoperabilidad entre redes empresariales</t>
+          <t>Ecosistema meme y DeFi comunitario</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -3898,194 +3898,194 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>Su tecnología Overledger busca conectar múltiples blockchains y redes existentes.</t>
+          <t>Token meme inspirado en Dogecoin, con ecosistema DeFi propio (ShibaSwap).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>shiba-inu</t>
+          <t>tether-gold</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>shib</t>
+          <t>xaut</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Shiba Inu</t>
+          <t>Tether Gold</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5.67e-06</v>
+        <v>4127.25</v>
       </c>
       <c r="F37" t="n">
-        <v>3342061176</v>
+        <v>3338894877</v>
       </c>
       <c r="G37" t="n">
         <v>36</v>
       </c>
       <c r="H37" t="n">
-        <v>106938634</v>
+        <v>383054420</v>
       </c>
       <c r="I37" t="n">
-        <v>5.97e-06</v>
+        <v>4260.39</v>
       </c>
       <c r="J37" t="n">
-        <v>5.57e-06</v>
+        <v>4117.57</v>
       </c>
       <c r="K37" t="n">
-        <v>-2.20313350693e-07</v>
+        <v>-136.2677125750724</v>
       </c>
       <c r="L37" t="n">
-        <v>-3.73928</v>
+        <v>-3.20662</v>
       </c>
       <c r="M37" t="n">
-        <v>589238950007622.8</v>
+        <v>808994.63</v>
       </c>
       <c r="N37" t="n">
-        <v>589496065678280.8</v>
+        <v>827417.63</v>
       </c>
       <c r="O37" t="n">
-        <v>8.616e-05</v>
+        <v>5504.62</v>
       </c>
       <c r="P37" s="1" t="n">
-        <v>44496.82980324074</v>
+        <v>46050.66666666666</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R37" t="b">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.001620511411735471</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Meme coin</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Ecosistema DeFi</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>N/A (token ERC-20)</t>
-        </is>
-      </c>
-      <c r="W37" t="n">
-        <v>2020</v>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>shibatoken.com</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>Ecosistema meme y DeFi comunitario</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>Token ERC-20 sobre Ethereum</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>Token meme inspirado en Dogecoin, con ecosistema DeFi propio (ShibaSwap).</t>
-        </is>
-      </c>
+        <v>0.001619845831049958</v>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>tether-gold</t>
+          <t>quant-network</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>xaut</t>
+          <t>qnt</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tether Gold</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4130.18</v>
+        <v>227.3</v>
       </c>
       <c r="F38" t="n">
-        <v>3341742939</v>
+        <v>3312781707</v>
       </c>
       <c r="G38" t="n">
         <v>37</v>
       </c>
       <c r="H38" t="n">
-        <v>382493388</v>
+        <v>1150676888</v>
       </c>
       <c r="I38" t="n">
-        <v>4260.39</v>
+        <v>318.36</v>
       </c>
       <c r="J38" t="n">
-        <v>4117.57</v>
+        <v>196.87</v>
       </c>
       <c r="K38" t="n">
-        <v>-129.6709194783843</v>
+        <v>-60.20917846949141</v>
       </c>
       <c r="L38" t="n">
-        <v>-3.04402</v>
+        <v>-20.29268</v>
       </c>
       <c r="M38" t="n">
-        <v>808994.63</v>
+        <v>14544176.16408117</v>
       </c>
       <c r="N38" t="n">
-        <v>827417.63</v>
+        <v>14612493</v>
       </c>
       <c r="O38" t="n">
-        <v>5504.62</v>
+        <v>427.42</v>
       </c>
       <c r="P38" s="1" t="n">
-        <v>46050.66666666666</v>
+        <v>44450.05208333334</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>0.001620321802867374</v>
-      </c>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr"/>
+        <v>0.001604275268436909</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Infraestructura empresarial</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>N/A (token ERC-20)</t>
+        </is>
+      </c>
+      <c r="W38" t="n">
+        <v>2018</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>quant.network</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>Interoperabilidad entre redes empresariales</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>Token ERC-20 sobre Ethereum</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>Su tecnología Overledger busca conectar múltiples blockchains y redes existentes.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4107,13 +4107,13 @@
         <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>3245641532</v>
+        <v>3245410404</v>
       </c>
       <c r="G39" t="n">
         <v>38</v>
       </c>
       <c r="H39" t="n">
-        <v>952102462</v>
+        <v>955537659</v>
       </c>
       <c r="I39" t="n">
         <v>1</v>
@@ -4122,10 +4122,10 @@
         <v>0.999722</v>
       </c>
       <c r="K39" t="n">
-        <v>0.00018089</v>
+        <v>0.00011095</v>
       </c>
       <c r="L39" t="n">
-        <v>0.01809</v>
+        <v>0.0167</v>
       </c>
       <c r="M39" t="n">
         <v>3245296082.805759</v>
@@ -4140,13 +4140,13 @@
         <v>45686.67436342593</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001563063599063797</v>
+        <v>0.001564103619736881</v>
       </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
@@ -4160,7 +4160,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4179,16 +4179,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="F40" t="n">
-        <v>3032135937</v>
+        <v>2997473961</v>
       </c>
       <c r="G40" t="n">
         <v>39</v>
       </c>
       <c r="H40" t="n">
-        <v>48416090</v>
+        <v>48014550</v>
       </c>
       <c r="I40" t="n">
         <v>1.43</v>
@@ -4197,10 +4197,10 @@
         <v>0.8876540000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.09268075734569159</v>
+        <v>-0.1072927496617395</v>
       </c>
       <c r="L40" t="n">
-        <v>-7.63968</v>
+        <v>-9.07586</v>
       </c>
       <c r="M40" t="n">
         <v>2708142280.000001</v>
@@ -4215,13 +4215,13 @@
         <v>46293.32349537037</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R40" t="b">
         <v>1</v>
       </c>
       <c r="S40" t="n">
-        <v>0.001435854776078364</v>
+        <v>0.001416265961199525</v>
       </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
@@ -4235,7 +4235,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4254,16 +4254,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>0.999715</v>
       </c>
       <c r="F41" t="n">
-        <v>2713619511</v>
+        <v>2712563633</v>
       </c>
       <c r="G41" t="n">
         <v>40</v>
       </c>
       <c r="H41" t="n">
-        <v>76340355</v>
+        <v>76650996</v>
       </c>
       <c r="I41" t="n">
         <v>1</v>
@@ -4272,10 +4272,10 @@
         <v>0.999622</v>
       </c>
       <c r="K41" t="n">
-        <v>0.00031337</v>
+        <v>-0.000121532847613515</v>
       </c>
       <c r="L41" t="n">
-        <v>0.03134</v>
+        <v>0.03266</v>
       </c>
       <c r="M41" t="n">
         <v>2713243486.123999</v>
@@ -4290,13 +4290,13 @@
         <v>45222.61454861111</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R41" t="b">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.001246079423104657</v>
+        <v>0.001246381795423096</v>
       </c>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
@@ -4310,7 +4310,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4332,13 +4332,13 @@
         <v>1.15</v>
       </c>
       <c r="F42" t="n">
-        <v>2625571250</v>
+        <v>2619916353</v>
       </c>
       <c r="G42" t="n">
         <v>41</v>
       </c>
       <c r="H42" t="n">
-        <v>980609</v>
+        <v>1027991</v>
       </c>
       <c r="I42" t="n">
         <v>1.19</v>
@@ -4347,10 +4347,10 @@
         <v>1.14</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.00887619437693199</v>
+        <v>-0.01622350712485643</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.76502</v>
+        <v>-1.22585</v>
       </c>
       <c r="M42" t="n">
         <v>2279845200.804474</v>
@@ -4365,13 +4365,13 @@
         <v>46205.17638888889</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R42" t="b">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.001193619366272309</v>
+        <v>0.001191138779191494</v>
       </c>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
@@ -4385,7 +4385,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4404,16 +4404,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.255935</v>
+        <v>0.256119</v>
       </c>
       <c r="F43" t="n">
-        <v>2584980367</v>
+        <v>2585716604</v>
       </c>
       <c r="G43" t="n">
         <v>42</v>
       </c>
       <c r="H43" t="n">
-        <v>578101430</v>
+        <v>553085185</v>
       </c>
       <c r="I43" t="n">
         <v>0.276244</v>
@@ -4422,10 +4422,10 @@
         <v>0.252859</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.01390925014699845</v>
+        <v>-0.01588835017343232</v>
       </c>
       <c r="L43" t="n">
-        <v>-5.15455</v>
+        <v>-5.87612</v>
       </c>
       <c r="M43" t="n">
         <v>10095312500</v>
@@ -4440,13 +4440,13 @@
         <v>45393.21892361111</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R43" t="b">
         <v>1</v>
       </c>
       <c r="S43" t="n">
-        <v>0.00116943490192434</v>
+        <v>0.00117074641269003</v>
       </c>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
@@ -4460,7 +4460,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4482,13 +4482,13 @@
         <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>2518062817</v>
+        <v>2517816513</v>
       </c>
       <c r="G44" t="n">
         <v>43</v>
       </c>
       <c r="H44" t="n">
-        <v>289618947</v>
+        <v>289856622</v>
       </c>
       <c r="I44" t="n">
         <v>1</v>
@@ -4497,10 +4497,10 @@
         <v>0.999804</v>
       </c>
       <c r="K44" t="n">
-        <v>2.755e-05</v>
+        <v>-5.6413705191716e-05</v>
       </c>
       <c r="L44" t="n">
-        <v>0.00276</v>
+        <v>0.00237</v>
       </c>
       <c r="M44" t="n">
         <v>2517692589.017203</v>
@@ -4515,13 +4515,13 @@
         <v>45652.11518518518</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R44" t="b">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.001129564739399706</v>
+        <v>0.001130259462298823</v>
       </c>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
@@ -4535,7 +4535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4554,16 +4554,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.516524</v>
+        <v>0.516871</v>
       </c>
       <c r="F45" t="n">
-        <v>2513007633</v>
+        <v>2516746669</v>
       </c>
       <c r="G45" t="n">
         <v>44</v>
       </c>
       <c r="H45" t="n">
-        <v>735237064</v>
+        <v>725129571</v>
       </c>
       <c r="I45" t="n">
         <v>0.606332</v>
@@ -4572,10 +4572,10 @@
         <v>0.507278</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.06008141897191299</v>
+        <v>-0.06680772998476125</v>
       </c>
       <c r="L45" t="n">
-        <v>-10.41985</v>
+        <v>-11.38418</v>
       </c>
       <c r="M45" t="n">
         <v>4869330647</v>
@@ -4590,13 +4590,13 @@
         <v>45641.69166666667</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R45" t="b">
         <v>1</v>
       </c>
       <c r="S45" t="n">
-        <v>0.001126552808931959</v>
+        <v>0.001129621543846632</v>
       </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
@@ -4610,7 +4610,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4629,16 +4629,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>118.92</v>
+        <v>118.85</v>
       </c>
       <c r="F46" t="n">
-        <v>2497437538</v>
+        <v>2495755168</v>
       </c>
       <c r="G46" t="n">
         <v>45</v>
       </c>
       <c r="H46" t="n">
-        <v>30711223</v>
+        <v>31160687</v>
       </c>
       <c r="I46" t="n">
         <v>121.52</v>
@@ -4647,10 +4647,10 @@
         <v>116.19</v>
       </c>
       <c r="K46" t="n">
-        <v>-2.007908685297622</v>
+        <v>-2.208398032957192</v>
       </c>
       <c r="L46" t="n">
-        <v>-1.66044</v>
+        <v>-1.81271</v>
       </c>
       <c r="M46" t="n">
         <v>21000000</v>
@@ -4665,13 +4665,13 @@
         <v>45934.66666666666</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R46" t="b">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.001117275986660762</v>
+        <v>0.001117104891113074</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4770,13 +4770,13 @@
         <v>46293.53819444445</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R47" t="b">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0.001062482150592827</v>
+        <v>0.001063271704331328</v>
       </c>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
@@ -4790,7 +4790,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4809,16 +4809,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>149.08</v>
+        <v>149.07</v>
       </c>
       <c r="F48" t="n">
-        <v>2300108110</v>
+        <v>2300549883</v>
       </c>
       <c r="G48" t="n">
         <v>47</v>
       </c>
       <c r="H48" t="n">
-        <v>305771857</v>
+        <v>306146543</v>
       </c>
       <c r="I48" t="n">
         <v>156.09</v>
@@ -4827,10 +4827,10 @@
         <v>144.24</v>
       </c>
       <c r="K48" t="n">
-        <v>-5.567608393971454</v>
+        <v>-6.222793981795434</v>
       </c>
       <c r="L48" t="n">
-        <v>-3.60016</v>
+        <v>-3.95236</v>
       </c>
       <c r="M48" t="n">
         <v>15429846.8408245</v>
@@ -4845,13 +4845,13 @@
         <v>44334.55554398148</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R48" t="b">
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0.000999705089859352</v>
+        <v>0.001000709366843505</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4914,16 +4914,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.00491688</v>
+        <v>0.00490913</v>
       </c>
       <c r="F49" t="n">
-        <v>2290748183</v>
+        <v>2286012913</v>
       </c>
       <c r="G49" t="n">
         <v>48</v>
       </c>
       <c r="H49" t="n">
-        <v>519720465</v>
+        <v>516355401</v>
       </c>
       <c r="I49" t="n">
         <v>0.00553383</v>
@@ -4932,10 +4932,10 @@
         <v>0.00475129</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.000190855359834726</v>
+        <v>-0.000239669080910867</v>
       </c>
       <c r="L49" t="n">
-        <v>-3.7366</v>
+        <v>-4.68013</v>
       </c>
       <c r="M49" t="n">
         <v>465601390833.6057</v>
@@ -4950,13 +4950,13 @@
         <v>45914.36296296296</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R49" t="b">
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>0.0009941283493673776</v>
+        <v>0.000992041372816391</v>
       </c>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
@@ -4970,7 +4970,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4992,13 +4992,13 @@
         <v>1.15</v>
       </c>
       <c r="F50" t="n">
-        <v>2277727629</v>
+        <v>2275776542</v>
       </c>
       <c r="G50" t="n">
         <v>49</v>
       </c>
       <c r="H50" t="n">
-        <v>6606951</v>
+        <v>3044903</v>
       </c>
       <c r="I50" t="n">
         <v>1.15</v>
@@ -5007,10 +5007,10 @@
         <v>1.14</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.001272510992295972</v>
+        <v>0.00010856</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.11085</v>
+        <v>-0.04188</v>
       </c>
       <c r="M50" t="n">
         <v>1984710539.255756</v>
@@ -5025,13 +5025,13 @@
         <v>45377.89175925926</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R50" t="b">
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0.0009863705697693381</v>
+        <v>0.0009859377072872389</v>
       </c>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
@@ -5045,7 +5045,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5100,13 +5100,13 @@
         <v>45699.87511574074</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R51" t="b">
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0.000977314485664627</v>
+        <v>0.0009780379780520495</v>
       </c>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
@@ -5120,7 +5120,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5139,16 +5139,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.664998</v>
+        <v>0.665032</v>
       </c>
       <c r="F52" t="n">
-        <v>2195882880</v>
+        <v>2196082731</v>
       </c>
       <c r="G52" t="n">
         <v>51</v>
       </c>
       <c r="H52" t="n">
-        <v>49538783</v>
+        <v>48639598</v>
       </c>
       <c r="I52" t="n">
         <v>0.678633</v>
@@ -5157,10 +5157,10 @@
         <v>0.645253</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.01170561711242624</v>
+        <v>-0.01238964705970558</v>
       </c>
       <c r="L52" t="n">
-        <v>-1.7298</v>
+        <v>-1.83291</v>
       </c>
       <c r="M52" t="n">
         <v>3302294382.53684</v>
@@ -5175,13 +5175,13 @@
         <v>45938.71164351852</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R52" t="b">
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0.0009376066290031576</v>
+        <v>0.0009384184871371032</v>
       </c>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
@@ -5195,7 +5195,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5217,13 +5217,13 @@
         <v>1.18</v>
       </c>
       <c r="F53" t="n">
-        <v>2010967813</v>
+        <v>2010185904</v>
       </c>
       <c r="G53" t="n">
         <v>52</v>
       </c>
       <c r="H53" t="n">
-        <v>238420983</v>
+        <v>225807110</v>
       </c>
       <c r="I53" t="n">
         <v>1.28</v>
@@ -5232,10 +5232,10 @@
         <v>1.15</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.08159105673549938</v>
+        <v>-0.08832864860613676</v>
       </c>
       <c r="L53" t="n">
-        <v>-6.46856</v>
+        <v>-6.88955</v>
       </c>
       <c r="M53" t="n">
         <v>1704933188.986922</v>
@@ -5250,13 +5250,13 @@
         <v>44504.25704861111</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R53" t="b">
         <v>1</v>
       </c>
       <c r="S53" t="n">
-        <v>0.000827432335793922</v>
+        <v>0.0008275733394828558</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5319,16 +5319,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.705874</v>
+        <v>0.706355</v>
       </c>
       <c r="F54" t="n">
-        <v>1913221851</v>
+        <v>1914549918</v>
       </c>
       <c r="G54" t="n">
         <v>53</v>
       </c>
       <c r="H54" t="n">
-        <v>148290397</v>
+        <v>148433776</v>
       </c>
       <c r="I54" t="n">
         <v>0.728537</v>
@@ -5337,10 +5337,10 @@
         <v>0.691268</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.01531979021963337</v>
+        <v>-0.01785122403266393</v>
       </c>
       <c r="L54" t="n">
-        <v>-2.12423</v>
+        <v>-2.41428</v>
       </c>
       <c r="M54" t="n">
         <v>2710487455.649731</v>
@@ -5355,13 +5355,13 @@
         <v>45924.13766203704</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R54" t="b">
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>0.0007691942892565524</v>
+        <v>0.0007705482403442377</v>
       </c>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
@@ -5375,7 +5375,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5394,16 +5394,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.489236</v>
+        <v>0.488795</v>
       </c>
       <c r="F55" t="n">
-        <v>1880285323</v>
+        <v>1877993895</v>
       </c>
       <c r="G55" t="n">
         <v>54</v>
       </c>
       <c r="H55" t="n">
-        <v>576858965</v>
+        <v>566474504</v>
       </c>
       <c r="I55" t="n">
         <v>0.550406</v>
@@ -5412,10 +5412,10 @@
         <v>0.479236</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.05424942963407592</v>
+        <v>-0.05741718969657156</v>
       </c>
       <c r="L55" t="n">
-        <v>-9.98176</v>
+        <v>-10.48643</v>
       </c>
       <c r="M55" t="n">
         <v>3842804411.877398</v>
@@ -5430,13 +5430,13 @@
         <v>45360.67409722223</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R55" t="b">
         <v>1</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0007495703681124403</v>
+        <v>0.0007487508926838224</v>
       </c>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
@@ -5450,7 +5450,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5469,16 +5469,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.07874100000000001</v>
+        <v>0.078726</v>
       </c>
       <c r="F56" t="n">
-        <v>1844658418</v>
+        <v>1844880074</v>
       </c>
       <c r="G56" t="n">
         <v>55</v>
       </c>
       <c r="H56" t="n">
-        <v>45824177</v>
+        <v>45897654</v>
       </c>
       <c r="I56" t="n">
         <v>0.086122</v>
@@ -5487,10 +5487,10 @@
         <v>0.076969</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.002860198225835303</v>
+        <v>-0.003361912272600215</v>
       </c>
       <c r="L56" t="n">
-        <v>-3.50511</v>
+        <v>-3.89053</v>
       </c>
       <c r="M56" t="n">
         <v>23427301924.81371</v>
@@ -5505,13 +5505,13 @@
         <v>45630.09302083333</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R56" t="b">
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0.0007283434927621067</v>
+        <v>0.0007290060350798714</v>
       </c>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
@@ -5525,7 +5525,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5544,16 +5544,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.05706</v>
+        <v>0.056965</v>
       </c>
       <c r="F57" t="n">
-        <v>1812807338</v>
+        <v>1810013629</v>
       </c>
       <c r="G57" t="n">
         <v>56</v>
       </c>
       <c r="H57" t="n">
-        <v>41472649</v>
+        <v>41819062</v>
       </c>
       <c r="I57" t="n">
         <v>0.058699</v>
@@ -5562,10 +5562,10 @@
         <v>0.055922</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.001561998729134401</v>
+        <v>-0.001663881070877254</v>
       </c>
       <c r="L57" t="n">
-        <v>-2.66453</v>
+        <v>-2.80263</v>
       </c>
       <c r="M57" t="n">
         <v>31778337976</v>
@@ -5580,13 +5580,13 @@
         <v>45901.18065972222</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R57" t="b">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0.0007093662926675854</v>
+        <v>0.000708216136152744</v>
       </c>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
@@ -5600,7 +5600,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5619,16 +5619,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4136.85</v>
+        <v>4133.98</v>
       </c>
       <c r="F58" t="n">
-        <v>1799291089</v>
+        <v>1797843599</v>
       </c>
       <c r="G58" t="n">
         <v>57</v>
       </c>
       <c r="H58" t="n">
-        <v>226703873</v>
+        <v>224373774</v>
       </c>
       <c r="I58" t="n">
         <v>4257.32</v>
@@ -5637,10 +5637,10 @@
         <v>4122.98</v>
       </c>
       <c r="K58" t="n">
-        <v>-120.5855415487467</v>
+        <v>-125.7795618399823</v>
       </c>
       <c r="L58" t="n">
-        <v>-2.83235</v>
+        <v>-2.95804</v>
       </c>
       <c r="M58" t="n">
         <v>434898.623539</v>
@@ -5655,13 +5655,13 @@
         <v>46050.93814814815</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R58" t="b">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0007013131729052296</v>
+        <v>0.0007009594831260271</v>
       </c>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
@@ -5675,7 +5675,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5697,13 +5697,13 @@
         <v>2.53</v>
       </c>
       <c r="F59" t="n">
-        <v>1770954366</v>
+        <v>1769047150</v>
       </c>
       <c r="G59" t="n">
         <v>58</v>
       </c>
       <c r="H59" t="n">
-        <v>37287589</v>
+        <v>37244026</v>
       </c>
       <c r="I59" t="n">
         <v>2.74</v>
@@ -5712,10 +5712,10 @@
         <v>2.48</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.1731332388288185</v>
+        <v>-0.1890342586627334</v>
       </c>
       <c r="L59" t="n">
-        <v>-6.40201</v>
+        <v>-6.91827</v>
       </c>
       <c r="M59" t="n">
         <v>699626678.4133558</v>
@@ -5730,13 +5730,13 @@
         <v>45674.19883101852</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R59" t="b">
         <v>1</v>
       </c>
       <c r="S59" t="n">
-        <v>0.0006844298627507851</v>
+        <v>0.0006837889552970448</v>
       </c>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
@@ -5750,7 +5750,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5772,13 +5772,13 @@
         <v>4.2e-06</v>
       </c>
       <c r="F60" t="n">
-        <v>1768776298</v>
+        <v>1767284039</v>
       </c>
       <c r="G60" t="n">
         <v>59</v>
       </c>
       <c r="H60" t="n">
-        <v>337465988</v>
+        <v>337571125</v>
       </c>
       <c r="I60" t="n">
         <v>4.41e-06</v>
@@ -5787,10 +5787,10 @@
         <v>4.11e-06</v>
       </c>
       <c r="K60" t="n">
-        <v>-1.35704872059e-07</v>
+        <v>-1.64590648184e-07</v>
       </c>
       <c r="L60" t="n">
-        <v>-3.12649</v>
+        <v>-3.66731</v>
       </c>
       <c r="M60" t="n">
         <v>420690000000000</v>
@@ -5805,13 +5805,13 @@
         <v>45635.35457175926</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R60" t="b">
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0.0006831321475004552</v>
+        <v>0.0006827376608651833</v>
       </c>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
@@ -5825,7 +5825,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5847,13 +5847,13 @@
         <v>3.11</v>
       </c>
       <c r="F61" t="n">
-        <v>1733015070</v>
+        <v>1734159801</v>
       </c>
       <c r="G61" t="n">
         <v>60</v>
       </c>
       <c r="H61" t="n">
-        <v>89623916</v>
+        <v>91457298</v>
       </c>
       <c r="I61" t="n">
         <v>3.16</v>
@@ -5862,10 +5862,10 @@
         <v>2.91</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.02113898384443047</v>
+        <v>-0.02654566726226149</v>
       </c>
       <c r="L61" t="n">
-        <v>-0.67499</v>
+        <v>-0.87218</v>
       </c>
       <c r="M61" t="n">
         <v>556920633.6324656</v>
@@ -5880,13 +5880,13 @@
         <v>44326.33741898148</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R61" t="b">
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>0.0006618252411292491</v>
+        <v>0.0006629865918916153</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5952,13 +5952,13 @@
         <v>1.73e-06</v>
       </c>
       <c r="F62" t="n">
-        <v>1552450723</v>
+        <v>1553393103</v>
       </c>
       <c r="G62" t="n">
         <v>61</v>
       </c>
       <c r="H62" t="n">
-        <v>71390824</v>
+        <v>71130540</v>
       </c>
       <c r="I62" t="n">
         <v>1.73e-06</v>
@@ -5967,10 +5967,10 @@
         <v>1.69e-06</v>
       </c>
       <c r="K62" t="n">
-        <v>3.3866e-08</v>
+        <v>3.5007e-08</v>
       </c>
       <c r="L62" t="n">
-        <v>1.9985</v>
+        <v>2.0436</v>
       </c>
       <c r="M62" t="n">
         <v>898232728634017.2</v>
@@ -5985,13 +5985,13 @@
         <v>45629.67800925926</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R62" t="b">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0.0005542431515123321</v>
+        <v>0.0005552003985813833</v>
       </c>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
@@ -6005,7 +6005,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6024,16 +6024,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.9996429999999999</v>
+        <v>0.999619</v>
       </c>
       <c r="F63" t="n">
-        <v>1541410445</v>
+        <v>1541224555</v>
       </c>
       <c r="G63" t="n">
         <v>62</v>
       </c>
       <c r="H63" t="n">
-        <v>157085622</v>
+        <v>157284253</v>
       </c>
       <c r="I63" t="n">
         <v>1</v>
@@ -6042,10 +6042,10 @@
         <v>0.999323</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.000191171553905467</v>
+        <v>-0.000315269886479452</v>
       </c>
       <c r="L63" t="n">
-        <v>-0.01912</v>
+        <v>-0.02802</v>
       </c>
       <c r="M63" t="n">
         <v>1541830391.63</v>
@@ -6060,13 +6060,13 @@
         <v>46058.54591435185</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R63" t="b">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0.0005476652406626799</v>
+        <v>0.0005479446292303669</v>
       </c>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
@@ -6080,7 +6080,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6099,16 +6099,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.998424</v>
+        <v>0.998373</v>
       </c>
       <c r="F64" t="n">
-        <v>1539266689</v>
+        <v>1539182227</v>
       </c>
       <c r="G64" t="n">
         <v>63</v>
       </c>
       <c r="H64" t="n">
-        <v>2345045</v>
+        <v>2342339</v>
       </c>
       <c r="I64" t="n">
         <v>0.999598</v>
@@ -6117,10 +6117,10 @@
         <v>0.997139</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.00059551229409438</v>
+        <v>0.00057735</v>
       </c>
       <c r="L64" t="n">
-        <v>-0.05961</v>
+        <v>0.12037</v>
       </c>
       <c r="M64" t="n">
         <v>1541691414</v>
@@ -6135,13 +6135,13 @@
         <v>46212.39942129629</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R64" t="b">
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0005463879688538172</v>
+        <v>0.0005467268454070938</v>
       </c>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
@@ -6155,7 +6155,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6177,7 +6177,7 @@
         <v>1.15</v>
       </c>
       <c r="F65" t="n">
-        <v>1487612740</v>
+        <v>1487360684</v>
       </c>
       <c r="G65" t="n">
         <v>64</v>
@@ -6192,10 +6192,10 @@
         <v>1.15</v>
       </c>
       <c r="K65" t="n">
-        <v>-4.6342781097941e-05</v>
+        <v>-0.000353152058114592</v>
       </c>
       <c r="L65" t="n">
-        <v>-0.00402</v>
+        <v>-0.03063</v>
       </c>
       <c r="M65" t="n">
         <v>1290400520.88146</v>
@@ -6210,13 +6210,13 @@
         <v>46255.48263888889</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R65" t="b">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0.0005156120163321067</v>
+        <v>0.0005158270894607165</v>
       </c>
       <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr"/>
@@ -6230,7 +6230,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6249,16 +6249,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>9.289999999999999</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="F66" t="n">
-        <v>1470078511</v>
+        <v>1469586290</v>
       </c>
       <c r="G66" t="n">
         <v>65</v>
       </c>
       <c r="H66" t="n">
-        <v>102249672</v>
+        <v>102281072</v>
       </c>
       <c r="I66" t="n">
         <v>9.630000000000001</v>
@@ -6267,10 +6267,10 @@
         <v>8.970000000000001</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.2738372789181227</v>
+        <v>-0.3152148123711491</v>
       </c>
       <c r="L66" t="n">
-        <v>-2.86439</v>
+        <v>-3.18118</v>
       </c>
       <c r="M66" t="n">
         <v>158315119.3216007</v>
@@ -6285,13 +6285,13 @@
         <v>44322.44053240741</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R66" t="b">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0.0005051649428816568</v>
+        <v>0.0005052287088471798</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6357,13 +6357,13 @@
         <v>1</v>
       </c>
       <c r="F67" t="n">
-        <v>1405841571</v>
+        <v>1405826817</v>
       </c>
       <c r="G67" t="n">
         <v>66</v>
       </c>
       <c r="H67" t="n">
-        <v>21458447</v>
+        <v>21451253</v>
       </c>
       <c r="I67" t="n">
         <v>1</v>
@@ -6372,10 +6372,10 @@
         <v>0.999569</v>
       </c>
       <c r="K67" t="n">
-        <v>0.00016125</v>
+        <v>0.00020202</v>
       </c>
       <c r="L67" t="n">
-        <v>0.01613</v>
+        <v>0.02464</v>
       </c>
       <c r="M67" t="n">
         <v>1405780804.97</v>
@@ -6390,13 +6390,13 @@
         <v>46092.00303240741</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R67" t="b">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.0004668919152844838</v>
+        <v>0.0004672106946987081</v>
       </c>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
@@ -6410,7 +6410,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6432,13 +6432,13 @@
         <v>2</v>
       </c>
       <c r="F68" t="n">
-        <v>1399137121</v>
+        <v>1400458319</v>
       </c>
       <c r="G68" t="n">
         <v>67</v>
       </c>
       <c r="H68" t="n">
-        <v>24662450</v>
+        <v>24654711</v>
       </c>
       <c r="I68" t="n">
         <v>2.04</v>
@@ -6447,10 +6447,10 @@
         <v>1.96</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.0211529442187357</v>
+        <v>-0.0157907715471346</v>
       </c>
       <c r="L68" t="n">
-        <v>-1.04721</v>
+        <v>-0.72504</v>
       </c>
       <c r="M68" t="n">
         <v>699992029.6481038</v>
@@ -6465,13 +6465,13 @@
         <v>45653.15375</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R68" t="b">
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0.000462897335220834</v>
+        <v>0.0004640096074983788</v>
       </c>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
@@ -6485,7 +6485,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6504,16 +6504,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9956930000000001</v>
+        <v>0.995642</v>
       </c>
       <c r="F69" t="n">
-        <v>1371499587</v>
+        <v>1371378647</v>
       </c>
       <c r="G69" t="n">
         <v>68</v>
       </c>
       <c r="H69" t="n">
-        <v>431019</v>
+        <v>430832</v>
       </c>
       <c r="I69" t="n">
         <v>0.996485</v>
@@ -6522,10 +6522,10 @@
         <v>0.995563</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.000373019832163979</v>
+        <v>-0.000451159038278637</v>
       </c>
       <c r="L69" t="n">
-        <v>-0.03745</v>
+        <v>-0.0458</v>
       </c>
       <c r="M69" t="n">
         <v>1377438577.534634</v>
@@ -6540,13 +6540,13 @@
         <v>45785.55951388889</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R69" t="b">
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>0.0004464306090427221</v>
+        <v>0.0004466702016107404</v>
       </c>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
@@ -6560,7 +6560,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6579,16 +6579,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.201268</v>
+        <v>0.201469</v>
       </c>
       <c r="F70" t="n">
-        <v>1365796592</v>
+        <v>1367019249</v>
       </c>
       <c r="G70" t="n">
         <v>69</v>
       </c>
       <c r="H70" t="n">
-        <v>321921982</v>
+        <v>321323404</v>
       </c>
       <c r="I70" t="n">
         <v>0.228493</v>
@@ -6597,10 +6597,10 @@
         <v>0.19785</v>
       </c>
       <c r="K70" t="n">
-        <v>-0.02485014670989169</v>
+        <v>-0.02599127895391523</v>
       </c>
       <c r="L70" t="n">
-        <v>-10.98992</v>
+        <v>-11.35261</v>
       </c>
       <c r="M70" t="n">
         <v>6785574605</v>
@@ -6615,13 +6615,13 @@
         <v>45303.18748842592</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R70" t="b">
         <v>1</v>
       </c>
       <c r="S70" t="n">
-        <v>0.0004430327061379209</v>
+        <v>0.0004440708128917838</v>
       </c>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
@@ -6635,7 +6635,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6654,16 +6654,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>27.9</v>
+        <v>27.82</v>
       </c>
       <c r="F71" t="n">
-        <v>1345616698</v>
+        <v>1341636789</v>
       </c>
       <c r="G71" t="n">
         <v>70</v>
       </c>
       <c r="H71" t="n">
-        <v>47354685</v>
+        <v>47580008</v>
       </c>
       <c r="I71" t="n">
         <v>29.43</v>
@@ -6672,10 +6672,10 @@
         <v>26.62</v>
       </c>
       <c r="K71" t="n">
-        <v>-1.357647037195715</v>
+        <v>-1.474875439986953</v>
       </c>
       <c r="L71" t="n">
-        <v>-4.64051</v>
+        <v>-5.0419</v>
       </c>
       <c r="M71" t="n">
         <v>48212581.75746144</v>
@@ -6690,13 +6690,13 @@
         <v>46286.34548611111</v>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R71" t="b">
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>0.0004310093183493677</v>
+        <v>0.0004289359524859737</v>
       </c>
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
@@ -6710,7 +6710,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6729,16 +6729,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.999</v>
+        <v>0.998945</v>
       </c>
       <c r="F72" t="n">
-        <v>1318674349</v>
+        <v>1318613303</v>
       </c>
       <c r="G72" t="n">
         <v>71</v>
       </c>
       <c r="H72" t="n">
-        <v>2400815</v>
+        <v>2402236</v>
       </c>
       <c r="I72" t="n">
         <v>0.999831</v>
@@ -6747,10 +6747,10 @@
         <v>0.998856</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.00064779606848675</v>
+        <v>-0.000730345676747124</v>
       </c>
       <c r="L72" t="n">
-        <v>-0.0648</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="M72" t="n">
         <v>1320000000</v>
@@ -6765,13 +6765,13 @@
         <v>45940.56990740741</v>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R72" t="b">
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>0.0004149567905233277</v>
+        <v>0.0004152076831746019</v>
       </c>
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
@@ -6785,7 +6785,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6804,16 +6804,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.04529207</v>
+        <v>0.04535947</v>
       </c>
       <c r="F73" t="n">
-        <v>1255918293</v>
+        <v>1257459274</v>
       </c>
       <c r="G73" t="n">
         <v>72</v>
       </c>
       <c r="H73" t="n">
-        <v>30399822</v>
+        <v>30343856</v>
       </c>
       <c r="I73" t="n">
         <v>0.04846213</v>
@@ -6822,10 +6822,10 @@
         <v>0.04423726</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.001377032437974476</v>
+        <v>-0.001420093847190218</v>
       </c>
       <c r="L73" t="n">
-        <v>-2.95063</v>
+        <v>-3.14532</v>
       </c>
       <c r="M73" t="n">
         <v>27726432137.69469</v>
@@ -6840,13 +6840,13 @@
         <v>45504.69498842592</v>
       </c>
       <c r="Q73" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R73" t="b">
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0.000377566088799713</v>
+        <v>0.000378743223379615</v>
       </c>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
@@ -6860,7 +6860,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6879,16 +6879,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.117084</v>
+        <v>0.117067</v>
       </c>
       <c r="F74" t="n">
-        <v>1243518815</v>
+        <v>1243521977</v>
       </c>
       <c r="G74" t="n">
         <v>73</v>
       </c>
       <c r="H74" t="n">
-        <v>152447718</v>
+        <v>152813918</v>
       </c>
       <c r="I74" t="n">
         <v>0.123201</v>
@@ -6897,10 +6897,10 @@
         <v>0.112007</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.004229877617648245</v>
+        <v>-0.00471659850751649</v>
       </c>
       <c r="L74" t="n">
-        <v>-3.48671</v>
+        <v>-3.8026</v>
       </c>
       <c r="M74" t="n">
         <v>10622244875.03591</v>
@@ -6915,13 +6915,13 @@
         <v>45364.45493055556</v>
       </c>
       <c r="Q74" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R74" t="b">
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>0.0003701783526515631</v>
+        <v>0.0003704327978129317</v>
       </c>
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
@@ -6935,7 +6935,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6954,16 +6954,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.13483</v>
+        <v>0.134807</v>
       </c>
       <c r="F75" t="n">
-        <v>1221251465</v>
+        <v>1221525607</v>
       </c>
       <c r="G75" t="n">
         <v>74</v>
       </c>
       <c r="H75" t="n">
-        <v>241054875</v>
+        <v>242173227</v>
       </c>
       <c r="I75" t="n">
         <v>0.13905</v>
@@ -6972,16 +6972,16 @@
         <v>0.115069</v>
       </c>
       <c r="K75" t="n">
-        <v>0.01603922</v>
+        <v>0.01547112</v>
       </c>
       <c r="L75" t="n">
-        <v>13.50211</v>
+        <v>13.15234</v>
       </c>
       <c r="M75" t="n">
         <v>9057776356.697313</v>
       </c>
       <c r="N75" t="n">
-        <v>9057846423.090742</v>
+        <v>9057855239.390703</v>
       </c>
       <c r="O75" t="n">
         <v>3.56</v>
@@ -6990,13 +6990,13 @@
         <v>43636.28563657407</v>
       </c>
       <c r="Q75" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R75" t="b">
         <v>1</v>
       </c>
       <c r="S75" t="n">
-        <v>0.0003569112371714996</v>
+        <v>0.0003573169694265362</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7059,16 +7059,16 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>10.87</v>
+        <v>10.88</v>
       </c>
       <c r="F76" t="n">
-        <v>1159938519</v>
+        <v>1159890897</v>
       </c>
       <c r="G76" t="n">
         <v>75</v>
       </c>
       <c r="H76" t="n">
-        <v>4692820</v>
+        <v>4691404</v>
       </c>
       <c r="I76" t="n">
         <v>11.3</v>
@@ -7077,10 +7077,10 @@
         <v>10.78</v>
       </c>
       <c r="K76" t="n">
-        <v>-0.3826935637173854</v>
+        <v>-0.3812862821837193</v>
       </c>
       <c r="L76" t="n">
-        <v>-3.39955</v>
+        <v>-3.38072</v>
       </c>
       <c r="M76" t="n">
         <v>106644263.3697571</v>
@@ -7095,13 +7095,13 @@
         <v>45682.66666666666</v>
       </c>
       <c r="Q76" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R76" t="b">
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0003203803551848737</v>
+        <v>0.0003205658928168385</v>
       </c>
       <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr"/>
@@ -7115,7 +7115,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7134,16 +7134,16 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4.44</v>
+        <v>4.45</v>
       </c>
       <c r="F77" t="n">
-        <v>1110658966</v>
+        <v>1112497244</v>
       </c>
       <c r="G77" t="n">
         <v>76</v>
       </c>
       <c r="H77" t="n">
-        <v>103597738</v>
+        <v>103864929</v>
       </c>
       <c r="I77" t="n">
         <v>4.66</v>
@@ -7152,10 +7152,10 @@
         <v>4.32</v>
       </c>
       <c r="K77" t="n">
-        <v>-0.2009295045816213</v>
+        <v>-0.2025775926833298</v>
       </c>
       <c r="L77" t="n">
-        <v>-4.32803</v>
+        <v>-4.37981</v>
       </c>
       <c r="M77" t="n">
         <v>250000000</v>
@@ -7170,13 +7170,13 @@
         <v>46021.04538194444</v>
       </c>
       <c r="Q77" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R77" t="b">
         <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0002910190921492224</v>
+        <v>0.0002923063654788105</v>
       </c>
       <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr"/>
@@ -7190,7 +7190,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7209,16 +7209,16 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.326262</v>
+        <v>0.326351</v>
       </c>
       <c r="F78" t="n">
-        <v>1083045706</v>
+        <v>1083160208</v>
       </c>
       <c r="G78" t="n">
         <v>77</v>
       </c>
       <c r="H78" t="n">
-        <v>142469140</v>
+        <v>137771675</v>
       </c>
       <c r="I78" t="n">
         <v>0.372198</v>
@@ -7227,10 +7227,10 @@
         <v>0.319689</v>
       </c>
       <c r="K78" t="n">
-        <v>-0.04654824195593921</v>
+        <v>-0.04660550101571981</v>
       </c>
       <c r="L78" t="n">
-        <v>-12.48576</v>
+        <v>-12.55982</v>
       </c>
       <c r="M78" t="n">
         <v>3319369204.37</v>
@@ -7245,13 +7245,13 @@
         <v>45322.29359953704</v>
       </c>
       <c r="Q78" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R78" t="b">
         <v>1</v>
       </c>
       <c r="S78" t="n">
-        <v>0.0002745668286692386</v>
+        <v>0.0002748135005405726</v>
       </c>
       <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr"/>
@@ -7265,7 +7265,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7284,16 +7284,16 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.12986</v>
+        <v>0.129966</v>
       </c>
       <c r="F79" t="n">
-        <v>1063329137</v>
+        <v>1064266580</v>
       </c>
       <c r="G79" t="n">
         <v>78</v>
       </c>
       <c r="H79" t="n">
-        <v>37836323</v>
+        <v>38641601</v>
       </c>
       <c r="I79" t="n">
         <v>0.131925</v>
@@ -7302,10 +7302,10 @@
         <v>0.126056</v>
       </c>
       <c r="K79" t="n">
-        <v>0.00354789</v>
+        <v>0.00351731</v>
       </c>
       <c r="L79" t="n">
-        <v>2.80884</v>
+        <v>2.8281</v>
       </c>
       <c r="M79" t="n">
         <v>8188743036.341737</v>
@@ -7320,13 +7320,13 @@
         <v>44290.85721064815</v>
       </c>
       <c r="Q79" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R79" t="b">
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0002628194946670498</v>
+        <v>0.0002635477515808853</v>
       </c>
       <c r="T79" t="inlineStr"/>
       <c r="U79" t="inlineStr"/>
@@ -7340,7 +7340,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7362,13 +7362,13 @@
         <v>7.44</v>
       </c>
       <c r="F80" t="n">
-        <v>1020951262</v>
+        <v>1020290481</v>
       </c>
       <c r="G80" t="n">
         <v>79</v>
       </c>
       <c r="H80" t="n">
-        <v>3048433</v>
+        <v>3105640</v>
       </c>
       <c r="I80" t="n">
         <v>7.45</v>
@@ -7377,10 +7377,10 @@
         <v>7.26</v>
       </c>
       <c r="K80" t="n">
-        <v>0.124544</v>
+        <v>0.115698</v>
       </c>
       <c r="L80" t="n">
-        <v>1.70282</v>
+        <v>1.58203</v>
       </c>
       <c r="M80" t="n">
         <v>137155021.7355672</v>
@@ -7395,13 +7395,13 @@
         <v>44531.29832175926</v>
       </c>
       <c r="Q80" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R80" t="b">
         <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>0.0002375703221600072</v>
+        <v>0.0002373260173771444</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7467,13 +7467,13 @@
         <v>1.94</v>
       </c>
       <c r="F81" t="n">
-        <v>1007878021</v>
+        <v>1007341574</v>
       </c>
       <c r="G81" t="n">
         <v>80</v>
       </c>
       <c r="H81" t="n">
-        <v>105811089</v>
+        <v>105956967</v>
       </c>
       <c r="I81" t="n">
         <v>2.09</v>
@@ -7482,10 +7482,10 @@
         <v>1.88</v>
       </c>
       <c r="K81" t="n">
-        <v>-0.1062081559773733</v>
+        <v>-0.1171924824666473</v>
       </c>
       <c r="L81" t="n">
-        <v>-5.18352</v>
+        <v>-5.62152</v>
       </c>
       <c r="M81" t="n">
         <v>518776241.2826915</v>
@@ -7500,13 +7500,13 @@
         <v>45368.35444444444</v>
       </c>
       <c r="Q81" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R81" t="b">
         <v>1</v>
       </c>
       <c r="S81" t="n">
-        <v>0.0002297811511070664</v>
+        <v>0.0002296049414903778</v>
       </c>
       <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr"/>
@@ -7520,7 +7520,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7539,16 +7539,16 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.089061</v>
+        <v>0.08892700000000001</v>
       </c>
       <c r="F82" t="n">
-        <v>1000529433</v>
+        <v>999760059</v>
       </c>
       <c r="G82" t="n">
         <v>81</v>
       </c>
       <c r="H82" t="n">
-        <v>8562997</v>
+        <v>7428322</v>
       </c>
       <c r="I82" t="n">
         <v>0.091534</v>
@@ -7557,10 +7557,10 @@
         <v>0.088142</v>
       </c>
       <c r="K82" t="n">
-        <v>-0.001592062216003651</v>
+        <v>-0.001871800112296637</v>
       </c>
       <c r="L82" t="n">
-        <v>-1.75621</v>
+        <v>-2.05283</v>
       </c>
       <c r="M82" t="n">
         <v>11243022455.381</v>
@@ -7575,13 +7575,13 @@
         <v>45714.36184027778</v>
       </c>
       <c r="Q82" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R82" t="b">
         <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0.0002254027870174281</v>
+        <v>0.0002250842933266634</v>
       </c>
       <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr"/>
@@ -7595,7 +7595,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7632,7 +7632,7 @@
         <v>107.53</v>
       </c>
       <c r="K83" t="n">
-        <v>-1.4211e-14</v>
+        <v>2.8422e-14</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -7650,13 +7650,13 @@
         <v>46287.17361111111</v>
       </c>
       <c r="Q83" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R83" t="b">
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.0002130670498734008</v>
+        <v>0.000213197744299189</v>
       </c>
       <c r="T83" t="inlineStr"/>
       <c r="U83" t="inlineStr"/>
@@ -7670,7 +7670,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7692,13 +7692,13 @@
         <v>1.73</v>
       </c>
       <c r="F84" t="n">
-        <v>922328114</v>
+        <v>923387307</v>
       </c>
       <c r="G84" t="n">
         <v>83</v>
       </c>
       <c r="H84" t="n">
-        <v>72353589</v>
+        <v>72366323</v>
       </c>
       <c r="I84" t="n">
         <v>1.89</v>
@@ -7707,16 +7707,16 @@
         <v>1.69</v>
       </c>
       <c r="K84" t="n">
-        <v>-0.1492814572188828</v>
+        <v>-0.154515911570152</v>
       </c>
       <c r="L84" t="n">
-        <v>-7.94375</v>
+        <v>-8.10905</v>
       </c>
       <c r="M84" t="n">
         <v>533140304.847045</v>
       </c>
       <c r="N84" t="n">
-        <v>533140304.847045</v>
+        <v>533147788.428225</v>
       </c>
       <c r="O84" t="n">
         <v>43.84</v>
@@ -7725,13 +7725,13 @@
         <v>44458.66666666666</v>
       </c>
       <c r="Q84" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R84" t="b">
         <v>1</v>
       </c>
       <c r="S84" t="n">
-        <v>0.0001788096392083586</v>
+        <v>0.0001795453290053346</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7794,16 +7794,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1.06</v>
+        <v>1.059</v>
       </c>
       <c r="F85" t="n">
-        <v>880685714</v>
+        <v>880334181</v>
       </c>
       <c r="G85" t="n">
         <v>84</v>
       </c>
       <c r="H85" t="n">
-        <v>166877189</v>
+        <v>166809551</v>
       </c>
       <c r="I85" t="n">
         <v>1.15</v>
@@ -7812,10 +7812,10 @@
         <v>1.021</v>
       </c>
       <c r="K85" t="n">
-        <v>-0.07233708610244571</v>
+        <v>-0.07912120889306262</v>
       </c>
       <c r="L85" t="n">
-        <v>-6.39048</v>
+        <v>-6.88845</v>
       </c>
       <c r="M85" t="n">
         <v>831252997</v>
@@ -7830,13 +7830,13 @@
         <v>44287.22894675926</v>
       </c>
       <c r="Q85" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R85" t="b">
         <v>1</v>
       </c>
       <c r="S85" t="n">
-        <v>0.000153998670248559</v>
+        <v>0.0001538739381297555</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7899,16 +7899,16 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>65.52</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="F86" t="n">
-        <v>841803422</v>
+        <v>841222192</v>
       </c>
       <c r="G86" t="n">
         <v>85</v>
       </c>
       <c r="H86" t="n">
-        <v>154007039</v>
+        <v>153840224</v>
       </c>
       <c r="I86" t="n">
         <v>68.88</v>
@@ -7917,10 +7917,10 @@
         <v>63.18</v>
       </c>
       <c r="K86" t="n">
-        <v>-2.774559080096893</v>
+        <v>-3.072780751194188</v>
       </c>
       <c r="L86" t="n">
-        <v>-4.06248</v>
+        <v>-4.5008</v>
       </c>
       <c r="M86" t="n">
         <v>12846801.60815124</v>
@@ -7935,13 +7935,13 @@
         <v>43088.66666666666</v>
       </c>
       <c r="Q86" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R86" t="b">
         <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0.0001308322019398672</v>
+        <v>0.0001305525384817868</v>
       </c>
       <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr"/>
@@ -7955,7 +7955,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7974,16 +7974,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.8269609999999999</v>
+        <v>0.826891</v>
       </c>
       <c r="F87" t="n">
-        <v>827073904</v>
+        <v>826929426</v>
       </c>
       <c r="G87" t="n">
         <v>86</v>
       </c>
       <c r="H87" t="n">
-        <v>7876360</v>
+        <v>7891069</v>
       </c>
       <c r="I87" t="n">
         <v>0.8834880000000001</v>
@@ -7992,10 +7992,10 @@
         <v>0.8333390000000001</v>
       </c>
       <c r="K87" t="n">
-        <v>-0.04848970496131588</v>
+        <v>-0.05032797479153561</v>
       </c>
       <c r="L87" t="n">
-        <v>-5.53883</v>
+        <v>-5.70937</v>
       </c>
       <c r="M87" t="n">
         <v>1000000000</v>
@@ -8010,13 +8010,13 @@
         <v>44328.27623842593</v>
       </c>
       <c r="Q87" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R87" t="b">
         <v>1</v>
       </c>
       <c r="S87" t="n">
-        <v>0.0001220562040653256</v>
+        <v>0.0001220301565604557</v>
       </c>
       <c r="T87" t="inlineStr"/>
       <c r="U87" t="inlineStr"/>
@@ -8030,7 +8030,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8052,13 +8052,13 @@
         <v>2.59</v>
       </c>
       <c r="F88" t="n">
-        <v>824919392</v>
+        <v>824960264</v>
       </c>
       <c r="G88" t="n">
         <v>87</v>
       </c>
       <c r="H88" t="n">
-        <v>104584532</v>
+        <v>104582217</v>
       </c>
       <c r="I88" t="n">
         <v>2.84</v>
@@ -8067,10 +8067,10 @@
         <v>2.56</v>
       </c>
       <c r="K88" t="n">
-        <v>-0.2411439652573488</v>
+        <v>-0.2452707882532104</v>
       </c>
       <c r="L88" t="n">
-        <v>-8.52224</v>
+        <v>-8.652699999999999</v>
       </c>
       <c r="M88" t="n">
         <v>318687703.0077946</v>
@@ -8085,13 +8085,13 @@
         <v>44316.08914351852</v>
       </c>
       <c r="Q88" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R88" t="b">
         <v>1</v>
       </c>
       <c r="S88" t="n">
-        <v>0.0001207725237213609</v>
+        <v>0.0001208559996037846</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8154,16 +8154,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.828161</v>
+        <v>0.822242</v>
       </c>
       <c r="F89" t="n">
-        <v>824769272</v>
+        <v>818449149</v>
       </c>
       <c r="G89" t="n">
         <v>88</v>
       </c>
       <c r="H89" t="n">
-        <v>93550416</v>
+        <v>93714235</v>
       </c>
       <c r="I89" t="n">
         <v>0.844204</v>
@@ -8172,10 +8172,10 @@
         <v>0.766646</v>
       </c>
       <c r="K89" t="n">
-        <v>-0.01108347407055277</v>
+        <v>-0.01866899560459523</v>
       </c>
       <c r="L89" t="n">
-        <v>-1.32065</v>
+        <v>-2.20927</v>
       </c>
       <c r="M89" t="n">
         <v>995760456.212387</v>
@@ -8190,13 +8190,13 @@
         <v>45633.25043981482</v>
       </c>
       <c r="Q89" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R89" t="b">
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>0.0001206830806858911</v>
+        <v>0.0001169736014197167</v>
       </c>
       <c r="T89" t="inlineStr"/>
       <c r="U89" t="inlineStr"/>
@@ -8210,7 +8210,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8265,13 +8265,13 @@
         <v>46293.65983796296</v>
       </c>
       <c r="Q90" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R90" t="b">
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>0.0001022153972638352</v>
+        <v>0.0001022601082363158</v>
       </c>
       <c r="T90" t="inlineStr"/>
       <c r="U90" t="inlineStr"/>
@@ -8285,7 +8285,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8304,16 +8304,16 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.02914287</v>
+        <v>0.02905721</v>
       </c>
       <c r="F91" t="n">
-        <v>779378621</v>
+        <v>776826525</v>
       </c>
       <c r="G91" t="n">
         <v>90</v>
       </c>
       <c r="H91" t="n">
-        <v>11011319</v>
+        <v>10987955</v>
       </c>
       <c r="I91" t="n">
         <v>0.02892869</v>
@@ -8322,10 +8322,10 @@
         <v>0.02667611</v>
       </c>
       <c r="K91" t="n">
-        <v>0.00166779</v>
+        <v>0.00154905</v>
       </c>
       <c r="L91" t="n">
-        <v>6.07018</v>
+        <v>5.54832</v>
       </c>
       <c r="M91" t="n">
         <v>26740211248</v>
@@ -8340,13 +8340,13 @@
         <v>46156.97986111111</v>
       </c>
       <c r="Q91" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>9.363886534224858e-05</v>
+        <v>9.215517940847267e-05</v>
       </c>
       <c r="T91" t="inlineStr"/>
       <c r="U91" t="inlineStr"/>
@@ -8360,7 +8360,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8379,16 +8379,16 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.00885798</v>
+        <v>0.008865629999999999</v>
       </c>
       <c r="F92" t="n">
-        <v>761736772</v>
+        <v>762085600</v>
       </c>
       <c r="G92" t="n">
         <v>91</v>
       </c>
       <c r="H92" t="n">
-        <v>13058453</v>
+        <v>12940244</v>
       </c>
       <c r="I92" t="n">
         <v>0.009248940000000001</v>
@@ -8397,10 +8397,10 @@
         <v>0.00864553</v>
       </c>
       <c r="K92" t="n">
-        <v>-0.000288199262861687</v>
+        <v>-0.00031451871537325</v>
       </c>
       <c r="L92" t="n">
-        <v>-3.15104</v>
+        <v>-3.33532</v>
       </c>
       <c r="M92" t="n">
         <v>85985041177</v>
@@ -8415,13 +8415,13 @@
         <v>44304.71413194444</v>
       </c>
       <c r="Q92" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R92" t="b">
         <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>8.312767079216326e-05</v>
+        <v>8.33655726435052e-05</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8487,13 +8487,13 @@
         <v>7.33</v>
       </c>
       <c r="F93" t="n">
-        <v>732881399</v>
+        <v>733409633</v>
       </c>
       <c r="G93" t="n">
         <v>92</v>
       </c>
       <c r="H93" t="n">
-        <v>124056405</v>
+        <v>130993122</v>
       </c>
       <c r="I93" t="n">
         <v>7.83</v>
@@ -8502,10 +8502,10 @@
         <v>7.19</v>
       </c>
       <c r="K93" t="n">
-        <v>-0.4105163792450979</v>
+        <v>-0.436336089499572</v>
       </c>
       <c r="L93" t="n">
-        <v>-5.30368</v>
+        <v>-5.64414</v>
       </c>
       <c r="M93" t="n">
         <v>100000000</v>
@@ -8520,13 +8520,13 @@
         <v>45365.29608796296</v>
       </c>
       <c r="Q93" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R93" t="b">
         <v>1</v>
       </c>
       <c r="S93" t="n">
-        <v>6.593534364900049e-05</v>
+        <v>6.62668849061221e-05</v>
       </c>
       <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr"/>
@@ -8540,7 +8540,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8562,7 +8562,7 @@
         <v>1.21</v>
       </c>
       <c r="F94" t="n">
-        <v>730775894</v>
+        <v>730652074</v>
       </c>
       <c r="G94" t="n">
         <v>93</v>
@@ -8577,10 +8577,10 @@
         <v>1.2</v>
       </c>
       <c r="K94" t="n">
-        <v>-7.068572791646399e-05</v>
+        <v>-0.000391451740396231</v>
       </c>
       <c r="L94" t="n">
-        <v>-0.00586</v>
+        <v>-0.03247</v>
       </c>
       <c r="M94" t="n">
         <v>606320017.89252</v>
@@ -8595,13 +8595,13 @@
         <v>46049.54175925926</v>
       </c>
       <c r="Q94" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R94" t="b">
         <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>6.468086217819902e-05</v>
+        <v>6.462262857612945e-05</v>
       </c>
       <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
@@ -8615,7 +8615,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8634,16 +8634,16 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.830133</v>
+        <v>0.828923</v>
       </c>
       <c r="F95" t="n">
-        <v>722897865</v>
+        <v>721944741</v>
       </c>
       <c r="G95" t="n">
         <v>94</v>
       </c>
       <c r="H95" t="n">
-        <v>97446300</v>
+        <v>94928585</v>
       </c>
       <c r="I95" t="n">
         <v>0.8736660000000001</v>
@@ -8652,10 +8652,10 @@
         <v>0.796221</v>
       </c>
       <c r="K95" t="n">
-        <v>-0.03436538616411289</v>
+        <v>-0.03804310850731984</v>
       </c>
       <c r="L95" t="n">
-        <v>-3.97518</v>
+        <v>-4.38482</v>
       </c>
       <c r="M95" t="n">
         <v>870942902.9405427</v>
@@ -8670,13 +8670,13 @@
         <v>44952.26755787037</v>
       </c>
       <c r="Q95" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R95" t="b">
         <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>5.998705171138151e-05</v>
+        <v>5.943068620876618e-05</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8739,16 +8739,16 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.03120101</v>
+        <v>0.03135164</v>
       </c>
       <c r="F96" t="n">
-        <v>711640350</v>
+        <v>714976415</v>
       </c>
       <c r="G96" t="n">
         <v>95</v>
       </c>
       <c r="H96" t="n">
-        <v>15865482</v>
+        <v>15860817</v>
       </c>
       <c r="I96" t="n">
         <v>0.03294704</v>
@@ -8757,10 +8757,10 @@
         <v>0.02846185</v>
       </c>
       <c r="K96" t="n">
-        <v>0.00081761</v>
+        <v>0.00057257</v>
       </c>
       <c r="L96" t="n">
-        <v>2.69098</v>
+        <v>2.18701</v>
       </c>
       <c r="M96" t="n">
         <v>22796250000</v>
@@ -8775,13 +8775,13 @@
         <v>46285.43993055556</v>
       </c>
       <c r="Q96" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R96" t="b">
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>5.327970882937953e-05</v>
+        <v>5.527566572327435e-05</v>
       </c>
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
@@ -8795,7 +8795,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8814,16 +8814,16 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.99948</v>
+        <v>0.999424</v>
       </c>
       <c r="F97" t="n">
-        <v>698633598</v>
+        <v>698600579</v>
       </c>
       <c r="G97" t="n">
         <v>96</v>
       </c>
       <c r="H97" t="n">
-        <v>12705371</v>
+        <v>12704698</v>
       </c>
       <c r="I97" t="n">
         <v>0.999571</v>
@@ -8832,10 +8832,10 @@
         <v>0.998854</v>
       </c>
       <c r="K97" t="n">
-        <v>0.00024192</v>
+        <v>0.00015647</v>
       </c>
       <c r="L97" t="n">
-        <v>0.02421</v>
+        <v>0.02012</v>
       </c>
       <c r="M97" t="n">
         <v>699000000</v>
@@ -8850,13 +8850,13 @@
         <v>45350.38608796296</v>
       </c>
       <c r="Q97" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R97" t="b">
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>4.553015260447865e-05</v>
+        <v>4.55112066484471e-05</v>
       </c>
       <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr"/>
@@ -8870,7 +8870,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8889,16 +8889,16 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.03446413</v>
+        <v>0.0344574</v>
       </c>
       <c r="F98" t="n">
-        <v>687460655</v>
+        <v>687315074</v>
       </c>
       <c r="G98" t="n">
         <v>97</v>
       </c>
       <c r="H98" t="n">
-        <v>40281267</v>
+        <v>40087567</v>
       </c>
       <c r="I98" t="n">
         <v>0.03635087</v>
@@ -8907,10 +8907,10 @@
         <v>0.03245616</v>
       </c>
       <c r="K98" t="n">
-        <v>0.00032728</v>
+        <v>0.00055294</v>
       </c>
       <c r="L98" t="n">
-        <v>0.95873</v>
+        <v>1.6053</v>
       </c>
       <c r="M98" t="n">
         <v>19946688440</v>
@@ -8925,13 +8925,13 @@
         <v>44428.86097222222</v>
       </c>
       <c r="Q98" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R98" t="b">
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>3.887319858735641e-05</v>
+        <v>3.87819714685602e-05</v>
       </c>
       <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr"/>
@@ -8945,7 +8945,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8964,16 +8964,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.705315</v>
+        <v>0.7070419999999999</v>
       </c>
       <c r="F99" t="n">
-        <v>681103656</v>
+        <v>682491324</v>
       </c>
       <c r="G99" t="n">
         <v>98</v>
       </c>
       <c r="H99" t="n">
-        <v>58090067</v>
+        <v>58990330</v>
       </c>
       <c r="I99" t="n">
         <v>0.7287400000000001</v>
@@ -8982,10 +8982,10 @@
         <v>0.66335</v>
       </c>
       <c r="K99" t="n">
-        <v>-0.01101288620817187</v>
+        <v>-0.01430198224047408</v>
       </c>
       <c r="L99" t="n">
-        <v>-1.53741</v>
+        <v>-2.01211</v>
       </c>
       <c r="M99" t="n">
         <v>965350000</v>
@@ -9000,13 +9000,13 @@
         <v>45378.63525462963</v>
       </c>
       <c r="Q99" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R99" t="b">
         <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>3.508563339259152e-05</v>
+        <v>3.590570246695333e-05</v>
       </c>
       <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr"/>
@@ -9020,7 +9020,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9039,16 +9039,16 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.080959</v>
+        <v>0.081133</v>
       </c>
       <c r="F100" t="n">
-        <v>637475365</v>
+        <v>638937957</v>
       </c>
       <c r="G100" t="n">
         <v>99</v>
       </c>
       <c r="H100" t="n">
-        <v>52852766</v>
+        <v>52863970</v>
       </c>
       <c r="I100" t="n">
         <v>0.08483</v>
@@ -9057,10 +9057,10 @@
         <v>0.07798099999999999</v>
       </c>
       <c r="K100" t="n">
-        <v>-0.002308890805568356</v>
+        <v>-0.002486254543250466</v>
       </c>
       <c r="L100" t="n">
-        <v>-2.77283</v>
+        <v>-2.91104</v>
       </c>
       <c r="M100" t="n">
         <v>7874959363.63714</v>
@@ -9075,13 +9075,13 @@
         <v>45366.95920138889</v>
       </c>
       <c r="Q100" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R100" t="b">
         <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>9.091450209823293e-06</v>
+        <v>9.936031688470234e-06</v>
       </c>
       <c r="T100" t="inlineStr"/>
       <c r="U100" t="inlineStr"/>
@@ -9095,7 +9095,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9114,16 +9114,16 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.00715495</v>
+        <v>0.00715552</v>
       </c>
       <c r="F101" t="n">
-        <v>622216396</v>
+        <v>622274379</v>
       </c>
       <c r="G101" t="n">
         <v>100</v>
       </c>
       <c r="H101" t="n">
-        <v>4627448</v>
+        <v>4625638</v>
       </c>
       <c r="I101" t="n">
         <v>0.00719155</v>
@@ -9132,10 +9132,10 @@
         <v>0.00693629</v>
       </c>
       <c r="K101" t="n">
-        <v>8.72e-06</v>
+        <v>-1.01279891111e-06</v>
       </c>
       <c r="L101" t="n">
-        <v>0.12203</v>
+        <v>0.02624</v>
       </c>
       <c r="M101" t="n">
         <v>86964280297.02844</v>
@@ -9150,7 +9150,7 @@
         <v>44935.80144675926</v>
       </c>
       <c r="Q101" s="1" t="n">
-        <v>46293.98981481481</v>
+        <v>46293.99340277778</v>
       </c>
       <c r="R101" t="b">
         <v>0</v>

--- a/src/xlsx/enriched_data.xlsx
+++ b/src/xlsx/enriched_data.xlsx
@@ -560,7 +560,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -579,34 +579,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>83507</v>
+        <v>83733</v>
       </c>
       <c r="F2" t="n">
-        <v>1677708109294</v>
+        <v>1682985218380</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>41723595724</v>
+        <v>34959956786</v>
       </c>
       <c r="I2" t="n">
-        <v>84945</v>
+        <v>85518</v>
       </c>
       <c r="J2" t="n">
-        <v>82581</v>
+        <v>82911</v>
       </c>
       <c r="K2" t="n">
-        <v>-943.0202493105753</v>
+        <v>729.05</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.09898</v>
+        <v>0.94076</v>
       </c>
       <c r="M2" t="n">
-        <v>20090481</v>
+        <v>20090909</v>
       </c>
       <c r="N2" t="n">
-        <v>20090790</v>
+        <v>20090909</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -615,7 +615,7 @@
         <v>45936.45673611111</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
@@ -665,7 +665,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -684,34 +684,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2688.58</v>
+        <v>2672.67</v>
       </c>
       <c r="F3" t="n">
-        <v>328230175563</v>
+        <v>326449172566</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>17124992169</v>
+        <v>14871641419</v>
       </c>
       <c r="I3" t="n">
-        <v>2717.37</v>
+        <v>2736.98</v>
       </c>
       <c r="J3" t="n">
-        <v>2636.99</v>
+        <v>2657.67</v>
       </c>
       <c r="K3" t="n">
-        <v>1.57</v>
+        <v>-3.372896421189125</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06862</v>
+        <v>-0.08332000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>122087473.8258867</v>
+        <v>122092940.7490518</v>
       </c>
       <c r="N3" t="n">
-        <v>122087473.8258867</v>
+        <v>122092940.7490518</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -720,13 +720,13 @@
         <v>45893.47295138889</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1953435503201923</v>
+        <v>0.193666391299686</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -789,34 +789,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.99966</v>
+        <v>0.999508</v>
       </c>
       <c r="F4" t="n">
-        <v>183812509434</v>
+        <v>183780430899</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>75915231025</v>
+        <v>63995119342</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9998359999999999</v>
+        <v>0.999907</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999602</v>
+        <v>0.999551</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.000117278820729316</v>
+        <v>-0.000268402896748121</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.00747</v>
+        <v>-0.02385</v>
       </c>
       <c r="M4" t="n">
-        <v>183874242892.1083</v>
+        <v>183870584013.1206</v>
       </c>
       <c r="N4" t="n">
-        <v>189285761986.9062</v>
+        <v>189337530060.8262</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -825,13 +825,13 @@
         <v>43304.66666666666</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1092312815725885</v>
+        <v>0.1088631885598317</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -894,34 +894,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>763.48</v>
+        <v>766.1799999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>101664628051</v>
+        <v>102063628562</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1057079982</v>
+        <v>957021712</v>
       </c>
       <c r="I5" t="n">
-        <v>783.74</v>
+        <v>778.49</v>
       </c>
       <c r="J5" t="n">
-        <v>757.15</v>
+        <v>750.63</v>
       </c>
       <c r="K5" t="n">
-        <v>-15.24681102564591</v>
+        <v>10.7</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.92599</v>
+        <v>1.43509</v>
       </c>
       <c r="M5" t="n">
-        <v>133159615.43</v>
+        <v>133159463.23</v>
       </c>
       <c r="N5" t="n">
-        <v>133159615.43</v>
+        <v>133159452.19</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -930,13 +930,13 @@
         <v>45943.02875</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06024876697925312</v>
+        <v>0.06029020421255249</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -999,34 +999,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="F6" t="n">
-        <v>94017254994</v>
+        <v>94386823528</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>4351788248</v>
+        <v>3577972373</v>
       </c>
       <c r="I6" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="J6" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.02329244526184704</v>
+        <v>-0.01884122113988318</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.49005</v>
+        <v>-1.26995</v>
       </c>
       <c r="M6" t="n">
-        <v>62879209849</v>
+        <v>63092975951</v>
       </c>
       <c r="N6" t="n">
-        <v>99985622230</v>
+        <v>99985612577</v>
       </c>
       <c r="O6" t="n">
         <v>3.65</v>
@@ -1035,13 +1035,13 @@
         <v>45855.82005787037</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R6" t="b">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05568884947366665</v>
+        <v>0.05572706272769828</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1104,34 +1104,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999868</v>
+        <v>0.999744</v>
       </c>
       <c r="F7" t="n">
-        <v>74718233752</v>
+        <v>74252256183</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>20699802142</v>
+        <v>17858609980</v>
       </c>
       <c r="I7" t="n">
-        <v>0.99999</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.99954</v>
+        <v>0.999736</v>
       </c>
       <c r="K7" t="n">
-        <v>1.402e-05</v>
+        <v>-0.000157659049448533</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00566</v>
+        <v>-0.01205</v>
       </c>
       <c r="M7" t="n">
-        <v>74728156839.12137</v>
+        <v>74271158723.4574</v>
       </c>
       <c r="N7" t="n">
-        <v>74784667843.85722</v>
+        <v>74219208687.05562</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -1140,13 +1140,13 @@
         <v>43418.66666666666</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04418137571161074</v>
+        <v>0.04375894850249071</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1209,34 +1209,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>118.72</v>
+        <v>118.35</v>
       </c>
       <c r="F8" t="n">
-        <v>69795574274</v>
+        <v>69629312154</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>4127386361</v>
+        <v>4170824395</v>
       </c>
       <c r="I8" t="n">
-        <v>122.78</v>
+        <v>122.6</v>
       </c>
       <c r="J8" t="n">
-        <v>117.29</v>
+        <v>117.46</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.397568826272234</v>
+        <v>0.04096635</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.76459</v>
+        <v>0.14214</v>
       </c>
       <c r="M8" t="n">
-        <v>587852966.003577</v>
+        <v>588005786.7804404</v>
       </c>
       <c r="N8" t="n">
-        <v>634919033.5810466</v>
+        <v>634996134.9104906</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -1245,13 +1245,13 @@
         <v>45676.13572916666</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R8" t="b">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.04124612971792581</v>
+        <v>0.04101104132138345</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1314,34 +1314,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.335426</v>
+        <v>0.338719</v>
       </c>
       <c r="F9" t="n">
-        <v>31855177757</v>
+        <v>32179982004</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>369670324</v>
+        <v>397692650</v>
       </c>
       <c r="I9" t="n">
-        <v>0.336428</v>
+        <v>0.340711</v>
       </c>
       <c r="J9" t="n">
-        <v>0.332966</v>
+        <v>0.333923</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0020336</v>
+        <v>0.00456806</v>
       </c>
       <c r="L9" t="n">
-        <v>0.63876</v>
+        <v>1.36379</v>
       </c>
       <c r="M9" t="n">
-        <v>94972937401.45468</v>
+        <v>94975594210.46889</v>
       </c>
       <c r="N9" t="n">
-        <v>94973450849.00569</v>
+        <v>94975566451.06459</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1350,13 +1350,13 @@
         <v>45629.67407407407</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01862331833455798</v>
+        <v>0.01875092253099832</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1400,187 +1400,187 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>zcash</t>
+          <t>figure-heloc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>zec</t>
+          <t>figr_heloc</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Zcash</t>
+          <t>Figure Heloc</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1482.49</v>
+        <v>1.03</v>
       </c>
       <c r="F10" t="n">
-        <v>25135097323</v>
+        <v>24032326816</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>1174267473</v>
+        <v>542904134</v>
       </c>
       <c r="I10" t="n">
-        <v>1597.81</v>
+        <v>1.03</v>
       </c>
       <c r="J10" t="n">
-        <v>1449.25</v>
+        <v>1.001</v>
       </c>
       <c r="K10" t="n">
-        <v>-109.1756073353763</v>
+        <v>0.02890712</v>
       </c>
       <c r="L10" t="n">
-        <v>-6.84076</v>
+        <v>2.88499</v>
       </c>
       <c r="M10" t="n">
-        <v>16954918.9155448</v>
+        <v>23338281494.918</v>
       </c>
       <c r="N10" t="n">
-        <v>16957822.0405448</v>
+        <v>23338281494.918</v>
       </c>
       <c r="O10" t="n">
-        <v>3191.93</v>
+        <v>1.062</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>42671.66666666666</v>
+        <v>46292.546875</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01461631982911739</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Privacidad</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Pagos privados</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Proof of Work</t>
-        </is>
-      </c>
-      <c r="W10" t="n">
-        <v>2016</v>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>z.cash</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Transacciones con privacidad opcional</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Layer 1)</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Ofrece transacciones opcionalmente privadas mediante pruebas de conocimiento cero (zk-SNARKs).</t>
-        </is>
-      </c>
+        <v>0.01390790473544563</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>figure-heloc</t>
+          <t>zcash</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>figr_heloc</t>
+          <t>zec</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Figure Heloc</t>
+          <t>Zcash</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.004</v>
+        <v>1412.92</v>
       </c>
       <c r="F11" t="n">
-        <v>23305129622</v>
+        <v>23993997090</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>346887269</v>
+        <v>1070334527</v>
       </c>
       <c r="I11" t="n">
-        <v>1.061</v>
+        <v>1490.56</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>1382.17</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>21.51</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.89807</v>
       </c>
       <c r="M11" t="n">
-        <v>23202972251.118</v>
+        <v>16960081.4155448</v>
       </c>
       <c r="N11" t="n">
-        <v>23202972251.118</v>
+        <v>16960843.9155448</v>
       </c>
       <c r="O11" t="n">
-        <v>1.062</v>
+        <v>3191.93</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>46292.546875</v>
+        <v>42671.66666666666</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R11" t="b">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01352516059152669</v>
-      </c>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
+        <v>0.01388512130379157</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Privacidad</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Pagos privados</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Proof of Work</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>2016</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>z.cash</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Transacciones con privacidad opcional</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Layer 1)</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Ofrece transacciones opcionalmente privadas mediante pruebas de conocimiento cero (zk-SNARKs).</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1599,28 +1599,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>87.42</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>19448324061</v>
+        <v>19102276091</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>945834851</v>
+        <v>856259432</v>
       </c>
       <c r="I12" t="n">
-        <v>92.02</v>
+        <v>87.78</v>
       </c>
       <c r="J12" t="n">
-        <v>86.41</v>
+        <v>84.94</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.268039658764607</v>
+        <v>-0.774846804013734</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.60868</v>
+        <v>-0.77765</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1635,13 +1635,13 @@
         <v>46288.22002314815</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R12" t="b">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01122545387365589</v>
+        <v>0.01097745139111193</v>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
@@ -1655,7 +1655,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1674,34 +1674,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.09386799999999999</v>
+        <v>0.094495</v>
       </c>
       <c r="F13" t="n">
-        <v>14653287577</v>
+        <v>14768716178</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>1169157074</v>
+        <v>1029914116</v>
       </c>
       <c r="I13" t="n">
-        <v>0.097729</v>
+        <v>0.097941</v>
       </c>
       <c r="J13" t="n">
-        <v>0.09178600000000001</v>
+        <v>0.09289799999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.003065646797607444</v>
+        <v>0.00081257</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.10572</v>
+        <v>0.96385</v>
       </c>
       <c r="M13" t="n">
-        <v>156108476383.7052</v>
+        <v>156131006383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>156108686383.7052</v>
+        <v>171843213126.579</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1710,13 +1710,13 @@
         <v>44323.88082175926</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R13" t="b">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.008366305949218835</v>
+        <v>0.008401555959544886</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1779,28 +1779,28 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>15.45</v>
+        <v>14.14</v>
       </c>
       <c r="F14" t="n">
-        <v>11559102076</v>
+        <v>10586902220</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>1380617023</v>
+        <v>604859057</v>
       </c>
       <c r="I14" t="n">
-        <v>15.44</v>
+        <v>14.88</v>
       </c>
       <c r="J14" t="n">
-        <v>13.54</v>
+        <v>14.07</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4</v>
+        <v>-0.6552530784628097</v>
       </c>
       <c r="L14" t="n">
-        <v>10.05567</v>
+        <v>-4.35529</v>
       </c>
       <c r="M14" t="n">
         <v>748099970.424884</v>
@@ -1815,13 +1815,13 @@
         <v>44325.67635416667</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.006521328526726429</v>
+        <v>0.005915859283756131</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1884,34 +1884,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>540.59</v>
+        <v>537.66</v>
       </c>
       <c r="F15" t="n">
-        <v>10167764151</v>
+        <v>10116067900</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>134744544</v>
+        <v>106446294</v>
       </c>
       <c r="I15" t="n">
-        <v>552.95</v>
+        <v>550.1900000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>526.49</v>
+        <v>536.75</v>
       </c>
       <c r="K15" t="n">
-        <v>-7.731023366242312</v>
+        <v>-1.387822398318121</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.42426</v>
+        <v>-0.26448</v>
       </c>
       <c r="M15" t="n">
-        <v>18810763.27902782</v>
+        <v>18811450.26886855</v>
       </c>
       <c r="N15" t="n">
-        <v>18810782.47899366</v>
+        <v>18811489.86840629</v>
       </c>
       <c r="O15" t="n">
         <v>797.73</v>
@@ -1920,13 +1920,13 @@
         <v>46036.48202546296</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.005691712119483614</v>
+        <v>0.005635992384887442</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1989,28 +1989,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>83.55</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>9929723944</v>
+        <v>9931440658</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>140390630</v>
+        <v>125736613</v>
       </c>
       <c r="I16" t="n">
-        <v>84.67</v>
+        <v>85.44</v>
       </c>
       <c r="J16" t="n">
-        <v>82.44</v>
+        <v>82.89</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.7241445535054822</v>
+        <v>0.461985</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.8309800000000001</v>
+        <v>0.65469</v>
       </c>
       <c r="M16" t="n">
         <v>118852171</v>
@@ -2025,13 +2025,13 @@
         <v>46286.85358796296</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R16" t="b">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.005549775313361782</v>
+        <v>0.005526248784070027</v>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
@@ -2045,7 +2045,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2064,34 +2064,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9993880000000001</v>
+        <v>0.99949</v>
       </c>
       <c r="F17" t="n">
-        <v>9780099329</v>
+        <v>9802734613</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>184157283</v>
+        <v>169565227</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0.999263</v>
+        <v>0.999121</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.000242087193309426</v>
+        <v>0.00020221</v>
       </c>
       <c r="L17" t="n">
-        <v>0.04688</v>
+        <v>0.02412</v>
       </c>
       <c r="M17" t="n">
-        <v>9785581101.437241</v>
+        <v>9807716175.04208</v>
       </c>
       <c r="N17" t="n">
-        <v>9785581101.437241</v>
+        <v>9801796986.491272</v>
       </c>
       <c r="O17" t="n">
         <v>1.057</v>
@@ -2100,13 +2100,13 @@
         <v>45593.90336805556</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.005460558284701121</v>
+        <v>0.005449745096573745</v>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
@@ -2120,7 +2120,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2139,28 +2139,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.246928</v>
+        <v>0.243803</v>
       </c>
       <c r="F18" t="n">
-        <v>9267950685</v>
+        <v>9160732353</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>688844092</v>
+        <v>517060573</v>
       </c>
       <c r="I18" t="n">
-        <v>0.257648</v>
+        <v>0.256263</v>
       </c>
       <c r="J18" t="n">
-        <v>0.239932</v>
+        <v>0.240145</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.008754438216891397</v>
+        <v>-0.001614369320090098</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.43806</v>
+        <v>-0.5736</v>
       </c>
       <c r="M18" t="n">
         <v>37535193928.91081</v>
@@ -2175,13 +2175,13 @@
         <v>44440.91678240741</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R18" t="b">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.00515517818230108</v>
+        <v>0.005068134891156074</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.01246908</v>
+        <v>0.01231888</v>
       </c>
       <c r="F19" t="n">
-        <v>8843668256</v>
+        <v>8736612893</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>24550183</v>
+        <v>23995582</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01272728</v>
+        <v>0.01289522</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01243449</v>
+        <v>0.01218467</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.000276699067652026</v>
+        <v>0.00011486</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.10203</v>
+        <v>0.8652</v>
       </c>
       <c r="M19" t="n">
-        <v>709245550890.849</v>
+        <v>709247494967.3281</v>
       </c>
       <c r="N19" t="n">
         <v>1142408526965.963</v>
@@ -2280,13 +2280,13 @@
         <v>46259.82847222222</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R19" t="b">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.004902190279018537</v>
+        <v>0.004816035600645426</v>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
@@ -2300,7 +2300,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2319,28 +2319,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9.01</v>
+        <v>9.02</v>
       </c>
       <c r="F20" t="n">
-        <v>8291891423</v>
+        <v>8301155927</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>514783</v>
+        <v>680856</v>
       </c>
       <c r="I20" t="n">
-        <v>9.09</v>
+        <v>9.1</v>
       </c>
       <c r="J20" t="n">
-        <v>8.99</v>
+        <v>9</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.02435654173043034</v>
+        <v>0.01950777</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.26776</v>
+        <v>0.21646</v>
       </c>
       <c r="M20" t="n">
         <v>919857851.9</v>
@@ -2355,13 +2355,13 @@
         <v>46146.39930555555</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.004573180981156352</v>
+        <v>0.004557197224833764</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2424,31 +2424,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.231172</v>
+        <v>0.221314</v>
       </c>
       <c r="F21" t="n">
-        <v>8093216704</v>
+        <v>7757401322</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>807501121</v>
+        <v>404294489</v>
       </c>
       <c r="I21" t="n">
-        <v>0.234286</v>
+        <v>0.231452</v>
       </c>
       <c r="J21" t="n">
-        <v>0.207092</v>
+        <v>0.219711</v>
       </c>
       <c r="K21" t="n">
-        <v>0.01511079</v>
+        <v>-0.005143103937809923</v>
       </c>
       <c r="L21" t="n">
-        <v>7.12082</v>
+        <v>-2.26628</v>
       </c>
       <c r="M21" t="n">
-        <v>35011603519.11985</v>
+        <v>35021215736.39494</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.69947</v>
@@ -2460,13 +2460,13 @@
         <v>43102.66666666666</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.004454716729140253</v>
+        <v>0.004233986047180192</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2529,34 +2529,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4.81</v>
+        <v>5.19</v>
       </c>
       <c r="F22" t="n">
-        <v>6288156938</v>
+        <v>6790690637</v>
       </c>
       <c r="G22" t="n">
         <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>1391815200</v>
+        <v>1442323555</v>
       </c>
       <c r="I22" t="n">
-        <v>5.41</v>
+        <v>5.44</v>
       </c>
       <c r="J22" t="n">
-        <v>4.68</v>
+        <v>4.77</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5524592487800861</v>
+        <v>0.289286</v>
       </c>
       <c r="L22" t="n">
-        <v>-10.19063</v>
+        <v>6.18059</v>
       </c>
       <c r="M22" t="n">
-        <v>1307555791</v>
+        <v>1307715243</v>
       </c>
       <c r="N22" t="n">
-        <v>1307555814</v>
+        <v>1307715233</v>
       </c>
       <c r="O22" t="n">
         <v>20.44</v>
@@ -2565,13 +2565,13 @@
         <v>44577.59010416667</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R22" t="b">
         <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0.003378409405793571</v>
+        <v>0.003659367099448904</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2634,34 +2634,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>310.25</v>
+        <v>305.08</v>
       </c>
       <c r="F23" t="n">
-        <v>6234765915</v>
+        <v>6135484248</v>
       </c>
       <c r="G23" t="n">
         <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>319374656</v>
+        <v>246978308</v>
       </c>
       <c r="I23" t="n">
-        <v>333.53</v>
+        <v>316.99</v>
       </c>
       <c r="J23" t="n">
-        <v>305.68</v>
+        <v>303.27</v>
       </c>
       <c r="K23" t="n">
-        <v>-22.80743476250382</v>
+        <v>-1.127444650024529</v>
       </c>
       <c r="L23" t="n">
-        <v>-6.83202</v>
+        <v>-0.25638</v>
       </c>
       <c r="M23" t="n">
-        <v>20095728.02165077</v>
+        <v>20096381.14665077</v>
       </c>
       <c r="N23" t="n">
-        <v>20095996.77165077</v>
+        <v>20096731.14665077</v>
       </c>
       <c r="O23" t="n">
         <v>3785.82</v>
@@ -2670,13 +2670,13 @@
         <v>43088.66666666666</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.003346573812236903</v>
+        <v>0.003269908276208529</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2739,34 +2739,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>8.789999999999999</v>
+        <v>8.82</v>
       </c>
       <c r="F24" t="n">
-        <v>5453702214</v>
+        <v>5480193588</v>
       </c>
       <c r="G24" t="n">
         <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>1053902012</v>
+        <v>737869827</v>
       </c>
       <c r="I24" t="n">
-        <v>9.75</v>
+        <v>9.18</v>
       </c>
       <c r="J24" t="n">
-        <v>8.619999999999999</v>
+        <v>8.73</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.8819458893726182</v>
+        <v>-0.01296086369426419</v>
       </c>
       <c r="L24" t="n">
-        <v>-9.08259</v>
+        <v>-0.00944</v>
       </c>
       <c r="M24" t="n">
-        <v>620402422.6104751</v>
+        <v>620330422.6104751</v>
       </c>
       <c r="N24" t="n">
-        <v>887650418.9163101</v>
+        <v>887578418.9163101</v>
       </c>
       <c r="O24" t="n">
         <v>44.92</v>
@@ -2775,13 +2775,13 @@
         <v>44318.89240740741</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.002880847082728399</v>
+        <v>0.002880399361752555</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2844,34 +2844,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>69.23999999999999</v>
+        <v>66.62</v>
       </c>
       <c r="F25" t="n">
-        <v>5375881728</v>
+        <v>5176153106</v>
       </c>
       <c r="G25" t="n">
         <v>24</v>
       </c>
       <c r="H25" t="n">
-        <v>624869305</v>
+        <v>376696142</v>
       </c>
       <c r="I25" t="n">
-        <v>72.37</v>
+        <v>68.2</v>
       </c>
       <c r="J25" t="n">
-        <v>68.67</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.091962717714054</v>
+        <v>-0.855481904872093</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.86092</v>
+        <v>-1.07264</v>
       </c>
       <c r="M25" t="n">
-        <v>77658035.78231663</v>
+        <v>77663917.04941112</v>
       </c>
       <c r="N25" t="n">
-        <v>77658392.03312041</v>
+        <v>77664179.55054182</v>
       </c>
       <c r="O25" t="n">
         <v>410.26</v>
@@ -2880,13 +2880,13 @@
         <v>44325.80077546297</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.002834444874576696</v>
+        <v>0.002699675775528251</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2930,173 +2930,143 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>hedera-hashgraph</t>
+          <t>canton-network</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>hbar</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Hedera</t>
+          <t>Canton</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.121675</v>
+        <v>0.124675</v>
       </c>
       <c r="F26" t="n">
-        <v>5332618809</v>
+        <v>4960665527</v>
       </c>
       <c r="G26" t="n">
         <v>25</v>
       </c>
       <c r="H26" t="n">
-        <v>1504736922</v>
+        <v>27436122</v>
       </c>
       <c r="I26" t="n">
-        <v>0.13063</v>
+        <v>0.12971</v>
       </c>
       <c r="J26" t="n">
-        <v>0.09417200000000001</v>
+        <v>0.122096</v>
       </c>
       <c r="K26" t="n">
-        <v>0.02572026</v>
+        <v>-0.002722972205727689</v>
       </c>
       <c r="L26" t="n">
-        <v>26.78407</v>
+        <v>-1.92594</v>
       </c>
       <c r="M26" t="n">
-        <v>43831706398.00587</v>
+        <v>39727804065.17841</v>
       </c>
       <c r="N26" t="n">
-        <v>50000000000</v>
+        <v>39727804065.17841</v>
       </c>
       <c r="O26" t="n">
-        <v>0.569229</v>
+        <v>0.194152</v>
       </c>
       <c r="P26" s="1" t="n">
-        <v>44454.11143518519</v>
+        <v>46056.00148148148</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.002808648389924977</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Infraestructura empresarial</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>DLT</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Hashgraph (aBFT)</t>
-        </is>
-      </c>
-      <c r="W26" t="n">
-        <v>2019</v>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>hedera.com</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>Aplicaciones empresariales y tokenización</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>Red propia (hashgraph, no blockchain tradicional)</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>Gobernada por un consejo de grandes empresas globales.</t>
-        </is>
-      </c>
+        <v>0.002571588595138657</v>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>canton-network</t>
+          <t>ethena-usde</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>usde</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Canton</t>
+          <t>Ethena USDe</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.130599</v>
+        <v>0.999541</v>
       </c>
       <c r="F27" t="n">
-        <v>5186854556</v>
+        <v>4874072574</v>
       </c>
       <c r="G27" t="n">
         <v>26</v>
       </c>
       <c r="H27" t="n">
-        <v>49511163</v>
+        <v>31499157</v>
       </c>
       <c r="I27" t="n">
-        <v>0.146469</v>
+        <v>0.999991</v>
       </c>
       <c r="J27" t="n">
-        <v>0.126784</v>
+        <v>0.99956</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.00562873057806304</v>
+        <v>-0.00032733957926534</v>
       </c>
       <c r="L27" t="n">
-        <v>-4.15985</v>
+        <v>-0.02938</v>
       </c>
       <c r="M27" t="n">
-        <v>39715601982.75846</v>
+        <v>4876263712.460404</v>
       </c>
       <c r="N27" t="n">
-        <v>39715601982.75846</v>
+        <v>4876272531.866214</v>
       </c>
       <c r="O27" t="n">
-        <v>0.194152</v>
+        <v>1.034</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>46056.00148148148</v>
+        <v>46000.38208333333</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R27" t="b">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.002721733188588614</v>
+        <v>0.002520117195984933</v>
       </c>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
@@ -3110,7 +3080,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3129,34 +3099,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>10.58</v>
+        <v>10.85</v>
       </c>
       <c r="F28" t="n">
-        <v>4970915308</v>
+        <v>4810256839</v>
       </c>
       <c r="G28" t="n">
         <v>27</v>
       </c>
       <c r="H28" t="n">
-        <v>632241115</v>
+        <v>731335490</v>
       </c>
       <c r="I28" t="n">
-        <v>10.97</v>
+        <v>11.54</v>
       </c>
       <c r="J28" t="n">
-        <v>10.15</v>
+        <v>10.83</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.3376764675811188</v>
+        <v>-0.3466362061973349</v>
       </c>
       <c r="L28" t="n">
-        <v>-2.93974</v>
+        <v>-2.95308</v>
       </c>
       <c r="M28" t="n">
-        <v>469757793.2209306</v>
+        <v>443103117.6235452</v>
       </c>
       <c r="N28" t="n">
-        <v>469757977.1927229</v>
+        <v>469771882.6681914</v>
       </c>
       <c r="O28" t="n">
         <v>144.96</v>
@@ -3165,13 +3135,13 @@
         <v>44521.26314814815</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R28" t="b">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.002592974574387484</v>
+        <v>0.002482184719326316</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3215,82 +3185,112 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ethena-usde</t>
+          <t>hedera-hashgraph</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>usde</t>
+          <t>hbar</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ethena USDe</t>
+          <t>Hedera</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.999611</v>
+        <v>0.107844</v>
       </c>
       <c r="F29" t="n">
-        <v>4902804026</v>
+        <v>4730157338</v>
       </c>
       <c r="G29" t="n">
         <v>28</v>
       </c>
       <c r="H29" t="n">
-        <v>38262359</v>
+        <v>432495681</v>
       </c>
       <c r="I29" t="n">
-        <v>0.999934</v>
+        <v>0.112621</v>
       </c>
       <c r="J29" t="n">
-        <v>0.999574</v>
+        <v>0.101164</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.00018926019552612</v>
+        <v>-0.004795633862834575</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.01496</v>
+        <v>-4.00576</v>
       </c>
       <c r="M29" t="n">
-        <v>4904709277.703256</v>
+        <v>43831706393.35206</v>
       </c>
       <c r="N29" t="n">
-        <v>4904709277.703256</v>
+        <v>50000000000</v>
       </c>
       <c r="O29" t="n">
-        <v>1.034</v>
+        <v>0.569229</v>
       </c>
       <c r="P29" s="1" t="n">
-        <v>46000.38208333333</v>
+        <v>44454.11143518519</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R29" t="b">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.002552361696631318</v>
-      </c>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
+        <v>0.002434573069126731</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Infraestructura empresarial</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>DLT</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Hashgraph (aBFT)</t>
+        </is>
+      </c>
+      <c r="W29" t="n">
+        <v>2019</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>hedera.com</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Aplicaciones empresariales y tokenización</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>Red propia (hashgraph, no blockchain tradicional)</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>Gobernada por un consejo de grandes empresas globales.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3309,28 +3309,28 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="F30" t="n">
-        <v>4772225187</v>
+        <v>4715373791</v>
       </c>
       <c r="G30" t="n">
         <v>29</v>
       </c>
       <c r="H30" t="n">
-        <v>1564352652</v>
+        <v>1009981403</v>
       </c>
       <c r="I30" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="J30" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.1093248864460741</v>
+        <v>0.01214087</v>
       </c>
       <c r="L30" t="n">
-        <v>-8.51948</v>
+        <v>1.14789</v>
       </c>
       <c r="M30" t="n">
         <v>4096537146.540959</v>
@@ -3345,13 +3345,13 @@
         <v>45661.62243055556</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.002474501138583841</v>
+        <v>0.002425785635251542</v>
       </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
@@ -3365,7 +3365,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3384,34 +3384,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.999929</v>
       </c>
       <c r="F31" t="n">
-        <v>4603721775</v>
+        <v>4580009438</v>
       </c>
       <c r="G31" t="n">
         <v>30</v>
       </c>
       <c r="H31" t="n">
-        <v>250957765</v>
+        <v>130822210</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>0.999637</v>
+        <v>0.999492</v>
       </c>
       <c r="K31" t="n">
-        <v>0.00023832</v>
+        <v>-2.3966619176696e-05</v>
       </c>
       <c r="L31" t="n">
-        <v>0.02834</v>
+        <v>0.02045</v>
       </c>
       <c r="M31" t="n">
-        <v>4603186689.020486</v>
+        <v>4579844016.246902</v>
       </c>
       <c r="N31" t="n">
-        <v>4662323535.788444</v>
+        <v>4584740080.938172</v>
       </c>
       <c r="O31" t="n">
         <v>1.22</v>
@@ -3420,13 +3420,13 @@
         <v>43902.79363425926</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R31" t="b">
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0.002374027204279495</v>
+        <v>0.002345324207351646</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3470,68 +3470,68 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>the-open-network</t>
+          <t>usd1-wlfi</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>gram</t>
+          <t>usd1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Gram (prev. Toncoin)</t>
+          <t>USD1</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1.57</v>
+        <v>0.999134</v>
       </c>
       <c r="F32" t="n">
-        <v>4421697849</v>
+        <v>4414777148</v>
       </c>
       <c r="G32" t="n">
         <v>31</v>
       </c>
       <c r="H32" t="n">
-        <v>135951517</v>
+        <v>913659539</v>
       </c>
       <c r="I32" t="n">
-        <v>1.72</v>
+        <v>0.999601</v>
       </c>
       <c r="J32" t="n">
-        <v>1.56</v>
+        <v>0.999123</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.05791636793099908</v>
+        <v>-0.000362190700057607</v>
       </c>
       <c r="L32" t="n">
-        <v>-3.51437</v>
+        <v>-0.02925</v>
       </c>
       <c r="M32" t="n">
-        <v>2815376675.777718</v>
+        <v>4418501462.099514</v>
       </c>
       <c r="N32" t="n">
-        <v>5257210699.824263</v>
+        <v>4418501462.099514</v>
       </c>
       <c r="O32" t="n">
-        <v>8.25</v>
+        <v>1.048</v>
       </c>
       <c r="P32" s="1" t="n">
-        <v>45457.69225694444</v>
+        <v>46212.42696759259</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R32" t="b">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.0022654913606092</v>
+        <v>0.00224710908871868</v>
       </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
@@ -3545,143 +3545,173 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>usd1-wlfi</t>
+          <t>quant-network</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>usd1</t>
+          <t>qnt</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>USD1</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.99943</v>
+        <v>297.44</v>
       </c>
       <c r="F33" t="n">
-        <v>4415979237</v>
+        <v>4317342487</v>
       </c>
       <c r="G33" t="n">
         <v>32</v>
       </c>
       <c r="H33" t="n">
-        <v>1100248355</v>
+        <v>985642105</v>
       </c>
       <c r="I33" t="n">
-        <v>0.999614</v>
+        <v>326.12</v>
       </c>
       <c r="J33" t="n">
-        <v>0.9992760000000001</v>
+        <v>243.48</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.6369358830269e-05</v>
+        <v>54.07</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.00066</v>
+        <v>22.46301</v>
       </c>
       <c r="M33" t="n">
-        <v>4418501462.568161</v>
+        <v>14544176.16408117</v>
       </c>
       <c r="N33" t="n">
-        <v>4418501462.568161</v>
+        <v>14612493</v>
       </c>
       <c r="O33" t="n">
-        <v>1.048</v>
+        <v>427.42</v>
       </c>
       <c r="P33" s="1" t="n">
-        <v>46212.42696759259</v>
+        <v>44450.05208333334</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S33" t="n">
-        <v>0.002262081510092939</v>
-      </c>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
+        <v>0.002189193309732152</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Interoperabilidad</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Infraestructura empresarial</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>N/A (token ERC-20)</t>
+        </is>
+      </c>
+      <c r="W33" t="n">
+        <v>2018</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>quant.network</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Interoperabilidad entre redes empresariales</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>Token ERC-20 sobre Ethereum</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>Su tecnología Overledger busca conectar múltiples blockchains y redes existentes.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>bittensor</t>
+          <t>the-open-network</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>tao</t>
+          <t>gram</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Bittensor</t>
+          <t>Gram (prev. Toncoin)</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>307.07</v>
+        <v>1.49</v>
       </c>
       <c r="F34" t="n">
-        <v>3481552392</v>
+        <v>4210336795</v>
       </c>
       <c r="G34" t="n">
         <v>33</v>
       </c>
       <c r="H34" t="n">
-        <v>357267906</v>
+        <v>81426352</v>
       </c>
       <c r="I34" t="n">
-        <v>322.51</v>
+        <v>1.55</v>
       </c>
       <c r="J34" t="n">
-        <v>294.98</v>
+        <v>1.46</v>
       </c>
       <c r="K34" t="n">
-        <v>-12.95459664751877</v>
+        <v>-0.04348900836743064</v>
       </c>
       <c r="L34" t="n">
-        <v>-4.00743</v>
+        <v>-2.7562</v>
       </c>
       <c r="M34" t="n">
-        <v>11339645.9251</v>
+        <v>2816299278.672016</v>
       </c>
       <c r="N34" t="n">
-        <v>21000000</v>
+        <v>5258155567.053657</v>
       </c>
       <c r="O34" t="n">
-        <v>757.6</v>
+        <v>8.25</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>45358.44833333333</v>
+        <v>45457.69225694444</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R34" t="b">
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0.001704908570255092</v>
+        <v>0.002125588449361442</v>
       </c>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
@@ -3695,112 +3725,82 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>crypto-com-chain</t>
+          <t>bittensor</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>cro</t>
+          <t>tao</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cronos</t>
+          <t>Bittensor</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.069276</v>
+        <v>302.2</v>
       </c>
       <c r="F35" t="n">
-        <v>3446526996</v>
+        <v>3430335373</v>
       </c>
       <c r="G35" t="n">
         <v>34</v>
       </c>
       <c r="H35" t="n">
-        <v>26946295</v>
+        <v>259413822</v>
       </c>
       <c r="I35" t="n">
-        <v>0.07027700000000001</v>
+        <v>314.22</v>
       </c>
       <c r="J35" t="n">
-        <v>0.063356</v>
+        <v>297.57</v>
       </c>
       <c r="K35" t="n">
-        <v>0.00250399</v>
+        <v>-5.058560426277154</v>
       </c>
       <c r="L35" t="n">
-        <v>3.77278</v>
+        <v>-1.49067</v>
       </c>
       <c r="M35" t="n">
-        <v>49749850607.73766</v>
+        <v>11339645.9251</v>
       </c>
       <c r="N35" t="n">
-        <v>98949813113.73965</v>
+        <v>21000000</v>
       </c>
       <c r="O35" t="n">
-        <v>0.891544</v>
+        <v>757.6</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>44523.66666666666</v>
+        <v>45358.44833333333</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R35" t="b">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.001684023893233313</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Token de exchange</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Layer 1 (Cronos)</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Proof of Stake</t>
-        </is>
-      </c>
-      <c r="W35" t="n">
-        <v>2018</v>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>cronos.org</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>Pagos y DeFi en el ecosistema Crypto.com</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>Blockchain propia (Cronos, EVM-compatible)</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>Token nativo del ecosistema Crypto.com y su red Cronos.</t>
-        </is>
-      </c>
+        <v>0.001661950668903323</v>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3819,34 +3819,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5.67e-06</v>
+        <v>5.81e-06</v>
       </c>
       <c r="F36" t="n">
-        <v>3342254447</v>
+        <v>3423713852</v>
       </c>
       <c r="G36" t="n">
         <v>35</v>
       </c>
       <c r="H36" t="n">
-        <v>106657770</v>
+        <v>99656029</v>
       </c>
       <c r="I36" t="n">
-        <v>5.97e-06</v>
+        <v>5.99e-06</v>
       </c>
       <c r="J36" t="n">
-        <v>5.57e-06</v>
+        <v>5.68e-06</v>
       </c>
       <c r="K36" t="n">
-        <v>-2.50118412735e-07</v>
+        <v>3.5207e-08</v>
       </c>
       <c r="L36" t="n">
-        <v>-4.21184</v>
+        <v>0.79487</v>
       </c>
       <c r="M36" t="n">
-        <v>589238950007622.8</v>
+        <v>589238865711358.6</v>
       </c>
       <c r="N36" t="n">
-        <v>589496065678280.8</v>
+        <v>589496063978280.8</v>
       </c>
       <c r="O36" t="n">
         <v>8.616e-05</v>
@@ -3855,13 +3855,13 @@
         <v>44496.82980324074</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R36" t="b">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.001621849049925258</v>
+        <v>0.001658014794925267</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3905,68 +3905,68 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>tether-gold</t>
+          <t>bitway</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>xaut</t>
+          <t>btw</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Tether Gold</t>
+          <t>Bitway</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4127.25</v>
+        <v>1.26</v>
       </c>
       <c r="F37" t="n">
-        <v>3338894877</v>
+        <v>3411548605</v>
       </c>
       <c r="G37" t="n">
         <v>36</v>
       </c>
       <c r="H37" t="n">
-        <v>383054420</v>
+        <v>43934083</v>
       </c>
       <c r="I37" t="n">
-        <v>4260.39</v>
+        <v>1.42</v>
       </c>
       <c r="J37" t="n">
-        <v>4117.57</v>
+        <v>1.019</v>
       </c>
       <c r="K37" t="n">
-        <v>-136.2677125750724</v>
+        <v>-0.03823865778750268</v>
       </c>
       <c r="L37" t="n">
-        <v>-3.20662</v>
+        <v>-2.93202</v>
       </c>
       <c r="M37" t="n">
-        <v>808994.63</v>
+        <v>2708142280.000001</v>
       </c>
       <c r="N37" t="n">
-        <v>827417.63</v>
+        <v>10000000000</v>
       </c>
       <c r="O37" t="n">
-        <v>5504.62</v>
+        <v>1.43</v>
       </c>
       <c r="P37" s="1" t="n">
-        <v>46050.66666666666</v>
+        <v>46293.32349537037</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R37" t="b">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.001619845831049958</v>
+        <v>0.001650783695136573</v>
       </c>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
@@ -3980,248 +3980,248 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>quant-network</t>
+          <t>tether-gold</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>qnt</t>
+          <t>xaut</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Tether Gold</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>227.3</v>
+        <v>4159.05</v>
       </c>
       <c r="F38" t="n">
-        <v>3312781707</v>
+        <v>3365227952</v>
       </c>
       <c r="G38" t="n">
         <v>37</v>
       </c>
       <c r="H38" t="n">
-        <v>1150676888</v>
+        <v>198777732</v>
       </c>
       <c r="I38" t="n">
-        <v>318.36</v>
+        <v>4212.71</v>
       </c>
       <c r="J38" t="n">
-        <v>196.87</v>
+        <v>4145.08</v>
       </c>
       <c r="K38" t="n">
-        <v>-60.20917846949141</v>
+        <v>2.74</v>
       </c>
       <c r="L38" t="n">
-        <v>-20.29268</v>
+        <v>0.07914</v>
       </c>
       <c r="M38" t="n">
-        <v>14544176.16408117</v>
+        <v>808994.63</v>
       </c>
       <c r="N38" t="n">
-        <v>14612493</v>
+        <v>827417.63</v>
       </c>
       <c r="O38" t="n">
-        <v>427.42</v>
+        <v>5504.62</v>
       </c>
       <c r="P38" s="1" t="n">
-        <v>44450.05208333334</v>
+        <v>46050.66666666666</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0.001604275268436909</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Interoperabilidad</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Infraestructura empresarial</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>N/A (token ERC-20)</t>
-        </is>
-      </c>
-      <c r="W38" t="n">
-        <v>2018</v>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>quant.network</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>Interoperabilidad entre redes empresariales</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>Token ERC-20 sobre Ethereum</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>Su tecnología Overledger busca conectar múltiples blockchains y redes existentes.</t>
-        </is>
-      </c>
+        <v>0.001623250405913556</v>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>global-dollar</t>
+          <t>crypto-com-chain</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>usdg</t>
+          <t>cro</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Global Dollar</t>
+          <t>Cronos</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>0.067277</v>
       </c>
       <c r="F39" t="n">
-        <v>3245410404</v>
+        <v>3347467665</v>
       </c>
       <c r="G39" t="n">
         <v>38</v>
       </c>
       <c r="H39" t="n">
-        <v>955537659</v>
+        <v>14304510</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0.070004</v>
       </c>
       <c r="J39" t="n">
-        <v>0.999722</v>
+        <v>0.066437</v>
       </c>
       <c r="K39" t="n">
-        <v>0.00011095</v>
+        <v>-0.002321058410480997</v>
       </c>
       <c r="L39" t="n">
-        <v>0.0167</v>
+        <v>-3.30642</v>
       </c>
       <c r="M39" t="n">
-        <v>3245296082.805759</v>
+        <v>49753034759.28843</v>
       </c>
       <c r="N39" t="n">
-        <v>3245296082.805759</v>
+        <v>98953089628.25546</v>
       </c>
       <c r="O39" t="n">
-        <v>1.65</v>
+        <v>0.891544</v>
       </c>
       <c r="P39" s="1" t="n">
-        <v>45686.67436342593</v>
+        <v>44523.66666666666</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>46293.99340277778</v>
+        <v>46295.64189814815</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001564103619736881</v>
-      </c>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr"/>
+        <v>0.001612693578947952</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Token de exchange</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Layer 1 (Cronos)</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Proof of Stake</t>
+        </is>
+      </c>
+      <c r="W39" t="n">
+        <v>2018</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>cronos.org</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>Pagos y DeFi en el ecosistema Crypto.com</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Cronos, EVM-compatible)</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>Token nativo del ecosistema Crypto.com y su red Cronos.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>bitway</t>
+          <t>global-dollar</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>btw</t>
+          <t>usdg</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Bitway</t>
+          <t>Global Dollar</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
  